--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,72 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Argentinian Primera Division</t>
+  </si>
+  <si>
+    <t>Brazilian Serie B</t>
+  </si>
+  <si>
+    <t>Paraguayan Primera Division</t>
+  </si>
+  <si>
+    <t>2026-07-29</t>
+  </si>
+  <si>
+    <t>00:15:00</t>
+  </si>
+  <si>
+    <t>00:35:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Rosario Central</t>
+  </si>
+  <si>
+    <t>Argentinos Juniors</t>
+  </si>
+  <si>
+    <t>Fortaleza EC</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Sportivo Luqueno</t>
+  </si>
+  <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
+    <t>Racing Club</t>
+  </si>
+  <si>
+    <t>Estudiantes Rio Cuarto</t>
+  </si>
+  <si>
+    <t>Botafogo SP</t>
+  </si>
+  <si>
+    <t>Aldosivi</t>
+  </si>
+  <si>
+    <t>Sportivo Trinidense</t>
+  </si>
+  <si>
+    <t>Deportivo Riestra</t>
+  </si>
+  <si>
+    <t>2026-07-27 01:47:59</t>
   </si>
 </sst>
 </file>
@@ -585,7 +651,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +894,1458 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2">
+        <v>2.32</v>
+      </c>
+      <c r="G2">
+        <v>2.54</v>
+      </c>
+      <c r="H2">
+        <v>3.6</v>
+      </c>
+      <c r="I2">
+        <v>4</v>
+      </c>
+      <c r="J2">
+        <v>3</v>
+      </c>
+      <c r="K2">
+        <v>3.25</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.01</v>
+      </c>
+      <c r="N2">
+        <v>2.58</v>
+      </c>
+      <c r="O2">
+        <v>1.51</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.56</v>
+      </c>
+      <c r="R2">
+        <v>1.17</v>
+      </c>
+      <c r="S2">
+        <v>5.1</v>
+      </c>
+      <c r="T2">
+        <v>2.06</v>
+      </c>
+      <c r="U2">
+        <v>1.74</v>
+      </c>
+      <c r="V2">
+        <v>1.33</v>
+      </c>
+      <c r="W2">
+        <v>1.64</v>
+      </c>
+      <c r="X2">
+        <v>9</v>
+      </c>
+      <c r="Y2">
+        <v>1000</v>
+      </c>
+      <c r="Z2">
+        <v>1000</v>
+      </c>
+      <c r="AA2">
+        <v>1000</v>
+      </c>
+      <c r="AB2">
+        <v>1000</v>
+      </c>
+      <c r="AC2">
+        <v>1000</v>
+      </c>
+      <c r="AD2">
+        <v>18</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.08</v>
+      </c>
+      <c r="AQ2">
+        <v>1.22</v>
+      </c>
+      <c r="AR2">
+        <v>1.23</v>
+      </c>
+      <c r="AS2">
+        <v>1.23</v>
+      </c>
+      <c r="AT2">
+        <v>1.22</v>
+      </c>
+      <c r="AU2">
+        <v>1.22</v>
+      </c>
+      <c r="AV2">
+        <v>1.15</v>
+      </c>
+      <c r="AW2">
+        <v>1.2</v>
+      </c>
+      <c r="AX2">
+        <v>1.23</v>
+      </c>
+      <c r="AY2">
+        <v>1.22</v>
+      </c>
+      <c r="AZ2">
+        <v>1.22</v>
+      </c>
+      <c r="BA2">
+        <v>1.23</v>
+      </c>
+      <c r="BB2">
+        <v>1.23</v>
+      </c>
+      <c r="BC2">
+        <v>1.23</v>
+      </c>
+      <c r="BD2">
+        <v>1.23</v>
+      </c>
+      <c r="BE2">
+        <v>1.23</v>
+      </c>
+      <c r="BF2">
+        <v>1.23</v>
+      </c>
+      <c r="BG2">
+        <v>1.23</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.68</v>
+      </c>
+      <c r="BJ2">
+        <v>16</v>
+      </c>
+      <c r="BK2">
+        <v>1.52</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.68</v>
+      </c>
+      <c r="BN2">
+        <v>7</v>
+      </c>
+      <c r="BO2">
+        <v>3.35</v>
+      </c>
+      <c r="BP2">
+        <v>30</v>
+      </c>
+      <c r="BQ2">
+        <v>1.59</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.64</v>
+      </c>
+      <c r="BT2">
+        <v>9.6</v>
+      </c>
+      <c r="BU2">
+        <v>4.3</v>
+      </c>
+      <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>1.62</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.65</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.64</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F3">
+        <v>1.41</v>
+      </c>
+      <c r="G3">
+        <v>1.48</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <v>15.5</v>
+      </c>
+      <c r="J3">
+        <v>4.1</v>
+      </c>
+      <c r="K3">
+        <v>4.6</v>
+      </c>
+      <c r="L3">
+        <v>1.5</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.56</v>
+      </c>
+      <c r="O3">
+        <v>1.48</v>
+      </c>
+      <c r="P3">
+        <v>1.54</v>
+      </c>
+      <c r="Q3">
+        <v>2.48</v>
+      </c>
+      <c r="R3">
+        <v>1.17</v>
+      </c>
+      <c r="S3">
+        <v>4.9</v>
+      </c>
+      <c r="T3">
+        <v>2.72</v>
+      </c>
+      <c r="U3">
+        <v>1.44</v>
+      </c>
+      <c r="V3">
+        <v>1.07</v>
+      </c>
+      <c r="W3">
+        <v>3</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>950</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>5.7</v>
+      </c>
+      <c r="AC3">
+        <v>12</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>12.5</v>
+      </c>
+      <c r="AH3">
+        <v>950</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>13</v>
+      </c>
+      <c r="AK3">
+        <v>24</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>2.06</v>
+      </c>
+      <c r="AQ3">
+        <v>17</v>
+      </c>
+      <c r="AR3">
+        <v>2.06</v>
+      </c>
+      <c r="AS3">
+        <v>2.06</v>
+      </c>
+      <c r="AT3">
+        <v>1.51</v>
+      </c>
+      <c r="AU3">
+        <v>1.76</v>
+      </c>
+      <c r="AV3">
+        <v>2.06</v>
+      </c>
+      <c r="AW3">
+        <v>2.06</v>
+      </c>
+      <c r="AX3">
+        <v>2.06</v>
+      </c>
+      <c r="AY3">
+        <v>1.77</v>
+      </c>
+      <c r="AZ3">
+        <v>1.98</v>
+      </c>
+      <c r="BA3">
+        <v>2.06</v>
+      </c>
+      <c r="BB3">
+        <v>1.78</v>
+      </c>
+      <c r="BC3">
+        <v>1.9</v>
+      </c>
+      <c r="BD3">
+        <v>2.06</v>
+      </c>
+      <c r="BE3">
+        <v>2.06</v>
+      </c>
+      <c r="BF3">
+        <v>2.06</v>
+      </c>
+      <c r="BG3">
+        <v>2.06</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.73</v>
+      </c>
+      <c r="BJ3">
+        <v>23</v>
+      </c>
+      <c r="BK3">
+        <v>1.61</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.73</v>
+      </c>
+      <c r="BN3">
+        <v>4.6</v>
+      </c>
+      <c r="BO3">
+        <v>2.48</v>
+      </c>
+      <c r="BP3">
+        <v>14.5</v>
+      </c>
+      <c r="BQ3">
+        <v>1.55</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.68</v>
+      </c>
+      <c r="BT3">
+        <v>21</v>
+      </c>
+      <c r="BU3">
+        <v>1.6</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.73</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.73</v>
+      </c>
+      <c r="BZ3">
+        <v>38</v>
+      </c>
+      <c r="CA3">
+        <v>1.66</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>97</v>
+      </c>
+      <c r="F4">
+        <v>1.81</v>
+      </c>
+      <c r="G4">
+        <v>1.95</v>
+      </c>
+      <c r="H4">
+        <v>4.8</v>
+      </c>
+      <c r="I4">
+        <v>6.2</v>
+      </c>
+      <c r="J4">
+        <v>3.05</v>
+      </c>
+      <c r="K4">
+        <v>3.75</v>
+      </c>
+      <c r="L4">
+        <v>1.45</v>
+      </c>
+      <c r="M4">
+        <v>1.09</v>
+      </c>
+      <c r="N4">
+        <v>2.78</v>
+      </c>
+      <c r="O4">
+        <v>1.23</v>
+      </c>
+      <c r="P4">
+        <v>1.67</v>
+      </c>
+      <c r="Q4">
+        <v>2.24</v>
+      </c>
+      <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>4.3</v>
+      </c>
+      <c r="T4">
+        <v>2.02</v>
+      </c>
+      <c r="U4">
+        <v>1.76</v>
+      </c>
+      <c r="V4">
+        <v>1.2</v>
+      </c>
+      <c r="W4">
+        <v>2.04</v>
+      </c>
+      <c r="X4">
+        <v>12.5</v>
+      </c>
+      <c r="Y4">
+        <v>1000</v>
+      </c>
+      <c r="Z4">
+        <v>1000</v>
+      </c>
+      <c r="AA4">
+        <v>1000</v>
+      </c>
+      <c r="AB4">
+        <v>8.4</v>
+      </c>
+      <c r="AC4">
+        <v>1000</v>
+      </c>
+      <c r="AD4">
+        <v>1000</v>
+      </c>
+      <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>12.5</v>
+      </c>
+      <c r="AG4">
+        <v>1000</v>
+      </c>
+      <c r="AH4">
+        <v>27</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>55</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>1.34</v>
+      </c>
+      <c r="AQ4">
+        <v>1.5</v>
+      </c>
+      <c r="AR4">
+        <v>1.5</v>
+      </c>
+      <c r="AS4">
+        <v>1.5</v>
+      </c>
+      <c r="AT4">
+        <v>6.2</v>
+      </c>
+      <c r="AU4">
+        <v>1.5</v>
+      </c>
+      <c r="AV4">
+        <v>1.5</v>
+      </c>
+      <c r="AW4">
+        <v>1.5</v>
+      </c>
+      <c r="AX4">
+        <v>1.34</v>
+      </c>
+      <c r="AY4">
+        <v>1.5</v>
+      </c>
+      <c r="AZ4">
+        <v>1.42</v>
+      </c>
+      <c r="BA4">
+        <v>1.5</v>
+      </c>
+      <c r="BB4">
+        <v>1.5</v>
+      </c>
+      <c r="BC4">
+        <v>1.5</v>
+      </c>
+      <c r="BD4">
+        <v>1.46</v>
+      </c>
+      <c r="BE4">
+        <v>1.5</v>
+      </c>
+      <c r="BF4">
+        <v>1.5</v>
+      </c>
+      <c r="BG4">
+        <v>1.5</v>
+      </c>
+      <c r="BH4">
+        <v>1000</v>
+      </c>
+      <c r="BI4">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4">
+        <v>1000</v>
+      </c>
+      <c r="BK4">
+        <v>1.01</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>1000</v>
+      </c>
+      <c r="BO4">
+        <v>1.01</v>
+      </c>
+      <c r="BP4">
+        <v>1000</v>
+      </c>
+      <c r="BQ4">
+        <v>1.01</v>
+      </c>
+      <c r="BR4">
+        <v>1000</v>
+      </c>
+      <c r="BS4">
+        <v>1.01</v>
+      </c>
+      <c r="BT4">
+        <v>1000</v>
+      </c>
+      <c r="BU4">
+        <v>1.01</v>
+      </c>
+      <c r="BV4">
+        <v>1000</v>
+      </c>
+      <c r="BW4">
+        <v>1.01</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4">
+        <v>1000</v>
+      </c>
+      <c r="CA4">
+        <v>1.01</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5">
+        <v>2.32</v>
+      </c>
+      <c r="G5">
+        <v>2.6</v>
+      </c>
+      <c r="H5">
+        <v>3.85</v>
+      </c>
+      <c r="I5">
+        <v>4.5</v>
+      </c>
+      <c r="J5">
+        <v>2.8</v>
+      </c>
+      <c r="K5">
+        <v>2.98</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.36</v>
+      </c>
+      <c r="Q5">
+        <v>3.25</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1.24</v>
+      </c>
+      <c r="Q6">
+        <v>1.01</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7">
+        <v>2.14</v>
+      </c>
+      <c r="G7">
+        <v>2.3</v>
+      </c>
+      <c r="H7">
+        <v>4.2</v>
+      </c>
+      <c r="I7">
+        <v>4.9</v>
+      </c>
+      <c r="J7">
+        <v>2.88</v>
+      </c>
+      <c r="K7">
+        <v>3.15</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.35</v>
+      </c>
+      <c r="Q7">
+        <v>2.92</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -319,7 +319,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 01:47:59</t>
+    <t>2026-07-27 03:55:36</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
         <v>95</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -925,214 +925,214 @@
         <v>4</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="K2">
         <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
         <v>2.58</v>
       </c>
       <c r="O2">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="P2">
         <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
         <v>5.1</v>
       </c>
       <c r="T2">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Y2">
+        <v>12.5</v>
+      </c>
+      <c r="Z2">
+        <v>30</v>
+      </c>
+      <c r="AA2">
+        <v>110</v>
+      </c>
+      <c r="AB2">
         <v>9</v>
       </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>1.08</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>1.22</v>
+        <v>8.6</v>
       </c>
       <c r="AR2">
-        <v>1.23</v>
+        <v>20</v>
       </c>
       <c r="AS2">
-        <v>1.23</v>
+        <v>4.7</v>
       </c>
       <c r="AT2">
-        <v>1.22</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>1.22</v>
+        <v>6</v>
       </c>
       <c r="AV2">
-        <v>1.15</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>1.2</v>
+        <v>4.6</v>
       </c>
       <c r="AX2">
-        <v>1.23</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>1.22</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>1.23</v>
+        <v>4.7</v>
       </c>
       <c r="BB2">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="BC2">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="BD2">
-        <v>1.23</v>
+        <v>4.6</v>
       </c>
       <c r="BE2">
-        <v>1.23</v>
+        <v>4.8</v>
       </c>
       <c r="BF2">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="BG2">
-        <v>1.23</v>
+        <v>4.7</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>1.68</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.52</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.68</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
+        <v>5.2</v>
+      </c>
+      <c r="BO2">
+        <v>3.85</v>
+      </c>
+      <c r="BP2">
+        <v>22</v>
+      </c>
+      <c r="BQ2">
+        <v>7.4</v>
+      </c>
+      <c r="BR2">
+        <v>46</v>
+      </c>
+      <c r="BS2">
+        <v>9</v>
+      </c>
+      <c r="BT2">
         <v>7</v>
       </c>
-      <c r="BO2">
-        <v>3.35</v>
-      </c>
-      <c r="BP2">
-        <v>30</v>
-      </c>
-      <c r="BQ2">
-        <v>1.59</v>
-      </c>
-      <c r="BR2">
-        <v>1000</v>
-      </c>
-      <c r="BS2">
-        <v>1.64</v>
-      </c>
-      <c r="BT2">
-        <v>9.6</v>
-      </c>
       <c r="BU2">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BW2">
-        <v>1.62</v>
+        <v>8.6</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.65</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2">
-        <v>1.64</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,166 +1155,166 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H3">
         <v>11</v>
       </c>
       <c r="I3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
         <v>1.5</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q3">
         <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="T3">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="U3">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="V3">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
         <v>3</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y3">
-        <v>950</v>
+        <v>29</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AJ3">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>590</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>2.06</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AR3">
-        <v>2.06</v>
+        <v>4.5</v>
       </c>
       <c r="AS3">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="AT3">
-        <v>1.51</v>
+        <v>4.7</v>
       </c>
       <c r="AU3">
-        <v>1.76</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="AW3">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="AX3">
-        <v>2.06</v>
+        <v>5.8</v>
       </c>
       <c r="AY3">
-        <v>1.77</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.98</v>
+        <v>4.3</v>
       </c>
       <c r="BA3">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="BB3">
-        <v>1.78</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>1.9</v>
+        <v>19</v>
       </c>
       <c r="BD3">
-        <v>2.06</v>
+        <v>4.4</v>
       </c>
       <c r="BE3">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="BF3">
-        <v>2.06</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG3">
-        <v>2.06</v>
+        <v>4.6</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1397,226 +1397,226 @@
         <v>97</v>
       </c>
       <c r="F4">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="K4">
         <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.23</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
         <v>4.3</v>
       </c>
       <c r="T4">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
         <v>27</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>1.34</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR4">
-        <v>1.5</v>
+        <v>6.4</v>
       </c>
       <c r="AS4">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW4">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
-        <v>1.34</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>1.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>1.42</v>
+        <v>5.6</v>
       </c>
       <c r="BA4">
-        <v>1.5</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>1.5</v>
+        <v>5.6</v>
       </c>
       <c r="BC4">
-        <v>1.5</v>
+        <v>5.8</v>
       </c>
       <c r="BD4">
-        <v>1.46</v>
+        <v>6.4</v>
       </c>
       <c r="BE4">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="BF4">
-        <v>1.5</v>
+        <v>13.5</v>
       </c>
       <c r="BG4">
-        <v>1.5</v>
+        <v>7</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>101</v>
@@ -1639,7 +1639,7 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
         <v>2.6</v>
@@ -1651,10 +1651,10 @@
         <v>4.5</v>
       </c>
       <c r="J5">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="K5">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -2123,22 +2123,22 @@
         <v>100</v>
       </c>
       <c r="F7">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G7">
         <v>2.3</v>
       </c>
       <c r="H7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K7">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2153,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="Q7">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R7">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -319,7 +319,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 03:55:36</t>
+    <t>2026-07-27 06:02:53</t>
   </si>
 </sst>
 </file>
@@ -916,16 +916,16 @@
         <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K2">
         <v>3.25</v>
@@ -937,7 +937,7 @@
         <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O2">
         <v>1.55</v>
@@ -952,7 +952,7 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -961,10 +961,10 @@
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X2">
         <v>8.800000000000001</v>
@@ -979,7 +979,7 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
@@ -991,10 +991,10 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
         <v>28</v>
@@ -1003,19 +1003,19 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK2">
         <v>42</v>
       </c>
       <c r="AL2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM2">
         <v>230</v>
       </c>
       <c r="AN2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -1030,7 +1030,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1042,7 +1042,7 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1054,25 +1054,25 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BD2">
+        <v>4.8</v>
+      </c>
+      <c r="BE2">
+        <v>5.1</v>
+      </c>
+      <c r="BF2">
         <v>4.6</v>
       </c>
-      <c r="BE2">
-        <v>4.8</v>
-      </c>
-      <c r="BF2">
-        <v>4.4</v>
-      </c>
       <c r="BG2">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BH2">
         <v>2.78</v>
@@ -1084,55 +1084,55 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2">
         <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
         <v>22</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
         <v>7</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>101</v>
@@ -1155,7 +1155,7 @@
         <v>96</v>
       </c>
       <c r="F3">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G3">
         <v>1.49</v>
@@ -1170,10 +1170,10 @@
         <v>4.2</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.1</v>
@@ -1254,7 +1254,7 @@
         <v>95</v>
       </c>
       <c r="AM3">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AN3">
         <v>14.5</v>
@@ -1275,7 +1275,7 @@
         <v>4.6</v>
       </c>
       <c r="AT3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU3">
         <v>9.199999999999999</v>
@@ -1415,7 +1415,7 @@
         <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1508,10 +1508,10 @@
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AR4">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AS4">
         <v>7</v>
@@ -1523,7 +1523,7 @@
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AW4">
         <v>6.8</v>
@@ -1535,16 +1535,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BA4">
         <v>6.8</v>
       </c>
       <c r="BB4">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD4">
         <v>6.4</v>
@@ -1639,16 +1639,16 @@
         <v>98</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G5">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H5">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="I5">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
         <v>2.76</v>
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="P5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q5">
         <v>3.25</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,9 @@
     <t>Brazilian Serie B</t>
   </si>
   <si>
+    <t>Canadian Premier League</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -274,6 +277,9 @@
     <t>00:35:00</t>
   </si>
   <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
@@ -292,6 +298,9 @@
     <t>Fortaleza EC</t>
   </si>
   <si>
+    <t>Cavalry</t>
+  </si>
+  <si>
     <t>Barracas Central</t>
   </si>
   <si>
@@ -310,6 +319,9 @@
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>FC Supra du Quebec</t>
+  </si>
+  <si>
     <t>Aldosivi</t>
   </si>
   <si>
@@ -319,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 06:02:53</t>
+    <t>2026-07-27 08:10:19</t>
   </si>
 </sst>
 </file>
@@ -651,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB7"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -901,25 +913,25 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
         <v>4.1</v>
@@ -964,7 +976,7 @@
         <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
         <v>8.800000000000001</v>
@@ -979,10 +991,10 @@
         <v>110</v>
       </c>
       <c r="AB2">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD2">
         <v>17.5</v>
@@ -991,13 +1003,13 @@
         <v>65</v>
       </c>
       <c r="AF2">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI2">
         <v>110</v>
@@ -1030,7 +1042,7 @@
         <v>20</v>
       </c>
       <c r="AS2">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AT2">
         <v>6.4</v>
@@ -1042,7 +1054,7 @@
         <v>14</v>
       </c>
       <c r="AW2">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
@@ -1054,25 +1066,25 @@
         <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB2">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC2">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD2">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BE2">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BF2">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG2">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH2">
         <v>2.78</v>
@@ -1135,7 +1147,7 @@
         <v>9</v>
       </c>
       <c r="CB2" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1143,16 +1155,16 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F3">
         <v>1.41</v>
@@ -1164,34 +1176,34 @@
         <v>11</v>
       </c>
       <c r="I3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
         <v>4.6</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O3">
         <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q3">
         <v>2.48</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
         <v>5.1</v>
@@ -1200,10 +1212,10 @@
         <v>2.74</v>
       </c>
       <c r="U3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="V3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W3">
         <v>3</v>
@@ -1224,10 +1236,10 @@
         <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE3">
         <v>450</v>
@@ -1239,25 +1251,25 @@
         <v>14</v>
       </c>
       <c r="AH3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI3">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AL3">
         <v>95</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="AN3">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1269,10 +1281,10 @@
         <v>20</v>
       </c>
       <c r="AR3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AS3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
@@ -1281,10 +1293,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AW3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
         <v>5.8</v>
@@ -1293,10 +1305,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BA3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
@@ -1305,79 +1317,79 @@
         <v>19</v>
       </c>
       <c r="BD3">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BF3">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BG3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>1.73</v>
+        <v>2.36</v>
       </c>
       <c r="BJ3">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>1.61</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.73</v>
+        <v>10.5</v>
       </c>
       <c r="BN3">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="BO3">
-        <v>2.48</v>
+        <v>2.76</v>
       </c>
       <c r="BP3">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="BQ3">
-        <v>1.55</v>
+        <v>5.3</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.68</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>1.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.73</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.73</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="CA3">
-        <v>1.66</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1385,37 +1397,37 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>1.83</v>
       </c>
       <c r="G4">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
         <v>3.45</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1430,10 +1442,10 @@
         <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.3</v>
@@ -1448,7 +1460,7 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X4">
         <v>11.5</v>
@@ -1472,7 +1484,7 @@
         <v>24</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
@@ -1481,7 +1493,7 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AI4">
         <v>110</v>
@@ -1493,7 +1505,7 @@
         <v>27</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>190</v>
@@ -1523,7 +1535,7 @@
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW4">
         <v>6.8</v>
@@ -1538,13 +1550,13 @@
         <v>6.2</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD4">
         <v>6.4</v>
@@ -1619,284 +1631,284 @@
         <v>10.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:80">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F5">
-        <v>2.4</v>
+        <v>1.04</v>
       </c>
       <c r="G5">
-        <v>2.58</v>
+        <v>990</v>
       </c>
       <c r="H5">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>990</v>
       </c>
       <c r="J5">
-        <v>2.76</v>
+        <v>1.02</v>
       </c>
       <c r="K5">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P5">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="Q5">
-        <v>3.25</v>
+        <v>1.3</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB5" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1911,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2103,249 +2115,491 @@
         <v>0</v>
       </c>
       <c r="CB6" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>1.24</v>
+      </c>
+      <c r="Q7">
+        <v>1.01</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
         <v>80</v>
       </c>
-      <c r="B7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" t="s">
-        <v>100</v>
-      </c>
-      <c r="F7">
-        <v>2.18</v>
-      </c>
-      <c r="G7">
-        <v>2.3</v>
-      </c>
-      <c r="H7">
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" t="s">
+        <v>104</v>
+      </c>
+      <c r="F8">
+        <v>2.2</v>
+      </c>
+      <c r="G8">
+        <v>2.34</v>
+      </c>
+      <c r="H8">
         <v>4.3</v>
       </c>
-      <c r="I7">
+      <c r="I8">
         <v>4.8</v>
       </c>
-      <c r="J7">
-        <v>2.9</v>
-      </c>
-      <c r="K7">
+      <c r="J8">
+        <v>2.88</v>
+      </c>
+      <c r="K8">
         <v>3.1</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>1.43</v>
-      </c>
-      <c r="Q7">
-        <v>3</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
-      <c r="V7">
-        <v>0</v>
-      </c>
-      <c r="W7">
-        <v>0</v>
-      </c>
-      <c r="X7">
-        <v>0</v>
-      </c>
-      <c r="Y7">
-        <v>0</v>
-      </c>
-      <c r="Z7">
-        <v>0</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
-      <c r="AG7">
-        <v>0</v>
-      </c>
-      <c r="AH7">
-        <v>0</v>
-      </c>
-      <c r="AI7">
-        <v>0</v>
-      </c>
-      <c r="AJ7">
-        <v>0</v>
-      </c>
-      <c r="AK7">
-        <v>0</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>0</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>0</v>
-      </c>
-      <c r="BC7">
-        <v>0</v>
-      </c>
-      <c r="BD7">
-        <v>0</v>
-      </c>
-      <c r="BE7">
-        <v>0</v>
-      </c>
-      <c r="BF7">
-        <v>0</v>
-      </c>
-      <c r="BG7">
-        <v>0</v>
-      </c>
-      <c r="BH7">
-        <v>0</v>
-      </c>
-      <c r="BI7">
-        <v>0</v>
-      </c>
-      <c r="BJ7">
-        <v>0</v>
-      </c>
-      <c r="BK7">
-        <v>0</v>
-      </c>
-      <c r="BL7">
-        <v>0</v>
-      </c>
-      <c r="BM7">
-        <v>0</v>
-      </c>
-      <c r="BN7">
-        <v>0</v>
-      </c>
-      <c r="BO7">
-        <v>0</v>
-      </c>
-      <c r="BP7">
-        <v>0</v>
-      </c>
-      <c r="BQ7">
-        <v>0</v>
-      </c>
-      <c r="BR7">
-        <v>0</v>
-      </c>
-      <c r="BS7">
-        <v>0</v>
-      </c>
-      <c r="BT7">
-        <v>0</v>
-      </c>
-      <c r="BU7">
-        <v>0</v>
-      </c>
-      <c r="BV7">
-        <v>0</v>
-      </c>
-      <c r="BW7">
-        <v>0</v>
-      </c>
-      <c r="BX7">
-        <v>0</v>
-      </c>
-      <c r="BY7">
-        <v>0</v>
-      </c>
-      <c r="BZ7">
-        <v>0</v>
-      </c>
-      <c r="CA7">
-        <v>0</v>
-      </c>
-      <c r="CB7" t="s">
-        <v>101</v>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1.41</v>
+      </c>
+      <c r="Q8">
+        <v>3.15</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 08:10:19</t>
+    <t>2026-07-27 08:59:28</t>
   </si>
 </sst>
 </file>
@@ -925,226 +925,226 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>1.45</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>1000</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="J2">
-        <v>2.96</v>
+        <v>1.12</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>1.24</v>
       </c>
       <c r="O2">
-        <v>1.55</v>
+        <v>1.09</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>1.09</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>1.59</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR2">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AS2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AW2">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BC2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BD2">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE2">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG2">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>2.78</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>1.04</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1167,226 +1167,226 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>1.41</v>
+        <v>1.04</v>
       </c>
       <c r="G3">
-        <v>1.49</v>
+        <v>85</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="I3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="K3">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.76</v>
+        <v>2.2</v>
       </c>
       <c r="O3">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="P3">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>2.48</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="S3">
-        <v>5.1</v>
+        <v>1.46</v>
       </c>
       <c r="T3">
-        <v>2.74</v>
+        <v>1.11</v>
       </c>
       <c r="U3">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="V3">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z3">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC3">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE3">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH3">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AI3">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AJ3">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL3">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>560</v>
+        <v>1000</v>
       </c>
       <c r="AN3">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AR3">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT3">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU3">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX3">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BB3">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC3">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD3">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF3">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="BI3">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="BJ3">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN3">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="BO3">
-        <v>2.76</v>
+        <v>1.04</v>
       </c>
       <c r="BP3">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BQ3">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT3">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,226 +1409,226 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="G4">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.05</v>
       </c>
       <c r="K4">
-        <v>3.7</v>
+        <v>500</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>1.39</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>1.39</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>1.6</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.53</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W4">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>1.04</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP4">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1663,7 +1663,7 @@
         <v>990</v>
       </c>
       <c r="J5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K5">
         <v>950</v>
@@ -1675,13 +1675,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="O5">
         <v>1.13</v>
       </c>
       <c r="P5">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="Q5">
         <v>1.3</v>
@@ -1690,7 +1690,7 @@
         <v>1.18</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
         <v>1.11</v>
@@ -1893,22 +1893,22 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>1.5</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J6">
         <v>2.78</v>
       </c>
       <c r="K6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2377,22 +2377,22 @@
         <v>104</v>
       </c>
       <c r="F8">
-        <v>2.2</v>
+        <v>1.42</v>
       </c>
       <c r="G8">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>4.3</v>
+        <v>1.42</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>2.88</v>
+        <v>1.01</v>
       </c>
       <c r="K8">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 08:59:28</t>
+    <t>2026-07-27 11:06:49</t>
   </si>
 </sst>
 </file>
@@ -925,226 +925,226 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>1.45</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>1000</v>
+        <v>2.48</v>
       </c>
       <c r="H2">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="I2">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>1.12</v>
+        <v>3</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M2">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>1.24</v>
+        <v>2.62</v>
       </c>
       <c r="O2">
-        <v>1.09</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>1.09</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
-        <v>1.05</v>
+        <v>5.3</v>
       </c>
       <c r="T2">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.47</v>
+        <v>1.8</v>
       </c>
       <c r="V2">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X2">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB2">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF2">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH2">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AT2">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AV2">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX2">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ2">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD2">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BE2">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF2">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BG2">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>1.04</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK2">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ2">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU2">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>1.04</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2">
-        <v>1.04</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1167,226 +1167,226 @@
         <v>99</v>
       </c>
       <c r="F3">
-        <v>1.04</v>
+        <v>1.43</v>
       </c>
       <c r="G3">
-        <v>85</v>
+        <v>1.46</v>
       </c>
       <c r="H3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="J3">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="K3">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="O3">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q3">
-        <v>1.46</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>1.46</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
-        <v>1.11</v>
+        <v>2.76</v>
       </c>
       <c r="U3">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="V3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AF3">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG3">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AJ3">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AN3">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR3">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AU3">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AW3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX3">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB3">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC3">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD3">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF3">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BG3">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>1.04</v>
+        <v>2.74</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ3">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>1.04</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA3">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,226 +1409,226 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="J4">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
-        <v>500</v>
+        <v>3.8</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>1.39</v>
+        <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S4">
-        <v>1.39</v>
+        <v>4.3</v>
       </c>
       <c r="T4">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
-        <v>1.53</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="X4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA4">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE4">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG4">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH4">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK4">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL4">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ4">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU4">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX4">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB4">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC4">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE4">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BF4">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG4">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK4">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>1.04</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>1.04</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>1.04</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1651,226 +1651,226 @@
         <v>101</v>
       </c>
       <c r="F5">
-        <v>1.04</v>
+        <v>1.52</v>
       </c>
       <c r="G5">
-        <v>990</v>
+        <v>1.68</v>
       </c>
       <c r="H5">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="I5">
-        <v>990</v>
+        <v>6.8</v>
       </c>
       <c r="J5">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="K5">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>1.26</v>
+        <v>2.16</v>
       </c>
       <c r="Q5">
-        <v>1.3</v>
+        <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>2.24</v>
       </c>
       <c r="T5">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U5">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO5">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BQ5">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS5">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA5">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="s">
         <v>105</v>
@@ -1893,19 +1893,19 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="H6">
-        <v>1.5</v>
+        <v>3.7</v>
       </c>
       <c r="I6">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J6">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="K6">
         <v>3</v>
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Q6">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2377,22 +2377,22 @@
         <v>104</v>
       </c>
       <c r="F8">
-        <v>1.42</v>
+        <v>2.16</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.32</v>
       </c>
       <c r="H8">
-        <v>1.42</v>
+        <v>4.2</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J8">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="K8">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="R8">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 11:06:49</t>
+    <t>2026-07-27 13:13:42</t>
   </si>
 </sst>
 </file>
@@ -925,73 +925,73 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="H2">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.56</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2">
         <v>100</v>
       </c>
       <c r="AB2">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC2">
         <v>7.4</v>
@@ -1003,10 +1003,10 @@
         <v>75</v>
       </c>
       <c r="AF2">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>25</v>
@@ -1015,19 +1015,19 @@
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -1036,55 +1036,55 @@
         <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>38</v>
+      </c>
+      <c r="BB2">
         <v>19.5</v>
       </c>
-      <c r="BA2">
-        <v>7</v>
-      </c>
-      <c r="BB2">
-        <v>6.4</v>
-      </c>
       <c r="BC2">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD2">
-        <v>6.8</v>
+        <v>32</v>
       </c>
       <c r="BE2">
-        <v>7.4</v>
+        <v>48</v>
       </c>
       <c r="BF2">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BG2">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BH2">
         <v>2.78</v>
@@ -1096,22 +1096,22 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>8.4</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BP2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
         <v>7.2</v>
@@ -1120,31 +1120,31 @@
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV2">
         <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
+        <v>9.6</v>
+      </c>
+      <c r="BZ2">
+        <v>50</v>
+      </c>
+      <c r="CA2">
         <v>9.199999999999999</v>
-      </c>
-      <c r="BZ2">
-        <v>55</v>
-      </c>
-      <c r="CA2">
-        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,91 +1170,91 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K3">
         <v>4.7</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="O3">
         <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S3">
         <v>4.9</v>
       </c>
       <c r="T3">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="V3">
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="X3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Z3">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC3">
         <v>12</v>
       </c>
       <c r="AD3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AE3">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="AF3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH3">
         <v>60</v>
       </c>
       <c r="AI3">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
@@ -1266,10 +1266,10 @@
         <v>100</v>
       </c>
       <c r="AM3">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1281,52 +1281,52 @@
         <v>21</v>
       </c>
       <c r="AR3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AS3">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AW3">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="AX3">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AZ3">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BA3">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BB3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
         <v>18</v>
       </c>
       <c r="BD3">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="BE3">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BF3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="BH3">
         <v>2.98</v>
@@ -1412,7 +1412,7 @@
         <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -1424,10 +1424,10 @@
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1439,7 +1439,7 @@
         <v>1.43</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
         <v>2.26</v>
@@ -1463,10 +1463,10 @@
         <v>2.1</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="Z4">
         <v>46</v>
@@ -1478,7 +1478,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD4">
         <v>24</v>
@@ -1502,7 +1502,7 @@
         <v>25</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL4">
         <v>55</v>
@@ -1511,22 +1511,22 @@
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP4">
         <v>10</v>
       </c>
       <c r="AQ4">
-        <v>4.7</v>
+        <v>13</v>
       </c>
       <c r="AR4">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="AS4">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1535,10 +1535,10 @@
         <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW4">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="AX4">
         <v>9.199999999999999</v>
@@ -1547,28 +1547,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BA4">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="BB4">
+        <v>16</v>
+      </c>
+      <c r="BC4">
+        <v>4.8</v>
+      </c>
+      <c r="BD4">
         <v>5.4</v>
       </c>
-      <c r="BC4">
-        <v>5.3</v>
-      </c>
-      <c r="BD4">
-        <v>6.2</v>
-      </c>
       <c r="BE4">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF4">
         <v>13</v>
       </c>
       <c r="BG4">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
@@ -1580,19 +1580,19 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>3.4</v>
+        <v>16</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
         <v>14</v>
@@ -1610,7 +1610,7 @@
         <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1651,10 +1651,10 @@
         <v>101</v>
       </c>
       <c r="F5">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G5">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="H5">
         <v>4.5</v>
@@ -1663,13 +1663,13 @@
         <v>6.8</v>
       </c>
       <c r="J5">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="M5">
         <v>1.01</v>
@@ -1681,25 +1681,25 @@
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="Q5">
         <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="S5">
         <v>2.24</v>
       </c>
       <c r="T5">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W5">
         <v>2.44</v>
@@ -1708,55 +1708,55 @@
         <v>32</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z5">
         <v>65</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB5">
         <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD5">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE5">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI5">
         <v>75</v>
       </c>
       <c r="AJ5">
+        <v>19.5</v>
+      </c>
+      <c r="AK5">
         <v>19</v>
-      </c>
-      <c r="AK5">
-        <v>18.5</v>
       </c>
       <c r="AL5">
         <v>34</v>
       </c>
       <c r="AM5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP5">
         <v>3.75</v>
@@ -1765,16 +1765,16 @@
         <v>3.75</v>
       </c>
       <c r="AR5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AS5">
         <v>4.1</v>
       </c>
       <c r="AT5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AV5">
         <v>3.7</v>
@@ -1783,7 +1783,7 @@
         <v>4</v>
       </c>
       <c r="AX5">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AY5">
         <v>3.15</v>
@@ -1795,7 +1795,7 @@
         <v>4</v>
       </c>
       <c r="BB5">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BC5">
         <v>3.45</v>
@@ -1807,7 +1807,7 @@
         <v>4</v>
       </c>
       <c r="BF5">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BG5">
         <v>4</v>
@@ -1837,28 +1837,28 @@
         <v>3.15</v>
       </c>
       <c r="BP5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1867,7 +1867,7 @@
         <v>8</v>
       </c>
       <c r="BZ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="CA5">
         <v>5.7</v>
@@ -1926,7 +1926,7 @@
         <v>1.36</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -2389,7 +2389,7 @@
         <v>4.7</v>
       </c>
       <c r="J8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K8">
         <v>3.2</v>
@@ -2407,10 +2407,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q8">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R8">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 13:13:42</t>
+    <t>2026-07-27 15:21:31</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -940,7 +940,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
         <v>1.48</v>
@@ -949,28 +949,28 @@
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
         <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
         <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="V2">
         <v>1.33</v>
@@ -988,7 +988,7 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
         <v>7.2</v>
@@ -1015,7 +1015,7 @@
         <v>100</v>
       </c>
       <c r="AJ2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AK2">
         <v>38</v>
@@ -1036,7 +1036,7 @@
         <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
         <v>21</v>
@@ -1096,7 +1096,7 @@
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>8.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1170,19 +1170,19 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I3">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>4.1</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
         <v>1.43</v>
@@ -1197,10 +1197,10 @@
         <v>1.5</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q3">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
         <v>1.2</v>
@@ -1275,10 +1275,10 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR3">
         <v>4.5</v>
@@ -1290,7 +1290,7 @@
         <v>4.8</v>
       </c>
       <c r="AU3">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV3">
         <v>4.3</v>
@@ -1412,10 +1412,10 @@
         <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
         <v>5.5</v>
@@ -1445,7 +1445,7 @@
         <v>2.26</v>
       </c>
       <c r="R4">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.3</v>
@@ -1460,13 +1460,13 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Z4">
         <v>46</v>
@@ -1481,7 +1481,7 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1499,7 +1499,7 @@
         <v>110</v>
       </c>
       <c r="AJ4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK4">
         <v>26</v>
@@ -1511,7 +1511,7 @@
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AO4">
         <v>150</v>
@@ -1523,10 +1523,10 @@
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS4">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1538,7 +1538,7 @@
         <v>16</v>
       </c>
       <c r="AW4">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX4">
         <v>9.199999999999999</v>
@@ -1547,34 +1547,34 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BA4">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB4">
         <v>16</v>
       </c>
       <c r="BC4">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD4">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE4">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF4">
         <v>13</v>
       </c>
       <c r="BG4">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1586,28 +1586,28 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
         <v>14</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU4">
         <v>6.6</v>
@@ -1616,19 +1616,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
+        <v>12.5</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
         <v>13</v>
       </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>13.5</v>
-      </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1651,226 +1651,226 @@
         <v>101</v>
       </c>
       <c r="F5">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="G5">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="H5">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="I5">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="L5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M5">
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="T5">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="U5">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.44</v>
+        <v>2.74</v>
       </c>
       <c r="X5">
+        <v>34</v>
+      </c>
+      <c r="Y5">
+        <v>38</v>
+      </c>
+      <c r="Z5">
+        <v>80</v>
+      </c>
+      <c r="AA5">
+        <v>220</v>
+      </c>
+      <c r="AB5">
+        <v>14</v>
+      </c>
+      <c r="AC5">
+        <v>14.5</v>
+      </c>
+      <c r="AD5">
         <v>32</v>
       </c>
-      <c r="Y5">
-        <v>32</v>
-      </c>
-      <c r="Z5">
-        <v>65</v>
-      </c>
-      <c r="AA5">
-        <v>170</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
+      <c r="AE5">
+        <v>110</v>
+      </c>
+      <c r="AF5">
         <v>13.5</v>
-      </c>
-      <c r="AD5">
-        <v>28</v>
-      </c>
-      <c r="AE5">
-        <v>80</v>
-      </c>
-      <c r="AF5">
-        <v>14.5</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AK5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AP5">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AR5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
         <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AV5">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AW5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AX5">
         <v>3.3</v>
       </c>
       <c r="AY5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BA5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
+        <v>3.45</v>
+      </c>
+      <c r="BC5">
         <v>3.5</v>
       </c>
-      <c r="BC5">
-        <v>3.45</v>
-      </c>
       <c r="BD5">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BE5">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>2.76</v>
+        <v>2.62</v>
       </c>
       <c r="BG5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH5">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BI5">
         <v>3.1</v>
       </c>
       <c r="BJ5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN5">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="BP5">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5">
+        <v>4.6</v>
+      </c>
+      <c r="BR5">
+        <v>21</v>
+      </c>
+      <c r="BS5">
+        <v>6.2</v>
+      </c>
+      <c r="BT5">
+        <v>11.5</v>
+      </c>
+      <c r="BU5">
         <v>5</v>
       </c>
-      <c r="BR5">
-        <v>22</v>
-      </c>
-      <c r="BS5">
-        <v>6.6</v>
-      </c>
-      <c r="BT5">
-        <v>10</v>
-      </c>
-      <c r="BU5">
-        <v>4.9</v>
-      </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CA5">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="CB5" t="s">
         <v>105</v>
@@ -1896,7 +1896,7 @@
         <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
         <v>3.7</v>
@@ -1908,211 +1908,211 @@
         <v>2.8</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="P6">
         <v>1.36</v>
       </c>
       <c r="Q6">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
         <v>105</v>
@@ -2380,16 +2380,16 @@
         <v>2.16</v>
       </c>
       <c r="G8">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="H8">
         <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J8">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>3.2</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 15:21:31</t>
+    <t>2026-07-27 17:28:26</t>
   </si>
 </sst>
 </file>
@@ -925,7 +925,7 @@
         <v>98</v>
       </c>
       <c r="F2">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G2">
         <v>2.4</v>
@@ -940,7 +940,7 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
         <v>1.48</v>
@@ -949,7 +949,7 @@
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O2">
         <v>1.56</v>
@@ -1069,10 +1069,10 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD2">
         <v>32</v>
@@ -1108,7 +1108,7 @@
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BP2">
         <v>21</v>
@@ -1129,7 +1129,7 @@
         <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW2">
         <v>8.800000000000001</v>
@@ -1138,13 +1138,13 @@
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
         <v>105</v>
@@ -1170,7 +1170,7 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H3">
         <v>11</v>
@@ -1188,7 +1188,7 @@
         <v>1.43</v>
       </c>
       <c r="M3">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N3">
         <v>2.74</v>
@@ -1206,7 +1206,7 @@
         <v>1.2</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T3">
         <v>2.82</v>
@@ -1227,7 +1227,7 @@
         <v>26</v>
       </c>
       <c r="Z3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1242,7 +1242,7 @@
         <v>65</v>
       </c>
       <c r="AE3">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="AF3">
         <v>8</v>
@@ -1266,7 +1266,7 @@
         <v>100</v>
       </c>
       <c r="AM3">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AN3">
         <v>14</v>
@@ -1293,7 +1293,7 @@
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW3">
         <v>4.6</v>
@@ -1412,10 +1412,10 @@
         <v>1.82</v>
       </c>
       <c r="G4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>5.5</v>
@@ -1424,10 +1424,10 @@
         <v>3.6</v>
       </c>
       <c r="K4">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L4">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="M4">
         <v>1.09</v>
@@ -1460,7 +1460,7 @@
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1481,7 +1481,7 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE4">
         <v>100</v>
@@ -1523,10 +1523,10 @@
         <v>13</v>
       </c>
       <c r="AR4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AS4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT4">
         <v>6.4</v>
@@ -1538,7 +1538,7 @@
         <v>16</v>
       </c>
       <c r="AW4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX4">
         <v>9.199999999999999</v>
@@ -1547,28 +1547,28 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BA4">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB4">
         <v>16</v>
       </c>
       <c r="BC4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BD4">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF4">
         <v>13</v>
       </c>
       <c r="BG4">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
@@ -1666,7 +1666,7 @@
         <v>4.1</v>
       </c>
       <c r="K5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="L5">
         <v>1.23</v>
@@ -1675,13 +1675,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="O5">
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="Q5">
         <v>1.51</v>
@@ -1693,13 +1693,13 @@
         <v>2.22</v>
       </c>
       <c r="T5">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
         <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
         <v>2.74</v>
@@ -1732,13 +1732,13 @@
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH5">
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
         <v>17</v>
@@ -1747,7 +1747,7 @@
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5">
         <v>110</v>
@@ -1756,7 +1756,7 @@
         <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP5">
         <v>3.85</v>
@@ -1786,7 +1786,7 @@
         <v>3.3</v>
       </c>
       <c r="AY5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ5">
         <v>3.7</v>
@@ -1801,7 +1801,7 @@
         <v>3.5</v>
       </c>
       <c r="BD5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BE5">
         <v>4.2</v>
@@ -1831,7 +1831,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
         <v>3</v>
@@ -1840,7 +1840,7 @@
         <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BR5">
         <v>21</v>
@@ -1867,10 +1867,10 @@
         <v>7.6</v>
       </c>
       <c r="BZ5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB5" t="s">
         <v>105</v>
@@ -1893,13 +1893,13 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G6">
         <v>2.6</v>
       </c>
       <c r="H6">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I6">
         <v>4.3</v>
@@ -1908,13 +1908,13 @@
         <v>2.8</v>
       </c>
       <c r="K6">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L6">
         <v>1.68</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
         <v>2</v>
@@ -1923,7 +1923,7 @@
         <v>1.71</v>
       </c>
       <c r="P6">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q6">
         <v>3.3</v>
@@ -1935,7 +1935,7 @@
         <v>5.7</v>
       </c>
       <c r="T6">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U6">
         <v>1.48</v>
@@ -1947,7 +1947,7 @@
         <v>1.62</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y6">
         <v>10.5</v>
@@ -1977,7 +1977,7 @@
         <v>16.5</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="AI6">
         <v>1000</v>
@@ -2010,10 +2010,10 @@
         <v>17</v>
       </c>
       <c r="AS6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="AT6">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="AU6">
         <v>6</v>
@@ -2022,55 +2022,55 @@
         <v>14</v>
       </c>
       <c r="AW6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="AX6">
         <v>9.800000000000001</v>
       </c>
       <c r="AY6">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="AZ6">
-        <v>2.34</v>
+        <v>3.3</v>
       </c>
       <c r="BA6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BB6">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="BC6">
-        <v>2.38</v>
+        <v>3.4</v>
       </c>
       <c r="BD6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BE6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BF6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BG6">
-        <v>2.5</v>
+        <v>3.65</v>
       </c>
       <c r="BH6">
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BJ6">
         <v>19</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BN6">
         <v>7</v>
@@ -2082,13 +2082,13 @@
         <v>36</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BT6">
         <v>10</v>
@@ -2100,19 +2100,19 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="CB6" t="s">
         <v>105</v>
@@ -2153,16 +2153,16 @@
         <v>0</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P7">
         <v>1.24</v>
@@ -2171,184 +2171,184 @@
         <v>1.01</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2377,10 +2377,10 @@
         <v>104</v>
       </c>
       <c r="F8">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H8">
         <v>4.2</v>
@@ -2389,214 +2389,214 @@
         <v>4.6</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K8">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="P8">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 17:28:26</t>
+    <t>2026-07-27 19:35:21</t>
   </si>
 </sst>
 </file>
@@ -943,16 +943,16 @@
         <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P2">
         <v>1.53</v>
@@ -1027,7 +1027,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AO2">
         <v>110</v>
@@ -1087,16 +1087,16 @@
         <v>36</v>
       </c>
       <c r="BH2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1117,10 +1117,10 @@
         <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS2">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
         <v>7.2</v>
@@ -1129,10 +1129,10 @@
         <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BX2">
         <v>65</v>
@@ -1170,7 +1170,7 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="H3">
         <v>11</v>
@@ -1185,7 +1185,7 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
         <v>1.11</v>
@@ -1218,7 +1218,7 @@
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X3">
         <v>12</v>
@@ -1251,10 +1251,10 @@
         <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AI3">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
@@ -1281,7 +1281,7 @@
         <v>19.5</v>
       </c>
       <c r="AR3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS3">
         <v>4.7</v>
@@ -1296,7 +1296,7 @@
         <v>4.4</v>
       </c>
       <c r="AW3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AX3">
         <v>5.9</v>
@@ -1308,7 +1308,7 @@
         <v>4.3</v>
       </c>
       <c r="BA3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
@@ -1320,7 +1320,7 @@
         <v>4.5</v>
       </c>
       <c r="BE3">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF3">
         <v>9.800000000000001</v>
@@ -1329,7 +1329,7 @@
         <v>4.7</v>
       </c>
       <c r="BH3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI3">
         <v>2.38</v>
@@ -1338,55 +1338,55 @@
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BP3">
         <v>10</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
         <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>27</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1409,82 +1409,82 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="G4">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="H4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I4">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
+        <v>3.45</v>
+      </c>
+      <c r="K4">
         <v>3.6</v>
-      </c>
-      <c r="K4">
-        <v>3.7</v>
       </c>
       <c r="L4">
         <v>1.49</v>
       </c>
       <c r="M4">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4">
         <v>3.05</v>
       </c>
       <c r="O4">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="X4">
+        <v>12.5</v>
+      </c>
+      <c r="Y4">
         <v>13.5</v>
       </c>
-      <c r="Y4">
-        <v>15.5</v>
-      </c>
       <c r="Z4">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AB4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AE4">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AF4">
         <v>12</v>
@@ -1493,10 +1493,10 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
         <v>24</v>
@@ -1508,28 +1508,28 @@
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN4">
         <v>19.5</v>
       </c>
       <c r="AO4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AP4">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR4">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
@@ -1538,43 +1538,43 @@
         <v>16</v>
       </c>
       <c r="AW4">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AY4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA4">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC4">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BD4">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG4">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1586,28 +1586,28 @@
         <v>1000</v>
       </c>
       <c r="BM4">
+        <v>15.5</v>
+      </c>
+      <c r="BN4">
+        <v>4.4</v>
+      </c>
+      <c r="BO4">
+        <v>3.9</v>
+      </c>
+      <c r="BP4">
         <v>14.5</v>
       </c>
-      <c r="BN4">
-        <v>4.3</v>
-      </c>
-      <c r="BO4">
-        <v>3.85</v>
-      </c>
-      <c r="BP4">
-        <v>14</v>
-      </c>
       <c r="BQ4">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
         <v>6.6</v>
@@ -1622,13 +1622,13 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1660,10 +1660,10 @@
         <v>5.3</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K5">
         <v>5.8</v>
@@ -1681,7 +1681,7 @@
         <v>1.17</v>
       </c>
       <c r="P5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="Q5">
         <v>1.51</v>
@@ -1690,7 +1690,7 @@
         <v>1.52</v>
       </c>
       <c r="S5">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="T5">
         <v>1.69</v>
@@ -1893,7 +1893,7 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
         <v>2.6</v>
@@ -1917,13 +1917,13 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="O6">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="P6">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
         <v>3.3</v>
@@ -1932,7 +1932,7 @@
         <v>1.12</v>
       </c>
       <c r="S6">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="T6">
         <v>2.26</v>
@@ -1947,112 +1947,112 @@
         <v>1.62</v>
       </c>
       <c r="X6">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z6">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB6">
+        <v>6.6</v>
+      </c>
+      <c r="AC6">
         <v>7.6</v>
       </c>
-      <c r="AC6">
+      <c r="AD6">
+        <v>20</v>
+      </c>
+      <c r="AE6">
+        <v>110</v>
+      </c>
+      <c r="AF6">
+        <v>14.5</v>
+      </c>
+      <c r="AG6">
+        <v>14.5</v>
+      </c>
+      <c r="AH6">
+        <v>38</v>
+      </c>
+      <c r="AI6">
+        <v>160</v>
+      </c>
+      <c r="AJ6">
+        <v>44</v>
+      </c>
+      <c r="AK6">
+        <v>48</v>
+      </c>
+      <c r="AL6">
+        <v>120</v>
+      </c>
+      <c r="AM6">
+        <v>420</v>
+      </c>
+      <c r="AN6">
+        <v>60</v>
+      </c>
+      <c r="AO6">
+        <v>190</v>
+      </c>
+      <c r="AP6">
+        <v>5.8</v>
+      </c>
+      <c r="AQ6">
+        <v>7.6</v>
+      </c>
+      <c r="AR6">
+        <v>21</v>
+      </c>
+      <c r="AS6">
+        <v>8.4</v>
+      </c>
+      <c r="AT6">
+        <v>5.6</v>
+      </c>
+      <c r="AU6">
+        <v>6.2</v>
+      </c>
+      <c r="AV6">
+        <v>16</v>
+      </c>
+      <c r="AW6">
+        <v>8.4</v>
+      </c>
+      <c r="AX6">
+        <v>11.5</v>
+      </c>
+      <c r="AY6">
+        <v>11.5</v>
+      </c>
+      <c r="AZ6">
+        <v>7</v>
+      </c>
+      <c r="BA6">
+        <v>8.6</v>
+      </c>
+      <c r="BB6">
+        <v>34</v>
+      </c>
+      <c r="BC6">
+        <v>34</v>
+      </c>
+      <c r="BD6">
+        <v>8.4</v>
+      </c>
+      <c r="BE6">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD6">
-        <v>24</v>
-      </c>
-      <c r="AE6">
-        <v>1000</v>
-      </c>
-      <c r="AF6">
-        <v>16.5</v>
-      </c>
-      <c r="AG6">
-        <v>16.5</v>
-      </c>
-      <c r="AH6">
-        <v>950</v>
-      </c>
-      <c r="AI6">
-        <v>1000</v>
-      </c>
-      <c r="AJ6">
-        <v>50</v>
-      </c>
-      <c r="AK6">
-        <v>55</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>1000</v>
-      </c>
-      <c r="AP6">
-        <v>2.5</v>
-      </c>
-      <c r="AQ6">
-        <v>7.2</v>
-      </c>
-      <c r="AR6">
-        <v>17</v>
-      </c>
-      <c r="AS6">
-        <v>3.65</v>
-      </c>
-      <c r="AT6">
-        <v>2.46</v>
-      </c>
-      <c r="AU6">
-        <v>6</v>
-      </c>
-      <c r="AV6">
-        <v>14</v>
-      </c>
-      <c r="AW6">
-        <v>3.65</v>
-      </c>
-      <c r="AX6">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY6">
-        <v>2.98</v>
-      </c>
-      <c r="AZ6">
-        <v>3.3</v>
-      </c>
-      <c r="BA6">
-        <v>3.65</v>
-      </c>
-      <c r="BB6">
-        <v>3.4</v>
-      </c>
-      <c r="BC6">
-        <v>3.4</v>
-      </c>
-      <c r="BD6">
-        <v>3.65</v>
-      </c>
-      <c r="BE6">
-        <v>3.65</v>
-      </c>
       <c r="BF6">
-        <v>3.65</v>
+        <v>40</v>
       </c>
       <c r="BG6">
-        <v>3.65</v>
+        <v>8.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2094,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2380,31 +2380,31 @@
         <v>2.18</v>
       </c>
       <c r="G8">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="H8">
         <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J8">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K8">
         <v>3.1</v>
       </c>
       <c r="L8">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N8">
         <v>2.28</v>
       </c>
       <c r="O8">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="P8">
         <v>1.4</v>
@@ -2413,148 +2413,148 @@
         <v>3.15</v>
       </c>
       <c r="R8">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S8">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="V8">
         <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB8">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC8">
+        <v>7.2</v>
+      </c>
+      <c r="AD8">
+        <v>22</v>
+      </c>
+      <c r="AE8">
+        <v>110</v>
+      </c>
+      <c r="AF8">
+        <v>13</v>
+      </c>
+      <c r="AG8">
+        <v>15.5</v>
+      </c>
+      <c r="AH8">
+        <v>38</v>
+      </c>
+      <c r="AI8">
+        <v>150</v>
+      </c>
+      <c r="AJ8">
+        <v>40</v>
+      </c>
+      <c r="AK8">
+        <v>44</v>
+      </c>
+      <c r="AL8">
+        <v>85</v>
+      </c>
+      <c r="AM8">
+        <v>350</v>
+      </c>
+      <c r="AN8">
+        <v>48</v>
+      </c>
+      <c r="AO8">
+        <v>200</v>
+      </c>
+      <c r="AP8">
+        <v>6.6</v>
+      </c>
+      <c r="AQ8">
+        <v>8.6</v>
+      </c>
+      <c r="AR8">
+        <v>7.2</v>
+      </c>
+      <c r="AS8">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT8">
+        <v>5.5</v>
+      </c>
+      <c r="AU8">
+        <v>6.4</v>
+      </c>
+      <c r="AV8">
+        <v>19</v>
+      </c>
+      <c r="AW8">
+        <v>8.6</v>
+      </c>
+      <c r="AX8">
+        <v>10</v>
+      </c>
+      <c r="AY8">
+        <v>11.5</v>
+      </c>
+      <c r="AZ8">
         <v>7.4</v>
       </c>
-      <c r="AD8">
-        <v>1000</v>
-      </c>
-      <c r="AE8">
-        <v>1000</v>
-      </c>
-      <c r="AF8">
-        <v>1000</v>
-      </c>
-      <c r="AG8">
-        <v>1000</v>
-      </c>
-      <c r="AH8">
-        <v>1000</v>
-      </c>
-      <c r="AI8">
-        <v>1000</v>
-      </c>
-      <c r="AJ8">
-        <v>1000</v>
-      </c>
-      <c r="AK8">
-        <v>1000</v>
-      </c>
-      <c r="AL8">
-        <v>1000</v>
-      </c>
-      <c r="AM8">
-        <v>1000</v>
-      </c>
-      <c r="AN8">
-        <v>1000</v>
-      </c>
-      <c r="AO8">
-        <v>1000</v>
-      </c>
-      <c r="AP8">
-        <v>1.42</v>
-      </c>
-      <c r="AQ8">
-        <v>1.42</v>
-      </c>
-      <c r="AR8">
-        <v>1.42</v>
-      </c>
-      <c r="AS8">
-        <v>1.42</v>
-      </c>
-      <c r="AT8">
-        <v>1.15</v>
-      </c>
-      <c r="AU8">
-        <v>1.19</v>
-      </c>
-      <c r="AV8">
-        <v>1.42</v>
-      </c>
-      <c r="AW8">
-        <v>1.42</v>
-      </c>
-      <c r="AX8">
-        <v>1.42</v>
-      </c>
-      <c r="AY8">
-        <v>1.42</v>
-      </c>
-      <c r="AZ8">
-        <v>1.42</v>
-      </c>
       <c r="BA8">
-        <v>1.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8">
-        <v>1.42</v>
+        <v>7.6</v>
       </c>
       <c r="BC8">
-        <v>1.42</v>
+        <v>7.6</v>
       </c>
       <c r="BD8">
-        <v>1.42</v>
+        <v>8.4</v>
       </c>
       <c r="BE8">
-        <v>1.42</v>
+        <v>9</v>
       </c>
       <c r="BF8">
-        <v>1.42</v>
+        <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>1.42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH8">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.08</v>
+        <v>1.67</v>
       </c>
       <c r="BJ8">
         <v>17.5</v>
       </c>
       <c r="BK8">
-        <v>8</v>
+        <v>1.53</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>21</v>
+        <v>1.67</v>
       </c>
       <c r="BN8">
         <v>6.2</v>
@@ -2566,13 +2566,13 @@
         <v>29</v>
       </c>
       <c r="BQ8">
-        <v>12.5</v>
+        <v>1.58</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>21</v>
+        <v>1.64</v>
       </c>
       <c r="BT8">
         <v>10</v>
@@ -2584,19 +2584,19 @@
         <v>1000</v>
       </c>
       <c r="BW8">
-        <v>21</v>
+        <v>1.64</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>21</v>
+        <v>1.65</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>21</v>
+        <v>1.64</v>
       </c>
       <c r="CB8" t="s">
         <v>105</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 19:35:21</t>
+    <t>2026-07-27 21:42:38</t>
   </si>
 </sst>
 </file>
@@ -940,49 +940,49 @@
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
         <v>1.75</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
         <v>1.71</v>
       </c>
       <c r="X2">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
         <v>26</v>
@@ -991,34 +991,34 @@
         <v>1000</v>
       </c>
       <c r="AB2">
+        <v>7.4</v>
+      </c>
+      <c r="AC2">
         <v>7.2</v>
       </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF2">
         <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
         <v>34</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL2">
         <v>1000</v>
@@ -1027,52 +1027,52 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>21</v>
       </c>
       <c r="AS2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BD2">
         <v>32</v>
@@ -1087,10 +1087,10 @@
         <v>36</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1102,7 +1102,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
@@ -1114,22 +1114,22 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
         <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BW2">
         <v>8.6</v>
@@ -1138,10 +1138,10 @@
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA2">
         <v>9</v>
@@ -1170,7 +1170,7 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
         <v>11</v>
@@ -1221,7 +1221,7 @@
         <v>3.05</v>
       </c>
       <c r="X3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
         <v>26</v>
@@ -1242,7 +1242,7 @@
         <v>65</v>
       </c>
       <c r="AE3">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AF3">
         <v>8</v>
@@ -1284,7 +1284,7 @@
         <v>4.6</v>
       </c>
       <c r="AS3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
@@ -1293,7 +1293,7 @@
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW3">
         <v>4.7</v>
@@ -1302,10 +1302,10 @@
         <v>5.9</v>
       </c>
       <c r="AY3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AZ3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA3">
         <v>4.7</v>
@@ -1317,19 +1317,19 @@
         <v>18</v>
       </c>
       <c r="BD3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BE3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF3">
         <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH3">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BI3">
         <v>2.38</v>
@@ -1338,55 +1338,55 @@
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BP3">
         <v>10</v>
       </c>
       <c r="BQ3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT3">
         <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
         <v>27</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>105</v>
@@ -1412,13 +1412,13 @@
         <v>1.94</v>
       </c>
       <c r="G4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H4">
         <v>4.7</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>3.45</v>
@@ -1448,16 +1448,16 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T4">
         <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W4">
         <v>2.02</v>
@@ -1472,7 +1472,7 @@
         <v>38</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="AB4">
         <v>8</v>
@@ -1523,7 +1523,7 @@
         <v>11</v>
       </c>
       <c r="AR4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AS4">
         <v>6.8</v>
@@ -1565,16 +1565,16 @@
         <v>6.8</v>
       </c>
       <c r="BF4">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
         <v>6.8</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1586,25 +1586,25 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
         <v>8.199999999999999</v>
@@ -1616,19 +1616,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
+        <v>12</v>
+      </c>
+      <c r="BX4">
+        <v>1000</v>
+      </c>
+      <c r="BY4">
         <v>12.5</v>
       </c>
-      <c r="BX4">
-        <v>1000</v>
-      </c>
-      <c r="BY4">
-        <v>13.5</v>
-      </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="CB4" t="s">
         <v>105</v>
@@ -1651,22 +1651,22 @@
         <v>101</v>
       </c>
       <c r="F5">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G5">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L5">
         <v>1.23</v>
@@ -1675,34 +1675,34 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>1.1</v>
+        <v>2.48</v>
       </c>
       <c r="O5">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="R5">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="S5">
+        <v>2.24</v>
+      </c>
+      <c r="T5">
+        <v>1.68</v>
+      </c>
+      <c r="U5">
         <v>2.14</v>
       </c>
-      <c r="T5">
-        <v>1.69</v>
-      </c>
-      <c r="U5">
-        <v>2.12</v>
-      </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X5">
         <v>34</v>
@@ -1711,13 +1711,13 @@
         <v>38</v>
       </c>
       <c r="Z5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AA5">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC5">
         <v>14.5</v>
@@ -1726,7 +1726,7 @@
         <v>32</v>
       </c>
       <c r="AE5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
@@ -1741,7 +1741,7 @@
         <v>85</v>
       </c>
       <c r="AJ5">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AK5">
         <v>18</v>
@@ -1759,13 +1759,13 @@
         <v>95</v>
       </c>
       <c r="AP5">
+        <v>3.8</v>
+      </c>
+      <c r="AQ5">
         <v>3.85</v>
       </c>
-      <c r="AQ5">
-        <v>3.9</v>
-      </c>
       <c r="AR5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AS5">
         <v>4.2</v>
@@ -1774,22 +1774,22 @@
         <v>3.3</v>
       </c>
       <c r="AU5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AV5">
         <v>3.8</v>
       </c>
       <c r="AW5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AY5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BA5">
         <v>4.1</v>
@@ -1798,16 +1798,16 @@
         <v>3.45</v>
       </c>
       <c r="BC5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BD5">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF5">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BG5">
         <v>4.1</v>
@@ -1834,13 +1834,13 @@
         <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP5">
         <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BR5">
         <v>21</v>
@@ -1858,7 +1858,7 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1893,7 +1893,7 @@
         <v>102</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="G6">
         <v>2.6</v>
@@ -1914,7 +1914,7 @@
         <v>1.68</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
         <v>2.14</v>
@@ -1935,10 +1935,10 @@
         <v>7.2</v>
       </c>
       <c r="T6">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="U6">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="V6">
         <v>1.3</v>
@@ -1992,7 +1992,7 @@
         <v>120</v>
       </c>
       <c r="AM6">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AN6">
         <v>60</v>
@@ -2395,7 +2395,7 @@
         <v>3.1</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M8">
         <v>1.15</v>
@@ -2530,13 +2530,13 @@
         <v>8.4</v>
       </c>
       <c r="BE8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
         <v>7.8</v>
       </c>
       <c r="BG8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2560,7 +2560,7 @@
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BP8">
         <v>29</v>
@@ -2578,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -331,7 +331,7 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 21:42:38</t>
+    <t>2026-07-27 23:49:23</t>
   </si>
 </sst>
 </file>
@@ -943,34 +943,34 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O2">
         <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U2">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V2">
         <v>1.32</v>
@@ -1036,7 +1036,7 @@
         <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
         <v>21</v>
@@ -1045,7 +1045,7 @@
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1081,16 +1081,16 @@
         <v>48</v>
       </c>
       <c r="BF2">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG2">
         <v>36</v>
       </c>
       <c r="BH2">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BJ2">
         <v>12</v>
@@ -1114,16 +1114,16 @@
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
         <v>5.2</v>
@@ -1138,7 +1138,7 @@
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>55</v>
@@ -1170,7 +1170,7 @@
         <v>1.43</v>
       </c>
       <c r="G3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H3">
         <v>11</v>
@@ -1218,13 +1218,13 @@
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X3">
         <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Z3">
         <v>140</v>
@@ -1251,16 +1251,16 @@
         <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AI3">
         <v>390</v>
       </c>
       <c r="AJ3">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL3">
         <v>100</v>
@@ -1281,10 +1281,10 @@
         <v>19.5</v>
       </c>
       <c r="AR3">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AS3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
@@ -1293,22 +1293,22 @@
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW3">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AX3">
         <v>5.9</v>
       </c>
       <c r="AY3">
-        <v>3.6</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>4.4</v>
+        <v>38</v>
       </c>
       <c r="BA3">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
@@ -1317,16 +1317,16 @@
         <v>18</v>
       </c>
       <c r="BD3">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BE3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF3">
         <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BH3">
         <v>2.98</v>
@@ -1409,16 +1409,16 @@
         <v>100</v>
       </c>
       <c r="F4">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G4">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J4">
         <v>3.45</v>
@@ -1427,7 +1427,7 @@
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1439,7 +1439,7 @@
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
         <v>2.32</v>
@@ -1448,7 +1448,7 @@
         <v>1.25</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T4">
         <v>2.1</v>
@@ -1460,7 +1460,7 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X4">
         <v>12.5</v>
@@ -1481,7 +1481,7 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AE4">
         <v>85</v>
@@ -1493,7 +1493,7 @@
         <v>12</v>
       </c>
       <c r="AH4">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI4">
         <v>95</v>
@@ -1526,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="AS4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1538,37 +1538,37 @@
         <v>16</v>
       </c>
       <c r="AW4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX4">
         <v>9</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>6.4</v>
       </c>
       <c r="BA4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB4">
         <v>18</v>
       </c>
       <c r="BC4">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BD4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF4">
         <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH4">
         <v>3.05</v>
@@ -1651,22 +1651,22 @@
         <v>101</v>
       </c>
       <c r="F5">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="H5">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
         <v>4.7</v>
       </c>
       <c r="K5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
         <v>1.23</v>
@@ -1675,16 +1675,16 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P5">
         <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="R5">
         <v>1.57</v>
@@ -1696,25 +1696,25 @@
         <v>1.68</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="X5">
         <v>34</v>
       </c>
       <c r="Y5">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AB5">
         <v>14.5</v>
@@ -1726,19 +1726,19 @@
         <v>32</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF5">
         <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ5">
         <v>17.5</v>
@@ -1753,103 +1753,103 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP5">
-        <v>3.8</v>
+        <v>19.5</v>
       </c>
       <c r="AQ5">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="AR5">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS5">
+        <v>4.3</v>
+      </c>
+      <c r="AT5">
+        <v>8.6</v>
+      </c>
+      <c r="AU5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV5">
+        <v>18.5</v>
+      </c>
+      <c r="AW5">
         <v>4.2</v>
       </c>
-      <c r="AT5">
-        <v>3.3</v>
-      </c>
-      <c r="AU5">
-        <v>3.3</v>
-      </c>
-      <c r="AV5">
-        <v>3.8</v>
-      </c>
-      <c r="AW5">
-        <v>4.1</v>
-      </c>
       <c r="AX5">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>3.2</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
         <v>4.1</v>
       </c>
       <c r="BB5">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>3.45</v>
+        <v>10.5</v>
       </c>
       <c r="BD5">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="BE5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>2.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5">
         <v>4.8</v>
       </c>
       <c r="BI5">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BN5">
         <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
         <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>21</v>
       </c>
       <c r="BS5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
         <v>5</v>
@@ -1858,19 +1858,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
+        <v>8</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>7.8</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>7.6</v>
       </c>
       <c r="BZ5">
         <v>12.5</v>
       </c>
       <c r="CA5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB5" t="s">
         <v>105</v>
@@ -1920,7 +1920,7 @@
         <v>2.14</v>
       </c>
       <c r="O6">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="P6">
         <v>1.39</v>
@@ -1950,7 +1950,7 @@
         <v>6.8</v>
       </c>
       <c r="Y6">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
         <v>27</v>
@@ -1977,7 +1977,7 @@
         <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI6">
         <v>160</v>
@@ -2010,7 +2010,7 @@
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT6">
         <v>5.6</v>
@@ -2031,7 +2031,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA6">
         <v>8.6</v>
@@ -2043,16 +2043,16 @@
         <v>34</v>
       </c>
       <c r="BD6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF6">
         <v>40</v>
       </c>
       <c r="BG6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2094,7 +2094,7 @@
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2416,10 +2416,10 @@
         <v>1.14</v>
       </c>
       <c r="S8">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T8">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="U8">
         <v>1.61</v>
@@ -2455,10 +2455,10 @@
         <v>110</v>
       </c>
       <c r="AF8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG8">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AH8">
         <v>38</v>
@@ -2491,10 +2491,10 @@
         <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS8">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT8">
         <v>5.5</v>
@@ -2506,7 +2506,7 @@
         <v>19</v>
       </c>
       <c r="AW8">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AX8">
         <v>10</v>
@@ -2515,28 +2515,28 @@
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BA8">
+        <v>10.5</v>
+      </c>
+      <c r="BB8">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB8">
-        <v>7.6</v>
-      </c>
       <c r="BC8">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD8">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE8">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF8">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BG8">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2560,7 +2560,7 @@
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BP8">
         <v>29</v>
@@ -2578,7 +2578,7 @@
         <v>10</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BV8">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="125">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Brazilian Serie A</t>
+  </si>
+  <si>
+    <t>US United Soccer League</t>
+  </si>
+  <si>
     <t>2026-07-29</t>
   </si>
   <si>
@@ -289,6 +295,21 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>21:30:00</t>
+  </si>
+  <si>
+    <t>22:15:00</t>
+  </si>
+  <si>
+    <t>22:30:00</t>
+  </si>
+  <si>
+    <t>23:00:00</t>
+  </si>
+  <si>
+    <t>23:30:00</t>
+  </si>
+  <si>
     <t>Rosario Central</t>
   </si>
   <si>
@@ -310,6 +331,24 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Nacional (Par)</t>
+  </si>
+  <si>
+    <t>Gimnasia La Plata</t>
+  </si>
+  <si>
+    <t>Mirassol</t>
+  </si>
+  <si>
+    <t>Internacional</t>
+  </si>
+  <si>
+    <t>Pittsburgh Riverhounds</t>
+  </si>
+  <si>
+    <t>Louisville FC</t>
+  </si>
+  <si>
     <t>Racing Club</t>
   </si>
   <si>
@@ -331,7 +370,25 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
-    <t>2026-07-27 23:49:23</t>
+    <t>Olimpia</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>Tulsa Roughnecks FC</t>
+  </si>
+  <si>
+    <t>Birmingham Legion FC</t>
+  </si>
+  <si>
+    <t>2026-07-28 01:56:17</t>
   </si>
 </sst>
 </file>
@@ -663,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -913,28 +970,28 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="F2">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -943,7 +1000,7 @@
         <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
         <v>1.13</v>
@@ -952,13 +1009,13 @@
         <v>2.72</v>
       </c>
       <c r="O2">
+        <v>1.55</v>
+      </c>
+      <c r="P2">
         <v>1.56</v>
       </c>
-      <c r="P2">
-        <v>1.55</v>
-      </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="R2">
         <v>1.19</v>
@@ -967,22 +1024,22 @@
         <v>5.7</v>
       </c>
       <c r="T2">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W2">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
         <v>26</v>
@@ -991,7 +1048,7 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
@@ -1000,7 +1057,7 @@
         <v>17</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
         <v>13.5</v>
@@ -1018,25 +1075,25 @@
         <v>34</v>
       </c>
       <c r="AK2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AO2">
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>21</v>
@@ -1057,7 +1114,7 @@
         <v>30</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1069,7 +1126,7 @@
         <v>38</v>
       </c>
       <c r="BB2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BC2">
         <v>21</v>
@@ -1078,10 +1135,10 @@
         <v>32</v>
       </c>
       <c r="BE2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BG2">
         <v>36</v>
@@ -1090,64 +1147,64 @@
         <v>2.78</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU2">
         <v>5.2</v>
       </c>
       <c r="BV2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX2">
         <v>65</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>55</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1155,70 +1212,70 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="F3">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="G3">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
         <v>11</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M3">
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="T3">
         <v>2.82</v>
       </c>
       <c r="U3">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="V3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X3">
         <v>11.5</v>
@@ -1227,7 +1284,7 @@
         <v>24</v>
       </c>
       <c r="Z3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA3">
         <v>1000</v>
@@ -1239,37 +1296,37 @@
         <v>12</v>
       </c>
       <c r="AD3">
-        <v>65</v>
+        <v>950</v>
       </c>
       <c r="AE3">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="AF3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AG3">
         <v>14.5</v>
       </c>
       <c r="AH3">
-        <v>950</v>
+        <v>50</v>
       </c>
       <c r="AI3">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AJ3">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AM3">
         <v>580</v>
       </c>
       <c r="AN3">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1281,10 +1338,10 @@
         <v>19.5</v>
       </c>
       <c r="AR3">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AS3">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT3">
         <v>4.8</v>
@@ -1293,10 +1350,10 @@
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AW3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX3">
         <v>5.9</v>
@@ -1308,7 +1365,7 @@
         <v>38</v>
       </c>
       <c r="BA3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
@@ -1317,79 +1374,79 @@
         <v>18</v>
       </c>
       <c r="BD3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BE3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF3">
         <v>9.800000000000001</v>
       </c>
       <c r="BG3">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BH3">
         <v>2.98</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3">
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BP3">
         <v>10</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>27</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB3" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1397,34 +1454,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="G4">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
         <v>5.1</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -1433,16 +1490,16 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
         <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
         <v>1.25</v>
@@ -1460,37 +1517,37 @@
         <v>1.25</v>
       </c>
       <c r="W4">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y4">
         <v>13.5</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH4">
         <v>24</v>
@@ -1499,82 +1556,82 @@
         <v>95</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AO4">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS4">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY4">
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BA4">
-        <v>6.8</v>
+        <v>75</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>7.6</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BG4">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1586,13 +1643,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
@@ -1604,10 +1661,10 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
         <v>6.6</v>
@@ -1622,16 +1679,16 @@
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1639,73 +1696,73 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="F5">
         <v>1.46</v>
       </c>
       <c r="G5">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="H5">
         <v>6.2</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="J5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="Q5">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="R5">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S5">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="T5">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W5">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="X5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y5">
         <v>36</v>
@@ -1717,7 +1774,7 @@
         <v>200</v>
       </c>
       <c r="AB5">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
         <v>14.5</v>
@@ -1729,25 +1786,25 @@
         <v>95</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5">
         <v>75</v>
       </c>
       <c r="AJ5">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK5">
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AM5">
         <v>110</v>
@@ -1765,10 +1822,10 @@
         <v>21</v>
       </c>
       <c r="AR5">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS5">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="AT5">
         <v>8.6</v>
@@ -1780,7 +1837,7 @@
         <v>18.5</v>
       </c>
       <c r="AW5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX5">
         <v>8.199999999999999</v>
@@ -1792,7 +1849,7 @@
         <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -1804,76 +1861,76 @@
         <v>20</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BF5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BG5">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH5">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
         <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR5">
         <v>21</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="CA5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1881,22 +1938,22 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="F6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H6">
         <v>3.75</v>
@@ -1917,13 +1974,13 @@
         <v>1.17</v>
       </c>
       <c r="N6">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O6">
         <v>1.74</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="Q6">
         <v>3.3</v>
@@ -1944,7 +2001,7 @@
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X6">
         <v>6.8</v>
@@ -2094,7 +2151,7 @@
         <v>10</v>
       </c>
       <c r="BU6">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BV6">
         <v>1000</v>
@@ -2115,7 +2172,7 @@
         <v>1.54</v>
       </c>
       <c r="CB6" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2123,16 +2180,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2357,7 +2414,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2365,19 +2422,19 @@
         <v>80</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G8">
         <v>2.3</v>
@@ -2386,16 +2443,16 @@
         <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J8">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K8">
         <v>3.1</v>
       </c>
       <c r="L8">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="M8">
         <v>1.15</v>
@@ -2425,10 +2482,10 @@
         <v>1.61</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X8">
         <v>7.4</v>
@@ -2440,7 +2497,7 @@
         <v>34</v>
       </c>
       <c r="AA8">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB8">
         <v>6</v>
@@ -2482,7 +2539,7 @@
         <v>48</v>
       </c>
       <c r="AO8">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP8">
         <v>6.6</v>
@@ -2497,7 +2554,7 @@
         <v>10.5</v>
       </c>
       <c r="AT8">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
@@ -2524,16 +2581,16 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BC8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD8">
         <v>9.800000000000001</v>
       </c>
       <c r="BE8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8">
         <v>10.5</v>
@@ -2560,7 +2617,7 @@
         <v>6.2</v>
       </c>
       <c r="BO8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP8">
         <v>29</v>
@@ -2578,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="BU8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BV8">
         <v>1000</v>
@@ -2599,7 +2656,1459 @@
         <v>1.64</v>
       </c>
       <c r="CB8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" t="s">
         <v>105</v>
+      </c>
+      <c r="E9" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1.01</v>
+      </c>
+      <c r="M9">
+        <v>1.01</v>
+      </c>
+      <c r="N9">
+        <v>1.05</v>
+      </c>
+      <c r="O9">
+        <v>1.01</v>
+      </c>
+      <c r="P9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9">
+        <v>1.01</v>
+      </c>
+      <c r="R9">
+        <v>1.18</v>
+      </c>
+      <c r="S9">
+        <v>1.05</v>
+      </c>
+      <c r="T9">
+        <v>1.11</v>
+      </c>
+      <c r="U9">
+        <v>1.11</v>
+      </c>
+      <c r="V9">
+        <v>1.01</v>
+      </c>
+      <c r="W9">
+        <v>1.01</v>
+      </c>
+      <c r="X9">
+        <v>1000</v>
+      </c>
+      <c r="Y9">
+        <v>1000</v>
+      </c>
+      <c r="Z9">
+        <v>1000</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>1000</v>
+      </c>
+      <c r="AC9">
+        <v>1000</v>
+      </c>
+      <c r="AD9">
+        <v>1000</v>
+      </c>
+      <c r="AE9">
+        <v>1000</v>
+      </c>
+      <c r="AF9">
+        <v>1000</v>
+      </c>
+      <c r="AG9">
+        <v>1000</v>
+      </c>
+      <c r="AH9">
+        <v>1000</v>
+      </c>
+      <c r="AI9">
+        <v>1000</v>
+      </c>
+      <c r="AJ9">
+        <v>1000</v>
+      </c>
+      <c r="AK9">
+        <v>1000</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>1000</v>
+      </c>
+      <c r="AN9">
+        <v>1000</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>1.01</v>
+      </c>
+      <c r="AQ9">
+        <v>1.01</v>
+      </c>
+      <c r="AR9">
+        <v>1.01</v>
+      </c>
+      <c r="AS9">
+        <v>1.01</v>
+      </c>
+      <c r="AT9">
+        <v>1.01</v>
+      </c>
+      <c r="AU9">
+        <v>1.01</v>
+      </c>
+      <c r="AV9">
+        <v>1.01</v>
+      </c>
+      <c r="AW9">
+        <v>1.01</v>
+      </c>
+      <c r="AX9">
+        <v>1.01</v>
+      </c>
+      <c r="AY9">
+        <v>1.01</v>
+      </c>
+      <c r="AZ9">
+        <v>1.01</v>
+      </c>
+      <c r="BA9">
+        <v>1.01</v>
+      </c>
+      <c r="BB9">
+        <v>1.01</v>
+      </c>
+      <c r="BC9">
+        <v>1.01</v>
+      </c>
+      <c r="BD9">
+        <v>1.01</v>
+      </c>
+      <c r="BE9">
+        <v>1.01</v>
+      </c>
+      <c r="BF9">
+        <v>1.01</v>
+      </c>
+      <c r="BG9">
+        <v>1.01</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.04</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.04</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.04</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.04</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.04</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.04</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.04</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.04</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.04</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.04</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10">
+        <v>4.3</v>
+      </c>
+      <c r="G10">
+        <v>4.8</v>
+      </c>
+      <c r="H10">
+        <v>2.06</v>
+      </c>
+      <c r="I10">
+        <v>2.2</v>
+      </c>
+      <c r="J10">
+        <v>3.15</v>
+      </c>
+      <c r="K10">
+        <v>3.45</v>
+      </c>
+      <c r="L10">
+        <v>1.01</v>
+      </c>
+      <c r="M10">
+        <v>1.12</v>
+      </c>
+      <c r="N10">
+        <v>2.7</v>
+      </c>
+      <c r="O10">
+        <v>1.5</v>
+      </c>
+      <c r="P10">
+        <v>1.59</v>
+      </c>
+      <c r="Q10">
+        <v>2.56</v>
+      </c>
+      <c r="R10">
+        <v>1.21</v>
+      </c>
+      <c r="S10">
+        <v>5</v>
+      </c>
+      <c r="T10">
+        <v>2.08</v>
+      </c>
+      <c r="U10">
+        <v>1.78</v>
+      </c>
+      <c r="V10">
+        <v>1.84</v>
+      </c>
+      <c r="W10">
+        <v>1.27</v>
+      </c>
+      <c r="X10">
+        <v>11</v>
+      </c>
+      <c r="Y10">
+        <v>7.2</v>
+      </c>
+      <c r="Z10">
+        <v>12</v>
+      </c>
+      <c r="AA10">
+        <v>28</v>
+      </c>
+      <c r="AB10">
+        <v>12.5</v>
+      </c>
+      <c r="AC10">
+        <v>7.8</v>
+      </c>
+      <c r="AD10">
+        <v>11.5</v>
+      </c>
+      <c r="AE10">
+        <v>29</v>
+      </c>
+      <c r="AF10">
+        <v>34</v>
+      </c>
+      <c r="AG10">
+        <v>970</v>
+      </c>
+      <c r="AH10">
+        <v>950</v>
+      </c>
+      <c r="AI10">
+        <v>55</v>
+      </c>
+      <c r="AJ10">
+        <v>140</v>
+      </c>
+      <c r="AK10">
+        <v>80</v>
+      </c>
+      <c r="AL10">
+        <v>120</v>
+      </c>
+      <c r="AM10">
+        <v>220</v>
+      </c>
+      <c r="AN10">
+        <v>140</v>
+      </c>
+      <c r="AO10">
+        <v>34</v>
+      </c>
+      <c r="AP10">
+        <v>7.8</v>
+      </c>
+      <c r="AQ10">
+        <v>6</v>
+      </c>
+      <c r="AR10">
+        <v>10.5</v>
+      </c>
+      <c r="AS10">
+        <v>6.8</v>
+      </c>
+      <c r="AT10">
+        <v>10.5</v>
+      </c>
+      <c r="AU10">
+        <v>6.8</v>
+      </c>
+      <c r="AV10">
+        <v>9.6</v>
+      </c>
+      <c r="AW10">
+        <v>6.8</v>
+      </c>
+      <c r="AX10">
+        <v>7</v>
+      </c>
+      <c r="AY10">
+        <v>16.5</v>
+      </c>
+      <c r="AZ10">
+        <v>20</v>
+      </c>
+      <c r="BA10">
+        <v>7.6</v>
+      </c>
+      <c r="BB10">
+        <v>8.4</v>
+      </c>
+      <c r="BC10">
+        <v>8</v>
+      </c>
+      <c r="BD10">
+        <v>8.4</v>
+      </c>
+      <c r="BE10">
+        <v>8.6</v>
+      </c>
+      <c r="BF10">
+        <v>8.4</v>
+      </c>
+      <c r="BG10">
+        <v>20</v>
+      </c>
+      <c r="BH10">
+        <v>1000</v>
+      </c>
+      <c r="BI10">
+        <v>1.68</v>
+      </c>
+      <c r="BJ10">
+        <v>17</v>
+      </c>
+      <c r="BK10">
+        <v>1.53</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.68</v>
+      </c>
+      <c r="BN10">
+        <v>10.5</v>
+      </c>
+      <c r="BO10">
+        <v>4.9</v>
+      </c>
+      <c r="BP10">
+        <v>1000</v>
+      </c>
+      <c r="BQ10">
+        <v>1.64</v>
+      </c>
+      <c r="BR10">
+        <v>1000</v>
+      </c>
+      <c r="BS10">
+        <v>1.65</v>
+      </c>
+      <c r="BT10">
+        <v>6.4</v>
+      </c>
+      <c r="BU10">
+        <v>3.45</v>
+      </c>
+      <c r="BV10">
+        <v>28</v>
+      </c>
+      <c r="BW10">
+        <v>1.58</v>
+      </c>
+      <c r="BX10">
+        <v>1000</v>
+      </c>
+      <c r="BY10">
+        <v>1.63</v>
+      </c>
+      <c r="BZ10">
+        <v>1000</v>
+      </c>
+      <c r="CA10">
+        <v>1.64</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>107</v>
+      </c>
+      <c r="E11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F11">
+        <v>1.76</v>
+      </c>
+      <c r="G11">
+        <v>1.79</v>
+      </c>
+      <c r="H11">
+        <v>5.6</v>
+      </c>
+      <c r="I11">
+        <v>5.9</v>
+      </c>
+      <c r="J11">
+        <v>3.8</v>
+      </c>
+      <c r="K11">
+        <v>3.95</v>
+      </c>
+      <c r="L11">
+        <v>1.4</v>
+      </c>
+      <c r="M11">
+        <v>1.08</v>
+      </c>
+      <c r="N11">
+        <v>3.55</v>
+      </c>
+      <c r="O11">
+        <v>1.35</v>
+      </c>
+      <c r="P11">
+        <v>1.86</v>
+      </c>
+      <c r="Q11">
+        <v>2.02</v>
+      </c>
+      <c r="R11">
+        <v>1.33</v>
+      </c>
+      <c r="S11">
+        <v>3.65</v>
+      </c>
+      <c r="T11">
+        <v>1.92</v>
+      </c>
+      <c r="U11">
+        <v>1.94</v>
+      </c>
+      <c r="V11">
+        <v>1.2</v>
+      </c>
+      <c r="W11">
+        <v>2.28</v>
+      </c>
+      <c r="X11">
+        <v>13.5</v>
+      </c>
+      <c r="Y11">
+        <v>18</v>
+      </c>
+      <c r="Z11">
+        <v>44</v>
+      </c>
+      <c r="AA11">
+        <v>180</v>
+      </c>
+      <c r="AB11">
+        <v>8</v>
+      </c>
+      <c r="AC11">
+        <v>8.6</v>
+      </c>
+      <c r="AD11">
+        <v>23</v>
+      </c>
+      <c r="AE11">
+        <v>95</v>
+      </c>
+      <c r="AF11">
+        <v>12</v>
+      </c>
+      <c r="AG11">
+        <v>12</v>
+      </c>
+      <c r="AH11">
+        <v>24</v>
+      </c>
+      <c r="AI11">
+        <v>100</v>
+      </c>
+      <c r="AJ11">
+        <v>22</v>
+      </c>
+      <c r="AK11">
+        <v>23</v>
+      </c>
+      <c r="AL11">
+        <v>46</v>
+      </c>
+      <c r="AM11">
+        <v>150</v>
+      </c>
+      <c r="AN11">
+        <v>14.5</v>
+      </c>
+      <c r="AO11">
+        <v>130</v>
+      </c>
+      <c r="AP11">
+        <v>11.5</v>
+      </c>
+      <c r="AQ11">
+        <v>15.5</v>
+      </c>
+      <c r="AR11">
+        <v>6.2</v>
+      </c>
+      <c r="AS11">
+        <v>7</v>
+      </c>
+      <c r="AT11">
+        <v>7</v>
+      </c>
+      <c r="AU11">
+        <v>7.6</v>
+      </c>
+      <c r="AV11">
+        <v>19.5</v>
+      </c>
+      <c r="AW11">
+        <v>6.8</v>
+      </c>
+      <c r="AX11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY11">
+        <v>9</v>
+      </c>
+      <c r="AZ11">
+        <v>18</v>
+      </c>
+      <c r="BA11">
+        <v>6.8</v>
+      </c>
+      <c r="BB11">
+        <v>16.5</v>
+      </c>
+      <c r="BC11">
+        <v>17.5</v>
+      </c>
+      <c r="BD11">
+        <v>6.4</v>
+      </c>
+      <c r="BE11">
+        <v>7</v>
+      </c>
+      <c r="BF11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG11">
+        <v>7</v>
+      </c>
+      <c r="BH11">
+        <v>1000</v>
+      </c>
+      <c r="BI11">
+        <v>1.89</v>
+      </c>
+      <c r="BJ11">
+        <v>14.5</v>
+      </c>
+      <c r="BK11">
+        <v>1.67</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>1.89</v>
+      </c>
+      <c r="BN11">
+        <v>5.6</v>
+      </c>
+      <c r="BO11">
+        <v>3</v>
+      </c>
+      <c r="BP11">
+        <v>17</v>
+      </c>
+      <c r="BQ11">
+        <v>1.7</v>
+      </c>
+      <c r="BR11">
+        <v>40</v>
+      </c>
+      <c r="BS11">
+        <v>1.8</v>
+      </c>
+      <c r="BT11">
+        <v>12</v>
+      </c>
+      <c r="BU11">
+        <v>1.63</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>1.84</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
+        <v>1.85</v>
+      </c>
+      <c r="BZ11">
+        <v>34</v>
+      </c>
+      <c r="CA11">
+        <v>1.79</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" t="s">
+        <v>121</v>
+      </c>
+      <c r="F12">
+        <v>4.3</v>
+      </c>
+      <c r="G12">
+        <v>4.4</v>
+      </c>
+      <c r="H12">
+        <v>1.99</v>
+      </c>
+      <c r="I12">
+        <v>2.02</v>
+      </c>
+      <c r="J12">
+        <v>3.65</v>
+      </c>
+      <c r="K12">
+        <v>3.7</v>
+      </c>
+      <c r="L12">
+        <v>1.38</v>
+      </c>
+      <c r="M12">
+        <v>1.07</v>
+      </c>
+      <c r="N12">
+        <v>3.8</v>
+      </c>
+      <c r="O12">
+        <v>1.32</v>
+      </c>
+      <c r="P12">
+        <v>2</v>
+      </c>
+      <c r="Q12">
+        <v>1.94</v>
+      </c>
+      <c r="R12">
+        <v>1.36</v>
+      </c>
+      <c r="S12">
+        <v>3.45</v>
+      </c>
+      <c r="T12">
+        <v>1.81</v>
+      </c>
+      <c r="U12">
+        <v>2.12</v>
+      </c>
+      <c r="V12">
+        <v>1.98</v>
+      </c>
+      <c r="W12">
+        <v>1.29</v>
+      </c>
+      <c r="X12">
+        <v>14.5</v>
+      </c>
+      <c r="Y12">
+        <v>9.4</v>
+      </c>
+      <c r="Z12">
+        <v>12.5</v>
+      </c>
+      <c r="AA12">
+        <v>23</v>
+      </c>
+      <c r="AB12">
+        <v>15</v>
+      </c>
+      <c r="AC12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12">
+        <v>10.5</v>
+      </c>
+      <c r="AE12">
+        <v>21</v>
+      </c>
+      <c r="AF12">
+        <v>34</v>
+      </c>
+      <c r="AG12">
+        <v>16.5</v>
+      </c>
+      <c r="AH12">
+        <v>18</v>
+      </c>
+      <c r="AI12">
+        <v>36</v>
+      </c>
+      <c r="AJ12">
+        <v>90</v>
+      </c>
+      <c r="AK12">
+        <v>55</v>
+      </c>
+      <c r="AL12">
+        <v>60</v>
+      </c>
+      <c r="AM12">
+        <v>110</v>
+      </c>
+      <c r="AN12">
+        <v>55</v>
+      </c>
+      <c r="AO12">
+        <v>14.5</v>
+      </c>
+      <c r="AP12">
+        <v>13</v>
+      </c>
+      <c r="AQ12">
+        <v>8.6</v>
+      </c>
+      <c r="AR12">
+        <v>11</v>
+      </c>
+      <c r="AS12">
+        <v>21</v>
+      </c>
+      <c r="AT12">
+        <v>13</v>
+      </c>
+      <c r="AU12">
+        <v>7.6</v>
+      </c>
+      <c r="AV12">
+        <v>9.6</v>
+      </c>
+      <c r="AW12">
+        <v>19</v>
+      </c>
+      <c r="AX12">
+        <v>24</v>
+      </c>
+      <c r="AY12">
+        <v>15</v>
+      </c>
+      <c r="AZ12">
+        <v>16.5</v>
+      </c>
+      <c r="BA12">
+        <v>32</v>
+      </c>
+      <c r="BB12">
+        <v>17</v>
+      </c>
+      <c r="BC12">
+        <v>46</v>
+      </c>
+      <c r="BD12">
+        <v>50</v>
+      </c>
+      <c r="BE12">
+        <v>18</v>
+      </c>
+      <c r="BF12">
+        <v>42</v>
+      </c>
+      <c r="BG12">
+        <v>12.5</v>
+      </c>
+      <c r="BH12">
+        <v>4.1</v>
+      </c>
+      <c r="BI12">
+        <v>2.74</v>
+      </c>
+      <c r="BJ12">
+        <v>13.5</v>
+      </c>
+      <c r="BK12">
+        <v>2.84</v>
+      </c>
+      <c r="BL12">
+        <v>1000</v>
+      </c>
+      <c r="BM12">
+        <v>3.6</v>
+      </c>
+      <c r="BN12">
+        <v>10</v>
+      </c>
+      <c r="BO12">
+        <v>5</v>
+      </c>
+      <c r="BP12">
+        <v>48</v>
+      </c>
+      <c r="BQ12">
+        <v>3.35</v>
+      </c>
+      <c r="BR12">
+        <v>1000</v>
+      </c>
+      <c r="BS12">
+        <v>3.4</v>
+      </c>
+      <c r="BT12">
+        <v>6.2</v>
+      </c>
+      <c r="BU12">
+        <v>3.3</v>
+      </c>
+      <c r="BV12">
+        <v>19</v>
+      </c>
+      <c r="BW12">
+        <v>3</v>
+      </c>
+      <c r="BX12">
+        <v>40</v>
+      </c>
+      <c r="BY12">
+        <v>3.3</v>
+      </c>
+      <c r="BZ12">
+        <v>34</v>
+      </c>
+      <c r="CA12">
+        <v>3.25</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>86</v>
+      </c>
+      <c r="C13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F13">
+        <v>1.85</v>
+      </c>
+      <c r="G13">
+        <v>1.98</v>
+      </c>
+      <c r="H13">
+        <v>4.6</v>
+      </c>
+      <c r="I13">
+        <v>5.3</v>
+      </c>
+      <c r="J13">
+        <v>3.45</v>
+      </c>
+      <c r="K13">
+        <v>3.75</v>
+      </c>
+      <c r="L13">
+        <v>1.01</v>
+      </c>
+      <c r="M13">
+        <v>1.09</v>
+      </c>
+      <c r="N13">
+        <v>3.05</v>
+      </c>
+      <c r="O13">
+        <v>1.41</v>
+      </c>
+      <c r="P13">
+        <v>1.71</v>
+      </c>
+      <c r="Q13">
+        <v>2.2</v>
+      </c>
+      <c r="R13">
+        <v>1.26</v>
+      </c>
+      <c r="S13">
+        <v>4.2</v>
+      </c>
+      <c r="T13">
+        <v>1.99</v>
+      </c>
+      <c r="U13">
+        <v>1.87</v>
+      </c>
+      <c r="V13">
+        <v>1.23</v>
+      </c>
+      <c r="W13">
+        <v>2.02</v>
+      </c>
+      <c r="X13">
+        <v>14</v>
+      </c>
+      <c r="Y13">
+        <v>17</v>
+      </c>
+      <c r="Z13">
+        <v>42</v>
+      </c>
+      <c r="AA13">
+        <v>140</v>
+      </c>
+      <c r="AB13">
+        <v>8.6</v>
+      </c>
+      <c r="AC13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD13">
+        <v>24</v>
+      </c>
+      <c r="AE13">
+        <v>85</v>
+      </c>
+      <c r="AF13">
+        <v>13.5</v>
+      </c>
+      <c r="AG13">
+        <v>12.5</v>
+      </c>
+      <c r="AH13">
+        <v>27</v>
+      </c>
+      <c r="AI13">
+        <v>100</v>
+      </c>
+      <c r="AJ13">
+        <v>28</v>
+      </c>
+      <c r="AK13">
+        <v>28</v>
+      </c>
+      <c r="AL13">
+        <v>55</v>
+      </c>
+      <c r="AM13">
+        <v>180</v>
+      </c>
+      <c r="AN13">
+        <v>22</v>
+      </c>
+      <c r="AO13">
+        <v>120</v>
+      </c>
+      <c r="AP13">
+        <v>8.6</v>
+      </c>
+      <c r="AQ13">
+        <v>10.5</v>
+      </c>
+      <c r="AR13">
+        <v>4.1</v>
+      </c>
+      <c r="AS13">
+        <v>4.4</v>
+      </c>
+      <c r="AT13">
+        <v>5.6</v>
+      </c>
+      <c r="AU13">
+        <v>7</v>
+      </c>
+      <c r="AV13">
+        <v>14</v>
+      </c>
+      <c r="AW13">
+        <v>4.3</v>
+      </c>
+      <c r="AX13">
+        <v>8.4</v>
+      </c>
+      <c r="AY13">
+        <v>7.6</v>
+      </c>
+      <c r="AZ13">
+        <v>16</v>
+      </c>
+      <c r="BA13">
+        <v>4.4</v>
+      </c>
+      <c r="BB13">
+        <v>17.5</v>
+      </c>
+      <c r="BC13">
+        <v>17</v>
+      </c>
+      <c r="BD13">
+        <v>4.2</v>
+      </c>
+      <c r="BE13">
+        <v>4.4</v>
+      </c>
+      <c r="BF13">
+        <v>13.5</v>
+      </c>
+      <c r="BG13">
+        <v>4.4</v>
+      </c>
+      <c r="BH13">
+        <v>3.6</v>
+      </c>
+      <c r="BI13">
+        <v>2.42</v>
+      </c>
+      <c r="BJ13">
+        <v>1000</v>
+      </c>
+      <c r="BK13">
+        <v>1.4</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>1.4</v>
+      </c>
+      <c r="BN13">
+        <v>1000</v>
+      </c>
+      <c r="BO13">
+        <v>1.4</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>1.4</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
+        <v>1.4</v>
+      </c>
+      <c r="BT13">
+        <v>1000</v>
+      </c>
+      <c r="BU13">
+        <v>1.4</v>
+      </c>
+      <c r="BV13">
+        <v>1000</v>
+      </c>
+      <c r="BW13">
+        <v>1.4</v>
+      </c>
+      <c r="BX13">
+        <v>1000</v>
+      </c>
+      <c r="BY13">
+        <v>1.4</v>
+      </c>
+      <c r="BZ13">
+        <v>1000</v>
+      </c>
+      <c r="CA13">
+        <v>1.4</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E14" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14">
+        <v>1.41</v>
+      </c>
+      <c r="G14">
+        <v>1.5</v>
+      </c>
+      <c r="H14">
+        <v>7</v>
+      </c>
+      <c r="I14">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J14">
+        <v>4.8</v>
+      </c>
+      <c r="K14">
+        <v>5.8</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>5.4</v>
+      </c>
+      <c r="O14">
+        <v>1.18</v>
+      </c>
+      <c r="P14">
+        <v>2.56</v>
+      </c>
+      <c r="Q14">
+        <v>1.54</v>
+      </c>
+      <c r="R14">
+        <v>1.62</v>
+      </c>
+      <c r="S14">
+        <v>2.36</v>
+      </c>
+      <c r="T14">
+        <v>1.75</v>
+      </c>
+      <c r="U14">
+        <v>2.06</v>
+      </c>
+      <c r="V14">
+        <v>1.13</v>
+      </c>
+      <c r="W14">
+        <v>3</v>
+      </c>
+      <c r="X14">
+        <v>32</v>
+      </c>
+      <c r="Y14">
+        <v>38</v>
+      </c>
+      <c r="Z14">
+        <v>85</v>
+      </c>
+      <c r="AA14">
+        <v>250</v>
+      </c>
+      <c r="AB14">
+        <v>11.5</v>
+      </c>
+      <c r="AC14">
+        <v>13</v>
+      </c>
+      <c r="AD14">
+        <v>34</v>
+      </c>
+      <c r="AE14">
+        <v>120</v>
+      </c>
+      <c r="AF14">
+        <v>12.5</v>
+      </c>
+      <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>23</v>
+      </c>
+      <c r="AI14">
+        <v>95</v>
+      </c>
+      <c r="AJ14">
+        <v>14</v>
+      </c>
+      <c r="AK14">
+        <v>15</v>
+      </c>
+      <c r="AL14">
+        <v>36</v>
+      </c>
+      <c r="AM14">
+        <v>120</v>
+      </c>
+      <c r="AN14">
+        <v>5.4</v>
+      </c>
+      <c r="AO14">
+        <v>110</v>
+      </c>
+      <c r="AP14">
+        <v>1.03</v>
+      </c>
+      <c r="AQ14">
+        <v>1.03</v>
+      </c>
+      <c r="AR14">
+        <v>1.03</v>
+      </c>
+      <c r="AS14">
+        <v>1.03</v>
+      </c>
+      <c r="AT14">
+        <v>1.03</v>
+      </c>
+      <c r="AU14">
+        <v>9</v>
+      </c>
+      <c r="AV14">
+        <v>20</v>
+      </c>
+      <c r="AW14">
+        <v>1.03</v>
+      </c>
+      <c r="AX14">
+        <v>1.03</v>
+      </c>
+      <c r="AY14">
+        <v>7.8</v>
+      </c>
+      <c r="AZ14">
+        <v>15.5</v>
+      </c>
+      <c r="BA14">
+        <v>1.03</v>
+      </c>
+      <c r="BB14">
+        <v>1.03</v>
+      </c>
+      <c r="BC14">
+        <v>10.5</v>
+      </c>
+      <c r="BD14">
+        <v>21</v>
+      </c>
+      <c r="BE14">
+        <v>1.03</v>
+      </c>
+      <c r="BF14">
+        <v>4.1</v>
+      </c>
+      <c r="BG14">
+        <v>65</v>
+      </c>
+      <c r="BH14">
+        <v>1000</v>
+      </c>
+      <c r="BI14">
+        <v>1.01</v>
+      </c>
+      <c r="BJ14">
+        <v>1000</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>1000</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>1000</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>1000</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>1000</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>1000</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -388,7 +388,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 01:56:17</t>
+    <t>2026-07-28 03:58:18</t>
   </si>
 </sst>
 </file>
@@ -982,46 +982,46 @@
         <v>111</v>
       </c>
       <c r="F2">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G2">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="H2">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N2">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
+        <v>1.56</v>
+      </c>
+      <c r="P2">
         <v>1.55</v>
       </c>
-      <c r="P2">
-        <v>1.56</v>
-      </c>
       <c r="Q2">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R2">
         <v>1.19</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="T2">
         <v>2.16</v>
@@ -1030,40 +1030,40 @@
         <v>1.76</v>
       </c>
       <c r="V2">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2">
         <v>24</v>
@@ -1072,13 +1072,13 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1090,118 +1090,118 @@
         <v>1000</v>
       </c>
       <c r="AP2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS2">
         <v>34</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>20</v>
       </c>
       <c r="BA2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BD2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE2">
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BG2">
         <v>36</v>
       </c>
       <c r="BH2">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BI2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN2">
         <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BX2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="CB2" t="s">
         <v>124</v>
@@ -1230,7 +1230,7 @@
         <v>1.48</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>12.5</v>
@@ -1248,28 +1248,28 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O3">
         <v>1.51</v>
       </c>
       <c r="P3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T3">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="V3">
         <v>1.09</v>
@@ -1278,85 +1278,85 @@
         <v>3.05</v>
       </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y3">
         <v>24</v>
       </c>
       <c r="Z3">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>1000</v>
       </c>
       <c r="AB3">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>950</v>
+        <v>210</v>
       </c>
       <c r="AE3">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AF3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AG3">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI3">
         <v>330</v>
       </c>
       <c r="AJ3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AK3">
         <v>23</v>
       </c>
       <c r="AL3">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO3">
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ3">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AR3">
-        <v>6.2</v>
+        <v>36</v>
       </c>
       <c r="AS3">
-        <v>6.6</v>
+        <v>55</v>
       </c>
       <c r="AT3">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AU3">
         <v>9.6</v>
       </c>
       <c r="AV3">
-        <v>5.9</v>
+        <v>27</v>
       </c>
       <c r="AW3">
-        <v>6.4</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AY3">
         <v>10.5</v>
@@ -1365,7 +1365,7 @@
         <v>38</v>
       </c>
       <c r="BA3">
-        <v>6.4</v>
+        <v>55</v>
       </c>
       <c r="BB3">
         <v>10.5</v>
@@ -1374,16 +1374,16 @@
         <v>18</v>
       </c>
       <c r="BD3">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>6.4</v>
+        <v>100</v>
       </c>
       <c r="BF3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
-        <v>6.6</v>
+        <v>60</v>
       </c>
       <c r="BH3">
         <v>2.98</v>
@@ -1440,7 +1440,7 @@
         <v>11.5</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
         <v>8.4</v>
@@ -1466,7 +1466,7 @@
         <v>113</v>
       </c>
       <c r="F4">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G4">
         <v>1.94</v>
@@ -1493,7 +1493,7 @@
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
         <v>1.7</v>
@@ -1514,7 +1514,7 @@
         <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
         <v>2.06</v>
@@ -1538,13 +1538,13 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE4">
         <v>80</v>
       </c>
       <c r="AF4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG4">
         <v>11.5</v>
@@ -1562,13 +1562,13 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO4">
         <v>120</v>
@@ -1580,10 +1580,10 @@
         <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>8.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
@@ -1595,10 +1595,10 @@
         <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX4">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1607,7 +1607,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>75</v>
+        <v>11.5</v>
       </c>
       <c r="BB4">
         <v>19.5</v>
@@ -1619,19 +1619,19 @@
         <v>44</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF4">
-        <v>16</v>
+        <v>7.8</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH4">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="BJ4">
         <v>11</v>
@@ -1643,7 +1643,7 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
@@ -1655,16 +1655,16 @@
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
         <v>6.6</v>
@@ -1673,19 +1673,19 @@
         <v>1000</v>
       </c>
       <c r="BW4">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
         <v>124</v>
@@ -1711,19 +1711,19 @@
         <v>1.46</v>
       </c>
       <c r="G5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="H5">
         <v>6.2</v>
       </c>
       <c r="I5">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5">
         <v>4.6</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1735,7 +1735,7 @@
         <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
         <v>2.52</v>
@@ -1753,7 +1753,7 @@
         <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.13</v>
@@ -1768,13 +1768,13 @@
         <v>36</v>
       </c>
       <c r="Z5">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC5">
         <v>14.5</v>
@@ -1783,7 +1783,7 @@
         <v>32</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF5">
         <v>13</v>
@@ -1792,10 +1792,10 @@
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI5">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AJ5">
         <v>17</v>
@@ -1804,55 +1804,55 @@
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP5">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5">
         <v>21</v>
       </c>
       <c r="AR5">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AS5">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU5">
         <v>8.800000000000001</v>
       </c>
       <c r="AV5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW5">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AY5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA5">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC5">
         <v>10.5</v>
@@ -1861,13 +1861,13 @@
         <v>20</v>
       </c>
       <c r="BE5">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="BF5">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG5">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1885,16 +1885,16 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ5">
         <v>4.8</v>
@@ -1903,31 +1903,31 @@
         <v>21</v>
       </c>
       <c r="BS5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT5">
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
+        <v>8.6</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>8.4</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
         <v>13</v>
       </c>
       <c r="CA5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="CB5" t="s">
         <v>124</v>
@@ -1953,7 +1953,7 @@
         <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H6">
         <v>3.75</v>
@@ -1965,7 +1965,7 @@
         <v>2.8</v>
       </c>
       <c r="K6">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L6">
         <v>1.68</v>
@@ -1977,7 +1977,7 @@
         <v>2.16</v>
       </c>
       <c r="O6">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="P6">
         <v>1.37</v>
@@ -1992,16 +1992,16 @@
         <v>7.2</v>
       </c>
       <c r="T6">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="U6">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="V6">
         <v>1.3</v>
       </c>
       <c r="W6">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X6">
         <v>6.8</v>
@@ -2434,7 +2434,7 @@
         <v>117</v>
       </c>
       <c r="F8">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G8">
         <v>2.3</v>
@@ -2443,10 +2443,10 @@
         <v>4.2</v>
       </c>
       <c r="I8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J8">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K8">
         <v>3.1</v>
@@ -2455,19 +2455,19 @@
         <v>1.68</v>
       </c>
       <c r="M8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N8">
         <v>2.28</v>
       </c>
       <c r="O8">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P8">
         <v>1.4</v>
       </c>
       <c r="Q8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="R8">
         <v>1.14</v>
@@ -2476,19 +2476,19 @@
         <v>7.2</v>
       </c>
       <c r="T8">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="U8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V8">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W8">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X8">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -2542,19 +2542,19 @@
         <v>190</v>
       </c>
       <c r="AP8">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ8">
         <v>8.6</v>
       </c>
       <c r="AR8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS8">
         <v>10.5</v>
       </c>
       <c r="AT8">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU8">
         <v>6.4</v>
@@ -2563,7 +2563,7 @@
         <v>19</v>
       </c>
       <c r="AW8">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX8">
         <v>10</v>
@@ -2572,88 +2572,88 @@
         <v>11.5</v>
       </c>
       <c r="AZ8">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8">
         <v>10.5</v>
       </c>
       <c r="BB8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC8">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD8">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE8">
         <v>11</v>
       </c>
       <c r="BF8">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG8">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.52</v>
       </c>
       <c r="BI8">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK8">
-        <v>1.53</v>
+        <v>8</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.67</v>
+        <v>16</v>
       </c>
       <c r="BN8">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BO8">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="BP8">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BQ8">
-        <v>1.58</v>
+        <v>9.4</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS8">
-        <v>1.64</v>
+        <v>12.5</v>
       </c>
       <c r="BT8">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW8">
-        <v>1.64</v>
+        <v>12.5</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY8">
-        <v>1.65</v>
+        <v>14</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="CA8">
-        <v>1.64</v>
+        <v>13</v>
       </c>
       <c r="CB8" t="s">
         <v>124</v>
@@ -2924,7 +2924,7 @@
         <v>4.8</v>
       </c>
       <c r="H10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="I10">
         <v>2.2</v>
@@ -2933,19 +2933,19 @@
         <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M10">
         <v>1.12</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O10">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
         <v>1.59</v>
@@ -2954,16 +2954,16 @@
         <v>2.56</v>
       </c>
       <c r="R10">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S10">
         <v>5</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="V10">
         <v>1.84</v>
@@ -2972,10 +2972,10 @@
         <v>1.27</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y10">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="Z10">
         <v>12</v>
@@ -3005,7 +3005,7 @@
         <v>950</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AJ10">
         <v>140</v>
@@ -3035,7 +3035,7 @@
         <v>10.5</v>
       </c>
       <c r="AS10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
         <v>10.5</v>
@@ -3047,97 +3047,97 @@
         <v>9.6</v>
       </c>
       <c r="AW10">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX10">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AY10">
         <v>16.5</v>
       </c>
       <c r="AZ10">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="BA10">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB10">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BC10">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD10">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE10">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF10">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BG10">
         <v>20</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="BI10">
-        <v>1.68</v>
+        <v>2.3</v>
       </c>
       <c r="BJ10">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BK10">
-        <v>1.53</v>
+        <v>8.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.68</v>
+        <v>14</v>
       </c>
       <c r="BN10">
-        <v>10.5</v>
+        <v>7.6</v>
       </c>
       <c r="BO10">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.64</v>
+        <v>11</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.65</v>
+        <v>12.5</v>
       </c>
       <c r="BT10">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BU10">
-        <v>3.45</v>
+        <v>4.1</v>
       </c>
       <c r="BV10">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BW10">
-        <v>1.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.63</v>
+        <v>11</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>1.64</v>
+        <v>11.5</v>
       </c>
       <c r="CB10" t="s">
         <v>124</v>
@@ -3160,13 +3160,13 @@
         <v>120</v>
       </c>
       <c r="F11">
+        <v>1.75</v>
+      </c>
+      <c r="G11">
         <v>1.76</v>
       </c>
-      <c r="G11">
-        <v>1.79</v>
-      </c>
       <c r="H11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I11">
         <v>5.9</v>
@@ -3193,7 +3193,7 @@
         <v>1.86</v>
       </c>
       <c r="Q11">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R11">
         <v>1.33</v>
@@ -3211,7 +3211,7 @@
         <v>1.2</v>
       </c>
       <c r="W11">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X11">
         <v>13.5</v>
@@ -3325,22 +3325,22 @@
         <v>1000</v>
       </c>
       <c r="BI11">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BJ11">
         <v>14.5</v>
       </c>
       <c r="BK11">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BN11">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BO11">
         <v>3</v>
@@ -3349,37 +3349,37 @@
         <v>17</v>
       </c>
       <c r="BQ11">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="BR11">
         <v>40</v>
       </c>
       <c r="BS11">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="BT11">
         <v>12</v>
       </c>
       <c r="BU11">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="BZ11">
         <v>34</v>
       </c>
       <c r="CA11">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CB11" t="s">
         <v>124</v>
@@ -3402,16 +3402,16 @@
         <v>121</v>
       </c>
       <c r="F12">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="G12">
         <v>4.4</v>
       </c>
       <c r="H12">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="I12">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J12">
         <v>3.65</v>
@@ -3420,28 +3420,28 @@
         <v>3.7</v>
       </c>
       <c r="L12">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M12">
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P12">
         <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="R12">
         <v>1.36</v>
       </c>
       <c r="S12">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T12">
         <v>1.81</v>
@@ -3450,10 +3450,10 @@
         <v>2.12</v>
       </c>
       <c r="V12">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X12">
         <v>14.5</v>
@@ -3465,7 +3465,7 @@
         <v>12.5</v>
       </c>
       <c r="AA12">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB12">
         <v>15</v>
@@ -3492,7 +3492,7 @@
         <v>36</v>
       </c>
       <c r="AJ12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AK12">
         <v>55</v>
@@ -3507,7 +3507,7 @@
         <v>55</v>
       </c>
       <c r="AO12">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AP12">
         <v>13</v>
@@ -3546,16 +3546,16 @@
         <v>32</v>
       </c>
       <c r="BB12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC12">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BD12">
         <v>50</v>
       </c>
       <c r="BE12">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BF12">
         <v>42</v>
@@ -3564,64 +3564,64 @@
         <v>12.5</v>
       </c>
       <c r="BH12">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="BI12">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="BJ12">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK12">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="BN12">
+        <v>7.6</v>
+      </c>
+      <c r="BO12">
+        <v>5.5</v>
+      </c>
+      <c r="BP12">
+        <v>36</v>
+      </c>
+      <c r="BQ12">
+        <v>11</v>
+      </c>
+      <c r="BR12">
+        <v>65</v>
+      </c>
+      <c r="BS12">
+        <v>11.5</v>
+      </c>
+      <c r="BT12">
+        <v>4.8</v>
+      </c>
+      <c r="BU12">
+        <v>4.2</v>
+      </c>
+      <c r="BV12">
+        <v>14.5</v>
+      </c>
+      <c r="BW12">
+        <v>10.5</v>
+      </c>
+      <c r="BX12">
+        <v>29</v>
+      </c>
+      <c r="BY12">
         <v>10</v>
       </c>
-      <c r="BO12">
-        <v>5</v>
-      </c>
-      <c r="BP12">
-        <v>48</v>
-      </c>
-      <c r="BQ12">
-        <v>3.35</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>3.4</v>
-      </c>
-      <c r="BT12">
-        <v>6.2</v>
-      </c>
-      <c r="BU12">
-        <v>3.3</v>
-      </c>
-      <c r="BV12">
-        <v>19</v>
-      </c>
-      <c r="BW12">
-        <v>3</v>
-      </c>
-      <c r="BX12">
-        <v>40</v>
-      </c>
-      <c r="BY12">
-        <v>3.3</v>
-      </c>
       <c r="BZ12">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA12">
-        <v>3.25</v>
+        <v>9.6</v>
       </c>
       <c r="CB12" t="s">
         <v>124</v>
@@ -3644,31 +3644,31 @@
         <v>122</v>
       </c>
       <c r="F13">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="G13">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H13">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I13">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M13">
         <v>1.09</v>
       </c>
       <c r="N13">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O13">
         <v>1.41</v>
@@ -3692,10 +3692,10 @@
         <v>1.87</v>
       </c>
       <c r="V13">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W13">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="X13">
         <v>14</v>
@@ -3710,13 +3710,13 @@
         <v>140</v>
       </c>
       <c r="AB13">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC13">
         <v>9.800000000000001</v>
       </c>
       <c r="AD13">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE13">
         <v>85</v>
@@ -3758,25 +3758,25 @@
         <v>10.5</v>
       </c>
       <c r="AR13">
-        <v>4.1</v>
+        <v>21</v>
       </c>
       <c r="AS13">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AT13">
         <v>5.6</v>
       </c>
       <c r="AU13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV13">
         <v>14</v>
       </c>
       <c r="AW13">
-        <v>4.3</v>
+        <v>42</v>
       </c>
       <c r="AX13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY13">
         <v>7.6</v>
@@ -3785,85 +3785,85 @@
         <v>16</v>
       </c>
       <c r="BA13">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BB13">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC13">
         <v>17</v>
       </c>
       <c r="BD13">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="BE13">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF13">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG13">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BH13">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="BI13">
-        <v>2.42</v>
+        <v>2.76</v>
       </c>
       <c r="BJ13">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK13">
-        <v>1.4</v>
+        <v>6</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>1.4</v>
+        <v>12.5</v>
       </c>
       <c r="BN13">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO13">
-        <v>1.4</v>
+        <v>3.55</v>
       </c>
       <c r="BP13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ13">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT13">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU13">
-        <v>1.4</v>
+        <v>5.8</v>
       </c>
       <c r="BV13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BW13">
-        <v>1.4</v>
+        <v>10.5</v>
       </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY13">
-        <v>1.4</v>
+        <v>11</v>
       </c>
       <c r="BZ13">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA13">
-        <v>1.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB13" t="s">
         <v>124</v>
@@ -3895,22 +3895,22 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J14">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K14">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="M14">
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O14">
         <v>1.18</v>
@@ -3928,10 +3928,10 @@
         <v>2.36</v>
       </c>
       <c r="T14">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U14">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V14">
         <v>1.13</v>
@@ -3994,7 +3994,7 @@
         <v>110</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AQ14">
         <v>1.03</v>
@@ -4006,10 +4006,10 @@
         <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AU14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV14">
         <v>20</v>
@@ -4018,7 +4018,7 @@
         <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY14">
         <v>7.8</v>
@@ -4030,7 +4030,7 @@
         <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC14">
         <v>10.5</v>
@@ -4048,16 +4048,16 @@
         <v>65</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL14">
         <v>1000</v>
@@ -4066,46 +4066,46 @@
         <v>1.01</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="s">
         <v>124</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -289,9 +292,15 @@
     <t>17:30:00</t>
   </si>
   <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
     <t>19:00:00</t>
   </si>
   <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -325,9 +334,18 @@
     <t>Barracas Central</t>
   </si>
   <si>
+    <t>Fylkir</t>
+  </si>
+  <si>
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>Throttur</t>
+  </si>
+  <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -364,9 +382,18 @@
     <t>Aldosivi</t>
   </si>
   <si>
+    <t>Volsungur</t>
+  </si>
+  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -388,7 +415,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 03:58:18</t>
+    <t>2026-07-28 06:05:36</t>
   </si>
 </sst>
 </file>
@@ -720,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB14"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -970,82 +997,82 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="F2">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G2">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J2">
         <v>3</v>
       </c>
       <c r="K2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M2">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X2">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Y2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA2">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>8</v>
@@ -1057,28 +1084,28 @@
         <v>16.5</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AK2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL2">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM2">
         <v>1000</v>
@@ -1087,124 +1114,124 @@
         <v>38</v>
       </c>
       <c r="AO2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP2">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS2">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AX2">
         <v>12</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BB2">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BC2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BD2">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BE2">
         <v>46</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BH2">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP2">
         <v>23</v>
       </c>
       <c r="BQ2">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BT2">
         <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="BV2">
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CB2" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1212,34 +1239,34 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L3">
         <v>1.55</v>
@@ -1248,7 +1275,7 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
         <v>1.51</v>
@@ -1257,25 +1284,25 @@
         <v>1.62</v>
       </c>
       <c r="Q3">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="R3">
         <v>1.22</v>
       </c>
       <c r="S3">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
         <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1296,13 +1323,13 @@
         <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AE3">
         <v>380</v>
       </c>
       <c r="AF3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AG3">
         <v>12.5</v>
@@ -1311,19 +1338,19 @@
         <v>55</v>
       </c>
       <c r="AI3">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="AJ3">
         <v>12</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL3">
         <v>1000</v>
       </c>
       <c r="AM3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AN3">
         <v>11.5</v>
@@ -1332,10 +1359,10 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR3">
         <v>36</v>
@@ -1347,10 +1374,10 @@
         <v>5</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV3">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="AW3">
         <v>50</v>
@@ -1362,7 +1389,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BA3">
         <v>55</v>
@@ -1380,16 +1407,16 @@
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BG3">
         <v>60</v>
       </c>
       <c r="BH3">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="BJ3">
         <v>16.5</v>
@@ -1401,7 +1428,7 @@
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN3">
         <v>3.55</v>
@@ -1413,16 +1440,16 @@
         <v>10</v>
       </c>
       <c r="BQ3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU3">
         <v>6.8</v>
@@ -1431,22 +1458,22 @@
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="CA3">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1454,22 +1481,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="F4">
+        <v>1.91</v>
+      </c>
+      <c r="G4">
         <v>1.93</v>
-      </c>
-      <c r="G4">
-        <v>1.94</v>
       </c>
       <c r="H4">
         <v>4.9</v>
@@ -1496,7 +1523,7 @@
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
         <v>2.36</v>
@@ -1508,10 +1535,10 @@
         <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
         <v>1.24</v>
@@ -1532,13 +1559,13 @@
         <v>140</v>
       </c>
       <c r="AB4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC4">
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AE4">
         <v>80</v>
@@ -1562,10 +1589,10 @@
         <v>25</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4">
         <v>18.5</v>
@@ -1580,25 +1607,25 @@
         <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AS4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>6.8</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>17.5</v>
       </c>
       <c r="AW4">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY4">
         <v>10</v>
@@ -1607,10 +1634,10 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BC4">
         <v>21</v>
@@ -1619,43 +1646,43 @@
         <v>44</v>
       </c>
       <c r="BE4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG4">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1667,7 +1694,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1682,13 +1709,13 @@
         <v>14</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
         <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1696,19 +1723,19 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G5">
         <v>1.55</v>
@@ -1729,31 +1756,31 @@
         <v>1.28</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="R5">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S5">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="T5">
         <v>1.72</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V5">
         <v>1.13</v>
@@ -1774,7 +1801,7 @@
         <v>220</v>
       </c>
       <c r="AB5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC5">
         <v>14.5</v>
@@ -1795,7 +1822,7 @@
         <v>25</v>
       </c>
       <c r="AI5">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ5">
         <v>17</v>
@@ -1825,31 +1852,31 @@
         <v>4.1</v>
       </c>
       <c r="AS5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT5">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV5">
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX5">
         <v>8</v>
       </c>
       <c r="AY5">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
         <v>15</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
         <v>10</v>
@@ -1861,19 +1888,19 @@
         <v>20</v>
       </c>
       <c r="BE5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BG5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
@@ -1885,22 +1912,22 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5">
         <v>4.8</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS5">
         <v>6.8</v>
@@ -1909,13 +1936,13 @@
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX5">
         <v>1000</v>
@@ -1927,10 +1954,10 @@
         <v>13</v>
       </c>
       <c r="CA5">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1938,37 +1965,37 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="F6">
         <v>2.4</v>
       </c>
       <c r="G6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H6">
         <v>3.75</v>
       </c>
       <c r="I6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J6">
         <v>2.8</v>
       </c>
       <c r="K6">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="L6">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="M6">
         <v>1.17</v>
@@ -1977,7 +2004,7 @@
         <v>2.16</v>
       </c>
       <c r="O6">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="P6">
         <v>1.37</v>
@@ -1989,7 +2016,7 @@
         <v>1.12</v>
       </c>
       <c r="S6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T6">
         <v>2.48</v>
@@ -1998,31 +2025,31 @@
         <v>1.59</v>
       </c>
       <c r="V6">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X6">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="Y6">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AA6">
         <v>130</v>
       </c>
       <c r="AB6">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AC6">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AE6">
         <v>110</v>
@@ -2031,25 +2058,25 @@
         <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AI6">
         <v>160</v>
       </c>
       <c r="AJ6">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AK6">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AL6">
         <v>120</v>
       </c>
       <c r="AM6">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="AN6">
         <v>60</v>
@@ -2058,121 +2085,121 @@
         <v>190</v>
       </c>
       <c r="AP6">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AQ6">
         <v>7.6</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AS6">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="AT6">
         <v>5.6</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="AV6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW6">
-        <v>8.4</v>
+        <v>4.4</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
       </c>
       <c r="AY6">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AZ6">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="BA6">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BB6">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="BC6">
         <v>34</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>4.4</v>
       </c>
       <c r="BE6">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="BF6">
-        <v>40</v>
+        <v>4.3</v>
       </c>
       <c r="BG6">
-        <v>8.800000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>1.56</v>
+        <v>2</v>
       </c>
       <c r="BJ6">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BK6">
-        <v>1.44</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.56</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="BP6">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="BQ6">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS6">
-        <v>1.53</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
+        <v>7.4</v>
+      </c>
+      <c r="BU6">
+        <v>5.3</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
         <v>10</v>
       </c>
-      <c r="BU6">
-        <v>4.7</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.53</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.56</v>
-      </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.54</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2180,34 +2207,34 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2216,28 +2243,28 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="P7">
+        <v>1.25</v>
+      </c>
+      <c r="Q7">
+        <v>1.07</v>
+      </c>
+      <c r="R7">
         <v>1.24</v>
       </c>
-      <c r="Q7">
-        <v>1.01</v>
-      </c>
-      <c r="R7">
-        <v>1.18</v>
-      </c>
       <c r="S7">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2357,306 +2384,306 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="F8">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="G8">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I8">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="L8">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.69</v>
+        <v>1.42</v>
       </c>
       <c r="P8">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>7.2</v>
+        <v>1.05</v>
       </c>
       <c r="T8">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>2.52</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>2.32</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="CA8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2664,34 +2691,34 @@
         <v>83</v>
       </c>
       <c r="B9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L9">
         <v>1.01</v>
@@ -2700,28 +2727,28 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="O9">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
+        <v>1.25</v>
+      </c>
+      <c r="Q9">
+        <v>1.1</v>
+      </c>
+      <c r="R9">
         <v>1.24</v>
       </c>
-      <c r="Q9">
-        <v>1.01</v>
-      </c>
-      <c r="R9">
-        <v>1.18</v>
-      </c>
       <c r="S9">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
         <v>1.01</v>
@@ -2841,548 +2868,548 @@
         <v>1000</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
         <v>1000</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
         <v>1000</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
         <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
         <v>1000</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
         <v>1000</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
         <v>1000</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F10">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="G10">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>2.1</v>
+        <v>1.04</v>
       </c>
       <c r="I10">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K10">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="L10">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>2.64</v>
+        <v>1.25</v>
       </c>
       <c r="O10">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="P10">
-        <v>1.59</v>
+        <v>1.25</v>
       </c>
       <c r="Q10">
-        <v>2.56</v>
+        <v>1.13</v>
       </c>
       <c r="R10">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S10">
-        <v>5</v>
+        <v>1.13</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
         <v>1000</v>
       </c>
       <c r="CA10">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F11">
-        <v>1.75</v>
+        <v>2.32</v>
       </c>
       <c r="G11">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="H11">
+        <v>3.9</v>
+      </c>
+      <c r="I11">
+        <v>4.2</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11">
+        <v>3.05</v>
+      </c>
+      <c r="L11">
+        <v>1.67</v>
+      </c>
+      <c r="M11">
+        <v>1.15</v>
+      </c>
+      <c r="N11">
+        <v>2.28</v>
+      </c>
+      <c r="O11">
+        <v>1.7</v>
+      </c>
+      <c r="P11">
+        <v>1.41</v>
+      </c>
+      <c r="Q11">
+        <v>3.15</v>
+      </c>
+      <c r="R11">
+        <v>1.14</v>
+      </c>
+      <c r="S11">
+        <v>7.2</v>
+      </c>
+      <c r="T11">
+        <v>2.48</v>
+      </c>
+      <c r="U11">
+        <v>1.62</v>
+      </c>
+      <c r="V11">
+        <v>1.32</v>
+      </c>
+      <c r="W11">
+        <v>1.71</v>
+      </c>
+      <c r="X11">
+        <v>7.8</v>
+      </c>
+      <c r="Y11">
+        <v>9.4</v>
+      </c>
+      <c r="Z11">
+        <v>26</v>
+      </c>
+      <c r="AA11">
+        <v>1000</v>
+      </c>
+      <c r="AB11">
+        <v>6.4</v>
+      </c>
+      <c r="AC11">
+        <v>7.2</v>
+      </c>
+      <c r="AD11">
+        <v>22</v>
+      </c>
+      <c r="AE11">
+        <v>85</v>
+      </c>
+      <c r="AF11">
+        <v>12.5</v>
+      </c>
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11">
+        <v>34</v>
+      </c>
+      <c r="AI11">
+        <v>1000</v>
+      </c>
+      <c r="AJ11">
+        <v>40</v>
+      </c>
+      <c r="AK11">
+        <v>46</v>
+      </c>
+      <c r="AL11">
+        <v>1000</v>
+      </c>
+      <c r="AM11">
+        <v>350</v>
+      </c>
+      <c r="AN11">
+        <v>48</v>
+      </c>
+      <c r="AO11">
+        <v>1000</v>
+      </c>
+      <c r="AP11">
+        <v>6.6</v>
+      </c>
+      <c r="AQ11">
+        <v>8.4</v>
+      </c>
+      <c r="AR11">
+        <v>20</v>
+      </c>
+      <c r="AS11">
+        <v>36</v>
+      </c>
+      <c r="AT11">
         <v>5.7</v>
       </c>
-      <c r="I11">
-        <v>5.9</v>
-      </c>
-      <c r="J11">
-        <v>3.8</v>
-      </c>
-      <c r="K11">
-        <v>3.95</v>
-      </c>
-      <c r="L11">
-        <v>1.4</v>
-      </c>
-      <c r="M11">
-        <v>1.08</v>
-      </c>
-      <c r="N11">
-        <v>3.55</v>
-      </c>
-      <c r="O11">
-        <v>1.35</v>
-      </c>
-      <c r="P11">
-        <v>1.86</v>
-      </c>
-      <c r="Q11">
-        <v>2.04</v>
-      </c>
-      <c r="R11">
-        <v>1.33</v>
-      </c>
-      <c r="S11">
-        <v>3.65</v>
-      </c>
-      <c r="T11">
-        <v>1.92</v>
-      </c>
-      <c r="U11">
-        <v>1.94</v>
-      </c>
-      <c r="V11">
-        <v>1.2</v>
-      </c>
-      <c r="W11">
+      <c r="AU11">
+        <v>6.4</v>
+      </c>
+      <c r="AV11">
+        <v>17</v>
+      </c>
+      <c r="AW11">
+        <v>34</v>
+      </c>
+      <c r="AX11">
+        <v>11</v>
+      </c>
+      <c r="AY11">
+        <v>12</v>
+      </c>
+      <c r="AZ11">
+        <v>27</v>
+      </c>
+      <c r="BA11">
+        <v>42</v>
+      </c>
+      <c r="BB11">
+        <v>21</v>
+      </c>
+      <c r="BC11">
+        <v>23</v>
+      </c>
+      <c r="BD11">
+        <v>36</v>
+      </c>
+      <c r="BE11">
+        <v>55</v>
+      </c>
+      <c r="BF11">
+        <v>24</v>
+      </c>
+      <c r="BG11">
+        <v>40</v>
+      </c>
+      <c r="BH11">
+        <v>2.5</v>
+      </c>
+      <c r="BI11">
         <v>2.3</v>
       </c>
-      <c r="X11">
+      <c r="BJ11">
+        <v>12.5</v>
+      </c>
+      <c r="BK11">
+        <v>7</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>15.5</v>
+      </c>
+      <c r="BN11">
+        <v>4.9</v>
+      </c>
+      <c r="BO11">
+        <v>4.3</v>
+      </c>
+      <c r="BP11">
+        <v>22</v>
+      </c>
+      <c r="BQ11">
+        <v>9.4</v>
+      </c>
+      <c r="BR11">
+        <v>55</v>
+      </c>
+      <c r="BS11">
+        <v>12.5</v>
+      </c>
+      <c r="BT11">
+        <v>7.2</v>
+      </c>
+      <c r="BU11">
+        <v>5.5</v>
+      </c>
+      <c r="BV11">
+        <v>1000</v>
+      </c>
+      <c r="BW11">
+        <v>12</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
         <v>13.5</v>
       </c>
-      <c r="Y11">
-        <v>18</v>
-      </c>
-      <c r="Z11">
-        <v>44</v>
-      </c>
-      <c r="AA11">
-        <v>180</v>
-      </c>
-      <c r="AB11">
-        <v>8</v>
-      </c>
-      <c r="AC11">
-        <v>8.6</v>
-      </c>
-      <c r="AD11">
-        <v>23</v>
-      </c>
-      <c r="AE11">
-        <v>95</v>
-      </c>
-      <c r="AF11">
-        <v>12</v>
-      </c>
-      <c r="AG11">
-        <v>12</v>
-      </c>
-      <c r="AH11">
-        <v>24</v>
-      </c>
-      <c r="AI11">
-        <v>100</v>
-      </c>
-      <c r="AJ11">
-        <v>22</v>
-      </c>
-      <c r="AK11">
-        <v>23</v>
-      </c>
-      <c r="AL11">
-        <v>46</v>
-      </c>
-      <c r="AM11">
-        <v>150</v>
-      </c>
-      <c r="AN11">
-        <v>14.5</v>
-      </c>
-      <c r="AO11">
-        <v>130</v>
-      </c>
-      <c r="AP11">
-        <v>11.5</v>
-      </c>
-      <c r="AQ11">
-        <v>15.5</v>
-      </c>
-      <c r="AR11">
-        <v>6.2</v>
-      </c>
-      <c r="AS11">
-        <v>7</v>
-      </c>
-      <c r="AT11">
-        <v>7</v>
-      </c>
-      <c r="AU11">
-        <v>7.6</v>
-      </c>
-      <c r="AV11">
-        <v>19.5</v>
-      </c>
-      <c r="AW11">
-        <v>6.8</v>
-      </c>
-      <c r="AX11">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY11">
-        <v>9</v>
-      </c>
-      <c r="AZ11">
-        <v>18</v>
-      </c>
-      <c r="BA11">
-        <v>6.8</v>
-      </c>
-      <c r="BB11">
-        <v>16.5</v>
-      </c>
-      <c r="BC11">
-        <v>17.5</v>
-      </c>
-      <c r="BD11">
-        <v>6.4</v>
-      </c>
-      <c r="BE11">
-        <v>7</v>
-      </c>
-      <c r="BF11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG11">
-        <v>7</v>
-      </c>
-      <c r="BH11">
-        <v>1000</v>
-      </c>
-      <c r="BI11">
-        <v>1.87</v>
-      </c>
-      <c r="BJ11">
-        <v>14.5</v>
-      </c>
-      <c r="BK11">
-        <v>1.66</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>1.87</v>
-      </c>
-      <c r="BN11">
-        <v>5.8</v>
-      </c>
-      <c r="BO11">
-        <v>3</v>
-      </c>
-      <c r="BP11">
-        <v>17</v>
-      </c>
-      <c r="BQ11">
-        <v>1.69</v>
-      </c>
-      <c r="BR11">
-        <v>40</v>
-      </c>
-      <c r="BS11">
-        <v>1.79</v>
-      </c>
-      <c r="BT11">
-        <v>12</v>
-      </c>
-      <c r="BU11">
-        <v>1.62</v>
-      </c>
-      <c r="BV11">
-        <v>1000</v>
-      </c>
-      <c r="BW11">
-        <v>1.82</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>1.83</v>
-      </c>
       <c r="BZ11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>1.78</v>
+        <v>13</v>
       </c>
       <c r="CB11" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3390,483 +3417,483 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F12">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="O12">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="Q12">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S12">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="T12">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13">
+        <v>4.3</v>
+      </c>
+      <c r="G13">
+        <v>4.8</v>
+      </c>
+      <c r="H13">
+        <v>2.1</v>
+      </c>
+      <c r="I13">
+        <v>2.2</v>
+      </c>
+      <c r="J13">
+        <v>3.15</v>
+      </c>
+      <c r="K13">
+        <v>3.35</v>
+      </c>
+      <c r="L13">
+        <v>1.59</v>
+      </c>
+      <c r="M13">
+        <v>1.13</v>
+      </c>
+      <c r="N13">
+        <v>2.5</v>
+      </c>
+      <c r="O13">
+        <v>1.57</v>
+      </c>
+      <c r="P13">
+        <v>1.58</v>
+      </c>
+      <c r="Q13">
+        <v>2.66</v>
+      </c>
+      <c r="R13">
+        <v>1.18</v>
+      </c>
+      <c r="S13">
+        <v>5.5</v>
+      </c>
+      <c r="T13">
+        <v>2.2</v>
+      </c>
+      <c r="U13">
+        <v>1.72</v>
+      </c>
+      <c r="V13">
+        <v>1.83</v>
+      </c>
+      <c r="W13">
+        <v>1.27</v>
+      </c>
+      <c r="X13">
+        <v>10</v>
+      </c>
+      <c r="Y13">
+        <v>6.8</v>
+      </c>
+      <c r="Z13">
+        <v>12.5</v>
+      </c>
+      <c r="AA13">
+        <v>29</v>
+      </c>
+      <c r="AB13">
+        <v>12.5</v>
+      </c>
+      <c r="AC13">
+        <v>7.8</v>
+      </c>
+      <c r="AD13">
+        <v>11.5</v>
+      </c>
+      <c r="AE13">
+        <v>38</v>
+      </c>
+      <c r="AF13">
+        <v>34</v>
+      </c>
+      <c r="AG13">
+        <v>970</v>
+      </c>
+      <c r="AH13">
+        <v>950</v>
+      </c>
+      <c r="AI13">
+        <v>65</v>
+      </c>
+      <c r="AJ13">
+        <v>140</v>
+      </c>
+      <c r="AK13">
         <v>85</v>
       </c>
-      <c r="B13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" t="s">
-        <v>96</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>122</v>
-      </c>
-      <c r="F13">
-        <v>1.9</v>
-      </c>
-      <c r="G13">
-        <v>2.06</v>
-      </c>
-      <c r="H13">
-        <v>4.4</v>
-      </c>
-      <c r="I13">
-        <v>5</v>
-      </c>
-      <c r="J13">
-        <v>3.4</v>
-      </c>
-      <c r="K13">
-        <v>3.8</v>
-      </c>
-      <c r="L13">
-        <v>1.4</v>
-      </c>
-      <c r="M13">
-        <v>1.09</v>
-      </c>
-      <c r="N13">
-        <v>3</v>
-      </c>
-      <c r="O13">
-        <v>1.41</v>
-      </c>
-      <c r="P13">
-        <v>1.71</v>
-      </c>
-      <c r="Q13">
-        <v>2.2</v>
-      </c>
-      <c r="R13">
-        <v>1.26</v>
-      </c>
-      <c r="S13">
-        <v>4.2</v>
-      </c>
-      <c r="T13">
-        <v>1.99</v>
-      </c>
-      <c r="U13">
-        <v>1.87</v>
-      </c>
-      <c r="V13">
-        <v>1.25</v>
-      </c>
-      <c r="W13">
-        <v>1.94</v>
-      </c>
-      <c r="X13">
-        <v>14</v>
-      </c>
-      <c r="Y13">
-        <v>17</v>
-      </c>
-      <c r="Z13">
-        <v>42</v>
-      </c>
-      <c r="AA13">
+      <c r="AL13">
+        <v>120</v>
+      </c>
+      <c r="AM13">
+        <v>220</v>
+      </c>
+      <c r="AN13">
         <v>140</v>
       </c>
-      <c r="AB13">
+      <c r="AO13">
+        <v>34</v>
+      </c>
+      <c r="AP13">
+        <v>7.4</v>
+      </c>
+      <c r="AQ13">
+        <v>5.8</v>
+      </c>
+      <c r="AR13">
+        <v>10.5</v>
+      </c>
+      <c r="AS13">
+        <v>6.8</v>
+      </c>
+      <c r="AT13">
+        <v>10</v>
+      </c>
+      <c r="AU13">
+        <v>6.8</v>
+      </c>
+      <c r="AV13">
+        <v>9.6</v>
+      </c>
+      <c r="AW13">
+        <v>7</v>
+      </c>
+      <c r="AX13">
+        <v>7</v>
+      </c>
+      <c r="AY13">
+        <v>16.5</v>
+      </c>
+      <c r="AZ13">
+        <v>6.6</v>
+      </c>
+      <c r="BA13">
+        <v>7.8</v>
+      </c>
+      <c r="BB13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC13">
+        <v>8</v>
+      </c>
+      <c r="BD13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE13">
+        <v>8.4</v>
+      </c>
+      <c r="BF13">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG13">
+        <v>20</v>
+      </c>
+      <c r="BH13">
+        <v>2.7</v>
+      </c>
+      <c r="BI13">
+        <v>2.3</v>
+      </c>
+      <c r="BJ13">
+        <v>12</v>
+      </c>
+      <c r="BK13">
+        <v>6.6</v>
+      </c>
+      <c r="BL13">
+        <v>1000</v>
+      </c>
+      <c r="BM13">
+        <v>14.5</v>
+      </c>
+      <c r="BN13">
         <v>7.6</v>
       </c>
-      <c r="AC13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD13">
-        <v>23</v>
-      </c>
-      <c r="AE13">
-        <v>85</v>
-      </c>
-      <c r="AF13">
-        <v>13.5</v>
-      </c>
-      <c r="AG13">
+      <c r="BO13">
+        <v>5.6</v>
+      </c>
+      <c r="BP13">
+        <v>1000</v>
+      </c>
+      <c r="BQ13">
+        <v>11.5</v>
+      </c>
+      <c r="BR13">
+        <v>1000</v>
+      </c>
+      <c r="BS13">
         <v>12.5</v>
       </c>
-      <c r="AH13">
-        <v>27</v>
-      </c>
-      <c r="AI13">
-        <v>100</v>
-      </c>
-      <c r="AJ13">
-        <v>28</v>
-      </c>
-      <c r="AK13">
-        <v>28</v>
-      </c>
-      <c r="AL13">
-        <v>55</v>
-      </c>
-      <c r="AM13">
-        <v>180</v>
-      </c>
-      <c r="AN13">
-        <v>22</v>
-      </c>
-      <c r="AO13">
-        <v>120</v>
-      </c>
-      <c r="AP13">
-        <v>8.6</v>
-      </c>
-      <c r="AQ13">
-        <v>10.5</v>
-      </c>
-      <c r="AR13">
-        <v>21</v>
-      </c>
-      <c r="AS13">
-        <v>4.8</v>
-      </c>
-      <c r="AT13">
-        <v>5.6</v>
-      </c>
-      <c r="AU13">
-        <v>6</v>
-      </c>
-      <c r="AV13">
-        <v>14</v>
-      </c>
-      <c r="AW13">
-        <v>42</v>
-      </c>
-      <c r="AX13">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY13">
-        <v>7.6</v>
-      </c>
-      <c r="AZ13">
-        <v>16</v>
-      </c>
-      <c r="BA13">
+      <c r="BT13">
         <v>4.7</v>
       </c>
-      <c r="BB13">
-        <v>16.5</v>
-      </c>
-      <c r="BC13">
-        <v>17</v>
-      </c>
-      <c r="BD13">
-        <v>27</v>
-      </c>
-      <c r="BE13">
-        <v>4.8</v>
-      </c>
-      <c r="BF13">
-        <v>13</v>
-      </c>
-      <c r="BG13">
-        <v>4.8</v>
-      </c>
-      <c r="BH13">
-        <v>3.1</v>
-      </c>
-      <c r="BI13">
-        <v>2.76</v>
-      </c>
-      <c r="BJ13">
-        <v>11</v>
-      </c>
-      <c r="BK13">
-        <v>6</v>
-      </c>
-      <c r="BL13">
-        <v>1000</v>
-      </c>
-      <c r="BM13">
-        <v>12.5</v>
-      </c>
-      <c r="BN13">
-        <v>4.6</v>
-      </c>
-      <c r="BO13">
-        <v>3.55</v>
-      </c>
-      <c r="BP13">
-        <v>15.5</v>
-      </c>
-      <c r="BQ13">
-        <v>7.2</v>
-      </c>
-      <c r="BR13">
-        <v>1000</v>
-      </c>
-      <c r="BS13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT13">
-        <v>7.8</v>
-      </c>
       <c r="BU13">
-        <v>5.8</v>
+        <v>3.6</v>
       </c>
       <c r="BV13">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW13">
-        <v>10.5</v>
+        <v>8.4</v>
       </c>
       <c r="BX13">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA13">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="CB13" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3874,241 +3901,967 @@
         <v>85</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="F14">
-        <v>1.41</v>
+        <v>1.75</v>
       </c>
       <c r="G14">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="H14">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="I14">
-        <v>8.6</v>
+        <v>5.9</v>
       </c>
       <c r="J14">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="K14">
-        <v>5.7</v>
+        <v>3.95</v>
       </c>
       <c r="L14">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N14">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="O14">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="P14">
-        <v>2.56</v>
+        <v>1.86</v>
       </c>
       <c r="Q14">
-        <v>1.54</v>
+        <v>2.02</v>
       </c>
       <c r="R14">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="S14">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="T14">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="U14">
-        <v>2.08</v>
+        <v>1.94</v>
       </c>
       <c r="V14">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="W14">
-        <v>3</v>
+        <v>2.28</v>
       </c>
       <c r="X14">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="Y14">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="AA14">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="AB14">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AC14">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AD14">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AE14">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG14">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI14">
         <v>95</v>
       </c>
       <c r="AJ14">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AK14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AL14">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="AM14">
+        <v>150</v>
+      </c>
+      <c r="AN14">
+        <v>14.5</v>
+      </c>
+      <c r="AO14">
         <v>120</v>
       </c>
-      <c r="AN14">
-        <v>5.4</v>
-      </c>
-      <c r="AO14">
-        <v>110</v>
-      </c>
       <c r="AP14">
+        <v>11.5</v>
+      </c>
+      <c r="AQ14">
+        <v>15.5</v>
+      </c>
+      <c r="AR14">
+        <v>5.6</v>
+      </c>
+      <c r="AS14">
+        <v>6.2</v>
+      </c>
+      <c r="AT14">
+        <v>7</v>
+      </c>
+      <c r="AU14">
+        <v>7.6</v>
+      </c>
+      <c r="AV14">
         <v>19.5</v>
       </c>
-      <c r="AQ14">
-        <v>1.03</v>
-      </c>
-      <c r="AR14">
-        <v>1.03</v>
-      </c>
-      <c r="AS14">
-        <v>1.03</v>
-      </c>
-      <c r="AT14">
-        <v>8.4</v>
-      </c>
-      <c r="AU14">
+      <c r="AW14">
+        <v>6</v>
+      </c>
+      <c r="AX14">
         <v>9.199999999999999</v>
       </c>
-      <c r="AV14">
-        <v>20</v>
-      </c>
-      <c r="AW14">
-        <v>1.03</v>
-      </c>
-      <c r="AX14">
-        <v>7.8</v>
-      </c>
       <c r="AY14">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ14">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BB14">
+        <v>16.5</v>
+      </c>
+      <c r="BC14">
+        <v>17.5</v>
+      </c>
+      <c r="BD14">
+        <v>5.6</v>
+      </c>
+      <c r="BE14">
+        <v>6.2</v>
+      </c>
+      <c r="BF14">
         <v>9.800000000000001</v>
       </c>
-      <c r="BC14">
-        <v>10.5</v>
-      </c>
-      <c r="BD14">
-        <v>21</v>
-      </c>
-      <c r="BE14">
-        <v>1.03</v>
-      </c>
-      <c r="BF14">
-        <v>4.1</v>
-      </c>
       <c r="BG14">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="BH14">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BI14">
-        <v>3.5</v>
+        <v>1.89</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BK14">
-        <v>7.6</v>
+        <v>1.67</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="BN14">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BO14">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="BP14">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="BQ14">
-        <v>6.2</v>
+        <v>1.7</v>
       </c>
       <c r="BR14">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BS14">
-        <v>14.5</v>
+        <v>1.8</v>
       </c>
       <c r="BT14">
         <v>12</v>
       </c>
       <c r="BU14">
+        <v>1.63</v>
+      </c>
+      <c r="BV14">
+        <v>1000</v>
+      </c>
+      <c r="BW14">
+        <v>1.84</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.85</v>
+      </c>
+      <c r="BZ14">
+        <v>34</v>
+      </c>
+      <c r="CA14">
+        <v>1.79</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>98</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15">
+        <v>4.2</v>
+      </c>
+      <c r="G15">
+        <v>4.4</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15">
+        <v>2.02</v>
+      </c>
+      <c r="J15">
+        <v>3.65</v>
+      </c>
+      <c r="K15">
+        <v>3.75</v>
+      </c>
+      <c r="L15">
+        <v>1.41</v>
+      </c>
+      <c r="M15">
+        <v>1.07</v>
+      </c>
+      <c r="N15">
+        <v>3.8</v>
+      </c>
+      <c r="O15">
+        <v>1.32</v>
+      </c>
+      <c r="P15">
+        <v>2</v>
+      </c>
+      <c r="Q15">
+        <v>1.96</v>
+      </c>
+      <c r="R15">
+        <v>1.37</v>
+      </c>
+      <c r="S15">
+        <v>3.4</v>
+      </c>
+      <c r="T15">
+        <v>1.81</v>
+      </c>
+      <c r="U15">
+        <v>2.1</v>
+      </c>
+      <c r="V15">
+        <v>1.98</v>
+      </c>
+      <c r="W15">
+        <v>1.29</v>
+      </c>
+      <c r="X15">
+        <v>14.5</v>
+      </c>
+      <c r="Y15">
+        <v>9.4</v>
+      </c>
+      <c r="Z15">
+        <v>12</v>
+      </c>
+      <c r="AA15">
+        <v>23</v>
+      </c>
+      <c r="AB15">
+        <v>15.5</v>
+      </c>
+      <c r="AC15">
+        <v>8.4</v>
+      </c>
+      <c r="AD15">
+        <v>11</v>
+      </c>
+      <c r="AE15">
+        <v>21</v>
+      </c>
+      <c r="AF15">
+        <v>34</v>
+      </c>
+      <c r="AG15">
+        <v>17</v>
+      </c>
+      <c r="AH15">
+        <v>18.5</v>
+      </c>
+      <c r="AI15">
+        <v>36</v>
+      </c>
+      <c r="AJ15">
+        <v>90</v>
+      </c>
+      <c r="AK15">
+        <v>55</v>
+      </c>
+      <c r="AL15">
+        <v>60</v>
+      </c>
+      <c r="AM15">
+        <v>110</v>
+      </c>
+      <c r="AN15">
+        <v>55</v>
+      </c>
+      <c r="AO15">
+        <v>14</v>
+      </c>
+      <c r="AP15">
+        <v>13</v>
+      </c>
+      <c r="AQ15">
+        <v>8.6</v>
+      </c>
+      <c r="AR15">
+        <v>11</v>
+      </c>
+      <c r="AS15">
+        <v>21</v>
+      </c>
+      <c r="AT15">
+        <v>13</v>
+      </c>
+      <c r="AU15">
+        <v>7.6</v>
+      </c>
+      <c r="AV15">
+        <v>9.6</v>
+      </c>
+      <c r="AW15">
+        <v>18.5</v>
+      </c>
+      <c r="AX15">
+        <v>24</v>
+      </c>
+      <c r="AY15">
+        <v>15</v>
+      </c>
+      <c r="AZ15">
+        <v>16.5</v>
+      </c>
+      <c r="BA15">
+        <v>32</v>
+      </c>
+      <c r="BB15">
+        <v>15.5</v>
+      </c>
+      <c r="BC15">
+        <v>44</v>
+      </c>
+      <c r="BD15">
+        <v>50</v>
+      </c>
+      <c r="BE15">
+        <v>16</v>
+      </c>
+      <c r="BF15">
+        <v>42</v>
+      </c>
+      <c r="BG15">
+        <v>12.5</v>
+      </c>
+      <c r="BH15">
+        <v>3.4</v>
+      </c>
+      <c r="BI15">
+        <v>3.1</v>
+      </c>
+      <c r="BJ15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK15">
+        <v>6</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>14</v>
+      </c>
+      <c r="BN15">
+        <v>7.6</v>
+      </c>
+      <c r="BO15">
+        <v>5.5</v>
+      </c>
+      <c r="BP15">
+        <v>36</v>
+      </c>
+      <c r="BQ15">
+        <v>10.5</v>
+      </c>
+      <c r="BR15">
+        <v>46</v>
+      </c>
+      <c r="BS15">
+        <v>11.5</v>
+      </c>
+      <c r="BT15">
+        <v>4.8</v>
+      </c>
+      <c r="BU15">
+        <v>4.2</v>
+      </c>
+      <c r="BV15">
+        <v>14.5</v>
+      </c>
+      <c r="BW15">
+        <v>7.4</v>
+      </c>
+      <c r="BX15">
+        <v>29</v>
+      </c>
+      <c r="BY15">
+        <v>10</v>
+      </c>
+      <c r="BZ15">
+        <v>25</v>
+      </c>
+      <c r="CA15">
+        <v>9.6</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16">
+        <v>1.91</v>
+      </c>
+      <c r="G16">
+        <v>2.04</v>
+      </c>
+      <c r="H16">
+        <v>4.3</v>
+      </c>
+      <c r="I16">
+        <v>5</v>
+      </c>
+      <c r="J16">
+        <v>3.45</v>
+      </c>
+      <c r="K16">
+        <v>3.65</v>
+      </c>
+      <c r="L16">
+        <v>1.4</v>
+      </c>
+      <c r="M16">
+        <v>1.09</v>
+      </c>
+      <c r="N16">
+        <v>3</v>
+      </c>
+      <c r="O16">
+        <v>1.4</v>
+      </c>
+      <c r="P16">
+        <v>1.7</v>
+      </c>
+      <c r="Q16">
+        <v>2.2</v>
+      </c>
+      <c r="R16">
+        <v>1.26</v>
+      </c>
+      <c r="S16">
+        <v>3.7</v>
+      </c>
+      <c r="T16">
+        <v>1.97</v>
+      </c>
+      <c r="U16">
+        <v>1.87</v>
+      </c>
+      <c r="V16">
+        <v>1.25</v>
+      </c>
+      <c r="W16">
+        <v>1.96</v>
+      </c>
+      <c r="X16">
+        <v>14</v>
+      </c>
+      <c r="Y16">
+        <v>17</v>
+      </c>
+      <c r="Z16">
+        <v>42</v>
+      </c>
+      <c r="AA16">
+        <v>140</v>
+      </c>
+      <c r="AB16">
+        <v>9</v>
+      </c>
+      <c r="AC16">
+        <v>9.6</v>
+      </c>
+      <c r="AD16">
+        <v>23</v>
+      </c>
+      <c r="AE16">
+        <v>85</v>
+      </c>
+      <c r="AF16">
+        <v>14</v>
+      </c>
+      <c r="AG16">
+        <v>13</v>
+      </c>
+      <c r="AH16">
+        <v>27</v>
+      </c>
+      <c r="AI16">
+        <v>100</v>
+      </c>
+      <c r="AJ16">
+        <v>29</v>
+      </c>
+      <c r="AK16">
+        <v>29</v>
+      </c>
+      <c r="AL16">
+        <v>55</v>
+      </c>
+      <c r="AM16">
+        <v>180</v>
+      </c>
+      <c r="AN16">
+        <v>23</v>
+      </c>
+      <c r="AO16">
+        <v>120</v>
+      </c>
+      <c r="AP16">
+        <v>8.4</v>
+      </c>
+      <c r="AQ16">
+        <v>10.5</v>
+      </c>
+      <c r="AR16">
+        <v>25</v>
+      </c>
+      <c r="AS16">
+        <v>4.2</v>
+      </c>
+      <c r="AT16">
+        <v>5.6</v>
+      </c>
+      <c r="AU16">
+        <v>6</v>
+      </c>
+      <c r="AV16">
+        <v>13.5</v>
+      </c>
+      <c r="AW16">
+        <v>4.1</v>
+      </c>
+      <c r="AX16">
+        <v>8.4</v>
+      </c>
+      <c r="AY16">
+        <v>8</v>
+      </c>
+      <c r="AZ16">
+        <v>16</v>
+      </c>
+      <c r="BA16">
+        <v>4.1</v>
+      </c>
+      <c r="BB16">
+        <v>18</v>
+      </c>
+      <c r="BC16">
+        <v>17</v>
+      </c>
+      <c r="BD16">
+        <v>32</v>
+      </c>
+      <c r="BE16">
+        <v>4.2</v>
+      </c>
+      <c r="BF16">
+        <v>14</v>
+      </c>
+      <c r="BG16">
+        <v>4.2</v>
+      </c>
+      <c r="BH16">
+        <v>3.1</v>
+      </c>
+      <c r="BI16">
+        <v>2.52</v>
+      </c>
+      <c r="BJ16">
+        <v>11</v>
+      </c>
+      <c r="BK16">
+        <v>6</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>12.5</v>
+      </c>
+      <c r="BN16">
+        <v>4.6</v>
+      </c>
+      <c r="BO16">
+        <v>3.55</v>
+      </c>
+      <c r="BP16">
+        <v>15.5</v>
+      </c>
+      <c r="BQ16">
+        <v>7.2</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT16">
+        <v>7.8</v>
+      </c>
+      <c r="BU16">
+        <v>5.8</v>
+      </c>
+      <c r="BV16">
+        <v>44</v>
+      </c>
+      <c r="BW16">
+        <v>10.5</v>
+      </c>
+      <c r="BX16">
+        <v>60</v>
+      </c>
+      <c r="BY16">
+        <v>11</v>
+      </c>
+      <c r="BZ16">
+        <v>34</v>
+      </c>
+      <c r="CA16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17">
+        <v>1.41</v>
+      </c>
+      <c r="G17">
+        <v>1.5</v>
+      </c>
+      <c r="H17">
+        <v>7</v>
+      </c>
+      <c r="I17">
+        <v>8.6</v>
+      </c>
+      <c r="J17">
+        <v>5.1</v>
+      </c>
+      <c r="K17">
+        <v>6</v>
+      </c>
+      <c r="L17">
+        <v>1.23</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>5.5</v>
+      </c>
+      <c r="O17">
+        <v>1.18</v>
+      </c>
+      <c r="P17">
+        <v>2.54</v>
+      </c>
+      <c r="Q17">
+        <v>1.52</v>
+      </c>
+      <c r="R17">
+        <v>1.61</v>
+      </c>
+      <c r="S17">
+        <v>2.3</v>
+      </c>
+      <c r="T17">
+        <v>1.76</v>
+      </c>
+      <c r="U17">
+        <v>2.1</v>
+      </c>
+      <c r="V17">
+        <v>1.13</v>
+      </c>
+      <c r="W17">
+        <v>3</v>
+      </c>
+      <c r="X17">
+        <v>34</v>
+      </c>
+      <c r="Y17">
+        <v>40</v>
+      </c>
+      <c r="Z17">
+        <v>85</v>
+      </c>
+      <c r="AA17">
+        <v>260</v>
+      </c>
+      <c r="AB17">
+        <v>13.5</v>
+      </c>
+      <c r="AC17">
+        <v>15.5</v>
+      </c>
+      <c r="AD17">
+        <v>36</v>
+      </c>
+      <c r="AE17">
+        <v>120</v>
+      </c>
+      <c r="AF17">
+        <v>12.5</v>
+      </c>
+      <c r="AG17">
+        <v>13</v>
+      </c>
+      <c r="AH17">
+        <v>27</v>
+      </c>
+      <c r="AI17">
+        <v>100</v>
+      </c>
+      <c r="AJ17">
+        <v>16</v>
+      </c>
+      <c r="AK17">
+        <v>17.5</v>
+      </c>
+      <c r="AL17">
+        <v>36</v>
+      </c>
+      <c r="AM17">
+        <v>120</v>
+      </c>
+      <c r="AN17">
+        <v>6.4</v>
+      </c>
+      <c r="AO17">
+        <v>120</v>
+      </c>
+      <c r="AP17">
+        <v>19.5</v>
+      </c>
+      <c r="AQ17">
+        <v>1.03</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>8.4</v>
+      </c>
+      <c r="AU17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV17">
+        <v>20</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>7.6</v>
+      </c>
+      <c r="AY17">
+        <v>7.8</v>
+      </c>
+      <c r="AZ17">
+        <v>16</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>9.6</v>
+      </c>
+      <c r="BC17">
+        <v>10.5</v>
+      </c>
+      <c r="BD17">
+        <v>21</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>4</v>
+      </c>
+      <c r="BG17">
+        <v>65</v>
+      </c>
+      <c r="BH17">
+        <v>4.7</v>
+      </c>
+      <c r="BI17">
+        <v>3.5</v>
+      </c>
+      <c r="BJ17">
+        <v>11</v>
+      </c>
+      <c r="BK17">
+        <v>7.6</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>4.4</v>
+      </c>
+      <c r="BO17">
+        <v>3.3</v>
+      </c>
+      <c r="BP17">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ17">
+        <v>6.2</v>
+      </c>
+      <c r="BR17">
+        <v>21</v>
+      </c>
+      <c r="BS17">
+        <v>14.5</v>
+      </c>
+      <c r="BT17">
+        <v>12</v>
+      </c>
+      <c r="BU17">
         <v>8.199999999999999</v>
       </c>
-      <c r="BV14">
-        <v>1000</v>
-      </c>
-      <c r="BW14">
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
         <v>40</v>
       </c>
-      <c r="BX14">
-        <v>1000</v>
-      </c>
-      <c r="BY14">
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
         <v>36</v>
       </c>
-      <c r="BZ14">
+      <c r="BZ17">
         <v>12</v>
       </c>
-      <c r="CA14">
+      <c r="CA17">
         <v>8.4</v>
       </c>
-      <c r="CB14" t="s">
-        <v>124</v>
+      <c r="CB17" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,9 @@
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
+    <t>Icelandic 2 Deild</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -337,13 +340,31 @@
     <t>Fylkir</t>
   </si>
   <si>
+    <t>Selfoss</t>
+  </si>
+  <si>
+    <t>IF Magni</t>
+  </si>
+  <si>
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>Throttur Vogar</t>
+  </si>
+  <si>
+    <t>Vikingur Olafsvik</t>
+  </si>
+  <si>
+    <t>Kari</t>
+  </si>
+  <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
     <t>Throttur</t>
   </si>
   <si>
-    <t>Grindavik</t>
+    <t>Haukar</t>
   </si>
   <si>
     <t>Defensa y Justicia</t>
@@ -385,13 +406,31 @@
     <t>Volsungur</t>
   </si>
   <si>
+    <t>Dalvik/Reynir</t>
+  </si>
+  <si>
+    <t>KFA Austfjarda</t>
+  </si>
+  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Hviti Riddarinn</t>
+  </si>
+  <si>
+    <t>Fjolnir</t>
+  </si>
+  <si>
+    <t>Kormakur/Hvot</t>
+  </si>
+  <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>Leiknir R</t>
+    <t>KFG</t>
   </si>
   <si>
     <t>Deportivo Riestra</t>
@@ -415,7 +454,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 06:05:36</t>
+    <t>2026-07-28 08:12:31</t>
   </si>
 </sst>
 </file>
@@ -747,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -997,16 +1036,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F2">
         <v>2.48</v>
@@ -1015,10 +1054,10 @@
         <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I2">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J2">
         <v>3</v>
@@ -1036,7 +1075,7 @@
         <v>2.78</v>
       </c>
       <c r="O2">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="P2">
         <v>1.58</v>
@@ -1051,28 +1090,28 @@
         <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="V2">
         <v>1.37</v>
       </c>
       <c r="W2">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
         <v>10.5</v>
       </c>
       <c r="Z2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2">
         <v>8</v>
@@ -1081,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE2">
         <v>60</v>
@@ -1096,7 +1135,7 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ2">
         <v>36</v>
@@ -1105,10 +1144,10 @@
         <v>36</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN2">
         <v>38</v>
@@ -1117,7 +1156,7 @@
         <v>85</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
         <v>9.199999999999999</v>
@@ -1138,19 +1177,19 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ2">
         <v>21</v>
       </c>
       <c r="BA2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB2">
         <v>32</v>
@@ -1162,25 +1201,25 @@
         <v>55</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF2">
         <v>30</v>
       </c>
       <c r="BG2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="BI2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1189,7 +1228,7 @@
         <v>10.5</v>
       </c>
       <c r="BN2">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BO2">
         <v>3.95</v>
@@ -1210,13 +1249,13 @@
         <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BV2">
         <v>36</v>
       </c>
       <c r="BW2">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX2">
         <v>60</v>
@@ -1228,10 +1267,10 @@
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1239,34 +1278,34 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G3">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>11.5</v>
       </c>
       <c r="J3">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L3">
         <v>1.55</v>
@@ -1275,7 +1314,7 @@
         <v>1.11</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
         <v>1.51</v>
@@ -1293,16 +1332,16 @@
         <v>5.3</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="U3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V3">
         <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X3">
         <v>10.5</v>
@@ -1320,40 +1359,40 @@
         <v>5.5</v>
       </c>
       <c r="AC3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="AE3">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AF3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH3">
         <v>55</v>
       </c>
       <c r="AI3">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AJ3">
         <v>12</v>
       </c>
       <c r="AK3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM3">
         <v>600</v>
       </c>
       <c r="AN3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO3">
         <v>1000</v>
@@ -1365,19 +1404,19 @@
         <v>19</v>
       </c>
       <c r="AR3">
+        <v>40</v>
+      </c>
+      <c r="AS3">
+        <v>12.5</v>
+      </c>
+      <c r="AT3">
+        <v>5.1</v>
+      </c>
+      <c r="AU3">
+        <v>9.6</v>
+      </c>
+      <c r="AV3">
         <v>36</v>
-      </c>
-      <c r="AS3">
-        <v>55</v>
-      </c>
-      <c r="AT3">
-        <v>5</v>
-      </c>
-      <c r="AU3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV3">
-        <v>38</v>
       </c>
       <c r="AW3">
         <v>50</v>
@@ -1398,16 +1437,16 @@
         <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE3">
         <v>100</v>
       </c>
       <c r="BF3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG3">
         <v>60</v>
@@ -1416,28 +1455,28 @@
         <v>2.96</v>
       </c>
       <c r="BI3">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="BJ3">
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BO3">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BP3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ3">
         <v>5.4</v>
@@ -1446,34 +1485,34 @@
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BT3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>27</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CB3" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1481,34 +1520,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F4">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -1517,16 +1556,16 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O4">
         <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R4">
         <v>1.25</v>
@@ -1541,22 +1580,22 @@
         <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X4">
         <v>11.5</v>
       </c>
       <c r="Y4">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB4">
         <v>7.4</v>
@@ -1565,94 +1604,94 @@
         <v>9.4</v>
       </c>
       <c r="AD4">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AE4">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF4">
         <v>10.5</v>
       </c>
       <c r="AG4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ4">
         <v>22</v>
       </c>
       <c r="AK4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO4">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP4">
         <v>9.6</v>
       </c>
       <c r="AQ4">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR4">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AW4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX4">
+        <v>9</v>
+      </c>
+      <c r="AY4">
         <v>9.4</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
       </c>
       <c r="AZ4">
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>12.5</v>
+        <v>44</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC4">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4">
         <v>44</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF4">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
@@ -1664,7 +1703,7 @@
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
@@ -1676,13 +1715,13 @@
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>1000</v>
@@ -1694,7 +1733,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>1000</v>
@@ -1709,13 +1748,13 @@
         <v>14</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA4">
         <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1723,91 +1762,91 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G5">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="H5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q5">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
         <v>2.1</v>
       </c>
       <c r="V5">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="W5">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="X5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="Z5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA5">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AB5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC5">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AD5">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE5">
         <v>100</v>
@@ -1825,7 +1864,7 @@
         <v>80</v>
       </c>
       <c r="AJ5">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK5">
         <v>18</v>
@@ -1840,67 +1879,67 @@
         <v>7</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP5">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AR5">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS5">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AT5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW5">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="AX5">
         <v>8</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA5">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BF5">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BG5">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BH5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
@@ -1912,7 +1951,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
@@ -1921,10 +1960,10 @@
         <v>3.35</v>
       </c>
       <c r="BP5">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BR5">
         <v>22</v>
@@ -1942,22 +1981,22 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ5">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="CA5">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="CB5" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1965,16 +2004,16 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F6">
         <v>2.4</v>
@@ -1986,25 +2025,25 @@
         <v>3.75</v>
       </c>
       <c r="I6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K6">
         <v>2.94</v>
       </c>
       <c r="L6">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="P6">
         <v>1.37</v>
@@ -2016,10 +2055,10 @@
         <v>1.12</v>
       </c>
       <c r="S6">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="T6">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
         <v>1.59</v>
@@ -2034,19 +2073,19 @@
         <v>7.8</v>
       </c>
       <c r="Y6">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA6">
         <v>130</v>
       </c>
       <c r="AB6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD6">
         <v>24</v>
@@ -2055,22 +2094,22 @@
         <v>110</v>
       </c>
       <c r="AF6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG6">
         <v>17</v>
       </c>
       <c r="AH6">
-        <v>40</v>
+        <v>950</v>
       </c>
       <c r="AI6">
         <v>160</v>
       </c>
       <c r="AJ6">
+        <v>55</v>
+      </c>
+      <c r="AK6">
         <v>50</v>
-      </c>
-      <c r="AK6">
-        <v>55</v>
       </c>
       <c r="AL6">
         <v>120</v>
@@ -2085,58 +2124,58 @@
         <v>190</v>
       </c>
       <c r="AP6">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AQ6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AS6">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT6">
         <v>5.6</v>
       </c>
       <c r="AU6">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW6">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
       </c>
       <c r="AY6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ6">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="BA6">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB6">
-        <v>29</v>
+        <v>5.3</v>
       </c>
       <c r="BC6">
-        <v>34</v>
+        <v>5.3</v>
       </c>
       <c r="BD6">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE6">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF6">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG6">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH6">
         <v>2.42</v>
@@ -2148,58 +2187,58 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
         <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP6">
         <v>26</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2207,16 +2246,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="F7">
         <v>1.04</v>
@@ -2231,7 +2270,7 @@
         <v>1000</v>
       </c>
       <c r="J7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K7">
         <v>1000</v>
@@ -2243,7 +2282,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O7">
         <v>1.07</v>
@@ -2255,16 +2294,16 @@
         <v>1.07</v>
       </c>
       <c r="R7">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2327,52 +2366,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2441,7 +2480,7 @@
         <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2449,34 +2488,34 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
         <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L8">
         <v>1.01</v>
@@ -2488,16 +2527,16 @@
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.01</v>
       </c>
       <c r="R8">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S8">
         <v>1.05</v>
@@ -2569,52 +2608,52 @@
         <v>1000</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
         <v>1.01</v>
@@ -2677,45 +2716,45 @@
         <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="G9">
         <v>1000</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="K9">
         <v>1000</v>
@@ -2727,28 +2766,28 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="P9">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="Q9">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="R9">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="T9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V9">
         <v>1.01</v>
@@ -2811,52 +2850,52 @@
         <v>1000</v>
       </c>
       <c r="AP9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF9">
         <v>1.01</v>
@@ -2925,42 +2964,42 @@
         <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s">
         <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -2969,28 +3008,28 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="P10">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="R10">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="T10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10">
         <v>1.01</v>
@@ -3110,306 +3149,306 @@
         <v>1000</v>
       </c>
       <c r="BI10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ10">
         <v>1000</v>
       </c>
       <c r="BK10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN10">
         <v>1000</v>
       </c>
       <c r="BO10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP10">
         <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR10">
         <v>1000</v>
       </c>
       <c r="BS10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT10">
         <v>1000</v>
       </c>
       <c r="BU10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX10">
         <v>1000</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA10">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C11" t="s">
         <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F11">
-        <v>2.32</v>
+        <v>1.02</v>
       </c>
       <c r="G11">
-        <v>2.4</v>
+        <v>1000</v>
       </c>
       <c r="H11">
-        <v>3.9</v>
+        <v>1.02</v>
       </c>
       <c r="I11">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K11">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="L11">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.7</v>
+        <v>1.09</v>
       </c>
       <c r="P11">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="Q11">
-        <v>3.15</v>
+        <v>1.09</v>
       </c>
       <c r="R11">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="S11">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="T11">
-        <v>2.48</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>1.62</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
         <v>1000</v>
       </c>
       <c r="AB11">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
         <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
         <v>1000</v>
       </c>
       <c r="AM11">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR11">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AS11">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT11">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AU11">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV11">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="AW11">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX11">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AY11">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BA11">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="BB11">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC11">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="BD11">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BE11">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BF11">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN11">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP11">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR11">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT11">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV11">
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ11">
         <v>1000</v>
       </c>
       <c r="CA11">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3417,34 +3456,34 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3453,19 +3492,19 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="O12">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="R12">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S12">
         <v>1.05</v>
@@ -3537,52 +3576,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3651,1217 +3690,2669 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F13">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="G13">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>2.1</v>
+        <v>1.02</v>
       </c>
       <c r="I13">
-        <v>2.2</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K13">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="L13">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O13">
-        <v>1.57</v>
+        <v>1.05</v>
       </c>
       <c r="P13">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S13">
-        <v>5.5</v>
+        <v>1.05</v>
       </c>
       <c r="T13">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U13">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="W13">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y13">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA13">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB13">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC13">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD13">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE13">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG13">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH13">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI13">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK13">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL13">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM13">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN13">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO13">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP13">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BH13">
-        <v>2.7</v>
+        <v>1000</v>
       </c>
       <c r="BI13">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ13">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK13">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL13">
         <v>1000</v>
       </c>
       <c r="BM13">
-        <v>14.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN13">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO13">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP13">
         <v>1000</v>
       </c>
       <c r="BQ13">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR13">
         <v>1000</v>
       </c>
       <c r="BS13">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT13">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BU13">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BV13">
         <v>1000</v>
       </c>
       <c r="BW13">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX13">
         <v>1000</v>
       </c>
       <c r="BY13">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ13">
         <v>1000</v>
       </c>
       <c r="CA13">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D14" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="F14">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
-        <v>1.78</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>5.6</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>3.8</v>
+        <v>1.02</v>
       </c>
       <c r="K14">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N14">
-        <v>3.5</v>
+        <v>1.26</v>
       </c>
       <c r="O14">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="P14">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="Q14">
-        <v>2.02</v>
+        <v>1.13</v>
       </c>
       <c r="R14">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S14">
-        <v>3.65</v>
+        <v>1.12</v>
       </c>
       <c r="T14">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U14">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="W14">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y14">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z14">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AA14">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC14">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE14">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH14">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ14">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK14">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM14">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO14">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP14">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR14">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AS14">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT14">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU14">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW14">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AX14">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY14">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA14">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="BB14">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC14">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD14">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE14">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF14">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG14">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BH14">
         <v>1000</v>
       </c>
       <c r="BI14">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BJ14">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BK14">
-        <v>1.67</v>
+        <v>1.04</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="BN14">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO14">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BP14">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="BQ14">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR14">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.8</v>
+        <v>1.04</v>
       </c>
       <c r="BT14">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU14">
-        <v>1.63</v>
+        <v>1.04</v>
       </c>
       <c r="BV14">
         <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.85</v>
+        <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA14">
-        <v>1.79</v>
+        <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F15">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="G15">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="H15">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="I15">
-        <v>2.02</v>
+        <v>1000</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>1.02</v>
       </c>
       <c r="K15">
-        <v>3.75</v>
+        <v>1000</v>
       </c>
       <c r="L15">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
-        <v>3.8</v>
+        <v>1.26</v>
       </c>
       <c r="O15">
-        <v>1.32</v>
+        <v>1.1</v>
       </c>
       <c r="P15">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="Q15">
-        <v>1.96</v>
+        <v>1.1</v>
       </c>
       <c r="R15">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="T15">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="W15">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>50</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>3.4</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>9.6</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F16">
-        <v>1.91</v>
+        <v>1.02</v>
       </c>
       <c r="G16">
-        <v>2.04</v>
+        <v>1000</v>
       </c>
       <c r="H16">
-        <v>4.3</v>
+        <v>1.02</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J16">
-        <v>3.45</v>
+        <v>1.02</v>
       </c>
       <c r="K16">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L16">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="O16">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="P16">
-        <v>1.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>1.03</v>
       </c>
       <c r="R16">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S16">
-        <v>3.7</v>
+        <v>1.05</v>
       </c>
       <c r="T16">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>1.87</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="W16">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="X16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BC16">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BD16">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BE16">
-        <v>4.2</v>
+        <v>1.03</v>
       </c>
       <c r="BF16">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>2.52</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
         <v>1000</v>
       </c>
       <c r="BS16">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>133</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F17">
-        <v>1.41</v>
+        <v>2.32</v>
       </c>
       <c r="G17">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="H17">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="I17">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="J17">
-        <v>5.1</v>
+        <v>2.88</v>
       </c>
       <c r="K17">
-        <v>6</v>
+        <v>3.05</v>
       </c>
       <c r="L17">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N17">
-        <v>5.5</v>
+        <v>2.36</v>
       </c>
       <c r="O17">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="P17">
-        <v>2.54</v>
+        <v>1.43</v>
       </c>
       <c r="Q17">
-        <v>1.52</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
-        <v>1.61</v>
+        <v>1.14</v>
       </c>
       <c r="S17">
-        <v>2.3</v>
+        <v>7.2</v>
       </c>
       <c r="T17">
-        <v>1.76</v>
+        <v>2.46</v>
       </c>
       <c r="U17">
-        <v>2.1</v>
+        <v>1.63</v>
       </c>
       <c r="V17">
-        <v>1.13</v>
+        <v>1.31</v>
       </c>
       <c r="W17">
-        <v>3</v>
+        <v>1.71</v>
       </c>
       <c r="X17">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="Y17">
-        <v>40</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="AA17">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="AC17">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="AD17">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AE17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
         <v>12.5</v>
       </c>
       <c r="AG17">
+        <v>13.5</v>
+      </c>
+      <c r="AH17">
+        <v>32</v>
+      </c>
+      <c r="AI17">
+        <v>1000</v>
+      </c>
+      <c r="AJ17">
+        <v>60</v>
+      </c>
+      <c r="AK17">
+        <v>42</v>
+      </c>
+      <c r="AL17">
+        <v>1000</v>
+      </c>
+      <c r="AM17">
+        <v>340</v>
+      </c>
+      <c r="AN17">
+        <v>95</v>
+      </c>
+      <c r="AO17">
+        <v>1000</v>
+      </c>
+      <c r="AP17">
+        <v>6.4</v>
+      </c>
+      <c r="AQ17">
+        <v>8.4</v>
+      </c>
+      <c r="AR17">
+        <v>17</v>
+      </c>
+      <c r="AS17">
+        <v>36</v>
+      </c>
+      <c r="AT17">
+        <v>5.8</v>
+      </c>
+      <c r="AU17">
+        <v>6.6</v>
+      </c>
+      <c r="AV17">
+        <v>16.5</v>
+      </c>
+      <c r="AW17">
+        <v>34</v>
+      </c>
+      <c r="AX17">
+        <v>11</v>
+      </c>
+      <c r="AY17">
+        <v>11</v>
+      </c>
+      <c r="AZ17">
+        <v>22</v>
+      </c>
+      <c r="BA17">
+        <v>42</v>
+      </c>
+      <c r="BB17">
+        <v>25</v>
+      </c>
+      <c r="BC17">
+        <v>34</v>
+      </c>
+      <c r="BD17">
+        <v>36</v>
+      </c>
+      <c r="BE17">
+        <v>50</v>
+      </c>
+      <c r="BF17">
+        <v>24</v>
+      </c>
+      <c r="BG17">
+        <v>40</v>
+      </c>
+      <c r="BH17">
+        <v>2.5</v>
+      </c>
+      <c r="BI17">
+        <v>2.3</v>
+      </c>
+      <c r="BJ17">
+        <v>12.5</v>
+      </c>
+      <c r="BK17">
+        <v>7.2</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>16</v>
+      </c>
+      <c r="BN17">
+        <v>4.9</v>
+      </c>
+      <c r="BO17">
+        <v>4.3</v>
+      </c>
+      <c r="BP17">
+        <v>22</v>
+      </c>
+      <c r="BQ17">
+        <v>9.6</v>
+      </c>
+      <c r="BR17">
+        <v>55</v>
+      </c>
+      <c r="BS17">
         <v>13</v>
       </c>
-      <c r="AH17">
+      <c r="BT17">
+        <v>7.2</v>
+      </c>
+      <c r="BU17">
+        <v>5.5</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>12.5</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>14</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>13</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" t="s">
+        <v>140</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>1.1</v>
+      </c>
+      <c r="O18">
+        <v>1.01</v>
+      </c>
+      <c r="P18">
+        <v>1.24</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>1.18</v>
+      </c>
+      <c r="S18">
+        <v>1.13</v>
+      </c>
+      <c r="T18">
+        <v>1.11</v>
+      </c>
+      <c r="U18">
+        <v>1.11</v>
+      </c>
+      <c r="V18">
+        <v>1.01</v>
+      </c>
+      <c r="W18">
+        <v>1.01</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.01</v>
+      </c>
+      <c r="AQ18">
+        <v>1.01</v>
+      </c>
+      <c r="AR18">
+        <v>1.01</v>
+      </c>
+      <c r="AS18">
+        <v>1.01</v>
+      </c>
+      <c r="AT18">
+        <v>1.01</v>
+      </c>
+      <c r="AU18">
+        <v>1.01</v>
+      </c>
+      <c r="AV18">
+        <v>1.01</v>
+      </c>
+      <c r="AW18">
+        <v>1.01</v>
+      </c>
+      <c r="AX18">
+        <v>1.01</v>
+      </c>
+      <c r="AY18">
+        <v>1.01</v>
+      </c>
+      <c r="AZ18">
+        <v>1.01</v>
+      </c>
+      <c r="BA18">
+        <v>1.01</v>
+      </c>
+      <c r="BB18">
+        <v>1.01</v>
+      </c>
+      <c r="BC18">
+        <v>1.01</v>
+      </c>
+      <c r="BD18">
+        <v>1.01</v>
+      </c>
+      <c r="BE18">
+        <v>1.01</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.04</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.04</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.04</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.04</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.04</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.04</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.04</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.04</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.04</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.04</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>80</v>
+      </c>
+      <c r="B19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+      <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" t="s">
+        <v>141</v>
+      </c>
+      <c r="F19">
+        <v>4.1</v>
+      </c>
+      <c r="G19">
+        <v>4.5</v>
+      </c>
+      <c r="H19">
+        <v>2.16</v>
+      </c>
+      <c r="I19">
+        <v>2.26</v>
+      </c>
+      <c r="J19">
+        <v>3.15</v>
+      </c>
+      <c r="K19">
+        <v>3.3</v>
+      </c>
+      <c r="L19">
+        <v>1.59</v>
+      </c>
+      <c r="M19">
+        <v>1.13</v>
+      </c>
+      <c r="N19">
+        <v>2.5</v>
+      </c>
+      <c r="O19">
+        <v>1.59</v>
+      </c>
+      <c r="P19">
+        <v>1.57</v>
+      </c>
+      <c r="Q19">
+        <v>2.72</v>
+      </c>
+      <c r="R19">
+        <v>1.19</v>
+      </c>
+      <c r="S19">
+        <v>5.7</v>
+      </c>
+      <c r="T19">
+        <v>2.22</v>
+      </c>
+      <c r="U19">
+        <v>1.73</v>
+      </c>
+      <c r="V19">
+        <v>1.79</v>
+      </c>
+      <c r="W19">
+        <v>1.29</v>
+      </c>
+      <c r="X19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y19">
+        <v>6.8</v>
+      </c>
+      <c r="Z19">
+        <v>13</v>
+      </c>
+      <c r="AA19">
+        <v>32</v>
+      </c>
+      <c r="AB19">
+        <v>11</v>
+      </c>
+      <c r="AC19">
+        <v>7.8</v>
+      </c>
+      <c r="AD19">
+        <v>11.5</v>
+      </c>
+      <c r="AE19">
+        <v>38</v>
+      </c>
+      <c r="AF19">
+        <v>32</v>
+      </c>
+      <c r="AG19">
+        <v>19.5</v>
+      </c>
+      <c r="AH19">
+        <v>950</v>
+      </c>
+      <c r="AI19">
+        <v>65</v>
+      </c>
+      <c r="AJ19">
+        <v>130</v>
+      </c>
+      <c r="AK19">
+        <v>80</v>
+      </c>
+      <c r="AL19">
+        <v>120</v>
+      </c>
+      <c r="AM19">
+        <v>220</v>
+      </c>
+      <c r="AN19">
+        <v>140</v>
+      </c>
+      <c r="AO19">
+        <v>34</v>
+      </c>
+      <c r="AP19">
+        <v>7.2</v>
+      </c>
+      <c r="AQ19">
+        <v>5.9</v>
+      </c>
+      <c r="AR19">
+        <v>10.5</v>
+      </c>
+      <c r="AS19">
+        <v>7.8</v>
+      </c>
+      <c r="AT19">
+        <v>9.6</v>
+      </c>
+      <c r="AU19">
+        <v>6.8</v>
+      </c>
+      <c r="AV19">
+        <v>10</v>
+      </c>
+      <c r="AW19">
+        <v>8</v>
+      </c>
+      <c r="AX19">
+        <v>7.8</v>
+      </c>
+      <c r="AY19">
+        <v>16.5</v>
+      </c>
+      <c r="AZ19">
+        <v>7.4</v>
+      </c>
+      <c r="BA19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB19">
+        <v>9</v>
+      </c>
+      <c r="BC19">
+        <v>8.6</v>
+      </c>
+      <c r="BD19">
+        <v>9</v>
+      </c>
+      <c r="BE19">
+        <v>9.4</v>
+      </c>
+      <c r="BF19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG19">
+        <v>7.8</v>
+      </c>
+      <c r="BH19">
+        <v>2.66</v>
+      </c>
+      <c r="BI19">
+        <v>2.3</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>7</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>16</v>
+      </c>
+      <c r="BN19">
+        <v>7.2</v>
+      </c>
+      <c r="BO19">
+        <v>5.4</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>12</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>13.5</v>
+      </c>
+      <c r="BT19">
+        <v>4.8</v>
+      </c>
+      <c r="BU19">
+        <v>3.75</v>
+      </c>
+      <c r="BV19">
+        <v>19.5</v>
+      </c>
+      <c r="BW19">
+        <v>9</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>12</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>12.5</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>142</v>
+      </c>
+      <c r="F20">
+        <v>1.73</v>
+      </c>
+      <c r="G20">
+        <v>1.78</v>
+      </c>
+      <c r="H20">
+        <v>5.6</v>
+      </c>
+      <c r="I20">
+        <v>5.9</v>
+      </c>
+      <c r="J20">
+        <v>3.85</v>
+      </c>
+      <c r="K20">
+        <v>4</v>
+      </c>
+      <c r="L20">
+        <v>1.42</v>
+      </c>
+      <c r="M20">
+        <v>1.08</v>
+      </c>
+      <c r="N20">
+        <v>3.55</v>
+      </c>
+      <c r="O20">
+        <v>1.35</v>
+      </c>
+      <c r="P20">
+        <v>1.87</v>
+      </c>
+      <c r="Q20">
+        <v>2.02</v>
+      </c>
+      <c r="R20">
+        <v>1.33</v>
+      </c>
+      <c r="S20">
+        <v>3.65</v>
+      </c>
+      <c r="T20">
+        <v>1.94</v>
+      </c>
+      <c r="U20">
+        <v>1.94</v>
+      </c>
+      <c r="V20">
+        <v>1.2</v>
+      </c>
+      <c r="W20">
+        <v>2.28</v>
+      </c>
+      <c r="X20">
+        <v>13.5</v>
+      </c>
+      <c r="Y20">
+        <v>18</v>
+      </c>
+      <c r="Z20">
+        <v>55</v>
+      </c>
+      <c r="AA20">
+        <v>170</v>
+      </c>
+      <c r="AB20">
+        <v>8</v>
+      </c>
+      <c r="AC20">
+        <v>10.5</v>
+      </c>
+      <c r="AD20">
+        <v>23</v>
+      </c>
+      <c r="AE20">
+        <v>95</v>
+      </c>
+      <c r="AF20">
+        <v>12</v>
+      </c>
+      <c r="AG20">
+        <v>11.5</v>
+      </c>
+      <c r="AH20">
+        <v>24</v>
+      </c>
+      <c r="AI20">
+        <v>95</v>
+      </c>
+      <c r="AJ20">
+        <v>21</v>
+      </c>
+      <c r="AK20">
+        <v>23</v>
+      </c>
+      <c r="AL20">
+        <v>46</v>
+      </c>
+      <c r="AM20">
+        <v>150</v>
+      </c>
+      <c r="AN20">
+        <v>14</v>
+      </c>
+      <c r="AO20">
+        <v>120</v>
+      </c>
+      <c r="AP20">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20">
+        <v>15.5</v>
+      </c>
+      <c r="AR20">
+        <v>5.9</v>
+      </c>
+      <c r="AS20">
+        <v>6.4</v>
+      </c>
+      <c r="AT20">
+        <v>7</v>
+      </c>
+      <c r="AU20">
+        <v>7.6</v>
+      </c>
+      <c r="AV20">
+        <v>19.5</v>
+      </c>
+      <c r="AW20">
+        <v>6.2</v>
+      </c>
+      <c r="AX20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY20">
+        <v>9</v>
+      </c>
+      <c r="AZ20">
+        <v>18</v>
+      </c>
+      <c r="BA20">
+        <v>6.2</v>
+      </c>
+      <c r="BB20">
+        <v>16</v>
+      </c>
+      <c r="BC20">
+        <v>17.5</v>
+      </c>
+      <c r="BD20">
+        <v>5.8</v>
+      </c>
+      <c r="BE20">
+        <v>6.2</v>
+      </c>
+      <c r="BF20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BG20">
+        <v>6.2</v>
+      </c>
+      <c r="BH20">
+        <v>3.35</v>
+      </c>
+      <c r="BI20">
+        <v>2.78</v>
+      </c>
+      <c r="BJ20">
+        <v>10.5</v>
+      </c>
+      <c r="BK20">
+        <v>6.4</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>15</v>
+      </c>
+      <c r="BN20">
+        <v>4.3</v>
+      </c>
+      <c r="BO20">
+        <v>3.45</v>
+      </c>
+      <c r="BP20">
+        <v>12</v>
+      </c>
+      <c r="BQ20">
+        <v>6.8</v>
+      </c>
+      <c r="BR20">
+        <v>29</v>
+      </c>
+      <c r="BS20">
+        <v>10.5</v>
+      </c>
+      <c r="BT20">
+        <v>9</v>
+      </c>
+      <c r="BU20">
+        <v>5.8</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>12.5</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>13</v>
+      </c>
+      <c r="BZ20">
+        <v>24</v>
+      </c>
+      <c r="CA20">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21">
+        <v>4.3</v>
+      </c>
+      <c r="G21">
+        <v>4.5</v>
+      </c>
+      <c r="H21">
+        <v>1.96</v>
+      </c>
+      <c r="I21">
+        <v>2</v>
+      </c>
+      <c r="J21">
+        <v>3.65</v>
+      </c>
+      <c r="K21">
+        <v>3.75</v>
+      </c>
+      <c r="L21">
+        <v>1.42</v>
+      </c>
+      <c r="M21">
+        <v>1.07</v>
+      </c>
+      <c r="N21">
+        <v>3.85</v>
+      </c>
+      <c r="O21">
+        <v>1.32</v>
+      </c>
+      <c r="P21">
+        <v>1.96</v>
+      </c>
+      <c r="Q21">
+        <v>1.98</v>
+      </c>
+      <c r="R21">
+        <v>1.36</v>
+      </c>
+      <c r="S21">
+        <v>3.45</v>
+      </c>
+      <c r="T21">
+        <v>1.84</v>
+      </c>
+      <c r="U21">
+        <v>2.16</v>
+      </c>
+      <c r="V21">
+        <v>2</v>
+      </c>
+      <c r="W21">
+        <v>1.28</v>
+      </c>
+      <c r="X21">
+        <v>14.5</v>
+      </c>
+      <c r="Y21">
+        <v>9.4</v>
+      </c>
+      <c r="Z21">
+        <v>12</v>
+      </c>
+      <c r="AA21">
+        <v>22</v>
+      </c>
+      <c r="AB21">
+        <v>15.5</v>
+      </c>
+      <c r="AC21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD21">
+        <v>11</v>
+      </c>
+      <c r="AE21">
+        <v>21</v>
+      </c>
+      <c r="AF21">
+        <v>34</v>
+      </c>
+      <c r="AG21">
+        <v>18</v>
+      </c>
+      <c r="AH21">
+        <v>18.5</v>
+      </c>
+      <c r="AI21">
+        <v>38</v>
+      </c>
+      <c r="AJ21">
+        <v>95</v>
+      </c>
+      <c r="AK21">
+        <v>55</v>
+      </c>
+      <c r="AL21">
+        <v>60</v>
+      </c>
+      <c r="AM21">
+        <v>110</v>
+      </c>
+      <c r="AN21">
+        <v>65</v>
+      </c>
+      <c r="AO21">
+        <v>14.5</v>
+      </c>
+      <c r="AP21">
+        <v>13</v>
+      </c>
+      <c r="AQ21">
+        <v>8.6</v>
+      </c>
+      <c r="AR21">
+        <v>10.5</v>
+      </c>
+      <c r="AS21">
+        <v>20</v>
+      </c>
+      <c r="AT21">
+        <v>14</v>
+      </c>
+      <c r="AU21">
+        <v>7.6</v>
+      </c>
+      <c r="AV21">
+        <v>9.6</v>
+      </c>
+      <c r="AW21">
+        <v>18.5</v>
+      </c>
+      <c r="AX21">
+        <v>24</v>
+      </c>
+      <c r="AY21">
+        <v>15</v>
+      </c>
+      <c r="AZ21">
+        <v>16.5</v>
+      </c>
+      <c r="BA21">
+        <v>32</v>
+      </c>
+      <c r="BB21">
+        <v>15</v>
+      </c>
+      <c r="BC21">
+        <v>48</v>
+      </c>
+      <c r="BD21">
+        <v>50</v>
+      </c>
+      <c r="BE21">
+        <v>15.5</v>
+      </c>
+      <c r="BF21">
+        <v>50</v>
+      </c>
+      <c r="BG21">
+        <v>12.5</v>
+      </c>
+      <c r="BH21">
+        <v>3.45</v>
+      </c>
+      <c r="BI21">
+        <v>3.2</v>
+      </c>
+      <c r="BJ21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK21">
+        <v>6.2</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>15.5</v>
+      </c>
+      <c r="BN21">
+        <v>7.4</v>
+      </c>
+      <c r="BO21">
+        <v>5.6</v>
+      </c>
+      <c r="BP21">
+        <v>36</v>
+      </c>
+      <c r="BQ21">
+        <v>12</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>12.5</v>
+      </c>
+      <c r="BT21">
+        <v>4.7</v>
+      </c>
+      <c r="BU21">
+        <v>4.2</v>
+      </c>
+      <c r="BV21">
+        <v>14</v>
+      </c>
+      <c r="BW21">
+        <v>7.8</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>11</v>
+      </c>
+      <c r="BZ21">
+        <v>25</v>
+      </c>
+      <c r="CA21">
+        <v>10.5</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>100</v>
+      </c>
+      <c r="D22" t="s">
+        <v>122</v>
+      </c>
+      <c r="E22" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22">
+        <v>1.91</v>
+      </c>
+      <c r="G22">
+        <v>2.04</v>
+      </c>
+      <c r="H22">
+        <v>4.3</v>
+      </c>
+      <c r="I22">
+        <v>5</v>
+      </c>
+      <c r="J22">
+        <v>3.35</v>
+      </c>
+      <c r="K22">
+        <v>3.65</v>
+      </c>
+      <c r="L22">
+        <v>1.39</v>
+      </c>
+      <c r="M22">
+        <v>1.09</v>
+      </c>
+      <c r="N22">
+        <v>3.05</v>
+      </c>
+      <c r="O22">
+        <v>1.41</v>
+      </c>
+      <c r="P22">
+        <v>1.71</v>
+      </c>
+      <c r="Q22">
+        <v>2.18</v>
+      </c>
+      <c r="R22">
+        <v>1.26</v>
+      </c>
+      <c r="S22">
+        <v>4.2</v>
+      </c>
+      <c r="T22">
+        <v>1.97</v>
+      </c>
+      <c r="U22">
+        <v>1.89</v>
+      </c>
+      <c r="V22">
+        <v>1.25</v>
+      </c>
+      <c r="W22">
+        <v>1.96</v>
+      </c>
+      <c r="X22">
+        <v>14</v>
+      </c>
+      <c r="Y22">
+        <v>17</v>
+      </c>
+      <c r="Z22">
+        <v>42</v>
+      </c>
+      <c r="AA22">
+        <v>140</v>
+      </c>
+      <c r="AB22">
+        <v>9</v>
+      </c>
+      <c r="AC22">
+        <v>9.6</v>
+      </c>
+      <c r="AD22">
+        <v>23</v>
+      </c>
+      <c r="AE22">
+        <v>85</v>
+      </c>
+      <c r="AF22">
+        <v>14</v>
+      </c>
+      <c r="AG22">
+        <v>12.5</v>
+      </c>
+      <c r="AH22">
         <v>27</v>
       </c>
-      <c r="AI17">
+      <c r="AI22">
         <v>100</v>
       </c>
-      <c r="AJ17">
+      <c r="AJ22">
+        <v>29</v>
+      </c>
+      <c r="AK22">
+        <v>29</v>
+      </c>
+      <c r="AL22">
+        <v>55</v>
+      </c>
+      <c r="AM22">
+        <v>180</v>
+      </c>
+      <c r="AN22">
+        <v>23</v>
+      </c>
+      <c r="AO22">
+        <v>120</v>
+      </c>
+      <c r="AP22">
+        <v>8.6</v>
+      </c>
+      <c r="AQ22">
+        <v>10</v>
+      </c>
+      <c r="AR22">
+        <v>4</v>
+      </c>
+      <c r="AS22">
+        <v>4.3</v>
+      </c>
+      <c r="AT22">
+        <v>5.7</v>
+      </c>
+      <c r="AU22">
+        <v>6</v>
+      </c>
+      <c r="AV22">
+        <v>13.5</v>
+      </c>
+      <c r="AW22">
+        <v>4.2</v>
+      </c>
+      <c r="AX22">
+        <v>8.4</v>
+      </c>
+      <c r="AY22">
+        <v>7.8</v>
+      </c>
+      <c r="AZ22">
+        <v>15.5</v>
+      </c>
+      <c r="BA22">
+        <v>4.2</v>
+      </c>
+      <c r="BB22">
+        <v>17</v>
+      </c>
+      <c r="BC22">
+        <v>17</v>
+      </c>
+      <c r="BD22">
+        <v>4.1</v>
+      </c>
+      <c r="BE22">
+        <v>4.3</v>
+      </c>
+      <c r="BF22">
+        <v>13.5</v>
+      </c>
+      <c r="BG22">
+        <v>4.2</v>
+      </c>
+      <c r="BH22">
+        <v>3.1</v>
+      </c>
+      <c r="BI22">
+        <v>2.78</v>
+      </c>
+      <c r="BJ22">
+        <v>11</v>
+      </c>
+      <c r="BK22">
+        <v>6</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>12.5</v>
+      </c>
+      <c r="BN22">
+        <v>4.6</v>
+      </c>
+      <c r="BO22">
+        <v>3.55</v>
+      </c>
+      <c r="BP22">
+        <v>15.5</v>
+      </c>
+      <c r="BQ22">
+        <v>7.2</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BT22">
+        <v>7.8</v>
+      </c>
+      <c r="BU22">
+        <v>5.8</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>10.5</v>
+      </c>
+      <c r="BX22">
+        <v>60</v>
+      </c>
+      <c r="BY22">
+        <v>11</v>
+      </c>
+      <c r="BZ22">
+        <v>34</v>
+      </c>
+      <c r="CA22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>87</v>
+      </c>
+      <c r="B23" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" t="s">
+        <v>123</v>
+      </c>
+      <c r="E23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F23">
+        <v>1.4</v>
+      </c>
+      <c r="G23">
+        <v>1.51</v>
+      </c>
+      <c r="H23">
+        <v>7</v>
+      </c>
+      <c r="I23">
+        <v>8.6</v>
+      </c>
+      <c r="J23">
+        <v>5</v>
+      </c>
+      <c r="K23">
+        <v>6</v>
+      </c>
+      <c r="L23">
+        <v>1.23</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>5.6</v>
+      </c>
+      <c r="O23">
+        <v>1.17</v>
+      </c>
+      <c r="P23">
+        <v>2.56</v>
+      </c>
+      <c r="Q23">
+        <v>1.51</v>
+      </c>
+      <c r="R23">
+        <v>1.63</v>
+      </c>
+      <c r="S23">
+        <v>2.32</v>
+      </c>
+      <c r="T23">
+        <v>1.76</v>
+      </c>
+      <c r="U23">
+        <v>2.1</v>
+      </c>
+      <c r="V23">
+        <v>1.13</v>
+      </c>
+      <c r="W23">
+        <v>2.96</v>
+      </c>
+      <c r="X23">
+        <v>34</v>
+      </c>
+      <c r="Y23">
+        <v>40</v>
+      </c>
+      <c r="Z23">
+        <v>85</v>
+      </c>
+      <c r="AA23">
+        <v>250</v>
+      </c>
+      <c r="AB23">
+        <v>13.5</v>
+      </c>
+      <c r="AC23">
+        <v>15.5</v>
+      </c>
+      <c r="AD23">
+        <v>36</v>
+      </c>
+      <c r="AE23">
+        <v>120</v>
+      </c>
+      <c r="AF23">
+        <v>12.5</v>
+      </c>
+      <c r="AG23">
+        <v>13</v>
+      </c>
+      <c r="AH23">
+        <v>27</v>
+      </c>
+      <c r="AI23">
+        <v>95</v>
+      </c>
+      <c r="AJ23">
         <v>16</v>
       </c>
-      <c r="AK17">
+      <c r="AK23">
         <v>17.5</v>
       </c>
-      <c r="AL17">
+      <c r="AL23">
         <v>36</v>
       </c>
-      <c r="AM17">
+      <c r="AM23">
         <v>120</v>
       </c>
-      <c r="AN17">
-        <v>6.4</v>
-      </c>
-      <c r="AO17">
+      <c r="AN23">
+        <v>6.2</v>
+      </c>
+      <c r="AO23">
         <v>120</v>
       </c>
-      <c r="AP17">
+      <c r="AP23">
         <v>19.5</v>
       </c>
-      <c r="AQ17">
-        <v>1.03</v>
-      </c>
-      <c r="AR17">
-        <v>1.03</v>
-      </c>
-      <c r="AS17">
-        <v>1.03</v>
-      </c>
-      <c r="AT17">
-        <v>8.4</v>
-      </c>
-      <c r="AU17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV17">
-        <v>20</v>
-      </c>
-      <c r="AW17">
-        <v>1.03</v>
-      </c>
-      <c r="AX17">
-        <v>7.6</v>
-      </c>
-      <c r="AY17">
-        <v>7.8</v>
-      </c>
-      <c r="AZ17">
-        <v>16</v>
-      </c>
-      <c r="BA17">
-        <v>1.03</v>
-      </c>
-      <c r="BB17">
-        <v>9.6</v>
-      </c>
-      <c r="BC17">
+      <c r="AQ23">
+        <v>1.03</v>
+      </c>
+      <c r="AR23">
+        <v>1.03</v>
+      </c>
+      <c r="AS23">
+        <v>1.03</v>
+      </c>
+      <c r="AT23">
+        <v>1.03</v>
+      </c>
+      <c r="AU23">
         <v>10.5</v>
       </c>
-      <c r="BD17">
+      <c r="AV23">
+        <v>1.03</v>
+      </c>
+      <c r="AW23">
+        <v>1.03</v>
+      </c>
+      <c r="AX23">
+        <v>9</v>
+      </c>
+      <c r="AY23">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23">
+        <v>18.5</v>
+      </c>
+      <c r="BA23">
+        <v>1.03</v>
+      </c>
+      <c r="BB23">
+        <v>11</v>
+      </c>
+      <c r="BC23">
+        <v>1.03</v>
+      </c>
+      <c r="BD23">
+        <v>1.03</v>
+      </c>
+      <c r="BE23">
+        <v>1.03</v>
+      </c>
+      <c r="BF23">
+        <v>4</v>
+      </c>
+      <c r="BG23">
+        <v>65</v>
+      </c>
+      <c r="BH23">
+        <v>4.8</v>
+      </c>
+      <c r="BI23">
+        <v>3.55</v>
+      </c>
+      <c r="BJ23">
+        <v>11</v>
+      </c>
+      <c r="BK23">
+        <v>1.04</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.04</v>
+      </c>
+      <c r="BN23">
+        <v>4.4</v>
+      </c>
+      <c r="BO23">
+        <v>3.3</v>
+      </c>
+      <c r="BP23">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ23">
+        <v>1.04</v>
+      </c>
+      <c r="BR23">
         <v>21</v>
       </c>
-      <c r="BE17">
-        <v>1.03</v>
-      </c>
-      <c r="BF17">
-        <v>4</v>
-      </c>
-      <c r="BG17">
-        <v>65</v>
-      </c>
-      <c r="BH17">
-        <v>4.7</v>
-      </c>
-      <c r="BI17">
-        <v>3.5</v>
-      </c>
-      <c r="BJ17">
-        <v>11</v>
-      </c>
-      <c r="BK17">
-        <v>7.6</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.01</v>
-      </c>
-      <c r="BN17">
-        <v>4.4</v>
-      </c>
-      <c r="BO17">
-        <v>3.3</v>
-      </c>
-      <c r="BP17">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BQ17">
-        <v>6.2</v>
-      </c>
-      <c r="BR17">
-        <v>21</v>
-      </c>
-      <c r="BS17">
-        <v>14.5</v>
-      </c>
-      <c r="BT17">
+      <c r="BS23">
+        <v>1.04</v>
+      </c>
+      <c r="BT23">
         <v>12</v>
       </c>
-      <c r="BU17">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BV17">
-        <v>1000</v>
-      </c>
-      <c r="BW17">
-        <v>40</v>
-      </c>
-      <c r="BX17">
-        <v>1000</v>
-      </c>
-      <c r="BY17">
-        <v>36</v>
-      </c>
-      <c r="BZ17">
+      <c r="BU23">
+        <v>1.04</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.04</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.04</v>
+      </c>
+      <c r="BZ23">
         <v>12</v>
       </c>
-      <c r="CA17">
-        <v>8.4</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>133</v>
+      <c r="CA23">
+        <v>1.04</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,9 @@
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
+    <t>Ecuadorian Serie B</t>
+  </si>
+  <si>
     <t>Brazilian Serie A</t>
   </si>
   <si>
@@ -307,6 +310,9 @@
     <t>20:00:00</t>
   </si>
   <si>
+    <t>20:30:00</t>
+  </si>
+  <si>
     <t>21:30:00</t>
   </si>
   <si>
@@ -358,18 +364,21 @@
     <t>Kari</t>
   </si>
   <si>
+    <t>Haukar</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
     <t>Throttur</t>
   </si>
   <si>
-    <t>Haukar</t>
-  </si>
-  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Vinotinto Ecuador</t>
+  </si>
+  <si>
     <t>Nacional (Par)</t>
   </si>
   <si>
@@ -424,18 +433,21 @@
     <t>Kormakur/Hvot</t>
   </si>
   <si>
+    <t>KFG</t>
+  </si>
+  <si>
     <t>Leiknir R</t>
   </si>
   <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>KFG</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>San Antonio FC</t>
+  </si>
+  <si>
     <t>Olimpia</t>
   </si>
   <si>
@@ -454,7 +466,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 08:12:31</t>
+    <t>2026-07-28 10:20:43</t>
   </si>
 </sst>
 </file>
@@ -786,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB23"/>
+  <dimension ref="A1:CB24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1036,34 +1048,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H2">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
         <v>1.59</v>
@@ -1072,16 +1084,16 @@
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P2">
         <v>1.58</v>
       </c>
       <c r="Q2">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R2">
         <v>1.2</v>
@@ -1090,85 +1102,85 @@
         <v>5.5</v>
       </c>
       <c r="T2">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="U2">
         <v>1.83</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X2">
         <v>8.800000000000001</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AB2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC2">
         <v>7</v>
       </c>
       <c r="AD2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE2">
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI2">
         <v>85</v>
       </c>
       <c r="AJ2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM2">
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AP2">
         <v>8</v>
       </c>
       <c r="AQ2">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR2">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS2">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AT2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1177,13 +1189,13 @@
         <v>14.5</v>
       </c>
       <c r="AW2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AY2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2">
         <v>21</v>
@@ -1192,25 +1204,25 @@
         <v>70</v>
       </c>
       <c r="BB2">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE2">
         <v>60</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BG2">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="BH2">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BI2">
         <v>2.26</v>
@@ -1219,58 +1231,58 @@
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="BM2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO2">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="BP2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
+        <v>9.4</v>
+      </c>
+      <c r="BT2">
+        <v>7</v>
+      </c>
+      <c r="BU2">
+        <v>5.1</v>
+      </c>
+      <c r="BV2">
+        <v>38</v>
+      </c>
+      <c r="BW2">
         <v>9</v>
-      </c>
-      <c r="BT2">
-        <v>6.8</v>
-      </c>
-      <c r="BU2">
-        <v>5.5</v>
-      </c>
-      <c r="BV2">
-        <v>36</v>
-      </c>
-      <c r="BW2">
-        <v>8.6</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CB2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1278,190 +1290,190 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F3">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="G3">
+        <v>1.44</v>
+      </c>
+      <c r="H3">
+        <v>11</v>
+      </c>
+      <c r="I3">
+        <v>12.5</v>
+      </c>
+      <c r="J3">
+        <v>4.6</v>
+      </c>
+      <c r="K3">
+        <v>4.8</v>
+      </c>
+      <c r="L3">
+        <v>1.53</v>
+      </c>
+      <c r="M3">
+        <v>1.1</v>
+      </c>
+      <c r="N3">
+        <v>2.98</v>
+      </c>
+      <c r="O3">
         <v>1.48</v>
       </c>
-      <c r="H3">
-        <v>10</v>
-      </c>
-      <c r="I3">
-        <v>11.5</v>
-      </c>
-      <c r="J3">
-        <v>4.3</v>
-      </c>
-      <c r="K3">
-        <v>4.6</v>
-      </c>
-      <c r="L3">
-        <v>1.55</v>
-      </c>
-      <c r="M3">
-        <v>1.11</v>
-      </c>
-      <c r="N3">
-        <v>2.88</v>
-      </c>
-      <c r="O3">
-        <v>1.51</v>
-      </c>
       <c r="P3">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q3">
-        <v>2.56</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S3">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="T3">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="V3">
         <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="X3">
         <v>10.5</v>
       </c>
       <c r="Y3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>840</v>
       </c>
       <c r="AB3">
         <v>5.5</v>
       </c>
       <c r="AC3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AE3">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="AF3">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AG3">
         <v>12</v>
       </c>
       <c r="AH3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AI3">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="AJ3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK3">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL3">
         <v>85</v>
       </c>
       <c r="AM3">
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="AN3">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>810</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AR3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS3">
-        <v>12.5</v>
+        <v>75</v>
       </c>
       <c r="AT3">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AU3">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="BA3">
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC3">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BE3">
+        <v>75</v>
+      </c>
+      <c r="BF3">
+        <v>9.6</v>
+      </c>
+      <c r="BG3">
         <v>100</v>
       </c>
-      <c r="BF3">
-        <v>10.5</v>
-      </c>
-      <c r="BG3">
-        <v>60</v>
-      </c>
       <c r="BH3">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="BJ3">
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
@@ -1470,16 +1482,16 @@
         <v>11</v>
       </c>
       <c r="BN3">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BP3">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1488,10 +1500,10 @@
         <v>9</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BV3">
         <v>1000</v>
@@ -1506,13 +1518,13 @@
         <v>10.5</v>
       </c>
       <c r="BZ3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="CA3">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="CB3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1520,34 +1532,34 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="G4">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H4">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
         <v>1.5</v>
@@ -1556,25 +1568,25 @@
         <v>1.1</v>
       </c>
       <c r="N4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S4">
         <v>4.5</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="U4">
         <v>1.84</v>
@@ -1583,13 +1595,13 @@
         <v>1.23</v>
       </c>
       <c r="W4">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="X4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z4">
         <v>38</v>
@@ -1598,10 +1610,10 @@
         <v>150</v>
       </c>
       <c r="AB4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>21</v>
@@ -1616,7 +1628,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI4">
         <v>100</v>
@@ -1628,13 +1640,13 @@
         <v>24</v>
       </c>
       <c r="AL4">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM4">
         <v>190</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO4">
         <v>130</v>
@@ -1649,22 +1661,22 @@
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY4">
         <v>9.4</v>
@@ -1676,22 +1688,22 @@
         <v>44</v>
       </c>
       <c r="BB4">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE4">
-        <v>10.5</v>
+        <v>16</v>
       </c>
       <c r="BF4">
+        <v>16.5</v>
+      </c>
+      <c r="BG4">
         <v>15.5</v>
-      </c>
-      <c r="BG4">
-        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
@@ -1721,10 +1733,10 @@
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS4">
         <v>11.5</v>
@@ -1733,16 +1745,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BW4">
         <v>13</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4">
         <v>14</v>
@@ -1754,7 +1766,7 @@
         <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1762,25 +1774,25 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F5">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G5">
         <v>1.59</v>
       </c>
       <c r="H5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I5">
         <v>7.4</v>
@@ -1789,37 +1801,37 @@
         <v>4.4</v>
       </c>
       <c r="K5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O5">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="S5">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U5">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V5">
         <v>1.16</v>
@@ -1828,7 +1840,7 @@
         <v>2.66</v>
       </c>
       <c r="X5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y5">
         <v>34</v>
@@ -1840,70 +1852,70 @@
         <v>200</v>
       </c>
       <c r="AB5">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD5">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI5">
         <v>80</v>
       </c>
       <c r="AJ5">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AK5">
         <v>18</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5">
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AQ5">
-        <v>19.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR5">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS5">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT5">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AU5">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
         <v>18</v>
       </c>
       <c r="AW5">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="AX5">
         <v>8</v>
@@ -1912,10 +1924,10 @@
         <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA5">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB5">
         <v>10.5</v>
@@ -1924,19 +1936,19 @@
         <v>11</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE5">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF5">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BI5">
         <v>3.4</v>
@@ -1945,58 +1957,58 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT5">
         <v>11</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BZ5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA5">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="CB5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2004,19 +2016,19 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E6" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="F6">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G6">
         <v>2.56</v>
@@ -2025,10 +2037,10 @@
         <v>3.75</v>
       </c>
       <c r="I6">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J6">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="K6">
         <v>2.94</v>
@@ -2040,142 +2052,142 @@
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="P6">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Q6">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R6">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S6">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W6">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X6">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y6">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z6">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA6">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
+        <v>6.4</v>
+      </c>
+      <c r="AC6">
         <v>7.2</v>
       </c>
-      <c r="AC6">
-        <v>8.6</v>
-      </c>
       <c r="AD6">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AE6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG6">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>950</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AK6">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AL6">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
         <v>410</v>
       </c>
       <c r="AN6">
-        <v>60</v>
+        <v>240</v>
       </c>
       <c r="AO6">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ6">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR6">
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>5.7</v>
+        <v>34</v>
       </c>
       <c r="AT6">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU6">
         <v>6.4</v>
       </c>
       <c r="AV6">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW6">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
       </c>
       <c r="AY6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ6">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="BA6">
-        <v>5.7</v>
+        <v>42</v>
       </c>
       <c r="BB6">
-        <v>5.3</v>
+        <v>23</v>
       </c>
       <c r="BC6">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="BD6">
-        <v>5.6</v>
+        <v>38</v>
       </c>
       <c r="BE6">
-        <v>5.8</v>
+        <v>90</v>
       </c>
       <c r="BF6">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="BG6">
-        <v>5.7</v>
+        <v>40</v>
       </c>
       <c r="BH6">
         <v>2.42</v>
@@ -2187,16 +2199,16 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO6">
         <v>3.9</v>
@@ -2205,13 +2217,13 @@
         <v>26</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
@@ -2223,22 +2235,22 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2246,241 +2258,241 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="F7">
-        <v>1.04</v>
+        <v>1.23</v>
       </c>
       <c r="G7">
-        <v>1000</v>
+        <v>1.31</v>
       </c>
       <c r="H7">
         <v>1.04</v>
       </c>
       <c r="I7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="J7">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="K7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M7">
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O7">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P7">
         <v>1.25</v>
       </c>
       <c r="Q7">
+        <v>1.28</v>
+      </c>
+      <c r="R7">
+        <v>1.86</v>
+      </c>
+      <c r="S7">
+        <v>1.79</v>
+      </c>
+      <c r="T7">
+        <v>1.75</v>
+      </c>
+      <c r="U7">
+        <v>2.08</v>
+      </c>
+      <c r="V7">
         <v>1.07</v>
       </c>
-      <c r="R7">
-        <v>1.25</v>
-      </c>
-      <c r="S7">
-        <v>1.06</v>
-      </c>
-      <c r="T7">
-        <v>1.11</v>
-      </c>
-      <c r="U7">
-        <v>1.11</v>
-      </c>
-      <c r="V7">
-        <v>1.01</v>
-      </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB7" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2488,37 +2500,37 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E8" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F8">
-        <v>1.02</v>
+        <v>1.81</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H8">
-        <v>1.02</v>
+        <v>2.78</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J8">
-        <v>1.02</v>
+        <v>3.15</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M8">
         <v>1.01</v>
@@ -2527,25 +2539,25 @@
         <v>1.1</v>
       </c>
       <c r="O8">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="P8">
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R8">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="S8">
-        <v>1.05</v>
+        <v>1.84</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>1.42</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="V8">
         <v>1.01</v>
@@ -2554,175 +2566,175 @@
         <v>1.01</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>3.45</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>3.6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>5.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2730,241 +2742,241 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F9">
-        <v>1.02</v>
+        <v>3.25</v>
       </c>
       <c r="G9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="H9">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="I9">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="J9">
-        <v>1.02</v>
+        <v>3.4</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M9">
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="P9">
-        <v>1.08</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>1.06</v>
+        <v>1.27</v>
       </c>
       <c r="R9">
-        <v>1.08</v>
+        <v>1.99</v>
       </c>
       <c r="S9">
-        <v>1.07</v>
+        <v>1.66</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.35</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>3</v>
       </c>
       <c r="V9">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="W9">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC9">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF9">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG9">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AH9">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ9">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AK9">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AN9">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AP9">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AQ9">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AU9">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV9">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX9">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AZ9">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB9">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG9">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="CB9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2972,16 +2984,16 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -3206,7 +3218,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3214,34 +3226,34 @@
         <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="F11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3250,7 +3262,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O11">
         <v>1.09</v>
@@ -3265,7 +3277,7 @@
         <v>1.25</v>
       </c>
       <c r="S11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3274,10 +3286,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3334,52 +3346,52 @@
         <v>1000</v>
       </c>
       <c r="AP11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
         <v>1.01</v>
@@ -3448,7 +3460,7 @@
         <v>1.04</v>
       </c>
       <c r="CB11" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3456,34 +3468,34 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="H12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="J12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>1.01</v>
@@ -3492,7 +3504,7 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O12">
         <v>1.06</v>
@@ -3516,10 +3528,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3576,52 +3588,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3690,7 +3702,7 @@
         <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3698,34 +3710,34 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E13" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="F13">
         <v>1.02</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="H13">
         <v>1.02</v>
       </c>
       <c r="I13">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J13">
         <v>1.02</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -3818,52 +3830,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3932,66 +3944,66 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D14" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F14">
+        <v>1.06</v>
+      </c>
+      <c r="G14">
+        <v>990</v>
+      </c>
+      <c r="H14">
+        <v>1.03</v>
+      </c>
+      <c r="I14">
+        <v>990</v>
+      </c>
+      <c r="J14">
+        <v>1.07</v>
+      </c>
+      <c r="K14">
+        <v>950</v>
+      </c>
+      <c r="L14">
+        <v>1.01</v>
+      </c>
+      <c r="M14">
+        <v>1.01</v>
+      </c>
+      <c r="N14">
+        <v>1.25</v>
+      </c>
+      <c r="O14">
         <v>1.04</v>
       </c>
-      <c r="G14">
-        <v>1000</v>
-      </c>
-      <c r="H14">
-        <v>1.04</v>
-      </c>
-      <c r="I14">
-        <v>1000</v>
-      </c>
-      <c r="J14">
-        <v>1.02</v>
-      </c>
-      <c r="K14">
-        <v>1000</v>
-      </c>
-      <c r="L14">
-        <v>1.01</v>
-      </c>
-      <c r="M14">
-        <v>1.01</v>
-      </c>
-      <c r="N14">
-        <v>1.26</v>
-      </c>
-      <c r="O14">
-        <v>1.13</v>
-      </c>
       <c r="P14">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="R14">
         <v>1.25</v>
       </c>
       <c r="S14">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="T14">
         <v>1.11</v>
@@ -4000,10 +4012,10 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4060,52 +4072,52 @@
         <v>1000</v>
       </c>
       <c r="AP14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF14">
         <v>1.01</v>
@@ -4174,7 +4186,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4182,483 +4194,483 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>3</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="J15">
-        <v>1.02</v>
+        <v>3.9</v>
       </c>
       <c r="K15">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O15">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q15">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.65</v>
       </c>
       <c r="S15">
-        <v>1.05</v>
+        <v>2.1</v>
       </c>
       <c r="T15">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U15">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BI15">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK15">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.04</v>
+        <v>9.4</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO15">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU15">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="CA15">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="CB15" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="F16">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="G16">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H16">
-        <v>1.02</v>
+        <v>2.68</v>
       </c>
       <c r="I16">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J16">
-        <v>1.02</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O16">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q16">
-        <v>1.03</v>
+        <v>1.41</v>
       </c>
       <c r="R16">
-        <v>1.25</v>
+        <v>1.66</v>
       </c>
       <c r="S16">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="T16">
-        <v>1.11</v>
+        <v>1.43</v>
       </c>
       <c r="U16">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="V16">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="W16">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AP16">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AQ16">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AR16">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AS16">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT16">
-        <v>1.03</v>
+        <v>3.55</v>
       </c>
       <c r="AU16">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV16">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW16">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AX16">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AY16">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AZ16">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="BA16">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="BB16">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BC16">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="BD16">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BE16">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BI16">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO16">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BQ16">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS16">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU16">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY16">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA16">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="CB16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4666,31 +4678,31 @@
         <v>80</v>
       </c>
       <c r="B17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F17">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G17">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H17">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I17">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J17">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="K17">
         <v>3.05</v>
@@ -4699,7 +4711,7 @@
         <v>1.67</v>
       </c>
       <c r="M17">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N17">
         <v>2.36</v>
@@ -4711,10 +4723,10 @@
         <v>1.43</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="R17">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S17">
         <v>7.2</v>
@@ -4726,16 +4738,16 @@
         <v>1.63</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W17">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X17">
         <v>7.2</v>
       </c>
       <c r="Y17">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z17">
         <v>27</v>
@@ -4747,19 +4759,19 @@
         <v>6.2</v>
       </c>
       <c r="AC17">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE17">
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG17">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH17">
         <v>32</v>
@@ -4777,34 +4789,34 @@
         <v>1000</v>
       </c>
       <c r="AM17">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="AN17">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ17">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AT17">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW17">
         <v>34</v>
@@ -4813,19 +4825,19 @@
         <v>11</v>
       </c>
       <c r="AY17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BA17">
         <v>42</v>
       </c>
       <c r="BB17">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BC17">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="BD17">
         <v>36</v>
@@ -4834,10 +4846,10 @@
         <v>50</v>
       </c>
       <c r="BF17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BG17">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH17">
         <v>2.5</v>
@@ -4849,16 +4861,16 @@
         <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>16</v>
+        <v>2.18</v>
       </c>
       <c r="BN17">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BO17">
         <v>4.3</v>
@@ -4867,13 +4879,13 @@
         <v>22</v>
       </c>
       <c r="BQ17">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT17">
         <v>7.2</v>
@@ -4885,939 +4897,939 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
+        <v>2.14</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
         <v>14</v>
       </c>
-      <c r="BZ17">
-        <v>1000</v>
-      </c>
-      <c r="CA17">
-        <v>13</v>
-      </c>
       <c r="CB17" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N18">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O18">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>1.62</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R18">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S18">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="T18">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U18">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V18">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W18">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y18">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC18">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD18">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG18">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ18">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK18">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM18">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN18">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP18">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR18">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU18">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW18">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX18">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AZ18">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA18">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC18">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD18">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF18">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG18">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="CB18" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="E19" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F19">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="G19">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="L19">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>1.1</v>
+      </c>
+      <c r="O19">
+        <v>1.01</v>
+      </c>
+      <c r="P19">
+        <v>1.24</v>
+      </c>
+      <c r="Q19">
+        <v>1.01</v>
+      </c>
+      <c r="R19">
+        <v>1.18</v>
+      </c>
+      <c r="S19">
         <v>1.13</v>
       </c>
-      <c r="N19">
-        <v>2.5</v>
-      </c>
-      <c r="O19">
-        <v>1.59</v>
-      </c>
-      <c r="P19">
-        <v>1.57</v>
-      </c>
-      <c r="Q19">
-        <v>2.72</v>
-      </c>
-      <c r="R19">
-        <v>1.19</v>
-      </c>
-      <c r="S19">
-        <v>5.7</v>
-      </c>
       <c r="T19">
-        <v>2.22</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="W19">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X19">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ19">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>7</v>
+        <v>1.04</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>16</v>
+        <v>1.04</v>
       </c>
       <c r="BN19">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT19">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV19">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ19">
         <v>1000</v>
       </c>
       <c r="CA19">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D20" t="s">
+        <v>122</v>
+      </c>
+      <c r="E20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F20">
+        <v>3.95</v>
+      </c>
+      <c r="G20">
+        <v>4.4</v>
+      </c>
+      <c r="H20">
+        <v>2.16</v>
+      </c>
+      <c r="I20">
+        <v>2.3</v>
+      </c>
+      <c r="J20">
+        <v>3.15</v>
+      </c>
+      <c r="K20">
+        <v>3.3</v>
+      </c>
+      <c r="L20">
+        <v>1.49</v>
+      </c>
+      <c r="M20">
+        <v>1.13</v>
+      </c>
+      <c r="N20">
+        <v>2.52</v>
+      </c>
+      <c r="O20">
+        <v>1.58</v>
+      </c>
+      <c r="P20">
+        <v>1.57</v>
+      </c>
+      <c r="Q20">
+        <v>2.7</v>
+      </c>
+      <c r="R20">
+        <v>1.19</v>
+      </c>
+      <c r="S20">
+        <v>5.7</v>
+      </c>
+      <c r="T20">
+        <v>2.2</v>
+      </c>
+      <c r="U20">
+        <v>1.73</v>
+      </c>
+      <c r="V20">
+        <v>1.77</v>
+      </c>
+      <c r="W20">
+        <v>1.3</v>
+      </c>
+      <c r="X20">
+        <v>8.6</v>
+      </c>
+      <c r="Y20">
+        <v>8</v>
+      </c>
+      <c r="Z20">
+        <v>15.5</v>
+      </c>
+      <c r="AA20">
+        <v>38</v>
+      </c>
+      <c r="AB20">
+        <v>11</v>
+      </c>
+      <c r="AC20">
+        <v>7.8</v>
+      </c>
+      <c r="AD20">
+        <v>14.5</v>
+      </c>
+      <c r="AE20">
+        <v>40</v>
+      </c>
+      <c r="AF20">
+        <v>36</v>
+      </c>
+      <c r="AG20">
+        <v>970</v>
+      </c>
+      <c r="AH20">
+        <v>950</v>
+      </c>
+      <c r="AI20">
+        <v>80</v>
+      </c>
+      <c r="AJ20">
+        <v>130</v>
+      </c>
+      <c r="AK20">
+        <v>90</v>
+      </c>
+      <c r="AL20">
         <v>120</v>
       </c>
-      <c r="E20" t="s">
-        <v>142</v>
-      </c>
-      <c r="F20">
-        <v>1.73</v>
-      </c>
-      <c r="G20">
-        <v>1.78</v>
-      </c>
-      <c r="H20">
+      <c r="AM20">
+        <v>260</v>
+      </c>
+      <c r="AN20">
+        <v>140</v>
+      </c>
+      <c r="AO20">
+        <v>40</v>
+      </c>
+      <c r="AP20">
+        <v>7.4</v>
+      </c>
+      <c r="AQ20">
+        <v>5.9</v>
+      </c>
+      <c r="AR20">
+        <v>11</v>
+      </c>
+      <c r="AS20">
         <v>5.6</v>
       </c>
-      <c r="I20">
+      <c r="AT20">
+        <v>9.4</v>
+      </c>
+      <c r="AU20">
+        <v>6.8</v>
+      </c>
+      <c r="AV20">
+        <v>10</v>
+      </c>
+      <c r="AW20">
+        <v>5.6</v>
+      </c>
+      <c r="AX20">
+        <v>5.5</v>
+      </c>
+      <c r="AY20">
+        <v>16</v>
+      </c>
+      <c r="AZ20">
+        <v>21</v>
+      </c>
+      <c r="BA20">
+        <v>6</v>
+      </c>
+      <c r="BB20">
+        <v>6</v>
+      </c>
+      <c r="BC20">
         <v>5.9</v>
       </c>
-      <c r="J20">
-        <v>3.85</v>
-      </c>
-      <c r="K20">
-        <v>4</v>
-      </c>
-      <c r="L20">
-        <v>1.42</v>
-      </c>
-      <c r="M20">
-        <v>1.08</v>
-      </c>
-      <c r="N20">
-        <v>3.55</v>
-      </c>
-      <c r="O20">
-        <v>1.35</v>
-      </c>
-      <c r="P20">
-        <v>1.87</v>
-      </c>
-      <c r="Q20">
-        <v>2.02</v>
-      </c>
-      <c r="R20">
-        <v>1.33</v>
-      </c>
-      <c r="S20">
-        <v>3.65</v>
-      </c>
-      <c r="T20">
-        <v>1.94</v>
-      </c>
-      <c r="U20">
-        <v>1.94</v>
-      </c>
-      <c r="V20">
-        <v>1.2</v>
-      </c>
-      <c r="W20">
-        <v>2.28</v>
-      </c>
-      <c r="X20">
-        <v>13.5</v>
-      </c>
-      <c r="Y20">
-        <v>18</v>
-      </c>
-      <c r="Z20">
-        <v>55</v>
-      </c>
-      <c r="AA20">
-        <v>170</v>
-      </c>
-      <c r="AB20">
-        <v>8</v>
-      </c>
-      <c r="AC20">
-        <v>10.5</v>
-      </c>
-      <c r="AD20">
-        <v>23</v>
-      </c>
-      <c r="AE20">
-        <v>95</v>
-      </c>
-      <c r="AF20">
-        <v>12</v>
-      </c>
-      <c r="AG20">
-        <v>11.5</v>
-      </c>
-      <c r="AH20">
-        <v>24</v>
-      </c>
-      <c r="AI20">
-        <v>95</v>
-      </c>
-      <c r="AJ20">
-        <v>21</v>
-      </c>
-      <c r="AK20">
-        <v>23</v>
-      </c>
-      <c r="AL20">
-        <v>46</v>
-      </c>
-      <c r="AM20">
-        <v>150</v>
-      </c>
-      <c r="AN20">
-        <v>14</v>
-      </c>
-      <c r="AO20">
-        <v>120</v>
-      </c>
-      <c r="AP20">
-        <v>11.5</v>
-      </c>
-      <c r="AQ20">
-        <v>15.5</v>
-      </c>
-      <c r="AR20">
-        <v>5.9</v>
-      </c>
-      <c r="AS20">
-        <v>6.4</v>
-      </c>
-      <c r="AT20">
-        <v>7</v>
-      </c>
-      <c r="AU20">
-        <v>7.6</v>
-      </c>
-      <c r="AV20">
-        <v>19.5</v>
-      </c>
-      <c r="AW20">
-        <v>6.2</v>
-      </c>
-      <c r="AX20">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY20">
-        <v>9</v>
-      </c>
-      <c r="AZ20">
-        <v>18</v>
-      </c>
-      <c r="BA20">
-        <v>6.2</v>
-      </c>
-      <c r="BB20">
-        <v>16</v>
-      </c>
-      <c r="BC20">
-        <v>17.5</v>
-      </c>
       <c r="BD20">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE20">
         <v>6.2</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="BG20">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH20">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="BI20">
-        <v>2.78</v>
+        <v>2.3</v>
       </c>
       <c r="BJ20">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK20">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>15</v>
+        <v>2.28</v>
       </c>
       <c r="BN20">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BO20">
-        <v>3.45</v>
+        <v>5.4</v>
       </c>
       <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
         <v>12</v>
       </c>
-      <c r="BQ20">
-        <v>6.8</v>
-      </c>
       <c r="BR20">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT20">
-        <v>9</v>
+        <v>4.8</v>
       </c>
       <c r="BU20">
-        <v>5.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW20">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
         <v>12.5</v>
       </c>
-      <c r="BX20">
-        <v>1000</v>
-      </c>
-      <c r="BY20">
-        <v>13</v>
-      </c>
       <c r="BZ20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="CB20" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="F21">
-        <v>4.3</v>
+        <v>1.73</v>
       </c>
       <c r="G21">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="H21">
-        <v>1.96</v>
+        <v>5.5</v>
       </c>
       <c r="I21">
-        <v>2</v>
+        <v>5.8</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K21">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M21">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O21">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P21">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="Q21">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R21">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T21">
-        <v>1.84</v>
+        <v>1.97</v>
       </c>
       <c r="U21">
-        <v>2.16</v>
+        <v>1.95</v>
       </c>
       <c r="V21">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="W21">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="X21">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="Z21">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AA21">
+        <v>180</v>
+      </c>
+      <c r="AB21">
+        <v>8</v>
+      </c>
+      <c r="AC21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD21">
+        <v>26</v>
+      </c>
+      <c r="AE21">
+        <v>100</v>
+      </c>
+      <c r="AF21">
+        <v>10.5</v>
+      </c>
+      <c r="AG21">
+        <v>10.5</v>
+      </c>
+      <c r="AH21">
+        <v>25</v>
+      </c>
+      <c r="AI21">
+        <v>100</v>
+      </c>
+      <c r="AJ21">
         <v>22</v>
       </c>
-      <c r="AB21">
+      <c r="AK21">
+        <v>23</v>
+      </c>
+      <c r="AL21">
+        <v>46</v>
+      </c>
+      <c r="AM21">
+        <v>150</v>
+      </c>
+      <c r="AN21">
+        <v>12.5</v>
+      </c>
+      <c r="AO21">
+        <v>130</v>
+      </c>
+      <c r="AP21">
+        <v>11.5</v>
+      </c>
+      <c r="AQ21">
         <v>15.5</v>
       </c>
-      <c r="AC21">
+      <c r="AR21">
+        <v>7.6</v>
+      </c>
+      <c r="AS21">
+        <v>8.4</v>
+      </c>
+      <c r="AT21">
+        <v>7.2</v>
+      </c>
+      <c r="AU21">
+        <v>7.8</v>
+      </c>
+      <c r="AV21">
+        <v>19.5</v>
+      </c>
+      <c r="AW21">
+        <v>8</v>
+      </c>
+      <c r="AX21">
+        <v>9</v>
+      </c>
+      <c r="AY21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21">
+        <v>18.5</v>
+      </c>
+      <c r="BA21">
+        <v>8</v>
+      </c>
+      <c r="BB21">
+        <v>16</v>
+      </c>
+      <c r="BC21">
+        <v>17</v>
+      </c>
+      <c r="BD21">
+        <v>7.4</v>
+      </c>
+      <c r="BE21">
+        <v>8.4</v>
+      </c>
+      <c r="BF21">
+        <v>11</v>
+      </c>
+      <c r="BG21">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD21">
-        <v>11</v>
-      </c>
-      <c r="AE21">
-        <v>21</v>
-      </c>
-      <c r="AF21">
-        <v>34</v>
-      </c>
-      <c r="AG21">
-        <v>18</v>
-      </c>
-      <c r="AH21">
-        <v>18.5</v>
-      </c>
-      <c r="AI21">
-        <v>38</v>
-      </c>
-      <c r="AJ21">
-        <v>95</v>
-      </c>
-      <c r="AK21">
-        <v>55</v>
-      </c>
-      <c r="AL21">
-        <v>60</v>
-      </c>
-      <c r="AM21">
-        <v>110</v>
-      </c>
-      <c r="AN21">
-        <v>65</v>
-      </c>
-      <c r="AO21">
-        <v>14.5</v>
-      </c>
-      <c r="AP21">
-        <v>13</v>
-      </c>
-      <c r="AQ21">
-        <v>8.6</v>
-      </c>
-      <c r="AR21">
+      <c r="BH21">
+        <v>3.3</v>
+      </c>
+      <c r="BI21">
+        <v>3.05</v>
+      </c>
+      <c r="BJ21">
         <v>10.5</v>
       </c>
-      <c r="AS21">
-        <v>20</v>
-      </c>
-      <c r="AT21">
-        <v>14</v>
-      </c>
-      <c r="AU21">
-        <v>7.6</v>
-      </c>
-      <c r="AV21">
-        <v>9.6</v>
-      </c>
-      <c r="AW21">
-        <v>18.5</v>
-      </c>
-      <c r="AX21">
-        <v>24</v>
-      </c>
-      <c r="AY21">
-        <v>15</v>
-      </c>
-      <c r="AZ21">
-        <v>16.5</v>
-      </c>
-      <c r="BA21">
-        <v>32</v>
-      </c>
-      <c r="BB21">
-        <v>15</v>
-      </c>
-      <c r="BC21">
-        <v>48</v>
-      </c>
-      <c r="BD21">
-        <v>50</v>
-      </c>
-      <c r="BE21">
-        <v>15.5</v>
-      </c>
-      <c r="BF21">
-        <v>50</v>
-      </c>
-      <c r="BG21">
-        <v>12.5</v>
-      </c>
-      <c r="BH21">
-        <v>3.45</v>
-      </c>
-      <c r="BI21">
-        <v>3.2</v>
-      </c>
-      <c r="BJ21">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL21">
         <v>1000</v>
@@ -5826,49 +5838,49 @@
         <v>15.5</v>
       </c>
       <c r="BN21">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="BP21">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BQ21">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="BR21">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS21">
+        <v>10.5</v>
+      </c>
+      <c r="BT21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU21">
+        <v>6</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
         <v>12.5</v>
       </c>
-      <c r="BT21">
-        <v>4.7</v>
-      </c>
-      <c r="BU21">
-        <v>4.2</v>
-      </c>
-      <c r="BV21">
-        <v>14</v>
-      </c>
-      <c r="BW21">
-        <v>7.8</v>
-      </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BZ21">
         <v>25</v>
       </c>
       <c r="CA21">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CB21" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5876,483 +5888,725 @@
         <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F22">
-        <v>1.91</v>
+        <v>4.3</v>
       </c>
       <c r="G22">
-        <v>2.04</v>
+        <v>4.5</v>
       </c>
       <c r="H22">
-        <v>4.3</v>
+        <v>1.96</v>
       </c>
       <c r="I22">
-        <v>5</v>
+        <v>1.98</v>
       </c>
       <c r="J22">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L22">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M22">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N22">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O22">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="P22">
-        <v>1.71</v>
+        <v>1.97</v>
       </c>
       <c r="Q22">
-        <v>2.18</v>
+        <v>1.97</v>
       </c>
       <c r="R22">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S22">
+        <v>3.5</v>
+      </c>
+      <c r="T22">
+        <v>1.84</v>
+      </c>
+      <c r="U22">
+        <v>2.1</v>
+      </c>
+      <c r="V22">
+        <v>2.02</v>
+      </c>
+      <c r="W22">
+        <v>1.28</v>
+      </c>
+      <c r="X22">
+        <v>14.5</v>
+      </c>
+      <c r="Y22">
+        <v>9.4</v>
+      </c>
+      <c r="Z22">
+        <v>12</v>
+      </c>
+      <c r="AA22">
+        <v>22</v>
+      </c>
+      <c r="AB22">
+        <v>15.5</v>
+      </c>
+      <c r="AC22">
+        <v>8.4</v>
+      </c>
+      <c r="AD22">
+        <v>10.5</v>
+      </c>
+      <c r="AE22">
+        <v>21</v>
+      </c>
+      <c r="AF22">
+        <v>34</v>
+      </c>
+      <c r="AG22">
+        <v>17.5</v>
+      </c>
+      <c r="AH22">
+        <v>19</v>
+      </c>
+      <c r="AI22">
+        <v>38</v>
+      </c>
+      <c r="AJ22">
+        <v>95</v>
+      </c>
+      <c r="AK22">
+        <v>55</v>
+      </c>
+      <c r="AL22">
+        <v>65</v>
+      </c>
+      <c r="AM22">
+        <v>110</v>
+      </c>
+      <c r="AN22">
+        <v>65</v>
+      </c>
+      <c r="AO22">
+        <v>14</v>
+      </c>
+      <c r="AP22">
+        <v>12.5</v>
+      </c>
+      <c r="AQ22">
+        <v>8.6</v>
+      </c>
+      <c r="AR22">
+        <v>10.5</v>
+      </c>
+      <c r="AS22">
+        <v>20</v>
+      </c>
+      <c r="AT22">
+        <v>14</v>
+      </c>
+      <c r="AU22">
+        <v>7.6</v>
+      </c>
+      <c r="AV22">
+        <v>9.6</v>
+      </c>
+      <c r="AW22">
+        <v>18</v>
+      </c>
+      <c r="AX22">
+        <v>25</v>
+      </c>
+      <c r="AY22">
+        <v>15.5</v>
+      </c>
+      <c r="AZ22">
+        <v>17</v>
+      </c>
+      <c r="BA22">
+        <v>32</v>
+      </c>
+      <c r="BB22">
+        <v>14.5</v>
+      </c>
+      <c r="BC22">
+        <v>48</v>
+      </c>
+      <c r="BD22">
+        <v>50</v>
+      </c>
+      <c r="BE22">
+        <v>14.5</v>
+      </c>
+      <c r="BF22">
+        <v>44</v>
+      </c>
+      <c r="BG22">
+        <v>12.5</v>
+      </c>
+      <c r="BH22">
+        <v>3.45</v>
+      </c>
+      <c r="BI22">
+        <v>3.15</v>
+      </c>
+      <c r="BJ22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK22">
+        <v>6.2</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>16</v>
+      </c>
+      <c r="BN22">
+        <v>7.6</v>
+      </c>
+      <c r="BO22">
+        <v>5.5</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>12</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>13</v>
+      </c>
+      <c r="BT22">
+        <v>4.6</v>
+      </c>
+      <c r="BU22">
         <v>4.2</v>
       </c>
-      <c r="T22">
-        <v>1.97</v>
-      </c>
-      <c r="U22">
-        <v>1.89</v>
-      </c>
-      <c r="V22">
-        <v>1.25</v>
-      </c>
-      <c r="W22">
-        <v>1.96</v>
-      </c>
-      <c r="X22">
+      <c r="BV22">
         <v>14</v>
       </c>
-      <c r="Y22">
-        <v>17</v>
-      </c>
-      <c r="Z22">
-        <v>42</v>
-      </c>
-      <c r="AA22">
-        <v>140</v>
-      </c>
-      <c r="AB22">
-        <v>9</v>
-      </c>
-      <c r="AC22">
-        <v>9.6</v>
-      </c>
-      <c r="AD22">
-        <v>23</v>
-      </c>
-      <c r="AE22">
-        <v>85</v>
-      </c>
-      <c r="AF22">
-        <v>14</v>
-      </c>
-      <c r="AG22">
-        <v>12.5</v>
-      </c>
-      <c r="AH22">
-        <v>27</v>
-      </c>
-      <c r="AI22">
-        <v>100</v>
-      </c>
-      <c r="AJ22">
-        <v>29</v>
-      </c>
-      <c r="AK22">
-        <v>29</v>
-      </c>
-      <c r="AL22">
-        <v>55</v>
-      </c>
-      <c r="AM22">
-        <v>180</v>
-      </c>
-      <c r="AN22">
-        <v>23</v>
-      </c>
-      <c r="AO22">
-        <v>120</v>
-      </c>
-      <c r="AP22">
-        <v>8.6</v>
-      </c>
-      <c r="AQ22">
-        <v>10</v>
-      </c>
-      <c r="AR22">
-        <v>4</v>
-      </c>
-      <c r="AS22">
-        <v>4.3</v>
-      </c>
-      <c r="AT22">
-        <v>5.7</v>
-      </c>
-      <c r="AU22">
-        <v>6</v>
-      </c>
-      <c r="AV22">
-        <v>13.5</v>
-      </c>
-      <c r="AW22">
-        <v>4.2</v>
-      </c>
-      <c r="AX22">
-        <v>8.4</v>
-      </c>
-      <c r="AY22">
+      <c r="BW22">
         <v>7.8</v>
       </c>
-      <c r="AZ22">
-        <v>15.5</v>
-      </c>
-      <c r="BA22">
-        <v>4.2</v>
-      </c>
-      <c r="BB22">
-        <v>17</v>
-      </c>
-      <c r="BC22">
-        <v>17</v>
-      </c>
-      <c r="BD22">
-        <v>4.1</v>
-      </c>
-      <c r="BE22">
-        <v>4.3</v>
-      </c>
-      <c r="BF22">
-        <v>13.5</v>
-      </c>
-      <c r="BG22">
-        <v>4.2</v>
-      </c>
-      <c r="BH22">
-        <v>3.1</v>
-      </c>
-      <c r="BI22">
-        <v>2.78</v>
-      </c>
-      <c r="BJ22">
-        <v>11</v>
-      </c>
-      <c r="BK22">
-        <v>6</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>12.5</v>
-      </c>
-      <c r="BN22">
-        <v>4.6</v>
-      </c>
-      <c r="BO22">
-        <v>3.55</v>
-      </c>
-      <c r="BP22">
-        <v>15.5</v>
-      </c>
-      <c r="BQ22">
-        <v>7.2</v>
-      </c>
-      <c r="BR22">
-        <v>1000</v>
-      </c>
-      <c r="BS22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT22">
-        <v>7.8</v>
-      </c>
-      <c r="BU22">
-        <v>5.8</v>
-      </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
-        <v>10.5</v>
-      </c>
       <c r="BX22">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BY22">
         <v>11</v>
       </c>
       <c r="BZ22">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA22">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="CB22" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E23" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F23">
+        <v>1.95</v>
+      </c>
+      <c r="G23">
+        <v>2.16</v>
+      </c>
+      <c r="H23">
+        <v>3.8</v>
+      </c>
+      <c r="I23">
+        <v>4.8</v>
+      </c>
+      <c r="J23">
+        <v>3</v>
+      </c>
+      <c r="K23">
+        <v>3.65</v>
+      </c>
+      <c r="L23">
         <v>1.4</v>
       </c>
-      <c r="G23">
-        <v>1.51</v>
-      </c>
-      <c r="H23">
-        <v>7</v>
-      </c>
-      <c r="I23">
-        <v>8.6</v>
-      </c>
-      <c r="J23">
-        <v>5</v>
-      </c>
-      <c r="K23">
-        <v>6</v>
-      </c>
-      <c r="L23">
-        <v>1.23</v>
-      </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
-        <v>5.6</v>
+        <v>2.66</v>
       </c>
       <c r="O23">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="P23">
-        <v>2.56</v>
+        <v>1.68</v>
       </c>
       <c r="Q23">
-        <v>1.51</v>
+        <v>2.12</v>
       </c>
       <c r="R23">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="S23">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="T23">
-        <v>1.76</v>
+        <v>1.95</v>
       </c>
       <c r="U23">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="V23">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
-        <v>2.96</v>
+        <v>1.86</v>
       </c>
       <c r="X23">
-        <v>34</v>
+        <v>13.5</v>
       </c>
       <c r="Y23">
+        <v>16</v>
+      </c>
+      <c r="Z23">
         <v>40</v>
       </c>
-      <c r="Z23">
-        <v>85</v>
-      </c>
       <c r="AA23">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="AB23">
-        <v>13.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC23">
-        <v>15.5</v>
+        <v>9.6</v>
       </c>
       <c r="AD23">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="AE23">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF23">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG23">
         <v>13</v>
       </c>
       <c r="AH23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI23">
         <v>95</v>
       </c>
       <c r="AJ23">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="AK23">
-        <v>17.5</v>
+        <v>30</v>
       </c>
       <c r="AL23">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AM23">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AN23">
-        <v>6.2</v>
+        <v>25</v>
       </c>
       <c r="AO23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP23">
-        <v>19.5</v>
+        <v>3.25</v>
       </c>
       <c r="AQ23">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AR23">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AS23">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT23">
-        <v>1.03</v>
+        <v>2.94</v>
       </c>
       <c r="AU23">
-        <v>10.5</v>
+        <v>3</v>
       </c>
       <c r="AV23">
-        <v>1.03</v>
+        <v>3.6</v>
       </c>
       <c r="AW23">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX23">
-        <v>9</v>
+        <v>3.35</v>
       </c>
       <c r="AY23">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AZ23">
-        <v>18.5</v>
+        <v>3.7</v>
       </c>
       <c r="BA23">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB23">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="BC23">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BD23">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE23">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF23">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="BG23">
-        <v>65</v>
+        <v>4.1</v>
       </c>
       <c r="BH23">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="BI23">
-        <v>3.55</v>
+        <v>2.44</v>
       </c>
       <c r="BJ23">
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>1.04</v>
+        <v>2.4</v>
       </c>
       <c r="BN23">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BO23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BP23">
-        <v>8.800000000000001</v>
+        <v>16.5</v>
       </c>
       <c r="BQ23">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR23">
+        <v>36</v>
+      </c>
+      <c r="BS23">
+        <v>2.28</v>
+      </c>
+      <c r="BT23">
+        <v>7.8</v>
+      </c>
+      <c r="BU23">
+        <v>4.6</v>
+      </c>
+      <c r="BV23">
+        <v>42</v>
+      </c>
+      <c r="BW23">
+        <v>2.3</v>
+      </c>
+      <c r="BX23">
+        <v>60</v>
+      </c>
+      <c r="BY23">
+        <v>2.34</v>
+      </c>
+      <c r="BZ23">
+        <v>36</v>
+      </c>
+      <c r="CA23">
+        <v>2.28</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" t="s">
+        <v>89</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" t="s">
+        <v>126</v>
+      </c>
+      <c r="E24" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24">
+        <v>1.41</v>
+      </c>
+      <c r="G24">
+        <v>1.5</v>
+      </c>
+      <c r="H24">
+        <v>6.8</v>
+      </c>
+      <c r="I24">
+        <v>9.6</v>
+      </c>
+      <c r="J24">
+        <v>4.9</v>
+      </c>
+      <c r="K24">
+        <v>5.8</v>
+      </c>
+      <c r="L24">
+        <v>1.22</v>
+      </c>
+      <c r="M24">
+        <v>1.01</v>
+      </c>
+      <c r="N24">
+        <v>5.7</v>
+      </c>
+      <c r="O24">
+        <v>1.17</v>
+      </c>
+      <c r="P24">
+        <v>2.56</v>
+      </c>
+      <c r="Q24">
+        <v>1.51</v>
+      </c>
+      <c r="R24">
+        <v>1.63</v>
+      </c>
+      <c r="S24">
+        <v>2.28</v>
+      </c>
+      <c r="T24">
+        <v>1.72</v>
+      </c>
+      <c r="U24">
+        <v>2.08</v>
+      </c>
+      <c r="V24">
+        <v>1.11</v>
+      </c>
+      <c r="W24">
+        <v>3</v>
+      </c>
+      <c r="X24">
+        <v>34</v>
+      </c>
+      <c r="Y24">
+        <v>40</v>
+      </c>
+      <c r="Z24">
+        <v>85</v>
+      </c>
+      <c r="AA24">
+        <v>250</v>
+      </c>
+      <c r="AB24">
+        <v>14</v>
+      </c>
+      <c r="AC24">
+        <v>15.5</v>
+      </c>
+      <c r="AD24">
+        <v>34</v>
+      </c>
+      <c r="AE24">
+        <v>110</v>
+      </c>
+      <c r="AF24">
+        <v>13</v>
+      </c>
+      <c r="AG24">
+        <v>13</v>
+      </c>
+      <c r="AH24">
+        <v>27</v>
+      </c>
+      <c r="AI24">
+        <v>95</v>
+      </c>
+      <c r="AJ24">
+        <v>16.5</v>
+      </c>
+      <c r="AK24">
+        <v>17.5</v>
+      </c>
+      <c r="AL24">
+        <v>36</v>
+      </c>
+      <c r="AM24">
+        <v>120</v>
+      </c>
+      <c r="AN24">
+        <v>6.2</v>
+      </c>
+      <c r="AO24">
+        <v>110</v>
+      </c>
+      <c r="AP24">
+        <v>20</v>
+      </c>
+      <c r="AQ24">
+        <v>1.03</v>
+      </c>
+      <c r="AR24">
+        <v>1.01</v>
+      </c>
+      <c r="AS24">
+        <v>1.01</v>
+      </c>
+      <c r="AT24">
+        <v>8.6</v>
+      </c>
+      <c r="AU24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV24">
+        <v>20</v>
+      </c>
+      <c r="AW24">
+        <v>1.01</v>
+      </c>
+      <c r="AX24">
+        <v>7.8</v>
+      </c>
+      <c r="AY24">
+        <v>7.8</v>
+      </c>
+      <c r="AZ24">
+        <v>15.5</v>
+      </c>
+      <c r="BA24">
+        <v>1.01</v>
+      </c>
+      <c r="BB24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC24">
+        <v>10.5</v>
+      </c>
+      <c r="BD24">
+        <v>20</v>
+      </c>
+      <c r="BE24">
+        <v>1.01</v>
+      </c>
+      <c r="BF24">
+        <v>4</v>
+      </c>
+      <c r="BG24">
+        <v>1.01</v>
+      </c>
+      <c r="BH24">
+        <v>4.8</v>
+      </c>
+      <c r="BI24">
+        <v>3.55</v>
+      </c>
+      <c r="BJ24">
+        <v>10.5</v>
+      </c>
+      <c r="BK24">
+        <v>5</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>9</v>
+      </c>
+      <c r="BN24">
+        <v>4.5</v>
+      </c>
+      <c r="BO24">
+        <v>3.35</v>
+      </c>
+      <c r="BP24">
+        <v>9</v>
+      </c>
+      <c r="BQ24">
+        <v>4.7</v>
+      </c>
+      <c r="BR24">
         <v>21</v>
       </c>
-      <c r="BS23">
-        <v>1.04</v>
-      </c>
-      <c r="BT23">
+      <c r="BS24">
+        <v>6.6</v>
+      </c>
+      <c r="BT24">
+        <v>11.5</v>
+      </c>
+      <c r="BU24">
+        <v>5.3</v>
+      </c>
+      <c r="BV24">
+        <v>60</v>
+      </c>
+      <c r="BW24">
+        <v>8.4</v>
+      </c>
+      <c r="BX24">
+        <v>55</v>
+      </c>
+      <c r="BY24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ24">
         <v>12</v>
       </c>
-      <c r="BU23">
-        <v>1.04</v>
-      </c>
-      <c r="BV23">
-        <v>1000</v>
-      </c>
-      <c r="BW23">
-        <v>1.04</v>
-      </c>
-      <c r="BX23">
-        <v>1000</v>
-      </c>
-      <c r="BY23">
-        <v>1.04</v>
-      </c>
-      <c r="BZ23">
-        <v>12</v>
-      </c>
-      <c r="CA23">
-        <v>1.04</v>
-      </c>
-      <c r="CB23" t="s">
-        <v>146</v>
+      <c r="CA24">
+        <v>5.4</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -466,7 +466,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 10:20:43</t>
+    <t>2026-07-28 12:28:20</t>
   </si>
 </sst>
 </file>
@@ -1060,61 +1060,61 @@
         <v>127</v>
       </c>
       <c r="F2">
+        <v>2.34</v>
+      </c>
+      <c r="G2">
         <v>2.38</v>
       </c>
-      <c r="G2">
-        <v>2.42</v>
-      </c>
       <c r="H2">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I2">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="J2">
         <v>3.1</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L2">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="O2">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="R2">
         <v>1.2</v>
       </c>
       <c r="S2">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="T2">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="Y2">
         <v>11</v>
@@ -1123,19 +1123,19 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AB2">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC2">
         <v>7</v>
       </c>
       <c r="AD2">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE2">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AF2">
         <v>13.5</v>
@@ -1144,10 +1144,10 @@
         <v>11.5</v>
       </c>
       <c r="AH2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ2">
         <v>34</v>
@@ -1156,43 +1156,43 @@
         <v>34</v>
       </c>
       <c r="AL2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM2">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN2">
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP2">
         <v>8</v>
       </c>
       <c r="AQ2">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AR2">
         <v>22</v>
       </c>
       <c r="AS2">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AT2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
       </c>
       <c r="AV2">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW2">
         <v>50</v>
       </c>
       <c r="AX2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1204,82 +1204,82 @@
         <v>70</v>
       </c>
       <c r="BB2">
+        <v>29</v>
+      </c>
+      <c r="BC2">
         <v>28</v>
-      </c>
-      <c r="BC2">
-        <v>29</v>
       </c>
       <c r="BD2">
         <v>50</v>
       </c>
       <c r="BE2">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="BF2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BG2">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BH2">
         <v>2.8</v>
       </c>
       <c r="BI2">
-        <v>2.26</v>
+        <v>2.44</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BL2">
         <v>210</v>
       </c>
       <c r="BM2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BO2">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP2">
         <v>21</v>
       </c>
       <c r="BQ2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BR2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BS2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BV2">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BW2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BX2">
         <v>60</v>
       </c>
       <c r="BY2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BZ2">
         <v>50</v>
       </c>
       <c r="CA2">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="CB2" t="s">
         <v>150</v>
@@ -1311,7 +1311,7 @@
         <v>11</v>
       </c>
       <c r="I3">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J3">
         <v>4.6</v>
@@ -1326,31 +1326,31 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q3">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R3">
         <v>1.24</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="U3">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
         <v>3.25</v>
@@ -1368,7 +1368,7 @@
         <v>840</v>
       </c>
       <c r="AB3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AC3">
         <v>11.5</v>
@@ -1407,7 +1407,7 @@
         <v>10.5</v>
       </c>
       <c r="AO3">
-        <v>810</v>
+        <v>890</v>
       </c>
       <c r="AP3">
         <v>9.800000000000001</v>
@@ -1431,19 +1431,19 @@
         <v>44</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX3">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AY3">
         <v>11</v>
       </c>
       <c r="AZ3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="BB3">
         <v>10</v>
@@ -1452,76 +1452,76 @@
         <v>18.5</v>
       </c>
       <c r="BD3">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BF3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG3">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ3">
         <v>16.5</v>
       </c>
       <c r="BK3">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>3.55</v>
       </c>
       <c r="BO3">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BP3">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ3">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
         <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BZ3">
         <v>25</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB3" t="s">
         <v>150</v>
@@ -1547,13 +1547,13 @@
         <v>1.9</v>
       </c>
       <c r="G4">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="H4">
         <v>4.9</v>
       </c>
       <c r="I4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J4">
         <v>3.5</v>
@@ -1562,7 +1562,7 @@
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1574,7 +1574,7 @@
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q4">
         <v>2.36</v>
@@ -1583,16 +1583,16 @@
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T4">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V4">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W4">
         <v>2.06</v>
@@ -1601,7 +1601,7 @@
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4">
         <v>38</v>
@@ -1613,7 +1613,7 @@
         <v>7.2</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD4">
         <v>21</v>
@@ -1631,7 +1631,7 @@
         <v>23</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ4">
         <v>22</v>
@@ -1643,16 +1643,16 @@
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AN4">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO4">
         <v>130</v>
       </c>
       <c r="AP4">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
         <v>12.5</v>
@@ -1661,7 +1661,7 @@
         <v>32</v>
       </c>
       <c r="AS4">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AT4">
         <v>6.6</v>
@@ -1673,19 +1673,19 @@
         <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>70</v>
+        <v>15.5</v>
       </c>
       <c r="AX4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY4">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ4">
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>44</v>
+        <v>15.5</v>
       </c>
       <c r="BB4">
         <v>19.5</v>
@@ -1697,73 +1697,73 @@
         <v>42</v>
       </c>
       <c r="BE4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BF4">
         <v>16.5</v>
       </c>
       <c r="BG4">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BN4">
         <v>4.4</v>
       </c>
       <c r="BO4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BP4">
         <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>12.5</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BT4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BV4">
         <v>50</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BZ4">
         <v>34</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
         <v>150</v>
@@ -1786,52 +1786,52 @@
         <v>130</v>
       </c>
       <c r="F5">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G5">
         <v>1.59</v>
       </c>
       <c r="H5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I5">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
         <v>5.2</v>
       </c>
       <c r="L5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q5">
+        <v>1.62</v>
+      </c>
+      <c r="R5">
         <v>1.58</v>
       </c>
-      <c r="R5">
-        <v>1.63</v>
-      </c>
       <c r="S5">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="T5">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U5">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="V5">
         <v>1.16</v>
@@ -1840,10 +1840,10 @@
         <v>2.66</v>
       </c>
       <c r="X5">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Z5">
         <v>70</v>
@@ -1852,103 +1852,103 @@
         <v>200</v>
       </c>
       <c r="AB5">
+        <v>11.5</v>
+      </c>
+      <c r="AC5">
         <v>12</v>
       </c>
-      <c r="AC5">
-        <v>14</v>
-      </c>
       <c r="AD5">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF5">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI5">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AJ5">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK5">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL5">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN5">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AO5">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="AR5">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AS5">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW5">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY5">
         <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC5">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE5">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BI5">
         <v>3.4</v>
@@ -1957,55 +1957,55 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BN5">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
         <v>9.800000000000001</v>
       </c>
       <c r="BQ5">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BU5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ5">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="CA5">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="CB5" t="s">
         <v>150</v>
@@ -2031,7 +2031,7 @@
         <v>2.46</v>
       </c>
       <c r="G6">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H6">
         <v>3.75</v>
@@ -2052,28 +2052,28 @@
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="O6">
         <v>1.76</v>
       </c>
       <c r="P6">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S6">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="T6">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="V6">
         <v>1.34</v>
@@ -2082,7 +2082,7 @@
         <v>1.65</v>
       </c>
       <c r="X6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Y6">
         <v>8.800000000000001</v>
@@ -2112,25 +2112,25 @@
         <v>14.5</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AI6">
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK6">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AL6">
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AN6">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AO6">
         <v>1000</v>
@@ -2145,25 +2145,25 @@
         <v>21</v>
       </c>
       <c r="AS6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AT6">
         <v>5.9</v>
       </c>
       <c r="AU6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
         <v>17</v>
       </c>
       <c r="AW6">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
       </c>
       <c r="AY6">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
         <v>21</v>
@@ -2178,10 +2178,10 @@
         <v>25</v>
       </c>
       <c r="BD6">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BE6">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="BF6">
         <v>28</v>
@@ -2199,55 +2199,55 @@
         <v>14</v>
       </c>
       <c r="BK6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BN6">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BO6">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
         <v>26</v>
       </c>
       <c r="BQ6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
       </c>
       <c r="BU6">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB6" t="s">
         <v>150</v>
@@ -2270,22 +2270,22 @@
         <v>132</v>
       </c>
       <c r="F7">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="G7">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="H7">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="I7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="J7">
-        <v>1.1</v>
+        <v>6.8</v>
       </c>
       <c r="K7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="L7">
         <v>1.16</v>
@@ -2294,202 +2294,202 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="O7">
         <v>1.1</v>
       </c>
       <c r="P7">
+        <v>3.7</v>
+      </c>
+      <c r="Q7">
         <v>1.25</v>
       </c>
-      <c r="Q7">
-        <v>1.28</v>
-      </c>
       <c r="R7">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="S7">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="T7">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="U7">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
         <v>1.07</v>
       </c>
       <c r="W7">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="X7">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y7">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Z7">
+        <v>140</v>
+      </c>
+      <c r="AA7">
+        <v>390</v>
+      </c>
+      <c r="AB7">
+        <v>21</v>
+      </c>
+      <c r="AC7">
+        <v>24</v>
+      </c>
+      <c r="AD7">
+        <v>44</v>
+      </c>
+      <c r="AE7">
         <v>160</v>
       </c>
-      <c r="AA7">
-        <v>470</v>
-      </c>
-      <c r="AB7">
-        <v>19.5</v>
-      </c>
-      <c r="AC7">
-        <v>23</v>
-      </c>
-      <c r="AD7">
-        <v>48</v>
-      </c>
-      <c r="AE7">
-        <v>180</v>
-      </c>
       <c r="AF7">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG7">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI7">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AJ7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AK7">
         <v>16.5</v>
       </c>
       <c r="AL7">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AM7">
+        <v>110</v>
+      </c>
+      <c r="AN7">
+        <v>3.1</v>
+      </c>
+      <c r="AO7">
         <v>120</v>
       </c>
-      <c r="AN7">
-        <v>3.55</v>
-      </c>
-      <c r="AO7">
-        <v>160</v>
-      </c>
       <c r="AP7">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ7">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR7">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AS7">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT7">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AU7">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AV7">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AW7">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AX7">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AY7">
-        <v>3.9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BA7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB7">
-        <v>3.65</v>
+        <v>10</v>
       </c>
       <c r="BC7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="BD7">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BE7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BF7">
         <v>2.5</v>
       </c>
       <c r="BG7">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="BH7">
+        <v>6.4</v>
+      </c>
+      <c r="BI7">
+        <v>4.6</v>
+      </c>
+      <c r="BJ7">
+        <v>11.5</v>
+      </c>
+      <c r="BK7">
+        <v>5.2</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>8.6</v>
+      </c>
+      <c r="BN7">
+        <v>4.7</v>
+      </c>
+      <c r="BO7">
+        <v>3.5</v>
+      </c>
+      <c r="BP7">
+        <v>7.4</v>
+      </c>
+      <c r="BQ7">
+        <v>5.3</v>
+      </c>
+      <c r="BR7">
+        <v>17.5</v>
+      </c>
+      <c r="BS7">
         <v>6.2</v>
       </c>
-      <c r="BI7">
-        <v>3.85</v>
-      </c>
-      <c r="BJ7">
-        <v>12</v>
-      </c>
-      <c r="BK7">
-        <v>5.5</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>3.05</v>
-      </c>
-      <c r="BN7">
-        <v>4.5</v>
-      </c>
-      <c r="BO7">
-        <v>3.1</v>
-      </c>
-      <c r="BP7">
-        <v>7</v>
-      </c>
-      <c r="BQ7">
-        <v>4.1</v>
-      </c>
-      <c r="BR7">
-        <v>18</v>
-      </c>
-      <c r="BS7">
-        <v>6.6</v>
-      </c>
       <c r="BT7">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BU7">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BY7">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>7.2</v>
       </c>
       <c r="CA7">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="CB7" t="s">
         <v>150</v>
@@ -2518,7 +2518,7 @@
         <v>2.24</v>
       </c>
       <c r="H8">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I8">
         <v>4.2</v>
@@ -2527,7 +2527,7 @@
         <v>3.15</v>
       </c>
       <c r="K8">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L8">
         <v>1.19</v>
@@ -2542,19 +2542,19 @@
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q8">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="R8">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="S8">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="T8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="U8">
         <v>2.84</v>
@@ -2778,7 +2778,7 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="O9">
         <v>1.09</v>
@@ -3277,7 +3277,7 @@
         <v>1.25</v>
       </c>
       <c r="S11">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -4206,226 +4206,226 @@
         <v>140</v>
       </c>
       <c r="F15">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
       <c r="G15">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="H15">
+        <v>2.72</v>
+      </c>
+      <c r="I15">
         <v>3</v>
-      </c>
-      <c r="I15">
-        <v>3.55</v>
       </c>
       <c r="J15">
         <v>3.9</v>
       </c>
       <c r="K15">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="O15">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q15">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="R15">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="S15">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="T15">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="U15">
         <v>2.62</v>
       </c>
       <c r="V15">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W15">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA15">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB15">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AC15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
         <v>15.5</v>
       </c>
       <c r="AE15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
+        <v>15</v>
+      </c>
+      <c r="AH15">
+        <v>17.5</v>
+      </c>
+      <c r="AI15">
+        <v>1000</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>28</v>
+      </c>
+      <c r="AL15">
+        <v>1000</v>
+      </c>
+      <c r="AM15">
+        <v>1000</v>
+      </c>
+      <c r="AN15">
+        <v>14.5</v>
+      </c>
+      <c r="AO15">
+        <v>19</v>
+      </c>
+      <c r="AP15">
+        <v>19.5</v>
+      </c>
+      <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>18</v>
+      </c>
+      <c r="AS15">
+        <v>1.76</v>
+      </c>
+      <c r="AT15">
         <v>12.5</v>
       </c>
-      <c r="AH15">
+      <c r="AU15">
+        <v>7.8</v>
+      </c>
+      <c r="AV15">
+        <v>10</v>
+      </c>
+      <c r="AW15">
+        <v>20</v>
+      </c>
+      <c r="AX15">
+        <v>15</v>
+      </c>
+      <c r="AY15">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ15">
+        <v>11</v>
+      </c>
+      <c r="BA15">
+        <v>1.82</v>
+      </c>
+      <c r="BB15">
+        <v>1.82</v>
+      </c>
+      <c r="BC15">
+        <v>17.5</v>
+      </c>
+      <c r="BD15">
+        <v>1.82</v>
+      </c>
+      <c r="BE15">
+        <v>1.82</v>
+      </c>
+      <c r="BF15">
+        <v>10.5</v>
+      </c>
+      <c r="BG15">
+        <v>12.5</v>
+      </c>
+      <c r="BH15">
+        <v>4.6</v>
+      </c>
+      <c r="BI15">
+        <v>3.65</v>
+      </c>
+      <c r="BJ15">
+        <v>8.6</v>
+      </c>
+      <c r="BK15">
+        <v>5.2</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>11</v>
+      </c>
+      <c r="BN15">
+        <v>5.9</v>
+      </c>
+      <c r="BO15">
+        <v>4.6</v>
+      </c>
+      <c r="BP15">
+        <v>1000</v>
+      </c>
+      <c r="BQ15">
+        <v>7</v>
+      </c>
+      <c r="BR15">
+        <v>1000</v>
+      </c>
+      <c r="BS15">
+        <v>8.4</v>
+      </c>
+      <c r="BT15">
+        <v>6.8</v>
+      </c>
+      <c r="BU15">
+        <v>5.2</v>
+      </c>
+      <c r="BV15">
+        <v>1000</v>
+      </c>
+      <c r="BW15">
+        <v>8</v>
+      </c>
+      <c r="BX15">
+        <v>1000</v>
+      </c>
+      <c r="BY15">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BZ15">
         <v>15.5</v>
       </c>
-      <c r="AI15">
-        <v>38</v>
-      </c>
-      <c r="AJ15">
-        <v>34</v>
-      </c>
-      <c r="AK15">
-        <v>24</v>
-      </c>
-      <c r="AL15">
-        <v>32</v>
-      </c>
-      <c r="AM15">
-        <v>60</v>
-      </c>
-      <c r="AN15">
-        <v>11.5</v>
-      </c>
-      <c r="AO15">
-        <v>22</v>
-      </c>
-      <c r="AP15">
-        <v>5</v>
-      </c>
-      <c r="AQ15">
-        <v>4.7</v>
-      </c>
-      <c r="AR15">
-        <v>5</v>
-      </c>
-      <c r="AS15">
-        <v>5.3</v>
-      </c>
-      <c r="AT15">
-        <v>4.3</v>
-      </c>
-      <c r="AU15">
-        <v>3.95</v>
-      </c>
-      <c r="AV15">
-        <v>4.2</v>
-      </c>
-      <c r="AW15">
-        <v>5</v>
-      </c>
-      <c r="AX15">
-        <v>4.6</v>
-      </c>
-      <c r="AY15">
-        <v>4</v>
-      </c>
-      <c r="AZ15">
-        <v>4.2</v>
-      </c>
-      <c r="BA15">
-        <v>5.1</v>
-      </c>
-      <c r="BB15">
-        <v>5</v>
-      </c>
-      <c r="BC15">
-        <v>4.7</v>
-      </c>
-      <c r="BD15">
-        <v>5</v>
-      </c>
-      <c r="BE15">
-        <v>5.3</v>
-      </c>
-      <c r="BF15">
-        <v>3.9</v>
-      </c>
-      <c r="BG15">
-        <v>4.6</v>
-      </c>
-      <c r="BH15">
-        <v>4.8</v>
-      </c>
-      <c r="BI15">
-        <v>3.3</v>
-      </c>
-      <c r="BJ15">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BK15">
-        <v>4.8</v>
-      </c>
-      <c r="BL15">
-        <v>1000</v>
-      </c>
-      <c r="BM15">
-        <v>9.4</v>
-      </c>
-      <c r="BN15">
-        <v>5.8</v>
-      </c>
-      <c r="BO15">
-        <v>3.75</v>
-      </c>
-      <c r="BP15">
-        <v>15</v>
-      </c>
-      <c r="BQ15">
-        <v>6.2</v>
-      </c>
-      <c r="BR15">
-        <v>1000</v>
-      </c>
-      <c r="BS15">
-        <v>7.2</v>
-      </c>
-      <c r="BT15">
-        <v>7.2</v>
-      </c>
-      <c r="BU15">
-        <v>4.3</v>
-      </c>
-      <c r="BV15">
-        <v>1000</v>
-      </c>
-      <c r="BW15">
-        <v>7.2</v>
-      </c>
-      <c r="BX15">
-        <v>1000</v>
-      </c>
-      <c r="BY15">
-        <v>7.8</v>
-      </c>
-      <c r="BZ15">
-        <v>15</v>
-      </c>
       <c r="CA15">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="s">
         <v>150</v>
@@ -4448,22 +4448,22 @@
         <v>141</v>
       </c>
       <c r="F16">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="G16">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="H16">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="I16">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J16">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="L16">
         <v>1.2</v>
@@ -4472,148 +4472,148 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>1.1</v>
+        <v>6.6</v>
       </c>
       <c r="O16">
         <v>1.14</v>
       </c>
       <c r="P16">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="Q16">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="R16">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="S16">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="T16">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="U16">
         <v>2.84</v>
       </c>
       <c r="V16">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="X16">
         <v>42</v>
       </c>
       <c r="Y16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z16">
+        <v>29</v>
+      </c>
+      <c r="AA16">
+        <v>60</v>
+      </c>
+      <c r="AB16">
+        <v>20</v>
+      </c>
+      <c r="AC16">
+        <v>11.5</v>
+      </c>
+      <c r="AD16">
+        <v>18</v>
+      </c>
+      <c r="AE16">
+        <v>34</v>
+      </c>
+      <c r="AF16">
+        <v>21</v>
+      </c>
+      <c r="AG16">
+        <v>13</v>
+      </c>
+      <c r="AH16">
+        <v>15</v>
+      </c>
+      <c r="AI16">
         <v>32</v>
       </c>
-      <c r="AA16">
-        <v>55</v>
-      </c>
-      <c r="AB16">
-        <v>24</v>
-      </c>
-      <c r="AC16">
-        <v>14</v>
-      </c>
-      <c r="AD16">
-        <v>17.5</v>
-      </c>
-      <c r="AE16">
+      <c r="AJ16">
         <v>32</v>
       </c>
-      <c r="AF16">
+      <c r="AK16">
+        <v>21</v>
+      </c>
+      <c r="AL16">
         <v>26</v>
       </c>
-      <c r="AG16">
-        <v>15.5</v>
-      </c>
-      <c r="AH16">
-        <v>17.5</v>
-      </c>
-      <c r="AI16">
-        <v>34</v>
-      </c>
-      <c r="AJ16">
-        <v>40</v>
-      </c>
-      <c r="AK16">
-        <v>26</v>
-      </c>
-      <c r="AL16">
-        <v>32</v>
-      </c>
       <c r="AM16">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN16">
+        <v>11</v>
+      </c>
+      <c r="AO16">
+        <v>18</v>
+      </c>
+      <c r="AP16">
+        <v>5.6</v>
+      </c>
+      <c r="AQ16">
+        <v>18.5</v>
+      </c>
+      <c r="AR16">
+        <v>21</v>
+      </c>
+      <c r="AS16">
+        <v>5.9</v>
+      </c>
+      <c r="AT16">
+        <v>15</v>
+      </c>
+      <c r="AU16">
+        <v>8.4</v>
+      </c>
+      <c r="AV16">
+        <v>11.5</v>
+      </c>
+      <c r="AW16">
+        <v>21</v>
+      </c>
+      <c r="AX16">
+        <v>16.5</v>
+      </c>
+      <c r="AY16">
+        <v>10.5</v>
+      </c>
+      <c r="AZ16">
         <v>12</v>
       </c>
-      <c r="AO16">
-        <v>16</v>
-      </c>
-      <c r="AP16">
-        <v>3.8</v>
-      </c>
-      <c r="AQ16">
-        <v>3.65</v>
-      </c>
-      <c r="AR16">
-        <v>3.7</v>
-      </c>
-      <c r="AS16">
-        <v>3.9</v>
-      </c>
-      <c r="AT16">
-        <v>3.55</v>
-      </c>
-      <c r="AU16">
-        <v>3.2</v>
-      </c>
-      <c r="AV16">
-        <v>3.4</v>
-      </c>
-      <c r="AW16">
-        <v>3.7</v>
-      </c>
-      <c r="AX16">
-        <v>3.6</v>
-      </c>
-      <c r="AY16">
-        <v>3.3</v>
-      </c>
-      <c r="AZ16">
-        <v>3.4</v>
-      </c>
       <c r="BA16">
-        <v>3.75</v>
+        <v>23</v>
       </c>
       <c r="BB16">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="BC16">
-        <v>3.6</v>
+        <v>16.5</v>
       </c>
       <c r="BD16">
-        <v>3.7</v>
+        <v>20</v>
       </c>
       <c r="BE16">
-        <v>3.9</v>
+        <v>5.8</v>
       </c>
       <c r="BF16">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="BG16">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="BH16">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BI16">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BJ16">
         <v>8.6</v>
@@ -4622,52 +4622,52 @@
         <v>4.5</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM16">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BP16">
         <v>15.5</v>
       </c>
       <c r="BQ16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BR16">
         <v>22</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT16">
         <v>7.2</v>
       </c>
       <c r="BU16">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV16">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BW16">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BY16">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BZ16">
         <v>13</v>
       </c>
       <c r="CA16">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="CB16" t="s">
         <v>150</v>
@@ -4702,10 +4702,10 @@
         <v>4.3</v>
       </c>
       <c r="J17">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>1.67</v>
@@ -4714,22 +4714,22 @@
         <v>1.16</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="O17">
         <v>1.7</v>
       </c>
       <c r="P17">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="Q17">
         <v>3.15</v>
       </c>
       <c r="R17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>2.46</v>
@@ -4744,10 +4744,10 @@
         <v>1.72</v>
       </c>
       <c r="X17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
         <v>27</v>
@@ -4762,16 +4762,16 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE17">
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG17">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH17">
         <v>32</v>
@@ -4783,7 +4783,7 @@
         <v>60</v>
       </c>
       <c r="AK17">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AL17">
         <v>1000</v>
@@ -4792,7 +4792,7 @@
         <v>350</v>
       </c>
       <c r="AN17">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AO17">
         <v>1000</v>
@@ -4801,16 +4801,16 @@
         <v>6.6</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR17">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AS17">
         <v>38</v>
       </c>
       <c r="AT17">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
@@ -4828,7 +4828,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ17">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA17">
         <v>42</v>
@@ -4837,16 +4837,16 @@
         <v>21</v>
       </c>
       <c r="BC17">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="BD17">
         <v>36</v>
       </c>
       <c r="BE17">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF17">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG17">
         <v>42</v>
@@ -4867,7 +4867,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.18</v>
+        <v>17</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -4879,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="BQ17">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BR17">
         <v>55</v>
@@ -4903,7 +4903,7 @@
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
@@ -4938,7 +4938,7 @@
         <v>1.96</v>
       </c>
       <c r="H18">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I18">
         <v>7.4</v>
@@ -4959,13 +4959,13 @@
         <v>2.68</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P18">
         <v>1.62</v>
       </c>
       <c r="Q18">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R18">
         <v>1.23</v>
@@ -4983,7 +4983,7 @@
         <v>1.16</v>
       </c>
       <c r="W18">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X18">
         <v>12.5</v>
@@ -4998,7 +4998,7 @@
         <v>220</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC18">
         <v>9.6</v>
@@ -5040,58 +5040,58 @@
         <v>200</v>
       </c>
       <c r="AP18">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AQ18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AR18">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AS18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AT18">
         <v>3.1</v>
       </c>
       <c r="AU18">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AV18">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW18">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AX18">
+        <v>3.55</v>
+      </c>
+      <c r="AY18">
         <v>3.65</v>
       </c>
-      <c r="AY18">
-        <v>3.8</v>
-      </c>
       <c r="AZ18">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BA18">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BB18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BC18">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BD18">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BE18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF18">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BG18">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH18">
         <v>3.15</v>
@@ -5422,16 +5422,16 @@
         <v>4.4</v>
       </c>
       <c r="H20">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="J20">
         <v>3.15</v>
       </c>
       <c r="K20">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L20">
         <v>1.49</v>
@@ -5440,7 +5440,7 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O20">
         <v>1.58</v>
@@ -5452,10 +5452,10 @@
         <v>2.7</v>
       </c>
       <c r="R20">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S20">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="T20">
         <v>2.2</v>
@@ -5464,46 +5464,46 @@
         <v>1.73</v>
       </c>
       <c r="V20">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="W20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X20">
         <v>8.6</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>6.8</v>
       </c>
       <c r="Z20">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AA20">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB20">
         <v>11</v>
       </c>
       <c r="AC20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AE20">
         <v>40</v>
       </c>
       <c r="AF20">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AG20">
         <v>970</v>
       </c>
       <c r="AH20">
-        <v>950</v>
+        <v>30</v>
       </c>
       <c r="AI20">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ20">
         <v>130</v>
@@ -5533,7 +5533,7 @@
         <v>11</v>
       </c>
       <c r="AS20">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT20">
         <v>9.4</v>
@@ -5545,10 +5545,10 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX20">
-        <v>5.5</v>
+        <v>7.8</v>
       </c>
       <c r="AY20">
         <v>16</v>
@@ -5557,82 +5557,82 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BB20">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC20">
-        <v>5.9</v>
+        <v>9.4</v>
       </c>
       <c r="BD20">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BE20">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="BF20">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG20">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH20">
         <v>2.66</v>
       </c>
       <c r="BI20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ20">
         <v>12</v>
       </c>
       <c r="BK20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.28</v>
+        <v>15.5</v>
       </c>
       <c r="BN20">
         <v>7.2</v>
       </c>
       <c r="BO20">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BT20">
         <v>4.8</v>
       </c>
       <c r="BU20">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BV20">
         <v>20</v>
       </c>
       <c r="BW20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA20">
         <v>12.5</v>
@@ -5658,7 +5658,7 @@
         <v>146</v>
       </c>
       <c r="F21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G21">
         <v>1.79</v>
@@ -5685,25 +5685,25 @@
         <v>3.55</v>
       </c>
       <c r="O21">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P21">
         <v>1.89</v>
       </c>
       <c r="Q21">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R21">
         <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="T21">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U21">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V21">
         <v>1.2</v>
@@ -5733,7 +5733,7 @@
         <v>26</v>
       </c>
       <c r="AE21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF21">
         <v>10.5</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="AH21">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI21">
         <v>100</v>
@@ -5772,10 +5772,10 @@
         <v>15.5</v>
       </c>
       <c r="AR21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AS21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT21">
         <v>7.2</v>
@@ -5784,7 +5784,7 @@
         <v>7.8</v>
       </c>
       <c r="AV21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AW21">
         <v>8</v>
@@ -5793,10 +5793,10 @@
         <v>9</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA21">
         <v>8</v>
@@ -5808,10 +5808,10 @@
         <v>17</v>
       </c>
       <c r="BD21">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE21">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF21">
         <v>11</v>
@@ -5820,10 +5820,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH21">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI21">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21">
         <v>10.5</v>
@@ -5835,19 +5835,19 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BN21">
         <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="BP21">
         <v>12.5</v>
       </c>
       <c r="BQ21">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR21">
         <v>29</v>
@@ -5859,13 +5859,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BV21">
         <v>1000</v>
       </c>
       <c r="BW21">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BX21">
         <v>1000</v>
@@ -5874,10 +5874,10 @@
         <v>13</v>
       </c>
       <c r="BZ21">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="CA21">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB21" t="s">
         <v>150</v>
@@ -5900,7 +5900,7 @@
         <v>147</v>
       </c>
       <c r="F22">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G22">
         <v>4.5</v>
@@ -5909,7 +5909,7 @@
         <v>1.96</v>
       </c>
       <c r="I22">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J22">
         <v>3.7</v>
@@ -5930,10 +5930,10 @@
         <v>1.32</v>
       </c>
       <c r="P22">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="Q22">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R22">
         <v>1.36</v>
@@ -5945,10 +5945,10 @@
         <v>1.84</v>
       </c>
       <c r="U22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V22">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W22">
         <v>1.28</v>
@@ -5969,10 +5969,10 @@
         <v>15.5</v>
       </c>
       <c r="AC22">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD22">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AE22">
         <v>21</v>
@@ -5981,10 +5981,10 @@
         <v>34</v>
       </c>
       <c r="AG22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH22">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI22">
         <v>38</v>
@@ -6005,13 +6005,13 @@
         <v>65</v>
       </c>
       <c r="AO22">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP22">
         <v>12.5</v>
       </c>
       <c r="AQ22">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR22">
         <v>10.5</v>
@@ -6029,7 +6029,7 @@
         <v>9.6</v>
       </c>
       <c r="AW22">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX22">
         <v>25</v>
@@ -6038,7 +6038,7 @@
         <v>15.5</v>
       </c>
       <c r="AZ22">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA22">
         <v>32</v>
@@ -6053,16 +6053,16 @@
         <v>50</v>
       </c>
       <c r="BE22">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BF22">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BG22">
         <v>12.5</v>
       </c>
       <c r="BH22">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BI22">
         <v>3.15</v>
@@ -6071,13 +6071,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK22">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BN22">
         <v>7.6</v>
@@ -6086,40 +6086,40 @@
         <v>5.5</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ22">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS22">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BT22">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BU22">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV22">
         <v>14</v>
       </c>
       <c r="BW22">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BX22">
         <v>28</v>
       </c>
       <c r="BY22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BZ22">
         <v>25</v>
       </c>
       <c r="CA22">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="CB22" t="s">
         <v>150</v>
@@ -6142,22 +6142,22 @@
         <v>148</v>
       </c>
       <c r="F23">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G23">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="H23">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I23">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L23">
         <v>1.4</v>
@@ -6166,202 +6166,202 @@
         <v>1.09</v>
       </c>
       <c r="N23">
-        <v>2.66</v>
+        <v>3.05</v>
       </c>
       <c r="O23">
         <v>1.41</v>
       </c>
       <c r="P23">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q23">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R23">
+        <v>1.26</v>
+      </c>
+      <c r="S23">
+        <v>3.7</v>
+      </c>
+      <c r="T23">
+        <v>1.98</v>
+      </c>
+      <c r="U23">
+        <v>1.88</v>
+      </c>
+      <c r="V23">
         <v>1.25</v>
       </c>
-      <c r="S23">
-        <v>3.4</v>
-      </c>
-      <c r="T23">
-        <v>1.95</v>
-      </c>
-      <c r="U23">
-        <v>1.86</v>
-      </c>
-      <c r="V23">
-        <v>1.26</v>
-      </c>
       <c r="W23">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="X23">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y23">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z23">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AA23">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB23">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC23">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD23">
+        <v>19</v>
+      </c>
+      <c r="AE23">
+        <v>70</v>
+      </c>
+      <c r="AF23">
+        <v>12</v>
+      </c>
+      <c r="AG23">
+        <v>11</v>
+      </c>
+      <c r="AH23">
         <v>22</v>
       </c>
-      <c r="AE23">
-        <v>80</v>
-      </c>
-      <c r="AF23">
-        <v>14.5</v>
-      </c>
-      <c r="AG23">
-        <v>13</v>
-      </c>
-      <c r="AH23">
-        <v>26</v>
-      </c>
       <c r="AI23">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ23">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AK23">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AL23">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AM23">
         <v>180</v>
       </c>
       <c r="AN23">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="AO23">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP23">
-        <v>3.25</v>
+        <v>8.4</v>
       </c>
       <c r="AQ23">
-        <v>3.4</v>
+        <v>10</v>
       </c>
       <c r="AR23">
-        <v>3.9</v>
+        <v>7.4</v>
       </c>
       <c r="AS23">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AT23">
-        <v>2.94</v>
+        <v>6.6</v>
       </c>
       <c r="AU23">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AV23">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW23">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="AX23">
-        <v>3.35</v>
+        <v>8.4</v>
       </c>
       <c r="AY23">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AZ23">
-        <v>3.7</v>
+        <v>15.5</v>
       </c>
       <c r="BA23">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB23">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="BC23">
-        <v>3.8</v>
+        <v>21</v>
       </c>
       <c r="BD23">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="BE23">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="BF23">
-        <v>3.7</v>
+        <v>14</v>
       </c>
       <c r="BG23">
-        <v>4.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="BI23">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="BJ23">
         <v>11</v>
       </c>
       <c r="BK23">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.4</v>
+        <v>13.5</v>
       </c>
       <c r="BN23">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BO23">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="BP23">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BQ23">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BR23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="BT23">
         <v>7.8</v>
       </c>
       <c r="BU23">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV23">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>2.3</v>
+        <v>11</v>
       </c>
       <c r="BX23">
         <v>60</v>
       </c>
       <c r="BY23">
-        <v>2.34</v>
+        <v>12</v>
       </c>
       <c r="BZ23">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="CA23">
-        <v>2.28</v>
+        <v>10</v>
       </c>
       <c r="CB23" t="s">
         <v>150</v>
@@ -6384,76 +6384,76 @@
         <v>149</v>
       </c>
       <c r="F24">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="G24">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H24">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I24">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K24">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="O24">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q24">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R24">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="S24">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T24">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="U24">
         <v>2.08</v>
       </c>
       <c r="V24">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W24">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X24">
         <v>34</v>
       </c>
       <c r="Y24">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z24">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA24">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB24">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AC24">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AD24">
         <v>34</v>
@@ -6465,13 +6465,13 @@
         <v>13</v>
       </c>
       <c r="AG24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AI24">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ24">
         <v>16.5</v>
@@ -6486,13 +6486,13 @@
         <v>120</v>
       </c>
       <c r="AN24">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AO24">
         <v>110</v>
       </c>
       <c r="AP24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AQ24">
         <v>1.03</v>
@@ -6504,13 +6504,13 @@
         <v>1.01</v>
       </c>
       <c r="AT24">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV24">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW24">
         <v>1.01</v>
@@ -6519,7 +6519,7 @@
         <v>7.8</v>
       </c>
       <c r="AY24">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ24">
         <v>15.5</v>
@@ -6528,7 +6528,7 @@
         <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC24">
         <v>10.5</v>
@@ -6540,28 +6540,28 @@
         <v>1.01</v>
       </c>
       <c r="BF24">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG24">
         <v>1.01</v>
       </c>
       <c r="BH24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ24">
         <v>10.5</v>
       </c>
       <c r="BK24">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN24">
         <v>4.5</v>
@@ -6579,7 +6579,7 @@
         <v>21</v>
       </c>
       <c r="BS24">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT24">
         <v>11.5</v>
@@ -6588,7 +6588,7 @@
         <v>5.3</v>
       </c>
       <c r="BV24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
         <v>8.4</v>
@@ -6597,13 +6597,13 @@
         <v>55</v>
       </c>
       <c r="BY24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA24">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB24" t="s">
         <v>150</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="154">
   <si>
     <t>League</t>
   </si>
@@ -271,6 +271,9 @@
     <t>Icelandic 2 Deild</t>
   </si>
   <si>
+    <t>Icelandic 3 Deild</t>
+  </si>
+  <si>
     <t>Paraguayan Primera Division</t>
   </si>
   <si>
@@ -352,27 +355,30 @@
     <t>IF Magni</t>
   </si>
   <si>
+    <t>Vidir Gardur</t>
+  </si>
+  <si>
     <t>Sportivo Luqueno</t>
   </si>
   <si>
+    <t>KV Vesturbaejar</t>
+  </si>
+  <si>
     <t>Throttur Vogar</t>
   </si>
   <si>
     <t>Vikingur Olafsvik</t>
   </si>
   <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
+    <t>Throttur</t>
+  </si>
+  <si>
     <t>Kari</t>
   </si>
   <si>
-    <t>Haukar</t>
-  </si>
-  <si>
-    <t>Grindavik</t>
-  </si>
-  <si>
-    <t>Throttur</t>
-  </si>
-  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -421,27 +427,30 @@
     <t>KFA Austfjarda</t>
   </si>
   <si>
+    <t>KF Fjallabyggd</t>
+  </si>
+  <si>
     <t>Sportivo Trinidense</t>
   </si>
   <si>
+    <t>Reynir Sandgeroi</t>
+  </si>
+  <si>
     <t>Hviti Riddarinn</t>
   </si>
   <si>
     <t>Fjolnir</t>
   </si>
   <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
     <t>Kormakur/Hvot</t>
   </si>
   <si>
-    <t>KFG</t>
-  </si>
-  <si>
-    <t>Leiknir R</t>
-  </si>
-  <si>
-    <t>Afturelding</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -466,7 +475,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 12:28:20</t>
+    <t>2026-07-28 14:35:52</t>
   </si>
 </sst>
 </file>
@@ -798,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB24"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,37 +1057,37 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G2">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="J2">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="M2">
         <v>1.13</v>
@@ -1087,46 +1096,46 @@
         <v>2.68</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="R2">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="T2">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
         <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="X2">
         <v>8.4</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z2">
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB2">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC2">
         <v>7</v>
@@ -1138,19 +1147,19 @@
         <v>70</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH2">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI2">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AJ2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK2">
         <v>34</v>
@@ -1159,28 +1168,28 @@
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN2">
         <v>34</v>
       </c>
       <c r="AO2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP2">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AR2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS2">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AT2">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU2">
         <v>6.4</v>
@@ -1189,43 +1198,43 @@
         <v>15.5</v>
       </c>
       <c r="AW2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="BB2">
+        <v>28</v>
+      </c>
+      <c r="BC2">
         <v>29</v>
-      </c>
-      <c r="BC2">
-        <v>28</v>
       </c>
       <c r="BD2">
         <v>50</v>
       </c>
       <c r="BE2">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="BF2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BG2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BH2">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="BI2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="BJ2">
         <v>11.5</v>
@@ -1234,16 +1243,16 @@
         <v>6</v>
       </c>
       <c r="BL2">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="BM2">
         <v>12.5</v>
       </c>
       <c r="BN2">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BO2">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
         <v>21</v>
@@ -1252,37 +1261,37 @@
         <v>8</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BS2">
         <v>10</v>
       </c>
       <c r="BT2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BU2">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BV2">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="BW2">
         <v>10</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BY2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="CA2">
         <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,91 +1299,91 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F3">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="G3">
+        <v>1.4</v>
+      </c>
+      <c r="H3">
+        <v>12.5</v>
+      </c>
+      <c r="I3">
+        <v>13.5</v>
+      </c>
+      <c r="J3">
+        <v>4.8</v>
+      </c>
+      <c r="K3">
+        <v>5</v>
+      </c>
+      <c r="L3">
+        <v>1.51</v>
+      </c>
+      <c r="M3">
+        <v>1.09</v>
+      </c>
+      <c r="N3">
+        <v>3.2</v>
+      </c>
+      <c r="O3">
         <v>1.44</v>
       </c>
-      <c r="H3">
-        <v>11</v>
-      </c>
-      <c r="I3">
-        <v>13</v>
-      </c>
-      <c r="J3">
-        <v>4.6</v>
-      </c>
-      <c r="K3">
-        <v>4.8</v>
-      </c>
-      <c r="L3">
-        <v>1.53</v>
-      </c>
-      <c r="M3">
-        <v>1.1</v>
-      </c>
-      <c r="N3">
-        <v>3</v>
-      </c>
-      <c r="O3">
-        <v>1.47</v>
-      </c>
       <c r="P3">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="Q3">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="T3">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="U3">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V3">
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="X3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Z3">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA3">
         <v>840</v>
       </c>
       <c r="AB3">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AC3">
         <v>11.5</v>
       </c>
       <c r="AD3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AE3">
         <v>390</v>
@@ -1389,76 +1398,76 @@
         <v>50</v>
       </c>
       <c r="AI3">
-        <v>450</v>
+        <v>360</v>
       </c>
       <c r="AJ3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK3">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>480</v>
+        <v>580</v>
       </c>
       <c r="AN3">
+        <v>9</v>
+      </c>
+      <c r="AO3">
+        <v>800</v>
+      </c>
+      <c r="AP3">
         <v>10.5</v>
-      </c>
-      <c r="AO3">
-        <v>890</v>
-      </c>
-      <c r="AP3">
-        <v>9.800000000000001</v>
       </c>
       <c r="AQ3">
         <v>22</v>
       </c>
       <c r="AR3">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AS3">
         <v>75</v>
       </c>
       <c r="AT3">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AW3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX3">
         <v>5.8</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BA3">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="BB3">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD3">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3">
         <v>70</v>
@@ -1467,64 +1476,64 @@
         <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="BJ3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BN3">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BO3">
-        <v>2.76</v>
+        <v>2.86</v>
       </c>
       <c r="BP3">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BQ3">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR3">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
         <v>15.5</v>
       </c>
       <c r="BU3">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ3">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="CA3">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,37 +1541,37 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F4">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="G4">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="H4">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1574,7 +1583,7 @@
         <v>1.44</v>
       </c>
       <c r="P4">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q4">
         <v>2.36</v>
@@ -1586,85 +1595,85 @@
         <v>4.6</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U4">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V4">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="X4">
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z4">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB4">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD4">
         <v>21</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AF4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
       </c>
       <c r="AH4">
+        <v>24</v>
+      </c>
+      <c r="AI4">
+        <v>100</v>
+      </c>
+      <c r="AJ4">
+        <v>21</v>
+      </c>
+      <c r="AK4">
         <v>23</v>
-      </c>
-      <c r="AI4">
-        <v>95</v>
-      </c>
-      <c r="AJ4">
-        <v>22</v>
-      </c>
-      <c r="AK4">
-        <v>24</v>
       </c>
       <c r="AL4">
         <v>48</v>
       </c>
       <c r="AM4">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN4">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO4">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AS4">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AT4">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
         <v>7.2</v>
@@ -1673,7 +1682,7 @@
         <v>18.5</v>
       </c>
       <c r="AW4">
-        <v>15.5</v>
+        <v>40</v>
       </c>
       <c r="AX4">
         <v>9.6</v>
@@ -1685,10 +1694,10 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>15.5</v>
+        <v>22</v>
       </c>
       <c r="BB4">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC4">
         <v>21</v>
@@ -1697,76 +1706,76 @@
         <v>42</v>
       </c>
       <c r="BE4">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BF4">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG4">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="BH4">
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.52</v>
+        <v>2.76</v>
       </c>
       <c r="BJ4">
         <v>11</v>
       </c>
       <c r="BK4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN4">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO4">
         <v>3.9</v>
       </c>
       <c r="BP4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU4">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV4">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW4">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX4">
         <v>65</v>
       </c>
       <c r="BY4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CB4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1774,70 +1783,70 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E5" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F5">
+        <v>1.47</v>
+      </c>
+      <c r="G5">
         <v>1.53</v>
       </c>
-      <c r="G5">
-        <v>1.59</v>
-      </c>
       <c r="H5">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="L5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O5">
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q5">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S5">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="U5">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="V5">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
-        <v>2.66</v>
+        <v>2.84</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1846,10 +1855,10 @@
         <v>32</v>
       </c>
       <c r="Z5">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA5">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="AB5">
         <v>11.5</v>
@@ -1858,10 +1867,10 @@
         <v>12</v>
       </c>
       <c r="AD5">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AE5">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AF5">
         <v>11</v>
@@ -1870,7 +1879,7 @@
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AI5">
         <v>85</v>
@@ -1891,31 +1900,31 @@
         <v>7.2</v>
       </c>
       <c r="AO5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="AR5">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="AS5">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AT5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
         <v>19</v>
       </c>
       <c r="AW5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX5">
         <v>8.800000000000001</v>
@@ -1927,7 +1936,7 @@
         <v>17.5</v>
       </c>
       <c r="BA5">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
@@ -1939,40 +1948,40 @@
         <v>21</v>
       </c>
       <c r="BE5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH5">
         <v>4.4</v>
       </c>
       <c r="BI5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BJ5">
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP5">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BQ5">
         <v>5</v>
@@ -1981,34 +1990,34 @@
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BZ5">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA5">
         <v>6</v>
       </c>
       <c r="CB5" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2016,31 +2025,31 @@
         <v>80</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F6">
+        <v>2.42</v>
+      </c>
+      <c r="G6">
         <v>2.46</v>
       </c>
-      <c r="G6">
-        <v>2.54</v>
-      </c>
       <c r="H6">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I6">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="J6">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K6">
         <v>2.94</v>
@@ -2052,46 +2061,46 @@
         <v>1.18</v>
       </c>
       <c r="N6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="O6">
         <v>1.76</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q6">
         <v>3.25</v>
       </c>
       <c r="R6">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S6">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="T6">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U6">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W6">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB6">
         <v>6.4</v>
@@ -2100,64 +2109,64 @@
         <v>7.2</v>
       </c>
       <c r="AD6">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF6">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG6">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ6">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AK6">
-        <v>130</v>
+        <v>46</v>
       </c>
       <c r="AL6">
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>420</v>
+        <v>380</v>
       </c>
       <c r="AN6">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP6">
         <v>6</v>
       </c>
       <c r="AQ6">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS6">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AT6">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AU6">
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW6">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AX6">
         <v>11.5</v>
@@ -2166,25 +2175,25 @@
         <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA6">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB6">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC6">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BD6">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BE6">
         <v>55</v>
       </c>
       <c r="BF6">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BG6">
         <v>40</v>
@@ -2193,10 +2202,10 @@
         <v>2.42</v>
       </c>
       <c r="BI6">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="BJ6">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK6">
         <v>6.4</v>
@@ -2205,7 +2214,7 @@
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN6">
         <v>5.2</v>
@@ -2217,13 +2226,13 @@
         <v>26</v>
       </c>
       <c r="BQ6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT6">
         <v>7.2</v>
@@ -2235,13 +2244,13 @@
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
@@ -2250,7 +2259,7 @@
         <v>10.5</v>
       </c>
       <c r="CB6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2258,16 +2267,16 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F7">
         <v>1.25</v>
@@ -2279,13 +2288,13 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="J7">
         <v>6.8</v>
       </c>
       <c r="K7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7">
         <v>1.16</v>
@@ -2303,7 +2312,7 @@
         <v>3.7</v>
       </c>
       <c r="Q7">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="R7">
         <v>2.1</v>
@@ -2318,22 +2327,22 @@
         <v>2.16</v>
       </c>
       <c r="V7">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W7">
         <v>4.1</v>
       </c>
       <c r="X7">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Y7">
         <v>70</v>
       </c>
       <c r="Z7">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AA7">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="AB7">
         <v>21</v>
@@ -2345,7 +2354,7 @@
         <v>44</v>
       </c>
       <c r="AE7">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AF7">
         <v>13</v>
@@ -2357,31 +2366,31 @@
         <v>32</v>
       </c>
       <c r="AI7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AJ7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AK7">
         <v>16.5</v>
       </c>
       <c r="AL7">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AO7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AP7">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AQ7">
-        <v>6.8</v>
+        <v>36</v>
       </c>
       <c r="AR7">
         <v>7</v>
@@ -2390,46 +2399,46 @@
         <v>7.2</v>
       </c>
       <c r="AT7">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AV7">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AW7">
         <v>7</v>
       </c>
       <c r="AX7">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY7">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AZ7">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC7">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD7">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BE7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF7">
         <v>2.5</v>
       </c>
       <c r="BG7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH7">
         <v>6.4</v>
@@ -2492,7 +2501,7 @@
         <v>5.2</v>
       </c>
       <c r="CB7" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2500,16 +2509,16 @@
         <v>84</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F8">
         <v>1.81</v>
@@ -2527,7 +2536,7 @@
         <v>3.15</v>
       </c>
       <c r="K8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L8">
         <v>1.19</v>
@@ -2542,7 +2551,7 @@
         <v>1.12</v>
       </c>
       <c r="P8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q8">
         <v>1.34</v>
@@ -2551,7 +2560,7 @@
         <v>1.75</v>
       </c>
       <c r="S8">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="T8">
         <v>1.41</v>
@@ -2734,7 +2743,7 @@
         <v>5.1</v>
       </c>
       <c r="CB8" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2742,16 +2751,16 @@
         <v>84</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F9">
         <v>3.25</v>
@@ -2976,7 +2985,7 @@
         <v>4</v>
       </c>
       <c r="CB9" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2984,34 +2993,34 @@
         <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" t="s">
         <v>95</v>
       </c>
       <c r="D10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>990</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L10">
         <v>1.01</v>
@@ -3023,19 +3032,19 @@
         <v>1.1</v>
       </c>
       <c r="O10">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>1.24</v>
+        <v>1.09</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="R10">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="S10">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="T10">
         <v>1.11</v>
@@ -3104,52 +3113,52 @@
         <v>1000</v>
       </c>
       <c r="AP10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF10">
         <v>1.01</v>
@@ -3212,48 +3221,48 @@
         <v>1.04</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="CB10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C11" t="s">
         <v>96</v>
       </c>
       <c r="D11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="G11">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>990</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3262,22 +3271,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O11">
-        <v>1.09</v>
+        <v>1.42</v>
       </c>
       <c r="P11">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q11">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="R11">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="T11">
         <v>1.11</v>
@@ -3286,10 +3295,10 @@
         <v>1.11</v>
       </c>
       <c r="V11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3454,45 +3463,45 @@
         <v>1.04</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="G12">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="I12">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="K12">
         <v>950</v>
@@ -3507,19 +3516,19 @@
         <v>1.26</v>
       </c>
       <c r="O12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="P12">
         <v>1.25</v>
       </c>
       <c r="Q12">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="R12">
         <v>1.25</v>
       </c>
       <c r="S12">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="T12">
         <v>1.11</v>
@@ -3528,10 +3537,10 @@
         <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3588,52 +3597,52 @@
         <v>1000</v>
       </c>
       <c r="AP12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
         <v>1.01</v>
@@ -3645,64 +3654,64 @@
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3710,31 +3719,31 @@
         <v>84</v>
       </c>
       <c r="B13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F13">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="G13">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I13">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J13">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3746,22 +3755,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O13">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q13">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="R13">
+        <v>1.25</v>
+      </c>
+      <c r="S13">
         <v>1.08</v>
-      </c>
-      <c r="S13">
-        <v>1.05</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3770,10 +3779,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3944,7 +3953,7 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3952,19 +3961,19 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C14" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="G14">
         <v>990</v>
@@ -3976,7 +3985,7 @@
         <v>990</v>
       </c>
       <c r="J14">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="K14">
         <v>950</v>
@@ -3988,16 +3997,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P14">
         <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="R14">
         <v>1.25</v>
@@ -4012,7 +4021,7 @@
         <v>1.11</v>
       </c>
       <c r="V14">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W14">
         <v>1.02</v>
@@ -4186,7 +4195,7 @@
         <v>1.04</v>
       </c>
       <c r="CB14" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4194,28 +4203,28 @@
         <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F15">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H15">
         <v>2.72</v>
       </c>
       <c r="I15">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J15">
         <v>3.9</v>
@@ -4224,13 +4233,13 @@
         <v>4.4</v>
       </c>
       <c r="L15">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="O15">
         <v>1.18</v>
@@ -4239,19 +4248,19 @@
         <v>2.56</v>
       </c>
       <c r="Q15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R15">
         <v>1.63</v>
       </c>
       <c r="S15">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="T15">
         <v>1.52</v>
       </c>
       <c r="U15">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V15">
         <v>1.5</v>
@@ -4260,52 +4269,52 @@
         <v>1.63</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Z15">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AA15">
         <v>50</v>
       </c>
       <c r="AB15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG15">
+        <v>13</v>
+      </c>
+      <c r="AH15">
         <v>15</v>
       </c>
-      <c r="AH15">
-        <v>17.5</v>
-      </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK15">
         <v>28</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN15">
         <v>14.5</v>
@@ -4320,16 +4329,16 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS15">
-        <v>1.76</v>
+        <v>5.7</v>
       </c>
       <c r="AT15">
         <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV15">
         <v>10</v>
@@ -4347,43 +4356,43 @@
         <v>11</v>
       </c>
       <c r="BA15">
-        <v>1.82</v>
+        <v>5.5</v>
       </c>
       <c r="BB15">
-        <v>1.82</v>
+        <v>5.5</v>
       </c>
       <c r="BC15">
         <v>17.5</v>
       </c>
       <c r="BD15">
-        <v>1.82</v>
+        <v>5.4</v>
       </c>
       <c r="BE15">
-        <v>1.82</v>
+        <v>5.8</v>
       </c>
       <c r="BF15">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG15">
         <v>12.5</v>
       </c>
       <c r="BH15">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BI15">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BJ15">
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN15">
         <v>5.9</v>
@@ -4392,19 +4401,19 @@
         <v>4.6</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BQ15">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT15">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BU15">
         <v>5.2</v>
@@ -4413,22 +4422,22 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15">
         <v>15.5</v>
       </c>
       <c r="CA15">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB15" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4436,94 +4445,94 @@
         <v>83</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F16">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="G16">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="H16">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I16">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L16">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>1.14</v>
       </c>
       <c r="P16">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="R16">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="S16">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="U16">
         <v>2.84</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="W16">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="X16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y16">
         <v>26</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="AA16">
         <v>60</v>
       </c>
       <c r="AB16">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE16">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AF16">
         <v>21</v>
@@ -4535,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="AI16">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AJ16">
         <v>32</v>
@@ -4550,109 +4559,109 @@
         <v>48</v>
       </c>
       <c r="AN16">
-        <v>11</v>
+        <v>8.4</v>
       </c>
       <c r="AO16">
+        <v>20</v>
+      </c>
+      <c r="AP16">
+        <v>5.7</v>
+      </c>
+      <c r="AQ16">
         <v>18</v>
       </c>
-      <c r="AP16">
+      <c r="AR16">
         <v>5.6</v>
       </c>
-      <c r="AQ16">
-        <v>18.5</v>
-      </c>
-      <c r="AR16">
-        <v>21</v>
-      </c>
       <c r="AS16">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT16">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AU16">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AV16">
         <v>11.5</v>
       </c>
       <c r="AW16">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="AX16">
+        <v>14</v>
+      </c>
+      <c r="AY16">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ16">
+        <v>10.5</v>
+      </c>
+      <c r="BA16">
+        <v>5.6</v>
+      </c>
+      <c r="BB16">
+        <v>19.5</v>
+      </c>
+      <c r="BC16">
+        <v>13.5</v>
+      </c>
+      <c r="BD16">
         <v>16.5</v>
-      </c>
-      <c r="AY16">
-        <v>10.5</v>
-      </c>
-      <c r="AZ16">
-        <v>12</v>
-      </c>
-      <c r="BA16">
-        <v>23</v>
-      </c>
-      <c r="BB16">
-        <v>5.5</v>
-      </c>
-      <c r="BC16">
-        <v>16.5</v>
-      </c>
-      <c r="BD16">
-        <v>20</v>
       </c>
       <c r="BE16">
         <v>5.8</v>
       </c>
       <c r="BF16">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="BG16">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BH16">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI16">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BJ16">
         <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BM16">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BP16">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BQ16">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BR16">
+        <v>20</v>
+      </c>
+      <c r="BS16">
+        <v>6.4</v>
+      </c>
+      <c r="BT16">
+        <v>7.6</v>
+      </c>
+      <c r="BU16">
+        <v>5.4</v>
+      </c>
+      <c r="BV16">
         <v>22</v>
-      </c>
-      <c r="BS16">
-        <v>6.8</v>
-      </c>
-      <c r="BT16">
-        <v>7.2</v>
-      </c>
-      <c r="BU16">
-        <v>5.2</v>
-      </c>
-      <c r="BV16">
-        <v>21</v>
       </c>
       <c r="BW16">
         <v>6.6</v>
@@ -4661,1468 +4670,1468 @@
         <v>25</v>
       </c>
       <c r="BY16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CA16">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB16" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C17" t="s">
         <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F17">
-        <v>2.3</v>
+        <v>1.02</v>
       </c>
       <c r="G17">
-        <v>2.38</v>
+        <v>600</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>1.02</v>
       </c>
       <c r="I17">
-        <v>4.3</v>
+        <v>870</v>
       </c>
       <c r="J17">
-        <v>2.96</v>
+        <v>1.02</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>950</v>
       </c>
       <c r="L17">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>2.28</v>
+        <v>1.1</v>
       </c>
       <c r="O17">
-        <v>1.7</v>
+        <v>1.05</v>
       </c>
       <c r="P17">
-        <v>1.42</v>
+        <v>1.07</v>
       </c>
       <c r="Q17">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="S17">
-        <v>7</v>
+        <v>1.05</v>
       </c>
       <c r="T17">
-        <v>2.46</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="W17">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="X17">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
         <v>1000</v>
       </c>
       <c r="AB17">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
         <v>1000</v>
       </c>
       <c r="AF17">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
         <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
         <v>1000</v>
       </c>
       <c r="AM17">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
         <v>1000</v>
       </c>
       <c r="AP17">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR17">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS17">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU17">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV17">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW17">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA17">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC17">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE17">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BF17">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG17">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BH17">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="BJ17">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>17</v>
+        <v>1.04</v>
       </c>
       <c r="BN17">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP17">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>9.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BR17">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BT17">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BV17">
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
         <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F18">
-        <v>1.69</v>
+        <v>2.32</v>
       </c>
       <c r="G18">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="H18">
-        <v>5.1</v>
+        <v>4</v>
       </c>
       <c r="I18">
-        <v>7.4</v>
+        <v>4.3</v>
       </c>
       <c r="J18">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="M18">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="N18">
-        <v>2.68</v>
+        <v>2.32</v>
       </c>
       <c r="O18">
+        <v>1.7</v>
+      </c>
+      <c r="P18">
         <v>1.42</v>
       </c>
-      <c r="P18">
-        <v>1.62</v>
-      </c>
       <c r="Q18">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="R18">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="S18">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="T18">
-        <v>2.06</v>
+        <v>2.44</v>
       </c>
       <c r="U18">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="V18">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="W18">
-        <v>2.04</v>
+        <v>1.71</v>
       </c>
       <c r="X18">
+        <v>7</v>
+      </c>
+      <c r="Y18">
+        <v>9.4</v>
+      </c>
+      <c r="Z18">
+        <v>27</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>6.4</v>
+      </c>
+      <c r="AC18">
+        <v>7.2</v>
+      </c>
+      <c r="AD18">
+        <v>20</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
         <v>12.5</v>
       </c>
-      <c r="Y18">
-        <v>18.5</v>
-      </c>
-      <c r="Z18">
+      <c r="AG18">
+        <v>13</v>
+      </c>
+      <c r="AH18">
+        <v>30</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>60</v>
+      </c>
+      <c r="AK18">
+        <v>95</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>330</v>
+      </c>
+      <c r="AN18">
+        <v>100</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>6.4</v>
+      </c>
+      <c r="AQ18">
+        <v>8.6</v>
+      </c>
+      <c r="AR18">
+        <v>17.5</v>
+      </c>
+      <c r="AS18">
+        <v>38</v>
+      </c>
+      <c r="AT18">
+        <v>5.7</v>
+      </c>
+      <c r="AU18">
+        <v>6.4</v>
+      </c>
+      <c r="AV18">
+        <v>17.5</v>
+      </c>
+      <c r="AW18">
+        <v>34</v>
+      </c>
+      <c r="AX18">
+        <v>11</v>
+      </c>
+      <c r="AY18">
+        <v>12</v>
+      </c>
+      <c r="AZ18">
+        <v>20</v>
+      </c>
+      <c r="BA18">
+        <v>42</v>
+      </c>
+      <c r="BB18">
+        <v>21</v>
+      </c>
+      <c r="BC18">
+        <v>24</v>
+      </c>
+      <c r="BD18">
+        <v>36</v>
+      </c>
+      <c r="BE18">
         <v>55</v>
       </c>
-      <c r="AA18">
-        <v>220</v>
-      </c>
-      <c r="AB18">
-        <v>7.8</v>
-      </c>
-      <c r="AC18">
-        <v>9.6</v>
-      </c>
-      <c r="AD18">
-        <v>28</v>
-      </c>
-      <c r="AE18">
-        <v>130</v>
-      </c>
-      <c r="AF18">
-        <v>11</v>
-      </c>
-      <c r="AG18">
-        <v>12</v>
-      </c>
-      <c r="AH18">
-        <v>29</v>
-      </c>
-      <c r="AI18">
-        <v>130</v>
-      </c>
-      <c r="AJ18">
-        <v>23</v>
-      </c>
-      <c r="AK18">
-        <v>26</v>
-      </c>
-      <c r="AL18">
-        <v>60</v>
-      </c>
-      <c r="AM18">
-        <v>220</v>
-      </c>
-      <c r="AN18">
-        <v>19</v>
-      </c>
-      <c r="AO18">
-        <v>200</v>
-      </c>
-      <c r="AP18">
-        <v>3.7</v>
-      </c>
-      <c r="AQ18">
-        <v>4</v>
-      </c>
-      <c r="AR18">
-        <v>4.7</v>
-      </c>
-      <c r="AS18">
-        <v>5.1</v>
-      </c>
-      <c r="AT18">
-        <v>3.1</v>
-      </c>
-      <c r="AU18">
-        <v>3.35</v>
-      </c>
-      <c r="AV18">
-        <v>4.4</v>
-      </c>
-      <c r="AW18">
-        <v>5</v>
-      </c>
-      <c r="AX18">
-        <v>3.55</v>
-      </c>
-      <c r="AY18">
-        <v>3.65</v>
-      </c>
-      <c r="AZ18">
-        <v>4.4</v>
-      </c>
-      <c r="BA18">
-        <v>5</v>
-      </c>
-      <c r="BB18">
-        <v>4.2</v>
-      </c>
-      <c r="BC18">
-        <v>4.3</v>
-      </c>
-      <c r="BD18">
-        <v>4.8</v>
-      </c>
-      <c r="BE18">
-        <v>5.1</v>
-      </c>
       <c r="BF18">
-        <v>4.1</v>
+        <v>24</v>
       </c>
       <c r="BG18">
-        <v>5.1</v>
+        <v>42</v>
       </c>
       <c r="BH18">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="BI18">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="BJ18">
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.3</v>
+        <v>18</v>
       </c>
       <c r="BN18">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BO18">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="BP18">
+        <v>22</v>
+      </c>
+      <c r="BQ18">
+        <v>10</v>
+      </c>
+      <c r="BR18">
+        <v>55</v>
+      </c>
+      <c r="BS18">
         <v>14</v>
       </c>
-      <c r="BQ18">
-        <v>5.4</v>
-      </c>
-      <c r="BR18">
-        <v>1000</v>
-      </c>
-      <c r="BS18">
-        <v>2.18</v>
-      </c>
       <c r="BT18">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BU18">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.24</v>
+        <v>13.5</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="BZ18">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="CA18">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="CB18" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C19" t="s">
         <v>99</v>
       </c>
       <c r="D19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L19">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
-        <v>1.1</v>
+        <v>2.68</v>
       </c>
       <c r="O19">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="P19">
+        <v>1.62</v>
+      </c>
+      <c r="Q19">
+        <v>2.12</v>
+      </c>
+      <c r="R19">
         <v>1.24</v>
       </c>
-      <c r="Q19">
-        <v>1.01</v>
-      </c>
-      <c r="R19">
-        <v>1.18</v>
-      </c>
       <c r="S19">
-        <v>1.13</v>
+        <v>3.5</v>
       </c>
       <c r="T19">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U19">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA19">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB19">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP19">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BE19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>2.26</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>2.18</v>
       </c>
       <c r="CB19" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F20">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="G20">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="H20">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="I20">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K20">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="L20">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="O20">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="P20">
-        <v>1.57</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="R20">
         <v>1.18</v>
       </c>
       <c r="S20">
-        <v>5.6</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
-        <v>2.2</v>
+        <v>1.11</v>
       </c>
       <c r="U20">
-        <v>1.73</v>
+        <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="W20">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>2.66</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.28</v>
+        <v>1.04</v>
       </c>
       <c r="BJ20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN20">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BP20">
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>13</v>
+        <v>1.04</v>
       </c>
       <c r="BT20">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="BV20">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BZ20">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>12.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
         <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>3.95</v>
       </c>
       <c r="G21">
-        <v>1.79</v>
+        <v>4.4</v>
       </c>
       <c r="H21">
-        <v>5.5</v>
+        <v>2.18</v>
       </c>
       <c r="I21">
-        <v>5.8</v>
+        <v>2.32</v>
       </c>
       <c r="J21">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="K21">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="L21">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="M21">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="N21">
-        <v>3.55</v>
+        <v>2.5</v>
       </c>
       <c r="O21">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="P21">
-        <v>1.89</v>
+        <v>1.57</v>
       </c>
       <c r="Q21">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="R21">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="S21">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="T21">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="U21">
-        <v>1.96</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="W21">
-        <v>2.26</v>
+        <v>1.3</v>
       </c>
       <c r="X21">
-        <v>13.5</v>
+        <v>8.6</v>
       </c>
       <c r="Y21">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="Z21">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="AA21">
-        <v>180</v>
+        <v>32</v>
       </c>
       <c r="AB21">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AC21">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD21">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="AE21">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="AF21">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="AG21">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AH21">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AI21">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="AJ21">
-        <v>22</v>
+        <v>130</v>
       </c>
       <c r="AK21">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AL21">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="AM21">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AN21">
-        <v>12.5</v>
+        <v>140</v>
       </c>
       <c r="AO21">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AP21">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AQ21">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR21">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AS21">
         <v>8.199999999999999</v>
       </c>
       <c r="AT21">
-        <v>7.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU21">
-        <v>7.8</v>
+        <v>6.8</v>
       </c>
       <c r="AV21">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AW21">
+        <v>8.6</v>
+      </c>
+      <c r="AX21">
         <v>8</v>
       </c>
-      <c r="AX21">
-        <v>9</v>
-      </c>
       <c r="AY21">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AZ21">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BA21">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="BB21">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD21">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BE21">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF21">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG21">
         <v>8.199999999999999</v>
       </c>
       <c r="BH21">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="BI21">
-        <v>2.78</v>
+        <v>2.28</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BK21">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN21">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="BO21">
-        <v>3.45</v>
+        <v>5.3</v>
       </c>
       <c r="BP21">
+        <v>1000</v>
+      </c>
+      <c r="BQ21">
+        <v>11.5</v>
+      </c>
+      <c r="BR21">
+        <v>1000</v>
+      </c>
+      <c r="BS21">
+        <v>13</v>
+      </c>
+      <c r="BT21">
+        <v>4.8</v>
+      </c>
+      <c r="BU21">
+        <v>3.7</v>
+      </c>
+      <c r="BV21">
+        <v>20</v>
+      </c>
+      <c r="BW21">
+        <v>9</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>12</v>
+      </c>
+      <c r="BZ21">
+        <v>55</v>
+      </c>
+      <c r="CA21">
         <v>12.5</v>
       </c>
-      <c r="BQ21">
-        <v>7</v>
-      </c>
-      <c r="BR21">
-        <v>29</v>
-      </c>
-      <c r="BS21">
-        <v>10.5</v>
-      </c>
-      <c r="BT21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU21">
-        <v>5.7</v>
-      </c>
-      <c r="BV21">
-        <v>1000</v>
-      </c>
-      <c r="BW21">
-        <v>12</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>13</v>
-      </c>
-      <c r="BZ21">
-        <v>24</v>
-      </c>
-      <c r="CA21">
-        <v>9.800000000000001</v>
-      </c>
       <c r="CB21" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F22">
-        <v>4.4</v>
+        <v>1.74</v>
       </c>
       <c r="G22">
-        <v>4.5</v>
+        <v>1.79</v>
       </c>
       <c r="H22">
+        <v>5.5</v>
+      </c>
+      <c r="I22">
+        <v>5.8</v>
+      </c>
+      <c r="J22">
+        <v>3.8</v>
+      </c>
+      <c r="K22">
+        <v>4</v>
+      </c>
+      <c r="L22">
+        <v>1.42</v>
+      </c>
+      <c r="M22">
+        <v>1.08</v>
+      </c>
+      <c r="N22">
+        <v>3.55</v>
+      </c>
+      <c r="O22">
+        <v>1.35</v>
+      </c>
+      <c r="P22">
+        <v>1.89</v>
+      </c>
+      <c r="Q22">
+        <v>2.02</v>
+      </c>
+      <c r="R22">
+        <v>1.34</v>
+      </c>
+      <c r="S22">
+        <v>3.7</v>
+      </c>
+      <c r="T22">
         <v>1.96</v>
       </c>
-      <c r="I22">
-        <v>1.99</v>
-      </c>
-      <c r="J22">
-        <v>3.7</v>
-      </c>
-      <c r="K22">
-        <v>3.75</v>
-      </c>
-      <c r="L22">
-        <v>1.41</v>
-      </c>
-      <c r="M22">
-        <v>1.07</v>
-      </c>
-      <c r="N22">
-        <v>3.8</v>
-      </c>
-      <c r="O22">
-        <v>1.32</v>
-      </c>
-      <c r="P22">
+      <c r="U22">
         <v>1.96</v>
       </c>
-      <c r="Q22">
-        <v>1.98</v>
-      </c>
-      <c r="R22">
-        <v>1.36</v>
-      </c>
-      <c r="S22">
-        <v>3.5</v>
-      </c>
-      <c r="T22">
-        <v>1.84</v>
-      </c>
-      <c r="U22">
-        <v>2.12</v>
-      </c>
       <c r="V22">
-        <v>2</v>
+        <v>1.21</v>
       </c>
       <c r="W22">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="X22">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y22">
-        <v>9.4</v>
+        <v>21</v>
       </c>
       <c r="Z22">
+        <v>50</v>
+      </c>
+      <c r="AA22">
+        <v>170</v>
+      </c>
+      <c r="AB22">
+        <v>8</v>
+      </c>
+      <c r="AC22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD22">
+        <v>26</v>
+      </c>
+      <c r="AE22">
+        <v>95</v>
+      </c>
+      <c r="AF22">
+        <v>10.5</v>
+      </c>
+      <c r="AG22">
+        <v>10.5</v>
+      </c>
+      <c r="AH22">
+        <v>21</v>
+      </c>
+      <c r="AI22">
+        <v>95</v>
+      </c>
+      <c r="AJ22">
+        <v>22</v>
+      </c>
+      <c r="AK22">
+        <v>23</v>
+      </c>
+      <c r="AL22">
+        <v>46</v>
+      </c>
+      <c r="AM22">
+        <v>150</v>
+      </c>
+      <c r="AN22">
+        <v>12.5</v>
+      </c>
+      <c r="AO22">
+        <v>120</v>
+      </c>
+      <c r="AP22">
+        <v>11.5</v>
+      </c>
+      <c r="AQ22">
+        <v>15.5</v>
+      </c>
+      <c r="AR22">
+        <v>8</v>
+      </c>
+      <c r="AS22">
+        <v>8.4</v>
+      </c>
+      <c r="AT22">
+        <v>7.2</v>
+      </c>
+      <c r="AU22">
+        <v>7.8</v>
+      </c>
+      <c r="AV22">
+        <v>19</v>
+      </c>
+      <c r="AW22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX22">
+        <v>9</v>
+      </c>
+      <c r="AY22">
+        <v>9</v>
+      </c>
+      <c r="AZ22">
+        <v>18</v>
+      </c>
+      <c r="BA22">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB22">
+        <v>16</v>
+      </c>
+      <c r="BC22">
+        <v>17</v>
+      </c>
+      <c r="BD22">
+        <v>8</v>
+      </c>
+      <c r="BE22">
+        <v>8.4</v>
+      </c>
+      <c r="BF22">
+        <v>11</v>
+      </c>
+      <c r="BG22">
+        <v>8.4</v>
+      </c>
+      <c r="BH22">
+        <v>3.35</v>
+      </c>
+      <c r="BI22">
+        <v>2.78</v>
+      </c>
+      <c r="BJ22">
+        <v>10.5</v>
+      </c>
+      <c r="BK22">
+        <v>6.4</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>15</v>
+      </c>
+      <c r="BN22">
+        <v>4.3</v>
+      </c>
+      <c r="BO22">
+        <v>3.45</v>
+      </c>
+      <c r="BP22">
+        <v>12.5</v>
+      </c>
+      <c r="BQ22">
+        <v>7</v>
+      </c>
+      <c r="BR22">
+        <v>29</v>
+      </c>
+      <c r="BS22">
+        <v>10.5</v>
+      </c>
+      <c r="BT22">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU22">
+        <v>5.7</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
         <v>12</v>
       </c>
-      <c r="AA22">
-        <v>22</v>
-      </c>
-      <c r="AB22">
-        <v>15.5</v>
-      </c>
-      <c r="AC22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD22">
-        <v>11</v>
-      </c>
-      <c r="AE22">
-        <v>21</v>
-      </c>
-      <c r="AF22">
-        <v>34</v>
-      </c>
-      <c r="AG22">
-        <v>17</v>
-      </c>
-      <c r="AH22">
-        <v>18.5</v>
-      </c>
-      <c r="AI22">
-        <v>38</v>
-      </c>
-      <c r="AJ22">
-        <v>95</v>
-      </c>
-      <c r="AK22">
-        <v>55</v>
-      </c>
-      <c r="AL22">
-        <v>65</v>
-      </c>
-      <c r="AM22">
-        <v>110</v>
-      </c>
-      <c r="AN22">
-        <v>65</v>
-      </c>
-      <c r="AO22">
-        <v>14.5</v>
-      </c>
-      <c r="AP22">
-        <v>12.5</v>
-      </c>
-      <c r="AQ22">
-        <v>8.4</v>
-      </c>
-      <c r="AR22">
-        <v>10.5</v>
-      </c>
-      <c r="AS22">
-        <v>20</v>
-      </c>
-      <c r="AT22">
-        <v>14</v>
-      </c>
-      <c r="AU22">
-        <v>7.6</v>
-      </c>
-      <c r="AV22">
-        <v>9.6</v>
-      </c>
-      <c r="AW22">
-        <v>18.5</v>
-      </c>
-      <c r="AX22">
-        <v>25</v>
-      </c>
-      <c r="AY22">
-        <v>15.5</v>
-      </c>
-      <c r="AZ22">
-        <v>17.5</v>
-      </c>
-      <c r="BA22">
-        <v>32</v>
-      </c>
-      <c r="BB22">
-        <v>14.5</v>
-      </c>
-      <c r="BC22">
-        <v>48</v>
-      </c>
-      <c r="BD22">
-        <v>50</v>
-      </c>
-      <c r="BE22">
-        <v>17</v>
-      </c>
-      <c r="BF22">
-        <v>48</v>
-      </c>
-      <c r="BG22">
-        <v>12.5</v>
-      </c>
-      <c r="BH22">
-        <v>3.5</v>
-      </c>
-      <c r="BI22">
-        <v>3.15</v>
-      </c>
-      <c r="BJ22">
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>13</v>
+      </c>
+      <c r="BZ22">
+        <v>24</v>
+      </c>
+      <c r="CA22">
         <v>9.800000000000001</v>
       </c>
-      <c r="BK22">
-        <v>6</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>14</v>
-      </c>
-      <c r="BN22">
-        <v>7.6</v>
-      </c>
-      <c r="BO22">
-        <v>5.5</v>
-      </c>
-      <c r="BP22">
-        <v>36</v>
-      </c>
-      <c r="BQ22">
-        <v>10.5</v>
-      </c>
-      <c r="BR22">
-        <v>46</v>
-      </c>
-      <c r="BS22">
-        <v>11.5</v>
-      </c>
-      <c r="BT22">
-        <v>4.7</v>
-      </c>
-      <c r="BU22">
-        <v>4.1</v>
-      </c>
-      <c r="BV22">
-        <v>14</v>
-      </c>
-      <c r="BW22">
-        <v>7.4</v>
-      </c>
-      <c r="BX22">
-        <v>28</v>
-      </c>
-      <c r="BY22">
-        <v>10</v>
-      </c>
-      <c r="BZ22">
-        <v>25</v>
-      </c>
-      <c r="CA22">
-        <v>9.6</v>
-      </c>
       <c r="CB22" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6130,187 +6139,187 @@
         <v>88</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
         <v>102</v>
       </c>
       <c r="D23" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F23">
-        <v>1.93</v>
+        <v>4.4</v>
       </c>
       <c r="G23">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="H23">
-        <v>4.3</v>
+        <v>1.96</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>1.99</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="K23">
         <v>3.75</v>
       </c>
       <c r="L23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M23">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N23">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="O23">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="P23">
-        <v>1.7</v>
+        <v>1.95</v>
       </c>
       <c r="Q23">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="R23">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="S23">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="T23">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="U23">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="V23">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="W23">
-        <v>1.93</v>
+        <v>1.28</v>
       </c>
       <c r="X23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>9.4</v>
       </c>
       <c r="Z23">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="AA23">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="AB23">
-        <v>7.6</v>
+        <v>15.5</v>
       </c>
       <c r="AC23">
         <v>8.199999999999999</v>
       </c>
       <c r="AD23">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AE23">
-        <v>70</v>
+        <v>21</v>
       </c>
       <c r="AF23">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AG23">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AH23">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AI23">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="AJ23">
+        <v>95</v>
+      </c>
+      <c r="AK23">
+        <v>55</v>
+      </c>
+      <c r="AL23">
+        <v>65</v>
+      </c>
+      <c r="AM23">
+        <v>110</v>
+      </c>
+      <c r="AN23">
+        <v>65</v>
+      </c>
+      <c r="AO23">
+        <v>14</v>
+      </c>
+      <c r="AP23">
+        <v>12.5</v>
+      </c>
+      <c r="AQ23">
+        <v>8.4</v>
+      </c>
+      <c r="AR23">
+        <v>10.5</v>
+      </c>
+      <c r="AS23">
+        <v>20</v>
+      </c>
+      <c r="AT23">
+        <v>14</v>
+      </c>
+      <c r="AU23">
+        <v>7.4</v>
+      </c>
+      <c r="AV23">
+        <v>9.6</v>
+      </c>
+      <c r="AW23">
+        <v>18.5</v>
+      </c>
+      <c r="AX23">
         <v>25</v>
       </c>
-      <c r="AK23">
-        <v>25</v>
-      </c>
-      <c r="AL23">
-        <v>46</v>
-      </c>
-      <c r="AM23">
-        <v>180</v>
-      </c>
-      <c r="AN23">
-        <v>19.5</v>
-      </c>
-      <c r="AO23">
-        <v>120</v>
-      </c>
-      <c r="AP23">
-        <v>8.4</v>
-      </c>
-      <c r="AQ23">
-        <v>10</v>
-      </c>
-      <c r="AR23">
-        <v>7.4</v>
-      </c>
-      <c r="AS23">
-        <v>9</v>
-      </c>
-      <c r="AT23">
-        <v>6.6</v>
-      </c>
-      <c r="AU23">
-        <v>6</v>
-      </c>
-      <c r="AV23">
-        <v>13.5</v>
-      </c>
-      <c r="AW23">
-        <v>8.4</v>
-      </c>
-      <c r="AX23">
-        <v>8.4</v>
-      </c>
       <c r="AY23">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AZ23">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA23">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BB23">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BC23">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="BD23">
-        <v>7.8</v>
+        <v>50</v>
       </c>
       <c r="BE23">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BF23">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="BG23">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BH23">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="BI23">
-        <v>2.76</v>
+        <v>3.15</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK23">
         <v>6.2</v>
@@ -6319,294 +6328,536 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN23">
+        <v>7.6</v>
+      </c>
+      <c r="BO23">
+        <v>5.5</v>
+      </c>
+      <c r="BP23">
+        <v>36</v>
+      </c>
+      <c r="BQ23">
+        <v>11.5</v>
+      </c>
+      <c r="BR23">
+        <v>46</v>
+      </c>
+      <c r="BS23">
+        <v>12</v>
+      </c>
+      <c r="BT23">
         <v>4.6</v>
       </c>
-      <c r="BO23">
-        <v>3.55</v>
-      </c>
-      <c r="BP23">
-        <v>15.5</v>
-      </c>
-      <c r="BQ23">
-        <v>7.6</v>
-      </c>
-      <c r="BR23">
-        <v>1000</v>
-      </c>
-      <c r="BS23">
-        <v>10</v>
-      </c>
-      <c r="BT23">
-        <v>7.8</v>
-      </c>
       <c r="BU23">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW23">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX23">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="BY23">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BZ23">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="CA23">
         <v>10</v>
       </c>
       <c r="CB23" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
         <v>103</v>
       </c>
       <c r="D24" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F24">
-        <v>1.43</v>
+        <v>2.08</v>
       </c>
       <c r="G24">
-        <v>1.52</v>
+        <v>2.14</v>
       </c>
       <c r="H24">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="I24">
+        <v>4.4</v>
+      </c>
+      <c r="J24">
+        <v>3.4</v>
+      </c>
+      <c r="K24">
+        <v>3.65</v>
+      </c>
+      <c r="L24">
+        <v>1.4</v>
+      </c>
+      <c r="M24">
+        <v>1.09</v>
+      </c>
+      <c r="N24">
+        <v>3</v>
+      </c>
+      <c r="O24">
+        <v>1.41</v>
+      </c>
+      <c r="P24">
+        <v>1.7</v>
+      </c>
+      <c r="Q24">
+        <v>2.26</v>
+      </c>
+      <c r="R24">
+        <v>1.26</v>
+      </c>
+      <c r="S24">
+        <v>4.2</v>
+      </c>
+      <c r="T24">
+        <v>2.02</v>
+      </c>
+      <c r="U24">
+        <v>1.84</v>
+      </c>
+      <c r="V24">
+        <v>1.29</v>
+      </c>
+      <c r="W24">
+        <v>1.87</v>
+      </c>
+      <c r="X24">
+        <v>13</v>
+      </c>
+      <c r="Y24">
+        <v>14</v>
+      </c>
+      <c r="Z24">
+        <v>34</v>
+      </c>
+      <c r="AA24">
+        <v>130</v>
+      </c>
+      <c r="AB24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC24">
         <v>8.199999999999999</v>
       </c>
-      <c r="J24">
-        <v>4.8</v>
-      </c>
-      <c r="K24">
-        <v>5.7</v>
-      </c>
-      <c r="L24">
-        <v>1.23</v>
-      </c>
-      <c r="M24">
-        <v>1.02</v>
-      </c>
-      <c r="N24">
-        <v>5.5</v>
-      </c>
-      <c r="O24">
-        <v>1.18</v>
-      </c>
-      <c r="P24">
-        <v>2.52</v>
-      </c>
-      <c r="Q24">
-        <v>1.53</v>
-      </c>
-      <c r="R24">
-        <v>1.61</v>
-      </c>
-      <c r="S24">
-        <v>2.38</v>
-      </c>
-      <c r="T24">
-        <v>1.74</v>
-      </c>
-      <c r="U24">
-        <v>2.08</v>
-      </c>
-      <c r="V24">
-        <v>1.13</v>
-      </c>
-      <c r="W24">
-        <v>2.92</v>
-      </c>
-      <c r="X24">
-        <v>34</v>
-      </c>
-      <c r="Y24">
-        <v>38</v>
-      </c>
-      <c r="Z24">
-        <v>80</v>
-      </c>
-      <c r="AA24">
-        <v>240</v>
-      </c>
-      <c r="AB24">
+      <c r="AD24">
+        <v>19</v>
+      </c>
+      <c r="AE24">
+        <v>70</v>
+      </c>
+      <c r="AF24">
         <v>12</v>
       </c>
-      <c r="AC24">
-        <v>13</v>
-      </c>
-      <c r="AD24">
-        <v>34</v>
-      </c>
-      <c r="AE24">
-        <v>110</v>
-      </c>
-      <c r="AF24">
-        <v>13</v>
-      </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH24">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ24">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK24">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="AL24">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM24">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="AN24">
-        <v>5.7</v>
+        <v>21</v>
       </c>
       <c r="AO24">
         <v>110</v>
       </c>
       <c r="AP24">
-        <v>19.5</v>
+        <v>8.4</v>
       </c>
       <c r="AQ24">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AT24">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU24">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AV24">
-        <v>19.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW24">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AX24">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY24">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AZ24">
         <v>15.5</v>
       </c>
       <c r="BA24">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BB24">
+        <v>21</v>
+      </c>
+      <c r="BC24">
+        <v>21</v>
+      </c>
+      <c r="BD24">
+        <v>3.6</v>
+      </c>
+      <c r="BE24">
+        <v>3.5</v>
+      </c>
+      <c r="BF24">
+        <v>14</v>
+      </c>
+      <c r="BG24">
+        <v>3.45</v>
+      </c>
+      <c r="BH24">
+        <v>3.05</v>
+      </c>
+      <c r="BI24">
+        <v>2.76</v>
+      </c>
+      <c r="BJ24">
+        <v>11</v>
+      </c>
+      <c r="BK24">
+        <v>6.2</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>13.5</v>
+      </c>
+      <c r="BN24">
+        <v>4.6</v>
+      </c>
+      <c r="BO24">
+        <v>3.55</v>
+      </c>
+      <c r="BP24">
+        <v>15.5</v>
+      </c>
+      <c r="BQ24">
+        <v>7.6</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
         <v>10</v>
       </c>
-      <c r="BC24">
+      <c r="BT24">
+        <v>7.8</v>
+      </c>
+      <c r="BU24">
+        <v>5.7</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>11</v>
+      </c>
+      <c r="BX24">
+        <v>60</v>
+      </c>
+      <c r="BY24">
+        <v>12</v>
+      </c>
+      <c r="BZ24">
+        <v>34</v>
+      </c>
+      <c r="CA24">
+        <v>10</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>89</v>
+      </c>
+      <c r="B25" t="s">
+        <v>90</v>
+      </c>
+      <c r="C25" t="s">
+        <v>104</v>
+      </c>
+      <c r="D25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" t="s">
+        <v>152</v>
+      </c>
+      <c r="F25">
+        <v>1.43</v>
+      </c>
+      <c r="G25">
+        <v>1.52</v>
+      </c>
+      <c r="H25">
+        <v>6.6</v>
+      </c>
+      <c r="I25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J25">
+        <v>5</v>
+      </c>
+      <c r="K25">
+        <v>5.7</v>
+      </c>
+      <c r="L25">
+        <v>1.23</v>
+      </c>
+      <c r="M25">
+        <v>1.02</v>
+      </c>
+      <c r="N25">
+        <v>5.7</v>
+      </c>
+      <c r="O25">
+        <v>1.18</v>
+      </c>
+      <c r="P25">
+        <v>2.6</v>
+      </c>
+      <c r="Q25">
+        <v>1.53</v>
+      </c>
+      <c r="R25">
+        <v>1.62</v>
+      </c>
+      <c r="S25">
+        <v>2.32</v>
+      </c>
+      <c r="T25">
+        <v>1.74</v>
+      </c>
+      <c r="U25">
+        <v>2.12</v>
+      </c>
+      <c r="V25">
+        <v>1.13</v>
+      </c>
+      <c r="W25">
+        <v>2.92</v>
+      </c>
+      <c r="X25">
+        <v>34</v>
+      </c>
+      <c r="Y25">
+        <v>38</v>
+      </c>
+      <c r="Z25">
+        <v>80</v>
+      </c>
+      <c r="AA25">
+        <v>230</v>
+      </c>
+      <c r="AB25">
+        <v>12</v>
+      </c>
+      <c r="AC25">
+        <v>13</v>
+      </c>
+      <c r="AD25">
+        <v>34</v>
+      </c>
+      <c r="AE25">
+        <v>110</v>
+      </c>
+      <c r="AF25">
+        <v>13</v>
+      </c>
+      <c r="AG25">
+        <v>12.5</v>
+      </c>
+      <c r="AH25">
+        <v>23</v>
+      </c>
+      <c r="AI25">
+        <v>90</v>
+      </c>
+      <c r="AJ25">
+        <v>16.5</v>
+      </c>
+      <c r="AK25">
+        <v>17.5</v>
+      </c>
+      <c r="AL25">
+        <v>36</v>
+      </c>
+      <c r="AM25">
+        <v>110</v>
+      </c>
+      <c r="AN25">
+        <v>5.6</v>
+      </c>
+      <c r="AO25">
+        <v>100</v>
+      </c>
+      <c r="AP25">
+        <v>19.5</v>
+      </c>
+      <c r="AQ25">
+        <v>4.9</v>
+      </c>
+      <c r="AR25">
+        <v>5.3</v>
+      </c>
+      <c r="AS25">
+        <v>5.6</v>
+      </c>
+      <c r="AT25">
+        <v>8.4</v>
+      </c>
+      <c r="AU25">
+        <v>9</v>
+      </c>
+      <c r="AV25">
+        <v>19.5</v>
+      </c>
+      <c r="AW25">
+        <v>5.4</v>
+      </c>
+      <c r="AX25">
+        <v>7.8</v>
+      </c>
+      <c r="AY25">
+        <v>7.6</v>
+      </c>
+      <c r="AZ25">
+        <v>15.5</v>
+      </c>
+      <c r="BA25">
+        <v>5.4</v>
+      </c>
+      <c r="BB25">
+        <v>10</v>
+      </c>
+      <c r="BC25">
         <v>10.5</v>
       </c>
-      <c r="BD24">
+      <c r="BD25">
         <v>20</v>
       </c>
-      <c r="BE24">
-        <v>1.01</v>
-      </c>
-      <c r="BF24">
-        <v>4.2</v>
-      </c>
-      <c r="BG24">
-        <v>1.01</v>
-      </c>
-      <c r="BH24">
+      <c r="BE25">
+        <v>5.4</v>
+      </c>
+      <c r="BF25">
+        <v>4.6</v>
+      </c>
+      <c r="BG25">
+        <v>5.4</v>
+      </c>
+      <c r="BH25">
         <v>4.7</v>
       </c>
-      <c r="BI24">
-        <v>3.5</v>
-      </c>
-      <c r="BJ24">
+      <c r="BI25">
+        <v>3.55</v>
+      </c>
+      <c r="BJ25">
         <v>10.5</v>
       </c>
-      <c r="BK24">
+      <c r="BK25">
         <v>5.1</v>
       </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
         <v>9.199999999999999</v>
       </c>
-      <c r="BN24">
+      <c r="BN25">
         <v>4.5</v>
       </c>
-      <c r="BO24">
+      <c r="BO25">
         <v>3.35</v>
       </c>
-      <c r="BP24">
+      <c r="BP25">
         <v>9</v>
       </c>
-      <c r="BQ24">
+      <c r="BQ25">
         <v>4.7</v>
       </c>
-      <c r="BR24">
+      <c r="BR25">
         <v>21</v>
       </c>
-      <c r="BS24">
+      <c r="BS25">
         <v>6.8</v>
       </c>
-      <c r="BT24">
+      <c r="BT25">
         <v>11.5</v>
       </c>
-      <c r="BU24">
+      <c r="BU25">
         <v>5.3</v>
       </c>
-      <c r="BV24">
-        <v>1000</v>
-      </c>
-      <c r="BW24">
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
         <v>8.4</v>
       </c>
-      <c r="BX24">
+      <c r="BX25">
         <v>55</v>
       </c>
-      <c r="BY24">
+      <c r="BY25">
         <v>8.4</v>
       </c>
-      <c r="BZ24">
+      <c r="BZ25">
         <v>12.5</v>
       </c>
-      <c r="CA24">
+      <c r="CA25">
         <v>5.5</v>
       </c>
-      <c r="CB24" t="s">
-        <v>150</v>
+      <c r="CB25" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="163">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>Canadian Premier League</t>
   </si>
   <si>
+    <t>Chinese League 2</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -298,6 +301,12 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>11:00:00</t>
+  </si>
+  <si>
+    <t>11:30:00</t>
+  </si>
+  <si>
     <t>17:30:00</t>
   </si>
   <si>
@@ -343,6 +352,15 @@
     <t>Cavalry</t>
   </si>
   <si>
+    <t>Beijing Tech FC</t>
+  </si>
+  <si>
+    <t>Lanzhou Longyuan Athletic</t>
+  </si>
+  <si>
+    <t>Wuhan Three Towns II</t>
+  </si>
+  <si>
     <t>Barracas Central</t>
   </si>
   <si>
@@ -370,12 +388,12 @@
     <t>Vikingur Olafsvik</t>
   </si>
   <si>
+    <t>Throttur</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
-    <t>Throttur</t>
-  </si>
-  <si>
     <t>Kari</t>
   </si>
   <si>
@@ -415,6 +433,15 @@
     <t>FC Supra du Quebec</t>
   </si>
   <si>
+    <t>Haimen Codion</t>
+  </si>
+  <si>
+    <t>Taian Tiankuang</t>
+  </si>
+  <si>
+    <t>Xiamen Feilu</t>
+  </si>
+  <si>
     <t>Aldosivi</t>
   </si>
   <si>
@@ -442,12 +469,12 @@
     <t>Fjolnir</t>
   </si>
   <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
     <t>Leiknir R</t>
   </si>
   <si>
-    <t>Afturelding</t>
-  </si>
-  <si>
     <t>Kormakur/Hvot</t>
   </si>
   <si>
@@ -475,7 +502,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 14:35:52</t>
+    <t>2026-07-28 16:43:34</t>
   </si>
 </sst>
 </file>
@@ -807,7 +834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB25"/>
+  <dimension ref="A1:CB28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1057,52 +1084,52 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="F2">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="G2">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="J2">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L2">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M2">
         <v>1.13</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="P2">
         <v>1.54</v>
       </c>
       <c r="Q2">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R2">
         <v>1.18</v>
@@ -1111,97 +1138,97 @@
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="X2">
         <v>8.4</v>
       </c>
       <c r="Y2">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AA2">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AC2">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE2">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AF2">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2">
         <v>26</v>
       </c>
       <c r="AI2">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ2">
+        <v>28</v>
+      </c>
+      <c r="AK2">
         <v>32</v>
-      </c>
-      <c r="AK2">
-        <v>34</v>
       </c>
       <c r="AL2">
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN2">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO2">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AP2">
         <v>7.8</v>
       </c>
       <c r="AQ2">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR2">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AS2">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV2">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY2">
         <v>10.5</v>
@@ -1210,88 +1237,88 @@
         <v>23</v>
       </c>
       <c r="BA2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BB2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BE2">
-        <v>85</v>
+        <v>48</v>
       </c>
       <c r="BF2">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="BG2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BH2">
         <v>2.72</v>
       </c>
       <c r="BI2">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BJ2">
+        <v>12</v>
+      </c>
+      <c r="BK2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BL2">
+        <v>240</v>
+      </c>
+      <c r="BM2">
+        <v>13</v>
+      </c>
+      <c r="BN2">
+        <v>4.7</v>
+      </c>
+      <c r="BO2">
+        <v>4.1</v>
+      </c>
+      <c r="BP2">
+        <v>18.5</v>
+      </c>
+      <c r="BQ2">
+        <v>7.8</v>
+      </c>
+      <c r="BR2">
+        <v>46</v>
+      </c>
+      <c r="BS2">
+        <v>10.5</v>
+      </c>
+      <c r="BT2">
+        <v>7.6</v>
+      </c>
+      <c r="BU2">
+        <v>6.2</v>
+      </c>
+      <c r="BV2">
+        <v>50</v>
+      </c>
+      <c r="BW2">
+        <v>10.5</v>
+      </c>
+      <c r="BX2">
+        <v>75</v>
+      </c>
+      <c r="BY2">
         <v>11.5</v>
       </c>
-      <c r="BK2">
-        <v>6</v>
-      </c>
-      <c r="BL2">
-        <v>230</v>
-      </c>
-      <c r="BM2">
-        <v>12.5</v>
-      </c>
-      <c r="BN2">
-        <v>5</v>
-      </c>
-      <c r="BO2">
-        <v>4.2</v>
-      </c>
-      <c r="BP2">
-        <v>21</v>
-      </c>
-      <c r="BQ2">
-        <v>8</v>
-      </c>
-      <c r="BR2">
-        <v>44</v>
-      </c>
-      <c r="BS2">
-        <v>10</v>
-      </c>
-      <c r="BT2">
-        <v>7.2</v>
-      </c>
-      <c r="BU2">
-        <v>4.9</v>
-      </c>
-      <c r="BV2">
-        <v>44</v>
-      </c>
-      <c r="BW2">
-        <v>10</v>
-      </c>
-      <c r="BX2">
-        <v>65</v>
-      </c>
-      <c r="BY2">
-        <v>11</v>
-      </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="CA2">
         <v>10.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1299,19 +1326,19 @@
         <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E3" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="F3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G3">
         <v>1.4</v>
@@ -1329,7 +1356,7 @@
         <v>5</v>
       </c>
       <c r="L3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M3">
         <v>1.09</v>
@@ -1338,13 +1365,13 @@
         <v>3.2</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R3">
         <v>1.26</v>
@@ -1353,10 +1380,10 @@
         <v>4.5</v>
       </c>
       <c r="T3">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V3">
         <v>1.08</v>
@@ -1365,22 +1392,22 @@
         <v>3.5</v>
       </c>
       <c r="X3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA3">
-        <v>840</v>
+        <v>910</v>
       </c>
       <c r="AB3">
         <v>5.9</v>
       </c>
       <c r="AC3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD3">
         <v>60</v>
@@ -1398,7 +1425,7 @@
         <v>50</v>
       </c>
       <c r="AI3">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="AJ3">
         <v>10</v>
@@ -1407,13 +1434,13 @@
         <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM3">
-        <v>580</v>
+        <v>480</v>
       </c>
       <c r="AN3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO3">
         <v>800</v>
@@ -1422,10 +1449,10 @@
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR3">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AS3">
         <v>75</v>
@@ -1440,13 +1467,13 @@
         <v>46</v>
       </c>
       <c r="AW3">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AX3">
         <v>5.8</v>
       </c>
       <c r="AY3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3">
         <v>42</v>
@@ -1455,85 +1482,85 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC3">
         <v>17.5</v>
       </c>
       <c r="BD3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE3">
         <v>55</v>
       </c>
       <c r="BF3">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BG3">
         <v>70</v>
       </c>
       <c r="BH3">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ3">
         <v>16</v>
       </c>
       <c r="BK3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BN3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="BO3">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="BP3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
+        <v>9.4</v>
+      </c>
+      <c r="BT3">
+        <v>17</v>
+      </c>
+      <c r="BU3">
+        <v>7.2</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
         <v>11.5</v>
       </c>
-      <c r="BT3">
-        <v>15.5</v>
-      </c>
-      <c r="BU3">
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>11.5</v>
+      </c>
+      <c r="BZ3">
+        <v>21</v>
+      </c>
+      <c r="CA3">
         <v>7.8</v>
       </c>
-      <c r="BV3">
-        <v>1000</v>
-      </c>
-      <c r="BW3">
-        <v>14.5</v>
-      </c>
-      <c r="BX3">
-        <v>1000</v>
-      </c>
-      <c r="BY3">
-        <v>14.5</v>
-      </c>
-      <c r="BZ3">
-        <v>22</v>
-      </c>
-      <c r="CA3">
-        <v>9.199999999999999</v>
-      </c>
       <c r="CB3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1541,22 +1568,22 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="F4">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G4">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H4">
         <v>5.2</v>
@@ -1565,13 +1592,13 @@
         <v>5.4</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M4">
         <v>1.1</v>
@@ -1580,25 +1607,25 @@
         <v>3.1</v>
       </c>
       <c r="O4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P4">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q4">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R4">
         <v>1.26</v>
       </c>
       <c r="S4">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U4">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
         <v>1.22</v>
@@ -1616,13 +1643,13 @@
         <v>40</v>
       </c>
       <c r="AA4">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AB4">
         <v>6.8</v>
       </c>
       <c r="AC4">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD4">
         <v>21</v>
@@ -1637,7 +1664,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI4">
         <v>100</v>
@@ -1655,10 +1682,10 @@
         <v>170</v>
       </c>
       <c r="AN4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO4">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="AP4">
         <v>9.800000000000001</v>
@@ -1670,22 +1697,22 @@
         <v>34</v>
       </c>
       <c r="AS4">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT4">
         <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW4">
         <v>40</v>
       </c>
       <c r="AX4">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY4">
         <v>9.6</v>
@@ -1694,7 +1721,7 @@
         <v>21</v>
       </c>
       <c r="BA4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB4">
         <v>18.5</v>
@@ -1703,10 +1730,10 @@
         <v>21</v>
       </c>
       <c r="BD4">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE4">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BF4">
         <v>15.5</v>
@@ -1718,10 +1745,10 @@
         <v>2.98</v>
       </c>
       <c r="BI4">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ4">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK4">
         <v>6.8</v>
@@ -1730,52 +1757,52 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BP4">
         <v>14</v>
       </c>
       <c r="BQ4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BT4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU4">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BV4">
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BY4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ4">
         <v>32</v>
       </c>
       <c r="CA4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CB4" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1783,34 +1810,34 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E5" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F5">
         <v>1.47</v>
       </c>
       <c r="G5">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H5">
         <v>6.6</v>
       </c>
       <c r="I5">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L5">
         <v>1.3</v>
@@ -1825,7 +1852,7 @@
         <v>1.21</v>
       </c>
       <c r="P5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
         <v>1.61</v>
@@ -1837,16 +1864,16 @@
         <v>2.52</v>
       </c>
       <c r="T5">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="X5">
         <v>27</v>
@@ -1870,7 +1897,7 @@
         <v>34</v>
       </c>
       <c r="AE5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF5">
         <v>11</v>
@@ -1879,7 +1906,7 @@
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI5">
         <v>85</v>
@@ -1897,46 +1924,46 @@
         <v>120</v>
       </c>
       <c r="AN5">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AO5">
         <v>110</v>
       </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AQ5">
-        <v>4.9</v>
+        <v>22</v>
       </c>
       <c r="AR5">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AS5">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU5">
         <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX5">
+        <v>8.6</v>
+      </c>
+      <c r="AY5">
         <v>8.800000000000001</v>
       </c>
-      <c r="AY5">
-        <v>7.6</v>
-      </c>
       <c r="AZ5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA5">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
@@ -1945,34 +1972,34 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BE5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BF5">
         <v>5.2</v>
       </c>
       <c r="BG5">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BH5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BI5">
         <v>3.35</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -1984,282 +2011,282 @@
         <v>9.4</v>
       </c>
       <c r="BQ5">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR5">
         <v>22</v>
       </c>
       <c r="BS5">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="CB5" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F6">
-        <v>2.42</v>
+        <v>5.3</v>
       </c>
       <c r="G6">
+        <v>990</v>
+      </c>
+      <c r="H6">
+        <v>1.41</v>
+      </c>
+      <c r="I6">
+        <v>1.68</v>
+      </c>
+      <c r="J6">
+        <v>3.25</v>
+      </c>
+      <c r="K6">
+        <v>9.4</v>
+      </c>
+      <c r="L6">
+        <v>1.32</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>3.3</v>
+      </c>
+      <c r="O6">
+        <v>1.33</v>
+      </c>
+      <c r="P6">
+        <v>1.69</v>
+      </c>
+      <c r="Q6">
+        <v>1.8</v>
+      </c>
+      <c r="R6">
+        <v>1.22</v>
+      </c>
+      <c r="S6">
+        <v>2.62</v>
+      </c>
+      <c r="T6">
+        <v>1.11</v>
+      </c>
+      <c r="U6">
+        <v>1.11</v>
+      </c>
+      <c r="V6">
         <v>2.46</v>
       </c>
-      <c r="H6">
-        <v>3.85</v>
-      </c>
-      <c r="I6">
-        <v>4.1</v>
-      </c>
-      <c r="J6">
-        <v>2.92</v>
-      </c>
-      <c r="K6">
-        <v>2.94</v>
-      </c>
-      <c r="L6">
-        <v>1.7</v>
-      </c>
-      <c r="M6">
-        <v>1.18</v>
-      </c>
-      <c r="N6">
-        <v>2.24</v>
-      </c>
-      <c r="O6">
-        <v>1.76</v>
-      </c>
-      <c r="P6">
-        <v>1.4</v>
-      </c>
-      <c r="Q6">
-        <v>3.25</v>
-      </c>
-      <c r="R6">
-        <v>1.14</v>
-      </c>
-      <c r="S6">
-        <v>7.8</v>
-      </c>
-      <c r="T6">
-        <v>2.5</v>
-      </c>
-      <c r="U6">
-        <v>1.6</v>
-      </c>
-      <c r="V6">
-        <v>1.32</v>
-      </c>
       <c r="W6">
-        <v>1.68</v>
+        <v>1.02</v>
       </c>
       <c r="X6">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
         <v>1000</v>
       </c>
       <c r="AM6">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ6">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AR6">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="AS6">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU6">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV6">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW6">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX6">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY6">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ6">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BA6">
-        <v>44</v>
+        <v>1.03</v>
       </c>
       <c r="BB6">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BC6">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BD6">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BE6">
-        <v>55</v>
+        <v>1.03</v>
       </c>
       <c r="BF6">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2267,1032 +2294,1032 @@
         <v>83</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E7" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F7">
-        <v>1.25</v>
+        <v>3.1</v>
       </c>
       <c r="G7">
+        <v>4.1</v>
+      </c>
+      <c r="H7">
+        <v>2.52</v>
+      </c>
+      <c r="I7">
+        <v>3.2</v>
+      </c>
+      <c r="J7">
+        <v>2.5</v>
+      </c>
+      <c r="K7">
+        <v>3.5</v>
+      </c>
+      <c r="L7">
+        <v>1.01</v>
+      </c>
+      <c r="M7">
+        <v>1.01</v>
+      </c>
+      <c r="N7">
+        <v>2.08</v>
+      </c>
+      <c r="O7">
+        <v>1.6</v>
+      </c>
+      <c r="P7">
+        <v>1.31</v>
+      </c>
+      <c r="Q7">
+        <v>2.96</v>
+      </c>
+      <c r="R7">
+        <v>1.09</v>
+      </c>
+      <c r="S7">
+        <v>2.96</v>
+      </c>
+      <c r="T7">
+        <v>1.11</v>
+      </c>
+      <c r="U7">
+        <v>1.11</v>
+      </c>
+      <c r="V7">
+        <v>1.46</v>
+      </c>
+      <c r="W7">
         <v>1.32</v>
       </c>
-      <c r="H7">
-        <v>10</v>
-      </c>
-      <c r="I7">
-        <v>13</v>
-      </c>
-      <c r="J7">
-        <v>6.8</v>
-      </c>
-      <c r="K7">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L7">
-        <v>1.16</v>
-      </c>
-      <c r="M7">
-        <v>1.01</v>
-      </c>
-      <c r="N7">
-        <v>7.6</v>
-      </c>
-      <c r="O7">
-        <v>1.1</v>
-      </c>
-      <c r="P7">
-        <v>3.7</v>
-      </c>
-      <c r="Q7">
-        <v>1.29</v>
-      </c>
-      <c r="R7">
-        <v>2.1</v>
-      </c>
-      <c r="S7">
-        <v>1.74</v>
-      </c>
-      <c r="T7">
-        <v>1.67</v>
-      </c>
-      <c r="U7">
-        <v>2.16</v>
-      </c>
-      <c r="V7">
-        <v>1.08</v>
-      </c>
-      <c r="W7">
-        <v>4.1</v>
-      </c>
       <c r="X7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="Y7">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="Z7">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA7">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AB7">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AD7">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE7">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI7">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ7">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL7">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM7">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AN7">
-        <v>3.2</v>
+        <v>1000</v>
       </c>
       <c r="AO7">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP7">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="AR7">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AS7">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AV7">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AW7">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AX7">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA7">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BB7">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="BC7">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BD7">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="BE7">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF7">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH7">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="F8">
-        <v>1.81</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
-        <v>2.24</v>
+        <v>4.4</v>
       </c>
       <c r="H8">
-        <v>2.82</v>
+        <v>2.28</v>
       </c>
       <c r="I8">
+        <v>2.76</v>
+      </c>
+      <c r="J8">
+        <v>2.72</v>
+      </c>
+      <c r="K8">
         <v>4.2</v>
       </c>
-      <c r="J8">
-        <v>3.15</v>
-      </c>
-      <c r="K8">
-        <v>5.1</v>
-      </c>
       <c r="L8">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.1</v>
+        <v>2.36</v>
       </c>
       <c r="O8">
-        <v>1.12</v>
+        <v>1.48</v>
       </c>
       <c r="P8">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="Q8">
-        <v>1.34</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.75</v>
+        <v>1.08</v>
       </c>
       <c r="S8">
-        <v>1.92</v>
+        <v>3</v>
       </c>
       <c r="T8">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="U8">
-        <v>2.84</v>
+        <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X8">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ8">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR8">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS8">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT8">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AU8">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>4</v>
+        <v>1.03</v>
       </c>
       <c r="AW8">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX8">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="AY8">
-        <v>3.75</v>
+        <v>1.03</v>
       </c>
       <c r="AZ8">
-        <v>3.95</v>
+        <v>1.03</v>
       </c>
       <c r="BA8">
-        <v>4.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB8">
-        <v>4.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC8">
-        <v>4.1</v>
+        <v>1.03</v>
       </c>
       <c r="BD8">
-        <v>4.3</v>
+        <v>1.03</v>
       </c>
       <c r="BE8">
-        <v>4.6</v>
+        <v>1.03</v>
       </c>
       <c r="BF8">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>3.45</v>
+        <v>1.04</v>
       </c>
       <c r="BJ8">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL8">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>7.8</v>
+        <v>1.04</v>
       </c>
       <c r="BN8">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP8">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="BR8">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BT8">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV8">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX8">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BZ8">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>5.1</v>
+        <v>1.04</v>
       </c>
       <c r="CB8" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E9" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9">
+        <v>2.42</v>
+      </c>
+      <c r="G9">
+        <v>2.46</v>
+      </c>
+      <c r="H9">
+        <v>3.85</v>
+      </c>
+      <c r="I9">
+        <v>4.1</v>
+      </c>
+      <c r="J9">
+        <v>2.9</v>
+      </c>
+      <c r="K9">
+        <v>2.94</v>
+      </c>
+      <c r="L9">
+        <v>1.7</v>
+      </c>
+      <c r="M9">
+        <v>1.18</v>
+      </c>
+      <c r="N9">
+        <v>2.2</v>
+      </c>
+      <c r="O9">
+        <v>1.76</v>
+      </c>
+      <c r="P9">
+        <v>1.38</v>
+      </c>
+      <c r="Q9">
+        <v>3.3</v>
+      </c>
+      <c r="R9">
+        <v>1.12</v>
+      </c>
+      <c r="S9">
+        <v>7.8</v>
+      </c>
+      <c r="T9">
+        <v>2.54</v>
+      </c>
+      <c r="U9">
+        <v>1.6</v>
+      </c>
+      <c r="V9">
+        <v>1.32</v>
+      </c>
+      <c r="W9">
+        <v>1.68</v>
+      </c>
+      <c r="X9">
+        <v>6.6</v>
+      </c>
+      <c r="Y9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z9">
+        <v>25</v>
+      </c>
+      <c r="AA9">
+        <v>1000</v>
+      </c>
+      <c r="AB9">
+        <v>6.4</v>
+      </c>
+      <c r="AC9">
+        <v>7.2</v>
+      </c>
+      <c r="AD9">
+        <v>20</v>
+      </c>
+      <c r="AE9">
         <v>90</v>
       </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>136</v>
-      </c>
-      <c r="F9">
-        <v>3.25</v>
-      </c>
-      <c r="G9">
-        <v>4.5</v>
-      </c>
-      <c r="H9">
-        <v>1.69</v>
-      </c>
-      <c r="I9">
-        <v>2.08</v>
-      </c>
-      <c r="J9">
-        <v>3.4</v>
-      </c>
-      <c r="K9">
+      <c r="AF9">
+        <v>13</v>
+      </c>
+      <c r="AG9">
+        <v>14</v>
+      </c>
+      <c r="AH9">
+        <v>34</v>
+      </c>
+      <c r="AI9">
+        <v>150</v>
+      </c>
+      <c r="AJ9">
+        <v>38</v>
+      </c>
+      <c r="AK9">
+        <v>46</v>
+      </c>
+      <c r="AL9">
+        <v>1000</v>
+      </c>
+      <c r="AM9">
+        <v>340</v>
+      </c>
+      <c r="AN9">
+        <v>55</v>
+      </c>
+      <c r="AO9">
+        <v>1000</v>
+      </c>
+      <c r="AP9">
+        <v>6</v>
+      </c>
+      <c r="AQ9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR9">
+        <v>22</v>
+      </c>
+      <c r="AS9">
+        <v>36</v>
+      </c>
+      <c r="AT9">
         <v>5.7</v>
       </c>
-      <c r="L9">
-        <v>1.16</v>
-      </c>
-      <c r="M9">
-        <v>1.01</v>
-      </c>
-      <c r="N9">
-        <v>8.4</v>
-      </c>
-      <c r="O9">
-        <v>1.09</v>
-      </c>
-      <c r="P9">
-        <v>3.2</v>
-      </c>
-      <c r="Q9">
-        <v>1.27</v>
-      </c>
-      <c r="R9">
-        <v>1.99</v>
-      </c>
-      <c r="S9">
-        <v>1.66</v>
-      </c>
-      <c r="T9">
-        <v>1.35</v>
-      </c>
-      <c r="U9">
-        <v>3</v>
-      </c>
-      <c r="V9">
-        <v>1.94</v>
-      </c>
-      <c r="W9">
-        <v>1.28</v>
-      </c>
-      <c r="X9">
-        <v>950</v>
-      </c>
-      <c r="Y9">
+      <c r="AU9">
+        <v>6.6</v>
+      </c>
+      <c r="AV9">
+        <v>17.5</v>
+      </c>
+      <c r="AW9">
+        <v>34</v>
+      </c>
+      <c r="AX9">
+        <v>11.5</v>
+      </c>
+      <c r="AY9">
+        <v>12.5</v>
+      </c>
+      <c r="AZ9">
         <v>27</v>
       </c>
-      <c r="Z9">
-        <v>24</v>
-      </c>
-      <c r="AA9">
-        <v>29</v>
-      </c>
-      <c r="AB9">
-        <v>40</v>
-      </c>
-      <c r="AC9">
-        <v>16.5</v>
-      </c>
-      <c r="AD9">
-        <v>14.5</v>
-      </c>
-      <c r="AE9">
-        <v>19.5</v>
-      </c>
-      <c r="AF9">
-        <v>50</v>
-      </c>
-      <c r="AG9">
-        <v>22</v>
-      </c>
-      <c r="AH9">
-        <v>17.5</v>
-      </c>
-      <c r="AI9">
-        <v>24</v>
-      </c>
-      <c r="AJ9">
-        <v>85</v>
-      </c>
-      <c r="AK9">
-        <v>40</v>
-      </c>
-      <c r="AL9">
-        <v>36</v>
-      </c>
-      <c r="AM9">
+      <c r="BA9">
         <v>44</v>
       </c>
-      <c r="AN9">
-        <v>18.5</v>
-      </c>
-      <c r="AO9">
-        <v>6.2</v>
-      </c>
-      <c r="AP9">
-        <v>4.7</v>
-      </c>
-      <c r="AQ9">
+      <c r="BB9">
+        <v>23</v>
+      </c>
+      <c r="BC9">
+        <v>38</v>
+      </c>
+      <c r="BD9">
+        <v>38</v>
+      </c>
+      <c r="BE9">
+        <v>55</v>
+      </c>
+      <c r="BF9">
+        <v>44</v>
+      </c>
+      <c r="BG9">
+        <v>42</v>
+      </c>
+      <c r="BH9">
+        <v>2.42</v>
+      </c>
+      <c r="BI9">
+        <v>2.02</v>
+      </c>
+      <c r="BJ9">
+        <v>13.5</v>
+      </c>
+      <c r="BK9">
+        <v>6.4</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>12</v>
+      </c>
+      <c r="BN9">
+        <v>5.2</v>
+      </c>
+      <c r="BO9">
         <v>4.3</v>
-      </c>
-      <c r="AR9">
-        <v>4.2</v>
-      </c>
-      <c r="AS9">
-        <v>4.4</v>
-      </c>
-      <c r="AT9">
-        <v>4.5</v>
-      </c>
-      <c r="AU9">
-        <v>3.95</v>
-      </c>
-      <c r="AV9">
-        <v>3.8</v>
-      </c>
-      <c r="AW9">
-        <v>4.1</v>
-      </c>
-      <c r="AX9">
-        <v>4.7</v>
-      </c>
-      <c r="AY9">
-        <v>4.2</v>
-      </c>
-      <c r="AZ9">
-        <v>4</v>
-      </c>
-      <c r="BA9">
-        <v>4.2</v>
-      </c>
-      <c r="BB9">
-        <v>4.8</v>
-      </c>
-      <c r="BC9">
-        <v>4.5</v>
-      </c>
-      <c r="BD9">
-        <v>4.5</v>
-      </c>
-      <c r="BE9">
-        <v>4.6</v>
-      </c>
-      <c r="BF9">
-        <v>4</v>
-      </c>
-      <c r="BG9">
-        <v>2.82</v>
-      </c>
-      <c r="BH9">
-        <v>6.8</v>
-      </c>
-      <c r="BI9">
-        <v>3.4</v>
-      </c>
-      <c r="BJ9">
-        <v>9</v>
-      </c>
-      <c r="BK9">
-        <v>3.85</v>
-      </c>
-      <c r="BL9">
-        <v>1000</v>
-      </c>
-      <c r="BM9">
-        <v>6</v>
-      </c>
-      <c r="BN9">
-        <v>9.4</v>
-      </c>
-      <c r="BO9">
-        <v>3.95</v>
       </c>
       <c r="BP9">
         <v>26</v>
       </c>
       <c r="BQ9">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT9">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU9">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="BV9">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BX9">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="BZ9">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="CB9" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C10" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E10" t="s">
+        <v>143</v>
+      </c>
+      <c r="F10">
+        <v>1.27</v>
+      </c>
+      <c r="G10">
+        <v>1.31</v>
+      </c>
+      <c r="H10">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>13</v>
+      </c>
+      <c r="J10">
+        <v>6.8</v>
+      </c>
+      <c r="K10">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L10">
+        <v>1.16</v>
+      </c>
+      <c r="M10">
+        <v>1.01</v>
+      </c>
+      <c r="N10">
+        <v>7.6</v>
+      </c>
+      <c r="O10">
+        <v>1.1</v>
+      </c>
+      <c r="P10">
+        <v>3.7</v>
+      </c>
+      <c r="Q10">
+        <v>1.3</v>
+      </c>
+      <c r="R10">
+        <v>2.1</v>
+      </c>
+      <c r="S10">
+        <v>1.74</v>
+      </c>
+      <c r="T10">
+        <v>1.69</v>
+      </c>
+      <c r="U10">
+        <v>2.2</v>
+      </c>
+      <c r="V10">
+        <v>1.08</v>
+      </c>
+      <c r="W10">
+        <v>4.2</v>
+      </c>
+      <c r="X10">
+        <v>55</v>
+      </c>
+      <c r="Y10">
+        <v>60</v>
+      </c>
+      <c r="Z10">
+        <v>130</v>
+      </c>
+      <c r="AA10">
+        <v>350</v>
+      </c>
+      <c r="AB10">
+        <v>18</v>
+      </c>
+      <c r="AC10">
+        <v>21</v>
+      </c>
+      <c r="AD10">
+        <v>44</v>
+      </c>
+      <c r="AE10">
+        <v>140</v>
+      </c>
+      <c r="AF10">
+        <v>13</v>
+      </c>
+      <c r="AG10">
+        <v>13</v>
+      </c>
+      <c r="AH10">
+        <v>27</v>
+      </c>
+      <c r="AI10">
+        <v>100</v>
+      </c>
+      <c r="AJ10">
+        <v>13</v>
+      </c>
+      <c r="AK10">
+        <v>14</v>
+      </c>
+      <c r="AL10">
+        <v>28</v>
+      </c>
+      <c r="AM10">
         <v>95</v>
       </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10">
-        <v>1.01</v>
-      </c>
-      <c r="G10">
-        <v>990</v>
-      </c>
-      <c r="H10">
-        <v>1.01</v>
-      </c>
-      <c r="I10">
-        <v>990</v>
-      </c>
-      <c r="J10">
-        <v>1.02</v>
-      </c>
-      <c r="K10">
-        <v>950</v>
-      </c>
-      <c r="L10">
-        <v>1.01</v>
-      </c>
-      <c r="M10">
-        <v>1.01</v>
-      </c>
-      <c r="N10">
-        <v>1.1</v>
-      </c>
-      <c r="O10">
-        <v>1.12</v>
-      </c>
-      <c r="P10">
-        <v>1.09</v>
-      </c>
-      <c r="Q10">
-        <v>1.12</v>
-      </c>
-      <c r="R10">
-        <v>1.09</v>
-      </c>
-      <c r="S10">
-        <v>1.12</v>
-      </c>
-      <c r="T10">
-        <v>1.11</v>
-      </c>
-      <c r="U10">
-        <v>1.11</v>
-      </c>
-      <c r="V10">
-        <v>1.01</v>
-      </c>
-      <c r="W10">
-        <v>1.01</v>
-      </c>
-      <c r="X10">
-        <v>1000</v>
-      </c>
-      <c r="Y10">
-        <v>1000</v>
-      </c>
-      <c r="Z10">
-        <v>1000</v>
-      </c>
-      <c r="AA10">
-        <v>1000</v>
-      </c>
-      <c r="AB10">
-        <v>1000</v>
-      </c>
-      <c r="AC10">
-        <v>1000</v>
-      </c>
-      <c r="AD10">
-        <v>1000</v>
-      </c>
-      <c r="AE10">
-        <v>1000</v>
-      </c>
-      <c r="AF10">
-        <v>1000</v>
-      </c>
-      <c r="AG10">
-        <v>1000</v>
-      </c>
-      <c r="AH10">
-        <v>1000</v>
-      </c>
-      <c r="AI10">
-        <v>1000</v>
-      </c>
-      <c r="AJ10">
-        <v>1000</v>
-      </c>
-      <c r="AK10">
-        <v>1000</v>
-      </c>
-      <c r="AL10">
-        <v>1000</v>
-      </c>
-      <c r="AM10">
-        <v>1000</v>
-      </c>
       <c r="AN10">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="AO10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP10">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>40</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AT10">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AU10">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY10">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC10">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BG10">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>3.5</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ10">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA10">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L11">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>1.1</v>
+        <v>7.4</v>
       </c>
       <c r="O11">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="P11">
-        <v>1.24</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.87</v>
       </c>
       <c r="S11">
-        <v>1.05</v>
+        <v>1.94</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>2.8</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3301,175 +3328,175 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AS11">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA11">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>5.5</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>7.4</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="CB11" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3477,273 +3504,273 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F12">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="H12">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>2.2</v>
       </c>
       <c r="J12">
-        <v>1.02</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
+        <v>5.4</v>
+      </c>
+      <c r="L12">
+        <v>1.15</v>
+      </c>
+      <c r="M12">
+        <v>1.01</v>
+      </c>
+      <c r="N12">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="O12">
+        <v>1.08</v>
+      </c>
+      <c r="P12">
+        <v>3.8</v>
+      </c>
+      <c r="Q12">
+        <v>1.24</v>
+      </c>
+      <c r="R12">
+        <v>2.16</v>
+      </c>
+      <c r="S12">
+        <v>1.66</v>
+      </c>
+      <c r="T12">
+        <v>1.32</v>
+      </c>
+      <c r="U12">
+        <v>3.3</v>
+      </c>
+      <c r="V12">
+        <v>1.83</v>
+      </c>
+      <c r="W12">
+        <v>1.38</v>
+      </c>
+      <c r="X12">
         <v>950</v>
       </c>
-      <c r="L12">
-        <v>1.01</v>
-      </c>
-      <c r="M12">
-        <v>1.01</v>
-      </c>
-      <c r="N12">
-        <v>1.26</v>
-      </c>
-      <c r="O12">
-        <v>1.02</v>
-      </c>
-      <c r="P12">
-        <v>1.25</v>
-      </c>
-      <c r="Q12">
-        <v>1.02</v>
-      </c>
-      <c r="R12">
-        <v>1.25</v>
-      </c>
-      <c r="S12">
-        <v>1.04</v>
-      </c>
-      <c r="T12">
-        <v>1.11</v>
-      </c>
-      <c r="U12">
-        <v>1.11</v>
-      </c>
-      <c r="V12">
-        <v>1.01</v>
-      </c>
-      <c r="W12">
-        <v>1.01</v>
-      </c>
-      <c r="X12">
-        <v>1000</v>
-      </c>
       <c r="Y12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Z12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB12">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AC12">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD12">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE12">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF12">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG12">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH12">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AI12">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AJ12">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK12">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL12">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM12">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AN12">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO12">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AP12">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AQ12">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR12">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AS12">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AT12">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AU12">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AV12">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AW12">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX12">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="AY12">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AZ12">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA12">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB12">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC12">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BD12">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BE12">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF12">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BG12">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="BH12">
         <v>1000</v>
       </c>
       <c r="BI12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ12">
         <v>1000</v>
       </c>
       <c r="BK12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN12">
         <v>1000</v>
       </c>
       <c r="BO12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP12">
         <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR12">
         <v>1000</v>
       </c>
       <c r="BS12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT12">
         <v>1000</v>
       </c>
       <c r="BU12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV12">
         <v>1000</v>
       </c>
       <c r="BW12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ12">
         <v>1000</v>
       </c>
       <c r="CA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E13" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F13">
-        <v>1.05</v>
+        <v>1.54</v>
       </c>
       <c r="G13">
-        <v>990</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>1.03</v>
+        <v>3</v>
       </c>
       <c r="I13">
-        <v>990</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>1.08</v>
+        <v>2.64</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3755,22 +3782,22 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="O13">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>1.25</v>
+        <v>2.46</v>
       </c>
       <c r="Q13">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="R13">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="S13">
-        <v>1.08</v>
+        <v>2.04</v>
       </c>
       <c r="T13">
         <v>1.11</v>
@@ -3779,10 +3806,10 @@
         <v>1.11</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>2</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3839,52 +3866,52 @@
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE13">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
@@ -3953,42 +3980,42 @@
         <v>1.04</v>
       </c>
       <c r="CB13" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="E14" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F14">
-        <v>1.05</v>
+        <v>2.98</v>
       </c>
       <c r="G14">
-        <v>990</v>
+        <v>4.4</v>
       </c>
       <c r="H14">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="I14">
-        <v>990</v>
+        <v>2.88</v>
       </c>
       <c r="J14">
-        <v>1.08</v>
+        <v>2.52</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>3.75</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -3997,34 +4024,34 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.27</v>
+        <v>2.92</v>
       </c>
       <c r="O14">
-        <v>1.06</v>
+        <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q14">
-        <v>1.06</v>
+        <v>2.22</v>
       </c>
       <c r="R14">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="S14">
-        <v>1.05</v>
+        <v>3.5</v>
       </c>
       <c r="T14">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="U14">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V14">
-        <v>1.02</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.29</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4189,532 +4216,532 @@
         <v>1.04</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="G15">
-        <v>2.6</v>
+        <v>3.45</v>
       </c>
       <c r="H15">
-        <v>2.72</v>
+        <v>2.04</v>
       </c>
       <c r="I15">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="J15">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="K15">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>5.5</v>
+        <v>1.26</v>
       </c>
       <c r="O15">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="P15">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="Q15">
-        <v>1.55</v>
+        <v>1.02</v>
       </c>
       <c r="R15">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="S15">
-        <v>2.34</v>
+        <v>1.05</v>
       </c>
       <c r="T15">
-        <v>1.52</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>2.64</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="X15">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ15">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AR15">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>5.7</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>12.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW15">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>5.5</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>5.4</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="BJ15">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BN15">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>4.6</v>
+        <v>1.04</v>
       </c>
       <c r="BP15">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>9</v>
+        <v>1.04</v>
       </c>
       <c r="BT15">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>5.2</v>
+        <v>1.04</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8.4</v>
+        <v>1.04</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ15">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB15" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E16" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F16">
-        <v>1.97</v>
+        <v>1.06</v>
       </c>
       <c r="G16">
-        <v>2.2</v>
+        <v>990</v>
       </c>
       <c r="H16">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="I16">
-        <v>3.65</v>
+        <v>990</v>
       </c>
       <c r="J16">
-        <v>4.1</v>
+        <v>1.08</v>
       </c>
       <c r="K16">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L16">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="P16">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="Q16">
-        <v>1.41</v>
+        <v>1.08</v>
       </c>
       <c r="R16">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="S16">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="T16">
-        <v>1.42</v>
+        <v>1.11</v>
       </c>
       <c r="U16">
-        <v>2.84</v>
+        <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="W16">
-        <v>1.83</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>5.4</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
-        <v>4</v>
+        <v>1.04</v>
       </c>
       <c r="BJ16">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BL16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BM16">
-        <v>8.199999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="BN16">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP16">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
-        <v>5.7</v>
+        <v>1.04</v>
       </c>
       <c r="BR16">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT16">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="BV16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BX16">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
-        <v>6.8</v>
+        <v>1.04</v>
       </c>
       <c r="BZ16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="CA16">
-        <v>5.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB16" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F17">
-        <v>1.02</v>
+        <v>2.64</v>
       </c>
       <c r="G17">
-        <v>600</v>
+        <v>990</v>
       </c>
       <c r="H17">
-        <v>1.02</v>
+        <v>2.04</v>
       </c>
       <c r="I17">
-        <v>870</v>
+        <v>990</v>
       </c>
       <c r="J17">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="K17">
-        <v>950</v>
+        <v>7.8</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -4723,22 +4750,22 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P17">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="R17">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="S17">
-        <v>1.05</v>
+        <v>1.74</v>
       </c>
       <c r="T17">
         <v>1.11</v>
@@ -4747,10 +4774,10 @@
         <v>1.11</v>
       </c>
       <c r="V17">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="W17">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -4921,526 +4948,526 @@
         <v>1.04</v>
       </c>
       <c r="CB17" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F18">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="G18">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H18">
+        <v>2.82</v>
+      </c>
+      <c r="I18">
+        <v>3.05</v>
+      </c>
+      <c r="J18">
         <v>4</v>
       </c>
-      <c r="I18">
-        <v>4.3</v>
-      </c>
-      <c r="J18">
-        <v>2.92</v>
-      </c>
       <c r="K18">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="L18">
-        <v>1.67</v>
+        <v>1.19</v>
       </c>
       <c r="M18">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N18">
-        <v>2.32</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="P18">
-        <v>1.42</v>
+        <v>2.96</v>
       </c>
       <c r="Q18">
-        <v>3.15</v>
+        <v>1.4</v>
       </c>
       <c r="R18">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="S18">
-        <v>7</v>
+        <v>2.04</v>
       </c>
       <c r="T18">
-        <v>2.44</v>
+        <v>1.44</v>
       </c>
       <c r="U18">
-        <v>1.63</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X18">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="Y18">
-        <v>9.4</v>
+        <v>25</v>
       </c>
       <c r="Z18">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA18">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB18">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AC18">
-        <v>7.2</v>
+        <v>12.5</v>
       </c>
       <c r="AD18">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF18">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AG18">
         <v>13</v>
       </c>
       <c r="AH18">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="AI18">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ18">
+        <v>32</v>
+      </c>
+      <c r="AK18">
+        <v>21</v>
+      </c>
+      <c r="AL18">
+        <v>26</v>
+      </c>
+      <c r="AM18">
+        <v>48</v>
+      </c>
+      <c r="AN18">
+        <v>9.6</v>
+      </c>
+      <c r="AO18">
+        <v>16</v>
+      </c>
+      <c r="AP18">
+        <v>6.2</v>
+      </c>
+      <c r="AQ18">
+        <v>19.5</v>
+      </c>
+      <c r="AR18">
+        <v>6</v>
+      </c>
+      <c r="AS18">
+        <v>6.4</v>
+      </c>
+      <c r="AT18">
+        <v>16</v>
+      </c>
+      <c r="AU18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV18">
+        <v>12.5</v>
+      </c>
+      <c r="AW18">
+        <v>6</v>
+      </c>
+      <c r="AX18">
+        <v>17.5</v>
+      </c>
+      <c r="AY18">
+        <v>10.5</v>
+      </c>
+      <c r="AZ18">
+        <v>12</v>
+      </c>
+      <c r="BA18">
+        <v>21</v>
+      </c>
+      <c r="BB18">
+        <v>5.9</v>
+      </c>
+      <c r="BC18">
+        <v>17</v>
+      </c>
+      <c r="BD18">
+        <v>20</v>
+      </c>
+      <c r="BE18">
+        <v>6.2</v>
+      </c>
+      <c r="BF18">
+        <v>7.6</v>
+      </c>
+      <c r="BG18">
+        <v>11.5</v>
+      </c>
+      <c r="BH18">
+        <v>5.4</v>
+      </c>
+      <c r="BI18">
+        <v>4.1</v>
+      </c>
+      <c r="BJ18">
+        <v>8.6</v>
+      </c>
+      <c r="BK18">
+        <v>6</v>
+      </c>
+      <c r="BL18">
         <v>60</v>
       </c>
-      <c r="AK18">
-        <v>95</v>
-      </c>
-      <c r="AL18">
-        <v>1000</v>
-      </c>
-      <c r="AM18">
-        <v>330</v>
-      </c>
-      <c r="AN18">
-        <v>100</v>
-      </c>
-      <c r="AO18">
-        <v>1000</v>
-      </c>
-      <c r="AP18">
+      <c r="BM18">
+        <v>8.4</v>
+      </c>
+      <c r="BN18">
         <v>6.4</v>
       </c>
-      <c r="AQ18">
-        <v>8.6</v>
-      </c>
-      <c r="AR18">
-        <v>17.5</v>
-      </c>
-      <c r="AS18">
-        <v>38</v>
-      </c>
-      <c r="AT18">
-        <v>5.7</v>
-      </c>
-      <c r="AU18">
-        <v>6.4</v>
-      </c>
-      <c r="AV18">
-        <v>17.5</v>
-      </c>
-      <c r="AW18">
-        <v>34</v>
-      </c>
-      <c r="AX18">
-        <v>11</v>
-      </c>
-      <c r="AY18">
-        <v>12</v>
-      </c>
-      <c r="AZ18">
-        <v>20</v>
-      </c>
-      <c r="BA18">
-        <v>42</v>
-      </c>
-      <c r="BB18">
+      <c r="BO18">
+        <v>4.6</v>
+      </c>
+      <c r="BP18">
+        <v>15.5</v>
+      </c>
+      <c r="BQ18">
+        <v>6</v>
+      </c>
+      <c r="BR18">
         <v>21</v>
       </c>
-      <c r="BC18">
-        <v>24</v>
-      </c>
-      <c r="BD18">
-        <v>36</v>
-      </c>
-      <c r="BE18">
-        <v>55</v>
-      </c>
-      <c r="BF18">
-        <v>24</v>
-      </c>
-      <c r="BG18">
-        <v>42</v>
-      </c>
-      <c r="BH18">
-        <v>2.48</v>
-      </c>
-      <c r="BI18">
-        <v>2.3</v>
-      </c>
-      <c r="BJ18">
-        <v>12.5</v>
-      </c>
-      <c r="BK18">
-        <v>7.4</v>
-      </c>
-      <c r="BL18">
-        <v>1000</v>
-      </c>
-      <c r="BM18">
-        <v>18</v>
-      </c>
-      <c r="BN18">
-        <v>4.8</v>
-      </c>
-      <c r="BO18">
-        <v>4.3</v>
-      </c>
-      <c r="BP18">
-        <v>22</v>
-      </c>
-      <c r="BQ18">
-        <v>10</v>
-      </c>
-      <c r="BR18">
-        <v>55</v>
-      </c>
       <c r="BS18">
-        <v>14</v>
+        <v>6.6</v>
       </c>
       <c r="BT18">
         <v>7.2</v>
       </c>
       <c r="BU18">
+        <v>5.2</v>
+      </c>
+      <c r="BV18">
+        <v>19.5</v>
+      </c>
+      <c r="BW18">
+        <v>6.4</v>
+      </c>
+      <c r="BX18">
+        <v>24</v>
+      </c>
+      <c r="BY18">
+        <v>6.8</v>
+      </c>
+      <c r="BZ18">
+        <v>12.5</v>
+      </c>
+      <c r="CA18">
         <v>5.5</v>
       </c>
-      <c r="BV18">
-        <v>1000</v>
-      </c>
-      <c r="BW18">
-        <v>13.5</v>
-      </c>
-      <c r="BX18">
-        <v>1000</v>
-      </c>
-      <c r="BY18">
-        <v>2.12</v>
-      </c>
-      <c r="BZ18">
-        <v>65</v>
-      </c>
-      <c r="CA18">
-        <v>2.12</v>
-      </c>
       <c r="CB18" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E19" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F19">
-        <v>1.69</v>
+        <v>2.38</v>
       </c>
       <c r="G19">
-        <v>1.98</v>
+        <v>2.6</v>
       </c>
       <c r="H19">
-        <v>5.1</v>
+        <v>2.76</v>
       </c>
       <c r="I19">
+        <v>2.98</v>
+      </c>
+      <c r="J19">
+        <v>3.9</v>
+      </c>
+      <c r="K19">
+        <v>4.4</v>
+      </c>
+      <c r="L19">
+        <v>1.24</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>5.6</v>
+      </c>
+      <c r="O19">
+        <v>1.18</v>
+      </c>
+      <c r="P19">
+        <v>2.56</v>
+      </c>
+      <c r="Q19">
+        <v>1.55</v>
+      </c>
+      <c r="R19">
+        <v>1.63</v>
+      </c>
+      <c r="S19">
+        <v>2.34</v>
+      </c>
+      <c r="T19">
+        <v>1.52</v>
+      </c>
+      <c r="U19">
+        <v>2.64</v>
+      </c>
+      <c r="V19">
+        <v>1.5</v>
+      </c>
+      <c r="W19">
+        <v>1.63</v>
+      </c>
+      <c r="X19">
+        <v>29</v>
+      </c>
+      <c r="Y19">
+        <v>19.5</v>
+      </c>
+      <c r="Z19">
+        <v>24</v>
+      </c>
+      <c r="AA19">
+        <v>50</v>
+      </c>
+      <c r="AB19">
+        <v>17</v>
+      </c>
+      <c r="AC19">
+        <v>11.5</v>
+      </c>
+      <c r="AD19">
+        <v>15</v>
+      </c>
+      <c r="AE19">
+        <v>32</v>
+      </c>
+      <c r="AF19">
+        <v>23</v>
+      </c>
+      <c r="AG19">
+        <v>13</v>
+      </c>
+      <c r="AH19">
+        <v>15</v>
+      </c>
+      <c r="AI19">
+        <v>36</v>
+      </c>
+      <c r="AJ19">
+        <v>38</v>
+      </c>
+      <c r="AK19">
+        <v>28</v>
+      </c>
+      <c r="AL19">
+        <v>34</v>
+      </c>
+      <c r="AM19">
+        <v>60</v>
+      </c>
+      <c r="AN19">
+        <v>14.5</v>
+      </c>
+      <c r="AO19">
+        <v>19</v>
+      </c>
+      <c r="AP19">
+        <v>19.5</v>
+      </c>
+      <c r="AQ19">
+        <v>13</v>
+      </c>
+      <c r="AR19">
+        <v>17.5</v>
+      </c>
+      <c r="AS19">
+        <v>5.7</v>
+      </c>
+      <c r="AT19">
+        <v>12.5</v>
+      </c>
+      <c r="AU19">
+        <v>7.6</v>
+      </c>
+      <c r="AV19">
+        <v>10</v>
+      </c>
+      <c r="AW19">
+        <v>20</v>
+      </c>
+      <c r="AX19">
+        <v>15</v>
+      </c>
+      <c r="AY19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ19">
+        <v>11</v>
+      </c>
+      <c r="BA19">
+        <v>5.5</v>
+      </c>
+      <c r="BB19">
+        <v>5.5</v>
+      </c>
+      <c r="BC19">
+        <v>17.5</v>
+      </c>
+      <c r="BD19">
+        <v>5.4</v>
+      </c>
+      <c r="BE19">
+        <v>5.8</v>
+      </c>
+      <c r="BF19">
+        <v>9.4</v>
+      </c>
+      <c r="BG19">
+        <v>12.5</v>
+      </c>
+      <c r="BH19">
+        <v>4.5</v>
+      </c>
+      <c r="BI19">
+        <v>3.6</v>
+      </c>
+      <c r="BJ19">
+        <v>8.6</v>
+      </c>
+      <c r="BK19">
+        <v>5.4</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>12</v>
+      </c>
+      <c r="BN19">
+        <v>5.9</v>
+      </c>
+      <c r="BO19">
+        <v>4.6</v>
+      </c>
+      <c r="BP19">
+        <v>16</v>
+      </c>
+      <c r="BQ19">
+        <v>7.6</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>9</v>
+      </c>
+      <c r="BT19">
+        <v>6.6</v>
+      </c>
+      <c r="BU19">
+        <v>5.2</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>8.4</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>9.4</v>
+      </c>
+      <c r="BZ19">
+        <v>15.5</v>
+      </c>
+      <c r="CA19">
         <v>7.4</v>
       </c>
-      <c r="J19">
-        <v>3.1</v>
-      </c>
-      <c r="K19">
-        <v>3.9</v>
-      </c>
-      <c r="L19">
-        <v>1.47</v>
-      </c>
-      <c r="M19">
-        <v>1.09</v>
-      </c>
-      <c r="N19">
-        <v>2.68</v>
-      </c>
-      <c r="O19">
-        <v>1.41</v>
-      </c>
-      <c r="P19">
-        <v>1.62</v>
-      </c>
-      <c r="Q19">
-        <v>2.12</v>
-      </c>
-      <c r="R19">
-        <v>1.24</v>
-      </c>
-      <c r="S19">
-        <v>3.5</v>
-      </c>
-      <c r="T19">
-        <v>2.06</v>
-      </c>
-      <c r="U19">
-        <v>1.72</v>
-      </c>
-      <c r="V19">
-        <v>1.16</v>
-      </c>
-      <c r="W19">
-        <v>2.02</v>
-      </c>
-      <c r="X19">
-        <v>12.5</v>
-      </c>
-      <c r="Y19">
-        <v>17</v>
-      </c>
-      <c r="Z19">
-        <v>55</v>
-      </c>
-      <c r="AA19">
-        <v>220</v>
-      </c>
-      <c r="AB19">
-        <v>7.2</v>
-      </c>
-      <c r="AC19">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD19">
-        <v>26</v>
-      </c>
-      <c r="AE19">
-        <v>130</v>
-      </c>
-      <c r="AF19">
-        <v>11</v>
-      </c>
-      <c r="AG19">
-        <v>12</v>
-      </c>
-      <c r="AH19">
-        <v>27</v>
-      </c>
-      <c r="AI19">
-        <v>130</v>
-      </c>
-      <c r="AJ19">
-        <v>23</v>
-      </c>
-      <c r="AK19">
-        <v>24</v>
-      </c>
-      <c r="AL19">
-        <v>60</v>
-      </c>
-      <c r="AM19">
-        <v>220</v>
-      </c>
-      <c r="AN19">
-        <v>17.5</v>
-      </c>
-      <c r="AO19">
-        <v>200</v>
-      </c>
-      <c r="AP19">
-        <v>4.3</v>
-      </c>
-      <c r="AQ19">
-        <v>4.7</v>
-      </c>
-      <c r="AR19">
-        <v>5.8</v>
-      </c>
-      <c r="AS19">
-        <v>6.2</v>
-      </c>
-      <c r="AT19">
-        <v>3.4</v>
-      </c>
-      <c r="AU19">
-        <v>3.75</v>
-      </c>
-      <c r="AV19">
-        <v>5.2</v>
-      </c>
-      <c r="AW19">
-        <v>6.2</v>
-      </c>
-      <c r="AX19">
-        <v>4.1</v>
-      </c>
-      <c r="AY19">
-        <v>4.2</v>
-      </c>
-      <c r="AZ19">
-        <v>5.2</v>
-      </c>
-      <c r="BA19">
-        <v>6.2</v>
-      </c>
-      <c r="BB19">
-        <v>5.1</v>
-      </c>
-      <c r="BC19">
-        <v>5.1</v>
-      </c>
-      <c r="BD19">
-        <v>5.9</v>
-      </c>
-      <c r="BE19">
-        <v>6.2</v>
-      </c>
-      <c r="BF19">
-        <v>4.7</v>
-      </c>
-      <c r="BG19">
-        <v>6.2</v>
-      </c>
-      <c r="BH19">
-        <v>3.15</v>
-      </c>
-      <c r="BI19">
-        <v>2.5</v>
-      </c>
-      <c r="BJ19">
-        <v>12.5</v>
-      </c>
-      <c r="BK19">
-        <v>5.2</v>
-      </c>
-      <c r="BL19">
-        <v>1000</v>
-      </c>
-      <c r="BM19">
-        <v>2.3</v>
-      </c>
-      <c r="BN19">
-        <v>4.4</v>
-      </c>
-      <c r="BO19">
-        <v>2.94</v>
-      </c>
-      <c r="BP19">
-        <v>14</v>
-      </c>
-      <c r="BQ19">
-        <v>5.4</v>
-      </c>
-      <c r="BR19">
-        <v>1000</v>
-      </c>
-      <c r="BS19">
-        <v>7</v>
-      </c>
-      <c r="BT19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BU19">
-        <v>4.6</v>
-      </c>
-      <c r="BV19">
-        <v>1000</v>
-      </c>
-      <c r="BW19">
-        <v>2.24</v>
-      </c>
-      <c r="BX19">
-        <v>1000</v>
-      </c>
-      <c r="BY19">
-        <v>2.26</v>
-      </c>
-      <c r="BZ19">
-        <v>34</v>
-      </c>
-      <c r="CA19">
-        <v>2.18</v>
-      </c>
       <c r="CB19" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C20" t="s">
         <v>100</v>
       </c>
       <c r="D20" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>870</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5452,19 +5479,19 @@
         <v>1.1</v>
       </c>
       <c r="O20">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q20">
         <v>1.01</v>
       </c>
       <c r="R20">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="S20">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="T20">
         <v>1.11</v>
@@ -5647,7 +5674,7 @@
         <v>1.04</v>
       </c>
       <c r="CB20" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5655,241 +5682,241 @@
         <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
         <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E21" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="F21">
-        <v>3.95</v>
+        <v>2.32</v>
       </c>
       <c r="G21">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="H21">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="I21">
-        <v>2.32</v>
+        <v>4.3</v>
       </c>
       <c r="J21">
+        <v>2.92</v>
+      </c>
+      <c r="K21">
+        <v>2.98</v>
+      </c>
+      <c r="L21">
+        <v>1.67</v>
+      </c>
+      <c r="M21">
+        <v>1.17</v>
+      </c>
+      <c r="N21">
+        <v>2.3</v>
+      </c>
+      <c r="O21">
+        <v>1.7</v>
+      </c>
+      <c r="P21">
+        <v>1.42</v>
+      </c>
+      <c r="Q21">
         <v>3.15</v>
       </c>
-      <c r="K21">
-        <v>3.25</v>
-      </c>
-      <c r="L21">
-        <v>1.49</v>
-      </c>
-      <c r="M21">
-        <v>1.13</v>
-      </c>
-      <c r="N21">
-        <v>2.5</v>
-      </c>
-      <c r="O21">
-        <v>1.58</v>
-      </c>
-      <c r="P21">
-        <v>1.57</v>
-      </c>
-      <c r="Q21">
-        <v>2.7</v>
-      </c>
       <c r="R21">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="S21">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="T21">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="U21">
-        <v>1.73</v>
+        <v>1.63</v>
       </c>
       <c r="V21">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="X21">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="Z21">
+        <v>27</v>
+      </c>
+      <c r="AA21">
+        <v>1000</v>
+      </c>
+      <c r="AB21">
+        <v>6.4</v>
+      </c>
+      <c r="AC21">
+        <v>7.2</v>
+      </c>
+      <c r="AD21">
+        <v>20</v>
+      </c>
+      <c r="AE21">
+        <v>1000</v>
+      </c>
+      <c r="AF21">
+        <v>12.5</v>
+      </c>
+      <c r="AG21">
         <v>13</v>
-      </c>
-      <c r="AA21">
-        <v>32</v>
-      </c>
-      <c r="AB21">
-        <v>11</v>
-      </c>
-      <c r="AC21">
-        <v>7.6</v>
-      </c>
-      <c r="AD21">
-        <v>12</v>
-      </c>
-      <c r="AE21">
-        <v>40</v>
-      </c>
-      <c r="AF21">
-        <v>30</v>
-      </c>
-      <c r="AG21">
-        <v>970</v>
       </c>
       <c r="AH21">
         <v>30</v>
       </c>
       <c r="AI21">
+        <v>1000</v>
+      </c>
+      <c r="AJ21">
+        <v>60</v>
+      </c>
+      <c r="AK21">
+        <v>95</v>
+      </c>
+      <c r="AL21">
+        <v>1000</v>
+      </c>
+      <c r="AM21">
+        <v>330</v>
+      </c>
+      <c r="AN21">
+        <v>100</v>
+      </c>
+      <c r="AO21">
+        <v>1000</v>
+      </c>
+      <c r="AP21">
+        <v>6.4</v>
+      </c>
+      <c r="AQ21">
+        <v>8.6</v>
+      </c>
+      <c r="AR21">
+        <v>17.5</v>
+      </c>
+      <c r="AS21">
+        <v>38</v>
+      </c>
+      <c r="AT21">
+        <v>5.7</v>
+      </c>
+      <c r="AU21">
+        <v>6.4</v>
+      </c>
+      <c r="AV21">
+        <v>17.5</v>
+      </c>
+      <c r="AW21">
+        <v>34</v>
+      </c>
+      <c r="AX21">
+        <v>11</v>
+      </c>
+      <c r="AY21">
+        <v>12</v>
+      </c>
+      <c r="AZ21">
+        <v>20</v>
+      </c>
+      <c r="BA21">
+        <v>42</v>
+      </c>
+      <c r="BB21">
+        <v>21</v>
+      </c>
+      <c r="BC21">
+        <v>24</v>
+      </c>
+      <c r="BD21">
+        <v>36</v>
+      </c>
+      <c r="BE21">
+        <v>55</v>
+      </c>
+      <c r="BF21">
+        <v>24</v>
+      </c>
+      <c r="BG21">
+        <v>42</v>
+      </c>
+      <c r="BH21">
+        <v>2.48</v>
+      </c>
+      <c r="BI21">
+        <v>2.3</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>7.4</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>18</v>
+      </c>
+      <c r="BN21">
+        <v>4.8</v>
+      </c>
+      <c r="BO21">
+        <v>4.3</v>
+      </c>
+      <c r="BP21">
+        <v>22</v>
+      </c>
+      <c r="BQ21">
+        <v>10</v>
+      </c>
+      <c r="BR21">
+        <v>55</v>
+      </c>
+      <c r="BS21">
+        <v>14</v>
+      </c>
+      <c r="BT21">
+        <v>7.2</v>
+      </c>
+      <c r="BU21">
+        <v>5.5</v>
+      </c>
+      <c r="BV21">
+        <v>1000</v>
+      </c>
+      <c r="BW21">
+        <v>13.5</v>
+      </c>
+      <c r="BX21">
+        <v>1000</v>
+      </c>
+      <c r="BY21">
+        <v>2.12</v>
+      </c>
+      <c r="BZ21">
         <v>65</v>
       </c>
-      <c r="AJ21">
-        <v>130</v>
-      </c>
-      <c r="AK21">
-        <v>90</v>
-      </c>
-      <c r="AL21">
-        <v>120</v>
-      </c>
-      <c r="AM21">
-        <v>250</v>
-      </c>
-      <c r="AN21">
-        <v>140</v>
-      </c>
-      <c r="AO21">
-        <v>32</v>
-      </c>
-      <c r="AP21">
-        <v>7.4</v>
-      </c>
-      <c r="AQ21">
-        <v>5.9</v>
-      </c>
-      <c r="AR21">
-        <v>11</v>
-      </c>
-      <c r="AS21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT21">
-        <v>9.4</v>
-      </c>
-      <c r="AU21">
-        <v>6.8</v>
-      </c>
-      <c r="AV21">
-        <v>10</v>
-      </c>
-      <c r="AW21">
-        <v>8.6</v>
-      </c>
-      <c r="AX21">
-        <v>8</v>
-      </c>
-      <c r="AY21">
-        <v>16</v>
-      </c>
-      <c r="AZ21">
-        <v>21</v>
-      </c>
-      <c r="BA21">
-        <v>9.4</v>
-      </c>
-      <c r="BB21">
-        <v>10</v>
-      </c>
-      <c r="BC21">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD21">
-        <v>10</v>
-      </c>
-      <c r="BE21">
-        <v>10.5</v>
-      </c>
-      <c r="BF21">
-        <v>10</v>
-      </c>
-      <c r="BG21">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BH21">
-        <v>2.66</v>
-      </c>
-      <c r="BI21">
-        <v>2.28</v>
-      </c>
-      <c r="BJ21">
-        <v>12</v>
-      </c>
-      <c r="BK21">
-        <v>6.8</v>
-      </c>
-      <c r="BL21">
-        <v>1000</v>
-      </c>
-      <c r="BM21">
-        <v>15.5</v>
-      </c>
-      <c r="BN21">
-        <v>7.2</v>
-      </c>
-      <c r="BO21">
-        <v>5.3</v>
-      </c>
-      <c r="BP21">
-        <v>1000</v>
-      </c>
-      <c r="BQ21">
-        <v>11.5</v>
-      </c>
-      <c r="BR21">
-        <v>1000</v>
-      </c>
-      <c r="BS21">
-        <v>13</v>
-      </c>
-      <c r="BT21">
-        <v>4.8</v>
-      </c>
-      <c r="BU21">
-        <v>3.7</v>
-      </c>
-      <c r="BV21">
-        <v>20</v>
-      </c>
-      <c r="BW21">
-        <v>9</v>
-      </c>
-      <c r="BX21">
-        <v>1000</v>
-      </c>
-      <c r="BY21">
-        <v>12</v>
-      </c>
-      <c r="BZ21">
-        <v>55</v>
-      </c>
       <c r="CA21">
-        <v>12.5</v>
+        <v>2.12</v>
       </c>
       <c r="CB21" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -5897,725 +5924,725 @@
         <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
         <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="E22" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F22">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="H22">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="J22">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="K22">
+        <v>3.9</v>
+      </c>
+      <c r="L22">
+        <v>1.47</v>
+      </c>
+      <c r="M22">
+        <v>1.09</v>
+      </c>
+      <c r="N22">
+        <v>2.68</v>
+      </c>
+      <c r="O22">
+        <v>1.42</v>
+      </c>
+      <c r="P22">
+        <v>1.62</v>
+      </c>
+      <c r="Q22">
+        <v>2.22</v>
+      </c>
+      <c r="R22">
+        <v>1.23</v>
+      </c>
+      <c r="S22">
+        <v>3.5</v>
+      </c>
+      <c r="T22">
+        <v>2.06</v>
+      </c>
+      <c r="U22">
+        <v>1.72</v>
+      </c>
+      <c r="V22">
+        <v>1.16</v>
+      </c>
+      <c r="W22">
+        <v>2.02</v>
+      </c>
+      <c r="X22">
+        <v>12.5</v>
+      </c>
+      <c r="Y22">
+        <v>18.5</v>
+      </c>
+      <c r="Z22">
+        <v>55</v>
+      </c>
+      <c r="AA22">
+        <v>220</v>
+      </c>
+      <c r="AB22">
+        <v>7.8</v>
+      </c>
+      <c r="AC22">
+        <v>9.6</v>
+      </c>
+      <c r="AD22">
+        <v>28</v>
+      </c>
+      <c r="AE22">
+        <v>130</v>
+      </c>
+      <c r="AF22">
+        <v>11</v>
+      </c>
+      <c r="AG22">
+        <v>12</v>
+      </c>
+      <c r="AH22">
+        <v>29</v>
+      </c>
+      <c r="AI22">
+        <v>130</v>
+      </c>
+      <c r="AJ22">
+        <v>23</v>
+      </c>
+      <c r="AK22">
+        <v>26</v>
+      </c>
+      <c r="AL22">
+        <v>60</v>
+      </c>
+      <c r="AM22">
+        <v>220</v>
+      </c>
+      <c r="AN22">
+        <v>19</v>
+      </c>
+      <c r="AO22">
+        <v>200</v>
+      </c>
+      <c r="AP22">
+        <v>3.7</v>
+      </c>
+      <c r="AQ22">
         <v>4</v>
       </c>
-      <c r="L22">
-        <v>1.42</v>
-      </c>
-      <c r="M22">
-        <v>1.08</v>
-      </c>
-      <c r="N22">
+      <c r="AR22">
+        <v>4.7</v>
+      </c>
+      <c r="AS22">
+        <v>5.1</v>
+      </c>
+      <c r="AT22">
+        <v>3.1</v>
+      </c>
+      <c r="AU22">
+        <v>3.35</v>
+      </c>
+      <c r="AV22">
+        <v>4.4</v>
+      </c>
+      <c r="AW22">
+        <v>5</v>
+      </c>
+      <c r="AX22">
         <v>3.55</v>
       </c>
-      <c r="O22">
-        <v>1.35</v>
-      </c>
-      <c r="P22">
-        <v>1.89</v>
-      </c>
-      <c r="Q22">
-        <v>2.02</v>
-      </c>
-      <c r="R22">
-        <v>1.34</v>
-      </c>
-      <c r="S22">
-        <v>3.7</v>
-      </c>
-      <c r="T22">
-        <v>1.96</v>
-      </c>
-      <c r="U22">
-        <v>1.96</v>
-      </c>
-      <c r="V22">
-        <v>1.21</v>
-      </c>
-      <c r="W22">
+      <c r="AY22">
+        <v>3.65</v>
+      </c>
+      <c r="AZ22">
+        <v>4.4</v>
+      </c>
+      <c r="BA22">
+        <v>5</v>
+      </c>
+      <c r="BB22">
+        <v>4.2</v>
+      </c>
+      <c r="BC22">
+        <v>4.3</v>
+      </c>
+      <c r="BD22">
+        <v>4.8</v>
+      </c>
+      <c r="BE22">
+        <v>5.1</v>
+      </c>
+      <c r="BF22">
+        <v>4.1</v>
+      </c>
+      <c r="BG22">
+        <v>5.1</v>
+      </c>
+      <c r="BH22">
+        <v>3.15</v>
+      </c>
+      <c r="BI22">
+        <v>2.5</v>
+      </c>
+      <c r="BJ22">
+        <v>12.5</v>
+      </c>
+      <c r="BK22">
+        <v>5.2</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>2.3</v>
+      </c>
+      <c r="BN22">
+        <v>4.4</v>
+      </c>
+      <c r="BO22">
+        <v>2.94</v>
+      </c>
+      <c r="BP22">
+        <v>14</v>
+      </c>
+      <c r="BQ22">
+        <v>5.4</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>7</v>
+      </c>
+      <c r="BT22">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU22">
+        <v>4.6</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>2.24</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
         <v>2.26</v>
       </c>
-      <c r="X22">
-        <v>13.5</v>
-      </c>
-      <c r="Y22">
-        <v>21</v>
-      </c>
-      <c r="Z22">
-        <v>50</v>
-      </c>
-      <c r="AA22">
-        <v>170</v>
-      </c>
-      <c r="AB22">
-        <v>8</v>
-      </c>
-      <c r="AC22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD22">
-        <v>26</v>
-      </c>
-      <c r="AE22">
-        <v>95</v>
-      </c>
-      <c r="AF22">
-        <v>10.5</v>
-      </c>
-      <c r="AG22">
-        <v>10.5</v>
-      </c>
-      <c r="AH22">
-        <v>21</v>
-      </c>
-      <c r="AI22">
-        <v>95</v>
-      </c>
-      <c r="AJ22">
-        <v>22</v>
-      </c>
-      <c r="AK22">
-        <v>23</v>
-      </c>
-      <c r="AL22">
-        <v>46</v>
-      </c>
-      <c r="AM22">
-        <v>150</v>
-      </c>
-      <c r="AN22">
-        <v>12.5</v>
-      </c>
-      <c r="AO22">
-        <v>120</v>
-      </c>
-      <c r="AP22">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22">
-        <v>15.5</v>
-      </c>
-      <c r="AR22">
-        <v>8</v>
-      </c>
-      <c r="AS22">
-        <v>8.4</v>
-      </c>
-      <c r="AT22">
-        <v>7.2</v>
-      </c>
-      <c r="AU22">
-        <v>7.8</v>
-      </c>
-      <c r="AV22">
-        <v>19</v>
-      </c>
-      <c r="AW22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX22">
-        <v>9</v>
-      </c>
-      <c r="AY22">
-        <v>9</v>
-      </c>
-      <c r="AZ22">
-        <v>18</v>
-      </c>
-      <c r="BA22">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BB22">
-        <v>16</v>
-      </c>
-      <c r="BC22">
-        <v>17</v>
-      </c>
-      <c r="BD22">
-        <v>8</v>
-      </c>
-      <c r="BE22">
-        <v>8.4</v>
-      </c>
-      <c r="BF22">
-        <v>11</v>
-      </c>
-      <c r="BG22">
-        <v>8.4</v>
-      </c>
-      <c r="BH22">
-        <v>3.35</v>
-      </c>
-      <c r="BI22">
-        <v>2.78</v>
-      </c>
-      <c r="BJ22">
-        <v>10.5</v>
-      </c>
-      <c r="BK22">
-        <v>6.4</v>
-      </c>
-      <c r="BL22">
-        <v>1000</v>
-      </c>
-      <c r="BM22">
-        <v>15</v>
-      </c>
-      <c r="BN22">
-        <v>4.3</v>
-      </c>
-      <c r="BO22">
-        <v>3.45</v>
-      </c>
-      <c r="BP22">
-        <v>12.5</v>
-      </c>
-      <c r="BQ22">
-        <v>7</v>
-      </c>
-      <c r="BR22">
-        <v>29</v>
-      </c>
-      <c r="BS22">
-        <v>10.5</v>
-      </c>
-      <c r="BT22">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BU22">
-        <v>5.7</v>
-      </c>
-      <c r="BV22">
-        <v>1000</v>
-      </c>
-      <c r="BW22">
-        <v>12</v>
-      </c>
-      <c r="BX22">
-        <v>1000</v>
-      </c>
-      <c r="BY22">
-        <v>13</v>
-      </c>
       <c r="BZ22">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="CA22">
-        <v>9.800000000000001</v>
+        <v>2.18</v>
       </c>
       <c r="CB22" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="E23" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F23">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="G23">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="K23">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L23">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N23">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="O23">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="P23">
-        <v>1.95</v>
+        <v>1.24</v>
       </c>
       <c r="Q23">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="R23">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="S23">
-        <v>3.5</v>
+        <v>1.13</v>
       </c>
       <c r="T23">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="W23">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X23">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="Z23">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AA23">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB23">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AC23">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AE23">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AF23">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG23">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AH23">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AI23">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AK23">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AL23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM23">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN23">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO23">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AP23">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR23">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS23">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AT23">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AU23">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV23">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW23">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX23">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY23">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA23">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BB23">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BC23">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BD23">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BF23">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG23">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH23">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="BI23">
-        <v>3.15</v>
+        <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
-        <v>6.2</v>
+        <v>1.04</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>15</v>
+        <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
-        <v>11.5</v>
+        <v>1.04</v>
       </c>
       <c r="BR23">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BS23">
-        <v>12</v>
+        <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
-        <v>10</v>
+        <v>1.04</v>
       </c>
       <c r="CB23" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="B24" t="s">
+        <v>91</v>
+      </c>
+      <c r="C24" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" t="s">
+        <v>130</v>
+      </c>
+      <c r="E24" t="s">
+        <v>157</v>
+      </c>
+      <c r="F24">
+        <v>3.95</v>
+      </c>
+      <c r="G24">
+        <v>4.4</v>
+      </c>
+      <c r="H24">
+        <v>2.18</v>
+      </c>
+      <c r="I24">
+        <v>2.32</v>
+      </c>
+      <c r="J24">
+        <v>3.15</v>
+      </c>
+      <c r="K24">
+        <v>3.35</v>
+      </c>
+      <c r="L24">
+        <v>1.6</v>
+      </c>
+      <c r="M24">
+        <v>1.13</v>
+      </c>
+      <c r="N24">
+        <v>2.5</v>
+      </c>
+      <c r="O24">
+        <v>1.58</v>
+      </c>
+      <c r="P24">
+        <v>1.53</v>
+      </c>
+      <c r="Q24">
+        <v>2.7</v>
+      </c>
+      <c r="R24">
+        <v>1.18</v>
+      </c>
+      <c r="S24">
+        <v>5.6</v>
+      </c>
+      <c r="T24">
+        <v>2.2</v>
+      </c>
+      <c r="U24">
+        <v>1.73</v>
+      </c>
+      <c r="V24">
+        <v>1.76</v>
+      </c>
+      <c r="W24">
+        <v>1.3</v>
+      </c>
+      <c r="X24">
+        <v>8.6</v>
+      </c>
+      <c r="Y24">
+        <v>6.8</v>
+      </c>
+      <c r="Z24">
+        <v>13</v>
+      </c>
+      <c r="AA24">
+        <v>32</v>
+      </c>
+      <c r="AB24">
+        <v>11</v>
+      </c>
+      <c r="AC24">
+        <v>7.6</v>
+      </c>
+      <c r="AD24">
+        <v>12</v>
+      </c>
+      <c r="AE24">
+        <v>40</v>
+      </c>
+      <c r="AF24">
+        <v>30</v>
+      </c>
+      <c r="AG24">
+        <v>970</v>
+      </c>
+      <c r="AH24">
+        <v>30</v>
+      </c>
+      <c r="AI24">
+        <v>65</v>
+      </c>
+      <c r="AJ24">
+        <v>130</v>
+      </c>
+      <c r="AK24">
         <v>90</v>
       </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24">
-        <v>2.08</v>
-      </c>
-      <c r="G24">
-        <v>2.14</v>
-      </c>
-      <c r="H24">
-        <v>4.1</v>
-      </c>
-      <c r="I24">
-        <v>4.4</v>
-      </c>
-      <c r="J24">
-        <v>3.4</v>
-      </c>
-      <c r="K24">
-        <v>3.65</v>
-      </c>
-      <c r="L24">
-        <v>1.4</v>
-      </c>
-      <c r="M24">
-        <v>1.09</v>
-      </c>
-      <c r="N24">
-        <v>3</v>
-      </c>
-      <c r="O24">
-        <v>1.41</v>
-      </c>
-      <c r="P24">
-        <v>1.7</v>
-      </c>
-      <c r="Q24">
-        <v>2.26</v>
-      </c>
-      <c r="R24">
-        <v>1.26</v>
-      </c>
-      <c r="S24">
-        <v>4.2</v>
-      </c>
-      <c r="T24">
-        <v>2.02</v>
-      </c>
-      <c r="U24">
-        <v>1.84</v>
-      </c>
-      <c r="V24">
-        <v>1.29</v>
-      </c>
-      <c r="W24">
-        <v>1.87</v>
-      </c>
-      <c r="X24">
+      <c r="AL24">
+        <v>120</v>
+      </c>
+      <c r="AM24">
+        <v>250</v>
+      </c>
+      <c r="AN24">
+        <v>140</v>
+      </c>
+      <c r="AO24">
+        <v>32</v>
+      </c>
+      <c r="AP24">
+        <v>7.4</v>
+      </c>
+      <c r="AQ24">
+        <v>5.9</v>
+      </c>
+      <c r="AR24">
+        <v>11</v>
+      </c>
+      <c r="AS24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT24">
+        <v>9.4</v>
+      </c>
+      <c r="AU24">
+        <v>6.8</v>
+      </c>
+      <c r="AV24">
+        <v>10</v>
+      </c>
+      <c r="AW24">
+        <v>8.6</v>
+      </c>
+      <c r="AX24">
+        <v>8</v>
+      </c>
+      <c r="AY24">
+        <v>16</v>
+      </c>
+      <c r="AZ24">
+        <v>21</v>
+      </c>
+      <c r="BA24">
+        <v>9.4</v>
+      </c>
+      <c r="BB24">
+        <v>10</v>
+      </c>
+      <c r="BC24">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD24">
+        <v>10</v>
+      </c>
+      <c r="BE24">
+        <v>10.5</v>
+      </c>
+      <c r="BF24">
+        <v>10</v>
+      </c>
+      <c r="BG24">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH24">
+        <v>2.66</v>
+      </c>
+      <c r="BI24">
+        <v>2.28</v>
+      </c>
+      <c r="BJ24">
+        <v>12</v>
+      </c>
+      <c r="BK24">
+        <v>6.8</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>15.5</v>
+      </c>
+      <c r="BN24">
+        <v>7.2</v>
+      </c>
+      <c r="BO24">
+        <v>5.3</v>
+      </c>
+      <c r="BP24">
+        <v>1000</v>
+      </c>
+      <c r="BQ24">
+        <v>11.5</v>
+      </c>
+      <c r="BR24">
+        <v>1000</v>
+      </c>
+      <c r="BS24">
         <v>13</v>
       </c>
-      <c r="Y24">
-        <v>14</v>
-      </c>
-      <c r="Z24">
-        <v>34</v>
-      </c>
-      <c r="AA24">
-        <v>130</v>
-      </c>
-      <c r="AB24">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC24">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD24">
-        <v>19</v>
-      </c>
-      <c r="AE24">
-        <v>70</v>
-      </c>
-      <c r="AF24">
-        <v>12</v>
-      </c>
-      <c r="AG24">
-        <v>1000</v>
-      </c>
-      <c r="AH24">
-        <v>22</v>
-      </c>
-      <c r="AI24">
-        <v>95</v>
-      </c>
-      <c r="AJ24">
-        <v>1000</v>
-      </c>
-      <c r="AK24">
-        <v>27</v>
-      </c>
-      <c r="AL24">
-        <v>1000</v>
-      </c>
-      <c r="AM24">
-        <v>180</v>
-      </c>
-      <c r="AN24">
-        <v>21</v>
-      </c>
-      <c r="AO24">
-        <v>110</v>
-      </c>
-      <c r="AP24">
-        <v>8.4</v>
-      </c>
-      <c r="AQ24">
-        <v>10</v>
-      </c>
-      <c r="AR24">
-        <v>3.25</v>
-      </c>
-      <c r="AS24">
-        <v>3.5</v>
-      </c>
-      <c r="AT24">
-        <v>6.6</v>
-      </c>
-      <c r="AU24">
-        <v>6</v>
-      </c>
-      <c r="AV24">
-        <v>13.5</v>
-      </c>
-      <c r="AW24">
-        <v>3.4</v>
-      </c>
-      <c r="AX24">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY24">
-        <v>8</v>
-      </c>
-      <c r="AZ24">
-        <v>15.5</v>
-      </c>
-      <c r="BA24">
-        <v>3.45</v>
-      </c>
-      <c r="BB24">
-        <v>21</v>
-      </c>
-      <c r="BC24">
-        <v>21</v>
-      </c>
-      <c r="BD24">
-        <v>3.6</v>
-      </c>
-      <c r="BE24">
-        <v>3.5</v>
-      </c>
-      <c r="BF24">
-        <v>14</v>
-      </c>
-      <c r="BG24">
-        <v>3.45</v>
-      </c>
-      <c r="BH24">
-        <v>3.05</v>
-      </c>
-      <c r="BI24">
-        <v>2.76</v>
-      </c>
-      <c r="BJ24">
-        <v>11</v>
-      </c>
-      <c r="BK24">
-        <v>6.2</v>
-      </c>
-      <c r="BL24">
-        <v>1000</v>
-      </c>
-      <c r="BM24">
-        <v>13.5</v>
-      </c>
-      <c r="BN24">
-        <v>4.6</v>
-      </c>
-      <c r="BO24">
-        <v>3.55</v>
-      </c>
-      <c r="BP24">
-        <v>15.5</v>
-      </c>
-      <c r="BQ24">
-        <v>7.6</v>
-      </c>
-      <c r="BR24">
-        <v>1000</v>
-      </c>
-      <c r="BS24">
-        <v>10</v>
-      </c>
       <c r="BT24">
-        <v>7.8</v>
+        <v>4.8</v>
       </c>
       <c r="BU24">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="BV24">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BW24">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BX24">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY24">
         <v>12</v>
       </c>
       <c r="BZ24">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="CA24">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="CB24" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:80">
@@ -6623,241 +6650,967 @@
         <v>89</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="F25">
-        <v>1.43</v>
+        <v>1.74</v>
       </c>
       <c r="G25">
-        <v>1.52</v>
+        <v>1.79</v>
       </c>
       <c r="H25">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="I25">
+        <v>5.8</v>
+      </c>
+      <c r="J25">
+        <v>3.8</v>
+      </c>
+      <c r="K25">
+        <v>4</v>
+      </c>
+      <c r="L25">
+        <v>1.42</v>
+      </c>
+      <c r="M25">
+        <v>1.08</v>
+      </c>
+      <c r="N25">
+        <v>3.55</v>
+      </c>
+      <c r="O25">
+        <v>1.35</v>
+      </c>
+      <c r="P25">
+        <v>1.89</v>
+      </c>
+      <c r="Q25">
+        <v>2.04</v>
+      </c>
+      <c r="R25">
+        <v>1.34</v>
+      </c>
+      <c r="S25">
+        <v>3.7</v>
+      </c>
+      <c r="T25">
+        <v>1.96</v>
+      </c>
+      <c r="U25">
+        <v>1.96</v>
+      </c>
+      <c r="V25">
+        <v>1.21</v>
+      </c>
+      <c r="W25">
+        <v>2.26</v>
+      </c>
+      <c r="X25">
+        <v>13.5</v>
+      </c>
+      <c r="Y25">
+        <v>21</v>
+      </c>
+      <c r="Z25">
+        <v>50</v>
+      </c>
+      <c r="AA25">
+        <v>170</v>
+      </c>
+      <c r="AB25">
+        <v>8</v>
+      </c>
+      <c r="AC25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD25">
+        <v>26</v>
+      </c>
+      <c r="AE25">
+        <v>95</v>
+      </c>
+      <c r="AF25">
+        <v>10.5</v>
+      </c>
+      <c r="AG25">
+        <v>10.5</v>
+      </c>
+      <c r="AH25">
+        <v>21</v>
+      </c>
+      <c r="AI25">
+        <v>95</v>
+      </c>
+      <c r="AJ25">
+        <v>22</v>
+      </c>
+      <c r="AK25">
+        <v>23</v>
+      </c>
+      <c r="AL25">
+        <v>46</v>
+      </c>
+      <c r="AM25">
+        <v>150</v>
+      </c>
+      <c r="AN25">
+        <v>12.5</v>
+      </c>
+      <c r="AO25">
+        <v>120</v>
+      </c>
+      <c r="AP25">
+        <v>11.5</v>
+      </c>
+      <c r="AQ25">
+        <v>15.5</v>
+      </c>
+      <c r="AR25">
+        <v>8</v>
+      </c>
+      <c r="AS25">
+        <v>8.4</v>
+      </c>
+      <c r="AT25">
+        <v>7.2</v>
+      </c>
+      <c r="AU25">
+        <v>7.8</v>
+      </c>
+      <c r="AV25">
+        <v>19</v>
+      </c>
+      <c r="AW25">
         <v>8.199999999999999</v>
       </c>
-      <c r="J25">
-        <v>5</v>
-      </c>
-      <c r="K25">
-        <v>5.7</v>
-      </c>
-      <c r="L25">
-        <v>1.23</v>
-      </c>
-      <c r="M25">
-        <v>1.02</v>
-      </c>
-      <c r="N25">
-        <v>5.7</v>
-      </c>
-      <c r="O25">
-        <v>1.18</v>
-      </c>
-      <c r="P25">
-        <v>2.6</v>
-      </c>
-      <c r="Q25">
-        <v>1.53</v>
-      </c>
-      <c r="R25">
-        <v>1.62</v>
-      </c>
-      <c r="S25">
-        <v>2.32</v>
-      </c>
-      <c r="T25">
-        <v>1.74</v>
-      </c>
-      <c r="U25">
-        <v>2.12</v>
-      </c>
-      <c r="V25">
-        <v>1.13</v>
-      </c>
-      <c r="W25">
-        <v>2.92</v>
-      </c>
-      <c r="X25">
-        <v>34</v>
-      </c>
-      <c r="Y25">
-        <v>38</v>
-      </c>
-      <c r="Z25">
-        <v>80</v>
-      </c>
-      <c r="AA25">
-        <v>230</v>
-      </c>
-      <c r="AB25">
-        <v>12</v>
-      </c>
-      <c r="AC25">
-        <v>13</v>
-      </c>
-      <c r="AD25">
-        <v>34</v>
-      </c>
-      <c r="AE25">
-        <v>110</v>
-      </c>
-      <c r="AF25">
-        <v>13</v>
-      </c>
-      <c r="AG25">
-        <v>12.5</v>
-      </c>
-      <c r="AH25">
-        <v>23</v>
-      </c>
-      <c r="AI25">
-        <v>90</v>
-      </c>
-      <c r="AJ25">
-        <v>16.5</v>
-      </c>
-      <c r="AK25">
-        <v>17.5</v>
-      </c>
-      <c r="AL25">
-        <v>36</v>
-      </c>
-      <c r="AM25">
-        <v>110</v>
-      </c>
-      <c r="AN25">
-        <v>5.6</v>
-      </c>
-      <c r="AO25">
-        <v>100</v>
-      </c>
-      <c r="AP25">
-        <v>19.5</v>
-      </c>
-      <c r="AQ25">
-        <v>4.9</v>
-      </c>
-      <c r="AR25">
-        <v>5.3</v>
-      </c>
-      <c r="AS25">
-        <v>5.6</v>
-      </c>
-      <c r="AT25">
+      <c r="AX25">
+        <v>9</v>
+      </c>
+      <c r="AY25">
+        <v>9</v>
+      </c>
+      <c r="AZ25">
+        <v>18</v>
+      </c>
+      <c r="BA25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB25">
+        <v>16</v>
+      </c>
+      <c r="BC25">
+        <v>17</v>
+      </c>
+      <c r="BD25">
+        <v>8</v>
+      </c>
+      <c r="BE25">
         <v>8.4</v>
       </c>
-      <c r="AU25">
-        <v>9</v>
-      </c>
-      <c r="AV25">
-        <v>19.5</v>
-      </c>
-      <c r="AW25">
-        <v>5.4</v>
-      </c>
-      <c r="AX25">
-        <v>7.8</v>
-      </c>
-      <c r="AY25">
-        <v>7.6</v>
-      </c>
-      <c r="AZ25">
-        <v>15.5</v>
-      </c>
-      <c r="BA25">
-        <v>5.4</v>
-      </c>
-      <c r="BB25">
-        <v>10</v>
-      </c>
-      <c r="BC25">
-        <v>10.5</v>
-      </c>
-      <c r="BD25">
-        <v>20</v>
-      </c>
-      <c r="BE25">
-        <v>5.4</v>
-      </c>
       <c r="BF25">
-        <v>4.6</v>
+        <v>11</v>
       </c>
       <c r="BG25">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BH25">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="BI25">
-        <v>3.55</v>
+        <v>2.78</v>
       </c>
       <c r="BJ25">
         <v>10.5</v>
       </c>
       <c r="BK25">
+        <v>6.4</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>15</v>
+      </c>
+      <c r="BN25">
+        <v>4.3</v>
+      </c>
+      <c r="BO25">
+        <v>3.45</v>
+      </c>
+      <c r="BP25">
+        <v>12.5</v>
+      </c>
+      <c r="BQ25">
+        <v>7</v>
+      </c>
+      <c r="BR25">
+        <v>29</v>
+      </c>
+      <c r="BS25">
+        <v>10.5</v>
+      </c>
+      <c r="BT25">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU25">
+        <v>5.7</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>12</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>13</v>
+      </c>
+      <c r="BZ25">
+        <v>24</v>
+      </c>
+      <c r="CA25">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" t="s">
+        <v>105</v>
+      </c>
+      <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26">
+        <v>4.4</v>
+      </c>
+      <c r="G26">
+        <v>4.5</v>
+      </c>
+      <c r="H26">
+        <v>1.96</v>
+      </c>
+      <c r="I26">
+        <v>1.98</v>
+      </c>
+      <c r="J26">
+        <v>3.7</v>
+      </c>
+      <c r="K26">
+        <v>3.75</v>
+      </c>
+      <c r="L26">
+        <v>1.41</v>
+      </c>
+      <c r="M26">
+        <v>1.08</v>
+      </c>
+      <c r="N26">
+        <v>3.8</v>
+      </c>
+      <c r="O26">
+        <v>1.33</v>
+      </c>
+      <c r="P26">
+        <v>1.95</v>
+      </c>
+      <c r="Q26">
+        <v>1.98</v>
+      </c>
+      <c r="R26">
+        <v>1.36</v>
+      </c>
+      <c r="S26">
+        <v>3.55</v>
+      </c>
+      <c r="T26">
+        <v>1.85</v>
+      </c>
+      <c r="U26">
+        <v>2.08</v>
+      </c>
+      <c r="V26">
+        <v>2.02</v>
+      </c>
+      <c r="W26">
+        <v>1.28</v>
+      </c>
+      <c r="X26">
+        <v>14.5</v>
+      </c>
+      <c r="Y26">
+        <v>9.4</v>
+      </c>
+      <c r="Z26">
+        <v>11.5</v>
+      </c>
+      <c r="AA26">
+        <v>22</v>
+      </c>
+      <c r="AB26">
+        <v>15.5</v>
+      </c>
+      <c r="AC26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD26">
+        <v>11</v>
+      </c>
+      <c r="AE26">
+        <v>21</v>
+      </c>
+      <c r="AF26">
+        <v>34</v>
+      </c>
+      <c r="AG26">
+        <v>17.5</v>
+      </c>
+      <c r="AH26">
+        <v>18.5</v>
+      </c>
+      <c r="AI26">
+        <v>38</v>
+      </c>
+      <c r="AJ26">
+        <v>95</v>
+      </c>
+      <c r="AK26">
+        <v>55</v>
+      </c>
+      <c r="AL26">
+        <v>65</v>
+      </c>
+      <c r="AM26">
+        <v>110</v>
+      </c>
+      <c r="AN26">
+        <v>65</v>
+      </c>
+      <c r="AO26">
+        <v>14</v>
+      </c>
+      <c r="AP26">
+        <v>12.5</v>
+      </c>
+      <c r="AQ26">
+        <v>8.4</v>
+      </c>
+      <c r="AR26">
+        <v>10.5</v>
+      </c>
+      <c r="AS26">
+        <v>20</v>
+      </c>
+      <c r="AT26">
+        <v>14</v>
+      </c>
+      <c r="AU26">
+        <v>7.6</v>
+      </c>
+      <c r="AV26">
+        <v>9.6</v>
+      </c>
+      <c r="AW26">
+        <v>18.5</v>
+      </c>
+      <c r="AX26">
+        <v>29</v>
+      </c>
+      <c r="AY26">
+        <v>16</v>
+      </c>
+      <c r="AZ26">
+        <v>17.5</v>
+      </c>
+      <c r="BA26">
+        <v>13</v>
+      </c>
+      <c r="BB26">
+        <v>15.5</v>
+      </c>
+      <c r="BC26">
+        <v>48</v>
+      </c>
+      <c r="BD26">
+        <v>50</v>
+      </c>
+      <c r="BE26">
+        <v>17</v>
+      </c>
+      <c r="BF26">
+        <v>50</v>
+      </c>
+      <c r="BG26">
+        <v>12.5</v>
+      </c>
+      <c r="BH26">
+        <v>3.5</v>
+      </c>
+      <c r="BI26">
+        <v>3.15</v>
+      </c>
+      <c r="BJ26">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK26">
+        <v>6.2</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>15</v>
+      </c>
+      <c r="BN26">
+        <v>7.6</v>
+      </c>
+      <c r="BO26">
+        <v>5.5</v>
+      </c>
+      <c r="BP26">
+        <v>36</v>
+      </c>
+      <c r="BQ26">
+        <v>11.5</v>
+      </c>
+      <c r="BR26">
+        <v>46</v>
+      </c>
+      <c r="BS26">
+        <v>12</v>
+      </c>
+      <c r="BT26">
+        <v>4.6</v>
+      </c>
+      <c r="BU26">
+        <v>4.1</v>
+      </c>
+      <c r="BV26">
+        <v>14</v>
+      </c>
+      <c r="BW26">
+        <v>10.5</v>
+      </c>
+      <c r="BX26">
+        <v>28</v>
+      </c>
+      <c r="BY26">
+        <v>10.5</v>
+      </c>
+      <c r="BZ26">
+        <v>25</v>
+      </c>
+      <c r="CA26">
+        <v>10</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>91</v>
+      </c>
+      <c r="C27" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27">
+        <v>2.1</v>
+      </c>
+      <c r="G27">
+        <v>2.14</v>
+      </c>
+      <c r="H27">
+        <v>4.1</v>
+      </c>
+      <c r="I27">
+        <v>4.4</v>
+      </c>
+      <c r="J27">
+        <v>3.35</v>
+      </c>
+      <c r="K27">
+        <v>3.5</v>
+      </c>
+      <c r="L27">
+        <v>1.4</v>
+      </c>
+      <c r="M27">
+        <v>1.1</v>
+      </c>
+      <c r="N27">
+        <v>2.9</v>
+      </c>
+      <c r="O27">
+        <v>1.41</v>
+      </c>
+      <c r="P27">
+        <v>1.65</v>
+      </c>
+      <c r="Q27">
+        <v>2.3</v>
+      </c>
+      <c r="R27">
+        <v>1.24</v>
+      </c>
+      <c r="S27">
+        <v>4.4</v>
+      </c>
+      <c r="T27">
+        <v>2.02</v>
+      </c>
+      <c r="U27">
+        <v>1.84</v>
+      </c>
+      <c r="V27">
+        <v>1.29</v>
+      </c>
+      <c r="W27">
+        <v>1.87</v>
+      </c>
+      <c r="X27">
+        <v>13</v>
+      </c>
+      <c r="Y27">
+        <v>12.5</v>
+      </c>
+      <c r="Z27">
+        <v>34</v>
+      </c>
+      <c r="AA27">
+        <v>130</v>
+      </c>
+      <c r="AB27">
+        <v>7.6</v>
+      </c>
+      <c r="AC27">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>19</v>
+      </c>
+      <c r="AE27">
+        <v>85</v>
+      </c>
+      <c r="AF27">
+        <v>12</v>
+      </c>
+      <c r="AG27">
+        <v>13.5</v>
+      </c>
+      <c r="AH27">
+        <v>23</v>
+      </c>
+      <c r="AI27">
+        <v>95</v>
+      </c>
+      <c r="AJ27">
+        <v>32</v>
+      </c>
+      <c r="AK27">
+        <v>27</v>
+      </c>
+      <c r="AL27">
+        <v>60</v>
+      </c>
+      <c r="AM27">
+        <v>180</v>
+      </c>
+      <c r="AN27">
+        <v>22</v>
+      </c>
+      <c r="AO27">
+        <v>110</v>
+      </c>
+      <c r="AP27">
+        <v>8.4</v>
+      </c>
+      <c r="AQ27">
+        <v>10</v>
+      </c>
+      <c r="AR27">
+        <v>6.2</v>
+      </c>
+      <c r="AS27">
+        <v>7</v>
+      </c>
+      <c r="AT27">
+        <v>6.6</v>
+      </c>
+      <c r="AU27">
+        <v>6</v>
+      </c>
+      <c r="AV27">
+        <v>13.5</v>
+      </c>
+      <c r="AW27">
+        <v>6.8</v>
+      </c>
+      <c r="AX27">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY27">
+        <v>10</v>
+      </c>
+      <c r="AZ27">
+        <v>15.5</v>
+      </c>
+      <c r="BA27">
+        <v>7</v>
+      </c>
+      <c r="BB27">
+        <v>21</v>
+      </c>
+      <c r="BC27">
+        <v>21</v>
+      </c>
+      <c r="BD27">
+        <v>6.6</v>
+      </c>
+      <c r="BE27">
+        <v>7.2</v>
+      </c>
+      <c r="BF27">
+        <v>14</v>
+      </c>
+      <c r="BG27">
+        <v>7</v>
+      </c>
+      <c r="BH27">
+        <v>3.05</v>
+      </c>
+      <c r="BI27">
+        <v>2.74</v>
+      </c>
+      <c r="BJ27">
+        <v>11</v>
+      </c>
+      <c r="BK27">
+        <v>6.2</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>13</v>
+      </c>
+      <c r="BN27">
+        <v>4.6</v>
+      </c>
+      <c r="BO27">
+        <v>3.55</v>
+      </c>
+      <c r="BP27">
+        <v>16</v>
+      </c>
+      <c r="BQ27">
+        <v>7.4</v>
+      </c>
+      <c r="BR27">
+        <v>1000</v>
+      </c>
+      <c r="BS27">
+        <v>10</v>
+      </c>
+      <c r="BT27">
+        <v>7.8</v>
+      </c>
+      <c r="BU27">
+        <v>5.7</v>
+      </c>
+      <c r="BV27">
+        <v>1000</v>
+      </c>
+      <c r="BW27">
+        <v>10.5</v>
+      </c>
+      <c r="BX27">
+        <v>60</v>
+      </c>
+      <c r="BY27">
+        <v>11.5</v>
+      </c>
+      <c r="BZ27">
+        <v>1000</v>
+      </c>
+      <c r="CA27">
+        <v>10</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28" t="s">
+        <v>107</v>
+      </c>
+      <c r="D28" t="s">
+        <v>134</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28">
+        <v>1.43</v>
+      </c>
+      <c r="G28">
+        <v>1.52</v>
+      </c>
+      <c r="H28">
+        <v>6.6</v>
+      </c>
+      <c r="I28">
+        <v>8</v>
+      </c>
+      <c r="J28">
+        <v>5</v>
+      </c>
+      <c r="K28">
+        <v>5.6</v>
+      </c>
+      <c r="L28">
+        <v>1.23</v>
+      </c>
+      <c r="M28">
+        <v>1.02</v>
+      </c>
+      <c r="N28">
+        <v>5.7</v>
+      </c>
+      <c r="O28">
+        <v>1.18</v>
+      </c>
+      <c r="P28">
+        <v>2.6</v>
+      </c>
+      <c r="Q28">
+        <v>1.53</v>
+      </c>
+      <c r="R28">
+        <v>1.62</v>
+      </c>
+      <c r="S28">
+        <v>2.34</v>
+      </c>
+      <c r="T28">
+        <v>1.74</v>
+      </c>
+      <c r="U28">
+        <v>2.12</v>
+      </c>
+      <c r="V28">
+        <v>1.14</v>
+      </c>
+      <c r="W28">
+        <v>2.92</v>
+      </c>
+      <c r="X28">
+        <v>34</v>
+      </c>
+      <c r="Y28">
+        <v>38</v>
+      </c>
+      <c r="Z28">
+        <v>80</v>
+      </c>
+      <c r="AA28">
+        <v>230</v>
+      </c>
+      <c r="AB28">
+        <v>12</v>
+      </c>
+      <c r="AC28">
+        <v>13</v>
+      </c>
+      <c r="AD28">
+        <v>34</v>
+      </c>
+      <c r="AE28">
+        <v>110</v>
+      </c>
+      <c r="AF28">
+        <v>13</v>
+      </c>
+      <c r="AG28">
+        <v>12.5</v>
+      </c>
+      <c r="AH28">
+        <v>23</v>
+      </c>
+      <c r="AI28">
+        <v>90</v>
+      </c>
+      <c r="AJ28">
+        <v>16.5</v>
+      </c>
+      <c r="AK28">
+        <v>17.5</v>
+      </c>
+      <c r="AL28">
+        <v>36</v>
+      </c>
+      <c r="AM28">
+        <v>110</v>
+      </c>
+      <c r="AN28">
+        <v>5.6</v>
+      </c>
+      <c r="AO28">
+        <v>100</v>
+      </c>
+      <c r="AP28">
+        <v>19.5</v>
+      </c>
+      <c r="AQ28">
+        <v>4.9</v>
+      </c>
+      <c r="AR28">
+        <v>5.3</v>
+      </c>
+      <c r="AS28">
+        <v>5.6</v>
+      </c>
+      <c r="AT28">
+        <v>8.4</v>
+      </c>
+      <c r="AU28">
+        <v>9</v>
+      </c>
+      <c r="AV28">
+        <v>19.5</v>
+      </c>
+      <c r="AW28">
+        <v>5.4</v>
+      </c>
+      <c r="AX28">
+        <v>7.8</v>
+      </c>
+      <c r="AY28">
+        <v>7.6</v>
+      </c>
+      <c r="AZ28">
+        <v>15.5</v>
+      </c>
+      <c r="BA28">
+        <v>5.4</v>
+      </c>
+      <c r="BB28">
+        <v>10</v>
+      </c>
+      <c r="BC28">
+        <v>10.5</v>
+      </c>
+      <c r="BD28">
+        <v>20</v>
+      </c>
+      <c r="BE28">
+        <v>5.4</v>
+      </c>
+      <c r="BF28">
+        <v>4.7</v>
+      </c>
+      <c r="BG28">
+        <v>5.4</v>
+      </c>
+      <c r="BH28">
+        <v>4.7</v>
+      </c>
+      <c r="BI28">
+        <v>3.55</v>
+      </c>
+      <c r="BJ28">
+        <v>10.5</v>
+      </c>
+      <c r="BK28">
         <v>5.1</v>
       </c>
-      <c r="BL25">
-        <v>1000</v>
-      </c>
-      <c r="BM25">
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
         <v>9.199999999999999</v>
       </c>
-      <c r="BN25">
+      <c r="BN28">
         <v>4.5</v>
       </c>
-      <c r="BO25">
+      <c r="BO28">
         <v>3.35</v>
       </c>
-      <c r="BP25">
+      <c r="BP28">
         <v>9</v>
       </c>
-      <c r="BQ25">
+      <c r="BQ28">
         <v>4.7</v>
       </c>
-      <c r="BR25">
+      <c r="BR28">
         <v>21</v>
       </c>
-      <c r="BS25">
+      <c r="BS28">
         <v>6.8</v>
       </c>
-      <c r="BT25">
+      <c r="BT28">
         <v>11.5</v>
       </c>
-      <c r="BU25">
+      <c r="BU28">
         <v>5.3</v>
       </c>
-      <c r="BV25">
-        <v>1000</v>
-      </c>
-      <c r="BW25">
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
         <v>8.4</v>
       </c>
-      <c r="BX25">
+      <c r="BX28">
         <v>55</v>
       </c>
-      <c r="BY25">
+      <c r="BY28">
         <v>8.4</v>
       </c>
-      <c r="BZ25">
+      <c r="BZ28">
         <v>12.5</v>
       </c>
-      <c r="CA25">
+      <c r="CA28">
         <v>5.5</v>
       </c>
-      <c r="CB25" t="s">
-        <v>153</v>
+      <c r="CB28" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -502,7 +502,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 16:43:34</t>
+    <t>2026-07-28 18:50:29</t>
   </si>
 </sst>
 </file>
@@ -1096,25 +1096,25 @@
         <v>135</v>
       </c>
       <c r="F2">
+        <v>2.08</v>
+      </c>
+      <c r="G2">
         <v>2.12</v>
       </c>
-      <c r="G2">
-        <v>2.16</v>
-      </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J2">
         <v>3.2</v>
       </c>
       <c r="K2">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="M2">
         <v>1.13</v>
@@ -1126,28 +1126,28 @@
         <v>1.59</v>
       </c>
       <c r="P2">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="R2">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S2">
         <v>6</v>
       </c>
       <c r="T2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W2">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="X2">
         <v>8.4</v>
@@ -1156,7 +1156,7 @@
         <v>11.5</v>
       </c>
       <c r="Z2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA2">
         <v>120</v>
@@ -1168,13 +1168,13 @@
         <v>7.4</v>
       </c>
       <c r="AD2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AE2">
         <v>80</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG2">
         <v>11.5</v>
@@ -1186,31 +1186,31 @@
         <v>110</v>
       </c>
       <c r="AJ2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>65</v>
       </c>
       <c r="AM2">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AN2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO2">
         <v>150</v>
       </c>
       <c r="AP2">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ2">
         <v>10</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS2">
         <v>100</v>
@@ -1243,7 +1243,7 @@
         <v>24</v>
       </c>
       <c r="BC2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD2">
         <v>55</v>
@@ -1252,31 +1252,31 @@
         <v>48</v>
       </c>
       <c r="BF2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BG2">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BH2">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="BI2">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
         <v>12</v>
       </c>
       <c r="BK2">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BL2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="BM2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BN2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO2">
         <v>4.1</v>
@@ -1285,37 +1285,37 @@
         <v>18.5</v>
       </c>
       <c r="BQ2">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BR2">
         <v>46</v>
       </c>
       <c r="BS2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT2">
         <v>7.6</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW2">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BX2">
         <v>75</v>
       </c>
       <c r="BY2">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BZ2">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="CA2">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1347,7 +1347,7 @@
         <v>12.5</v>
       </c>
       <c r="I3">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="J3">
         <v>4.8</v>
@@ -1362,31 +1362,31 @@
         <v>1.09</v>
       </c>
       <c r="N3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P3">
         <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R3">
         <v>1.26</v>
       </c>
       <c r="S3">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T3">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="U3">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="V3">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W3">
         <v>3.5</v>
@@ -1404,7 +1404,7 @@
         <v>910</v>
       </c>
       <c r="AB3">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AC3">
         <v>12</v>
@@ -1413,19 +1413,19 @@
         <v>60</v>
       </c>
       <c r="AE3">
-        <v>390</v>
+        <v>440</v>
       </c>
       <c r="AF3">
         <v>6.2</v>
       </c>
       <c r="AG3">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AI3">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AJ3">
         <v>10</v>
@@ -1434,16 +1434,16 @@
         <v>19.5</v>
       </c>
       <c r="AL3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM3">
-        <v>480</v>
+        <v>620</v>
       </c>
       <c r="AN3">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO3">
-        <v>800</v>
+        <v>840</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
@@ -1452,13 +1452,13 @@
         <v>24</v>
       </c>
       <c r="AR3">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="AS3">
         <v>75</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
@@ -1470,7 +1470,7 @@
         <v>70</v>
       </c>
       <c r="AX3">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY3">
         <v>11</v>
@@ -1482,7 +1482,7 @@
         <v>55</v>
       </c>
       <c r="BB3">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3">
         <v>17.5</v>
@@ -1491,7 +1491,7 @@
         <v>60</v>
       </c>
       <c r="BE3">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="BF3">
         <v>8.4</v>
@@ -1500,64 +1500,64 @@
         <v>70</v>
       </c>
       <c r="BH3">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BI3">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="BJ3">
         <v>16</v>
       </c>
       <c r="BK3">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="BN3">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BO3">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BQ3">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BT3">
         <v>17</v>
       </c>
       <c r="BU3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BV3">
         <v>1000</v>
       </c>
       <c r="BW3">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BX3">
         <v>1000</v>
       </c>
       <c r="BY3">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="BZ3">
         <v>21</v>
       </c>
       <c r="CA3">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="s">
         <v>162</v>
@@ -1586,7 +1586,7 @@
         <v>1.9</v>
       </c>
       <c r="H4">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I4">
         <v>5.4</v>
@@ -1595,67 +1595,67 @@
         <v>3.5</v>
       </c>
       <c r="K4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L4">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="M4">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N4">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="O4">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="Q4">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R4">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="V4">
         <v>1.22</v>
       </c>
       <c r="W4">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X4">
         <v>10.5</v>
       </c>
       <c r="Y4">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Z4">
         <v>40</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC4">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE4">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF4">
         <v>9.800000000000001</v>
@@ -1664,31 +1664,31 @@
         <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AJ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK4">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL4">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM4">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AN4">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AO4">
         <v>140</v>
       </c>
       <c r="AP4">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4">
         <v>13.5</v>
@@ -1697,19 +1697,19 @@
         <v>34</v>
       </c>
       <c r="AS4">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT4">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV4">
         <v>19.5</v>
       </c>
       <c r="AW4">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AX4">
         <v>9</v>
@@ -1718,88 +1718,88 @@
         <v>9.6</v>
       </c>
       <c r="AZ4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA4">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BB4">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC4">
         <v>21</v>
       </c>
       <c r="BD4">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="BE4">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BF4">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG4">
-        <v>60</v>
+        <v>19.5</v>
       </c>
       <c r="BH4">
-        <v>2.98</v>
+        <v>2.84</v>
       </c>
       <c r="BI4">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BJ4">
         <v>11.5</v>
       </c>
       <c r="BK4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BN4">
         <v>4.3</v>
       </c>
       <c r="BO4">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BP4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BQ4">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS4">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT4">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU4">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BV4">
         <v>55</v>
       </c>
       <c r="BW4">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BX4">
         <v>70</v>
       </c>
       <c r="BY4">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="BZ4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="CA4">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1822,61 +1822,61 @@
         <v>138</v>
       </c>
       <c r="F5">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G5">
         <v>1.5</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>4.9</v>
       </c>
       <c r="K5">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M5">
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O5">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="Q5">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="R5">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="S5">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="T5">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="U5">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W5">
         <v>3</v>
       </c>
       <c r="X5">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="Y5">
         <v>32</v>
@@ -1885,28 +1885,28 @@
         <v>65</v>
       </c>
       <c r="AA5">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB5">
+        <v>14.5</v>
+      </c>
+      <c r="AC5">
+        <v>14.5</v>
+      </c>
+      <c r="AD5">
+        <v>32</v>
+      </c>
+      <c r="AE5">
+        <v>100</v>
+      </c>
+      <c r="AF5">
         <v>11.5</v>
-      </c>
-      <c r="AC5">
-        <v>12</v>
-      </c>
-      <c r="AD5">
-        <v>34</v>
-      </c>
-      <c r="AE5">
-        <v>110</v>
-      </c>
-      <c r="AF5">
-        <v>11</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5">
         <v>85</v>
@@ -1915,55 +1915,55 @@
         <v>15</v>
       </c>
       <c r="AK5">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AL5">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN5">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP5">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ5">
         <v>22</v>
       </c>
       <c r="AR5">
+        <v>5.4</v>
+      </c>
+      <c r="AS5">
         <v>5.8</v>
       </c>
-      <c r="AS5">
-        <v>6.2</v>
-      </c>
       <c r="AT5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AV5">
         <v>22</v>
       </c>
       <c r="AW5">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AX5">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ5">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA5">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
@@ -1972,76 +1972,76 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
+        <v>5.6</v>
+      </c>
+      <c r="BE5">
+        <v>5.6</v>
+      </c>
+      <c r="BF5">
+        <v>4.8</v>
+      </c>
+      <c r="BG5">
+        <v>5.6</v>
+      </c>
+      <c r="BH5">
+        <v>4.7</v>
+      </c>
+      <c r="BI5">
+        <v>4</v>
+      </c>
+      <c r="BJ5">
+        <v>10.5</v>
+      </c>
+      <c r="BK5">
+        <v>7.2</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>9.4</v>
+      </c>
+      <c r="BN5">
+        <v>4.5</v>
+      </c>
+      <c r="BO5">
+        <v>3.8</v>
+      </c>
+      <c r="BP5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BQ5">
+        <v>6.4</v>
+      </c>
+      <c r="BR5">
+        <v>21</v>
+      </c>
+      <c r="BS5">
+        <v>7</v>
+      </c>
+      <c r="BT5">
+        <v>11</v>
+      </c>
+      <c r="BU5">
+        <v>5.7</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>8.6</v>
+      </c>
+      <c r="BZ5">
+        <v>12.5</v>
+      </c>
+      <c r="CA5">
         <v>6</v>
-      </c>
-      <c r="BE5">
-        <v>6</v>
-      </c>
-      <c r="BF5">
-        <v>5.2</v>
-      </c>
-      <c r="BG5">
-        <v>6</v>
-      </c>
-      <c r="BH5">
-        <v>4.5</v>
-      </c>
-      <c r="BI5">
-        <v>3.35</v>
-      </c>
-      <c r="BJ5">
-        <v>11</v>
-      </c>
-      <c r="BK5">
-        <v>5.1</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN5">
-        <v>4.4</v>
-      </c>
-      <c r="BO5">
-        <v>3.3</v>
-      </c>
-      <c r="BP5">
-        <v>9.4</v>
-      </c>
-      <c r="BQ5">
-        <v>4.7</v>
-      </c>
-      <c r="BR5">
-        <v>22</v>
-      </c>
-      <c r="BS5">
-        <v>6.6</v>
-      </c>
-      <c r="BT5">
-        <v>11.5</v>
-      </c>
-      <c r="BU5">
-        <v>5.2</v>
-      </c>
-      <c r="BV5">
-        <v>1000</v>
-      </c>
-      <c r="BW5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BZ5">
-        <v>13.5</v>
-      </c>
-      <c r="CA5">
-        <v>5.6</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2070,7 +2070,7 @@
         <v>990</v>
       </c>
       <c r="H6">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="I6">
         <v>1.68</v>
@@ -2079,13 +2079,13 @@
         <v>3.25</v>
       </c>
       <c r="K6">
-        <v>9.4</v>
+        <v>5.4</v>
       </c>
       <c r="L6">
         <v>1.32</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
         <v>3.3</v>
@@ -2121,25 +2121,25 @@
         <v>1000</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB6">
         <v>1000</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF6">
         <v>1000</v>
@@ -2151,7 +2151,7 @@
         <v>1000</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6">
         <v>1000</v>
@@ -2169,58 +2169,58 @@
         <v>1000</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>2.5</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BG6">
         <v>1.01</v>
@@ -2229,61 +2229,61 @@
         <v>1000</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
         <v>1000</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6">
         <v>1000</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT6">
         <v>1000</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6">
         <v>1000</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB6" t="s">
         <v>162</v>
@@ -2309,19 +2309,19 @@
         <v>3.1</v>
       </c>
       <c r="G7">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H7">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I7">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J7">
         <v>2.5</v>
       </c>
       <c r="K7">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2342,7 +2342,7 @@
         <v>2.96</v>
       </c>
       <c r="R7">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="S7">
         <v>2.96</v>
@@ -2354,10 +2354,10 @@
         <v>1.11</v>
       </c>
       <c r="V7">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD7">
         <v>1000</v>
@@ -2414,52 +2414,52 @@
         <v>1000</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
         <v>1.01</v>
@@ -2471,61 +2471,61 @@
         <v>1000</v>
       </c>
       <c r="BI7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BJ7">
         <v>1000</v>
       </c>
       <c r="BK7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN7">
         <v>1000</v>
       </c>
       <c r="BO7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BP7">
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BT7">
         <v>1000</v>
       </c>
       <c r="BU7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BV7">
         <v>1000</v>
       </c>
       <c r="BW7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="s">
         <v>162</v>
@@ -2548,13 +2548,13 @@
         <v>141</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G8">
         <v>4.4</v>
       </c>
       <c r="H8">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="I8">
         <v>2.76</v>
@@ -2563,7 +2563,7 @@
         <v>2.72</v>
       </c>
       <c r="K8">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L8">
         <v>1.46</v>
@@ -2596,118 +2596,118 @@
         <v>1.11</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="W8">
         <v>1.29</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AU8">
         <v>1.03</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -2793,10 +2793,10 @@
         <v>2.42</v>
       </c>
       <c r="G9">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H9">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I9">
         <v>4.1</v>
@@ -2814,10 +2814,10 @@
         <v>1.18</v>
       </c>
       <c r="N9">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="O9">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="P9">
         <v>1.38</v>
@@ -2826,13 +2826,13 @@
         <v>3.3</v>
       </c>
       <c r="R9">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S9">
         <v>7.8</v>
       </c>
       <c r="T9">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U9">
         <v>1.6</v>
@@ -2841,19 +2841,19 @@
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X9">
         <v>6.6</v>
       </c>
       <c r="Y9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="Z9">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB9">
         <v>6.4</v>
@@ -2880,37 +2880,37 @@
         <v>150</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK9">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL9">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AM9">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AN9">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="AO9">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AP9">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AQ9">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR9">
         <v>22</v>
       </c>
       <c r="AS9">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AT9">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
@@ -2931,25 +2931,25 @@
         <v>27</v>
       </c>
       <c r="BA9">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BB9">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="BC9">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BD9">
         <v>38</v>
       </c>
       <c r="BE9">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BF9">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="BG9">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH9">
         <v>2.42</v>
@@ -3032,7 +3032,7 @@
         <v>143</v>
       </c>
       <c r="F10">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="G10">
         <v>1.31</v>
@@ -3062,7 +3062,7 @@
         <v>1.1</v>
       </c>
       <c r="P10">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="Q10">
         <v>1.3</v>
@@ -3182,7 +3182,7 @@
         <v>11</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="BE10">
         <v>8.800000000000001</v>
@@ -3274,13 +3274,13 @@
         <v>144</v>
       </c>
       <c r="F11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G11">
         <v>1.94</v>
       </c>
       <c r="H11">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I11">
         <v>4.3</v>
@@ -3289,7 +3289,7 @@
         <v>4.3</v>
       </c>
       <c r="K11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L11">
         <v>1.19</v>
@@ -3310,13 +3310,13 @@
         <v>1.37</v>
       </c>
       <c r="R11">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="S11">
         <v>1.94</v>
       </c>
       <c r="T11">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="U11">
         <v>2.8</v>
@@ -3328,16 +3328,16 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Y11">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z11">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA11">
-        <v>85</v>
+        <v>290</v>
       </c>
       <c r="AB11">
         <v>22</v>
@@ -3358,10 +3358,10 @@
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AI11">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ11">
         <v>27</v>
@@ -3370,55 +3370,55 @@
         <v>19.5</v>
       </c>
       <c r="AL11">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AM11">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AN11">
         <v>7.2</v>
       </c>
       <c r="AO11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AQ11">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AR11">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS11">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AT11">
         <v>15.5</v>
       </c>
       <c r="AU11">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AW11">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX11">
         <v>15</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ11">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BA11">
-        <v>4.5</v>
+        <v>16</v>
       </c>
       <c r="BB11">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC11">
         <v>14</v>
@@ -3427,10 +3427,10 @@
         <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BF11">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BG11">
         <v>16.5</v>
@@ -3519,16 +3519,16 @@
         <v>3</v>
       </c>
       <c r="G12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H12">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I12">
         <v>2.2</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K12">
         <v>5.4</v>
@@ -3549,7 +3549,7 @@
         <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R12">
         <v>2.16</v>
@@ -3576,28 +3576,28 @@
         <v>32</v>
       </c>
       <c r="Z12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AA12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB12">
         <v>40</v>
       </c>
       <c r="AC12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AD12">
         <v>15.5</v>
       </c>
       <c r="AE12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AG12">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH12">
         <v>16.5</v>
@@ -3606,19 +3606,19 @@
         <v>24</v>
       </c>
       <c r="AJ12">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK12">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM12">
-        <v>38</v>
+        <v>200</v>
       </c>
       <c r="AN12">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO12">
         <v>6.8</v>
@@ -3627,10 +3627,10 @@
         <v>4.9</v>
       </c>
       <c r="AQ12">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="AR12">
-        <v>4.5</v>
+        <v>20</v>
       </c>
       <c r="AS12">
         <v>4.6</v>
@@ -3639,43 +3639,43 @@
         <v>4.6</v>
       </c>
       <c r="AU12">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AV12">
-        <v>3.9</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="AX12">
         <v>4.7</v>
       </c>
       <c r="AY12">
-        <v>4.1</v>
+        <v>14</v>
       </c>
       <c r="AZ12">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BA12">
-        <v>4.3</v>
+        <v>17</v>
       </c>
       <c r="BB12">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC12">
         <v>4.5</v>
       </c>
       <c r="BD12">
-        <v>4.4</v>
+        <v>21</v>
       </c>
       <c r="BE12">
         <v>4.6</v>
       </c>
       <c r="BF12">
-        <v>3.7</v>
+        <v>10</v>
       </c>
       <c r="BG12">
-        <v>2.96</v>
+        <v>5</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3761,13 +3761,13 @@
         <v>1.54</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
         <v>2.64</v>
@@ -3809,7 +3809,7 @@
         <v>1.17</v>
       </c>
       <c r="W13">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3860,64 +3860,64 @@
         <v>1000</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO13">
         <v>1000</v>
       </c>
       <c r="AP13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AQ13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AR13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AS13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AT13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AU13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AV13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AW13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AX13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AY13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AZ13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BA13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BB13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BC13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BD13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BE13">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF13">
         <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4000,13 +4000,13 @@
         <v>147</v>
       </c>
       <c r="F14">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="G14">
         <v>4.4</v>
       </c>
       <c r="H14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I14">
         <v>2.88</v>
@@ -4015,7 +4015,7 @@
         <v>2.52</v>
       </c>
       <c r="K14">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4054,112 +4054,112 @@
         <v>1.29</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4242,22 +4242,22 @@
         <v>148</v>
       </c>
       <c r="F15">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="G15">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="H15">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="I15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="J15">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K15">
-        <v>7.6</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4266,22 +4266,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.26</v>
+        <v>2.36</v>
       </c>
       <c r="O15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="P15">
         <v>2.36</v>
       </c>
       <c r="Q15">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.05</v>
+        <v>1.47</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -4293,7 +4293,7 @@
         <v>1.68</v>
       </c>
       <c r="W15">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4350,52 +4350,52 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4484,22 +4484,22 @@
         <v>149</v>
       </c>
       <c r="F16">
-        <v>1.06</v>
+        <v>1.71</v>
       </c>
       <c r="G16">
-        <v>990</v>
+        <v>2.06</v>
       </c>
       <c r="H16">
-        <v>1.05</v>
+        <v>3</v>
       </c>
       <c r="I16">
-        <v>990</v>
+        <v>5.5</v>
       </c>
       <c r="J16">
-        <v>1.08</v>
+        <v>4</v>
       </c>
       <c r="K16">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4508,22 +4508,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>6.8</v>
       </c>
       <c r="O16">
         <v>1.08</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="Q16">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="R16">
         <v>1.86</v>
       </c>
       <c r="S16">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4532,118 +4532,118 @@
         <v>1.11</v>
       </c>
       <c r="V16">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.95</v>
       </c>
       <c r="X16">
         <v>1000</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO16">
         <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>2.62</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4726,226 +4726,226 @@
         <v>150</v>
       </c>
       <c r="F17">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="G17">
-        <v>990</v>
+        <v>2.78</v>
       </c>
       <c r="H17">
-        <v>2.04</v>
+        <v>2.34</v>
       </c>
       <c r="I17">
-        <v>990</v>
+        <v>2.66</v>
       </c>
       <c r="J17">
-        <v>1.08</v>
+        <v>3.8</v>
       </c>
       <c r="K17">
+        <v>5.1</v>
+      </c>
+      <c r="L17">
+        <v>1.17</v>
+      </c>
+      <c r="M17">
+        <v>1.01</v>
+      </c>
+      <c r="N17">
+        <v>1.1</v>
+      </c>
+      <c r="O17">
+        <v>1.11</v>
+      </c>
+      <c r="P17">
+        <v>3.05</v>
+      </c>
+      <c r="Q17">
+        <v>1.32</v>
+      </c>
+      <c r="R17">
+        <v>2</v>
+      </c>
+      <c r="S17">
+        <v>1.8</v>
+      </c>
+      <c r="T17">
+        <v>1.36</v>
+      </c>
+      <c r="U17">
+        <v>3.15</v>
+      </c>
+      <c r="V17">
+        <v>1.6</v>
+      </c>
+      <c r="W17">
+        <v>1.56</v>
+      </c>
+      <c r="X17">
+        <v>55</v>
+      </c>
+      <c r="Y17">
+        <v>30</v>
+      </c>
+      <c r="Z17">
+        <v>32</v>
+      </c>
+      <c r="AA17">
+        <v>46</v>
+      </c>
+      <c r="AB17">
+        <v>32</v>
+      </c>
+      <c r="AC17">
+        <v>14</v>
+      </c>
+      <c r="AD17">
+        <v>17</v>
+      </c>
+      <c r="AE17">
+        <v>27</v>
+      </c>
+      <c r="AF17">
+        <v>34</v>
+      </c>
+      <c r="AG17">
+        <v>17.5</v>
+      </c>
+      <c r="AH17">
+        <v>15</v>
+      </c>
+      <c r="AI17">
+        <v>29</v>
+      </c>
+      <c r="AJ17">
+        <v>50</v>
+      </c>
+      <c r="AK17">
+        <v>28</v>
+      </c>
+      <c r="AL17">
+        <v>29</v>
+      </c>
+      <c r="AM17">
+        <v>40</v>
+      </c>
+      <c r="AN17">
+        <v>11.5</v>
+      </c>
+      <c r="AO17">
+        <v>11</v>
+      </c>
+      <c r="AP17">
+        <v>4.3</v>
+      </c>
+      <c r="AQ17">
+        <v>4</v>
+      </c>
+      <c r="AR17">
+        <v>4.1</v>
+      </c>
+      <c r="AS17">
+        <v>4.2</v>
+      </c>
+      <c r="AT17">
+        <v>4.1</v>
+      </c>
+      <c r="AU17">
+        <v>3.5</v>
+      </c>
+      <c r="AV17">
+        <v>3.7</v>
+      </c>
+      <c r="AW17">
+        <v>4</v>
+      </c>
+      <c r="AX17">
+        <v>4.1</v>
+      </c>
+      <c r="AY17">
+        <v>3.7</v>
+      </c>
+      <c r="AZ17">
+        <v>3.55</v>
+      </c>
+      <c r="BA17">
+        <v>4</v>
+      </c>
+      <c r="BB17">
+        <v>4.3</v>
+      </c>
+      <c r="BC17">
+        <v>4</v>
+      </c>
+      <c r="BD17">
+        <v>4</v>
+      </c>
+      <c r="BE17">
+        <v>4.2</v>
+      </c>
+      <c r="BF17">
+        <v>3.35</v>
+      </c>
+      <c r="BG17">
+        <v>3.3</v>
+      </c>
+      <c r="BH17">
+        <v>6.2</v>
+      </c>
+      <c r="BI17">
+        <v>3.7</v>
+      </c>
+      <c r="BJ17">
+        <v>8.4</v>
+      </c>
+      <c r="BK17">
+        <v>4.4</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
         <v>7.8</v>
       </c>
-      <c r="L17">
-        <v>1.01</v>
-      </c>
-      <c r="M17">
-        <v>1.01</v>
-      </c>
-      <c r="N17">
-        <v>1.27</v>
-      </c>
-      <c r="O17">
-        <v>1.06</v>
-      </c>
-      <c r="P17">
-        <v>1.25</v>
-      </c>
-      <c r="Q17">
-        <v>1.06</v>
-      </c>
-      <c r="R17">
-        <v>1.25</v>
-      </c>
-      <c r="S17">
-        <v>1.74</v>
-      </c>
-      <c r="T17">
-        <v>1.11</v>
-      </c>
-      <c r="U17">
-        <v>1.11</v>
-      </c>
-      <c r="V17">
-        <v>1.68</v>
-      </c>
-      <c r="W17">
-        <v>1.37</v>
-      </c>
-      <c r="X17">
-        <v>1000</v>
-      </c>
-      <c r="Y17">
-        <v>1000</v>
-      </c>
-      <c r="Z17">
-        <v>1000</v>
-      </c>
-      <c r="AA17">
-        <v>1000</v>
-      </c>
-      <c r="AB17">
-        <v>1000</v>
-      </c>
-      <c r="AC17">
-        <v>1000</v>
-      </c>
-      <c r="AD17">
-        <v>1000</v>
-      </c>
-      <c r="AE17">
-        <v>1000</v>
-      </c>
-      <c r="AF17">
-        <v>1000</v>
-      </c>
-      <c r="AG17">
-        <v>1000</v>
-      </c>
-      <c r="AH17">
-        <v>1000</v>
-      </c>
-      <c r="AI17">
-        <v>1000</v>
-      </c>
-      <c r="AJ17">
-        <v>1000</v>
-      </c>
-      <c r="AK17">
-        <v>1000</v>
-      </c>
-      <c r="AL17">
-        <v>1000</v>
-      </c>
-      <c r="AM17">
-        <v>1000</v>
-      </c>
-      <c r="AN17">
-        <v>1000</v>
-      </c>
-      <c r="AO17">
-        <v>1000</v>
-      </c>
-      <c r="AP17">
-        <v>1.01</v>
-      </c>
-      <c r="AQ17">
-        <v>1.01</v>
-      </c>
-      <c r="AR17">
-        <v>1.01</v>
-      </c>
-      <c r="AS17">
-        <v>1.01</v>
-      </c>
-      <c r="AT17">
-        <v>1.01</v>
-      </c>
-      <c r="AU17">
-        <v>1.01</v>
-      </c>
-      <c r="AV17">
-        <v>1.01</v>
-      </c>
-      <c r="AW17">
-        <v>1.01</v>
-      </c>
-      <c r="AX17">
-        <v>1.01</v>
-      </c>
-      <c r="AY17">
-        <v>1.01</v>
-      </c>
-      <c r="AZ17">
-        <v>1.01</v>
-      </c>
-      <c r="BA17">
-        <v>1.01</v>
-      </c>
-      <c r="BB17">
-        <v>1.01</v>
-      </c>
-      <c r="BC17">
-        <v>1.01</v>
-      </c>
-      <c r="BD17">
-        <v>1.01</v>
-      </c>
-      <c r="BE17">
-        <v>1.01</v>
-      </c>
-      <c r="BF17">
-        <v>1.01</v>
-      </c>
-      <c r="BG17">
-        <v>1.01</v>
-      </c>
-      <c r="BH17">
-        <v>1000</v>
-      </c>
-      <c r="BI17">
-        <v>1.04</v>
-      </c>
-      <c r="BJ17">
-        <v>1000</v>
-      </c>
-      <c r="BK17">
-        <v>1.04</v>
-      </c>
-      <c r="BL17">
-        <v>1000</v>
-      </c>
-      <c r="BM17">
-        <v>1.04</v>
-      </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO17">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BQ17">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS17">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU17">
-        <v>1.04</v>
+        <v>3.95</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="BW17">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY17">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA17">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB17" t="s">
         <v>162</v>
@@ -4968,19 +4968,19 @@
         <v>151</v>
       </c>
       <c r="F18">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G18">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="H18">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I18">
         <v>3.05</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
         <v>4.7</v>
@@ -5001,7 +5001,7 @@
         <v>2.96</v>
       </c>
       <c r="Q18">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R18">
         <v>1.8</v>
@@ -5013,13 +5013,13 @@
         <v>1.44</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
         <v>1.48</v>
       </c>
       <c r="W18">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X18">
         <v>40</v>
@@ -5067,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="AM18">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN18">
         <v>9.6</v>
@@ -5082,7 +5082,7 @@
         <v>19.5</v>
       </c>
       <c r="AR18">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="AS18">
         <v>6.4</v>
@@ -5112,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="BB18">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC18">
         <v>17</v>
@@ -5210,7 +5210,7 @@
         <v>152</v>
       </c>
       <c r="F19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G19">
         <v>2.6</v>
@@ -5219,58 +5219,58 @@
         <v>2.76</v>
       </c>
       <c r="I19">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L19">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="M19">
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="O19">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="P19">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="Q19">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="R19">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="S19">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="T19">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="U19">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="V19">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W19">
         <v>1.63</v>
       </c>
       <c r="X19">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y19">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AA19">
         <v>50</v>
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="AC19">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD19">
         <v>15</v>
@@ -5309,7 +5309,7 @@
         <v>34</v>
       </c>
       <c r="AM19">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="AN19">
         <v>14.5</v>
@@ -5327,7 +5327,7 @@
         <v>17.5</v>
       </c>
       <c r="AS19">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT19">
         <v>12.5</v>
@@ -5351,85 +5351,85 @@
         <v>11</v>
       </c>
       <c r="BA19">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BB19">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BC19">
         <v>17.5</v>
       </c>
       <c r="BD19">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE19">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF19">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BG19">
         <v>12.5</v>
       </c>
       <c r="BH19">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BI19">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BJ19">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BK19">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BN19">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO19">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP19">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS19">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT19">
         <v>6.6</v>
       </c>
       <c r="BU19">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW19">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ19">
-        <v>15.5</v>
+        <v>23</v>
       </c>
       <c r="CA19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB19" t="s">
         <v>162</v>
@@ -5452,19 +5452,19 @@
         <v>153</v>
       </c>
       <c r="F20">
-        <v>1.02</v>
+        <v>1.93</v>
       </c>
       <c r="G20">
         <v>600</v>
       </c>
       <c r="H20">
-        <v>1.02</v>
+        <v>1.69</v>
       </c>
       <c r="I20">
         <v>870</v>
       </c>
       <c r="J20">
-        <v>1.02</v>
+        <v>2.5</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -5479,7 +5479,7 @@
         <v>1.1</v>
       </c>
       <c r="O20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P20">
         <v>1.07</v>
@@ -5488,10 +5488,10 @@
         <v>1.01</v>
       </c>
       <c r="R20">
-        <v>1.08</v>
+        <v>1.94</v>
       </c>
       <c r="S20">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="T20">
         <v>1.11</v>
@@ -5500,10 +5500,10 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.01</v>
+        <v>1.19</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -5709,10 +5709,10 @@
         <v>2.92</v>
       </c>
       <c r="K21">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L21">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="M21">
         <v>1.17</v>
@@ -5721,13 +5721,13 @@
         <v>2.3</v>
       </c>
       <c r="O21">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q21">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="R21">
         <v>1.14</v>
@@ -5739,25 +5739,25 @@
         <v>2.44</v>
       </c>
       <c r="U21">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="V21">
         <v>1.3</v>
       </c>
       <c r="W21">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X21">
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Z21">
         <v>27</v>
       </c>
       <c r="AA21">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AB21">
         <v>6.4</v>
@@ -5769,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AE21">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AF21">
         <v>12.5</v>
@@ -5778,28 +5778,28 @@
         <v>13</v>
       </c>
       <c r="AH21">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI21">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AJ21">
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AL21">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AM21">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AN21">
         <v>100</v>
       </c>
       <c r="AO21">
-        <v>1000</v>
+        <v>490</v>
       </c>
       <c r="AP21">
         <v>6.4</v>
@@ -5814,10 +5814,10 @@
         <v>38</v>
       </c>
       <c r="AT21">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AU21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV21">
         <v>17.5</v>
@@ -5829,7 +5829,7 @@
         <v>11</v>
       </c>
       <c r="AY21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ21">
         <v>20</v>
@@ -5841,13 +5841,13 @@
         <v>21</v>
       </c>
       <c r="BC21">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD21">
         <v>36</v>
       </c>
       <c r="BE21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF21">
         <v>24</v>
@@ -5871,7 +5871,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BN21">
         <v>4.8</v>
@@ -5889,7 +5889,7 @@
         <v>55</v>
       </c>
       <c r="BS21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BT21">
         <v>7.2</v>
@@ -5898,7 +5898,7 @@
         <v>5.5</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW21">
         <v>13.5</v>
@@ -5939,19 +5939,19 @@
         <v>1.69</v>
       </c>
       <c r="G22">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J22">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K22">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L22">
         <v>1.47</v>
@@ -5984,10 +5984,10 @@
         <v>1.72</v>
       </c>
       <c r="V22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W22">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="X22">
         <v>12.5</v>
@@ -5999,19 +5999,19 @@
         <v>55</v>
       </c>
       <c r="AA22">
-        <v>220</v>
+        <v>700</v>
       </c>
       <c r="AB22">
         <v>7.8</v>
       </c>
       <c r="AC22">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD22">
         <v>28</v>
       </c>
       <c r="AE22">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AF22">
         <v>11</v>
@@ -6020,10 +6020,10 @@
         <v>12</v>
       </c>
       <c r="AH22">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AI22">
-        <v>130</v>
+        <v>700</v>
       </c>
       <c r="AJ22">
         <v>23</v>
@@ -6035,67 +6035,67 @@
         <v>60</v>
       </c>
       <c r="AM22">
-        <v>220</v>
+        <v>500</v>
       </c>
       <c r="AN22">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AO22">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="AP22">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AQ22">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AR22">
+        <v>5.2</v>
+      </c>
+      <c r="AS22">
+        <v>5.6</v>
+      </c>
+      <c r="AT22">
+        <v>3.3</v>
+      </c>
+      <c r="AU22">
+        <v>3.45</v>
+      </c>
+      <c r="AV22">
         <v>4.7</v>
       </c>
-      <c r="AS22">
-        <v>5.1</v>
-      </c>
-      <c r="AT22">
-        <v>3.1</v>
-      </c>
-      <c r="AU22">
-        <v>3.35</v>
-      </c>
-      <c r="AV22">
-        <v>4.4</v>
-      </c>
       <c r="AW22">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AX22">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AY22">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="AZ22">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BA22">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB22">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BC22">
+        <v>4.7</v>
+      </c>
+      <c r="BD22">
+        <v>5.2</v>
+      </c>
+      <c r="BE22">
+        <v>5.6</v>
+      </c>
+      <c r="BF22">
         <v>4.3</v>
       </c>
-      <c r="BD22">
-        <v>4.8</v>
-      </c>
-      <c r="BE22">
-        <v>5.1</v>
-      </c>
-      <c r="BF22">
-        <v>4.1</v>
-      </c>
       <c r="BG22">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BH22">
         <v>3.15</v>
@@ -6178,22 +6178,22 @@
         <v>156</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6202,34 +6202,34 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.1</v>
+        <v>3.2</v>
       </c>
       <c r="O23">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="P23">
-        <v>1.24</v>
+        <v>1.73</v>
       </c>
       <c r="Q23">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R23">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S23">
-        <v>1.13</v>
+        <v>3.8</v>
       </c>
       <c r="T23">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="U23">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6274,7 +6274,7 @@
         <v>1000</v>
       </c>
       <c r="AL23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM23">
         <v>1000</v>
@@ -6286,58 +6286,58 @@
         <v>1000</v>
       </c>
       <c r="AP23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AS23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AT23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AX23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AY23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BB23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BC23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BD23">
         <v>1.01</v>
       </c>
       <c r="BE23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BF23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6346,7 +6346,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK23">
         <v>1.04</v>
@@ -6358,13 +6358,13 @@
         <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO23">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BQ23">
         <v>1.04</v>
@@ -6376,25 +6376,25 @@
         <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU23">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW23">
         <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY23">
         <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="CA23">
         <v>1.04</v>
@@ -6426,7 +6426,7 @@
         <v>4.4</v>
       </c>
       <c r="H24">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I24">
         <v>2.32</v>
@@ -6471,7 +6471,7 @@
         <v>1.76</v>
       </c>
       <c r="W24">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X24">
         <v>8.6</v>
@@ -6483,7 +6483,7 @@
         <v>13</v>
       </c>
       <c r="AA24">
-        <v>32</v>
+        <v>500</v>
       </c>
       <c r="AB24">
         <v>11</v>
@@ -6498,7 +6498,7 @@
         <v>40</v>
       </c>
       <c r="AF24">
-        <v>30</v>
+        <v>500</v>
       </c>
       <c r="AG24">
         <v>970</v>
@@ -6507,22 +6507,22 @@
         <v>30</v>
       </c>
       <c r="AI24">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AJ24">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AK24">
         <v>90</v>
       </c>
       <c r="AL24">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AM24">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN24">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AO24">
         <v>32</v>
@@ -6662,7 +6662,7 @@
         <v>158</v>
       </c>
       <c r="F25">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G25">
         <v>1.79</v>
@@ -6677,10 +6677,10 @@
         <v>3.8</v>
       </c>
       <c r="K25">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M25">
         <v>1.08</v>
@@ -6707,7 +6707,7 @@
         <v>1.96</v>
       </c>
       <c r="U25">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V25">
         <v>1.21</v>
@@ -6725,7 +6725,7 @@
         <v>50</v>
       </c>
       <c r="AA25">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -6815,7 +6815,7 @@
         <v>8</v>
       </c>
       <c r="BE25">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF25">
         <v>11</v>
@@ -6839,7 +6839,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN25">
         <v>4.3</v>
@@ -6875,13 +6875,13 @@
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BZ25">
         <v>24</v>
       </c>
       <c r="CA25">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="CB25" t="s">
         <v>162</v>
@@ -6907,7 +6907,7 @@
         <v>4.4</v>
       </c>
       <c r="G26">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="H26">
         <v>1.96</v>
@@ -6919,13 +6919,13 @@
         <v>3.7</v>
       </c>
       <c r="K26">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L26">
         <v>1.41</v>
       </c>
       <c r="M26">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N26">
         <v>3.8</v>
@@ -6958,7 +6958,7 @@
         <v>1.28</v>
       </c>
       <c r="X26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y26">
         <v>9.4</v>
@@ -6970,7 +6970,7 @@
         <v>22</v>
       </c>
       <c r="AB26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC26">
         <v>8.199999999999999</v>
@@ -6985,10 +6985,10 @@
         <v>34</v>
       </c>
       <c r="AG26">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AH26">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI26">
         <v>38</v>
@@ -6997,7 +6997,7 @@
         <v>95</v>
       </c>
       <c r="AK26">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AL26">
         <v>65</v>
@@ -7006,7 +7006,7 @@
         <v>110</v>
       </c>
       <c r="AN26">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO26">
         <v>14</v>
@@ -7027,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="AU26">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV26">
         <v>9.6</v>
@@ -7045,10 +7045,10 @@
         <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="BB26">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC26">
         <v>48</v>
@@ -7057,7 +7057,7 @@
         <v>50</v>
       </c>
       <c r="BE26">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="BF26">
         <v>50</v>
@@ -7173,7 +7173,7 @@
         <v>2.9</v>
       </c>
       <c r="O27">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="P27">
         <v>1.65</v>
@@ -7388,7 +7388,7 @@
         <v>161</v>
       </c>
       <c r="F28">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="G28">
         <v>1.52</v>
@@ -7424,7 +7424,7 @@
         <v>1.53</v>
       </c>
       <c r="R28">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S28">
         <v>2.34</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -502,7 +502,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 18:50:29</t>
+    <t>2026-07-28 20:57:49</t>
   </si>
 </sst>
 </file>
@@ -1096,226 +1096,226 @@
         <v>135</v>
       </c>
       <c r="F2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G2">
         <v>2.12</v>
       </c>
       <c r="H2">
+        <v>4.4</v>
+      </c>
+      <c r="I2">
         <v>4.5</v>
       </c>
-      <c r="I2">
-        <v>4.7</v>
-      </c>
       <c r="J2">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K2">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L2">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="M2">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="O2">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q2">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="R2">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S2">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="T2">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U2">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y2">
+        <v>12</v>
+      </c>
+      <c r="Z2">
+        <v>29</v>
+      </c>
+      <c r="AA2">
+        <v>100</v>
+      </c>
+      <c r="AB2">
+        <v>7</v>
+      </c>
+      <c r="AC2">
+        <v>7.2</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>75</v>
+      </c>
+      <c r="AF2">
         <v>11.5</v>
       </c>
-      <c r="Z2">
-        <v>32</v>
-      </c>
-      <c r="AA2">
-        <v>120</v>
-      </c>
-      <c r="AB2">
-        <v>6.6</v>
-      </c>
-      <c r="AC2">
-        <v>7.4</v>
-      </c>
-      <c r="AD2">
-        <v>20</v>
-      </c>
-      <c r="AE2">
-        <v>80</v>
-      </c>
-      <c r="AF2">
+      <c r="AG2">
         <v>11</v>
       </c>
-      <c r="AG2">
-        <v>11.5</v>
-      </c>
       <c r="AH2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI2">
+        <v>95</v>
+      </c>
+      <c r="AJ2">
+        <v>28</v>
+      </c>
+      <c r="AK2">
+        <v>29</v>
+      </c>
+      <c r="AL2">
+        <v>55</v>
+      </c>
+      <c r="AM2">
+        <v>180</v>
+      </c>
+      <c r="AN2">
+        <v>27</v>
+      </c>
+      <c r="AO2">
         <v>110</v>
       </c>
-      <c r="AJ2">
-        <v>27</v>
-      </c>
-      <c r="AK2">
-        <v>30</v>
-      </c>
-      <c r="AL2">
-        <v>65</v>
-      </c>
-      <c r="AM2">
-        <v>220</v>
-      </c>
-      <c r="AN2">
-        <v>28</v>
-      </c>
-      <c r="AO2">
-        <v>150</v>
-      </c>
       <c r="AP2">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR2">
         <v>27</v>
       </c>
       <c r="AS2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AT2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV2">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AX2">
+        <v>10.5</v>
+      </c>
+      <c r="AY2">
         <v>10</v>
       </c>
-      <c r="AY2">
-        <v>10.5</v>
-      </c>
       <c r="AZ2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BB2">
         <v>24</v>
       </c>
       <c r="BC2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BE2">
         <v>48</v>
       </c>
       <c r="BF2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BG2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="BH2">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="BI2">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BJ2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BL2">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="BM2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BN2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BP2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BQ2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BR2">
+        <v>42</v>
+      </c>
+      <c r="BS2">
+        <v>22</v>
+      </c>
+      <c r="BT2">
+        <v>7.4</v>
+      </c>
+      <c r="BU2">
+        <v>6.6</v>
+      </c>
+      <c r="BV2">
         <v>46</v>
       </c>
-      <c r="BS2">
-        <v>12.5</v>
-      </c>
-      <c r="BT2">
-        <v>7.6</v>
-      </c>
-      <c r="BU2">
-        <v>6.8</v>
-      </c>
-      <c r="BV2">
-        <v>55</v>
-      </c>
       <c r="BW2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BX2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="CA2">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1338,25 +1338,25 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="G3">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="H3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="I3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J3">
+        <v>4.7</v>
+      </c>
+      <c r="K3">
         <v>4.8</v>
       </c>
-      <c r="K3">
-        <v>5</v>
-      </c>
       <c r="L3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M3">
         <v>1.09</v>
@@ -1365,70 +1365,70 @@
         <v>3.15</v>
       </c>
       <c r="O3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P3">
         <v>1.73</v>
       </c>
       <c r="Q3">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R3">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S3">
         <v>4.6</v>
       </c>
       <c r="T3">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="X3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Z3">
         <v>130</v>
       </c>
       <c r="AA3">
-        <v>910</v>
+        <v>710</v>
       </c>
       <c r="AB3">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AC3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AE3">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="AF3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AG3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH3">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AI3">
-        <v>420</v>
+        <v>330</v>
       </c>
       <c r="AJ3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK3">
         <v>19.5</v>
@@ -1437,85 +1437,85 @@
         <v>75</v>
       </c>
       <c r="AM3">
-        <v>620</v>
+        <v>490</v>
       </c>
       <c r="AN3">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AO3">
-        <v>840</v>
+        <v>690</v>
       </c>
       <c r="AP3">
         <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR3">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="AS3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AT3">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AU3">
         <v>10.5</v>
       </c>
       <c r="AV3">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AW3">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="AX3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AY3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BA3">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BB3">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC3">
         <v>17.5</v>
       </c>
       <c r="BD3">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BE3">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="BF3">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG3">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="BH3">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BI3">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="BJ3">
         <v>16</v>
       </c>
       <c r="BK3">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BN3">
         <v>3.35</v>
@@ -1524,10 +1524,10 @@
         <v>3.15</v>
       </c>
       <c r="BP3">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BR3">
         <v>1000</v>
@@ -1536,28 +1536,28 @@
         <v>13</v>
       </c>
       <c r="BT3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BU3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="BW3">
         <v>18</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="BY3">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BZ3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="CA3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB3" t="s">
         <v>162</v>
@@ -1580,22 +1580,22 @@
         <v>137</v>
       </c>
       <c r="F4">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="H4">
-        <v>5.3</v>
+        <v>4.4</v>
       </c>
       <c r="I4">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.54</v>
@@ -1604,16 +1604,16 @@
         <v>1.11</v>
       </c>
       <c r="N4">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="O4">
         <v>1.5</v>
       </c>
       <c r="P4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q4">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R4">
         <v>1.23</v>
@@ -1622,43 +1622,43 @@
         <v>5</v>
       </c>
       <c r="T4">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="U4">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="X4">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AA4">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AB4">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE4">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF4">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AG4">
         <v>10.5</v>
@@ -1667,139 +1667,139 @@
         <v>26</v>
       </c>
       <c r="AI4">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AJ4">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AK4">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AL4">
         <v>55</v>
       </c>
       <c r="AM4">
+        <v>180</v>
+      </c>
+      <c r="AN4">
+        <v>25</v>
+      </c>
+      <c r="AO4">
         <v>190</v>
       </c>
-      <c r="AN4">
-        <v>19</v>
-      </c>
-      <c r="AO4">
-        <v>140</v>
-      </c>
       <c r="AP4">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AR4">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AS4">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AT4">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV4">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AW4">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AX4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY4">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ4">
         <v>22</v>
       </c>
       <c r="BA4">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BB4">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BC4">
+        <v>24</v>
+      </c>
+      <c r="BD4">
+        <v>44</v>
+      </c>
+      <c r="BE4">
+        <v>17.5</v>
+      </c>
+      <c r="BF4">
         <v>21</v>
       </c>
-      <c r="BD4">
-        <v>16</v>
-      </c>
-      <c r="BE4">
-        <v>19.5</v>
-      </c>
-      <c r="BF4">
-        <v>17.5</v>
-      </c>
       <c r="BG4">
-        <v>19.5</v>
+        <v>90</v>
       </c>
       <c r="BH4">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="BI4">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK4">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
+        <v>18.5</v>
+      </c>
+      <c r="BN4">
+        <v>4.5</v>
+      </c>
+      <c r="BO4">
+        <v>4.2</v>
+      </c>
+      <c r="BP4">
+        <v>16.5</v>
+      </c>
+      <c r="BQ4">
+        <v>12.5</v>
+      </c>
+      <c r="BR4">
+        <v>38</v>
+      </c>
+      <c r="BS4">
+        <v>18.5</v>
+      </c>
+      <c r="BT4">
+        <v>7.2</v>
+      </c>
+      <c r="BU4">
+        <v>6.6</v>
+      </c>
+      <c r="BV4">
+        <v>50</v>
+      </c>
+      <c r="BW4">
+        <v>24</v>
+      </c>
+      <c r="BX4">
+        <v>65</v>
+      </c>
+      <c r="BY4">
+        <v>16.5</v>
+      </c>
+      <c r="BZ4">
+        <v>40</v>
+      </c>
+      <c r="CA4">
         <v>20</v>
-      </c>
-      <c r="BN4">
-        <v>4.3</v>
-      </c>
-      <c r="BO4">
-        <v>3.95</v>
-      </c>
-      <c r="BP4">
-        <v>14.5</v>
-      </c>
-      <c r="BQ4">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR4">
-        <v>36</v>
-      </c>
-      <c r="BS4">
-        <v>13.5</v>
-      </c>
-      <c r="BT4">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BU4">
-        <v>7.6</v>
-      </c>
-      <c r="BV4">
-        <v>55</v>
-      </c>
-      <c r="BW4">
-        <v>15.5</v>
-      </c>
-      <c r="BX4">
-        <v>70</v>
-      </c>
-      <c r="BY4">
-        <v>17</v>
-      </c>
-      <c r="BZ4">
-        <v>36</v>
-      </c>
-      <c r="CA4">
-        <v>13.5</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1822,22 +1822,22 @@
         <v>138</v>
       </c>
       <c r="F5">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="G5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J5">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="K5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L5">
         <v>1.28</v>
@@ -1846,34 +1846,34 @@
         <v>1.04</v>
       </c>
       <c r="N5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O5">
         <v>1.18</v>
       </c>
       <c r="P5">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Q5">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R5">
         <v>1.67</v>
       </c>
       <c r="S5">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U5">
         <v>2.16</v>
       </c>
       <c r="V5">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W5">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="X5">
         <v>34</v>
@@ -1891,7 +1891,7 @@
         <v>14.5</v>
       </c>
       <c r="AC5">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD5">
         <v>32</v>
@@ -1903,7 +1903,7 @@
         <v>11.5</v>
       </c>
       <c r="AG5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH5">
         <v>25</v>
@@ -1912,7 +1912,7 @@
         <v>85</v>
       </c>
       <c r="AJ5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK5">
         <v>15</v>
@@ -1924,22 +1924,22 @@
         <v>110</v>
       </c>
       <c r="AN5">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AO5">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP5">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AQ5">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AR5">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="AS5">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AT5">
         <v>10</v>
@@ -1948,10 +1948,10 @@
         <v>10</v>
       </c>
       <c r="AV5">
-        <v>22</v>
+        <v>6.2</v>
       </c>
       <c r="AW5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX5">
         <v>9.199999999999999</v>
@@ -1963,7 +1963,7 @@
         <v>17</v>
       </c>
       <c r="BA5">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BB5">
         <v>11.5</v>
@@ -1972,16 +1972,16 @@
         <v>12.5</v>
       </c>
       <c r="BD5">
-        <v>5.6</v>
+        <v>23</v>
       </c>
       <c r="BE5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF5">
         <v>4.8</v>
       </c>
       <c r="BG5">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH5">
         <v>4.7</v>
@@ -1993,25 +1993,25 @@
         <v>10.5</v>
       </c>
       <c r="BK5">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN5">
         <v>4.5</v>
       </c>
       <c r="BO5">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP5">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BQ5">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="BR5">
         <v>21</v>
@@ -2029,13 +2029,13 @@
         <v>1000</v>
       </c>
       <c r="BW5">
+        <v>9</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
         <v>8.800000000000001</v>
-      </c>
-      <c r="BX5">
-        <v>1000</v>
-      </c>
-      <c r="BY5">
-        <v>8.6</v>
       </c>
       <c r="BZ5">
         <v>12.5</v>
@@ -2064,226 +2064,226 @@
         <v>139</v>
       </c>
       <c r="F6">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="G6">
-        <v>990</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H6">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="I6">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="J6">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K6">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="L6">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="M6">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
         <v>1.33</v>
       </c>
       <c r="P6">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="Q6">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R6">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
+        <v>3.2</v>
+      </c>
+      <c r="T6">
+        <v>2.06</v>
+      </c>
+      <c r="U6">
+        <v>1.76</v>
+      </c>
+      <c r="V6">
         <v>2.62</v>
       </c>
-      <c r="T6">
-        <v>1.11</v>
-      </c>
-      <c r="U6">
-        <v>1.11</v>
-      </c>
-      <c r="V6">
+      <c r="W6">
+        <v>1.13</v>
+      </c>
+      <c r="X6">
+        <v>16.5</v>
+      </c>
+      <c r="Y6">
+        <v>7.6</v>
+      </c>
+      <c r="Z6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AA6">
+        <v>14.5</v>
+      </c>
+      <c r="AB6">
+        <v>23</v>
+      </c>
+      <c r="AC6">
+        <v>10.5</v>
+      </c>
+      <c r="AD6">
+        <v>10.5</v>
+      </c>
+      <c r="AE6">
+        <v>18.5</v>
+      </c>
+      <c r="AF6">
+        <v>160</v>
+      </c>
+      <c r="AG6">
+        <v>32</v>
+      </c>
+      <c r="AH6">
+        <v>27</v>
+      </c>
+      <c r="AI6">
+        <v>46</v>
+      </c>
+      <c r="AJ6">
+        <v>330</v>
+      </c>
+      <c r="AK6">
+        <v>160</v>
+      </c>
+      <c r="AL6">
+        <v>150</v>
+      </c>
+      <c r="AM6">
+        <v>200</v>
+      </c>
+      <c r="AN6">
+        <v>250</v>
+      </c>
+      <c r="AO6">
+        <v>10</v>
+      </c>
+      <c r="AP6">
+        <v>5.9</v>
+      </c>
+      <c r="AQ6">
+        <v>4.1</v>
+      </c>
+      <c r="AR6">
+        <v>4.5</v>
+      </c>
+      <c r="AS6">
+        <v>5.6</v>
+      </c>
+      <c r="AT6">
+        <v>6.6</v>
+      </c>
+      <c r="AU6">
+        <v>4.9</v>
+      </c>
+      <c r="AV6">
+        <v>4.9</v>
+      </c>
+      <c r="AW6">
+        <v>6</v>
+      </c>
+      <c r="AX6">
+        <v>8</v>
+      </c>
+      <c r="AY6">
+        <v>7</v>
+      </c>
+      <c r="AZ6">
+        <v>6.8</v>
+      </c>
+      <c r="BA6">
+        <v>7.6</v>
+      </c>
+      <c r="BB6">
+        <v>9</v>
+      </c>
+      <c r="BC6">
+        <v>8.6</v>
+      </c>
+      <c r="BD6">
+        <v>8.6</v>
+      </c>
+      <c r="BE6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF6">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG6">
+        <v>4.8</v>
+      </c>
+      <c r="BH6">
+        <v>3.5</v>
+      </c>
+      <c r="BI6">
+        <v>2.8</v>
+      </c>
+      <c r="BJ6">
+        <v>12</v>
+      </c>
+      <c r="BK6">
+        <v>5.8</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>2.64</v>
+      </c>
+      <c r="BN6">
+        <v>11.5</v>
+      </c>
+      <c r="BO6">
+        <v>5.7</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>2.58</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>2.58</v>
+      </c>
+      <c r="BT6">
+        <v>4</v>
+      </c>
+      <c r="BU6">
+        <v>2.96</v>
+      </c>
+      <c r="BV6">
+        <v>10.5</v>
+      </c>
+      <c r="BW6">
+        <v>5.4</v>
+      </c>
+      <c r="BX6">
+        <v>30</v>
+      </c>
+      <c r="BY6">
         <v>2.46</v>
       </c>
-      <c r="W6">
-        <v>1.02</v>
-      </c>
-      <c r="X6">
-        <v>1000</v>
-      </c>
-      <c r="Y6">
-        <v>500</v>
-      </c>
-      <c r="Z6">
-        <v>500</v>
-      </c>
-      <c r="AA6">
-        <v>500</v>
-      </c>
-      <c r="AB6">
-        <v>1000</v>
-      </c>
-      <c r="AC6">
-        <v>42</v>
-      </c>
-      <c r="AD6">
-        <v>500</v>
-      </c>
-      <c r="AE6">
-        <v>500</v>
-      </c>
-      <c r="AF6">
-        <v>1000</v>
-      </c>
-      <c r="AG6">
-        <v>1000</v>
-      </c>
-      <c r="AH6">
-        <v>1000</v>
-      </c>
-      <c r="AI6">
-        <v>500</v>
-      </c>
-      <c r="AJ6">
-        <v>1000</v>
-      </c>
-      <c r="AK6">
-        <v>1000</v>
-      </c>
-      <c r="AL6">
-        <v>1000</v>
-      </c>
-      <c r="AM6">
-        <v>1000</v>
-      </c>
-      <c r="AN6">
-        <v>1000</v>
-      </c>
-      <c r="AO6">
-        <v>500</v>
-      </c>
-      <c r="AP6">
-        <v>1.01</v>
-      </c>
-      <c r="AQ6">
-        <v>1.01</v>
-      </c>
-      <c r="AR6">
-        <v>1.01</v>
-      </c>
-      <c r="AS6">
-        <v>1.01</v>
-      </c>
-      <c r="AT6">
-        <v>2.5</v>
-      </c>
-      <c r="AU6">
-        <v>1.01</v>
-      </c>
-      <c r="AV6">
-        <v>1.01</v>
-      </c>
-      <c r="AW6">
-        <v>1.01</v>
-      </c>
-      <c r="AX6">
-        <v>2.5</v>
-      </c>
-      <c r="AY6">
-        <v>2.5</v>
-      </c>
-      <c r="AZ6">
-        <v>1.01</v>
-      </c>
-      <c r="BA6">
-        <v>1.01</v>
-      </c>
-      <c r="BB6">
-        <v>2.5</v>
-      </c>
-      <c r="BC6">
-        <v>2.5</v>
-      </c>
-      <c r="BD6">
-        <v>2.5</v>
-      </c>
-      <c r="BE6">
-        <v>1.01</v>
-      </c>
-      <c r="BF6">
-        <v>3.2</v>
-      </c>
-      <c r="BG6">
-        <v>1.01</v>
-      </c>
-      <c r="BH6">
-        <v>1000</v>
-      </c>
-      <c r="BI6">
-        <v>1.04</v>
-      </c>
-      <c r="BJ6">
-        <v>1000</v>
-      </c>
-      <c r="BK6">
-        <v>1.04</v>
-      </c>
-      <c r="BL6">
-        <v>1000</v>
-      </c>
-      <c r="BM6">
-        <v>1.04</v>
-      </c>
-      <c r="BN6">
-        <v>1000</v>
-      </c>
-      <c r="BO6">
-        <v>1.04</v>
-      </c>
-      <c r="BP6">
-        <v>1000</v>
-      </c>
-      <c r="BQ6">
-        <v>1.04</v>
-      </c>
-      <c r="BR6">
-        <v>1000</v>
-      </c>
-      <c r="BS6">
-        <v>1.04</v>
-      </c>
-      <c r="BT6">
-        <v>1000</v>
-      </c>
-      <c r="BU6">
-        <v>1.04</v>
-      </c>
-      <c r="BV6">
-        <v>1000</v>
-      </c>
-      <c r="BW6">
-        <v>1.04</v>
-      </c>
-      <c r="BX6">
-        <v>1000</v>
-      </c>
-      <c r="BY6">
-        <v>1.04</v>
-      </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA6">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="CB6" t="s">
         <v>162</v>
@@ -2306,226 +2306,226 @@
         <v>140</v>
       </c>
       <c r="F7">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="G7">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="H7">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="I7">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J7">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="K7">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="L7">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N7">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="O7">
         <v>1.6</v>
       </c>
       <c r="P7">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="Q7">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="R7">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="S7">
-        <v>2.96</v>
+        <v>5.1</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>1.58</v>
       </c>
       <c r="V7">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC7">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AP7">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AQ7">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT7">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU7">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AV7">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX7">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BC7">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BD7">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE7">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH7">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="BI7">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="BJ7">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK7">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="BN7">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO7">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BP7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ7">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS7">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BT7">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU7">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="BV7">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW7">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BX7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="BZ7">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA7">
-        <v>1.04</v>
+        <v>1.86</v>
       </c>
       <c r="CB7" t="s">
         <v>162</v>
@@ -2548,100 +2548,100 @@
         <v>141</v>
       </c>
       <c r="F8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="G8">
-        <v>4.4</v>
+        <v>3.95</v>
       </c>
       <c r="H8">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="I8">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="J8">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="K8">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="L8">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N8">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R8">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S8">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="T8">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="V8">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>9</v>
       </c>
       <c r="Y8">
-        <v>950</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="AA8">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AB8">
-        <v>950</v>
+        <v>10.5</v>
       </c>
       <c r="AC8">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="AD8">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AE8">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF8">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AG8">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="AH8">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI8">
         <v>500</v>
       </c>
       <c r="AJ8">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK8">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AL8">
         <v>500</v>
@@ -2650,124 +2650,124 @@
         <v>500</v>
       </c>
       <c r="AN8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO8">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP8">
-        <v>1.05</v>
+        <v>4.6</v>
       </c>
       <c r="AQ8">
-        <v>1.05</v>
+        <v>4.3</v>
       </c>
       <c r="AR8">
-        <v>1.05</v>
+        <v>5.8</v>
       </c>
       <c r="AS8">
-        <v>1.05</v>
+        <v>7.6</v>
       </c>
       <c r="AT8">
-        <v>1.05</v>
+        <v>5</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV8">
-        <v>1.05</v>
+        <v>5.5</v>
       </c>
       <c r="AW8">
-        <v>1.05</v>
+        <v>7.6</v>
       </c>
       <c r="AX8">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="AY8">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="AZ8">
-        <v>1.05</v>
+        <v>6.8</v>
       </c>
       <c r="BA8">
-        <v>1.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB8">
-        <v>1.05</v>
+        <v>8.6</v>
       </c>
       <c r="BC8">
-        <v>1.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8">
-        <v>1.05</v>
+        <v>8.6</v>
       </c>
       <c r="BE8">
-        <v>1.05</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8">
-        <v>1.05</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>1.05</v>
+        <v>7.6</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>2.1</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>3.55</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>2.14</v>
       </c>
       <c r="CB8" t="s">
         <v>162</v>
@@ -2811,7 +2811,7 @@
         <v>1.7</v>
       </c>
       <c r="M9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="N9">
         <v>2.26</v>
@@ -2820,10 +2820,10 @@
         <v>1.74</v>
       </c>
       <c r="P9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="Q9">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
         <v>1.13</v>
@@ -2835,7 +2835,7 @@
         <v>2.5</v>
       </c>
       <c r="U9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="V9">
         <v>1.32</v>
@@ -2853,7 +2853,7 @@
         <v>26</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
         <v>6.4</v>
@@ -2862,10 +2862,10 @@
         <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE9">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="AF9">
         <v>13</v>
@@ -2874,28 +2874,28 @@
         <v>14</v>
       </c>
       <c r="AH9">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI9">
-        <v>150</v>
+        <v>490</v>
       </c>
       <c r="AJ9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK9">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AL9">
-        <v>540</v>
+        <v>200</v>
       </c>
       <c r="AM9">
         <v>500</v>
       </c>
       <c r="AN9">
-        <v>180</v>
+        <v>130</v>
       </c>
       <c r="AO9">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AP9">
         <v>5.9</v>
@@ -2910,7 +2910,7 @@
         <v>34</v>
       </c>
       <c r="AT9">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU9">
         <v>6.6</v>
@@ -2919,7 +2919,7 @@
         <v>17.5</v>
       </c>
       <c r="AW9">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AX9">
         <v>11.5</v>
@@ -2943,7 +2943,7 @@
         <v>38</v>
       </c>
       <c r="BE9">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="BF9">
         <v>27</v>
@@ -3032,7 +3032,7 @@
         <v>143</v>
       </c>
       <c r="F10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="G10">
         <v>1.31</v>
@@ -3047,7 +3047,7 @@
         <v>6.8</v>
       </c>
       <c r="K10">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>1.16</v>
@@ -3056,13 +3056,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="O10">
         <v>1.1</v>
       </c>
       <c r="P10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q10">
         <v>1.3</v>
@@ -3074,10 +3074,10 @@
         <v>1.74</v>
       </c>
       <c r="T10">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V10">
         <v>1.08</v>
@@ -3128,10 +3128,10 @@
         <v>14</v>
       </c>
       <c r="AL10">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM10">
-        <v>95</v>
+        <v>320</v>
       </c>
       <c r="AN10">
         <v>3.2</v>
@@ -3140,13 +3140,13 @@
         <v>110</v>
       </c>
       <c r="AP10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ10">
         <v>40</v>
       </c>
       <c r="AR10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS10">
         <v>9.6</v>
@@ -3158,10 +3158,10 @@
         <v>16.5</v>
       </c>
       <c r="AV10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW10">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX10">
         <v>10.5</v>
@@ -3173,7 +3173,7 @@
         <v>21</v>
       </c>
       <c r="BA10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB10">
         <v>10</v>
@@ -3185,13 +3185,13 @@
         <v>14.5</v>
       </c>
       <c r="BE10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF10">
         <v>2.76</v>
       </c>
       <c r="BG10">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BH10">
         <v>6.4</v>
@@ -3200,52 +3200,52 @@
         <v>4.6</v>
       </c>
       <c r="BJ10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK10">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BN10">
         <v>4.7</v>
       </c>
       <c r="BO10">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP10">
         <v>7.4</v>
       </c>
       <c r="BQ10">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BR10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BS10">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU10">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX10">
         <v>55</v>
       </c>
       <c r="BY10">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>7.2</v>
@@ -3274,52 +3274,52 @@
         <v>144</v>
       </c>
       <c r="F11">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G11">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H11">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="I11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J11">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K11">
         <v>5.2</v>
       </c>
       <c r="L11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O11">
         <v>1.11</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="R11">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S11">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T11">
-        <v>1.43</v>
+        <v>1.11</v>
       </c>
       <c r="U11">
-        <v>2.8</v>
+        <v>1.11</v>
       </c>
       <c r="V11">
         <v>1.01</v>
@@ -3328,43 +3328,43 @@
         <v>1.01</v>
       </c>
       <c r="X11">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Y11">
         <v>30</v>
       </c>
       <c r="Z11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA11">
         <v>290</v>
       </c>
       <c r="AB11">
+        <v>21</v>
+      </c>
+      <c r="AC11">
+        <v>13</v>
+      </c>
+      <c r="AD11">
         <v>22</v>
-      </c>
-      <c r="AC11">
-        <v>14.5</v>
-      </c>
-      <c r="AD11">
-        <v>21</v>
       </c>
       <c r="AE11">
         <v>42</v>
       </c>
       <c r="AF11">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG11">
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AI11">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ11">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AK11">
         <v>19.5</v>
@@ -3373,73 +3373,73 @@
         <v>24</v>
       </c>
       <c r="AM11">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AN11">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AO11">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AQ11">
         <v>14.5</v>
       </c>
       <c r="AR11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AS11">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AT11">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AU11">
         <v>10.5</v>
       </c>
       <c r="AV11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW11">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX11">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY11">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA11">
-        <v>16</v>
+        <v>5.9</v>
       </c>
       <c r="BB11">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BC11">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD11">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BE11">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF11">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="BG11">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BH11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BI11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ11">
         <v>8.800000000000001</v>
@@ -3448,22 +3448,22 @@
         <v>4.7</v>
       </c>
       <c r="BL11">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BM11">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP11">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BR11">
         <v>18.5</v>
@@ -3472,28 +3472,28 @@
         <v>6.6</v>
       </c>
       <c r="BT11">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU11">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BW11">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ11">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="CA11">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="CB11" t="s">
         <v>162</v>
@@ -3516,16 +3516,16 @@
         <v>145</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="G12">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H12">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I12">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J12">
         <v>4.3</v>
@@ -3549,7 +3549,7 @@
         <v>3.8</v>
       </c>
       <c r="Q12">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R12">
         <v>2.16</v>
@@ -3558,124 +3558,124 @@
         <v>1.66</v>
       </c>
       <c r="T12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U12">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V12">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="W12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="X12">
         <v>950</v>
       </c>
       <c r="Y12">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Z12">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB12">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AC12">
         <v>17</v>
       </c>
       <c r="AD12">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE12">
         <v>22</v>
       </c>
       <c r="AF12">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AG12">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH12">
         <v>16.5</v>
       </c>
       <c r="AI12">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AJ12">
         <v>500</v>
       </c>
       <c r="AK12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL12">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="AM12">
         <v>200</v>
       </c>
       <c r="AN12">
+        <v>12.5</v>
+      </c>
+      <c r="AO12">
+        <v>6.2</v>
+      </c>
+      <c r="AP12">
+        <v>6.4</v>
+      </c>
+      <c r="AQ12">
+        <v>20</v>
+      </c>
+      <c r="AR12">
+        <v>19</v>
+      </c>
+      <c r="AS12">
+        <v>6</v>
+      </c>
+      <c r="AT12">
+        <v>6</v>
+      </c>
+      <c r="AU12">
+        <v>11</v>
+      </c>
+      <c r="AV12">
+        <v>10.5</v>
+      </c>
+      <c r="AW12">
+        <v>14.5</v>
+      </c>
+      <c r="AX12">
+        <v>6.2</v>
+      </c>
+      <c r="AY12">
         <v>13</v>
       </c>
-      <c r="AO12">
-        <v>6.8</v>
-      </c>
-      <c r="AP12">
-        <v>4.9</v>
-      </c>
-      <c r="AQ12">
+      <c r="AZ12">
+        <v>10.5</v>
+      </c>
+      <c r="BA12">
+        <v>15.5</v>
+      </c>
+      <c r="BB12">
+        <v>6.4</v>
+      </c>
+      <c r="BC12">
         <v>21</v>
       </c>
-      <c r="AR12">
-        <v>20</v>
-      </c>
-      <c r="AS12">
-        <v>4.6</v>
-      </c>
-      <c r="AT12">
-        <v>4.6</v>
-      </c>
-      <c r="AU12">
-        <v>12</v>
-      </c>
-      <c r="AV12">
-        <v>11</v>
-      </c>
-      <c r="AW12">
-        <v>15</v>
-      </c>
-      <c r="AX12">
-        <v>4.7</v>
-      </c>
-      <c r="AY12">
-        <v>14</v>
-      </c>
-      <c r="AZ12">
-        <v>11.5</v>
-      </c>
-      <c r="BA12">
-        <v>17</v>
-      </c>
-      <c r="BB12">
-        <v>4.9</v>
-      </c>
-      <c r="BC12">
-        <v>4.5</v>
-      </c>
       <c r="BD12">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BE12">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BF12">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BG12">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3761,16 +3761,16 @@
         <v>1.54</v>
       </c>
       <c r="G13">
-        <v>1.96</v>
+        <v>1.89</v>
       </c>
       <c r="H13">
         <v>3</v>
       </c>
       <c r="I13">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="J13">
-        <v>2.64</v>
+        <v>3.75</v>
       </c>
       <c r="K13">
         <v>950</v>
@@ -3779,7 +3779,7 @@
         <v>1.01</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N13">
         <v>2.46</v>
@@ -3809,7 +3809,7 @@
         <v>1.17</v>
       </c>
       <c r="W13">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -3917,7 +3917,7 @@
         <v>1.01</v>
       </c>
       <c r="BG13">
-        <v>1.02</v>
+        <v>1.55</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4003,19 +4003,19 @@
         <v>3.15</v>
       </c>
       <c r="G14">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="H14">
         <v>2.5</v>
       </c>
       <c r="I14">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="J14">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="K14">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O14">
         <v>1.42</v>
@@ -4033,7 +4033,7 @@
         <v>1.62</v>
       </c>
       <c r="Q14">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>1.2</v>
@@ -4042,16 +4042,16 @@
         <v>3.5</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="U14">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="V14">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="X14">
         <v>950</v>
@@ -4063,7 +4063,7 @@
         <v>500</v>
       </c>
       <c r="AA14">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AB14">
         <v>950</v>
@@ -4090,7 +4090,7 @@
         <v>500</v>
       </c>
       <c r="AJ14">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK14">
         <v>500</v>
@@ -4108,58 +4108,58 @@
         <v>500</v>
       </c>
       <c r="AP14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AQ14">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="AR14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AS14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AT14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AU14">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="AV14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AW14">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AX14">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AY14">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="AZ14">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="BA14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BB14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BC14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BD14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BE14">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="BF14">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BG14">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4242,7 +4242,7 @@
         <v>148</v>
       </c>
       <c r="F15">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G15">
         <v>3.55</v>
@@ -4251,13 +4251,13 @@
         <v>1.94</v>
       </c>
       <c r="I15">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="J15">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="K15">
-        <v>950</v>
+        <v>14.5</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4290,7 +4290,7 @@
         <v>1.11</v>
       </c>
       <c r="V15">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="W15">
         <v>1.39</v>
@@ -4311,7 +4311,7 @@
         <v>1000</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD15">
         <v>1000</v>
@@ -4350,58 +4350,58 @@
         <v>1000</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AU15">
         <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4487,10 +4487,10 @@
         <v>1.71</v>
       </c>
       <c r="G16">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H16">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I16">
         <v>5.5</v>
@@ -4502,19 +4502,19 @@
         <v>6.6</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="M16">
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>1.08</v>
       </c>
       <c r="P16">
-        <v>2.96</v>
+        <v>2.72</v>
       </c>
       <c r="Q16">
         <v>1.23</v>
@@ -4523,7 +4523,7 @@
         <v>1.86</v>
       </c>
       <c r="S16">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="T16">
         <v>1.11</v>
@@ -4535,22 +4535,22 @@
         <v>1.22</v>
       </c>
       <c r="W16">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y16">
         <v>950</v>
       </c>
       <c r="Z16">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA16">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="AB16">
-        <v>950</v>
+        <v>75</v>
       </c>
       <c r="AC16">
         <v>19.5</v>
@@ -4559,10 +4559,10 @@
         <v>26</v>
       </c>
       <c r="AE16">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AF16">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AG16">
         <v>16.5</v>
@@ -4571,76 +4571,76 @@
         <v>20</v>
       </c>
       <c r="AI16">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AK16">
         <v>23</v>
       </c>
       <c r="AL16">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="AM16">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AN16">
         <v>7.6</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP16">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="AQ16">
-        <v>2.46</v>
+        <v>2.74</v>
       </c>
       <c r="AR16">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AS16">
+        <v>2.84</v>
+      </c>
+      <c r="AT16">
+        <v>2.68</v>
+      </c>
+      <c r="AU16">
         <v>2.54</v>
       </c>
-      <c r="AT16">
-        <v>2.42</v>
-      </c>
-      <c r="AU16">
-        <v>2.3</v>
-      </c>
       <c r="AV16">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="AW16">
+        <v>2.76</v>
+      </c>
+      <c r="AX16">
+        <v>2.64</v>
+      </c>
+      <c r="AY16">
         <v>2.48</v>
       </c>
-      <c r="AX16">
-        <v>2.4</v>
-      </c>
-      <c r="AY16">
-        <v>2.26</v>
-      </c>
       <c r="AZ16">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="BA16">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="BB16">
-        <v>2.42</v>
+        <v>2.68</v>
       </c>
       <c r="BC16">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="BD16">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="BE16">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="BF16">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="BG16">
         <v>2.62</v>
@@ -4738,16 +4738,16 @@
         <v>2.66</v>
       </c>
       <c r="J17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K17">
         <v>5.1</v>
       </c>
       <c r="L17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N17">
         <v>1.1</v>
@@ -4780,112 +4780,112 @@
         <v>1.56</v>
       </c>
       <c r="X17">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="Y17">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="Z17">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA17">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AB17">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AC17">
         <v>14</v>
       </c>
       <c r="AD17">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AE17">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AF17">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AG17">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AH17">
         <v>15</v>
       </c>
       <c r="AI17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AJ17">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AK17">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AL17">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AM17">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN17">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO17">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AP17">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="AQ17">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="AR17">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AS17">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT17">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AU17">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="AV17">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AW17">
-        <v>4</v>
+        <v>6.4</v>
       </c>
       <c r="AX17">
-        <v>4.1</v>
+        <v>6.8</v>
       </c>
       <c r="AY17">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="AZ17">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="BA17">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BB17">
-        <v>4.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC17">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BD17">
-        <v>4</v>
+        <v>6.6</v>
       </c>
       <c r="BE17">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF17">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="BG17">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH17">
         <v>6.2</v>
@@ -4989,7 +4989,7 @@
         <v>1.19</v>
       </c>
       <c r="M18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N18">
         <v>7</v>
@@ -5004,7 +5004,7 @@
         <v>1.41</v>
       </c>
       <c r="R18">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S18">
         <v>2.04</v>
@@ -5022,28 +5022,28 @@
         <v>1.74</v>
       </c>
       <c r="X18">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Y18">
         <v>25</v>
       </c>
       <c r="Z18">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA18">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AB18">
         <v>20</v>
       </c>
       <c r="AC18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD18">
         <v>16</v>
       </c>
       <c r="AE18">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AF18">
         <v>21</v>
@@ -5064,19 +5064,19 @@
         <v>21</v>
       </c>
       <c r="AL18">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM18">
         <v>46</v>
       </c>
       <c r="AN18">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO18">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AP18">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18">
         <v>19.5</v>
@@ -5085,7 +5085,7 @@
         <v>23</v>
       </c>
       <c r="AS18">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AT18">
         <v>16</v>
@@ -5097,7 +5097,7 @@
         <v>12.5</v>
       </c>
       <c r="AW18">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AX18">
         <v>17.5</v>
@@ -5112,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="BB18">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC18">
         <v>17</v>
@@ -5121,7 +5121,7 @@
         <v>20</v>
       </c>
       <c r="BE18">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="BF18">
         <v>7.6</v>
@@ -5133,7 +5133,7 @@
         <v>5.4</v>
       </c>
       <c r="BI18">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BJ18">
         <v>8.6</v>
@@ -5222,7 +5222,7 @@
         <v>2.88</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K19">
         <v>4.2</v>
@@ -5231,28 +5231,28 @@
         <v>1.26</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
         <v>5.1</v>
       </c>
       <c r="O19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P19">
         <v>2.38</v>
       </c>
       <c r="Q19">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R19">
         <v>1.56</v>
       </c>
       <c r="S19">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T19">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U19">
         <v>2.54</v>
@@ -5270,13 +5270,13 @@
         <v>16.5</v>
       </c>
       <c r="Z19">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AA19">
-        <v>50</v>
+        <v>440</v>
       </c>
       <c r="AB19">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC19">
         <v>11</v>
@@ -5309,10 +5309,10 @@
         <v>34</v>
       </c>
       <c r="AM19">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="AN19">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO19">
         <v>19</v>
@@ -5327,7 +5327,7 @@
         <v>17.5</v>
       </c>
       <c r="AS19">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT19">
         <v>12.5</v>
@@ -5351,22 +5351,22 @@
         <v>11</v>
       </c>
       <c r="BA19">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BB19">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="BC19">
         <v>17.5</v>
       </c>
       <c r="BD19">
-        <v>5.9</v>
+        <v>13</v>
       </c>
       <c r="BE19">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF19">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG19">
         <v>12.5</v>
@@ -5402,7 +5402,7 @@
         <v>7.2</v>
       </c>
       <c r="BR19">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
         <v>8.800000000000001</v>
@@ -5411,10 +5411,10 @@
         <v>6.6</v>
       </c>
       <c r="BU19">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BV19">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
         <v>8.199999999999999</v>
@@ -5452,22 +5452,22 @@
         <v>153</v>
       </c>
       <c r="F20">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="G20">
-        <v>600</v>
+        <v>2.74</v>
       </c>
       <c r="H20">
-        <v>1.69</v>
+        <v>2.04</v>
       </c>
       <c r="I20">
-        <v>870</v>
+        <v>4.4</v>
       </c>
       <c r="J20">
-        <v>2.5</v>
+        <v>3.85</v>
       </c>
       <c r="K20">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5500,118 +5500,118 @@
         <v>1.11</v>
       </c>
       <c r="V20">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="W20">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="X20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Z20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH20">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ20">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AL20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM20">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AO20">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AQ20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AR20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AS20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AT20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AU20">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="AV20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AW20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AX20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AY20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AZ20">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BA20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BB20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BC20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BD20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BE20">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="BF20">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG20">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -5697,7 +5697,7 @@
         <v>2.32</v>
       </c>
       <c r="G21">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H21">
         <v>4</v>
@@ -5709,7 +5709,7 @@
         <v>2.92</v>
       </c>
       <c r="K21">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="L21">
         <v>1.68</v>
@@ -5727,7 +5727,7 @@
         <v>1.43</v>
       </c>
       <c r="Q21">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="R21">
         <v>1.14</v>
@@ -5748,7 +5748,7 @@
         <v>1.72</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y21">
         <v>9.6</v>
@@ -5769,7 +5769,7 @@
         <v>20</v>
       </c>
       <c r="AE21">
-        <v>490</v>
+        <v>180</v>
       </c>
       <c r="AF21">
         <v>12.5</v>
@@ -5778,7 +5778,7 @@
         <v>13</v>
       </c>
       <c r="AH21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AI21">
         <v>490</v>
@@ -5787,16 +5787,16 @@
         <v>60</v>
       </c>
       <c r="AK21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AL21">
-        <v>490</v>
+        <v>180</v>
       </c>
       <c r="AM21">
         <v>500</v>
       </c>
       <c r="AN21">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AO21">
         <v>490</v>
@@ -5811,7 +5811,7 @@
         <v>17.5</v>
       </c>
       <c r="AS21">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT21">
         <v>5.9</v>
@@ -5832,7 +5832,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ21">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BA21">
         <v>42</v>
@@ -5847,7 +5847,7 @@
         <v>36</v>
       </c>
       <c r="BE21">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BF21">
         <v>24</v>
@@ -5898,7 +5898,7 @@
         <v>5.5</v>
       </c>
       <c r="BV21">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
         <v>13.5</v>
@@ -5910,7 +5910,7 @@
         <v>2.12</v>
       </c>
       <c r="BZ21">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
         <v>2.12</v>
@@ -5942,7 +5942,7 @@
         <v>1.9</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I22">
         <v>6.8</v>
@@ -5963,19 +5963,19 @@
         <v>2.68</v>
       </c>
       <c r="O22">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P22">
         <v>1.62</v>
       </c>
       <c r="Q22">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R22">
         <v>1.23</v>
       </c>
       <c r="S22">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="T22">
         <v>2.06</v>
@@ -5990,34 +5990,34 @@
         <v>2.1</v>
       </c>
       <c r="X22">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y22">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="Z22">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="AA22">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="AB22">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC22">
         <v>8.800000000000001</v>
       </c>
       <c r="AD22">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE22">
         <v>700</v>
       </c>
       <c r="AF22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG22">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH22">
         <v>27</v>
@@ -6026,76 +6026,76 @@
         <v>700</v>
       </c>
       <c r="AJ22">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK22">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL22">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AM22">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN22">
         <v>17.5</v>
       </c>
       <c r="AO22">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AP22">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ22">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AR22">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS22">
+        <v>7.4</v>
+      </c>
+      <c r="AT22">
+        <v>3.7</v>
+      </c>
+      <c r="AU22">
+        <v>4.1</v>
+      </c>
+      <c r="AV22">
+        <v>5.9</v>
+      </c>
+      <c r="AW22">
+        <v>7.2</v>
+      </c>
+      <c r="AX22">
+        <v>4.4</v>
+      </c>
+      <c r="AY22">
+        <v>4.6</v>
+      </c>
+      <c r="AZ22">
+        <v>6</v>
+      </c>
+      <c r="BA22">
+        <v>7.2</v>
+      </c>
+      <c r="BB22">
         <v>5.6</v>
       </c>
-      <c r="AT22">
-        <v>3.3</v>
-      </c>
-      <c r="AU22">
-        <v>3.45</v>
-      </c>
-      <c r="AV22">
-        <v>4.7</v>
-      </c>
-      <c r="AW22">
-        <v>5.5</v>
-      </c>
-      <c r="AX22">
-        <v>3.75</v>
-      </c>
-      <c r="AY22">
-        <v>3.85</v>
-      </c>
-      <c r="AZ22">
-        <v>4.7</v>
-      </c>
-      <c r="BA22">
-        <v>5.5</v>
-      </c>
-      <c r="BB22">
-        <v>4.6</v>
-      </c>
       <c r="BC22">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD22">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE22">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF22">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BG22">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH22">
         <v>3.15</v>
@@ -6190,22 +6190,22 @@
         <v>2.56</v>
       </c>
       <c r="J23">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K23">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N23">
         <v>3.2</v>
       </c>
       <c r="O23">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P23">
         <v>1.73</v>
@@ -6214,130 +6214,130 @@
         <v>2.1</v>
       </c>
       <c r="R23">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S23">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T23">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="U23">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="V23">
         <v>1.64</v>
       </c>
       <c r="W23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y23">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z23">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA23">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC23">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD23">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE23">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AG23">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH23">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI23">
         <v>1000</v>
       </c>
       <c r="AJ23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK23">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AL23">
         <v>65</v>
       </c>
       <c r="AM23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN23">
         <v>1000</v>
       </c>
       <c r="AO23">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP23">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AQ23">
-        <v>1.02</v>
+        <v>7.4</v>
       </c>
       <c r="AR23">
-        <v>1.02</v>
+        <v>12</v>
       </c>
       <c r="AS23">
-        <v>1.02</v>
+        <v>5.2</v>
       </c>
       <c r="AT23">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AU23">
-        <v>1.02</v>
+        <v>5.8</v>
       </c>
       <c r="AV23">
-        <v>1.02</v>
+        <v>10</v>
       </c>
       <c r="AW23">
-        <v>1.02</v>
+        <v>5.1</v>
       </c>
       <c r="AX23">
-        <v>1.02</v>
+        <v>19</v>
       </c>
       <c r="AY23">
-        <v>1.02</v>
+        <v>11</v>
       </c>
       <c r="AZ23">
-        <v>1.02</v>
+        <v>13.5</v>
       </c>
       <c r="BA23">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="BB23">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="BC23">
-        <v>1.02</v>
+        <v>5.4</v>
       </c>
       <c r="BD23">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BE23">
-        <v>1.02</v>
+        <v>5.7</v>
       </c>
       <c r="BF23">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="BG23">
-        <v>1.02</v>
+        <v>19.5</v>
       </c>
       <c r="BH23">
         <v>1000</v>
@@ -6346,7 +6346,7 @@
         <v>1.04</v>
       </c>
       <c r="BJ23">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK23">
         <v>1.04</v>
@@ -6358,13 +6358,13 @@
         <v>1.04</v>
       </c>
       <c r="BN23">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="BO23">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="BP23">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BQ23">
         <v>1.04</v>
@@ -6376,25 +6376,25 @@
         <v>1.04</v>
       </c>
       <c r="BT23">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="BU23">
-        <v>3.75</v>
+        <v>1.04</v>
       </c>
       <c r="BV23">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BW23">
         <v>1.04</v>
       </c>
       <c r="BX23">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
         <v>1.04</v>
       </c>
       <c r="BZ23">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="CA23">
         <v>1.04</v>
@@ -6438,13 +6438,13 @@
         <v>3.35</v>
       </c>
       <c r="L24">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="M24">
         <v>1.13</v>
       </c>
       <c r="N24">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="O24">
         <v>1.58</v>
@@ -6456,7 +6456,7 @@
         <v>2.7</v>
       </c>
       <c r="R24">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S24">
         <v>5.6</v>
@@ -6465,7 +6465,7 @@
         <v>2.2</v>
       </c>
       <c r="U24">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V24">
         <v>1.76</v>
@@ -6483,10 +6483,10 @@
         <v>13</v>
       </c>
       <c r="AA24">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AB24">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC24">
         <v>7.6</v>
@@ -6498,25 +6498,25 @@
         <v>40</v>
       </c>
       <c r="AF24">
+        <v>100</v>
+      </c>
+      <c r="AG24">
         <v>500</v>
-      </c>
-      <c r="AG24">
-        <v>970</v>
       </c>
       <c r="AH24">
         <v>30</v>
       </c>
       <c r="AI24">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ24">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK24">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="AL24">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM24">
         <v>500</v>
@@ -6525,7 +6525,7 @@
         <v>500</v>
       </c>
       <c r="AO24">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="AP24">
         <v>7.4</v>
@@ -6537,10 +6537,10 @@
         <v>11</v>
       </c>
       <c r="AS24">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AT24">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU24">
         <v>6.8</v>
@@ -6549,10 +6549,10 @@
         <v>10</v>
       </c>
       <c r="AW24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AX24">
         <v>8.6</v>
-      </c>
-      <c r="AX24">
-        <v>8</v>
       </c>
       <c r="AY24">
         <v>16</v>
@@ -6561,43 +6561,43 @@
         <v>21</v>
       </c>
       <c r="BA24">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC24">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BD24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE24">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG24">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="BH24">
         <v>2.66</v>
       </c>
       <c r="BI24">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BJ24">
         <v>12</v>
       </c>
       <c r="BK24">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN24">
         <v>7.2</v>
@@ -6609,34 +6609,34 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BT24">
         <v>4.8</v>
       </c>
       <c r="BU24">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BV24">
         <v>20</v>
       </c>
       <c r="BW24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ24">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA24">
         <v>12.5</v>
@@ -6662,7 +6662,7 @@
         <v>158</v>
       </c>
       <c r="F25">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G25">
         <v>1.79</v>
@@ -6680,19 +6680,19 @@
         <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M25">
         <v>1.08</v>
       </c>
       <c r="N25">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O25">
         <v>1.35</v>
       </c>
       <c r="P25">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q25">
         <v>2.04</v>
@@ -6707,7 +6707,7 @@
         <v>1.96</v>
       </c>
       <c r="U25">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="V25">
         <v>1.21</v>
@@ -6719,70 +6719,70 @@
         <v>13.5</v>
       </c>
       <c r="Y25">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="Z25">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AA25">
-        <v>700</v>
+        <v>690</v>
       </c>
       <c r="AB25">
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD25">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE25">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AF25">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG25">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH25">
         <v>21</v>
       </c>
       <c r="AI25">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AJ25">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AK25">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL25">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM25">
-        <v>150</v>
+        <v>380</v>
       </c>
       <c r="AN25">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO25">
-        <v>120</v>
+        <v>400</v>
       </c>
       <c r="AP25">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ25">
         <v>15.5</v>
       </c>
       <c r="AR25">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AS25">
-        <v>8.4</v>
+        <v>42</v>
       </c>
       <c r="AT25">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU25">
         <v>7.8</v>
@@ -6791,19 +6791,19 @@
         <v>19</v>
       </c>
       <c r="AW25">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="AX25">
         <v>9</v>
       </c>
       <c r="AY25">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA25">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BB25">
         <v>16</v>
@@ -6812,16 +6812,16 @@
         <v>17</v>
       </c>
       <c r="BD25">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="BE25">
-        <v>8.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="BF25">
         <v>11</v>
       </c>
       <c r="BG25">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="BH25">
         <v>3.35</v>
@@ -6839,7 +6839,7 @@
         <v>1000</v>
       </c>
       <c r="BM25">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN25">
         <v>4.3</v>
@@ -6875,13 +6875,13 @@
         <v>1000</v>
       </c>
       <c r="BY25">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ25">
         <v>24</v>
       </c>
       <c r="CA25">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB25" t="s">
         <v>162</v>
@@ -6904,10 +6904,10 @@
         <v>159</v>
       </c>
       <c r="F26">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G26">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="H26">
         <v>1.96</v>
@@ -6916,19 +6916,19 @@
         <v>1.98</v>
       </c>
       <c r="J26">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L26">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M26">
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O26">
         <v>1.33</v>
@@ -6937,7 +6937,7 @@
         <v>1.95</v>
       </c>
       <c r="Q26">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R26">
         <v>1.36</v>
@@ -6946,7 +6946,7 @@
         <v>3.55</v>
       </c>
       <c r="T26">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U26">
         <v>2.08</v>
@@ -6976,7 +6976,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE26">
         <v>21</v>
@@ -6985,7 +6985,7 @@
         <v>34</v>
       </c>
       <c r="AG26">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH26">
         <v>19</v>
@@ -6994,7 +6994,7 @@
         <v>38</v>
       </c>
       <c r="AJ26">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AK26">
         <v>60</v>
@@ -7027,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="AU26">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV26">
         <v>9.6</v>
@@ -7036,7 +7036,7 @@
         <v>18.5</v>
       </c>
       <c r="AX26">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AY26">
         <v>16</v>
@@ -7066,58 +7066,58 @@
         <v>12.5</v>
       </c>
       <c r="BH26">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BI26">
         <v>3.15</v>
       </c>
       <c r="BJ26">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BK26">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN26">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO26">
         <v>5.5</v>
       </c>
       <c r="BP26">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BQ26">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BR26">
         <v>46</v>
       </c>
       <c r="BS26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT26">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BU26">
         <v>4.1</v>
       </c>
       <c r="BV26">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BW26">
-        <v>10.5</v>
+        <v>8</v>
       </c>
       <c r="BX26">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BY26">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ26">
         <v>25</v>
@@ -7155,16 +7155,16 @@
         <v>4.1</v>
       </c>
       <c r="I27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J27">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K27">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L27">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="M27">
         <v>1.1</v>
@@ -7200,16 +7200,16 @@
         <v>1.87</v>
       </c>
       <c r="X27">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y27">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="Z27">
         <v>34</v>
       </c>
       <c r="AA27">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB27">
         <v>7.6</v>
@@ -7221,7 +7221,7 @@
         <v>19</v>
       </c>
       <c r="AE27">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF27">
         <v>12</v>
@@ -7239,7 +7239,7 @@
         <v>32</v>
       </c>
       <c r="AK27">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL27">
         <v>60</v>
@@ -7260,10 +7260,10 @@
         <v>10</v>
       </c>
       <c r="AR27">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AT27">
         <v>6.6</v>
@@ -7275,7 +7275,7 @@
         <v>13.5</v>
       </c>
       <c r="AW27">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX27">
         <v>8.800000000000001</v>
@@ -7287,7 +7287,7 @@
         <v>15.5</v>
       </c>
       <c r="BA27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB27">
         <v>21</v>
@@ -7296,22 +7296,22 @@
         <v>21</v>
       </c>
       <c r="BD27">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE27">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BF27">
         <v>14</v>
       </c>
       <c r="BG27">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BH27">
         <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BJ27">
         <v>11</v>
@@ -7323,7 +7323,7 @@
         <v>1000</v>
       </c>
       <c r="BM27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BN27">
         <v>4.6</v>
@@ -7332,10 +7332,10 @@
         <v>3.55</v>
       </c>
       <c r="BP27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BQ27">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR27">
         <v>1000</v>
@@ -7353,13 +7353,13 @@
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BX27">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
@@ -7391,7 +7391,7 @@
         <v>1.44</v>
       </c>
       <c r="G28">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="H28">
         <v>6.6</v>
@@ -7400,7 +7400,7 @@
         <v>8</v>
       </c>
       <c r="J28">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="K28">
         <v>5.6</v>
@@ -7424,7 +7424,7 @@
         <v>1.53</v>
       </c>
       <c r="R28">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S28">
         <v>2.34</v>
@@ -7433,13 +7433,13 @@
         <v>1.74</v>
       </c>
       <c r="U28">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V28">
         <v>1.14</v>
       </c>
       <c r="W28">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="X28">
         <v>34</v>
@@ -7451,7 +7451,7 @@
         <v>80</v>
       </c>
       <c r="AA28">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AB28">
         <v>12</v>
@@ -7475,7 +7475,7 @@
         <v>23</v>
       </c>
       <c r="AI28">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ28">
         <v>16.5</v>
@@ -7484,7 +7484,7 @@
         <v>17.5</v>
       </c>
       <c r="AL28">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AM28">
         <v>110</v>
@@ -7493,16 +7493,16 @@
         <v>5.6</v>
       </c>
       <c r="AO28">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AP28">
         <v>19.5</v>
       </c>
       <c r="AQ28">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR28">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS28">
         <v>5.6</v>
@@ -7517,7 +7517,7 @@
         <v>19.5</v>
       </c>
       <c r="AW28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX28">
         <v>7.8</v>
@@ -7541,19 +7541,19 @@
         <v>20</v>
       </c>
       <c r="BE28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF28">
         <v>4.7</v>
       </c>
       <c r="BG28">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH28">
         <v>4.7</v>
       </c>
       <c r="BI28">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ28">
         <v>10.5</v>
@@ -7565,7 +7565,7 @@
         <v>1000</v>
       </c>
       <c r="BM28">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BN28">
         <v>4.5</v>
@@ -7583,7 +7583,7 @@
         <v>21</v>
       </c>
       <c r="BS28">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT28">
         <v>11.5</v>
@@ -7592,7 +7592,7 @@
         <v>5.3</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW28">
         <v>8.4</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -502,7 +502,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-28 20:57:49</t>
+    <t>2026-07-28 23:04:14</t>
   </si>
 </sst>
 </file>
@@ -1096,226 +1096,226 @@
         <v>135</v>
       </c>
       <c r="F2">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="G2">
-        <v>2.12</v>
+        <v>8</v>
       </c>
       <c r="H2">
-        <v>4.4</v>
+        <v>9</v>
       </c>
       <c r="I2">
-        <v>4.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2">
-        <v>3.3</v>
+        <v>1.29</v>
       </c>
       <c r="K2">
-        <v>3.35</v>
+        <v>1.3</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="N2">
-        <v>2.76</v>
+        <v>1.03</v>
       </c>
       <c r="O2">
-        <v>1.56</v>
+        <v>30</v>
       </c>
       <c r="P2">
-        <v>1.61</v>
+        <v>1.01</v>
       </c>
       <c r="Q2">
-        <v>2.6</v>
+        <v>200</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>5.4</v>
+        <v>470</v>
       </c>
       <c r="T2">
-        <v>2.22</v>
+        <v>1.71</v>
       </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="W2">
-        <v>1.9</v>
+        <v>1.14</v>
       </c>
       <c r="X2">
-        <v>8.800000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="Y2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z2">
-        <v>29</v>
+        <v>970</v>
       </c>
       <c r="AA2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>970</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>1000</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>1.3</v>
+      </c>
+      <c r="AQ2">
         <v>11</v>
       </c>
-      <c r="AH2">
-        <v>24</v>
-      </c>
-      <c r="AI2">
-        <v>95</v>
-      </c>
-      <c r="AJ2">
-        <v>28</v>
-      </c>
-      <c r="AK2">
-        <v>29</v>
-      </c>
-      <c r="AL2">
-        <v>55</v>
-      </c>
-      <c r="AM2">
-        <v>180</v>
-      </c>
-      <c r="AN2">
-        <v>27</v>
-      </c>
-      <c r="AO2">
-        <v>110</v>
-      </c>
-      <c r="AP2">
-        <v>8.6</v>
-      </c>
-      <c r="AQ2">
-        <v>10.5</v>
-      </c>
       <c r="AR2">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AS2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="AT2">
         <v>6.6</v>
       </c>
       <c r="AU2">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="AV2">
-        <v>16.5</v>
+        <v>240</v>
       </c>
       <c r="AW2">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AX2">
-        <v>10.5</v>
+        <v>55</v>
       </c>
       <c r="AY2">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="BA2">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="BB2">
-        <v>24</v>
+        <v>310</v>
       </c>
       <c r="BC2">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="BD2">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="BE2">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="BF2">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BG2">
-        <v>95</v>
+        <v>13</v>
       </c>
       <c r="BH2">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>162</v>
@@ -1338,226 +1338,226 @@
         <v>136</v>
       </c>
       <c r="F3">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="G3">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="H3">
+        <v>1000</v>
+      </c>
+      <c r="I3">
+        <v>1000</v>
+      </c>
+      <c r="J3">
+        <v>200</v>
+      </c>
+      <c r="K3">
+        <v>390</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1.31</v>
+      </c>
+      <c r="Q3">
+        <v>4</v>
+      </c>
+      <c r="R3">
+        <v>1.02</v>
+      </c>
+      <c r="S3">
+        <v>30</v>
+      </c>
+      <c r="T3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="U3">
+        <v>1.09</v>
+      </c>
+      <c r="V3">
+        <v>1.01</v>
+      </c>
+      <c r="W3">
+        <v>160</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>1000</v>
+      </c>
+      <c r="AD3">
+        <v>1000</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1.33</v>
+      </c>
+      <c r="AG3">
+        <v>17.5</v>
+      </c>
+      <c r="AH3">
+        <v>540</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>8.4</v>
+      </c>
+      <c r="AK3">
+        <v>170</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>190</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>16</v>
+      </c>
+      <c r="AQ3">
         <v>11.5</v>
       </c>
-      <c r="I3">
-        <v>12</v>
-      </c>
-      <c r="J3">
-        <v>4.7</v>
-      </c>
-      <c r="K3">
-        <v>4.8</v>
-      </c>
-      <c r="L3">
-        <v>1.51</v>
-      </c>
-      <c r="M3">
-        <v>1.09</v>
-      </c>
-      <c r="N3">
-        <v>3.15</v>
-      </c>
-      <c r="O3">
-        <v>1.45</v>
-      </c>
-      <c r="P3">
-        <v>1.73</v>
-      </c>
-      <c r="Q3">
-        <v>2.34</v>
-      </c>
-      <c r="R3">
-        <v>1.27</v>
-      </c>
-      <c r="S3">
-        <v>4.6</v>
-      </c>
-      <c r="T3">
-        <v>2.82</v>
-      </c>
-      <c r="U3">
-        <v>1.53</v>
-      </c>
-      <c r="V3">
-        <v>1.09</v>
-      </c>
-      <c r="W3">
-        <v>3.3</v>
-      </c>
-      <c r="X3">
+      <c r="AR3">
+        <v>11.5</v>
+      </c>
+      <c r="AS3">
+        <v>11.5</v>
+      </c>
+      <c r="AT3">
+        <v>11.5</v>
+      </c>
+      <c r="AU3">
+        <v>16</v>
+      </c>
+      <c r="AV3">
+        <v>11.5</v>
+      </c>
+      <c r="AW3">
+        <v>11.5</v>
+      </c>
+      <c r="AX3">
+        <v>1.28</v>
+      </c>
+      <c r="AY3">
         <v>11</v>
       </c>
-      <c r="Y3">
-        <v>26</v>
-      </c>
-      <c r="Z3">
-        <v>130</v>
-      </c>
-      <c r="AA3">
-        <v>710</v>
-      </c>
-      <c r="AB3">
-        <v>5.6</v>
-      </c>
-      <c r="AC3">
+      <c r="AZ3">
+        <v>120</v>
+      </c>
+      <c r="BA3">
         <v>11</v>
       </c>
-      <c r="AD3">
-        <v>55</v>
-      </c>
-      <c r="AE3">
-        <v>410</v>
-      </c>
-      <c r="AF3">
+      <c r="BB3">
         <v>6.4</v>
       </c>
-      <c r="AG3">
+      <c r="BC3">
+        <v>48</v>
+      </c>
+      <c r="BD3">
+        <v>28</v>
+      </c>
+      <c r="BE3">
+        <v>16</v>
+      </c>
+      <c r="BF3">
+        <v>48</v>
+      </c>
+      <c r="BG3">
         <v>11.5</v>
       </c>
-      <c r="AH3">
-        <v>46</v>
-      </c>
-      <c r="AI3">
-        <v>330</v>
-      </c>
-      <c r="AJ3">
-        <v>11</v>
-      </c>
-      <c r="AK3">
-        <v>19.5</v>
-      </c>
-      <c r="AL3">
-        <v>75</v>
-      </c>
-      <c r="AM3">
-        <v>490</v>
-      </c>
-      <c r="AN3">
-        <v>9.6</v>
-      </c>
-      <c r="AO3">
-        <v>690</v>
-      </c>
-      <c r="AP3">
-        <v>10.5</v>
-      </c>
-      <c r="AQ3">
-        <v>22</v>
-      </c>
-      <c r="AR3">
-        <v>46</v>
-      </c>
-      <c r="AS3">
-        <v>110</v>
-      </c>
-      <c r="AT3">
-        <v>5.3</v>
-      </c>
-      <c r="AU3">
-        <v>10.5</v>
-      </c>
-      <c r="AV3">
-        <v>42</v>
-      </c>
-      <c r="AW3">
-        <v>100</v>
-      </c>
-      <c r="AX3">
-        <v>6</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>40</v>
-      </c>
-      <c r="BA3">
-        <v>60</v>
-      </c>
-      <c r="BB3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC3">
-        <v>17.5</v>
-      </c>
-      <c r="BD3">
-        <v>65</v>
-      </c>
-      <c r="BE3">
-        <v>90</v>
-      </c>
-      <c r="BF3">
-        <v>9</v>
-      </c>
-      <c r="BG3">
-        <v>130</v>
-      </c>
       <c r="BH3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>162</v>
@@ -1580,226 +1580,226 @@
         <v>137</v>
       </c>
       <c r="F4">
-        <v>2.06</v>
+        <v>1.21</v>
       </c>
       <c r="G4">
-        <v>2.1</v>
+        <v>1.22</v>
       </c>
       <c r="H4">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>48</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>6.4</v>
       </c>
       <c r="K4">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
       <c r="L4">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.94</v>
+        <v>2.5</v>
       </c>
       <c r="O4">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="P4">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
-        <v>2.48</v>
+        <v>4.8</v>
       </c>
       <c r="R4">
-        <v>1.23</v>
+        <v>1.03</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="T4">
-        <v>2.14</v>
+        <v>3.5</v>
       </c>
       <c r="U4">
-        <v>1.83</v>
+        <v>1.35</v>
       </c>
       <c r="V4">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="W4">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="X4">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="AC4">
         <v>7.6</v>
       </c>
       <c r="AD4">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AE4">
+        <v>1000</v>
+      </c>
+      <c r="AF4">
+        <v>4.7</v>
+      </c>
+      <c r="AG4">
+        <v>990</v>
+      </c>
+      <c r="AH4">
+        <v>990</v>
+      </c>
+      <c r="AI4">
+        <v>1000</v>
+      </c>
+      <c r="AJ4">
+        <v>970</v>
+      </c>
+      <c r="AK4">
+        <v>1000</v>
+      </c>
+      <c r="AL4">
+        <v>1000</v>
+      </c>
+      <c r="AM4">
+        <v>1000</v>
+      </c>
+      <c r="AN4">
+        <v>1000</v>
+      </c>
+      <c r="AO4">
+        <v>1000</v>
+      </c>
+      <c r="AP4">
+        <v>5</v>
+      </c>
+      <c r="AQ4">
+        <v>5</v>
+      </c>
+      <c r="AR4">
+        <v>5</v>
+      </c>
+      <c r="AS4">
+        <v>5</v>
+      </c>
+      <c r="AT4">
+        <v>2.24</v>
+      </c>
+      <c r="AU4">
+        <v>6.4</v>
+      </c>
+      <c r="AV4">
+        <v>40</v>
+      </c>
+      <c r="AW4">
+        <v>16.5</v>
+      </c>
+      <c r="AX4">
+        <v>4</v>
+      </c>
+      <c r="AY4">
+        <v>12</v>
+      </c>
+      <c r="AZ4">
+        <v>44</v>
+      </c>
+      <c r="BA4">
         <v>85</v>
       </c>
-      <c r="AF4">
-        <v>11.5</v>
-      </c>
-      <c r="AG4">
-        <v>10.5</v>
-      </c>
-      <c r="AH4">
-        <v>26</v>
-      </c>
-      <c r="AI4">
+      <c r="BB4">
+        <v>15</v>
+      </c>
+      <c r="BC4">
+        <v>17.5</v>
+      </c>
+      <c r="BD4">
         <v>90</v>
       </c>
-      <c r="AJ4">
-        <v>27</v>
-      </c>
-      <c r="AK4">
-        <v>27</v>
-      </c>
-      <c r="AL4">
-        <v>55</v>
-      </c>
-      <c r="AM4">
-        <v>180</v>
-      </c>
-      <c r="AN4">
-        <v>25</v>
-      </c>
-      <c r="AO4">
-        <v>190</v>
-      </c>
-      <c r="AP4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ4">
-        <v>11.5</v>
-      </c>
-      <c r="AR4">
-        <v>29</v>
-      </c>
-      <c r="AS4">
-        <v>17</v>
-      </c>
-      <c r="AT4">
-        <v>6.2</v>
-      </c>
-      <c r="AU4">
-        <v>7</v>
-      </c>
-      <c r="AV4">
-        <v>17</v>
-      </c>
-      <c r="AW4">
-        <v>48</v>
-      </c>
-      <c r="AX4">
-        <v>10</v>
-      </c>
-      <c r="AY4">
-        <v>10</v>
-      </c>
-      <c r="AZ4">
-        <v>22</v>
-      </c>
-      <c r="BA4">
-        <v>17</v>
-      </c>
-      <c r="BB4">
-        <v>22</v>
-      </c>
-      <c r="BC4">
-        <v>24</v>
-      </c>
-      <c r="BD4">
-        <v>44</v>
-      </c>
       <c r="BE4">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BF4">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="BG4">
-        <v>90</v>
+        <v>5.1</v>
       </c>
       <c r="BH4">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>162</v>
@@ -1822,226 +1822,226 @@
         <v>138</v>
       </c>
       <c r="F5">
-        <v>1.48</v>
+        <v>1.22</v>
       </c>
       <c r="G5">
-        <v>1.52</v>
+        <v>1.23</v>
       </c>
       <c r="H5">
-        <v>6.6</v>
+        <v>22</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="J5">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="K5">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="L5">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>5.8</v>
       </c>
       <c r="O5">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>2.62</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="R5">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="S5">
-        <v>2.42</v>
+        <v>3.75</v>
       </c>
       <c r="T5">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="U5">
-        <v>2.16</v>
+        <v>1.73</v>
       </c>
       <c r="V5">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="W5">
-        <v>2.92</v>
+        <v>5.2</v>
       </c>
       <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>6.4</v>
+      </c>
+      <c r="AC5">
+        <v>11</v>
+      </c>
+      <c r="AD5">
+        <v>42</v>
+      </c>
+      <c r="AE5">
+        <v>260</v>
+      </c>
+      <c r="AF5">
+        <v>5.4</v>
+      </c>
+      <c r="AG5">
+        <v>8.6</v>
+      </c>
+      <c r="AH5">
         <v>34</v>
       </c>
-      <c r="Y5">
-        <v>32</v>
-      </c>
-      <c r="Z5">
+      <c r="AI5">
+        <v>220</v>
+      </c>
+      <c r="AJ5">
+        <v>8.4</v>
+      </c>
+      <c r="AK5">
+        <v>18</v>
+      </c>
+      <c r="AL5">
         <v>65</v>
       </c>
-      <c r="AA5">
-        <v>210</v>
-      </c>
-      <c r="AB5">
-        <v>14.5</v>
-      </c>
-      <c r="AC5">
-        <v>12.5</v>
-      </c>
-      <c r="AD5">
-        <v>32</v>
-      </c>
-      <c r="AE5">
-        <v>100</v>
-      </c>
-      <c r="AF5">
+      <c r="AM5">
+        <v>380</v>
+      </c>
+      <c r="AN5">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
         <v>11.5</v>
-      </c>
-      <c r="AG5">
-        <v>12</v>
-      </c>
-      <c r="AH5">
-        <v>25</v>
-      </c>
-      <c r="AI5">
-        <v>85</v>
-      </c>
-      <c r="AJ5">
-        <v>14.5</v>
-      </c>
-      <c r="AK5">
-        <v>15</v>
-      </c>
-      <c r="AL5">
-        <v>34</v>
-      </c>
-      <c r="AM5">
-        <v>110</v>
-      </c>
-      <c r="AN5">
-        <v>5.7</v>
-      </c>
-      <c r="AO5">
-        <v>110</v>
-      </c>
-      <c r="AP5">
-        <v>6.2</v>
       </c>
       <c r="AQ5">
         <v>24</v>
       </c>
       <c r="AR5">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="AS5">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AT5">
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AV5">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="AW5">
-        <v>6.8</v>
+        <v>160</v>
       </c>
       <c r="AX5">
-        <v>9.199999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="AY5">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AZ5">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="BA5">
-        <v>6.6</v>
+        <v>130</v>
       </c>
       <c r="BB5">
-        <v>11.5</v>
+        <v>7.6</v>
       </c>
       <c r="BC5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD5">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="BE5">
-        <v>6.8</v>
+        <v>200</v>
       </c>
       <c r="BF5">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BG5">
-        <v>6.8</v>
+        <v>290</v>
       </c>
       <c r="BH5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>162</v>
@@ -2067,223 +2067,223 @@
         <v>6.6</v>
       </c>
       <c r="G6">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H6">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="I6">
+        <v>1.67</v>
+      </c>
+      <c r="J6">
+        <v>3.45</v>
+      </c>
+      <c r="K6">
+        <v>4.3</v>
+      </c>
+      <c r="L6">
+        <v>1.5</v>
+      </c>
+      <c r="M6">
+        <v>1.1</v>
+      </c>
+      <c r="N6">
+        <v>2.72</v>
+      </c>
+      <c r="O6">
+        <v>1.44</v>
+      </c>
+      <c r="P6">
         <v>1.61</v>
       </c>
-      <c r="J6">
+      <c r="Q6">
+        <v>2.18</v>
+      </c>
+      <c r="R6">
+        <v>1.24</v>
+      </c>
+      <c r="S6">
+        <v>3.9</v>
+      </c>
+      <c r="T6">
+        <v>2.32</v>
+      </c>
+      <c r="U6">
+        <v>1.63</v>
+      </c>
+      <c r="V6">
+        <v>2.48</v>
+      </c>
+      <c r="W6">
+        <v>1.12</v>
+      </c>
+      <c r="X6">
+        <v>11</v>
+      </c>
+      <c r="Y6">
+        <v>6.2</v>
+      </c>
+      <c r="Z6">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA6">
+        <v>15.5</v>
+      </c>
+      <c r="AB6">
+        <v>21</v>
+      </c>
+      <c r="AC6">
+        <v>9.4</v>
+      </c>
+      <c r="AD6">
+        <v>11.5</v>
+      </c>
+      <c r="AE6">
+        <v>23</v>
+      </c>
+      <c r="AF6">
+        <v>95</v>
+      </c>
+      <c r="AG6">
+        <v>36</v>
+      </c>
+      <c r="AH6">
+        <v>34</v>
+      </c>
+      <c r="AI6">
+        <v>80</v>
+      </c>
+      <c r="AJ6">
+        <v>410</v>
+      </c>
+      <c r="AK6">
+        <v>220</v>
+      </c>
+      <c r="AL6">
+        <v>210</v>
+      </c>
+      <c r="AM6">
+        <v>580</v>
+      </c>
+      <c r="AN6">
+        <v>410</v>
+      </c>
+      <c r="AO6">
+        <v>14</v>
+      </c>
+      <c r="AP6">
+        <v>5.2</v>
+      </c>
+      <c r="AQ6">
         <v>3.8</v>
       </c>
-      <c r="K6">
-        <v>4.7</v>
-      </c>
-      <c r="L6">
-        <v>1.41</v>
-      </c>
-      <c r="M6">
-        <v>1.07</v>
-      </c>
-      <c r="N6">
-        <v>3.15</v>
-      </c>
-      <c r="O6">
-        <v>1.33</v>
-      </c>
-      <c r="P6">
-        <v>1.82</v>
-      </c>
-      <c r="Q6">
-        <v>1.9</v>
-      </c>
-      <c r="R6">
-        <v>1.32</v>
-      </c>
-      <c r="S6">
-        <v>3.2</v>
-      </c>
-      <c r="T6">
-        <v>2.06</v>
-      </c>
-      <c r="U6">
-        <v>1.76</v>
-      </c>
-      <c r="V6">
-        <v>2.62</v>
-      </c>
-      <c r="W6">
-        <v>1.13</v>
-      </c>
-      <c r="X6">
-        <v>16.5</v>
-      </c>
-      <c r="Y6">
-        <v>7.6</v>
-      </c>
-      <c r="Z6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA6">
-        <v>14.5</v>
-      </c>
-      <c r="AB6">
-        <v>23</v>
-      </c>
-      <c r="AC6">
-        <v>10.5</v>
-      </c>
-      <c r="AD6">
-        <v>10.5</v>
-      </c>
-      <c r="AE6">
-        <v>18.5</v>
-      </c>
-      <c r="AF6">
-        <v>160</v>
-      </c>
-      <c r="AG6">
-        <v>32</v>
-      </c>
-      <c r="AH6">
-        <v>27</v>
-      </c>
-      <c r="AI6">
-        <v>46</v>
-      </c>
-      <c r="AJ6">
-        <v>330</v>
-      </c>
-      <c r="AK6">
-        <v>160</v>
-      </c>
-      <c r="AL6">
-        <v>150</v>
-      </c>
-      <c r="AM6">
-        <v>200</v>
-      </c>
-      <c r="AN6">
-        <v>250</v>
-      </c>
-      <c r="AO6">
-        <v>10</v>
-      </c>
-      <c r="AP6">
-        <v>5.9</v>
-      </c>
-      <c r="AQ6">
-        <v>4.1</v>
-      </c>
       <c r="AR6">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AS6">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
         <v>6.6</v>
       </c>
       <c r="AU6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV6">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AX6">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AY6">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AZ6">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BA6">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB6">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BC6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BD6">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF6">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG6">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BH6">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="BI6">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="BJ6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BN6">
         <v>11.5</v>
       </c>
       <c r="BO6">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BP6">
         <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="BR6">
         <v>1000</v>
       </c>
       <c r="BS6">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="BT6">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BU6">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="BV6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BW6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BX6">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BY6">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="BZ6">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="CA6">
-        <v>7.2</v>
+        <v>2.28</v>
       </c>
       <c r="CB6" t="s">
         <v>162</v>
@@ -2312,7 +2312,7 @@
         <v>3.8</v>
       </c>
       <c r="H7">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I7">
         <v>3.3</v>
@@ -2333,22 +2333,22 @@
         <v>2.12</v>
       </c>
       <c r="O7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="P7">
         <v>1.36</v>
       </c>
       <c r="Q7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R7">
         <v>1.12</v>
       </c>
       <c r="S7">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="T7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="U7">
         <v>1.58</v>
@@ -2357,7 +2357,7 @@
         <v>1.43</v>
       </c>
       <c r="W7">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X7">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>75</v>
       </c>
       <c r="BS7">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="BT7">
         <v>6.4</v>
@@ -2519,13 +2519,13 @@
         <v>70</v>
       </c>
       <c r="BY7">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="BZ7">
         <v>80</v>
       </c>
       <c r="CA7">
-        <v>1.86</v>
+        <v>6</v>
       </c>
       <c r="CB7" t="s">
         <v>162</v>
@@ -2548,7 +2548,7 @@
         <v>141</v>
       </c>
       <c r="F8">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="G8">
         <v>3.95</v>
@@ -2587,19 +2587,19 @@
         <v>1.19</v>
       </c>
       <c r="S8">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="T8">
         <v>2.04</v>
       </c>
       <c r="U8">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V8">
         <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -2638,7 +2638,7 @@
         <v>500</v>
       </c>
       <c r="AJ8">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK8">
         <v>220</v>
@@ -2790,10 +2790,10 @@
         <v>142</v>
       </c>
       <c r="F9">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G9">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H9">
         <v>3.9</v>
@@ -2811,49 +2811,49 @@
         <v>1.7</v>
       </c>
       <c r="M9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N9">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="O9">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="P9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R9">
         <v>1.13</v>
       </c>
       <c r="S9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="U9">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="V9">
         <v>1.32</v>
       </c>
       <c r="W9">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Y9">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AB9">
         <v>6.4</v>
@@ -2862,10 +2862,10 @@
         <v>7.2</v>
       </c>
       <c r="AD9">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="AF9">
         <v>13</v>
@@ -2880,34 +2880,34 @@
         <v>490</v>
       </c>
       <c r="AJ9">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK9">
         <v>100</v>
       </c>
       <c r="AL9">
-        <v>200</v>
+        <v>95</v>
       </c>
       <c r="AM9">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN9">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AO9">
         <v>150</v>
       </c>
       <c r="AP9">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AQ9">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR9">
         <v>22</v>
       </c>
       <c r="AS9">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AT9">
         <v>5.7</v>
@@ -2931,13 +2931,13 @@
         <v>27</v>
       </c>
       <c r="BA9">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB9">
         <v>32</v>
       </c>
       <c r="BC9">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="BD9">
         <v>38</v>
@@ -2946,7 +2946,7 @@
         <v>110</v>
       </c>
       <c r="BF9">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BG9">
         <v>40</v>
@@ -3310,7 +3310,7 @@
         <v>1.39</v>
       </c>
       <c r="R11">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="S11">
         <v>1.96</v>
@@ -3522,7 +3522,7 @@
         <v>3.5</v>
       </c>
       <c r="H12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I12">
         <v>2.22</v>
@@ -3558,7 +3558,7 @@
         <v>1.66</v>
       </c>
       <c r="T12">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="U12">
         <v>3.35</v>
@@ -3585,13 +3585,13 @@
         <v>85</v>
       </c>
       <c r="AC12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AD12">
         <v>14.5</v>
       </c>
       <c r="AE12">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AF12">
         <v>100</v>
@@ -3624,7 +3624,7 @@
         <v>6.2</v>
       </c>
       <c r="AP12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ12">
         <v>20</v>
@@ -3633,10 +3633,10 @@
         <v>19</v>
       </c>
       <c r="AS12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU12">
         <v>11</v>
@@ -3648,7 +3648,7 @@
         <v>14.5</v>
       </c>
       <c r="AX12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY12">
         <v>13</v>
@@ -3660,7 +3660,7 @@
         <v>15.5</v>
       </c>
       <c r="BB12">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC12">
         <v>21</v>
@@ -3669,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="BE12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF12">
         <v>9.6</v>
@@ -4009,10 +4009,10 @@
         <v>2.5</v>
       </c>
       <c r="I14">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="J14">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K14">
         <v>3.3</v>
@@ -4021,7 +4021,7 @@
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N14">
         <v>2.96</v>
@@ -4030,136 +4030,136 @@
         <v>1.42</v>
       </c>
       <c r="P14">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R14">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S14">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="T14">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="U14">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="V14">
         <v>1.57</v>
       </c>
       <c r="W14">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X14">
-        <v>950</v>
+        <v>11</v>
       </c>
       <c r="Y14">
-        <v>950</v>
+        <v>9.4</v>
       </c>
       <c r="Z14">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AA14">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB14">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AC14">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD14">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AE14">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AF14">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG14">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AH14">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AI14">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AK14">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AM14">
         <v>500</v>
       </c>
       <c r="AN14">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AO14">
-        <v>500</v>
+        <v>34</v>
       </c>
       <c r="AP14">
-        <v>1.24</v>
+        <v>9</v>
       </c>
       <c r="AQ14">
-        <v>1.21</v>
+        <v>7.6</v>
       </c>
       <c r="AR14">
-        <v>1.22</v>
+        <v>13.5</v>
       </c>
       <c r="AS14">
-        <v>1.24</v>
+        <v>7.4</v>
       </c>
       <c r="AT14">
-        <v>1.22</v>
+        <v>9.4</v>
       </c>
       <c r="AU14">
-        <v>1.14</v>
+        <v>6</v>
       </c>
       <c r="AV14">
-        <v>1.22</v>
+        <v>10</v>
       </c>
       <c r="AW14">
-        <v>1.23</v>
+        <v>7</v>
       </c>
       <c r="AX14">
-        <v>1.23</v>
+        <v>18.5</v>
       </c>
       <c r="AY14">
-        <v>1.23</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14">
-        <v>1.22</v>
+        <v>14</v>
       </c>
       <c r="BA14">
-        <v>1.24</v>
+        <v>7.6</v>
       </c>
       <c r="BB14">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="BC14">
-        <v>1.24</v>
+        <v>7.6</v>
       </c>
       <c r="BD14">
-        <v>1.24</v>
+        <v>7.8</v>
       </c>
       <c r="BE14">
-        <v>1.24</v>
+        <v>8.4</v>
       </c>
       <c r="BF14">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4266,7 +4266,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
         <v>1.03</v>
@@ -4281,7 +4281,7 @@
         <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
         <v>1.11</v>
@@ -5133,7 +5133,7 @@
         <v>5.4</v>
       </c>
       <c r="BI18">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ18">
         <v>8.6</v>
@@ -5213,16 +5213,16 @@
         <v>2.4</v>
       </c>
       <c r="G19">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H19">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I19">
         <v>2.88</v>
       </c>
       <c r="J19">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="K19">
         <v>4.2</v>
@@ -5240,7 +5240,7 @@
         <v>1.21</v>
       </c>
       <c r="P19">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q19">
         <v>1.62</v>
@@ -5261,19 +5261,19 @@
         <v>1.53</v>
       </c>
       <c r="W19">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X19">
         <v>26</v>
       </c>
       <c r="Y19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z19">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AA19">
-        <v>440</v>
+        <v>900</v>
       </c>
       <c r="AB19">
         <v>15.5</v>
@@ -5291,7 +5291,7 @@
         <v>23</v>
       </c>
       <c r="AG19">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH19">
         <v>15</v>
@@ -5300,7 +5300,7 @@
         <v>36</v>
       </c>
       <c r="AJ19">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK19">
         <v>28</v>
@@ -5312,7 +5312,7 @@
         <v>150</v>
       </c>
       <c r="AN19">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AO19">
         <v>19</v>
@@ -5327,7 +5327,7 @@
         <v>17.5</v>
       </c>
       <c r="AS19">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT19">
         <v>12.5</v>
@@ -5363,7 +5363,7 @@
         <v>13</v>
       </c>
       <c r="BE19">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF19">
         <v>11.5</v>
@@ -5378,58 +5378,58 @@
         <v>3.8</v>
       </c>
       <c r="BJ19">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK19">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BN19">
         <v>5.8</v>
       </c>
       <c r="BO19">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP19">
         <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BR19">
         <v>1000</v>
       </c>
       <c r="BS19">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BT19">
         <v>6.6</v>
       </c>
       <c r="BU19">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV19">
         <v>1000</v>
       </c>
       <c r="BW19">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BX19">
         <v>1000</v>
       </c>
       <c r="BY19">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BZ19">
         <v>23</v>
       </c>
       <c r="CA19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB19" t="s">
         <v>162</v>
@@ -5718,10 +5718,10 @@
         <v>1.17</v>
       </c>
       <c r="N21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O21">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="P21">
         <v>1.43</v>
@@ -5963,19 +5963,19 @@
         <v>2.68</v>
       </c>
       <c r="O22">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P22">
         <v>1.62</v>
       </c>
       <c r="Q22">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R22">
         <v>1.23</v>
       </c>
       <c r="S22">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="T22">
         <v>2.06</v>
@@ -6181,19 +6181,19 @@
         <v>3.35</v>
       </c>
       <c r="G23">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="H23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I23">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="J23">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K23">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L23">
         <v>1.37</v>
@@ -6205,10 +6205,10 @@
         <v>3.2</v>
       </c>
       <c r="O23">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P23">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q23">
         <v>2.1</v>
@@ -6220,16 +6220,16 @@
         <v>3.85</v>
       </c>
       <c r="T23">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="U23">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="V23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W23">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="X23">
         <v>12.5</v>
@@ -6247,7 +6247,7 @@
         <v>12.5</v>
       </c>
       <c r="AC23">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD23">
         <v>12.5</v>
@@ -6262,10 +6262,10 @@
         <v>15.5</v>
       </c>
       <c r="AH23">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ23">
         <v>65</v>
@@ -6280,7 +6280,7 @@
         <v>130</v>
       </c>
       <c r="AN23">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO23">
         <v>28</v>
@@ -6295,7 +6295,7 @@
         <v>12</v>
       </c>
       <c r="AS23">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT23">
         <v>10</v>
@@ -6307,7 +6307,7 @@
         <v>10</v>
       </c>
       <c r="AW23">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AX23">
         <v>19</v>
@@ -6319,22 +6319,22 @@
         <v>13.5</v>
       </c>
       <c r="BA23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB23">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BC23">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BD23">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BE23">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="BF23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG23">
         <v>19.5</v>
@@ -6435,10 +6435,10 @@
         <v>3.15</v>
       </c>
       <c r="K24">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L24">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="M24">
         <v>1.13</v>
@@ -6465,13 +6465,13 @@
         <v>2.2</v>
       </c>
       <c r="U24">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V24">
         <v>1.76</v>
       </c>
       <c r="W24">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X24">
         <v>8.6</v>
@@ -6540,7 +6540,7 @@
         <v>14.5</v>
       </c>
       <c r="AT24">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU24">
         <v>6.8</v>
@@ -6585,10 +6585,10 @@
         <v>2.66</v>
       </c>
       <c r="BI24">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="BJ24">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK24">
         <v>7</v>
@@ -6597,7 +6597,7 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="BN24">
         <v>7.2</v>
@@ -6609,37 +6609,37 @@
         <v>1000</v>
       </c>
       <c r="BQ24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BT24">
         <v>4.8</v>
       </c>
       <c r="BU24">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BV24">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BW24">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ24">
         <v>1000</v>
       </c>
       <c r="CA24">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="CB24" t="s">
         <v>162</v>
@@ -6665,7 +6665,7 @@
         <v>1.76</v>
       </c>
       <c r="G25">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H25">
         <v>5.5</v>
@@ -6674,25 +6674,25 @@
         <v>5.8</v>
       </c>
       <c r="J25">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K25">
         <v>3.95</v>
       </c>
       <c r="L25">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M25">
         <v>1.08</v>
       </c>
       <c r="N25">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O25">
         <v>1.35</v>
       </c>
       <c r="P25">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q25">
         <v>2.04</v>
@@ -6704,7 +6704,7 @@
         <v>3.7</v>
       </c>
       <c r="T25">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U25">
         <v>1.98</v>
@@ -6713,13 +6713,13 @@
         <v>1.21</v>
       </c>
       <c r="W25">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X25">
         <v>13.5</v>
       </c>
       <c r="Y25">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="Z25">
         <v>48</v>
@@ -6755,7 +6755,7 @@
         <v>19.5</v>
       </c>
       <c r="AK25">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL25">
         <v>44</v>
@@ -6791,7 +6791,7 @@
         <v>19</v>
       </c>
       <c r="AW25">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AX25">
         <v>9</v>
@@ -6904,82 +6904,82 @@
         <v>159</v>
       </c>
       <c r="F26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G26">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="H26">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I26">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J26">
         <v>3.65</v>
       </c>
       <c r="K26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L26">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M26">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N26">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P26">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
+        <v>2.06</v>
+      </c>
+      <c r="R26">
+        <v>1.34</v>
+      </c>
+      <c r="S26">
+        <v>3.7</v>
+      </c>
+      <c r="T26">
+        <v>1.89</v>
+      </c>
+      <c r="U26">
+        <v>2.06</v>
+      </c>
+      <c r="V26">
         <v>2</v>
-      </c>
-      <c r="R26">
-        <v>1.36</v>
-      </c>
-      <c r="S26">
-        <v>3.55</v>
-      </c>
-      <c r="T26">
-        <v>1.86</v>
-      </c>
-      <c r="U26">
-        <v>2.08</v>
-      </c>
-      <c r="V26">
-        <v>2.02</v>
       </c>
       <c r="W26">
         <v>1.28</v>
       </c>
       <c r="X26">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Y26">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z26">
         <v>11.5</v>
       </c>
       <c r="AA26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB26">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC26">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD26">
         <v>10.5</v>
       </c>
       <c r="AE26">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF26">
         <v>34</v>
@@ -6991,7 +6991,7 @@
         <v>19</v>
       </c>
       <c r="AI26">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ26">
         <v>100</v>
@@ -7000,22 +7000,22 @@
         <v>60</v>
       </c>
       <c r="AL26">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM26">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN26">
         <v>70</v>
       </c>
       <c r="AO26">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AP26">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ26">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR26">
         <v>10.5</v>
@@ -7027,7 +7027,7 @@
         <v>14</v>
       </c>
       <c r="AU26">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV26">
         <v>9.6</v>
@@ -7036,7 +7036,7 @@
         <v>18.5</v>
       </c>
       <c r="AX26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AY26">
         <v>16</v>
@@ -7045,10 +7045,10 @@
         <v>17.5</v>
       </c>
       <c r="BA26">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BB26">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC26">
         <v>48</v>
@@ -7060,16 +7060,16 @@
         <v>28</v>
       </c>
       <c r="BF26">
-        <v>50</v>
+        <v>15.5</v>
       </c>
       <c r="BG26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BH26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BI26">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="BJ26">
         <v>10.5</v>
@@ -7081,7 +7081,7 @@
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BN26">
         <v>7.4</v>
@@ -7093,13 +7093,13 @@
         <v>38</v>
       </c>
       <c r="BQ26">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR26">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BS26">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT26">
         <v>4.5</v>
@@ -7111,19 +7111,19 @@
         <v>14.5</v>
       </c>
       <c r="BW26">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX26">
         <v>30</v>
       </c>
       <c r="BY26">
+        <v>11.5</v>
+      </c>
+      <c r="BZ26">
+        <v>28</v>
+      </c>
+      <c r="CA26">
         <v>11</v>
-      </c>
-      <c r="BZ26">
-        <v>25</v>
-      </c>
-      <c r="CA26">
-        <v>10</v>
       </c>
       <c r="CB26" t="s">
         <v>162</v>
@@ -7170,19 +7170,19 @@
         <v>1.1</v>
       </c>
       <c r="N27">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O27">
         <v>1.45</v>
       </c>
       <c r="P27">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q27">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R27">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S27">
         <v>4.4</v>
@@ -7191,7 +7191,7 @@
         <v>2.02</v>
       </c>
       <c r="U27">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V27">
         <v>1.29</v>
@@ -7224,13 +7224,13 @@
         <v>80</v>
       </c>
       <c r="AF27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG27">
         <v>13.5</v>
       </c>
       <c r="AH27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI27">
         <v>95</v>
@@ -7248,7 +7248,7 @@
         <v>180</v>
       </c>
       <c r="AN27">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO27">
         <v>110</v>
@@ -7281,7 +7281,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY27">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ27">
         <v>15.5</v>
@@ -7311,7 +7311,7 @@
         <v>3.05</v>
       </c>
       <c r="BI27">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BJ27">
         <v>11</v>
@@ -7335,10 +7335,10 @@
         <v>15.5</v>
       </c>
       <c r="BQ27">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS27">
         <v>10</v>
@@ -7353,13 +7353,13 @@
         <v>1000</v>
       </c>
       <c r="BW27">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY27">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BZ27">
         <v>1000</v>
@@ -7427,7 +7427,7 @@
         <v>1.64</v>
       </c>
       <c r="S28">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T28">
         <v>1.74</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -463,7 +463,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 01:11:05</t>
+    <t>2026-07-29 03:18:48</t>
   </si>
 </sst>
 </file>
@@ -1057,10 +1057,10 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="G2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H2">
         <v>1.57</v>
@@ -1069,19 +1069,19 @@
         <v>1.67</v>
       </c>
       <c r="J2">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L2">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M2">
         <v>1.1</v>
       </c>
       <c r="N2">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="O2">
         <v>1.44</v>
@@ -1090,16 +1090,16 @@
         <v>1.61</v>
       </c>
       <c r="Q2">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R2">
         <v>1.23</v>
       </c>
       <c r="S2">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="T2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U2">
         <v>1.63</v>
@@ -1114,7 +1114,7 @@
         <v>11</v>
       </c>
       <c r="Y2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z2">
         <v>8.199999999999999</v>
@@ -1129,16 +1129,16 @@
         <v>9.4</v>
       </c>
       <c r="AD2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF2">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="AG2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH2">
         <v>34</v>
@@ -1147,10 +1147,10 @@
         <v>80</v>
       </c>
       <c r="AJ2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AK2">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AL2">
         <v>210</v>
@@ -1159,64 +1159,64 @@
         <v>700</v>
       </c>
       <c r="AN2">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AO2">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP2">
+        <v>9</v>
+      </c>
+      <c r="AQ2">
         <v>5.2</v>
       </c>
-      <c r="AQ2">
-        <v>3.8</v>
-      </c>
       <c r="AR2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS2">
         <v>6.6</v>
       </c>
       <c r="AT2">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU2">
         <v>4.8</v>
       </c>
       <c r="AV2">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AW2">
-        <v>6.8</v>
+        <v>18</v>
       </c>
       <c r="AX2">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AY2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BA2">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB2">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC2">
+        <v>9.4</v>
+      </c>
+      <c r="BD2">
+        <v>9.4</v>
+      </c>
+      <c r="BE2">
+        <v>9.4</v>
+      </c>
+      <c r="BF2">
         <v>9.6</v>
       </c>
-      <c r="BD2">
-        <v>9.6</v>
-      </c>
-      <c r="BE2">
-        <v>9.6</v>
-      </c>
-      <c r="BF2">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BG2">
-        <v>5.8</v>
+        <v>11.5</v>
       </c>
       <c r="BH2">
         <v>3.05</v>
@@ -1234,7 +1234,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="BN2">
         <v>11.5</v>
@@ -1246,22 +1246,22 @@
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BT2">
         <v>3.9</v>
       </c>
       <c r="BU2">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="BV2">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BW2">
         <v>6</v>
@@ -1270,13 +1270,13 @@
         <v>36</v>
       </c>
       <c r="BY2">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="BZ2">
         <v>29</v>
       </c>
       <c r="CA2">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,88 +1299,88 @@
         <v>127</v>
       </c>
       <c r="F3">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="G3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H3">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="I3">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>2.52</v>
+        <v>2.72</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="M3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="O3">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="P3">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Q3">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="R3">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="S3">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="T3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V3">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="W3">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="X3">
+        <v>7.6</v>
+      </c>
+      <c r="Y3">
         <v>8</v>
       </c>
-      <c r="Y3">
-        <v>8.4</v>
-      </c>
       <c r="Z3">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA3">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB3">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD3">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE3">
         <v>60</v>
       </c>
       <c r="AF3">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG3">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>32</v>
@@ -1389,10 +1389,10 @@
         <v>230</v>
       </c>
       <c r="AJ3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AK3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL3">
         <v>240</v>
@@ -1401,124 +1401,124 @@
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP3">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="AQ3">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="AR3">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="AS3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT3">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU3">
-        <v>3.25</v>
+        <v>5.7</v>
       </c>
       <c r="AV3">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AX3">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AY3">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AZ3">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="BA3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC3">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BD3">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE3">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BF3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BG3">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH3">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="BI3">
         <v>2.04</v>
       </c>
       <c r="BJ3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BK3">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.89</v>
+        <v>7.6</v>
       </c>
       <c r="BN3">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BO3">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="BP3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ3">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR3">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BS3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BT3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU3">
-        <v>3.25</v>
+        <v>4.3</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BX3">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BZ3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="CA3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CB3" t="s">
         <v>149</v>
@@ -1541,10 +1541,10 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G4">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H4">
         <v>2.34</v>
@@ -1553,19 +1553,19 @@
         <v>2.64</v>
       </c>
       <c r="J4">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="K4">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L4">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O4">
         <v>1.53</v>
@@ -1574,25 +1574,25 @@
         <v>1.52</v>
       </c>
       <c r="Q4">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R4">
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="T4">
         <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="V4">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W4">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -1619,7 +1619,7 @@
         <v>85</v>
       </c>
       <c r="AF4">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="AG4">
         <v>17</v>
@@ -1652,22 +1652,22 @@
         <v>4.6</v>
       </c>
       <c r="AQ4">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AR4">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AS4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AU4">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="AV4">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW4">
         <v>7.6</v>
@@ -1676,19 +1676,19 @@
         <v>7</v>
       </c>
       <c r="AY4">
-        <v>6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ4">
         <v>6.8</v>
       </c>
       <c r="BA4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB4">
         <v>8.6</v>
       </c>
       <c r="BC4">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BD4">
         <v>8.6</v>
@@ -1700,25 +1700,25 @@
         <v>8.6</v>
       </c>
       <c r="BG4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BI4">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ4">
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>2.2</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1730,13 +1730,13 @@
         <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>2.1</v>
+        <v>8.4</v>
       </c>
       <c r="BR4">
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1748,19 +1748,19 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>2.12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>2.14</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1786,7 +1786,7 @@
         <v>2.42</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
         <v>3.95</v>
@@ -1810,13 +1810,13 @@
         <v>2.24</v>
       </c>
       <c r="O5">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="P5">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="R5">
         <v>1.13</v>
@@ -1828,7 +1828,7 @@
         <v>2.52</v>
       </c>
       <c r="U5">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="V5">
         <v>1.32</v>
@@ -1837,7 +1837,7 @@
         <v>1.68</v>
       </c>
       <c r="X5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="Y5">
         <v>9.4</v>
@@ -1852,7 +1852,7 @@
         <v>6.2</v>
       </c>
       <c r="AC5">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>21</v>
@@ -1867,10 +1867,10 @@
         <v>14</v>
       </c>
       <c r="AH5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI5">
-        <v>530</v>
+        <v>490</v>
       </c>
       <c r="AJ5">
         <v>38</v>
@@ -1894,7 +1894,7 @@
         <v>5.9</v>
       </c>
       <c r="AQ5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR5">
         <v>22</v>
@@ -1903,13 +1903,13 @@
         <v>48</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW5">
         <v>70</v>
@@ -1933,7 +1933,7 @@
         <v>38</v>
       </c>
       <c r="BD5">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="BE5">
         <v>110</v>
@@ -1948,7 +1948,7 @@
         <v>2.42</v>
       </c>
       <c r="BI5">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="BJ5">
         <v>13.5</v>
@@ -1960,7 +1960,7 @@
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>5.2</v>
@@ -1969,7 +1969,7 @@
         <v>4.3</v>
       </c>
       <c r="BP5">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BQ5">
         <v>8.6</v>
@@ -2031,16 +2031,16 @@
         <v>1.32</v>
       </c>
       <c r="H6">
-        <v>6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="J6">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="K6">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>1.19</v>
@@ -2049,31 +2049,31 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P6">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="Q6">
         <v>1.31</v>
       </c>
       <c r="R6">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S6">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="T6">
-        <v>1.11</v>
+        <v>1.66</v>
       </c>
       <c r="U6">
-        <v>1.11</v>
+        <v>2.28</v>
       </c>
       <c r="V6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
         <v>4.1</v>
@@ -2109,13 +2109,13 @@
         <v>13</v>
       </c>
       <c r="AH6">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AJ6">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AK6">
         <v>14</v>
@@ -2127,34 +2127,34 @@
         <v>320</v>
       </c>
       <c r="AN6">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="AO6">
         <v>110</v>
       </c>
       <c r="AP6">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>7.2</v>
+        <v>23</v>
       </c>
       <c r="AR6">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AS6">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AT6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU6">
         <v>16</v>
       </c>
       <c r="AV6">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AW6">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX6">
         <v>10.5</v>
@@ -2163,13 +2163,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BA6">
-        <v>7.4</v>
+        <v>29</v>
       </c>
       <c r="BB6">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BC6">
         <v>11</v>
@@ -2178,10 +2178,10 @@
         <v>21</v>
       </c>
       <c r="BE6">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="BF6">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
@@ -2190,19 +2190,19 @@
         <v>6.4</v>
       </c>
       <c r="BI6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BJ6">
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2211,7 +2211,7 @@
         <v>3.55</v>
       </c>
       <c r="BP6">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BQ6">
         <v>5.4</v>
@@ -2220,25 +2220,25 @@
         <v>17</v>
       </c>
       <c r="BS6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT6">
         <v>14.5</v>
       </c>
       <c r="BU6">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX6">
         <v>55</v>
       </c>
       <c r="BY6">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BZ6">
         <v>7.2</v>
@@ -2267,22 +2267,22 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G7">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H7">
         <v>3.9</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J7">
         <v>4.4</v>
       </c>
       <c r="K7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
         <v>1.22</v>
@@ -2291,28 +2291,28 @@
         <v>1.02</v>
       </c>
       <c r="N7">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="O7">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P7">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="Q7">
         <v>1.4</v>
       </c>
       <c r="R7">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="S7">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="T7">
-        <v>1.11</v>
+        <v>1.44</v>
       </c>
       <c r="U7">
-        <v>1.11</v>
+        <v>2.78</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2330,7 +2330,7 @@
         <v>42</v>
       </c>
       <c r="AA7">
-        <v>290</v>
+        <v>160</v>
       </c>
       <c r="AB7">
         <v>21</v>
@@ -2339,94 +2339,94 @@
         <v>13</v>
       </c>
       <c r="AD7">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AE7">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF7">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AG7">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7">
         <v>22</v>
       </c>
       <c r="AK7">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL7">
         <v>24</v>
       </c>
       <c r="AM7">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AN7">
         <v>6.4</v>
       </c>
       <c r="AO7">
+        <v>22</v>
+      </c>
+      <c r="AP7">
+        <v>12</v>
+      </c>
+      <c r="AQ7">
+        <v>15.5</v>
+      </c>
+      <c r="AR7">
+        <v>21</v>
+      </c>
+      <c r="AS7">
+        <v>55</v>
+      </c>
+      <c r="AT7">
+        <v>12.5</v>
+      </c>
+      <c r="AU7">
+        <v>10.5</v>
+      </c>
+      <c r="AV7">
+        <v>15.5</v>
+      </c>
+      <c r="AW7">
+        <v>27</v>
+      </c>
+      <c r="AX7">
+        <v>12</v>
+      </c>
+      <c r="AY7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ7">
+        <v>13</v>
+      </c>
+      <c r="BA7">
+        <v>23</v>
+      </c>
+      <c r="BB7">
+        <v>16</v>
+      </c>
+      <c r="BC7">
+        <v>11.5</v>
+      </c>
+      <c r="BD7">
+        <v>17</v>
+      </c>
+      <c r="BE7">
         <v>24</v>
       </c>
-      <c r="AP7">
-        <v>6</v>
-      </c>
-      <c r="AQ7">
-        <v>5.7</v>
-      </c>
-      <c r="AR7">
-        <v>6</v>
-      </c>
-      <c r="AS7">
-        <v>6.4</v>
-      </c>
-      <c r="AT7">
-        <v>5.3</v>
-      </c>
-      <c r="AU7">
-        <v>6.4</v>
-      </c>
-      <c r="AV7">
-        <v>5.4</v>
-      </c>
-      <c r="AW7">
-        <v>6</v>
-      </c>
-      <c r="AX7">
-        <v>5.2</v>
-      </c>
-      <c r="AY7">
+      <c r="BF7">
         <v>4.6</v>
       </c>
-      <c r="AZ7">
-        <v>5</v>
-      </c>
-      <c r="BA7">
-        <v>6</v>
-      </c>
-      <c r="BB7">
-        <v>5.4</v>
-      </c>
-      <c r="BC7">
-        <v>5.2</v>
-      </c>
-      <c r="BD7">
-        <v>5.5</v>
-      </c>
-      <c r="BE7">
-        <v>6.2</v>
-      </c>
-      <c r="BF7">
-        <v>3.35</v>
-      </c>
       <c r="BG7">
-        <v>5.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH7">
         <v>5.6</v>
@@ -2438,55 +2438,55 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BK7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BL7">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BQ7">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BR7">
         <v>18.5</v>
       </c>
       <c r="BS7">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BU7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BW7">
         <v>7.4</v>
       </c>
       <c r="BX7">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BY7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ7">
         <v>11</v>
       </c>
       <c r="CA7">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="CB7" t="s">
         <v>149</v>
@@ -2512,10 +2512,10 @@
         <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I8">
         <v>2.16</v>
@@ -2524,7 +2524,7 @@
         <v>4.3</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L8">
         <v>1.2</v>
@@ -2533,43 +2533,43 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="O8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P8">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q8">
         <v>1.34</v>
       </c>
       <c r="R8">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S8">
         <v>1.84</v>
       </c>
       <c r="T8">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="U8">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V8">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="W8">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="Y8">
         <v>24</v>
       </c>
       <c r="Z8">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AA8">
         <v>32</v>
@@ -2584,151 +2584,151 @@
         <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="AG8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH8">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AI8">
         <v>23</v>
       </c>
       <c r="AJ8">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AK8">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="AL8">
+        <v>40</v>
+      </c>
+      <c r="AM8">
+        <v>55</v>
+      </c>
+      <c r="AN8">
+        <v>13</v>
+      </c>
+      <c r="AO8">
+        <v>6.8</v>
+      </c>
+      <c r="AP8">
+        <v>19</v>
+      </c>
+      <c r="AQ8">
+        <v>20</v>
+      </c>
+      <c r="AR8">
+        <v>19.5</v>
+      </c>
+      <c r="AS8">
+        <v>22</v>
+      </c>
+      <c r="AT8">
+        <v>23</v>
+      </c>
+      <c r="AU8">
+        <v>11.5</v>
+      </c>
+      <c r="AV8">
+        <v>10</v>
+      </c>
+      <c r="AW8">
+        <v>16</v>
+      </c>
+      <c r="AX8">
         <v>29</v>
       </c>
-      <c r="AM8">
-        <v>200</v>
-      </c>
-      <c r="AN8">
-        <v>14</v>
-      </c>
-      <c r="AO8">
-        <v>7.6</v>
-      </c>
-      <c r="AP8">
-        <v>6.6</v>
-      </c>
-      <c r="AQ8">
-        <v>5.8</v>
-      </c>
-      <c r="AR8">
-        <v>5.8</v>
-      </c>
-      <c r="AS8">
+      <c r="AY8">
+        <v>13.5</v>
+      </c>
+      <c r="AZ8">
+        <v>12</v>
+      </c>
+      <c r="BA8">
+        <v>18</v>
+      </c>
+      <c r="BB8">
+        <v>26</v>
+      </c>
+      <c r="BC8">
+        <v>21</v>
+      </c>
+      <c r="BD8">
+        <v>21</v>
+      </c>
+      <c r="BE8">
+        <v>30</v>
+      </c>
+      <c r="BF8">
+        <v>10.5</v>
+      </c>
+      <c r="BG8">
+        <v>5.7</v>
+      </c>
+      <c r="BH8">
         <v>6.2</v>
       </c>
-      <c r="AT8">
-        <v>6</v>
-      </c>
-      <c r="AU8">
-        <v>4.9</v>
-      </c>
-      <c r="AV8">
-        <v>4.9</v>
-      </c>
-      <c r="AW8">
-        <v>5.5</v>
-      </c>
-      <c r="AX8">
-        <v>6.2</v>
-      </c>
-      <c r="AY8">
-        <v>5.4</v>
-      </c>
-      <c r="AZ8">
-        <v>5.2</v>
-      </c>
-      <c r="BA8">
-        <v>5.8</v>
-      </c>
-      <c r="BB8">
-        <v>6.8</v>
-      </c>
-      <c r="BC8">
-        <v>6</v>
-      </c>
-      <c r="BD8">
-        <v>6</v>
-      </c>
-      <c r="BE8">
-        <v>6.4</v>
-      </c>
-      <c r="BF8">
-        <v>4.9</v>
-      </c>
-      <c r="BG8">
-        <v>5.5</v>
-      </c>
-      <c r="BH8">
-        <v>1000</v>
-      </c>
       <c r="BI8">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK8">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BP8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ8">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS8">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW8">
-        <v>1.04</v>
+        <v>5.7</v>
       </c>
       <c r="BX8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="BY8">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BZ8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA8">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="s">
         <v>149</v>
@@ -2751,22 +2751,22 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="G9">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="H9">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I9">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="J9">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K9">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>1.26</v>
@@ -2775,202 +2775,202 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="O9">
         <v>1.17</v>
       </c>
       <c r="P9">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="Q9">
         <v>1.51</v>
       </c>
       <c r="R9">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T9">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="U9">
-        <v>1.11</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W9">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="X9">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Y9">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="Z9">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA9">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9">
-        <v>950</v>
+        <v>14</v>
       </c>
       <c r="AC9">
-        <v>950</v>
+        <v>12</v>
       </c>
       <c r="AD9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AF9">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="AG9">
-        <v>950</v>
+        <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>950</v>
+        <v>18</v>
       </c>
       <c r="AI9">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ9">
-        <v>900</v>
+        <v>19</v>
       </c>
       <c r="AK9">
-        <v>120</v>
+        <v>16.5</v>
       </c>
       <c r="AL9">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="AM9">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN9">
-        <v>60</v>
+        <v>6.8</v>
       </c>
       <c r="AO9">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AP9">
-        <v>1.19</v>
+        <v>21</v>
       </c>
       <c r="AQ9">
-        <v>1.19</v>
+        <v>19.5</v>
       </c>
       <c r="AR9">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="AS9">
-        <v>1.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AU9">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV9">
-        <v>1.19</v>
+        <v>15.5</v>
       </c>
       <c r="AW9">
-        <v>1.19</v>
+        <v>7.6</v>
       </c>
       <c r="AX9">
-        <v>1.16</v>
+        <v>10</v>
       </c>
       <c r="AY9">
-        <v>1.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>1.18</v>
+        <v>13</v>
       </c>
       <c r="BA9">
-        <v>1.19</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
-        <v>1.18</v>
+        <v>13.5</v>
       </c>
       <c r="BC9">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="BD9">
-        <v>1.18</v>
+        <v>19</v>
       </c>
       <c r="BE9">
-        <v>1.19</v>
+        <v>7.8</v>
       </c>
       <c r="BF9">
-        <v>1.17</v>
+        <v>5.1</v>
       </c>
       <c r="BG9">
-        <v>1.55</v>
+        <v>7.2</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI9">
-        <v>1.04</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO9">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BS9">
-        <v>1.04</v>
+        <v>6.8</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU9">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA9">
-        <v>1.04</v>
+        <v>5.6</v>
       </c>
       <c r="CB9" t="s">
         <v>149</v>
@@ -2993,25 +2993,25 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G10">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H10">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J10">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L10">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M10">
         <v>1.1</v>
@@ -3023,28 +3023,28 @@
         <v>1.42</v>
       </c>
       <c r="P10">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q10">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S10">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T10">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U10">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V10">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X10">
         <v>11</v>
@@ -3065,37 +3065,37 @@
         <v>7.4</v>
       </c>
       <c r="AD10">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE10">
         <v>34</v>
       </c>
       <c r="AF10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG10">
         <v>15.5</v>
       </c>
       <c r="AH10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI10">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ10">
         <v>65</v>
       </c>
       <c r="AK10">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL10">
+        <v>60</v>
+      </c>
+      <c r="AM10">
+        <v>580</v>
+      </c>
+      <c r="AN10">
         <v>65</v>
-      </c>
-      <c r="AM10">
-        <v>500</v>
-      </c>
-      <c r="AN10">
-        <v>55</v>
       </c>
       <c r="AO10">
         <v>32</v>
@@ -3110,7 +3110,7 @@
         <v>13.5</v>
       </c>
       <c r="AS10">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT10">
         <v>9.4</v>
@@ -3122,7 +3122,7 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AX10">
         <v>18.5</v>
@@ -3131,82 +3131,82 @@
         <v>12.5</v>
       </c>
       <c r="AZ10">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA10">
-        <v>7.8</v>
+        <v>36</v>
       </c>
       <c r="BB10">
+        <v>21</v>
+      </c>
+      <c r="BC10">
+        <v>28</v>
+      </c>
+      <c r="BD10">
+        <v>38</v>
+      </c>
+      <c r="BE10">
+        <v>9.6</v>
+      </c>
+      <c r="BF10">
+        <v>36</v>
+      </c>
+      <c r="BG10">
         <v>8</v>
       </c>
-      <c r="BC10">
-        <v>7.6</v>
-      </c>
-      <c r="BD10">
-        <v>8</v>
-      </c>
-      <c r="BE10">
-        <v>8.6</v>
-      </c>
-      <c r="BF10">
-        <v>7.8</v>
-      </c>
-      <c r="BG10">
-        <v>7</v>
-      </c>
       <c r="BH10">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI10">
-        <v>1.04</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN10">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>1.04</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ10">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BR10">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS10">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU10">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="BV10">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW10">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3238,37 +3238,37 @@
         <v>2.84</v>
       </c>
       <c r="G11">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="H11">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I11">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J11">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K11">
-        <v>7.8</v>
+        <v>5.6</v>
       </c>
       <c r="L11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>5.3</v>
+        <v>13.5</v>
       </c>
       <c r="O11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Q11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="R11">
         <v>2.72</v>
@@ -3277,184 +3277,184 @@
         <v>1.5</v>
       </c>
       <c r="T11">
-        <v>1.11</v>
+        <v>1.26</v>
       </c>
       <c r="U11">
-        <v>1.11</v>
+        <v>4.1</v>
       </c>
       <c r="V11">
         <v>1.79</v>
       </c>
       <c r="W11">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AC11">
-        <v>950</v>
+        <v>19.5</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="AP11">
-        <v>1.02</v>
+        <v>6</v>
       </c>
       <c r="AQ11">
-        <v>1.02</v>
+        <v>5.5</v>
       </c>
       <c r="AR11">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AS11">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT11">
-        <v>1.02</v>
+        <v>5.6</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AV11">
-        <v>1.02</v>
+        <v>11.5</v>
       </c>
       <c r="AW11">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AX11">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AY11">
-        <v>1.02</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11">
-        <v>1.02</v>
+        <v>10.5</v>
       </c>
       <c r="BA11">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BB11">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BC11">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="BD11">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BE11">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="BF11">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="BG11">
-        <v>1.55</v>
+        <v>4.6</v>
       </c>
       <c r="BH11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BI11">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BJ11">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK11">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="BL11">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BM11">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BN11">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO11">
-        <v>1.04</v>
+        <v>4.7</v>
       </c>
       <c r="BP11">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BQ11">
-        <v>1.04</v>
+        <v>6.6</v>
       </c>
       <c r="BR11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS11">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="BT11">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU11">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BW11">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BY11">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="BZ11">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="CA11">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="CB11" t="s">
         <v>149</v>
@@ -3477,22 +3477,22 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G12">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="H12">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I12">
+        <v>4.4</v>
+      </c>
+      <c r="J12">
+        <v>4.4</v>
+      </c>
+      <c r="K12">
         <v>5.5</v>
-      </c>
-      <c r="J12">
-        <v>4</v>
-      </c>
-      <c r="K12">
-        <v>6.6</v>
       </c>
       <c r="L12">
         <v>1.18</v>
@@ -3501,142 +3501,142 @@
         <v>1.01</v>
       </c>
       <c r="N12">
+        <v>1.1</v>
+      </c>
+      <c r="O12">
+        <v>1.1</v>
+      </c>
+      <c r="P12">
+        <v>3</v>
+      </c>
+      <c r="Q12">
+        <v>1.32</v>
+      </c>
+      <c r="R12">
+        <v>1.95</v>
+      </c>
+      <c r="S12">
+        <v>1.8</v>
+      </c>
+      <c r="T12">
+        <v>1.39</v>
+      </c>
+      <c r="U12">
+        <v>2.92</v>
+      </c>
+      <c r="V12">
+        <v>1.29</v>
+      </c>
+      <c r="W12">
+        <v>2.02</v>
+      </c>
+      <c r="X12">
+        <v>48</v>
+      </c>
+      <c r="Y12">
+        <v>34</v>
+      </c>
+      <c r="Z12">
+        <v>44</v>
+      </c>
+      <c r="AA12">
+        <v>170</v>
+      </c>
+      <c r="AB12">
+        <v>22</v>
+      </c>
+      <c r="AC12">
+        <v>14.5</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>40</v>
+      </c>
+      <c r="AF12">
+        <v>21</v>
+      </c>
+      <c r="AG12">
+        <v>13</v>
+      </c>
+      <c r="AH12">
+        <v>16.5</v>
+      </c>
+      <c r="AI12">
+        <v>36</v>
+      </c>
+      <c r="AJ12">
+        <v>25</v>
+      </c>
+      <c r="AK12">
+        <v>18</v>
+      </c>
+      <c r="AL12">
+        <v>23</v>
+      </c>
+      <c r="AM12">
+        <v>48</v>
+      </c>
+      <c r="AN12">
+        <v>6.2</v>
+      </c>
+      <c r="AO12">
+        <v>19.5</v>
+      </c>
+      <c r="AP12">
+        <v>6.2</v>
+      </c>
+      <c r="AQ12">
+        <v>5.8</v>
+      </c>
+      <c r="AR12">
         <v>6</v>
       </c>
-      <c r="O12">
-        <v>1.08</v>
-      </c>
-      <c r="P12">
-        <v>2.72</v>
-      </c>
-      <c r="Q12">
-        <v>1.09</v>
-      </c>
-      <c r="R12">
-        <v>1.86</v>
-      </c>
-      <c r="S12">
-        <v>1.69</v>
-      </c>
-      <c r="T12">
-        <v>1.11</v>
-      </c>
-      <c r="U12">
-        <v>1.11</v>
-      </c>
-      <c r="V12">
-        <v>1.22</v>
-      </c>
-      <c r="W12">
-        <v>1.94</v>
-      </c>
-      <c r="X12">
-        <v>950</v>
-      </c>
-      <c r="Y12">
-        <v>950</v>
-      </c>
-      <c r="Z12">
-        <v>500</v>
-      </c>
-      <c r="AA12">
-        <v>900</v>
-      </c>
-      <c r="AB12">
-        <v>75</v>
-      </c>
-      <c r="AC12">
-        <v>19.5</v>
-      </c>
-      <c r="AD12">
-        <v>26</v>
-      </c>
-      <c r="AE12">
-        <v>120</v>
-      </c>
-      <c r="AF12">
-        <v>48</v>
-      </c>
-      <c r="AG12">
-        <v>16.5</v>
-      </c>
-      <c r="AH12">
-        <v>20</v>
-      </c>
-      <c r="AI12">
-        <v>100</v>
-      </c>
-      <c r="AJ12">
-        <v>75</v>
-      </c>
-      <c r="AK12">
-        <v>23</v>
-      </c>
-      <c r="AL12">
-        <v>48</v>
-      </c>
-      <c r="AM12">
-        <v>500</v>
-      </c>
-      <c r="AN12">
-        <v>7.6</v>
-      </c>
-      <c r="AO12">
-        <v>26</v>
-      </c>
-      <c r="AP12">
-        <v>2.9</v>
-      </c>
-      <c r="AQ12">
-        <v>2.74</v>
-      </c>
-      <c r="AR12">
-        <v>2.76</v>
-      </c>
       <c r="AS12">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="AT12">
-        <v>2.68</v>
+        <v>5.3</v>
       </c>
       <c r="AU12">
-        <v>2.54</v>
+        <v>4.7</v>
       </c>
       <c r="AV12">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="AW12">
-        <v>2.76</v>
+        <v>6</v>
       </c>
       <c r="AX12">
-        <v>2.64</v>
+        <v>5.3</v>
       </c>
       <c r="AY12">
-        <v>2.48</v>
+        <v>4.6</v>
       </c>
       <c r="AZ12">
-        <v>2.54</v>
+        <v>4.9</v>
       </c>
       <c r="BA12">
-        <v>2.74</v>
+        <v>5.9</v>
       </c>
       <c r="BB12">
-        <v>2.68</v>
+        <v>5.5</v>
       </c>
       <c r="BC12">
-        <v>2.58</v>
+        <v>5.1</v>
       </c>
       <c r="BD12">
-        <v>2.64</v>
+        <v>5.4</v>
       </c>
       <c r="BE12">
-        <v>2.76</v>
+        <v>6.2</v>
       </c>
       <c r="BF12">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="BG12">
-        <v>2.62</v>
+        <v>5.2</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -3961,22 +3961,22 @@
         <v>138</v>
       </c>
       <c r="F14">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="G14">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="H14">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="I14">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="J14">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K14">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
         <v>1.15</v>
@@ -3988,199 +3988,199 @@
         <v>1.1</v>
       </c>
       <c r="O14">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P14">
         <v>1.07</v>
       </c>
       <c r="Q14">
+        <v>1.25</v>
+      </c>
+      <c r="R14">
+        <v>2.06</v>
+      </c>
+      <c r="S14">
+        <v>1.61</v>
+      </c>
+      <c r="T14">
+        <v>1.32</v>
+      </c>
+      <c r="U14">
+        <v>3.35</v>
+      </c>
+      <c r="V14">
         <v>1.01</v>
-      </c>
-      <c r="R14">
-        <v>1.94</v>
-      </c>
-      <c r="S14">
-        <v>1.52</v>
-      </c>
-      <c r="T14">
-        <v>1.11</v>
-      </c>
-      <c r="U14">
-        <v>1.11</v>
-      </c>
-      <c r="V14">
-        <v>1.4</v>
       </c>
       <c r="W14">
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Y14">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="Z14">
+        <v>90</v>
+      </c>
+      <c r="AA14">
         <v>500</v>
       </c>
-      <c r="AA14">
-        <v>900</v>
-      </c>
       <c r="AB14">
-        <v>950</v>
+        <v>55</v>
       </c>
       <c r="AC14">
-        <v>950</v>
+        <v>15.5</v>
       </c>
       <c r="AD14">
-        <v>950</v>
+        <v>17.5</v>
       </c>
       <c r="AE14">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AF14">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AG14">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AH14">
-        <v>950</v>
+        <v>15</v>
       </c>
       <c r="AI14">
-        <v>500</v>
+        <v>26</v>
       </c>
       <c r="AJ14">
-        <v>900</v>
+        <v>160</v>
       </c>
       <c r="AK14">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AL14">
-        <v>500</v>
+        <v>23</v>
       </c>
       <c r="AM14">
-        <v>580</v>
+        <v>200</v>
       </c>
       <c r="AN14">
-        <v>500</v>
+        <v>7.6</v>
       </c>
       <c r="AO14">
-        <v>500</v>
+        <v>11.5</v>
       </c>
       <c r="AP14">
-        <v>1.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ14">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="AR14">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="AS14">
-        <v>1.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT14">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="AU14">
-        <v>1.08</v>
+        <v>7</v>
       </c>
       <c r="AV14">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="AW14">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="AX14">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="AY14">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="AZ14">
-        <v>1.06</v>
+        <v>4.8</v>
       </c>
       <c r="BA14">
-        <v>1.1</v>
+        <v>5.6</v>
       </c>
       <c r="BB14">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="BC14">
-        <v>1.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD14">
-        <v>1.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE14">
-        <v>1.1</v>
+        <v>5.9</v>
       </c>
       <c r="BF14">
-        <v>1.55</v>
+        <v>3.65</v>
       </c>
       <c r="BG14">
-        <v>1.55</v>
+        <v>4.4</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BI14">
-        <v>1.04</v>
+        <v>3.8</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BK14">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BO14">
-        <v>1.04</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BS14">
-        <v>1.04</v>
+        <v>5.8</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU14">
-        <v>1.04</v>
+        <v>4.1</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW14">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BY14">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="CA14">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4203,25 +4203,25 @@
         <v>139</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G15">
         <v>2.48</v>
       </c>
       <c r="H15">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="I15">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K15">
         <v>4.2</v>
       </c>
       <c r="L15">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M15">
         <v>1.04</v>
@@ -4251,7 +4251,7 @@
         <v>2.54</v>
       </c>
       <c r="V15">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
         <v>1.67</v>
@@ -4305,7 +4305,7 @@
         <v>150</v>
       </c>
       <c r="AN15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO15">
         <v>19</v>
@@ -4320,7 +4320,7 @@
         <v>17.5</v>
       </c>
       <c r="AS15">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15">
         <v>12.5</v>
@@ -4356,7 +4356,7 @@
         <v>13</v>
       </c>
       <c r="BE15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF15">
         <v>11.5</v>
@@ -4368,37 +4368,37 @@
         <v>4.3</v>
       </c>
       <c r="BI15">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BJ15">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BN15">
         <v>5.8</v>
       </c>
       <c r="BO15">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BP15">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="BQ15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BT15">
         <v>6.6</v>
@@ -4410,19 +4410,19 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15">
         <v>23</v>
       </c>
       <c r="CA15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="s">
         <v>149</v>
@@ -4445,76 +4445,76 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G16">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H16">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I16">
         <v>3.05</v>
       </c>
       <c r="J16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L16">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="M16">
         <v>1.02</v>
       </c>
       <c r="N16">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="O16">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="Q16">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="R16">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="S16">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="T16">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="V16">
         <v>1.48</v>
       </c>
       <c r="W16">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X16">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Y16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="Z16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AA16">
         <v>130</v>
       </c>
       <c r="AB16">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AC16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD16">
         <v>15.5</v>
@@ -4541,34 +4541,34 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM16">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AN16">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO16">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AP16">
         <v>14.5</v>
       </c>
       <c r="AQ16">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AR16">
-        <v>23</v>
+        <v>14.5</v>
       </c>
       <c r="AS16">
         <v>38</v>
       </c>
       <c r="AT16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU16">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16">
         <v>12.5</v>
@@ -4607,64 +4607,64 @@
         <v>11.5</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BI16">
-        <v>2.08</v>
+        <v>3.7</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="BK16">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM16">
-        <v>2.04</v>
+        <v>8.6</v>
       </c>
       <c r="BN16">
-        <v>8.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="BP16">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="BQ16">
-        <v>1.9</v>
+        <v>6</v>
       </c>
       <c r="BR16">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="BS16">
-        <v>1.95</v>
+        <v>7</v>
       </c>
       <c r="BT16">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="BU16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BV16">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="BW16">
-        <v>1.94</v>
+        <v>6.6</v>
       </c>
       <c r="BX16">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="BY16">
-        <v>1.97</v>
+        <v>7</v>
       </c>
       <c r="BZ16">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA16">
-        <v>1.87</v>
+        <v>5.9</v>
       </c>
       <c r="CB16" t="s">
         <v>149</v>
@@ -4687,28 +4687,28 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G17">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H17">
         <v>4</v>
       </c>
       <c r="I17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J17">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K17">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L17">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="M17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N17">
         <v>2.38</v>
@@ -4717,7 +4717,7 @@
         <v>1.69</v>
       </c>
       <c r="P17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q17">
         <v>3.2</v>
@@ -4726,31 +4726,31 @@
         <v>1.15</v>
       </c>
       <c r="S17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="T17">
         <v>2.48</v>
       </c>
       <c r="U17">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V17">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA17">
-        <v>490</v>
+        <v>110</v>
       </c>
       <c r="AB17">
         <v>6.4</v>
@@ -4759,10 +4759,10 @@
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE17">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="AF17">
         <v>12.5</v>
@@ -4777,19 +4777,19 @@
         <v>490</v>
       </c>
       <c r="AJ17">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AK17">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="AL17">
         <v>180</v>
       </c>
       <c r="AM17">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN17">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AO17">
         <v>490</v>
@@ -4798,58 +4798,58 @@
         <v>6.4</v>
       </c>
       <c r="AQ17">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR17">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AS17">
         <v>36</v>
       </c>
       <c r="AT17">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU17">
         <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AW17">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="AX17">
         <v>11</v>
       </c>
       <c r="AY17">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ17">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BA17">
         <v>42</v>
       </c>
       <c r="BB17">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BC17">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BD17">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BE17">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="BF17">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BG17">
         <v>42</v>
       </c>
       <c r="BH17">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BI17">
         <v>2.3</v>
@@ -4858,13 +4858,13 @@
         <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>17</v>
+        <v>2.18</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -4876,16 +4876,16 @@
         <v>22</v>
       </c>
       <c r="BQ17">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>13.5</v>
+        <v>2.12</v>
       </c>
       <c r="BT17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU17">
         <v>5.5</v>
@@ -4894,19 +4894,19 @@
         <v>50</v>
       </c>
       <c r="BW17">
-        <v>13.5</v>
+        <v>2.1</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BZ17">
         <v>65</v>
       </c>
       <c r="CA17">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CB17" t="s">
         <v>149</v>
@@ -4929,64 +4929,64 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="G18">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H18">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="I18">
-        <v>21</v>
+        <v>6.8</v>
       </c>
       <c r="J18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K18">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L18">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M18">
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P18">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="R18">
         <v>1.23</v>
       </c>
       <c r="S18">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T18">
+        <v>2.06</v>
+      </c>
+      <c r="U18">
         <v>1.72</v>
       </c>
-      <c r="U18">
-        <v>1.44</v>
-      </c>
       <c r="V18">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W18">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X18">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y18">
-        <v>970</v>
+        <v>17</v>
       </c>
       <c r="Z18">
         <v>500</v>
@@ -4995,160 +4995,160 @@
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC18">
-        <v>42</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE18">
         <v>700</v>
       </c>
       <c r="AF18">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AG18">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AH18">
-        <v>950</v>
+        <v>27</v>
       </c>
       <c r="AI18">
         <v>700</v>
       </c>
       <c r="AJ18">
-        <v>900</v>
+        <v>21</v>
       </c>
       <c r="AK18">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AL18">
-        <v>500</v>
+        <v>55</v>
       </c>
       <c r="AM18">
         <v>580</v>
       </c>
       <c r="AN18">
-        <v>85</v>
+        <v>17.5</v>
       </c>
       <c r="AO18">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP18">
-        <v>1.65</v>
+        <v>4.6</v>
       </c>
       <c r="AQ18">
-        <v>1.69</v>
+        <v>5.3</v>
       </c>
       <c r="AR18">
-        <v>1.77</v>
+        <v>6.6</v>
       </c>
       <c r="AS18">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="AT18">
-        <v>1.56</v>
+        <v>3.7</v>
       </c>
       <c r="AU18">
-        <v>1.59</v>
+        <v>4.1</v>
       </c>
       <c r="AV18">
-        <v>1.77</v>
+        <v>5.9</v>
       </c>
       <c r="AW18">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="AX18">
-        <v>1.63</v>
+        <v>4.4</v>
       </c>
       <c r="AY18">
-        <v>1.64</v>
+        <v>4.6</v>
       </c>
       <c r="AZ18">
-        <v>1.74</v>
+        <v>6</v>
       </c>
       <c r="BA18">
-        <v>1.79</v>
+        <v>7.2</v>
       </c>
       <c r="BB18">
-        <v>1.77</v>
+        <v>5.6</v>
       </c>
       <c r="BC18">
-        <v>1.72</v>
+        <v>5.8</v>
       </c>
       <c r="BD18">
-        <v>1.77</v>
+        <v>6.6</v>
       </c>
       <c r="BE18">
-        <v>1.79</v>
+        <v>7.4</v>
       </c>
       <c r="BF18">
-        <v>1.74</v>
+        <v>5.3</v>
       </c>
       <c r="BG18">
-        <v>1.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI18">
-        <v>1.04</v>
+        <v>2.5</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>1.04</v>
+        <v>5.2</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO18">
-        <v>1.04</v>
+        <v>2.94</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ18">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BU18">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>1.04</v>
+        <v>7.8</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>1.04</v>
+        <v>8</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA18">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="CB18" t="s">
         <v>149</v>
@@ -5171,25 +5171,25 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G19">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="I19">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="J19">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="K19">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L19">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M19">
         <v>1.09</v>
@@ -5198,19 +5198,19 @@
         <v>3.3</v>
       </c>
       <c r="O19">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P19">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q19">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="R19">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S19">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T19">
         <v>1.82</v>
@@ -5219,16 +5219,16 @@
         <v>2.02</v>
       </c>
       <c r="V19">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X19">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z19">
         <v>16.5</v>
@@ -5240,7 +5240,7 @@
         <v>12.5</v>
       </c>
       <c r="AC19">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD19">
         <v>12.5</v>
@@ -5276,10 +5276,10 @@
         <v>55</v>
       </c>
       <c r="AO19">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AP19">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19">
         <v>7.4</v>
@@ -5288,7 +5288,7 @@
         <v>12</v>
       </c>
       <c r="AS19">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT19">
         <v>10</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX19">
         <v>19</v>
@@ -5312,85 +5312,85 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB19">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BC19">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BD19">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BE19">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG19">
         <v>19.5</v>
       </c>
       <c r="BH19">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI19">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="BJ19">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>1.04</v>
+        <v>10</v>
       </c>
       <c r="BN19">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO19">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="BP19">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ19">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="BR19">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS19">
-        <v>1.04</v>
+        <v>8.6</v>
       </c>
       <c r="BT19">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="BU19">
-        <v>1.04</v>
+        <v>4.3</v>
       </c>
       <c r="BV19">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW19">
-        <v>1.04</v>
+        <v>7.2</v>
       </c>
       <c r="BX19">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY19">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ19">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA19">
-        <v>1.04</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB19" t="s">
         <v>149</v>
@@ -5413,22 +5413,22 @@
         <v>144</v>
       </c>
       <c r="F20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G20">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H20">
         <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J20">
         <v>3.15</v>
       </c>
       <c r="K20">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L20">
         <v>1.6</v>
@@ -5437,7 +5437,7 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O20">
         <v>1.56</v>
@@ -5446,7 +5446,7 @@
         <v>1.56</v>
       </c>
       <c r="Q20">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="R20">
         <v>1.2</v>
@@ -5455,10 +5455,10 @@
         <v>5.8</v>
       </c>
       <c r="T20">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U20">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="V20">
         <v>1.78</v>
@@ -5473,7 +5473,7 @@
         <v>7</v>
       </c>
       <c r="Z20">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AA20">
         <v>150</v>
@@ -5482,7 +5482,7 @@
         <v>11</v>
       </c>
       <c r="AC20">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD20">
         <v>11.5</v>
@@ -5509,7 +5509,7 @@
         <v>190</v>
       </c>
       <c r="AL20">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AM20">
         <v>500</v>
@@ -5530,19 +5530,19 @@
         <v>11</v>
       </c>
       <c r="AS20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT20">
         <v>9.6</v>
       </c>
       <c r="AU20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV20">
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX20">
         <v>11.5</v>
@@ -5557,7 +5557,7 @@
         <v>10.5</v>
       </c>
       <c r="BB20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BC20">
         <v>11</v>
@@ -5569,10 +5569,10 @@
         <v>12</v>
       </c>
       <c r="BF20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG20">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH20">
         <v>2.66</v>
@@ -5658,7 +5658,7 @@
         <v>1.75</v>
       </c>
       <c r="G21">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H21">
         <v>5.7</v>
@@ -5670,52 +5670,52 @@
         <v>3.85</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M21">
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P21">
         <v>1.9</v>
       </c>
       <c r="Q21">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R21">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S21">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T21">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V21">
         <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X21">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y21">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z21">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA21">
         <v>690</v>
@@ -5727,49 +5727,49 @@
         <v>8.6</v>
       </c>
       <c r="AD21">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AE21">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AF21">
         <v>9.800000000000001</v>
       </c>
       <c r="AG21">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH21">
         <v>21</v>
       </c>
       <c r="AI21">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AJ21">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AK21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL21">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM21">
-        <v>380</v>
+        <v>140</v>
       </c>
       <c r="AN21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO21">
-        <v>400</v>
+        <v>110</v>
       </c>
       <c r="AP21">
         <v>12</v>
       </c>
       <c r="AQ21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AR21">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AS21">
         <v>42</v>
@@ -5778,10 +5778,10 @@
         <v>7.4</v>
       </c>
       <c r="AU21">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV21">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW21">
         <v>40</v>
@@ -5790,61 +5790,61 @@
         <v>9</v>
       </c>
       <c r="AY21">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA21">
         <v>36</v>
       </c>
       <c r="BB21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD21">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="BE21">
         <v>42</v>
       </c>
       <c r="BF21">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG21">
         <v>38</v>
       </c>
       <c r="BH21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI21">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BJ21">
         <v>10.5</v>
       </c>
       <c r="BK21">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN21">
         <v>4.3</v>
       </c>
       <c r="BO21">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="BP21">
         <v>12</v>
       </c>
       <c r="BQ21">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR21">
         <v>29</v>
@@ -5856,19 +5856,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BV21">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW21">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BZ21">
         <v>24</v>
@@ -5921,19 +5921,19 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O22">
         <v>1.35</v>
       </c>
       <c r="P22">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R22">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S22">
         <v>3.75</v>
@@ -5957,13 +5957,13 @@
         <v>8.6</v>
       </c>
       <c r="Z22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA22">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AB22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AC22">
         <v>8</v>
@@ -5981,16 +5981,16 @@
         <v>18</v>
       </c>
       <c r="AH22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AI22">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AJ22">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AK22">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL22">
         <v>70</v>
@@ -5999,7 +5999,7 @@
         <v>120</v>
       </c>
       <c r="AN22">
-        <v>140</v>
+        <v>80</v>
       </c>
       <c r="AO22">
         <v>15</v>
@@ -6014,7 +6014,7 @@
         <v>10</v>
       </c>
       <c r="AS22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AT22">
         <v>14.5</v>
@@ -6032,19 +6032,19 @@
         <v>30</v>
       </c>
       <c r="AY22">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ22">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA22">
         <v>34</v>
       </c>
       <c r="BB22">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC22">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BD22">
         <v>50</v>
@@ -6104,7 +6104,7 @@
         <v>14.5</v>
       </c>
       <c r="BW22">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BX22">
         <v>30</v>
@@ -6139,22 +6139,22 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G23">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H23">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I23">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J23">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L23">
         <v>1.52</v>
@@ -6163,16 +6163,16 @@
         <v>1.11</v>
       </c>
       <c r="N23">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O23">
         <v>1.48</v>
       </c>
       <c r="P23">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q23">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R23">
         <v>1.24</v>
@@ -6181,130 +6181,130 @@
         <v>4.8</v>
       </c>
       <c r="T23">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U23">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W23">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X23">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y23">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z23">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB23">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AC23">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE23">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AF23">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH23">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI23">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ23">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AK23">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL23">
         <v>55</v>
       </c>
       <c r="AM23">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN23">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AO23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP23">
+        <v>9</v>
+      </c>
+      <c r="AQ23">
+        <v>11</v>
+      </c>
+      <c r="AR23">
+        <v>23</v>
+      </c>
+      <c r="AS23">
+        <v>7.4</v>
+      </c>
+      <c r="AT23">
+        <v>6.6</v>
+      </c>
+      <c r="AU23">
+        <v>7</v>
+      </c>
+      <c r="AV23">
+        <v>16</v>
+      </c>
+      <c r="AW23">
+        <v>50</v>
+      </c>
+      <c r="AX23">
+        <v>10.5</v>
+      </c>
+      <c r="AY23">
+        <v>10</v>
+      </c>
+      <c r="AZ23">
+        <v>20</v>
+      </c>
+      <c r="BA23">
+        <v>7.2</v>
+      </c>
+      <c r="BB23">
+        <v>23</v>
+      </c>
+      <c r="BC23">
+        <v>23</v>
+      </c>
+      <c r="BD23">
+        <v>44</v>
+      </c>
+      <c r="BE23">
         <v>7.6</v>
       </c>
-      <c r="AQ23">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR23">
-        <v>4.1</v>
-      </c>
-      <c r="AS23">
-        <v>4.5</v>
-      </c>
-      <c r="AT23">
-        <v>5.6</v>
-      </c>
-      <c r="AU23">
-        <v>5.9</v>
-      </c>
-      <c r="AV23">
-        <v>12.5</v>
-      </c>
-      <c r="AW23">
-        <v>4.3</v>
-      </c>
-      <c r="AX23">
-        <v>9.4</v>
-      </c>
-      <c r="AY23">
-        <v>8.4</v>
-      </c>
-      <c r="AZ23">
-        <v>16</v>
-      </c>
-      <c r="BA23">
-        <v>4.4</v>
-      </c>
-      <c r="BB23">
-        <v>19</v>
-      </c>
-      <c r="BC23">
-        <v>19</v>
-      </c>
-      <c r="BD23">
-        <v>4.3</v>
-      </c>
-      <c r="BE23">
-        <v>4.5</v>
-      </c>
       <c r="BF23">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BG23">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BH23">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="BI23">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="BJ23">
         <v>11</v>
@@ -6316,7 +6316,7 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BN23">
         <v>4.6</v>
@@ -6325,10 +6325,10 @@
         <v>3.65</v>
       </c>
       <c r="BP23">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BQ23">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR23">
         <v>36</v>
@@ -6337,16 +6337,16 @@
         <v>12</v>
       </c>
       <c r="BT23">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BU23">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BX23">
         <v>60</v>
@@ -6384,58 +6384,58 @@
         <v>1.43</v>
       </c>
       <c r="G24">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="H24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I24">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J24">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K24">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L24">
         <v>1.28</v>
       </c>
       <c r="M24">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N24">
         <v>5.8</v>
       </c>
       <c r="O24">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S24">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T24">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
         <v>1.13</v>
       </c>
       <c r="W24">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="X24">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y24">
         <v>38</v>
@@ -6444,13 +6444,13 @@
         <v>80</v>
       </c>
       <c r="AA24">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB24">
         <v>12</v>
       </c>
       <c r="AC24">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD24">
         <v>34</v>
@@ -6465,10 +6465,10 @@
         <v>12.5</v>
       </c>
       <c r="AH24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ24">
         <v>15</v>
@@ -6483,22 +6483,22 @@
         <v>110</v>
       </c>
       <c r="AN24">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AO24">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP24">
         <v>19.5</v>
       </c>
       <c r="AQ24">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AR24">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AS24">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AT24">
         <v>8.4</v>
@@ -6510,7 +6510,7 @@
         <v>19.5</v>
       </c>
       <c r="AW24">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX24">
         <v>7.8</v>
@@ -6522,7 +6522,7 @@
         <v>15.5</v>
       </c>
       <c r="BA24">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="BB24">
         <v>10</v>
@@ -6534,19 +6534,19 @@
         <v>20</v>
       </c>
       <c r="BE24">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BF24">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BG24">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BH24">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI24">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ24">
         <v>11</v>
@@ -6558,13 +6558,13 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN24">
         <v>4.4</v>
       </c>
       <c r="BO24">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP24">
         <v>8.800000000000001</v>
@@ -6573,7 +6573,7 @@
         <v>4.6</v>
       </c>
       <c r="BR24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS24">
         <v>6.6</v>
@@ -6582,25 +6582,25 @@
         <v>12</v>
       </c>
       <c r="BU24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV24">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BW24">
         <v>8.4</v>
       </c>
       <c r="BX24">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BY24">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ24">
         <v>12</v>
       </c>
       <c r="CA24">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB24" t="s">
         <v>149</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -463,7 +463,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 03:18:48</t>
+    <t>2026-07-29 05:26:39</t>
   </si>
 </sst>
 </file>
@@ -1057,151 +1057,151 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="G2">
         <v>9</v>
       </c>
       <c r="H2">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="I2">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="J2">
+        <v>4</v>
+      </c>
+      <c r="K2">
+        <v>4.6</v>
+      </c>
+      <c r="L2">
+        <v>1.43</v>
+      </c>
+      <c r="M2">
+        <v>1.07</v>
+      </c>
+      <c r="N2">
+        <v>3.45</v>
+      </c>
+      <c r="O2">
+        <v>1.35</v>
+      </c>
+      <c r="P2">
+        <v>1.85</v>
+      </c>
+      <c r="Q2">
+        <v>2.04</v>
+      </c>
+      <c r="R2">
+        <v>1.32</v>
+      </c>
+      <c r="S2">
         <v>3.6</v>
       </c>
-      <c r="K2">
-        <v>4.1</v>
-      </c>
-      <c r="L2">
-        <v>1.49</v>
-      </c>
-      <c r="M2">
-        <v>1.1</v>
-      </c>
-      <c r="N2">
-        <v>2.84</v>
-      </c>
-      <c r="O2">
-        <v>1.44</v>
-      </c>
-      <c r="P2">
-        <v>1.61</v>
-      </c>
-      <c r="Q2">
-        <v>2.32</v>
-      </c>
-      <c r="R2">
-        <v>1.23</v>
-      </c>
-      <c r="S2">
-        <v>4.6</v>
-      </c>
       <c r="T2">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="U2">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="V2">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="W2">
         <v>1.12</v>
       </c>
       <c r="X2">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z2">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA2">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AB2">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AC2">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AD2">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AF2">
         <v>160</v>
       </c>
       <c r="AG2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AI2">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AJ2">
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="AK2">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AL2">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AM2">
         <v>700</v>
       </c>
       <c r="AN2">
-        <v>390</v>
+        <v>250</v>
       </c>
       <c r="AO2">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP2">
+        <v>11.5</v>
+      </c>
+      <c r="AQ2">
+        <v>6.2</v>
+      </c>
+      <c r="AR2">
+        <v>7.4</v>
+      </c>
+      <c r="AS2">
+        <v>12</v>
+      </c>
+      <c r="AT2">
+        <v>18.5</v>
+      </c>
+      <c r="AU2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2">
+        <v>8.6</v>
+      </c>
+      <c r="AW2">
+        <v>15.5</v>
+      </c>
+      <c r="AX2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY2">
+        <v>8</v>
+      </c>
+      <c r="AZ2">
+        <v>12</v>
+      </c>
+      <c r="BA2">
         <v>9</v>
       </c>
-      <c r="AQ2">
-        <v>5.2</v>
-      </c>
-      <c r="AR2">
-        <v>4.6</v>
-      </c>
-      <c r="AS2">
-        <v>6.6</v>
-      </c>
-      <c r="AT2">
-        <v>6.6</v>
-      </c>
-      <c r="AU2">
-        <v>4.8</v>
-      </c>
-      <c r="AV2">
-        <v>5.2</v>
-      </c>
-      <c r="AW2">
-        <v>18</v>
-      </c>
-      <c r="AX2">
-        <v>8.6</v>
-      </c>
-      <c r="AY2">
-        <v>7.6</v>
-      </c>
-      <c r="AZ2">
-        <v>9</v>
-      </c>
-      <c r="BA2">
-        <v>8.4</v>
-      </c>
       <c r="BB2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2">
         <v>9.4</v>
@@ -1210,22 +1210,22 @@
         <v>9.4</v>
       </c>
       <c r="BE2">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BF2">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2">
-        <v>11.5</v>
+        <v>8.4</v>
       </c>
       <c r="BH2">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BI2">
-        <v>2.64</v>
+        <v>2.94</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK2">
         <v>6.4</v>
@@ -1234,7 +1234,7 @@
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>2.44</v>
+        <v>12.5</v>
       </c>
       <c r="BN2">
         <v>11.5</v>
@@ -1246,37 +1246,37 @@
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>2.4</v>
+        <v>11.5</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>2.4</v>
+        <v>11.5</v>
       </c>
       <c r="BT2">
         <v>3.9</v>
       </c>
       <c r="BU2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BV2">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BW2">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BX2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BY2">
-        <v>2.3</v>
+        <v>9.4</v>
       </c>
       <c r="BZ2">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="CA2">
-        <v>2.26</v>
+        <v>8.4</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,100 +1299,100 @@
         <v>127</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G3">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="H3">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J3">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="K3">
         <v>2.94</v>
       </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M3">
+        <v>1.13</v>
+      </c>
+      <c r="N3">
+        <v>2.24</v>
+      </c>
+      <c r="O3">
+        <v>1.69</v>
+      </c>
+      <c r="P3">
+        <v>1.45</v>
+      </c>
+      <c r="Q3">
+        <v>2.84</v>
+      </c>
+      <c r="R3">
         <v>1.15</v>
       </c>
-      <c r="N3">
-        <v>2.26</v>
-      </c>
-      <c r="O3">
+      <c r="S3">
+        <v>6</v>
+      </c>
+      <c r="T3">
+        <v>2.28</v>
+      </c>
+      <c r="U3">
         <v>1.62</v>
       </c>
-      <c r="P3">
-        <v>1.39</v>
-      </c>
-      <c r="Q3">
-        <v>2.92</v>
-      </c>
-      <c r="R3">
-        <v>1.17</v>
-      </c>
-      <c r="S3">
-        <v>6.4</v>
-      </c>
-      <c r="T3">
-        <v>2.2</v>
-      </c>
-      <c r="U3">
-        <v>1.61</v>
-      </c>
       <c r="V3">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W3">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="X3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="Y3">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Z3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AA3">
         <v>60</v>
       </c>
       <c r="AB3">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AE3">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AG3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH3">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AJ3">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AK3">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AL3">
         <v>240</v>
@@ -1401,124 +1401,124 @@
         <v>500</v>
       </c>
       <c r="AN3">
+        <v>85</v>
+      </c>
+      <c r="AO3">
         <v>600</v>
       </c>
-      <c r="AO3">
-        <v>75</v>
-      </c>
       <c r="AP3">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3">
-        <v>3.7</v>
+        <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="AS3">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT3">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU3">
+        <v>5.8</v>
+      </c>
+      <c r="AV3">
+        <v>12</v>
+      </c>
+      <c r="AW3">
+        <v>6.6</v>
+      </c>
+      <c r="AX3">
+        <v>15.5</v>
+      </c>
+      <c r="AY3">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3">
+        <v>19.5</v>
+      </c>
+      <c r="BA3">
+        <v>6.8</v>
+      </c>
+      <c r="BB3">
+        <v>6.8</v>
+      </c>
+      <c r="BC3">
+        <v>6.6</v>
+      </c>
+      <c r="BD3">
+        <v>7</v>
+      </c>
+      <c r="BE3">
+        <v>7.4</v>
+      </c>
+      <c r="BF3">
+        <v>6.8</v>
+      </c>
+      <c r="BG3">
+        <v>6.8</v>
+      </c>
+      <c r="BH3">
+        <v>2.54</v>
+      </c>
+      <c r="BI3">
+        <v>2.08</v>
+      </c>
+      <c r="BJ3">
+        <v>13</v>
+      </c>
+      <c r="BK3">
         <v>5.7</v>
-      </c>
-      <c r="AV3">
-        <v>4.8</v>
-      </c>
-      <c r="AW3">
-        <v>6.2</v>
-      </c>
-      <c r="AX3">
-        <v>5.3</v>
-      </c>
-      <c r="AY3">
-        <v>5</v>
-      </c>
-      <c r="AZ3">
-        <v>5.7</v>
-      </c>
-      <c r="BA3">
-        <v>6.4</v>
-      </c>
-      <c r="BB3">
-        <v>6.4</v>
-      </c>
-      <c r="BC3">
-        <v>6.2</v>
-      </c>
-      <c r="BD3">
-        <v>6.6</v>
-      </c>
-      <c r="BE3">
-        <v>6.8</v>
-      </c>
-      <c r="BF3">
-        <v>6.4</v>
-      </c>
-      <c r="BG3">
-        <v>6.4</v>
-      </c>
-      <c r="BH3">
-        <v>2.62</v>
-      </c>
-      <c r="BI3">
-        <v>2.04</v>
-      </c>
-      <c r="BJ3">
-        <v>13.5</v>
-      </c>
-      <c r="BK3">
-        <v>4.9</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>7.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN3">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BO3">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BP3">
         <v>36</v>
       </c>
       <c r="BQ3">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR3">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="BS3">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT3">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BU3">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BV3">
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY3">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BZ3">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="CA3">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>149</v>
@@ -1541,70 +1541,70 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G4">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="H4">
         <v>2.34</v>
       </c>
       <c r="I4">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J4">
         <v>2.88</v>
       </c>
       <c r="K4">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L4">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N4">
         <v>2.58</v>
       </c>
       <c r="O4">
+        <v>1.56</v>
+      </c>
+      <c r="P4">
         <v>1.53</v>
       </c>
-      <c r="P4">
-        <v>1.52</v>
-      </c>
       <c r="Q4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R4">
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="T4">
         <v>2.06</v>
       </c>
       <c r="U4">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="V4">
         <v>1.62</v>
       </c>
       <c r="W4">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X4">
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z4">
         <v>15</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB4">
         <v>10.5</v>
@@ -1625,10 +1625,10 @@
         <v>17</v>
       </c>
       <c r="AH4">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="AI4">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AJ4">
         <v>500</v>
@@ -1646,10 +1646,10 @@
         <v>600</v>
       </c>
       <c r="AO4">
-        <v>600</v>
+        <v>110</v>
       </c>
       <c r="AP4">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AQ4">
         <v>6.4</v>
@@ -1658,10 +1658,10 @@
         <v>11</v>
       </c>
       <c r="AS4">
-        <v>7.8</v>
+        <v>13</v>
       </c>
       <c r="AT4">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AU4">
         <v>6</v>
@@ -1670,37 +1670,37 @@
         <v>9.6</v>
       </c>
       <c r="AW4">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX4">
-        <v>7</v>
+        <v>18.5</v>
       </c>
       <c r="AY4">
         <v>12.5</v>
       </c>
       <c r="AZ4">
-        <v>6.8</v>
+        <v>19</v>
       </c>
       <c r="BA4">
+        <v>9</v>
+      </c>
+      <c r="BB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4">
+        <v>9</v>
+      </c>
+      <c r="BD4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG4">
         <v>8.4</v>
-      </c>
-      <c r="BB4">
-        <v>8.6</v>
-      </c>
-      <c r="BC4">
-        <v>8.4</v>
-      </c>
-      <c r="BD4">
-        <v>8.6</v>
-      </c>
-      <c r="BE4">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF4">
-        <v>8.6</v>
-      </c>
-      <c r="BG4">
-        <v>7.8</v>
       </c>
       <c r="BH4">
         <v>2.78</v>
@@ -1718,13 +1718,13 @@
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
       </c>
       <c r="BO4">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="BP4">
         <v>1000</v>
@@ -1742,7 +1742,7 @@
         <v>5.3</v>
       </c>
       <c r="BU4">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="BV4">
         <v>23</v>
@@ -1760,7 +1760,7 @@
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1783,10 +1783,10 @@
         <v>129</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G5">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="H5">
         <v>3.95</v>
@@ -1795,10 +1795,10 @@
         <v>4.1</v>
       </c>
       <c r="J5">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K5">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="L5">
         <v>1.74</v>
@@ -1807,10 +1807,10 @@
         <v>1.18</v>
       </c>
       <c r="N5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="O5">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="P5">
         <v>1.39</v>
@@ -1822,10 +1822,10 @@
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="T5">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U5">
         <v>1.6</v>
@@ -1834,7 +1834,7 @@
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
         <v>6.6</v>
@@ -1849,7 +1849,7 @@
         <v>110</v>
       </c>
       <c r="AB5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1891,7 +1891,7 @@
         <v>490</v>
       </c>
       <c r="AP5">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ5">
         <v>8.4</v>
@@ -1900,13 +1900,13 @@
         <v>22</v>
       </c>
       <c r="AS5">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="AT5">
         <v>5.8</v>
       </c>
       <c r="AU5">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV5">
         <v>18</v>
@@ -1933,7 +1933,7 @@
         <v>38</v>
       </c>
       <c r="BD5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BE5">
         <v>110</v>
@@ -2028,13 +2028,13 @@
         <v>1.28</v>
       </c>
       <c r="G6">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="J6">
         <v>6.8</v>
@@ -2043,34 +2043,34 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="M6">
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="O6">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="P6">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="Q6">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="R6">
-        <v>2.16</v>
+        <v>2.32</v>
       </c>
       <c r="S6">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="T6">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="U6">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
         <v>1.09</v>
@@ -2079,58 +2079,58 @@
         <v>4.1</v>
       </c>
       <c r="X6">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Y6">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Z6">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AA6">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="AB6">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AC6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AD6">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AE6">
         <v>140</v>
       </c>
       <c r="AF6">
+        <v>15</v>
+      </c>
+      <c r="AG6">
         <v>13.5</v>
       </c>
-      <c r="AG6">
-        <v>13</v>
-      </c>
       <c r="AH6">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AI6">
-        <v>85</v>
+        <v>230</v>
       </c>
       <c r="AJ6">
+        <v>14.5</v>
+      </c>
+      <c r="AK6">
         <v>13.5</v>
       </c>
-      <c r="AK6">
-        <v>14</v>
-      </c>
       <c r="AL6">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AM6">
         <v>320</v>
       </c>
       <c r="AN6">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="AO6">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="AP6">
         <v>20</v>
@@ -2139,28 +2139,28 @@
         <v>23</v>
       </c>
       <c r="AR6">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS6">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT6">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AU6">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AV6">
         <v>20</v>
       </c>
       <c r="AW6">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AX6">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AY6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ6">
         <v>20</v>
@@ -2169,82 +2169,82 @@
         <v>29</v>
       </c>
       <c r="BB6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC6">
         <v>11</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE6">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>2.84</v>
+        <v>2.62</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
       </c>
       <c r="BH6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BI6">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
       </c>
       <c r="BO6">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="BP6">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BQ6">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BR6">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU6">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BX6">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BY6">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BZ6">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="CA6">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="CB6" t="s">
         <v>149</v>
@@ -2270,16 +2270,16 @@
         <v>1.78</v>
       </c>
       <c r="G7">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I7">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K7">
         <v>5.1</v>
@@ -2288,7 +2288,7 @@
         <v>1.22</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
         <v>7.6</v>
@@ -2297,7 +2297,7 @@
         <v>1.13</v>
       </c>
       <c r="P7">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="Q7">
         <v>1.4</v>
@@ -2306,10 +2306,10 @@
         <v>1.89</v>
       </c>
       <c r="S7">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T7">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="U7">
         <v>2.78</v>
@@ -2387,7 +2387,7 @@
         <v>55</v>
       </c>
       <c r="AT7">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU7">
         <v>10.5</v>
@@ -2399,7 +2399,7 @@
         <v>27</v>
       </c>
       <c r="AX7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
@@ -2408,7 +2408,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB7">
         <v>16</v>
@@ -2423,7 +2423,7 @@
         <v>24</v>
       </c>
       <c r="BF7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG7">
         <v>17.5</v>
@@ -2512,223 +2512,223 @@
         <v>3.15</v>
       </c>
       <c r="G8">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H8">
         <v>2.02</v>
       </c>
       <c r="I8">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="J8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K8">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="L8">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N8">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="O8">
+        <v>1.08</v>
+      </c>
+      <c r="P8">
+        <v>4.1</v>
+      </c>
+      <c r="Q8">
+        <v>1.28</v>
+      </c>
+      <c r="R8">
+        <v>2.3</v>
+      </c>
+      <c r="S8">
+        <v>1.7</v>
+      </c>
+      <c r="T8">
+        <v>1.31</v>
+      </c>
+      <c r="U8">
         <v>1.11</v>
       </c>
-      <c r="P8">
-        <v>3.55</v>
-      </c>
-      <c r="Q8">
-        <v>1.34</v>
-      </c>
-      <c r="R8">
-        <v>2.06</v>
-      </c>
-      <c r="S8">
-        <v>1.84</v>
-      </c>
-      <c r="T8">
-        <v>1.36</v>
-      </c>
-      <c r="U8">
-        <v>3.2</v>
-      </c>
       <c r="V8">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="Y8">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="Z8">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AA8">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AB8">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="AC8">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD8">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE8">
         <v>19.5</v>
       </c>
       <c r="AF8">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="AG8">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ8">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AK8">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AL8">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AM8">
-        <v>55</v>
+        <v>580</v>
       </c>
       <c r="AN8">
+        <v>11.5</v>
+      </c>
+      <c r="AO8">
+        <v>6.2</v>
+      </c>
+      <c r="AP8">
+        <v>8</v>
+      </c>
+      <c r="AQ8">
+        <v>17.5</v>
+      </c>
+      <c r="AR8">
+        <v>18.5</v>
+      </c>
+      <c r="AS8">
+        <v>13.5</v>
+      </c>
+      <c r="AT8">
+        <v>14</v>
+      </c>
+      <c r="AU8">
         <v>13</v>
       </c>
-      <c r="AO8">
-        <v>6.8</v>
-      </c>
-      <c r="AP8">
-        <v>19</v>
-      </c>
-      <c r="AQ8">
-        <v>20</v>
-      </c>
-      <c r="AR8">
-        <v>19.5</v>
-      </c>
-      <c r="AS8">
-        <v>22</v>
-      </c>
-      <c r="AT8">
-        <v>23</v>
-      </c>
-      <c r="AU8">
+      <c r="AV8">
         <v>11.5</v>
-      </c>
-      <c r="AV8">
-        <v>10</v>
       </c>
       <c r="AW8">
         <v>16</v>
       </c>
       <c r="AX8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY8">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
         <v>12</v>
       </c>
       <c r="BA8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BB8">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD8">
         <v>21</v>
       </c>
       <c r="BE8">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="BF8">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG8">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH8">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BI8">
+        <v>5.2</v>
+      </c>
+      <c r="BJ8">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK8">
         <v>4.8</v>
-      </c>
-      <c r="BJ8">
-        <v>8.4</v>
-      </c>
-      <c r="BK8">
-        <v>4.5</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN8">
         <v>8.199999999999999</v>
       </c>
       <c r="BO8">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="BP8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BQ8">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BS8">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BT8">
         <v>6.4</v>
       </c>
       <c r="BU8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BW8">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX8">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BY8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BZ8">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA8">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="CB8" t="s">
         <v>149</v>
@@ -2751,22 +2751,22 @@
         <v>133</v>
       </c>
       <c r="F9">
+        <v>1.57</v>
+      </c>
+      <c r="G9">
         <v>1.64</v>
       </c>
-      <c r="G9">
-        <v>1.72</v>
-      </c>
       <c r="H9">
+        <v>5.3</v>
+      </c>
+      <c r="I9">
+        <v>6.2</v>
+      </c>
+      <c r="J9">
         <v>4.7</v>
       </c>
-      <c r="I9">
-        <v>5.5</v>
-      </c>
-      <c r="J9">
-        <v>4.4</v>
-      </c>
       <c r="K9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="L9">
         <v>1.26</v>
@@ -2775,55 +2775,55 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="O9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P9">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q9">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="R9">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S9">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="T9">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U9">
         <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W9">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="X9">
         <v>34</v>
       </c>
       <c r="Y9">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="Z9">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AA9">
         <v>900</v>
       </c>
       <c r="AB9">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AC9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AE9">
         <v>700</v>
@@ -2835,142 +2835,142 @@
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AI9">
         <v>700</v>
       </c>
       <c r="AJ9">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AK9">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AL9">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="AM9">
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="AO9">
         <v>600</v>
       </c>
       <c r="AP9">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AR9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS9">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT9">
+        <v>10.5</v>
+      </c>
+      <c r="AU9">
+        <v>9.4</v>
+      </c>
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AT9">
-        <v>10</v>
-      </c>
-      <c r="AU9">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV9">
-        <v>15.5</v>
-      </c>
-      <c r="AW9">
-        <v>7.6</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB9">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD9">
         <v>19</v>
       </c>
       <c r="BE9">
+        <v>8.4</v>
+      </c>
+      <c r="BF9">
+        <v>4.9</v>
+      </c>
+      <c r="BG9">
         <v>7.8</v>
       </c>
-      <c r="BF9">
+      <c r="BH9">
         <v>5.1</v>
       </c>
-      <c r="BG9">
-        <v>7.2</v>
-      </c>
-      <c r="BH9">
+      <c r="BI9">
+        <v>3.95</v>
+      </c>
+      <c r="BJ9">
+        <v>9.6</v>
+      </c>
+      <c r="BK9">
         <v>4.9</v>
-      </c>
-      <c r="BI9">
-        <v>3.75</v>
-      </c>
-      <c r="BJ9">
-        <v>9.4</v>
-      </c>
-      <c r="BK9">
-        <v>4.8</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN9">
+        <v>4.9</v>
+      </c>
+      <c r="BO9">
+        <v>3.8</v>
+      </c>
+      <c r="BP9">
+        <v>10</v>
+      </c>
+      <c r="BQ9">
         <v>5</v>
       </c>
-      <c r="BO9">
-        <v>3.85</v>
-      </c>
-      <c r="BP9">
-        <v>11</v>
-      </c>
-      <c r="BQ9">
-        <v>5.2</v>
-      </c>
       <c r="BR9">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BS9">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CA9">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="CB9" t="s">
         <v>149</v>
@@ -2993,19 +2993,19 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G10">
         <v>3.55</v>
       </c>
       <c r="H10">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I10">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K10">
         <v>3.3</v>
@@ -3023,7 +3023,7 @@
         <v>1.42</v>
       </c>
       <c r="P10">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q10">
         <v>2.28</v>
@@ -3032,19 +3032,19 @@
         <v>1.27</v>
       </c>
       <c r="S10">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T10">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U10">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V10">
         <v>1.59</v>
       </c>
       <c r="W10">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X10">
         <v>11</v>
@@ -3053,10 +3053,10 @@
         <v>9.4</v>
       </c>
       <c r="Z10">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB10">
         <v>11.5</v>
@@ -3083,13 +3083,13 @@
         <v>50</v>
       </c>
       <c r="AJ10">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK10">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="AL10">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AM10">
         <v>580</v>
@@ -3101,28 +3101,28 @@
         <v>32</v>
       </c>
       <c r="AP10">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AR10">
         <v>13.5</v>
       </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT10">
         <v>9.4</v>
       </c>
       <c r="AU10">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV10">
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
         <v>18.5</v>
@@ -3137,7 +3137,7 @@
         <v>36</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>9.4</v>
       </c>
       <c r="BC10">
         <v>28</v>
@@ -3146,67 +3146,67 @@
         <v>38</v>
       </c>
       <c r="BE10">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BF10">
         <v>36</v>
       </c>
       <c r="BG10">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="BH10">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI10">
-        <v>2.54</v>
+        <v>2.76</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BN10">
         <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BP10">
         <v>28</v>
       </c>
       <c r="BQ10">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BR10">
         <v>44</v>
       </c>
       <c r="BS10">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT10">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BU10">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BV10">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BW10">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX10">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY10">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3235,22 +3235,22 @@
         <v>135</v>
       </c>
       <c r="F11">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G11">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H11">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I11">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J11">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.14</v>
@@ -3265,34 +3265,34 @@
         <v>1.06</v>
       </c>
       <c r="P11">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Q11">
         <v>1.2</v>
       </c>
       <c r="R11">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="S11">
         <v>1.5</v>
       </c>
       <c r="T11">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="U11">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="V11">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="W11">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="X11">
         <v>110</v>
       </c>
       <c r="Y11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Z11">
         <v>36</v>
@@ -3301,34 +3301,34 @@
         <v>40</v>
       </c>
       <c r="AB11">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AC11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AD11">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AE11">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF11">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AG11">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH11">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AI11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ11">
         <v>130</v>
       </c>
       <c r="AK11">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL11">
         <v>24</v>
@@ -3337,10 +3337,10 @@
         <v>34</v>
       </c>
       <c r="AN11">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AO11">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AP11">
         <v>6</v>
@@ -3349,7 +3349,7 @@
         <v>5.5</v>
       </c>
       <c r="AR11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AS11">
         <v>5.5</v>
@@ -3358,7 +3358,7 @@
         <v>5.6</v>
       </c>
       <c r="AU11">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV11">
         <v>11.5</v>
@@ -3379,28 +3379,28 @@
         <v>14</v>
       </c>
       <c r="BB11">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BC11">
         <v>19.5</v>
       </c>
       <c r="BD11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BE11">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BF11">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG11">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH11">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BI11">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BJ11">
         <v>8.199999999999999</v>
@@ -3412,7 +3412,7 @@
         <v>36</v>
       </c>
       <c r="BM11">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BN11">
         <v>8.800000000000001</v>
@@ -3424,7 +3424,7 @@
         <v>19</v>
       </c>
       <c r="BQ11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BR11">
         <v>18</v>
@@ -3433,28 +3433,28 @@
         <v>6.4</v>
       </c>
       <c r="BT11">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BU11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BV11">
         <v>14</v>
       </c>
       <c r="BW11">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BX11">
         <v>15.5</v>
       </c>
       <c r="BY11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BZ11">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="CA11">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="CB11" t="s">
         <v>149</v>
@@ -3477,22 +3477,22 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="G12">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="H12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I12">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="J12">
         <v>4.4</v>
       </c>
       <c r="K12">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L12">
         <v>1.18</v>
@@ -3501,202 +3501,202 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>1.1</v>
+        <v>7.8</v>
       </c>
       <c r="O12">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="Q12">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R12">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="T12">
         <v>1.39</v>
       </c>
       <c r="U12">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="V12">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="W12">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y12">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="Z12">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AA12">
         <v>170</v>
       </c>
       <c r="AB12">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AC12">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD12">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AE12">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AF12">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AG12">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH12">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AI12">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AJ12">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AK12">
+        <v>19.5</v>
+      </c>
+      <c r="AL12">
+        <v>24</v>
+      </c>
+      <c r="AM12">
+        <v>42</v>
+      </c>
+      <c r="AN12">
+        <v>7.2</v>
+      </c>
+      <c r="AO12">
+        <v>15</v>
+      </c>
+      <c r="AP12">
+        <v>6.8</v>
+      </c>
+      <c r="AQ12">
+        <v>6.4</v>
+      </c>
+      <c r="AR12">
+        <v>6.6</v>
+      </c>
+      <c r="AS12">
+        <v>7</v>
+      </c>
+      <c r="AT12">
+        <v>17.5</v>
+      </c>
+      <c r="AU12">
+        <v>10.5</v>
+      </c>
+      <c r="AV12">
+        <v>13.5</v>
+      </c>
+      <c r="AW12">
+        <v>6.4</v>
+      </c>
+      <c r="AX12">
+        <v>17.5</v>
+      </c>
+      <c r="AY12">
+        <v>10.5</v>
+      </c>
+      <c r="AZ12">
+        <v>12</v>
+      </c>
+      <c r="BA12">
+        <v>6.4</v>
+      </c>
+      <c r="BB12">
+        <v>6.4</v>
+      </c>
+      <c r="BC12">
+        <v>15</v>
+      </c>
+      <c r="BD12">
         <v>18</v>
       </c>
-      <c r="AL12">
+      <c r="BE12">
+        <v>6.8</v>
+      </c>
+      <c r="BF12">
+        <v>3.8</v>
+      </c>
+      <c r="BG12">
+        <v>11.5</v>
+      </c>
+      <c r="BH12">
+        <v>6.2</v>
+      </c>
+      <c r="BI12">
+        <v>4.5</v>
+      </c>
+      <c r="BJ12">
+        <v>8.6</v>
+      </c>
+      <c r="BK12">
+        <v>4.1</v>
+      </c>
+      <c r="BL12">
+        <v>55</v>
+      </c>
+      <c r="BM12">
+        <v>7</v>
+      </c>
+      <c r="BN12">
+        <v>6.4</v>
+      </c>
+      <c r="BO12">
+        <v>3.55</v>
+      </c>
+      <c r="BP12">
+        <v>13.5</v>
+      </c>
+      <c r="BQ12">
+        <v>5</v>
+      </c>
+      <c r="BR12">
+        <v>19</v>
+      </c>
+      <c r="BS12">
+        <v>5.6</v>
+      </c>
+      <c r="BT12">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BU12">
+        <v>4</v>
+      </c>
+      <c r="BV12">
         <v>23</v>
       </c>
-      <c r="AM12">
-        <v>48</v>
-      </c>
-      <c r="AN12">
-        <v>6.2</v>
-      </c>
-      <c r="AO12">
-        <v>19.5</v>
-      </c>
-      <c r="AP12">
-        <v>6.2</v>
-      </c>
-      <c r="AQ12">
-        <v>5.8</v>
-      </c>
-      <c r="AR12">
+      <c r="BW12">
+        <v>5.9</v>
+      </c>
+      <c r="BX12">
+        <v>24</v>
+      </c>
+      <c r="BY12">
         <v>6</v>
       </c>
-      <c r="AS12">
-        <v>6.4</v>
-      </c>
-      <c r="AT12">
-        <v>5.3</v>
-      </c>
-      <c r="AU12">
-        <v>4.7</v>
-      </c>
-      <c r="AV12">
-        <v>5.3</v>
-      </c>
-      <c r="AW12">
-        <v>6</v>
-      </c>
-      <c r="AX12">
-        <v>5.3</v>
-      </c>
-      <c r="AY12">
+      <c r="BZ12">
+        <v>11</v>
+      </c>
+      <c r="CA12">
         <v>4.6</v>
-      </c>
-      <c r="AZ12">
-        <v>4.9</v>
-      </c>
-      <c r="BA12">
-        <v>5.9</v>
-      </c>
-      <c r="BB12">
-        <v>5.5</v>
-      </c>
-      <c r="BC12">
-        <v>5.1</v>
-      </c>
-      <c r="BD12">
-        <v>5.4</v>
-      </c>
-      <c r="BE12">
-        <v>6.2</v>
-      </c>
-      <c r="BF12">
-        <v>3.3</v>
-      </c>
-      <c r="BG12">
-        <v>5.2</v>
-      </c>
-      <c r="BH12">
-        <v>1000</v>
-      </c>
-      <c r="BI12">
-        <v>1.04</v>
-      </c>
-      <c r="BJ12">
-        <v>1000</v>
-      </c>
-      <c r="BK12">
-        <v>1.04</v>
-      </c>
-      <c r="BL12">
-        <v>1000</v>
-      </c>
-      <c r="BM12">
-        <v>1.04</v>
-      </c>
-      <c r="BN12">
-        <v>1000</v>
-      </c>
-      <c r="BO12">
-        <v>1.04</v>
-      </c>
-      <c r="BP12">
-        <v>1000</v>
-      </c>
-      <c r="BQ12">
-        <v>1.04</v>
-      </c>
-      <c r="BR12">
-        <v>1000</v>
-      </c>
-      <c r="BS12">
-        <v>1.04</v>
-      </c>
-      <c r="BT12">
-        <v>1000</v>
-      </c>
-      <c r="BU12">
-        <v>1.04</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>1.04</v>
-      </c>
-      <c r="BX12">
-        <v>1000</v>
-      </c>
-      <c r="BY12">
-        <v>1.04</v>
-      </c>
-      <c r="BZ12">
-        <v>1000</v>
-      </c>
-      <c r="CA12">
-        <v>1.04</v>
       </c>
       <c r="CB12" t="s">
         <v>149</v>
@@ -3722,10 +3722,10 @@
         <v>2.6</v>
       </c>
       <c r="G13">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H13">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="I13">
         <v>2.66</v>
@@ -3734,7 +3734,7 @@
         <v>3.75</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>1.18</v>
@@ -3749,19 +3749,19 @@
         <v>1.11</v>
       </c>
       <c r="P13">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="Q13">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R13">
         <v>2</v>
       </c>
       <c r="S13">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="T13">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="U13">
         <v>3.15</v>
@@ -3770,10 +3770,10 @@
         <v>1.61</v>
       </c>
       <c r="W13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X13">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y13">
         <v>26</v>
@@ -3785,10 +3785,10 @@
         <v>40</v>
       </c>
       <c r="AB13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC13">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD13">
         <v>15</v>
@@ -3797,7 +3797,7 @@
         <v>23</v>
       </c>
       <c r="AF13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG13">
         <v>15</v>
@@ -3812,7 +3812,7 @@
         <v>42</v>
       </c>
       <c r="AK13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13">
         <v>25</v>
@@ -3824,13 +3824,13 @@
         <v>10</v>
       </c>
       <c r="AO13">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AP13">
         <v>7.6</v>
       </c>
       <c r="AQ13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR13">
         <v>6.8</v>
@@ -3842,22 +3842,22 @@
         <v>6.8</v>
       </c>
       <c r="AU13">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="AV13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW13">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX13">
         <v>6.8</v>
       </c>
       <c r="AY13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ13">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BA13">
         <v>6.6</v>
@@ -3872,19 +3872,19 @@
         <v>6.6</v>
       </c>
       <c r="BE13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF13">
+        <v>4.8</v>
+      </c>
+      <c r="BG13">
         <v>4.7</v>
       </c>
-      <c r="BG13">
-        <v>4.5</v>
-      </c>
       <c r="BH13">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI13">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BJ13">
         <v>8.4</v>
@@ -3893,19 +3893,19 @@
         <v>4.4</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BN13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO13">
         <v>4</v>
       </c>
       <c r="BP13">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BQ13">
         <v>6</v>
@@ -3920,25 +3920,25 @@
         <v>7</v>
       </c>
       <c r="BU13">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BV13">
         <v>16.5</v>
       </c>
       <c r="BW13">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BX13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA13">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="CB13" t="s">
         <v>149</v>
@@ -3961,52 +3961,52 @@
         <v>138</v>
       </c>
       <c r="F14">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G14">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="H14">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="I14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J14">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
         <v>5.3</v>
       </c>
       <c r="L14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N14">
-        <v>1.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O14">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P14">
-        <v>1.07</v>
+        <v>3.85</v>
       </c>
       <c r="Q14">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="R14">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="T14">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="U14">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -4015,7 +4015,7 @@
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>150</v>
+        <v>950</v>
       </c>
       <c r="Y14">
         <v>60</v>
@@ -4024,25 +4024,25 @@
         <v>90</v>
       </c>
       <c r="AA14">
-        <v>500</v>
+        <v>210</v>
       </c>
       <c r="AB14">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AC14">
         <v>15.5</v>
       </c>
       <c r="AD14">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE14">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="AF14">
         <v>65</v>
       </c>
       <c r="AG14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH14">
         <v>15</v>
@@ -4051,136 +4051,136 @@
         <v>26</v>
       </c>
       <c r="AJ14">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AK14">
         <v>21</v>
       </c>
       <c r="AL14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM14">
         <v>200</v>
       </c>
       <c r="AN14">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AO14">
+        <v>10.5</v>
+      </c>
+      <c r="AP14">
+        <v>7.8</v>
+      </c>
+      <c r="AQ14">
+        <v>7</v>
+      </c>
+      <c r="AR14">
+        <v>7.2</v>
+      </c>
+      <c r="AS14">
+        <v>7.8</v>
+      </c>
+      <c r="AT14">
+        <v>6.8</v>
+      </c>
+      <c r="AU14">
+        <v>12</v>
+      </c>
+      <c r="AV14">
+        <v>13.5</v>
+      </c>
+      <c r="AW14">
+        <v>6.8</v>
+      </c>
+      <c r="AX14">
+        <v>6.8</v>
+      </c>
+      <c r="AY14">
         <v>11.5</v>
       </c>
-      <c r="AP14">
-        <v>6.4</v>
-      </c>
-      <c r="AQ14">
-        <v>5.9</v>
-      </c>
-      <c r="AR14">
-        <v>6</v>
-      </c>
-      <c r="AS14">
-        <v>6.2</v>
-      </c>
-      <c r="AT14">
-        <v>5.7</v>
-      </c>
-      <c r="AU14">
-        <v>7</v>
-      </c>
-      <c r="AV14">
-        <v>5</v>
-      </c>
-      <c r="AW14">
-        <v>5.7</v>
-      </c>
-      <c r="AX14">
-        <v>5.7</v>
-      </c>
-      <c r="AY14">
-        <v>4.8</v>
-      </c>
       <c r="AZ14">
-        <v>4.8</v>
+        <v>12</v>
       </c>
       <c r="BA14">
-        <v>5.6</v>
+        <v>20</v>
       </c>
       <c r="BB14">
-        <v>5.9</v>
+        <v>18</v>
       </c>
       <c r="BC14">
-        <v>5.3</v>
+        <v>16.5</v>
       </c>
       <c r="BD14">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="BE14">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="BF14">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="BG14">
-        <v>4.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH14">
         <v>6.8</v>
       </c>
       <c r="BI14">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="BJ14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK14">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BN14">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BO14">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP14">
         <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BR14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS14">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BT14">
         <v>8</v>
       </c>
       <c r="BU14">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BV14">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BW14">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BX14">
         <v>21</v>
       </c>
       <c r="BY14">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ14">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CA14">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4206,10 +4206,10 @@
         <v>2.36</v>
       </c>
       <c r="G15">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H15">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I15">
         <v>3.1</v>
@@ -4254,7 +4254,7 @@
         <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X15">
         <v>23</v>
@@ -4266,7 +4266,7 @@
         <v>28</v>
       </c>
       <c r="AA15">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AB15">
         <v>15.5</v>
@@ -4293,7 +4293,7 @@
         <v>36</v>
       </c>
       <c r="AJ15">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AK15">
         <v>28</v>
@@ -4302,7 +4302,7 @@
         <v>34</v>
       </c>
       <c r="AM15">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AN15">
         <v>14</v>
@@ -4311,52 +4311,52 @@
         <v>19</v>
       </c>
       <c r="AP15">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR15">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AS15">
-        <v>8.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="AT15">
         <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV15">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX15">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AY15">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BB15">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC15">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BD15">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BE15">
-        <v>9.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BF15">
         <v>11.5</v>
@@ -4374,7 +4374,7 @@
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL15">
         <v>1000</v>
@@ -4392,7 +4392,7 @@
         <v>970</v>
       </c>
       <c r="BQ15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR15">
         <v>1000</v>
@@ -4404,7 +4404,7 @@
         <v>6.6</v>
       </c>
       <c r="BU15">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BV15">
         <v>1000</v>
@@ -4422,7 +4422,7 @@
         <v>23</v>
       </c>
       <c r="CA15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="CB15" t="s">
         <v>149</v>
@@ -4445,13 +4445,13 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G16">
         <v>2.38</v>
       </c>
       <c r="H16">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="I16">
         <v>3.05</v>
@@ -4466,10 +4466,10 @@
         <v>1.27</v>
       </c>
       <c r="M16">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4481,13 +4481,13 @@
         <v>1.49</v>
       </c>
       <c r="R16">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S16">
         <v>2.24</v>
       </c>
       <c r="T16">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="U16">
         <v>2.78</v>
@@ -4502,19 +4502,19 @@
         <v>32</v>
       </c>
       <c r="Y16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z16">
         <v>28</v>
       </c>
       <c r="AA16">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AB16">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AC16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD16">
         <v>15.5</v>
@@ -4523,7 +4523,7 @@
         <v>29</v>
       </c>
       <c r="AF16">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG16">
         <v>13</v>
@@ -4544,28 +4544,28 @@
         <v>27</v>
       </c>
       <c r="AM16">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AN16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO16">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AP16">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AQ16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR16">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AS16">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AT16">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4574,10 +4574,10 @@
         <v>12.5</v>
       </c>
       <c r="AW16">
-        <v>14.5</v>
+        <v>21</v>
       </c>
       <c r="AX16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4586,49 +4586,49 @@
         <v>12</v>
       </c>
       <c r="BA16">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BB16">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="BC16">
         <v>17</v>
       </c>
       <c r="BD16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE16">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BF16">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI16">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BJ16">
         <v>8.6</v>
       </c>
       <c r="BK16">
+        <v>4.5</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>8.4</v>
+      </c>
+      <c r="BN16">
+        <v>6.4</v>
+      </c>
+      <c r="BO16">
         <v>4.6</v>
-      </c>
-      <c r="BL16">
-        <v>65</v>
-      </c>
-      <c r="BM16">
-        <v>8.6</v>
-      </c>
-      <c r="BN16">
-        <v>6.2</v>
-      </c>
-      <c r="BO16">
-        <v>4.5</v>
       </c>
       <c r="BP16">
         <v>16</v>
@@ -4637,10 +4637,10 @@
         <v>6</v>
       </c>
       <c r="BR16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS16">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BT16">
         <v>7</v>
@@ -4649,10 +4649,10 @@
         <v>5</v>
       </c>
       <c r="BV16">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BX16">
         <v>25</v>
@@ -4661,10 +4661,10 @@
         <v>7</v>
       </c>
       <c r="BZ16">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="CA16">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="CB16" t="s">
         <v>149</v>
@@ -4687,13 +4687,13 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G17">
         <v>2.42</v>
       </c>
       <c r="H17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I17">
         <v>4.1</v>
@@ -4702,25 +4702,25 @@
         <v>2.96</v>
       </c>
       <c r="K17">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L17">
         <v>1.69</v>
       </c>
       <c r="M17">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N17">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="O17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P17">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="R17">
         <v>1.15</v>
@@ -4729,7 +4729,7 @@
         <v>7.4</v>
       </c>
       <c r="T17">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="U17">
         <v>1.64</v>
@@ -4738,16 +4738,16 @@
         <v>1.32</v>
       </c>
       <c r="W17">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Y17">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA17">
         <v>110</v>
@@ -4783,7 +4783,7 @@
         <v>40</v>
       </c>
       <c r="AL17">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="AM17">
         <v>320</v>
@@ -4792,7 +4792,7 @@
         <v>46</v>
       </c>
       <c r="AO17">
-        <v>490</v>
+        <v>140</v>
       </c>
       <c r="AP17">
         <v>6.4</v>
@@ -4813,10 +4813,10 @@
         <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AW17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AX17">
         <v>11</v>
@@ -4831,7 +4831,7 @@
         <v>42</v>
       </c>
       <c r="BB17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BC17">
         <v>34</v>
@@ -4858,13 +4858,13 @@
         <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -5174,25 +5174,25 @@
         <v>3.3</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="H19">
         <v>2.54</v>
       </c>
       <c r="I19">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J19">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K19">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L19">
         <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N19">
         <v>3.3</v>
@@ -5237,7 +5237,7 @@
         <v>42</v>
       </c>
       <c r="AB19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC19">
         <v>7.2</v>
@@ -5249,7 +5249,7 @@
         <v>34</v>
       </c>
       <c r="AF19">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG19">
         <v>15.5</v>
@@ -5261,22 +5261,22 @@
         <v>55</v>
       </c>
       <c r="AJ19">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AK19">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AL19">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM19">
-        <v>130</v>
+        <v>450</v>
       </c>
       <c r="AN19">
         <v>55</v>
       </c>
       <c r="AO19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP19">
         <v>9.199999999999999</v>
@@ -5288,7 +5288,7 @@
         <v>12</v>
       </c>
       <c r="AS19">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AT19">
         <v>10</v>
@@ -5300,7 +5300,7 @@
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AX19">
         <v>19</v>
@@ -5312,22 +5312,22 @@
         <v>13.5</v>
       </c>
       <c r="BA19">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BB19">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BC19">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD19">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BE19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BF19">
         <v>8.199999999999999</v>
-      </c>
-      <c r="BF19">
-        <v>7.4</v>
       </c>
       <c r="BG19">
         <v>19.5</v>
@@ -5336,7 +5336,7 @@
         <v>3.2</v>
       </c>
       <c r="BI19">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="BJ19">
         <v>10.5</v>
@@ -5422,7 +5422,7 @@
         <v>2.22</v>
       </c>
       <c r="I20">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="J20">
         <v>3.15</v>
@@ -5437,31 +5437,31 @@
         <v>1.13</v>
       </c>
       <c r="N20">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="O20">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P20">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q20">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="R20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S20">
         <v>5.8</v>
       </c>
       <c r="T20">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="U20">
         <v>1.74</v>
       </c>
       <c r="V20">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W20">
         <v>1.31</v>
@@ -5509,7 +5509,7 @@
         <v>190</v>
       </c>
       <c r="AL20">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="AM20">
         <v>500</v>
@@ -5530,7 +5530,7 @@
         <v>11</v>
       </c>
       <c r="AS20">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT20">
         <v>9.6</v>
@@ -5542,7 +5542,7 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX20">
         <v>11.5</v>
@@ -5569,10 +5569,10 @@
         <v>12</v>
       </c>
       <c r="BF20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BG20">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH20">
         <v>2.66</v>
@@ -5655,7 +5655,7 @@
         <v>145</v>
       </c>
       <c r="F21">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="G21">
         <v>1.76</v>
@@ -5670,7 +5670,7 @@
         <v>3.85</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L21">
         <v>1.44</v>
@@ -5679,40 +5679,40 @@
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O21">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P21">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q21">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R21">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S21">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T21">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U21">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V21">
         <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X21">
         <v>13</v>
       </c>
       <c r="Y21">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z21">
         <v>44</v>
@@ -5730,13 +5730,13 @@
         <v>22</v>
       </c>
       <c r="AE21">
-        <v>85</v>
+        <v>200</v>
       </c>
       <c r="AF21">
         <v>9.800000000000001</v>
       </c>
       <c r="AG21">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AH21">
         <v>21</v>
@@ -5745,7 +5745,7 @@
         <v>90</v>
       </c>
       <c r="AJ21">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AK21">
         <v>19</v>
@@ -5790,7 +5790,7 @@
         <v>9</v>
       </c>
       <c r="AY21">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AZ21">
         <v>19.5</v>
@@ -5811,7 +5811,7 @@
         <v>42</v>
       </c>
       <c r="BF21">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG21">
         <v>38</v>
@@ -5820,7 +5820,7 @@
         <v>3.3</v>
       </c>
       <c r="BI21">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ21">
         <v>10.5</v>
@@ -5832,7 +5832,7 @@
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BN21">
         <v>4.3</v>
@@ -5856,10 +5856,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BU21">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BV21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW21">
         <v>13.5</v>
@@ -5874,7 +5874,7 @@
         <v>24</v>
       </c>
       <c r="CA21">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="CB21" t="s">
         <v>149</v>
@@ -5903,16 +5903,16 @@
         <v>4.7</v>
       </c>
       <c r="H22">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="I22">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J22">
+        <v>3.6</v>
+      </c>
+      <c r="K22">
         <v>3.65</v>
-      </c>
-      <c r="K22">
-        <v>3.7</v>
       </c>
       <c r="L22">
         <v>1.44</v>
@@ -5927,10 +5927,10 @@
         <v>1.35</v>
       </c>
       <c r="P22">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q22">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R22">
         <v>1.34</v>
@@ -5942,7 +5942,7 @@
         <v>1.89</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V22">
         <v>2.04</v>
@@ -5954,7 +5954,7 @@
         <v>13.5</v>
       </c>
       <c r="Y22">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22">
         <v>11</v>
@@ -5966,10 +5966,10 @@
         <v>15.5</v>
       </c>
       <c r="AC22">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AE22">
         <v>21</v>
@@ -5981,7 +5981,7 @@
         <v>18</v>
       </c>
       <c r="AH22">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI22">
         <v>40</v>
@@ -5990,7 +5990,7 @@
         <v>110</v>
       </c>
       <c r="AK22">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL22">
         <v>70</v>
@@ -6005,7 +6005,7 @@
         <v>15</v>
       </c>
       <c r="AP22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ22">
         <v>8</v>
@@ -6014,7 +6014,7 @@
         <v>10</v>
       </c>
       <c r="AS22">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AT22">
         <v>14.5</v>
@@ -6023,10 +6023,10 @@
         <v>7.4</v>
       </c>
       <c r="AV22">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AW22">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AX22">
         <v>30</v>
@@ -6041,13 +6041,13 @@
         <v>34</v>
       </c>
       <c r="BB22">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC22">
+        <v>50</v>
+      </c>
+      <c r="BD22">
         <v>55</v>
-      </c>
-      <c r="BD22">
-        <v>50</v>
       </c>
       <c r="BE22">
         <v>28</v>
@@ -6068,31 +6068,31 @@
         <v>10.5</v>
       </c>
       <c r="BK22">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN22">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BO22">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BP22">
         <v>40</v>
       </c>
       <c r="BQ22">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BR22">
         <v>50</v>
       </c>
       <c r="BS22">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BT22">
         <v>4.5</v>
@@ -6101,7 +6101,7 @@
         <v>4.1</v>
       </c>
       <c r="BV22">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BW22">
         <v>10.5</v>
@@ -6110,13 +6110,13 @@
         <v>30</v>
       </c>
       <c r="BY22">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BZ22">
         <v>27</v>
       </c>
       <c r="CA22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB22" t="s">
         <v>149</v>
@@ -6139,22 +6139,22 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="G23">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="H23">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I23">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="J23">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L23">
         <v>1.52</v>
@@ -6163,76 +6163,76 @@
         <v>1.11</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O23">
         <v>1.48</v>
       </c>
       <c r="P23">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q23">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R23">
         <v>1.24</v>
       </c>
       <c r="S23">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U23">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="V23">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W23">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="X23">
         <v>11</v>
       </c>
       <c r="Y23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z23">
         <v>32</v>
       </c>
       <c r="AA23">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AB23">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AC23">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD23">
         <v>20</v>
       </c>
       <c r="AE23">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG23">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH23">
         <v>26</v>
       </c>
       <c r="AI23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AJ23">
+        <v>25</v>
+      </c>
+      <c r="AK23">
         <v>29</v>
-      </c>
-      <c r="AK23">
-        <v>30</v>
       </c>
       <c r="AL23">
         <v>55</v>
@@ -6241,10 +6241,10 @@
         <v>180</v>
       </c>
       <c r="AN23">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO23">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AP23">
         <v>9</v>
@@ -6253,10 +6253,10 @@
         <v>11</v>
       </c>
       <c r="AR23">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AS23">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT23">
         <v>6.6</v>
@@ -6265,13 +6265,13 @@
         <v>7</v>
       </c>
       <c r="AV23">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="AX23">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY23">
         <v>10</v>
@@ -6280,28 +6280,28 @@
         <v>20</v>
       </c>
       <c r="BA23">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB23">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC23">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD23">
         <v>44</v>
       </c>
       <c r="BE23">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF23">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG23">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BH23">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BI23">
         <v>2.7</v>
@@ -6316,43 +6316,43 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN23">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO23">
         <v>3.65</v>
       </c>
       <c r="BP23">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BQ23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BR23">
         <v>36</v>
       </c>
       <c r="BS23">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT23">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BU23">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV23">
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX23">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY23">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BZ23">
         <v>1000</v>
@@ -6417,16 +6417,16 @@
         <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S24">
         <v>2.44</v>
       </c>
       <c r="T24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
         <v>1.13</v>
@@ -6492,7 +6492,7 @@
         <v>19.5</v>
       </c>
       <c r="AQ24">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="AR24">
         <v>5.6</v>
@@ -6519,7 +6519,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA24">
         <v>5.6</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -463,7 +463,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 05:26:39</t>
+    <t>2026-07-29 07:34:29</t>
   </si>
 </sst>
 </file>
@@ -1057,58 +1057,58 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="G2">
         <v>9</v>
       </c>
       <c r="H2">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="I2">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="J2">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L2">
         <v>1.43</v>
       </c>
       <c r="M2">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q2">
+        <v>2.02</v>
+      </c>
+      <c r="R2">
+        <v>1.34</v>
+      </c>
+      <c r="S2">
+        <v>3.55</v>
+      </c>
+      <c r="T2">
         <v>2.04</v>
       </c>
-      <c r="R2">
-        <v>1.32</v>
-      </c>
-      <c r="S2">
-        <v>3.6</v>
-      </c>
-      <c r="T2">
-        <v>2.06</v>
-      </c>
       <c r="U2">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="V2">
-        <v>2.62</v>
+        <v>2.68</v>
       </c>
       <c r="W2">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1120,10 +1120,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AA2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AB2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC2">
         <v>10</v>
@@ -1132,7 +1132,7 @@
         <v>10.5</v>
       </c>
       <c r="AE2">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF2">
         <v>160</v>
@@ -1141,88 +1141,88 @@
         <v>32</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ2">
-        <v>330</v>
+        <v>290</v>
       </c>
       <c r="AK2">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AL2">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="AM2">
         <v>700</v>
       </c>
       <c r="AN2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AO2">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
       </c>
       <c r="AQ2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR2">
         <v>7.4</v>
       </c>
       <c r="AS2">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT2">
         <v>18.5</v>
       </c>
       <c r="AU2">
+        <v>8.6</v>
+      </c>
+      <c r="AV2">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AW2">
+        <v>15</v>
+      </c>
+      <c r="AX2">
+        <v>10</v>
+      </c>
+      <c r="AY2">
+        <v>23</v>
+      </c>
+      <c r="AZ2">
+        <v>21</v>
+      </c>
+      <c r="BA2">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB2">
+        <v>11.5</v>
+      </c>
+      <c r="BC2">
+        <v>11</v>
+      </c>
+      <c r="BD2">
+        <v>11</v>
+      </c>
+      <c r="BE2">
+        <v>11.5</v>
+      </c>
+      <c r="BF2">
+        <v>11.5</v>
+      </c>
+      <c r="BG2">
         <v>8.199999999999999</v>
       </c>
-      <c r="AV2">
-        <v>8.6</v>
-      </c>
-      <c r="AW2">
-        <v>15.5</v>
-      </c>
-      <c r="AX2">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY2">
-        <v>8</v>
-      </c>
-      <c r="AZ2">
-        <v>12</v>
-      </c>
-      <c r="BA2">
-        <v>9</v>
-      </c>
-      <c r="BB2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC2">
-        <v>9.4</v>
-      </c>
-      <c r="BD2">
-        <v>9.4</v>
-      </c>
-      <c r="BE2">
-        <v>15</v>
-      </c>
-      <c r="BF2">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG2">
-        <v>8.4</v>
-      </c>
       <c r="BH2">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
-        <v>2.94</v>
+        <v>2.74</v>
       </c>
       <c r="BJ2">
         <v>12.5</v>
@@ -1246,7 +1246,7 @@
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BR2">
         <v>1000</v>
@@ -1258,7 +1258,7 @@
         <v>3.9</v>
       </c>
       <c r="BU2">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BV2">
         <v>10.5</v>
@@ -1267,16 +1267,16 @@
         <v>5.8</v>
       </c>
       <c r="BX2">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BY2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="CA2">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,73 +1299,73 @@
         <v>127</v>
       </c>
       <c r="F3">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="G3">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="I3">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J3">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="K3">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="L3">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M3">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="N3">
+        <v>2.42</v>
+      </c>
+      <c r="O3">
+        <v>1.67</v>
+      </c>
+      <c r="P3">
+        <v>1.46</v>
+      </c>
+      <c r="Q3">
+        <v>2.9</v>
+      </c>
+      <c r="R3">
+        <v>1.16</v>
+      </c>
+      <c r="S3">
+        <v>6.2</v>
+      </c>
+      <c r="T3">
         <v>2.24</v>
       </c>
-      <c r="O3">
+      <c r="U3">
         <v>1.69</v>
       </c>
-      <c r="P3">
-        <v>1.45</v>
-      </c>
-      <c r="Q3">
-        <v>2.84</v>
-      </c>
-      <c r="R3">
-        <v>1.15</v>
-      </c>
-      <c r="S3">
-        <v>6</v>
-      </c>
-      <c r="T3">
-        <v>2.28</v>
-      </c>
-      <c r="U3">
-        <v>1.62</v>
-      </c>
       <c r="V3">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W3">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X3">
+        <v>7.6</v>
+      </c>
+      <c r="Y3">
+        <v>8.6</v>
+      </c>
+      <c r="Z3">
+        <v>21</v>
+      </c>
+      <c r="AA3">
+        <v>85</v>
+      </c>
+      <c r="AB3">
         <v>8.4</v>
-      </c>
-      <c r="Y3">
-        <v>8.4</v>
-      </c>
-      <c r="Z3">
-        <v>19</v>
-      </c>
-      <c r="AA3">
-        <v>60</v>
-      </c>
-      <c r="AB3">
-        <v>9.199999999999999</v>
       </c>
       <c r="AC3">
         <v>7.4</v>
@@ -1374,19 +1374,19 @@
         <v>15</v>
       </c>
       <c r="AE3">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AF3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI3">
-        <v>85</v>
+        <v>270</v>
       </c>
       <c r="AJ3">
         <v>65</v>
@@ -1395,109 +1395,109 @@
         <v>55</v>
       </c>
       <c r="AL3">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="AM3">
         <v>500</v>
       </c>
       <c r="AN3">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="AO3">
         <v>600</v>
       </c>
       <c r="AP3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ3">
         <v>6.8</v>
       </c>
       <c r="AR3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AS3">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AT3">
         <v>7</v>
       </c>
       <c r="AU3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AV3">
+        <v>12.5</v>
+      </c>
+      <c r="AW3">
+        <v>8.4</v>
+      </c>
+      <c r="AX3">
+        <v>16</v>
+      </c>
+      <c r="AY3">
         <v>12</v>
       </c>
-      <c r="AW3">
-        <v>6.6</v>
-      </c>
-      <c r="AX3">
-        <v>15.5</v>
-      </c>
-      <c r="AY3">
+      <c r="AZ3">
+        <v>20</v>
+      </c>
+      <c r="BA3">
+        <v>9</v>
+      </c>
+      <c r="BB3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC3">
+        <v>18</v>
+      </c>
+      <c r="BD3">
+        <v>9</v>
+      </c>
+      <c r="BE3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG3">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BH3">
+        <v>2.58</v>
+      </c>
+      <c r="BI3">
+        <v>2.1</v>
+      </c>
+      <c r="BJ3">
         <v>12.5</v>
       </c>
-      <c r="AZ3">
-        <v>19.5</v>
-      </c>
-      <c r="BA3">
-        <v>6.8</v>
-      </c>
-      <c r="BB3">
-        <v>6.8</v>
-      </c>
-      <c r="BC3">
-        <v>6.6</v>
-      </c>
-      <c r="BD3">
-        <v>7</v>
-      </c>
-      <c r="BE3">
-        <v>7.4</v>
-      </c>
-      <c r="BF3">
-        <v>6.8</v>
-      </c>
-      <c r="BG3">
-        <v>6.8</v>
-      </c>
-      <c r="BH3">
-        <v>2.54</v>
-      </c>
-      <c r="BI3">
-        <v>2.08</v>
-      </c>
-      <c r="BJ3">
-        <v>13</v>
-      </c>
       <c r="BK3">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BN3">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BO3">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BQ3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BR3">
         <v>1000</v>
       </c>
       <c r="BS3">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BT3">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BU3">
         <v>4.4</v>
@@ -1506,19 +1506,19 @@
         <v>32</v>
       </c>
       <c r="BW3">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY3">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ3">
         <v>1000</v>
       </c>
       <c r="CA3">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB3" t="s">
         <v>149</v>
@@ -1541,70 +1541,70 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="G4">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H4">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I4">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="J4">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K4">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L4">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="M4">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N4">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O4">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P4">
         <v>1.53</v>
       </c>
       <c r="Q4">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="R4">
         <v>1.19</v>
       </c>
       <c r="S4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="T4">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U4">
         <v>1.78</v>
       </c>
       <c r="V4">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W4">
         <v>1.34</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4">
         <v>7.8</v>
       </c>
       <c r="Z4">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AA4">
-        <v>150</v>
+        <v>85</v>
       </c>
       <c r="AB4">
         <v>10.5</v>
@@ -1616,25 +1616,25 @@
         <v>13</v>
       </c>
       <c r="AE4">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF4">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AG4">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AH4">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI4">
         <v>210</v>
       </c>
       <c r="AJ4">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AK4">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AL4">
         <v>500</v>
@@ -1649,34 +1649,34 @@
         <v>110</v>
       </c>
       <c r="AP4">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR4">
         <v>11</v>
       </c>
       <c r="AS4">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU4">
         <v>6</v>
       </c>
       <c r="AV4">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AW4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX4">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AY4">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AZ4">
         <v>19</v>
@@ -1685,25 +1685,25 @@
         <v>9</v>
       </c>
       <c r="BB4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC4">
         <v>9</v>
       </c>
       <c r="BD4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE4">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG4">
         <v>8.4</v>
       </c>
       <c r="BH4">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BI4">
         <v>2.28</v>
@@ -1712,13 +1712,13 @@
         <v>12</v>
       </c>
       <c r="BK4">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN4">
         <v>6.8</v>
@@ -1736,7 +1736,7 @@
         <v>1000</v>
       </c>
       <c r="BS4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT4">
         <v>5.3</v>
@@ -1748,19 +1748,19 @@
         <v>23</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>1000</v>
       </c>
       <c r="BY4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4">
         <v>1000</v>
       </c>
       <c r="CA4">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1783,46 +1783,46 @@
         <v>129</v>
       </c>
       <c r="F5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
         <v>4.1</v>
       </c>
       <c r="J5">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K5">
         <v>2.98</v>
       </c>
       <c r="L5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="M5">
         <v>1.18</v>
       </c>
       <c r="N5">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="P5">
         <v>1.39</v>
       </c>
       <c r="Q5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
         <v>1.13</v>
       </c>
       <c r="S5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>2.54</v>
@@ -1834,13 +1834,13 @@
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X5">
         <v>6.6</v>
       </c>
       <c r="Y5">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z5">
         <v>26</v>
@@ -1849,7 +1849,7 @@
         <v>110</v>
       </c>
       <c r="AB5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
@@ -1867,25 +1867,25 @@
         <v>14</v>
       </c>
       <c r="AH5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AI5">
         <v>490</v>
       </c>
       <c r="AJ5">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK5">
+        <v>95</v>
+      </c>
+      <c r="AL5">
         <v>100</v>
-      </c>
-      <c r="AL5">
-        <v>200</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AO5">
         <v>490</v>
@@ -1900,16 +1900,16 @@
         <v>22</v>
       </c>
       <c r="AS5">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AT5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU5">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW5">
         <v>70</v>
@@ -1945,7 +1945,7 @@
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="BI5">
         <v>2.04</v>
@@ -1954,13 +1954,13 @@
         <v>13.5</v>
       </c>
       <c r="BK5">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BN5">
         <v>5.2</v>
@@ -1972,13 +1972,13 @@
         <v>25</v>
       </c>
       <c r="BQ5">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR5">
         <v>1000</v>
       </c>
       <c r="BS5">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>7.2</v>
@@ -1990,19 +1990,19 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ5">
         <v>1000</v>
       </c>
       <c r="CA5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB5" t="s">
         <v>149</v>
@@ -2031,13 +2031,13 @@
         <v>1.31</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I6">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J6">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -2049,31 +2049,31 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="O6">
         <v>1.08</v>
       </c>
       <c r="P6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q6">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="R6">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="S6">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="T6">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W6">
         <v>4.1</v>
@@ -2085,7 +2085,7 @@
         <v>70</v>
       </c>
       <c r="Z6">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="AA6">
         <v>370</v>
@@ -2100,7 +2100,7 @@
         <v>44</v>
       </c>
       <c r="AE6">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AF6">
         <v>15</v>
@@ -2109,10 +2109,10 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>230</v>
+        <v>75</v>
       </c>
       <c r="AJ6">
         <v>14.5</v>
@@ -2130,19 +2130,19 @@
         <v>2.9</v>
       </c>
       <c r="AO6">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AP6">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="AQ6">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="AR6">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="AS6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT6">
         <v>17.5</v>
@@ -2151,22 +2151,22 @@
         <v>18</v>
       </c>
       <c r="AV6">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AW6">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="AX6">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY6">
         <v>11</v>
       </c>
       <c r="AZ6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2178,13 +2178,13 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BF6">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>46</v>
       </c>
       <c r="BH6">
         <v>6.6</v>
@@ -2196,13 +2196,13 @@
         <v>10.5</v>
       </c>
       <c r="BK6">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BN6">
         <v>4.8</v>
@@ -2220,10 +2220,10 @@
         <v>16.5</v>
       </c>
       <c r="BS6">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT6">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU6">
         <v>6.8</v>
@@ -2267,22 +2267,22 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="G7">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H7">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I7">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J7">
         <v>4.6</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L7">
         <v>1.22</v>
@@ -2297,22 +2297,22 @@
         <v>1.13</v>
       </c>
       <c r="P7">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q7">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R7">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="S7">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="T7">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="U7">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2345,49 +2345,49 @@
         <v>40</v>
       </c>
       <c r="AF7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH7">
         <v>16</v>
       </c>
       <c r="AI7">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ7">
         <v>22</v>
       </c>
       <c r="AK7">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM7">
         <v>48</v>
       </c>
       <c r="AN7">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AO7">
+        <v>23</v>
+      </c>
+      <c r="AP7">
         <v>22</v>
       </c>
-      <c r="AP7">
-        <v>12</v>
-      </c>
       <c r="AQ7">
-        <v>15.5</v>
+        <v>25</v>
       </c>
       <c r="AR7">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="AS7">
         <v>55</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AU7">
         <v>10.5</v>
@@ -2396,10 +2396,10 @@
         <v>15.5</v>
       </c>
       <c r="AW7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX7">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY7">
         <v>9.800000000000001</v>
@@ -2408,25 +2408,25 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB7">
         <v>16</v>
       </c>
       <c r="BC7">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="BE7">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BF7">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG7">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BH7">
         <v>5.6</v>
@@ -2450,13 +2450,13 @@
         <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BP7">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ7">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="BR7">
         <v>18.5</v>
@@ -2465,19 +2465,19 @@
         <v>6.6</v>
       </c>
       <c r="BT7">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU7">
         <v>4.7</v>
       </c>
       <c r="BV7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BW7">
         <v>7.4</v>
       </c>
       <c r="BX7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BY7">
         <v>7.6</v>
@@ -2509,226 +2509,226 @@
         <v>132</v>
       </c>
       <c r="F8">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G8">
         <v>3.35</v>
       </c>
       <c r="H8">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="I8">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J8">
         <v>4.5</v>
       </c>
       <c r="K8">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L8">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="M8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O8">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="P8">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.46</v>
       </c>
       <c r="S8">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="U8">
-        <v>1.11</v>
+        <v>3.75</v>
       </c>
       <c r="V8">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="W8">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X8">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="Y8">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="Z8">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="AA8">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AC8">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AD8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AF8">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AG8">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH8">
         <v>14.5</v>
       </c>
       <c r="AI8">
+        <v>19.5</v>
+      </c>
+      <c r="AJ8">
+        <v>150</v>
+      </c>
+      <c r="AK8">
+        <v>34</v>
+      </c>
+      <c r="AL8">
+        <v>34</v>
+      </c>
+      <c r="AM8">
+        <v>32</v>
+      </c>
+      <c r="AN8">
+        <v>11</v>
+      </c>
+      <c r="AO8">
+        <v>5.5</v>
+      </c>
+      <c r="AP8">
+        <v>29</v>
+      </c>
+      <c r="AQ8">
+        <v>24</v>
+      </c>
+      <c r="AR8">
+        <v>22</v>
+      </c>
+      <c r="AS8">
+        <v>22</v>
+      </c>
+      <c r="AT8">
+        <v>30</v>
+      </c>
+      <c r="AU8">
+        <v>14</v>
+      </c>
+      <c r="AV8">
+        <v>12</v>
+      </c>
+      <c r="AW8">
+        <v>15.5</v>
+      </c>
+      <c r="AX8">
+        <v>36</v>
+      </c>
+      <c r="AY8">
+        <v>16</v>
+      </c>
+      <c r="AZ8">
+        <v>11.5</v>
+      </c>
+      <c r="BA8">
+        <v>16</v>
+      </c>
+      <c r="BB8">
+        <v>38</v>
+      </c>
+      <c r="BC8">
         <v>21</v>
       </c>
-      <c r="AJ8">
-        <v>500</v>
-      </c>
-      <c r="AK8">
-        <v>29</v>
-      </c>
-      <c r="AL8">
-        <v>28</v>
-      </c>
-      <c r="AM8">
-        <v>580</v>
-      </c>
-      <c r="AN8">
-        <v>11.5</v>
-      </c>
-      <c r="AO8">
-        <v>6.2</v>
-      </c>
-      <c r="AP8">
-        <v>8</v>
-      </c>
-      <c r="AQ8">
-        <v>17.5</v>
-      </c>
-      <c r="AR8">
-        <v>18.5</v>
-      </c>
-      <c r="AS8">
-        <v>13.5</v>
-      </c>
-      <c r="AT8">
-        <v>14</v>
-      </c>
-      <c r="AU8">
-        <v>13</v>
-      </c>
-      <c r="AV8">
-        <v>11.5</v>
-      </c>
-      <c r="AW8">
-        <v>16</v>
-      </c>
-      <c r="AX8">
-        <v>28</v>
-      </c>
-      <c r="AY8">
-        <v>14.5</v>
-      </c>
-      <c r="AZ8">
-        <v>12</v>
-      </c>
-      <c r="BA8">
-        <v>17.5</v>
-      </c>
-      <c r="BB8">
-        <v>8</v>
-      </c>
-      <c r="BC8">
-        <v>22</v>
-      </c>
       <c r="BD8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BE8">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BF8">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG8">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="BH8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BI8">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BJ8">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BK8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BO8">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BP8">
         <v>21</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="BT8">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BV8">
         <v>13</v>
       </c>
       <c r="BW8">
+        <v>5.7</v>
+      </c>
+      <c r="BX8">
+        <v>16</v>
+      </c>
+      <c r="BY8">
         <v>6.2</v>
       </c>
-      <c r="BX8">
-        <v>16.5</v>
-      </c>
-      <c r="BY8">
-        <v>6.8</v>
-      </c>
       <c r="BZ8">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CA8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CB8" t="s">
         <v>149</v>
@@ -2751,40 +2751,40 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="G9">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="H9">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I9">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J9">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="K9">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="L9">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M9">
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O9">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P9">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="Q9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R9">
         <v>1.75</v>
@@ -2793,55 +2793,55 @@
         <v>2.2</v>
       </c>
       <c r="T9">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="X9">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="Y9">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="Z9">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AA9">
-        <v>900</v>
+        <v>700</v>
       </c>
       <c r="AB9">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC9">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD9">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="AE9">
         <v>700</v>
       </c>
       <c r="AF9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG9">
         <v>11.5</v>
       </c>
       <c r="AH9">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AI9">
         <v>700</v>
       </c>
       <c r="AJ9">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK9">
         <v>15.5</v>
@@ -2853,10 +2853,10 @@
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO9">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AP9">
         <v>12.5</v>
@@ -2865,82 +2865,82 @@
         <v>12</v>
       </c>
       <c r="AR9">
+        <v>7.4</v>
+      </c>
+      <c r="AS9">
         <v>8</v>
       </c>
-      <c r="AS9">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AT9">
+        <v>11</v>
+      </c>
+      <c r="AU9">
         <v>10.5</v>
       </c>
-      <c r="AU9">
-        <v>9.4</v>
-      </c>
       <c r="AV9">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AW9">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AX9">
         <v>10</v>
       </c>
       <c r="AY9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA9">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="BB9">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC9">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD9">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE9">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BF9">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BG9">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH9">
         <v>5.1</v>
       </c>
       <c r="BI9">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BJ9">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BK9">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="BP9">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BQ9">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BR9">
         <v>19.5</v>
@@ -2949,16 +2949,16 @@
         <v>6.6</v>
       </c>
       <c r="BT9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BU9">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
         <v>1000</v>
       </c>
       <c r="BW9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX9">
         <v>1000</v>
@@ -2967,10 +2967,10 @@
         <v>8</v>
       </c>
       <c r="BZ9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CA9">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="CB9" t="s">
         <v>149</v>
@@ -2999,16 +2999,16 @@
         <v>3.55</v>
       </c>
       <c r="H10">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I10">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J10">
         <v>3.05</v>
       </c>
       <c r="K10">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L10">
         <v>1.5</v>
@@ -3017,16 +3017,16 @@
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O10">
         <v>1.42</v>
       </c>
       <c r="P10">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q10">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R10">
         <v>1.27</v>
@@ -3035,31 +3035,31 @@
         <v>4.2</v>
       </c>
       <c r="T10">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="U10">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="V10">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y10">
         <v>9.4</v>
       </c>
       <c r="Z10">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA10">
         <v>40</v>
       </c>
       <c r="AB10">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
@@ -3068,40 +3068,40 @@
         <v>12.5</v>
       </c>
       <c r="AE10">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF10">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AG10">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH10">
         <v>19</v>
       </c>
       <c r="AI10">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ10">
         <v>150</v>
       </c>
       <c r="AK10">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AL10">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AM10">
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ10">
         <v>8</v>
@@ -3110,10 +3110,10 @@
         <v>13.5</v>
       </c>
       <c r="AS10">
-        <v>8.6</v>
+        <v>18</v>
       </c>
       <c r="AT10">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10">
         <v>6.2</v>
@@ -3122,10 +3122,10 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>10.5</v>
+        <v>21</v>
       </c>
       <c r="AX10">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AY10">
         <v>12.5</v>
@@ -3134,37 +3134,37 @@
         <v>16</v>
       </c>
       <c r="BA10">
+        <v>22</v>
+      </c>
+      <c r="BB10">
+        <v>21</v>
+      </c>
+      <c r="BC10">
         <v>36</v>
       </c>
-      <c r="BB10">
-        <v>9.4</v>
-      </c>
-      <c r="BC10">
-        <v>28</v>
-      </c>
       <c r="BD10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE10">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF10">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BG10">
-        <v>20</v>
+        <v>9.6</v>
       </c>
       <c r="BH10">
         <v>3.1</v>
       </c>
       <c r="BI10">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BL10">
         <v>1000</v>
@@ -3235,7 +3235,7 @@
         <v>135</v>
       </c>
       <c r="F11">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="G11">
         <v>3.1</v>
@@ -3244,16 +3244,16 @@
         <v>2.1</v>
       </c>
       <c r="I11">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="J11">
         <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L11">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="M11">
         <v>1.01</v>
@@ -3265,10 +3265,10 @@
         <v>1.06</v>
       </c>
       <c r="P11">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q11">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R11">
         <v>2.8</v>
@@ -3289,16 +3289,16 @@
         <v>1.48</v>
       </c>
       <c r="X11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="Y11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Z11">
         <v>36</v>
       </c>
       <c r="AA11">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB11">
         <v>50</v>
@@ -3325,7 +3325,7 @@
         <v>20</v>
       </c>
       <c r="AJ11">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AK11">
         <v>29</v>
@@ -3337,7 +3337,7 @@
         <v>34</v>
       </c>
       <c r="AN11">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AO11">
         <v>6.2</v>
@@ -3349,7 +3349,7 @@
         <v>5.5</v>
       </c>
       <c r="AR11">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="AS11">
         <v>5.5</v>
@@ -3358,46 +3358,46 @@
         <v>5.6</v>
       </c>
       <c r="AU11">
+        <v>16</v>
+      </c>
+      <c r="AV11">
         <v>13.5</v>
       </c>
-      <c r="AV11">
-        <v>11.5</v>
-      </c>
       <c r="AW11">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AX11">
         <v>5.6</v>
       </c>
       <c r="AY11">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AZ11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BA11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB11">
         <v>5.7</v>
       </c>
       <c r="BC11">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD11">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>19.5</v>
+        <v>10.5</v>
       </c>
       <c r="BF11">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BG11">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BH11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BI11">
         <v>6</v>
@@ -3409,16 +3409,16 @@
         <v>4.5</v>
       </c>
       <c r="BL11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BM11">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BN11">
         <v>8.800000000000001</v>
       </c>
       <c r="BO11">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BP11">
         <v>19</v>
@@ -3454,7 +3454,7 @@
         <v>7</v>
       </c>
       <c r="CA11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="CB11" t="s">
         <v>149</v>
@@ -3477,28 +3477,28 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G12">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="H12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I12">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
         <v>7.8</v>
@@ -3507,37 +3507,37 @@
         <v>1.11</v>
       </c>
       <c r="P12">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="Q12">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R12">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="S12">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="T12">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="U12">
         <v>3</v>
       </c>
       <c r="V12">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="X12">
         <v>46</v>
       </c>
       <c r="Y12">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Z12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA12">
         <v>170</v>
@@ -3555,7 +3555,7 @@
         <v>32</v>
       </c>
       <c r="AF12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12">
         <v>13.5</v>
@@ -3585,16 +3585,16 @@
         <v>15</v>
       </c>
       <c r="AP12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ12">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="AR12">
-        <v>6.6</v>
+        <v>15</v>
       </c>
       <c r="AS12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT12">
         <v>17.5</v>
@@ -3606,10 +3606,10 @@
         <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="AX12">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
@@ -3618,10 +3618,10 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="BB12">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BC12">
         <v>15</v>
@@ -3630,10 +3630,10 @@
         <v>18</v>
       </c>
       <c r="BE12">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BF12">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="BG12">
         <v>11.5</v>
@@ -3642,61 +3642,61 @@
         <v>6.2</v>
       </c>
       <c r="BI12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ12">
         <v>8.6</v>
       </c>
       <c r="BK12">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BL12">
         <v>55</v>
       </c>
       <c r="BM12">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BN12">
         <v>6.4</v>
       </c>
       <c r="BO12">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BP12">
         <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BR12">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BS12">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BT12">
         <v>8.199999999999999</v>
       </c>
       <c r="BU12">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV12">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BW12">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BX12">
         <v>24</v>
       </c>
       <c r="BY12">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BZ12">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="CB12" t="s">
         <v>149</v>
@@ -3719,226 +3719,226 @@
         <v>137</v>
       </c>
       <c r="F13">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="G13">
-        <v>2.74</v>
+        <v>3.35</v>
       </c>
       <c r="H13">
-        <v>2.4</v>
+        <v>2.06</v>
       </c>
       <c r="I13">
-        <v>2.66</v>
+        <v>2.26</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>1.1</v>
+        <v>6</v>
       </c>
       <c r="O13">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P13">
+        <v>3.75</v>
+      </c>
+      <c r="Q13">
+        <v>1.3</v>
+      </c>
+      <c r="R13">
+        <v>2.14</v>
+      </c>
+      <c r="S13">
+        <v>1.76</v>
+      </c>
+      <c r="T13">
+        <v>1.36</v>
+      </c>
+      <c r="U13">
         <v>3.2</v>
       </c>
-      <c r="Q13">
-        <v>1.33</v>
-      </c>
-      <c r="R13">
-        <v>2</v>
-      </c>
-      <c r="S13">
-        <v>1.83</v>
-      </c>
-      <c r="T13">
-        <v>1.37</v>
-      </c>
-      <c r="U13">
-        <v>3.15</v>
-      </c>
       <c r="V13">
-        <v>1.61</v>
+        <v>1.8</v>
       </c>
       <c r="W13">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="X13">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="Y13">
+        <v>27</v>
+      </c>
+      <c r="Z13">
         <v>26</v>
       </c>
-      <c r="Z13">
-        <v>28</v>
-      </c>
       <c r="AA13">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AB13">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AC13">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD13">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AF13">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="AG13">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AH13">
         <v>15</v>
       </c>
       <c r="AI13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AJ13">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AK13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AL13">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AM13">
         <v>38</v>
       </c>
       <c r="AN13">
+        <v>12.5</v>
+      </c>
+      <c r="AO13">
+        <v>7.2</v>
+      </c>
+      <c r="AP13">
+        <v>7.4</v>
+      </c>
+      <c r="AQ13">
+        <v>6.6</v>
+      </c>
+      <c r="AR13">
         <v>10</v>
       </c>
-      <c r="AO13">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AP13">
-        <v>7.6</v>
-      </c>
-      <c r="AQ13">
-        <v>6.8</v>
-      </c>
-      <c r="AR13">
-        <v>6.8</v>
-      </c>
       <c r="AS13">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT13">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AU13">
         <v>7</v>
       </c>
       <c r="AV13">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AW13">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX13">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY13">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AZ13">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BA13">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13">
         <v>7.4</v>
       </c>
       <c r="BC13">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD13">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE13">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BF13">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BG13">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BH13">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BI13">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BJ13">
         <v>8.4</v>
       </c>
       <c r="BK13">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BL13">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BM13">
+        <v>7.6</v>
+      </c>
+      <c r="BN13">
         <v>8</v>
       </c>
-      <c r="BN13">
-        <v>7</v>
-      </c>
       <c r="BO13">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BP13">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BQ13">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BR13">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BS13">
         <v>6.4</v>
       </c>
       <c r="BT13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BV13">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BW13">
+        <v>5.5</v>
+      </c>
+      <c r="BX13">
+        <v>18.5</v>
+      </c>
+      <c r="BY13">
         <v>6</v>
       </c>
-      <c r="BX13">
-        <v>21</v>
-      </c>
-      <c r="BY13">
-        <v>6.4</v>
-      </c>
       <c r="BZ13">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CA13">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="CB13" t="s">
         <v>149</v>
@@ -3967,46 +3967,46 @@
         <v>2.36</v>
       </c>
       <c r="H14">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="I14">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K14">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="M14">
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O14">
         <v>1.09</v>
       </c>
       <c r="P14">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="Q14">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="R14">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="T14">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="U14">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -4021,7 +4021,7 @@
         <v>60</v>
       </c>
       <c r="Z14">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA14">
         <v>210</v>
@@ -4030,7 +4030,7 @@
         <v>48</v>
       </c>
       <c r="AC14">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AD14">
         <v>17</v>
@@ -4051,7 +4051,7 @@
         <v>26</v>
       </c>
       <c r="AJ14">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="AK14">
         <v>21</v>
@@ -4063,37 +4063,37 @@
         <v>200</v>
       </c>
       <c r="AN14">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AO14">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AP14">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AQ14">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AR14">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="AS14">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AT14">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="AU14">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV14">
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AX14">
-        <v>6.8</v>
+        <v>20</v>
       </c>
       <c r="AY14">
         <v>11.5</v>
@@ -4114,7 +4114,7 @@
         <v>17.5</v>
       </c>
       <c r="BE14">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BF14">
         <v>5.8</v>
@@ -4123,52 +4123,52 @@
         <v>8.6</v>
       </c>
       <c r="BH14">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BI14">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BK14">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BN14">
         <v>6.8</v>
       </c>
       <c r="BO14">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BP14">
         <v>14.5</v>
       </c>
       <c r="BQ14">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BR14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BS14">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BT14">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BV14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BW14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX14">
         <v>21</v>
@@ -4177,10 +4177,10 @@
         <v>6.6</v>
       </c>
       <c r="BZ14">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="CA14">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4203,13 +4203,13 @@
         <v>139</v>
       </c>
       <c r="F15">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H15">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I15">
         <v>3.1</v>
@@ -4218,34 +4218,34 @@
         <v>3.75</v>
       </c>
       <c r="K15">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M15">
         <v>1.04</v>
       </c>
       <c r="N15">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O15">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="R15">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="S15">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U15">
         <v>2.54</v>
@@ -4254,19 +4254,19 @@
         <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X15">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Y15">
         <v>16</v>
       </c>
       <c r="Z15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA15">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AB15">
         <v>15.5</v>
@@ -4275,7 +4275,7 @@
         <v>9.6</v>
       </c>
       <c r="AD15">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE15">
         <v>32</v>
@@ -4296,7 +4296,7 @@
         <v>38</v>
       </c>
       <c r="AK15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL15">
         <v>34</v>
@@ -4311,13 +4311,13 @@
         <v>19</v>
       </c>
       <c r="AP15">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AQ15">
         <v>14</v>
       </c>
       <c r="AR15">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS15">
         <v>32</v>
@@ -4326,7 +4326,7 @@
         <v>12.5</v>
       </c>
       <c r="AU15">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV15">
         <v>11.5</v>
@@ -4344,7 +4344,7 @@
         <v>13</v>
       </c>
       <c r="BA15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB15">
         <v>23</v>
@@ -4353,7 +4353,7 @@
         <v>20</v>
       </c>
       <c r="BD15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE15">
         <v>46</v>
@@ -4365,7 +4365,7 @@
         <v>15.5</v>
       </c>
       <c r="BH15">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BI15">
         <v>3.8</v>
@@ -4374,13 +4374,13 @@
         <v>8.6</v>
       </c>
       <c r="BK15">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN15">
         <v>5.8</v>
@@ -4392,13 +4392,13 @@
         <v>970</v>
       </c>
       <c r="BQ15">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BT15">
         <v>6.6</v>
@@ -4410,19 +4410,19 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ15">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="s">
         <v>149</v>
@@ -4448,13 +4448,13 @@
         <v>2.3</v>
       </c>
       <c r="G16">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="I16">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J16">
         <v>4.1</v>
@@ -4475,7 +4475,7 @@
         <v>1.16</v>
       </c>
       <c r="P16">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="Q16">
         <v>1.49</v>
@@ -4487,22 +4487,22 @@
         <v>2.24</v>
       </c>
       <c r="T16">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="U16">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="V16">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W16">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X16">
         <v>32</v>
       </c>
       <c r="Y16">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Z16">
         <v>28</v>
@@ -4511,22 +4511,22 @@
         <v>55</v>
       </c>
       <c r="AB16">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC16">
         <v>11</v>
       </c>
       <c r="AD16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE16">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF16">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AG16">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH16">
         <v>15</v>
@@ -4541,31 +4541,31 @@
         <v>21</v>
       </c>
       <c r="AL16">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AM16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AN16">
         <v>10.5</v>
       </c>
       <c r="AO16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AP16">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AQ16">
         <v>17.5</v>
       </c>
       <c r="AR16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AT16">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AU16">
         <v>9</v>
@@ -4577,7 +4577,7 @@
         <v>21</v>
       </c>
       <c r="AX16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AY16">
         <v>10.5</v>
@@ -4586,10 +4586,10 @@
         <v>12</v>
       </c>
       <c r="BA16">
+        <v>23</v>
+      </c>
+      <c r="BB16">
         <v>24</v>
-      </c>
-      <c r="BB16">
-        <v>23</v>
       </c>
       <c r="BC16">
         <v>17</v>
@@ -4598,7 +4598,7 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BF16">
         <v>8.800000000000001</v>
@@ -4607,64 +4607,64 @@
         <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BI16">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="BJ16">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK16">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN16">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="BP16">
         <v>16</v>
       </c>
       <c r="BQ16">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BR16">
         <v>22</v>
       </c>
       <c r="BS16">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BT16">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU16">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BV16">
         <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX16">
         <v>25</v>
       </c>
       <c r="BY16">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BZ16">
         <v>14</v>
       </c>
       <c r="CA16">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="CB16" t="s">
         <v>149</v>
@@ -4693,10 +4693,10 @@
         <v>2.42</v>
       </c>
       <c r="H17">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I17">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J17">
         <v>2.96</v>
@@ -4714,7 +4714,7 @@
         <v>2.36</v>
       </c>
       <c r="O17">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="P17">
         <v>1.43</v>
@@ -4723,19 +4723,19 @@
         <v>3.25</v>
       </c>
       <c r="R17">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S17">
         <v>7.4</v>
       </c>
       <c r="T17">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="U17">
         <v>1.64</v>
       </c>
       <c r="V17">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
         <v>1.7</v>
@@ -4747,19 +4747,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA17">
         <v>110</v>
       </c>
       <c r="AB17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC17">
         <v>7.2</v>
       </c>
       <c r="AD17">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE17">
         <v>80</v>
@@ -4777,7 +4777,7 @@
         <v>490</v>
       </c>
       <c r="AJ17">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK17">
         <v>40</v>
@@ -4792,7 +4792,7 @@
         <v>46</v>
       </c>
       <c r="AO17">
-        <v>140</v>
+        <v>490</v>
       </c>
       <c r="AP17">
         <v>6.4</v>
@@ -4828,7 +4828,7 @@
         <v>28</v>
       </c>
       <c r="BA17">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="BB17">
         <v>32</v>
@@ -4864,7 +4864,7 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>2.2</v>
+        <v>20</v>
       </c>
       <c r="BN17">
         <v>4.8</v>
@@ -4888,13 +4888,13 @@
         <v>7</v>
       </c>
       <c r="BU17">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BV17">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>2.1</v>
+        <v>15</v>
       </c>
       <c r="BX17">
         <v>1000</v>
@@ -4903,7 +4903,7 @@
         <v>2.14</v>
       </c>
       <c r="BZ17">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
         <v>2.14</v>
@@ -4929,64 +4929,64 @@
         <v>142</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="G18">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="H18">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="I18">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L18">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="M18">
         <v>1.09</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P18">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q18">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R18">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T18">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W18">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="X18">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y18">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="Z18">
         <v>500</v>
@@ -4995,160 +4995,160 @@
         <v>900</v>
       </c>
       <c r="AB18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC18">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD18">
-        <v>26</v>
+        <v>140</v>
       </c>
       <c r="AE18">
         <v>700</v>
       </c>
       <c r="AF18">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG18">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH18">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI18">
         <v>700</v>
       </c>
       <c r="AJ18">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AK18">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL18">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AM18">
         <v>580</v>
       </c>
       <c r="AN18">
+        <v>15</v>
+      </c>
+      <c r="AO18">
+        <v>230</v>
+      </c>
+      <c r="AP18">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18">
+        <v>15.5</v>
+      </c>
+      <c r="AR18">
+        <v>24</v>
+      </c>
+      <c r="AS18">
+        <v>8.6</v>
+      </c>
+      <c r="AT18">
+        <v>5.8</v>
+      </c>
+      <c r="AU18">
+        <v>7.6</v>
+      </c>
+      <c r="AV18">
+        <v>12</v>
+      </c>
+      <c r="AW18">
+        <v>8.6</v>
+      </c>
+      <c r="AX18">
+        <v>7.6</v>
+      </c>
+      <c r="AY18">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ18">
+        <v>21</v>
+      </c>
+      <c r="BA18">
+        <v>8.4</v>
+      </c>
+      <c r="BB18">
+        <v>14</v>
+      </c>
+      <c r="BC18">
         <v>17.5</v>
       </c>
-      <c r="AO18">
-        <v>200</v>
-      </c>
-      <c r="AP18">
-        <v>4.6</v>
-      </c>
-      <c r="AQ18">
-        <v>5.3</v>
-      </c>
-      <c r="AR18">
-        <v>6.6</v>
-      </c>
-      <c r="AS18">
-        <v>7.4</v>
-      </c>
-      <c r="AT18">
-        <v>3.7</v>
-      </c>
-      <c r="AU18">
-        <v>4.1</v>
-      </c>
-      <c r="AV18">
-        <v>5.9</v>
-      </c>
-      <c r="AW18">
-        <v>7.2</v>
-      </c>
-      <c r="AX18">
-        <v>4.4</v>
-      </c>
-      <c r="AY18">
-        <v>4.6</v>
-      </c>
-      <c r="AZ18">
-        <v>6</v>
-      </c>
-      <c r="BA18">
-        <v>7.2</v>
-      </c>
-      <c r="BB18">
-        <v>5.6</v>
-      </c>
-      <c r="BC18">
-        <v>5.8</v>
-      </c>
       <c r="BD18">
-        <v>6.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE18">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF18">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG18">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH18">
         <v>3.15</v>
       </c>
       <c r="BI18">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ18">
         <v>12.5</v>
       </c>
       <c r="BK18">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.3</v>
+        <v>9.6</v>
       </c>
       <c r="BN18">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BO18">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="BP18">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BQ18">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BR18">
         <v>1000</v>
       </c>
       <c r="BS18">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BT18">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BU18">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BV18">
         <v>1000</v>
       </c>
       <c r="BW18">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX18">
         <v>1000</v>
       </c>
       <c r="BY18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BZ18">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="CA18">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB18" t="s">
         <v>149</v>
@@ -5174,13 +5174,13 @@
         <v>3.3</v>
       </c>
       <c r="G19">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="H19">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I19">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="J19">
         <v>3</v>
@@ -5195,31 +5195,31 @@
         <v>1.1</v>
       </c>
       <c r="N19">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O19">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P19">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q19">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R19">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S19">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T19">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U19">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W19">
         <v>1.39</v>
@@ -5228,25 +5228,25 @@
         <v>11.5</v>
       </c>
       <c r="Y19">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z19">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA19">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AB19">
         <v>12</v>
       </c>
       <c r="AC19">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD19">
         <v>12.5</v>
       </c>
       <c r="AE19">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF19">
         <v>23</v>
@@ -5273,19 +5273,19 @@
         <v>450</v>
       </c>
       <c r="AN19">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AO19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AP19">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ19">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR19">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AS19">
         <v>16</v>
@@ -5294,103 +5294,103 @@
         <v>10</v>
       </c>
       <c r="AU19">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV19">
         <v>10</v>
       </c>
       <c r="AW19">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AX19">
         <v>19</v>
       </c>
       <c r="AY19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ19">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BA19">
-        <v>8.4</v>
+        <v>25</v>
       </c>
       <c r="BB19">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC19">
+        <v>18.5</v>
+      </c>
+      <c r="BD19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF19">
         <v>8.6</v>
       </c>
-      <c r="BC19">
-        <v>8</v>
-      </c>
-      <c r="BD19">
-        <v>8.6</v>
-      </c>
-      <c r="BE19">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF19">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BG19">
-        <v>19.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH19">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI19">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="BJ19">
         <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>5.3</v>
+        <v>8.6</v>
       </c>
       <c r="BL19">
         <v>1000</v>
       </c>
       <c r="BM19">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN19">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO19">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BP19">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BQ19">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BR19">
         <v>44</v>
       </c>
       <c r="BS19">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT19">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BU19">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BV19">
         <v>22</v>
       </c>
       <c r="BW19">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BX19">
         <v>38</v>
       </c>
       <c r="BY19">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BZ19">
         <v>36</v>
       </c>
       <c r="CA19">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="CB19" t="s">
         <v>149</v>
@@ -5413,22 +5413,22 @@
         <v>144</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G20">
         <v>4.3</v>
       </c>
       <c r="H20">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I20">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J20">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K20">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L20">
         <v>1.6</v>
@@ -5449,7 +5449,7 @@
         <v>2.76</v>
       </c>
       <c r="R20">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S20">
         <v>5.8</v>
@@ -5458,40 +5458,40 @@
         <v>2.28</v>
       </c>
       <c r="U20">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V20">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W20">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X20">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="Z20">
         <v>12.5</v>
       </c>
       <c r="AA20">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="AB20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC20">
         <v>7.8</v>
       </c>
       <c r="AD20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE20">
         <v>65</v>
       </c>
       <c r="AF20">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="AG20">
         <v>500</v>
@@ -5500,13 +5500,13 @@
         <v>30</v>
       </c>
       <c r="AI20">
-        <v>500</v>
+        <v>460</v>
       </c>
       <c r="AJ20">
         <v>900</v>
       </c>
       <c r="AK20">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="AL20">
         <v>540</v>
@@ -5515,7 +5515,7 @@
         <v>500</v>
       </c>
       <c r="AN20">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO20">
         <v>90</v>
@@ -5524,13 +5524,13 @@
         <v>7.4</v>
       </c>
       <c r="AQ20">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR20">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS20">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="AT20">
         <v>9.6</v>
@@ -5542,10 +5542,10 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>9.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="AX20">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY20">
         <v>16</v>
@@ -5554,43 +5554,43 @@
         <v>21</v>
       </c>
       <c r="BA20">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BB20">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BC20">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="BD20">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BE20">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BF20">
-        <v>11.5</v>
+        <v>30</v>
       </c>
       <c r="BG20">
-        <v>9.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BH20">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="BI20">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="BJ20">
         <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN20">
         <v>7.2</v>
@@ -5602,37 +5602,37 @@
         <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BR20">
         <v>1000</v>
       </c>
       <c r="BS20">
-        <v>14.5</v>
+        <v>2.3</v>
       </c>
       <c r="BT20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BW20">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="CB20" t="s">
         <v>149</v>
@@ -5658,7 +5658,7 @@
         <v>1.74</v>
       </c>
       <c r="G21">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H21">
         <v>5.7</v>
@@ -5667,13 +5667,13 @@
         <v>5.8</v>
       </c>
       <c r="J21">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K21">
         <v>3.95</v>
       </c>
       <c r="L21">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M21">
         <v>1.08</v>
@@ -5685,7 +5685,7 @@
         <v>1.35</v>
       </c>
       <c r="P21">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q21">
         <v>2.06</v>
@@ -5697,7 +5697,7 @@
         <v>3.75</v>
       </c>
       <c r="T21">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U21">
         <v>1.98</v>
@@ -5706,10 +5706,10 @@
         <v>1.2</v>
       </c>
       <c r="W21">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X21">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y21">
         <v>17.5</v>
@@ -5733,7 +5733,7 @@
         <v>200</v>
       </c>
       <c r="AF21">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG21">
         <v>9.4</v>
@@ -5745,7 +5745,7 @@
         <v>90</v>
       </c>
       <c r="AJ21">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AK21">
         <v>19</v>
@@ -5754,7 +5754,7 @@
         <v>40</v>
       </c>
       <c r="AM21">
-        <v>140</v>
+        <v>380</v>
       </c>
       <c r="AN21">
         <v>12.5</v>
@@ -5763,7 +5763,7 @@
         <v>110</v>
       </c>
       <c r="AP21">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ21">
         <v>16</v>
@@ -5772,10 +5772,10 @@
         <v>38</v>
       </c>
       <c r="AS21">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT21">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU21">
         <v>8</v>
@@ -5784,7 +5784,7 @@
         <v>20</v>
       </c>
       <c r="AW21">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AX21">
         <v>9</v>
@@ -5796,19 +5796,19 @@
         <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BB21">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD21">
         <v>36</v>
       </c>
       <c r="BE21">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BF21">
         <v>11</v>
@@ -5900,19 +5900,19 @@
         <v>4.6</v>
       </c>
       <c r="G22">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="H22">
+        <v>1.93</v>
+      </c>
+      <c r="I22">
         <v>1.95</v>
       </c>
-      <c r="I22">
-        <v>1.96</v>
-      </c>
       <c r="J22">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K22">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L22">
         <v>1.44</v>
@@ -5921,16 +5921,16 @@
         <v>1.08</v>
       </c>
       <c r="N22">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O22">
         <v>1.35</v>
       </c>
       <c r="P22">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="Q22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R22">
         <v>1.34</v>
@@ -5948,7 +5948,7 @@
         <v>2.04</v>
       </c>
       <c r="W22">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X22">
         <v>13.5</v>
@@ -5963,22 +5963,22 @@
         <v>21</v>
       </c>
       <c r="AB22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AC22">
         <v>7.8</v>
       </c>
       <c r="AD22">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF22">
         <v>34</v>
       </c>
       <c r="AG22">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AH22">
         <v>19.5</v>
@@ -5993,10 +5993,10 @@
         <v>60</v>
       </c>
       <c r="AL22">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AM22">
-        <v>120</v>
+        <v>320</v>
       </c>
       <c r="AN22">
         <v>80</v>
@@ -6008,7 +6008,7 @@
         <v>12.5</v>
       </c>
       <c r="AQ22">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR22">
         <v>10</v>
@@ -6020,10 +6020,10 @@
         <v>14.5</v>
       </c>
       <c r="AU22">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV22">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22">
         <v>19</v>
@@ -6041,16 +6041,16 @@
         <v>34</v>
       </c>
       <c r="BB22">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="BC22">
         <v>50</v>
       </c>
       <c r="BD22">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BE22">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BF22">
         <v>60</v>
@@ -6068,16 +6068,16 @@
         <v>10.5</v>
       </c>
       <c r="BK22">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL22">
         <v>1000</v>
       </c>
       <c r="BM22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN22">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BO22">
         <v>5.5</v>
@@ -6086,13 +6086,13 @@
         <v>40</v>
       </c>
       <c r="BQ22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR22">
         <v>50</v>
       </c>
       <c r="BS22">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT22">
         <v>4.5</v>
@@ -6104,7 +6104,7 @@
         <v>14</v>
       </c>
       <c r="BW22">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="BX22">
         <v>30</v>
@@ -6139,19 +6139,19 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G23">
         <v>2.04</v>
       </c>
       <c r="H23">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I23">
         <v>4.7</v>
       </c>
       <c r="J23">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K23">
         <v>3.5</v>
@@ -6160,31 +6160,31 @@
         <v>1.52</v>
       </c>
       <c r="M23">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N23">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O23">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P23">
         <v>1.68</v>
       </c>
       <c r="Q23">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="R23">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S23">
         <v>4.7</v>
       </c>
       <c r="T23">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U23">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="V23">
         <v>1.27</v>
@@ -6196,7 +6196,7 @@
         <v>11</v>
       </c>
       <c r="Y23">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Z23">
         <v>32</v>
@@ -6205,10 +6205,10 @@
         <v>130</v>
       </c>
       <c r="AB23">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AC23">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD23">
         <v>20</v>
@@ -6235,7 +6235,7 @@
         <v>29</v>
       </c>
       <c r="AL23">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM23">
         <v>180</v>
@@ -6244,22 +6244,22 @@
         <v>24</v>
       </c>
       <c r="AO23">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP23">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR23">
-        <v>28</v>
+        <v>7.4</v>
       </c>
       <c r="AS23">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT23">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU23">
         <v>7</v>
@@ -6268,10 +6268,10 @@
         <v>16.5</v>
       </c>
       <c r="AW23">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AX23">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY23">
         <v>10</v>
@@ -6280,31 +6280,31 @@
         <v>20</v>
       </c>
       <c r="BA23">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="BB23">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC23">
         <v>22</v>
       </c>
       <c r="BD23">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE23">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF23">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BG23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BH23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BI23">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BJ23">
         <v>11</v>
@@ -6316,25 +6316,25 @@
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>10</v>
+        <v>2.48</v>
       </c>
       <c r="BN23">
         <v>4.4</v>
       </c>
       <c r="BO23">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="BP23">
         <v>15</v>
       </c>
       <c r="BQ23">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BR23">
         <v>36</v>
       </c>
       <c r="BS23">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT23">
         <v>8.199999999999999</v>
@@ -6346,19 +6346,19 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="CB23" t="s">
         <v>149</v>
@@ -6390,7 +6390,7 @@
         <v>7.4</v>
       </c>
       <c r="I24">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24">
         <v>5.1</v>
@@ -6402,7 +6402,7 @@
         <v>1.28</v>
       </c>
       <c r="M24">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N24">
         <v>5.8</v>
@@ -6414,7 +6414,7 @@
         <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R24">
         <v>1.64</v>
@@ -6423,16 +6423,16 @@
         <v>2.44</v>
       </c>
       <c r="T24">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U24">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
         <v>1.13</v>
       </c>
       <c r="W24">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X24">
         <v>32</v>
@@ -6441,106 +6441,106 @@
         <v>38</v>
       </c>
       <c r="Z24">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AA24">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="AB24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AC24">
         <v>15</v>
       </c>
       <c r="AD24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AE24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AF24">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG24">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH24">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AI24">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AJ24">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK24">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AL24">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM24">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN24">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AO24">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP24">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AQ24">
+        <v>4.7</v>
+      </c>
+      <c r="AR24">
+        <v>5</v>
+      </c>
+      <c r="AS24">
+        <v>5.3</v>
+      </c>
+      <c r="AT24">
+        <v>9.6</v>
+      </c>
+      <c r="AU24">
+        <v>10.5</v>
+      </c>
+      <c r="AV24">
         <v>24</v>
       </c>
-      <c r="AR24">
-        <v>5.6</v>
-      </c>
-      <c r="AS24">
-        <v>5.9</v>
-      </c>
-      <c r="AT24">
-        <v>8.4</v>
-      </c>
-      <c r="AU24">
-        <v>10</v>
-      </c>
-      <c r="AV24">
-        <v>19.5</v>
-      </c>
       <c r="AW24">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AX24">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AY24">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ24">
         <v>18.5</v>
       </c>
       <c r="BA24">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB24">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BC24">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD24">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BE24">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BF24">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BG24">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="BH24">
         <v>4.7</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -463,7 +463,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 07:34:29</t>
+    <t>2026-07-29 09:42:01</t>
   </si>
 </sst>
 </file>
@@ -1057,226 +1057,226 @@
         <v>126</v>
       </c>
       <c r="F2">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>1.52</v>
+        <v>3.3</v>
       </c>
       <c r="I2">
+        <v>3.45</v>
+      </c>
+      <c r="J2">
         <v>1.59</v>
       </c>
-      <c r="J2">
-        <v>4</v>
-      </c>
       <c r="K2">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="L2">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="Q2">
-        <v>2.02</v>
+        <v>2.56</v>
       </c>
       <c r="R2">
-        <v>1.34</v>
+        <v>1.06</v>
       </c>
       <c r="S2">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="T2">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="V2">
-        <v>2.68</v>
+        <v>1.36</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AC2">
+        <v>1.7</v>
+      </c>
+      <c r="AD2">
+        <v>4.3</v>
+      </c>
+      <c r="AE2">
+        <v>970</v>
+      </c>
+      <c r="AF2">
+        <v>1000</v>
+      </c>
+      <c r="AG2">
+        <v>1000</v>
+      </c>
+      <c r="AH2">
+        <v>970</v>
+      </c>
+      <c r="AI2">
+        <v>1000</v>
+      </c>
+      <c r="AJ2">
+        <v>1000</v>
+      </c>
+      <c r="AK2">
+        <v>970</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>5.1</v>
+      </c>
+      <c r="AQ2">
+        <v>5.1</v>
+      </c>
+      <c r="AR2">
+        <v>5.1</v>
+      </c>
+      <c r="AS2">
+        <v>5.1</v>
+      </c>
+      <c r="AT2">
+        <v>5.1</v>
+      </c>
+      <c r="AU2">
+        <v>1.59</v>
+      </c>
+      <c r="AV2">
+        <v>3.8</v>
+      </c>
+      <c r="AW2">
+        <v>5.1</v>
+      </c>
+      <c r="AX2">
+        <v>5.1</v>
+      </c>
+      <c r="AY2">
         <v>10</v>
       </c>
-      <c r="AD2">
-        <v>10.5</v>
-      </c>
-      <c r="AE2">
-        <v>17.5</v>
-      </c>
-      <c r="AF2">
-        <v>160</v>
-      </c>
-      <c r="AG2">
-        <v>32</v>
-      </c>
-      <c r="AH2">
-        <v>25</v>
-      </c>
-      <c r="AI2">
-        <v>42</v>
-      </c>
-      <c r="AJ2">
-        <v>290</v>
-      </c>
-      <c r="AK2">
-        <v>180</v>
-      </c>
-      <c r="AL2">
-        <v>130</v>
-      </c>
-      <c r="AM2">
-        <v>700</v>
-      </c>
-      <c r="AN2">
-        <v>240</v>
-      </c>
-      <c r="AO2">
-        <v>9.6</v>
-      </c>
-      <c r="AP2">
-        <v>11.5</v>
-      </c>
-      <c r="AQ2">
-        <v>6.6</v>
-      </c>
-      <c r="AR2">
-        <v>7.4</v>
-      </c>
-      <c r="AS2">
-        <v>12.5</v>
-      </c>
-      <c r="AT2">
-        <v>18.5</v>
-      </c>
-      <c r="AU2">
-        <v>8.6</v>
-      </c>
-      <c r="AV2">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AW2">
-        <v>15</v>
-      </c>
-      <c r="AX2">
-        <v>10</v>
-      </c>
-      <c r="AY2">
-        <v>23</v>
-      </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>5.7</v>
       </c>
       <c r="BA2">
-        <v>9.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC2">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BD2">
-        <v>11</v>
+        <v>5.1</v>
       </c>
       <c r="BE2">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF2">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG2">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>149</v>
@@ -1299,226 +1299,226 @@
         <v>127</v>
       </c>
       <c r="F3">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="G3">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="H3">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="I3">
-        <v>3.2</v>
+        <v>5.8</v>
       </c>
       <c r="J3">
-        <v>2.74</v>
+        <v>2.1</v>
       </c>
       <c r="K3">
-        <v>3.2</v>
+        <v>2.24</v>
       </c>
       <c r="L3">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="N3">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O3">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.46</v>
+        <v>2.56</v>
       </c>
       <c r="Q3">
-        <v>2.9</v>
+        <v>1.54</v>
       </c>
       <c r="R3">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="S3">
+        <v>3.65</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <v>1.2</v>
+      </c>
+      <c r="W3">
+        <v>1.48</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>1000</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>2.84</v>
+      </c>
+      <c r="AD3">
+        <v>9.4</v>
+      </c>
+      <c r="AE3">
+        <v>70</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>4.9</v>
+      </c>
+      <c r="AH3">
+        <v>11</v>
+      </c>
+      <c r="AI3">
+        <v>110</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>21</v>
+      </c>
+      <c r="AL3">
+        <v>48</v>
+      </c>
+      <c r="AM3">
+        <v>290</v>
+      </c>
+      <c r="AN3">
+        <v>75</v>
+      </c>
+      <c r="AO3">
+        <v>310</v>
+      </c>
+      <c r="AP3">
+        <v>6.6</v>
+      </c>
+      <c r="AQ3">
+        <v>6.6</v>
+      </c>
+      <c r="AR3">
+        <v>6.6</v>
+      </c>
+      <c r="AS3">
+        <v>6.6</v>
+      </c>
+      <c r="AT3">
+        <v>6.6</v>
+      </c>
+      <c r="AU3">
+        <v>2.66</v>
+      </c>
+      <c r="AV3">
+        <v>6.4</v>
+      </c>
+      <c r="AW3">
+        <v>6.4</v>
+      </c>
+      <c r="AX3">
+        <v>6.6</v>
+      </c>
+      <c r="AY3">
+        <v>3.95</v>
+      </c>
+      <c r="AZ3">
+        <v>8.4</v>
+      </c>
+      <c r="BA3">
         <v>6.2</v>
       </c>
-      <c r="T3">
-        <v>2.24</v>
-      </c>
-      <c r="U3">
-        <v>1.69</v>
-      </c>
-      <c r="V3">
-        <v>1.47</v>
-      </c>
-      <c r="W3">
-        <v>1.43</v>
-      </c>
-      <c r="X3">
+      <c r="BB3">
+        <v>6.6</v>
+      </c>
+      <c r="BC3">
+        <v>15</v>
+      </c>
+      <c r="BD3">
+        <v>6.4</v>
+      </c>
+      <c r="BE3">
+        <v>6.4</v>
+      </c>
+      <c r="BF3">
+        <v>6</v>
+      </c>
+      <c r="BG3">
         <v>7.6</v>
       </c>
-      <c r="Y3">
-        <v>8.6</v>
-      </c>
-      <c r="Z3">
-        <v>21</v>
-      </c>
-      <c r="AA3">
-        <v>85</v>
-      </c>
-      <c r="AB3">
-        <v>8.4</v>
-      </c>
-      <c r="AC3">
-        <v>7.4</v>
-      </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
-      <c r="AE3">
-        <v>80</v>
-      </c>
-      <c r="AF3">
-        <v>20</v>
-      </c>
-      <c r="AG3">
-        <v>15.5</v>
-      </c>
-      <c r="AH3">
-        <v>25</v>
-      </c>
-      <c r="AI3">
-        <v>270</v>
-      </c>
-      <c r="AJ3">
-        <v>65</v>
-      </c>
-      <c r="AK3">
-        <v>55</v>
-      </c>
-      <c r="AL3">
-        <v>140</v>
-      </c>
-      <c r="AM3">
-        <v>500</v>
-      </c>
-      <c r="AN3">
-        <v>100</v>
-      </c>
-      <c r="AO3">
-        <v>600</v>
-      </c>
-      <c r="AP3">
-        <v>6.2</v>
-      </c>
-      <c r="AQ3">
-        <v>6.8</v>
-      </c>
-      <c r="AR3">
-        <v>16</v>
-      </c>
-      <c r="AS3">
-        <v>9</v>
-      </c>
-      <c r="AT3">
-        <v>7</v>
-      </c>
-      <c r="AU3">
-        <v>6</v>
-      </c>
-      <c r="AV3">
-        <v>12.5</v>
-      </c>
-      <c r="AW3">
-        <v>8.4</v>
-      </c>
-      <c r="AX3">
-        <v>16</v>
-      </c>
-      <c r="AY3">
-        <v>12</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3">
-        <v>9</v>
-      </c>
-      <c r="BB3">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC3">
-        <v>18</v>
-      </c>
-      <c r="BD3">
-        <v>9</v>
-      </c>
-      <c r="BE3">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF3">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BG3">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BH3">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>149</v>
@@ -1541,226 +1541,226 @@
         <v>128</v>
       </c>
       <c r="F4">
-        <v>3.55</v>
+        <v>4.3</v>
       </c>
       <c r="G4">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H4">
+        <v>2.76</v>
+      </c>
+      <c r="I4">
+        <v>2.9</v>
+      </c>
+      <c r="J4">
         <v>2.36</v>
       </c>
-      <c r="I4">
-        <v>2.56</v>
-      </c>
-      <c r="J4">
-        <v>2.9</v>
-      </c>
       <c r="K4">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="L4">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O4">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>1.53</v>
+        <v>3.15</v>
       </c>
       <c r="Q4">
-        <v>2.68</v>
+        <v>1.43</v>
       </c>
       <c r="R4">
-        <v>1.19</v>
+        <v>1.47</v>
       </c>
       <c r="S4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="T4">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W4">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="X4">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD4">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="AE4">
+        <v>16</v>
+      </c>
+      <c r="AF4">
+        <v>1000</v>
+      </c>
+      <c r="AG4">
+        <v>6.8</v>
+      </c>
+      <c r="AH4">
+        <v>9.4</v>
+      </c>
+      <c r="AI4">
+        <v>34</v>
+      </c>
+      <c r="AJ4">
+        <v>1000</v>
+      </c>
+      <c r="AK4">
+        <v>42</v>
+      </c>
+      <c r="AL4">
+        <v>50</v>
+      </c>
+      <c r="AM4">
+        <v>160</v>
+      </c>
+      <c r="AN4">
+        <v>120</v>
+      </c>
+      <c r="AO4">
+        <v>44</v>
+      </c>
+      <c r="AP4">
+        <v>12</v>
+      </c>
+      <c r="AQ4">
+        <v>12</v>
+      </c>
+      <c r="AR4">
+        <v>12</v>
+      </c>
+      <c r="AS4">
+        <v>12</v>
+      </c>
+      <c r="AT4">
+        <v>11</v>
+      </c>
+      <c r="AU4">
+        <v>3.4</v>
+      </c>
+      <c r="AV4">
+        <v>4.3</v>
+      </c>
+      <c r="AW4">
+        <v>12.5</v>
+      </c>
+      <c r="AX4">
+        <v>11</v>
+      </c>
+      <c r="AY4">
+        <v>6.2</v>
+      </c>
+      <c r="AZ4">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BA4">
+        <v>22</v>
+      </c>
+      <c r="BB4">
+        <v>11</v>
+      </c>
+      <c r="BC4">
+        <v>27</v>
+      </c>
+      <c r="BD4">
+        <v>34</v>
+      </c>
+      <c r="BE4">
+        <v>90</v>
+      </c>
+      <c r="BF4">
         <v>60</v>
       </c>
-      <c r="AF4">
-        <v>38</v>
-      </c>
-      <c r="AG4">
-        <v>17.5</v>
-      </c>
-      <c r="AH4">
-        <v>38</v>
-      </c>
-      <c r="AI4">
-        <v>210</v>
-      </c>
-      <c r="AJ4">
-        <v>220</v>
-      </c>
-      <c r="AK4">
-        <v>150</v>
-      </c>
-      <c r="AL4">
-        <v>500</v>
-      </c>
-      <c r="AM4">
-        <v>500</v>
-      </c>
-      <c r="AN4">
-        <v>600</v>
-      </c>
-      <c r="AO4">
-        <v>110</v>
-      </c>
-      <c r="AP4">
-        <v>7.6</v>
-      </c>
-      <c r="AQ4">
-        <v>6.6</v>
-      </c>
-      <c r="AR4">
-        <v>11</v>
-      </c>
-      <c r="AS4">
-        <v>23</v>
-      </c>
-      <c r="AT4">
-        <v>9</v>
-      </c>
-      <c r="AU4">
-        <v>6</v>
-      </c>
-      <c r="AV4">
-        <v>10.5</v>
-      </c>
-      <c r="AW4">
-        <v>9</v>
-      </c>
-      <c r="AX4">
-        <v>20</v>
-      </c>
-      <c r="AY4">
-        <v>14</v>
-      </c>
-      <c r="AZ4">
-        <v>19</v>
-      </c>
-      <c r="BA4">
-        <v>9</v>
-      </c>
-      <c r="BB4">
-        <v>9.4</v>
-      </c>
-      <c r="BC4">
-        <v>9</v>
-      </c>
-      <c r="BD4">
-        <v>9.4</v>
-      </c>
-      <c r="BE4">
-        <v>10</v>
-      </c>
-      <c r="BF4">
-        <v>9.4</v>
-      </c>
       <c r="BG4">
-        <v>8.4</v>
+        <v>26</v>
       </c>
       <c r="BH4">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>149</v>
@@ -1783,10 +1783,10 @@
         <v>129</v>
       </c>
       <c r="F5">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G5">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H5">
         <v>3.9</v>
@@ -1795,52 +1795,52 @@
         <v>4.1</v>
       </c>
       <c r="J5">
+        <v>2.88</v>
+      </c>
+      <c r="K5">
         <v>2.9</v>
       </c>
-      <c r="K5">
-        <v>2.98</v>
-      </c>
       <c r="L5">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="M5">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="N5">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O5">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="P5">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S5">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="T5">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="U5">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V5">
         <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X5">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Y5">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5">
         <v>26</v>
@@ -1849,160 +1849,160 @@
         <v>110</v>
       </c>
       <c r="AB5">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AC5">
         <v>7.2</v>
       </c>
       <c r="AD5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE5">
         <v>180</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
         <v>34</v>
       </c>
       <c r="AI5">
-        <v>490</v>
+        <v>530</v>
       </c>
       <c r="AJ5">
         <v>40</v>
       </c>
       <c r="AK5">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="AL5">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM5">
         <v>500</v>
       </c>
       <c r="AN5">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AO5">
-        <v>490</v>
+        <v>180</v>
       </c>
       <c r="AP5">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ5">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AR5">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS5">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AT5">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
         <v>6.6</v>
       </c>
       <c r="AV5">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW5">
+        <v>60</v>
+      </c>
+      <c r="AX5">
+        <v>12</v>
+      </c>
+      <c r="AY5">
+        <v>13</v>
+      </c>
+      <c r="AZ5">
+        <v>30</v>
+      </c>
+      <c r="BA5">
+        <v>60</v>
+      </c>
+      <c r="BB5">
+        <v>36</v>
+      </c>
+      <c r="BC5">
+        <v>40</v>
+      </c>
+      <c r="BD5">
         <v>70</v>
-      </c>
-      <c r="AX5">
-        <v>11.5</v>
-      </c>
-      <c r="AY5">
-        <v>12.5</v>
-      </c>
-      <c r="AZ5">
-        <v>27</v>
-      </c>
-      <c r="BA5">
-        <v>44</v>
-      </c>
-      <c r="BB5">
-        <v>32</v>
-      </c>
-      <c r="BC5">
-        <v>38</v>
-      </c>
-      <c r="BD5">
-        <v>46</v>
       </c>
       <c r="BE5">
         <v>110</v>
       </c>
       <c r="BF5">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BG5">
         <v>42</v>
       </c>
       <c r="BH5">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="BI5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="BP5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BQ5">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT5">
         <v>7.2</v>
       </c>
       <c r="BU5">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BW5">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="BY5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA5">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB5" t="s">
         <v>149</v>
@@ -2031,13 +2031,13 @@
         <v>1.31</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="I6">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>8</v>
@@ -2067,25 +2067,25 @@
         <v>1.66</v>
       </c>
       <c r="T6">
-        <v>1.57</v>
+        <v>1.11</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W6">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X6">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="Y6">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="Z6">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="AA6">
         <v>370</v>
@@ -2097,10 +2097,10 @@
         <v>22</v>
       </c>
       <c r="AD6">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="AE6">
-        <v>170</v>
+        <v>260</v>
       </c>
       <c r="AF6">
         <v>15</v>
@@ -2109,10 +2109,10 @@
         <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AI6">
-        <v>75</v>
+        <v>230</v>
       </c>
       <c r="AJ6">
         <v>14.5</v>
@@ -2127,22 +2127,22 @@
         <v>320</v>
       </c>
       <c r="AN6">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AO6">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AP6">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AQ6">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AR6">
-        <v>40</v>
+        <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT6">
         <v>17.5</v>
@@ -2151,10 +2151,10 @@
         <v>18</v>
       </c>
       <c r="AV6">
-        <v>34</v>
+        <v>19.5</v>
       </c>
       <c r="AW6">
-        <v>75</v>
+        <v>11.5</v>
       </c>
       <c r="AX6">
         <v>12.5</v>
@@ -2166,7 +2166,7 @@
         <v>19</v>
       </c>
       <c r="BA6">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2178,43 +2178,43 @@
         <v>20</v>
       </c>
       <c r="BE6">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="BF6">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BG6">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="BH6">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BI6">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="BJ6">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BL6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM6">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN6">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO6">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="BP6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BQ6">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="BR6">
         <v>16.5</v>
@@ -2223,28 +2223,28 @@
         <v>7.2</v>
       </c>
       <c r="BT6">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BU6">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW6">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BX6">
         <v>48</v>
       </c>
       <c r="BY6">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ6">
         <v>6.6</v>
       </c>
       <c r="CA6">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB6" t="s">
         <v>149</v>
@@ -2267,19 +2267,19 @@
         <v>131</v>
       </c>
       <c r="F7">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G7">
         <v>1.86</v>
       </c>
       <c r="H7">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I7">
         <v>4.5</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K7">
         <v>5.3</v>
@@ -2291,28 +2291,28 @@
         <v>1.03</v>
       </c>
       <c r="N7">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="O7">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P7">
         <v>3.35</v>
       </c>
       <c r="Q7">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="R7">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="S7">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T7">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="U7">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="V7">
         <v>1.01</v>
@@ -2321,13 +2321,13 @@
         <v>1.01</v>
       </c>
       <c r="X7">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y7">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Z7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AA7">
         <v>160</v>
@@ -2336,16 +2336,16 @@
         <v>21</v>
       </c>
       <c r="AC7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AD7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AE7">
         <v>40</v>
       </c>
       <c r="AF7">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AG7">
         <v>12</v>
@@ -2354,85 +2354,85 @@
         <v>16</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK7">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL7">
         <v>23</v>
       </c>
       <c r="AM7">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="AO7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP7">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR7">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AS7">
         <v>55</v>
       </c>
       <c r="AT7">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU7">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AV7">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW7">
         <v>28</v>
       </c>
       <c r="AX7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY7">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BA7">
         <v>23</v>
       </c>
       <c r="BB7">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC7">
         <v>13.5</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BE7">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BF7">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BG7">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BH7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BI7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BJ7">
         <v>8.800000000000001</v>
@@ -2444,13 +2444,13 @@
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BN7">
         <v>5.6</v>
       </c>
       <c r="BO7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BP7">
         <v>11.5</v>
@@ -2459,10 +2459,10 @@
         <v>5.4</v>
       </c>
       <c r="BR7">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BS7">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT7">
         <v>8.800000000000001</v>
@@ -2477,10 +2477,10 @@
         <v>7.4</v>
       </c>
       <c r="BX7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY7">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BZ7">
         <v>11</v>
@@ -2509,13 +2509,13 @@
         <v>132</v>
       </c>
       <c r="F8">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G8">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H8">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="I8">
         <v>2.14</v>
@@ -2524,7 +2524,7 @@
         <v>4.5</v>
       </c>
       <c r="K8">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L8">
         <v>1.16</v>
@@ -2533,7 +2533,7 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="O8">
         <v>1.07</v>
@@ -2542,43 +2542,43 @@
         <v>4.6</v>
       </c>
       <c r="Q8">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="R8">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S8">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="T8">
         <v>1.29</v>
       </c>
       <c r="U8">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="V8">
         <v>1.87</v>
       </c>
       <c r="W8">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Y8">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="Z8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8">
         <v>38</v>
       </c>
       <c r="AB8">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AC8">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AD8">
         <v>15.5</v>
@@ -2599,19 +2599,19 @@
         <v>19.5</v>
       </c>
       <c r="AJ8">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK8">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AM8">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AN8">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO8">
         <v>5.5</v>
@@ -2620,13 +2620,13 @@
         <v>29</v>
       </c>
       <c r="AQ8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR8">
         <v>22</v>
       </c>
       <c r="AS8">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT8">
         <v>30</v>
@@ -2635,13 +2635,13 @@
         <v>14</v>
       </c>
       <c r="AV8">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW8">
         <v>15.5</v>
       </c>
       <c r="AX8">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AY8">
         <v>16</v>
@@ -2653,16 +2653,16 @@
         <v>16</v>
       </c>
       <c r="BB8">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC8">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BD8">
         <v>20</v>
       </c>
       <c r="BE8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BF8">
         <v>8.800000000000001</v>
@@ -2671,10 +2671,10 @@
         <v>4.6</v>
       </c>
       <c r="BH8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BI8">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BJ8">
         <v>8.6</v>
@@ -2689,19 +2689,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BN8">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP8">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
         <v>6.8</v>
       </c>
       <c r="BR8">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BS8">
         <v>6.8</v>
@@ -2710,7 +2710,7 @@
         <v>6.8</v>
       </c>
       <c r="BU8">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV8">
         <v>13</v>
@@ -2725,7 +2725,7 @@
         <v>6.2</v>
       </c>
       <c r="BZ8">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA8">
         <v>6</v>
@@ -2751,10 +2751,10 @@
         <v>133</v>
       </c>
       <c r="F9">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="H9">
         <v>5.9</v>
@@ -2763,10 +2763,10 @@
         <v>7</v>
       </c>
       <c r="J9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K9">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="L9">
         <v>1.24</v>
@@ -2775,34 +2775,34 @@
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O9">
         <v>1.15</v>
       </c>
       <c r="P9">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="Q9">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R9">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="S9">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T9">
         <v>1.62</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V9">
         <v>1.16</v>
       </c>
       <c r="W9">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X9">
         <v>36</v>
@@ -2853,7 +2853,7 @@
         <v>580</v>
       </c>
       <c r="AN9">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AO9">
         <v>700</v>
@@ -2865,10 +2865,10 @@
         <v>12</v>
       </c>
       <c r="AR9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9">
         <v>11</v>
@@ -2880,7 +2880,7 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX9">
         <v>10</v>
@@ -2892,7 +2892,7 @@
         <v>16</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB9">
         <v>12.5</v>
@@ -2904,37 +2904,37 @@
         <v>21</v>
       </c>
       <c r="BE9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF9">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BG9">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH9">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BI9">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BJ9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BP9">
         <v>9.4</v>
@@ -2943,10 +2943,10 @@
         <v>4.8</v>
       </c>
       <c r="BR9">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BS9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BT9">
         <v>11</v>
@@ -2967,10 +2967,10 @@
         <v>8</v>
       </c>
       <c r="BZ9">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA9">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="CB9" t="s">
         <v>149</v>
@@ -2993,22 +2993,22 @@
         <v>134</v>
       </c>
       <c r="F10">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G10">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="H10">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I10">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J10">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L10">
         <v>1.5</v>
@@ -3017,16 +3017,16 @@
         <v>1.1</v>
       </c>
       <c r="N10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10">
         <v>1.42</v>
       </c>
       <c r="P10">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q10">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R10">
         <v>1.27</v>
@@ -3035,31 +3035,31 @@
         <v>4.2</v>
       </c>
       <c r="T10">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U10">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V10">
         <v>1.6</v>
       </c>
       <c r="W10">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X10">
         <v>12</v>
       </c>
       <c r="Y10">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="Z10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AA10">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AB10">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC10">
         <v>7.4</v>
@@ -3068,25 +3068,25 @@
         <v>12.5</v>
       </c>
       <c r="AE10">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AF10">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG10">
         <v>15</v>
       </c>
       <c r="AH10">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ10">
         <v>150</v>
       </c>
       <c r="AK10">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL10">
         <v>60</v>
@@ -3095,25 +3095,25 @@
         <v>580</v>
       </c>
       <c r="AN10">
-        <v>500</v>
+        <v>48</v>
       </c>
       <c r="AO10">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AP10">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR10">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS10">
-        <v>18</v>
+        <v>7.4</v>
       </c>
       <c r="AT10">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU10">
         <v>6.2</v>
@@ -3122,91 +3122,91 @@
         <v>10</v>
       </c>
       <c r="AW10">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AX10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AY10">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ10">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BA10">
-        <v>22</v>
+        <v>7.6</v>
       </c>
       <c r="BB10">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BC10">
-        <v>36</v>
+        <v>7.4</v>
       </c>
       <c r="BD10">
-        <v>40</v>
+        <v>7.8</v>
       </c>
       <c r="BE10">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF10">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BG10">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BH10">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BI10">
-        <v>2.78</v>
+        <v>2.54</v>
       </c>
       <c r="BJ10">
         <v>10.5</v>
       </c>
       <c r="BK10">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BN10">
         <v>6.4</v>
       </c>
       <c r="BO10">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="BP10">
         <v>28</v>
       </c>
       <c r="BQ10">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="BR10">
         <v>44</v>
       </c>
       <c r="BS10">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BU10">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="BV10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BW10">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BX10">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY10">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ10">
         <v>0</v>
@@ -3235,13 +3235,13 @@
         <v>135</v>
       </c>
       <c r="F11">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="G11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H11">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I11">
         <v>2.24</v>
@@ -3250,7 +3250,7 @@
         <v>4.8</v>
       </c>
       <c r="K11">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L11">
         <v>1.13</v>
@@ -3268,13 +3268,13 @@
         <v>5.5</v>
       </c>
       <c r="Q11">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="R11">
         <v>2.8</v>
       </c>
       <c r="S11">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T11">
         <v>1.25</v>
@@ -3283,10 +3283,10 @@
         <v>4.2</v>
       </c>
       <c r="V11">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="W11">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="X11">
         <v>120</v>
@@ -3337,64 +3337,64 @@
         <v>34</v>
       </c>
       <c r="AN11">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO11">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AP11">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ11">
-        <v>5.5</v>
+        <v>23</v>
       </c>
       <c r="AR11">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AS11">
-        <v>5.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT11">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AU11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AV11">
         <v>13.5</v>
       </c>
       <c r="AW11">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AX11">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AY11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AZ11">
         <v>12</v>
       </c>
       <c r="BA11">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BB11">
-        <v>5.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC11">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="BD11">
         <v>18.5</v>
       </c>
       <c r="BE11">
-        <v>10.5</v>
+        <v>22</v>
       </c>
       <c r="BF11">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG11">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH11">
         <v>8.6</v>
@@ -3477,19 +3477,19 @@
         <v>136</v>
       </c>
       <c r="F12">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G12">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H12">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="I12">
         <v>3.55</v>
       </c>
       <c r="J12">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -3501,202 +3501,202 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="O12">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P12">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="Q12">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="R12">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="S12">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="T12">
         <v>1.4</v>
       </c>
       <c r="U12">
-        <v>3</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
         <v>1.4</v>
       </c>
       <c r="W12">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="X12">
-        <v>46</v>
+        <v>950</v>
       </c>
       <c r="Y12">
+        <v>28</v>
+      </c>
+      <c r="Z12">
+        <v>34</v>
+      </c>
+      <c r="AA12">
+        <v>900</v>
+      </c>
+      <c r="AB12">
+        <v>38</v>
+      </c>
+      <c r="AC12">
+        <v>13</v>
+      </c>
+      <c r="AD12">
+        <v>22</v>
+      </c>
+      <c r="AE12">
+        <v>85</v>
+      </c>
+      <c r="AF12">
+        <v>38</v>
+      </c>
+      <c r="AG12">
+        <v>970</v>
+      </c>
+      <c r="AH12">
+        <v>20</v>
+      </c>
+      <c r="AI12">
+        <v>80</v>
+      </c>
+      <c r="AJ12">
+        <v>65</v>
+      </c>
+      <c r="AK12">
+        <v>970</v>
+      </c>
+      <c r="AL12">
+        <v>40</v>
+      </c>
+      <c r="AM12">
+        <v>580</v>
+      </c>
+      <c r="AN12">
         <v>29</v>
       </c>
-      <c r="Z12">
-        <v>36</v>
-      </c>
-      <c r="AA12">
-        <v>170</v>
-      </c>
-      <c r="AB12">
-        <v>23</v>
-      </c>
-      <c r="AC12">
-        <v>14</v>
-      </c>
-      <c r="AD12">
-        <v>17.5</v>
-      </c>
-      <c r="AE12">
-        <v>32</v>
-      </c>
-      <c r="AF12">
-        <v>22</v>
-      </c>
-      <c r="AG12">
+      <c r="AO12">
+        <v>19.5</v>
+      </c>
+      <c r="AP12">
+        <v>2.2</v>
+      </c>
+      <c r="AQ12">
+        <v>17</v>
+      </c>
+      <c r="AR12">
+        <v>21</v>
+      </c>
+      <c r="AS12">
+        <v>4.1</v>
+      </c>
+      <c r="AT12">
         <v>13.5</v>
       </c>
-      <c r="AH12">
-        <v>15.5</v>
-      </c>
-      <c r="AI12">
-        <v>30</v>
-      </c>
-      <c r="AJ12">
-        <v>30</v>
-      </c>
-      <c r="AK12">
-        <v>19.5</v>
-      </c>
-      <c r="AL12">
-        <v>24</v>
-      </c>
-      <c r="AM12">
-        <v>42</v>
-      </c>
-      <c r="AN12">
-        <v>7.2</v>
-      </c>
-      <c r="AO12">
-        <v>15</v>
-      </c>
-      <c r="AP12">
-        <v>7</v>
-      </c>
-      <c r="AQ12">
-        <v>20</v>
-      </c>
-      <c r="AR12">
-        <v>15</v>
-      </c>
-      <c r="AS12">
-        <v>7.4</v>
-      </c>
-      <c r="AT12">
-        <v>17.5</v>
-      </c>
       <c r="AU12">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AV12">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AW12">
-        <v>13</v>
+        <v>18.5</v>
       </c>
       <c r="AX12">
-        <v>17</v>
+        <v>2.08</v>
       </c>
       <c r="AY12">
         <v>10.5</v>
       </c>
       <c r="AZ12">
+        <v>9.4</v>
+      </c>
+      <c r="BA12">
+        <v>18</v>
+      </c>
+      <c r="BB12">
+        <v>2.16</v>
+      </c>
+      <c r="BC12">
         <v>12</v>
       </c>
-      <c r="BA12">
-        <v>12.5</v>
-      </c>
-      <c r="BB12">
-        <v>12</v>
-      </c>
-      <c r="BC12">
-        <v>15</v>
-      </c>
       <c r="BD12">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="BE12">
-        <v>17.5</v>
+        <v>2.16</v>
       </c>
       <c r="BF12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH12">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BI12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ12">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BK12">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BL12">
         <v>55</v>
       </c>
       <c r="BM12">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BN12">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO12">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="BP12">
         <v>13.5</v>
       </c>
       <c r="BQ12">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BR12">
         <v>18.5</v>
       </c>
       <c r="BS12">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BT12">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BU12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV12">
         <v>22</v>
       </c>
       <c r="BW12">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BX12">
         <v>24</v>
       </c>
       <c r="BY12">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BZ12">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CA12">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="CB12" t="s">
         <v>149</v>
@@ -3719,73 +3719,73 @@
         <v>137</v>
       </c>
       <c r="F13">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G13">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="H13">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I13">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="J13">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="L13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M13">
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O13">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P13">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="Q13">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="R13">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="T13">
         <v>1.36</v>
       </c>
       <c r="U13">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V13">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="W13">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X13">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y13">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="Z13">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA13">
         <v>32</v>
       </c>
       <c r="AB13">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AC13">
         <v>14</v>
@@ -3797,13 +3797,13 @@
         <v>21</v>
       </c>
       <c r="AF13">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG13">
         <v>16.5</v>
       </c>
       <c r="AH13">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI13">
         <v>23</v>
@@ -3812,7 +3812,7 @@
         <v>55</v>
       </c>
       <c r="AK13">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL13">
         <v>27</v>
@@ -3821,124 +3821,124 @@
         <v>38</v>
       </c>
       <c r="AN13">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO13">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AP13">
-        <v>7.4</v>
+        <v>23</v>
       </c>
       <c r="AQ13">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AR13">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AS13">
-        <v>7.8</v>
+        <v>16</v>
       </c>
       <c r="AT13">
-        <v>7.8</v>
+        <v>22</v>
       </c>
       <c r="AU13">
-        <v>7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV13">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW13">
-        <v>8.800000000000001</v>
+        <v>17</v>
       </c>
       <c r="AX13">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="AY13">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AZ13">
+        <v>11.5</v>
+      </c>
+      <c r="BA13">
+        <v>18.5</v>
+      </c>
+      <c r="BB13">
+        <v>32</v>
+      </c>
+      <c r="BC13">
+        <v>19.5</v>
+      </c>
+      <c r="BD13">
+        <v>19</v>
+      </c>
+      <c r="BE13">
+        <v>29</v>
+      </c>
+      <c r="BF13">
+        <v>8.4</v>
+      </c>
+      <c r="BG13">
         <v>6.2</v>
       </c>
-      <c r="BA13">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB13">
-        <v>7.4</v>
-      </c>
-      <c r="BC13">
-        <v>7.8</v>
-      </c>
-      <c r="BD13">
-        <v>7.8</v>
-      </c>
-      <c r="BE13">
-        <v>7</v>
-      </c>
-      <c r="BF13">
-        <v>5.1</v>
-      </c>
-      <c r="BG13">
-        <v>3.95</v>
-      </c>
       <c r="BH13">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BI13">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="BJ13">
         <v>8.4</v>
       </c>
       <c r="BK13">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL13">
         <v>48</v>
       </c>
       <c r="BM13">
+        <v>8.6</v>
+      </c>
+      <c r="BN13">
         <v>7.6</v>
       </c>
-      <c r="BN13">
-        <v>8</v>
-      </c>
       <c r="BO13">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BP13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BQ13">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BR13">
         <v>22</v>
       </c>
       <c r="BS13">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BT13">
         <v>6.6</v>
       </c>
       <c r="BU13">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BV13">
         <v>14</v>
       </c>
       <c r="BW13">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BX13">
         <v>18.5</v>
       </c>
       <c r="BY13">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BZ13">
         <v>10</v>
       </c>
       <c r="CA13">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="CB13" t="s">
         <v>149</v>
@@ -3961,22 +3961,22 @@
         <v>138</v>
       </c>
       <c r="F14">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G14">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H14">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="I14">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J14">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K14">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>1.18</v>
@@ -3985,28 +3985,28 @@
         <v>1.02</v>
       </c>
       <c r="N14">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="O14">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P14">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q14">
         <v>1.31</v>
       </c>
       <c r="R14">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="S14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T14">
         <v>1.35</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V14">
         <v>1.01</v>
@@ -4015,43 +4015,43 @@
         <v>1.01</v>
       </c>
       <c r="X14">
-        <v>950</v>
+        <v>150</v>
       </c>
       <c r="Y14">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="Z14">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="AA14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="AB14">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AC14">
         <v>14</v>
       </c>
       <c r="AD14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE14">
-        <v>210</v>
+        <v>36</v>
       </c>
       <c r="AF14">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="AG14">
         <v>14.5</v>
       </c>
       <c r="AH14">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI14">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AJ14">
-        <v>160</v>
+        <v>38</v>
       </c>
       <c r="AK14">
         <v>21</v>
@@ -4060,25 +4060,25 @@
         <v>22</v>
       </c>
       <c r="AM14">
-        <v>200</v>
+        <v>46</v>
       </c>
       <c r="AN14">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AO14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP14">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="AQ14">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="AR14">
-        <v>15.5</v>
+        <v>26</v>
       </c>
       <c r="AS14">
-        <v>8.6</v>
+        <v>36</v>
       </c>
       <c r="AT14">
         <v>21</v>
@@ -4090,7 +4090,7 @@
         <v>13.5</v>
       </c>
       <c r="AW14">
-        <v>12</v>
+        <v>18.5</v>
       </c>
       <c r="AX14">
         <v>20</v>
@@ -4105,82 +4105,82 @@
         <v>20</v>
       </c>
       <c r="BB14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BC14">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="BD14">
         <v>17.5</v>
       </c>
       <c r="BE14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BF14">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BG14">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH14">
         <v>6.4</v>
       </c>
       <c r="BI14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BJ14">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BK14">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BN14">
+        <v>6.6</v>
+      </c>
+      <c r="BO14">
+        <v>5.2</v>
+      </c>
+      <c r="BP14">
+        <v>14</v>
+      </c>
+      <c r="BQ14">
         <v>6.8</v>
       </c>
-      <c r="BO14">
-        <v>5.1</v>
-      </c>
-      <c r="BP14">
-        <v>14.5</v>
-      </c>
-      <c r="BQ14">
-        <v>5.9</v>
-      </c>
       <c r="BR14">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS14">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BT14">
+        <v>7.6</v>
+      </c>
+      <c r="BU14">
+        <v>4.9</v>
+      </c>
+      <c r="BV14">
+        <v>18.5</v>
+      </c>
+      <c r="BW14">
         <v>7.8</v>
-      </c>
-      <c r="BU14">
-        <v>4.3</v>
-      </c>
-      <c r="BV14">
-        <v>19.5</v>
-      </c>
-      <c r="BW14">
-        <v>6.6</v>
       </c>
       <c r="BX14">
         <v>21</v>
       </c>
       <c r="BY14">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ14">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="CA14">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="CB14" t="s">
         <v>149</v>
@@ -4206,25 +4206,25 @@
         <v>2.38</v>
       </c>
       <c r="G15">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H15">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J15">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L15">
         <v>1.31</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N15">
         <v>5.1</v>
@@ -4233,118 +4233,118 @@
         <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R15">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S15">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="T15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="U15">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="V15">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W15">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="Y15">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="Z15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AA15">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="AB15">
-        <v>15.5</v>
+        <v>24</v>
       </c>
       <c r="AC15">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD15">
         <v>13.5</v>
       </c>
       <c r="AE15">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AF15">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AH15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AI15">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AJ15">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AK15">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="AL15">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AM15">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AN15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO15">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="AP15">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AQ15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AR15">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS15">
         <v>32</v>
       </c>
       <c r="AT15">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AU15">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV15">
         <v>11.5</v>
       </c>
       <c r="AW15">
-        <v>23</v>
+        <v>13.5</v>
       </c>
       <c r="AX15">
         <v>16.5</v>
       </c>
       <c r="AY15">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA15">
-        <v>27</v>
+        <v>16.5</v>
       </c>
       <c r="BB15">
         <v>23</v>
@@ -4353,16 +4353,16 @@
         <v>20</v>
       </c>
       <c r="BD15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE15">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="BF15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG15">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BH15">
         <v>4.2</v>
@@ -4380,25 +4380,25 @@
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BN15">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO15">
         <v>5</v>
       </c>
       <c r="BP15">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="BQ15">
         <v>7.8</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BS15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BT15">
         <v>6.6</v>
@@ -4410,19 +4410,19 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="CA15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB15" t="s">
         <v>149</v>
@@ -4445,19 +4445,19 @@
         <v>140</v>
       </c>
       <c r="F16">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G16">
         <v>2.42</v>
       </c>
       <c r="H16">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="I16">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="J16">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K16">
         <v>4.4</v>
@@ -4472,28 +4472,28 @@
         <v>6.4</v>
       </c>
       <c r="O16">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="Q16">
         <v>1.49</v>
       </c>
       <c r="R16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="S16">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T16">
         <v>1.46</v>
       </c>
       <c r="U16">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W16">
         <v>1.7</v>
@@ -4502,7 +4502,7 @@
         <v>32</v>
       </c>
       <c r="Y16">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z16">
         <v>28</v>
@@ -4529,13 +4529,13 @@
         <v>12.5</v>
       </c>
       <c r="AH16">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI16">
         <v>32</v>
       </c>
       <c r="AJ16">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK16">
         <v>21</v>
@@ -4544,7 +4544,7 @@
         <v>26</v>
       </c>
       <c r="AM16">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN16">
         <v>10.5</v>
@@ -4553,7 +4553,7 @@
         <v>15</v>
       </c>
       <c r="AP16">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AQ16">
         <v>17.5</v>
@@ -4598,73 +4598,73 @@
         <v>21</v>
       </c>
       <c r="BE16">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG16">
         <v>12.5</v>
       </c>
       <c r="BH16">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BI16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ16">
         <v>8.4</v>
       </c>
       <c r="BK16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM16">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN16">
         <v>6.2</v>
       </c>
       <c r="BO16">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP16">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ16">
+        <v>7</v>
+      </c>
+      <c r="BR16">
+        <v>23</v>
+      </c>
+      <c r="BS16">
+        <v>7.8</v>
+      </c>
+      <c r="BT16">
         <v>6.6</v>
       </c>
-      <c r="BR16">
-        <v>22</v>
-      </c>
-      <c r="BS16">
-        <v>7.4</v>
-      </c>
-      <c r="BT16">
-        <v>6.8</v>
-      </c>
       <c r="BU16">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV16">
         <v>19.5</v>
       </c>
       <c r="BW16">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX16">
         <v>25</v>
       </c>
       <c r="BY16">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ16">
         <v>14</v>
       </c>
       <c r="CA16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="CB16" t="s">
         <v>149</v>
@@ -4687,40 +4687,40 @@
         <v>141</v>
       </c>
       <c r="F17">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G17">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="H17">
         <v>3.9</v>
       </c>
       <c r="I17">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J17">
         <v>2.96</v>
       </c>
       <c r="K17">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L17">
         <v>1.69</v>
       </c>
       <c r="M17">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N17">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="O17">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="P17">
         <v>1.43</v>
       </c>
       <c r="Q17">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
         <v>1.14</v>
@@ -4732,40 +4732,40 @@
         <v>2.44</v>
       </c>
       <c r="U17">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V17">
         <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="X17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9.199999999999999</v>
       </c>
       <c r="Z17">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA17">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB17">
         <v>6.6</v>
       </c>
       <c r="AC17">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AF17">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG17">
         <v>13</v>
@@ -4774,10 +4774,10 @@
         <v>32</v>
       </c>
       <c r="AI17">
-        <v>490</v>
+        <v>260</v>
       </c>
       <c r="AJ17">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK17">
         <v>40</v>
@@ -4786,25 +4786,25 @@
         <v>85</v>
       </c>
       <c r="AM17">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AN17">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="AO17">
         <v>490</v>
       </c>
       <c r="AP17">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ17">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR17">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS17">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AT17">
         <v>6</v>
@@ -4813,13 +4813,13 @@
         <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW17">
         <v>65</v>
       </c>
       <c r="AX17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY17">
         <v>12</v>
@@ -4828,13 +4828,13 @@
         <v>28</v>
       </c>
       <c r="BA17">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BB17">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BC17">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BD17">
         <v>65</v>
@@ -4843,10 +4843,10 @@
         <v>110</v>
       </c>
       <c r="BF17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BG17">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BH17">
         <v>2.46</v>
@@ -4858,34 +4858,34 @@
         <v>12.5</v>
       </c>
       <c r="BK17">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>20</v>
+        <v>2.16</v>
       </c>
       <c r="BN17">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO17">
         <v>4.3</v>
       </c>
       <c r="BP17">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BQ17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BR17">
         <v>55</v>
       </c>
       <c r="BS17">
-        <v>2.12</v>
+        <v>14.5</v>
       </c>
       <c r="BT17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU17">
         <v>6</v>
@@ -4894,19 +4894,19 @@
         <v>1000</v>
       </c>
       <c r="BW17">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BX17">
         <v>1000</v>
       </c>
       <c r="BY17">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="BZ17">
         <v>1000</v>
       </c>
       <c r="CA17">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="CB17" t="s">
         <v>149</v>
@@ -4932,22 +4932,22 @@
         <v>1.68</v>
       </c>
       <c r="G18">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H18">
         <v>6</v>
       </c>
       <c r="I18">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="J18">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="M18">
         <v>1.09</v>
@@ -4956,13 +4956,13 @@
         <v>3.1</v>
       </c>
       <c r="O18">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P18">
         <v>1.7</v>
       </c>
       <c r="Q18">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="R18">
         <v>1.26</v>
@@ -4971,10 +4971,10 @@
         <v>4.2</v>
       </c>
       <c r="T18">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U18">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="V18">
         <v>1.17</v>
@@ -4989,7 +4989,7 @@
         <v>19</v>
       </c>
       <c r="Z18">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AA18">
         <v>900</v>
@@ -5013,7 +5013,7 @@
         <v>11</v>
       </c>
       <c r="AH18">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI18">
         <v>700</v>
@@ -5025,13 +5025,13 @@
         <v>22</v>
       </c>
       <c r="AL18">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AM18">
         <v>580</v>
       </c>
       <c r="AN18">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO18">
         <v>230</v>
@@ -5040,13 +5040,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ18">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR18">
         <v>24</v>
       </c>
       <c r="AS18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT18">
         <v>5.8</v>
@@ -5058,7 +5058,7 @@
         <v>12</v>
       </c>
       <c r="AW18">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX18">
         <v>7.6</v>
@@ -5070,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="BA18">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB18">
         <v>14</v>
@@ -5082,13 +5082,13 @@
         <v>17.5</v>
       </c>
       <c r="BE18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF18">
         <v>11.5</v>
       </c>
       <c r="BG18">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH18">
         <v>3.15</v>
@@ -5171,28 +5171,28 @@
         <v>143</v>
       </c>
       <c r="F19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G19">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H19">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I19">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="J19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K19">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L19">
         <v>1.47</v>
       </c>
       <c r="M19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N19">
         <v>3.35</v>
@@ -5204,7 +5204,7 @@
         <v>1.8</v>
       </c>
       <c r="Q19">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R19">
         <v>1.29</v>
@@ -5219,10 +5219,10 @@
         <v>2.06</v>
       </c>
       <c r="V19">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W19">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X19">
         <v>11.5</v>
@@ -5234,7 +5234,7 @@
         <v>17</v>
       </c>
       <c r="AA19">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="AB19">
         <v>12</v>
@@ -5252,13 +5252,13 @@
         <v>23</v>
       </c>
       <c r="AG19">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AH19">
         <v>18.5</v>
       </c>
       <c r="AI19">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ19">
         <v>150</v>
@@ -5288,7 +5288,7 @@
         <v>13.5</v>
       </c>
       <c r="AS19">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AT19">
         <v>10</v>
@@ -5315,34 +5315,34 @@
         <v>25</v>
       </c>
       <c r="BB19">
-        <v>9.199999999999999</v>
+        <v>20</v>
       </c>
       <c r="BC19">
         <v>18.5</v>
       </c>
       <c r="BD19">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE19">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF19">
-        <v>8.6</v>
+        <v>14</v>
       </c>
       <c r="BG19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH19">
         <v>3.15</v>
       </c>
       <c r="BI19">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="BJ19">
         <v>10.5</v>
       </c>
       <c r="BK19">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL19">
         <v>1000</v>
@@ -5354,7 +5354,7 @@
         <v>6.2</v>
       </c>
       <c r="BO19">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP19">
         <v>27</v>
@@ -5372,7 +5372,7 @@
         <v>5.5</v>
       </c>
       <c r="BU19">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV19">
         <v>22</v>
@@ -5413,58 +5413,58 @@
         <v>144</v>
       </c>
       <c r="F20">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G20">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="H20">
+        <v>2.04</v>
+      </c>
+      <c r="I20">
+        <v>2.06</v>
+      </c>
+      <c r="J20">
+        <v>3.25</v>
+      </c>
+      <c r="K20">
+        <v>3.35</v>
+      </c>
+      <c r="L20">
+        <v>1.57</v>
+      </c>
+      <c r="M20">
+        <v>1.12</v>
+      </c>
+      <c r="N20">
+        <v>2.74</v>
+      </c>
+      <c r="O20">
+        <v>1.54</v>
+      </c>
+      <c r="P20">
+        <v>1.58</v>
+      </c>
+      <c r="Q20">
+        <v>2.66</v>
+      </c>
+      <c r="R20">
+        <v>1.21</v>
+      </c>
+      <c r="S20">
+        <v>5.5</v>
+      </c>
+      <c r="T20">
         <v>2.18</v>
       </c>
-      <c r="I20">
-        <v>2.24</v>
-      </c>
-      <c r="J20">
-        <v>3.2</v>
-      </c>
-      <c r="K20">
-        <v>3.3</v>
-      </c>
-      <c r="L20">
-        <v>1.6</v>
-      </c>
-      <c r="M20">
-        <v>1.13</v>
-      </c>
-      <c r="N20">
-        <v>2.66</v>
-      </c>
-      <c r="O20">
-        <v>1.57</v>
-      </c>
-      <c r="P20">
-        <v>1.55</v>
-      </c>
-      <c r="Q20">
-        <v>2.76</v>
-      </c>
-      <c r="R20">
-        <v>1.2</v>
-      </c>
-      <c r="S20">
-        <v>5.8</v>
-      </c>
-      <c r="T20">
-        <v>2.28</v>
-      </c>
       <c r="U20">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="W20">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="X20">
         <v>8.6</v>
@@ -5473,67 +5473,67 @@
         <v>6.8</v>
       </c>
       <c r="Z20">
+        <v>11</v>
+      </c>
+      <c r="AA20">
+        <v>25</v>
+      </c>
+      <c r="AB20">
         <v>12.5</v>
       </c>
-      <c r="AA20">
-        <v>29</v>
-      </c>
-      <c r="AB20">
-        <v>10.5</v>
-      </c>
       <c r="AC20">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE20">
+        <v>28</v>
+      </c>
+      <c r="AF20">
         <v>65</v>
       </c>
-      <c r="AF20">
-        <v>32</v>
-      </c>
       <c r="AG20">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="AH20">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI20">
-        <v>460</v>
+        <v>60</v>
       </c>
       <c r="AJ20">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK20">
         <v>90</v>
       </c>
       <c r="AL20">
-        <v>540</v>
+        <v>260</v>
       </c>
       <c r="AM20">
         <v>500</v>
       </c>
       <c r="AN20">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="AO20">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="AP20">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ20">
         <v>6</v>
       </c>
       <c r="AR20">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS20">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT20">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AU20">
         <v>7</v>
@@ -5542,40 +5542,40 @@
         <v>10</v>
       </c>
       <c r="AW20">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AX20">
+        <v>15.5</v>
+      </c>
+      <c r="AY20">
+        <v>18.5</v>
+      </c>
+      <c r="AZ20">
+        <v>22</v>
+      </c>
+      <c r="BA20">
+        <v>55</v>
+      </c>
+      <c r="BB20">
+        <v>16</v>
+      </c>
+      <c r="BC20">
+        <v>15</v>
+      </c>
+      <c r="BD20">
+        <v>90</v>
+      </c>
+      <c r="BE20">
+        <v>17</v>
+      </c>
+      <c r="BF20">
         <v>16.5</v>
       </c>
-      <c r="AY20">
-        <v>16</v>
-      </c>
-      <c r="AZ20">
-        <v>21</v>
-      </c>
-      <c r="BA20">
-        <v>36</v>
-      </c>
-      <c r="BB20">
-        <v>13.5</v>
-      </c>
-      <c r="BC20">
-        <v>60</v>
-      </c>
-      <c r="BD20">
-        <v>46</v>
-      </c>
-      <c r="BE20">
-        <v>14.5</v>
-      </c>
-      <c r="BF20">
-        <v>30</v>
-      </c>
       <c r="BG20">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH20">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BI20">
         <v>2.38</v>
@@ -5584,55 +5584,55 @@
         <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>19.5</v>
+        <v>2.36</v>
       </c>
       <c r="BN20">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BO20">
         <v>5.4</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BQ20">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS20">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="BT20">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BU20">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="BV20">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BW20">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="CA20">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="CB20" t="s">
         <v>149</v>
@@ -5658,19 +5658,19 @@
         <v>1.74</v>
       </c>
       <c r="G21">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="H21">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I21">
         <v>5.8</v>
       </c>
       <c r="J21">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K21">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.43</v>
@@ -5679,16 +5679,16 @@
         <v>1.08</v>
       </c>
       <c r="N21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O21">
         <v>1.35</v>
       </c>
       <c r="P21">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="Q21">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R21">
         <v>1.34</v>
@@ -5700,13 +5700,13 @@
         <v>1.98</v>
       </c>
       <c r="U21">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W21">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X21">
         <v>13.5</v>
@@ -5718,22 +5718,22 @@
         <v>44</v>
       </c>
       <c r="AA21">
-        <v>690</v>
+        <v>150</v>
       </c>
       <c r="AB21">
         <v>8</v>
       </c>
       <c r="AC21">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD21">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE21">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="AF21">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG21">
         <v>9.4</v>
@@ -5742,10 +5742,10 @@
         <v>21</v>
       </c>
       <c r="AI21">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK21">
         <v>19</v>
@@ -5754,58 +5754,58 @@
         <v>40</v>
       </c>
       <c r="AM21">
-        <v>380</v>
+        <v>130</v>
       </c>
       <c r="AN21">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AO21">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP21">
         <v>12.5</v>
       </c>
       <c r="AQ21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR21">
         <v>38</v>
       </c>
       <c r="AS21">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AT21">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU21">
         <v>8</v>
       </c>
       <c r="AV21">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW21">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AX21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY21">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ21">
         <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB21">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD21">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE21">
         <v>50</v>
@@ -5817,64 +5817,64 @@
         <v>38</v>
       </c>
       <c r="BH21">
-        <v>3.3</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="BJ21">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>6.6</v>
+        <v>1.04</v>
       </c>
       <c r="BL21">
         <v>1000</v>
       </c>
       <c r="BM21">
-        <v>16.5</v>
+        <v>1.04</v>
       </c>
       <c r="BN21">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>3.8</v>
+        <v>1.04</v>
       </c>
       <c r="BP21">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>7.2</v>
+        <v>1.04</v>
       </c>
       <c r="BR21">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="BT21">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BV21">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>13.5</v>
+        <v>1.04</v>
       </c>
       <c r="BX21">
         <v>1000</v>
       </c>
       <c r="BY21">
-        <v>14</v>
+        <v>1.04</v>
       </c>
       <c r="BZ21">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>10.5</v>
+        <v>1.04</v>
       </c>
       <c r="CB21" t="s">
         <v>149</v>
@@ -5897,22 +5897,22 @@
         <v>146</v>
       </c>
       <c r="F22">
-        <v>4.6</v>
+        <v>3.95</v>
       </c>
       <c r="G22">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H22">
-        <v>1.93</v>
+        <v>2.12</v>
       </c>
       <c r="I22">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="J22">
+        <v>3.55</v>
+      </c>
+      <c r="K22">
         <v>3.65</v>
-      </c>
-      <c r="K22">
-        <v>3.7</v>
       </c>
       <c r="L22">
         <v>1.44</v>
@@ -5927,10 +5927,10 @@
         <v>1.35</v>
       </c>
       <c r="P22">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="Q22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R22">
         <v>1.34</v>
@@ -5939,169 +5939,169 @@
         <v>3.75</v>
       </c>
       <c r="T22">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U22">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="W22">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="X22">
         <v>13.5</v>
       </c>
       <c r="Y22">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AA22">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AB22">
+        <v>14</v>
+      </c>
+      <c r="AC22">
+        <v>7.6</v>
+      </c>
+      <c r="AD22">
+        <v>9.6</v>
+      </c>
+      <c r="AE22">
+        <v>22</v>
+      </c>
+      <c r="AF22">
+        <v>29</v>
+      </c>
+      <c r="AG22">
         <v>16</v>
       </c>
-      <c r="AC22">
-        <v>7.8</v>
-      </c>
-      <c r="AD22">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AE22">
-        <v>20</v>
-      </c>
-      <c r="AF22">
-        <v>34</v>
-      </c>
-      <c r="AG22">
-        <v>17.5</v>
-      </c>
       <c r="AH22">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AI22">
         <v>40</v>
       </c>
       <c r="AJ22">
+        <v>80</v>
+      </c>
+      <c r="AK22">
+        <v>50</v>
+      </c>
+      <c r="AL22">
+        <v>60</v>
+      </c>
+      <c r="AM22">
         <v>110</v>
       </c>
-      <c r="AK22">
+      <c r="AN22">
         <v>60</v>
       </c>
-      <c r="AL22">
-        <v>150</v>
-      </c>
-      <c r="AM22">
-        <v>320</v>
-      </c>
-      <c r="AN22">
-        <v>80</v>
-      </c>
       <c r="AO22">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP22">
         <v>12.5</v>
       </c>
       <c r="AQ22">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR22">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AS22">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AT22">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AU22">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW22">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX22">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AY22">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AZ22">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA22">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BB22">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BC22">
+        <v>46</v>
+      </c>
+      <c r="BD22">
         <v>50</v>
       </c>
-      <c r="BD22">
-        <v>60</v>
-      </c>
       <c r="BE22">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="BF22">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="BG22">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH22">
         <v>3.3</v>
       </c>
       <c r="BI22">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BJ22">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK22">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM22">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BN22">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO22">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP22">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="BQ22">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BR22">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BS22">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BT22">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BU22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV22">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BW22">
         <v>7.8</v>
@@ -6110,10 +6110,10 @@
         <v>30</v>
       </c>
       <c r="BY22">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BZ22">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA22">
         <v>10.5</v>
@@ -6139,7 +6139,7 @@
         <v>147</v>
       </c>
       <c r="F23">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G23">
         <v>2.04</v>
@@ -6148,46 +6148,46 @@
         <v>4.5</v>
       </c>
       <c r="I23">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="J23">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L23">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M23">
         <v>1.1</v>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O23">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P23">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="Q23">
         <v>2.36</v>
       </c>
       <c r="R23">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S23">
         <v>4.7</v>
       </c>
       <c r="T23">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U23">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V23">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W23">
         <v>1.96</v>
@@ -6196,7 +6196,7 @@
         <v>11</v>
       </c>
       <c r="Y23">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Z23">
         <v>32</v>
@@ -6205,7 +6205,7 @@
         <v>130</v>
       </c>
       <c r="AB23">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC23">
         <v>7.8</v>
@@ -6214,25 +6214,25 @@
         <v>20</v>
       </c>
       <c r="AE23">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF23">
         <v>11.5</v>
       </c>
       <c r="AG23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH23">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AI23">
         <v>95</v>
       </c>
       <c r="AJ23">
+        <v>26</v>
+      </c>
+      <c r="AK23">
         <v>25</v>
-      </c>
-      <c r="AK23">
-        <v>29</v>
       </c>
       <c r="AL23">
         <v>50</v>
@@ -6241,22 +6241,22 @@
         <v>180</v>
       </c>
       <c r="AN23">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO23">
         <v>110</v>
       </c>
       <c r="AP23">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23">
         <v>12</v>
       </c>
       <c r="AR23">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="AS23">
-        <v>9.199999999999999</v>
+        <v>75</v>
       </c>
       <c r="AT23">
         <v>6.8</v>
@@ -6265,13 +6265,13 @@
         <v>7</v>
       </c>
       <c r="AV23">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW23">
-        <v>8.6</v>
+        <v>46</v>
       </c>
       <c r="AX23">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AY23">
         <v>10</v>
@@ -6280,7 +6280,7 @@
         <v>20</v>
       </c>
       <c r="BA23">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB23">
         <v>20</v>
@@ -6289,52 +6289,52 @@
         <v>22</v>
       </c>
       <c r="BD23">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BE23">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="BF23">
         <v>18</v>
       </c>
       <c r="BG23">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="BH23">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BI23">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ23">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK23">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="BN23">
         <v>4.4</v>
       </c>
       <c r="BO23">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BP23">
         <v>15</v>
       </c>
       <c r="BQ23">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR23">
         <v>36</v>
       </c>
       <c r="BS23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT23">
         <v>8.199999999999999</v>
@@ -6346,7 +6346,7 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BX23">
         <v>1000</v>
@@ -6358,7 +6358,7 @@
         <v>36</v>
       </c>
       <c r="CA23">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB23" t="s">
         <v>149</v>
@@ -6384,19 +6384,19 @@
         <v>1.43</v>
       </c>
       <c r="G24">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H24">
         <v>7.4</v>
       </c>
       <c r="I24">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J24">
         <v>5.1</v>
       </c>
       <c r="K24">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="L24">
         <v>1.28</v>
@@ -6405,142 +6405,142 @@
         <v>1.03</v>
       </c>
       <c r="N24">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="O24">
         <v>1.19</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q24">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R24">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="S24">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T24">
         <v>1.78</v>
       </c>
       <c r="U24">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V24">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W24">
         <v>3.05</v>
       </c>
       <c r="X24">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y24">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="Z24">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AA24">
         <v>270</v>
       </c>
       <c r="AB24">
+        <v>11.5</v>
+      </c>
+      <c r="AC24">
         <v>13</v>
       </c>
-      <c r="AC24">
-        <v>15</v>
-      </c>
       <c r="AD24">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AE24">
         <v>120</v>
       </c>
       <c r="AF24">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG24">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH24">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI24">
         <v>100</v>
       </c>
       <c r="AJ24">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK24">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AL24">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM24">
+        <v>110</v>
+      </c>
+      <c r="AN24">
+        <v>5.4</v>
+      </c>
+      <c r="AO24">
         <v>120</v>
       </c>
-      <c r="AN24">
-        <v>5.6</v>
-      </c>
-      <c r="AO24">
-        <v>130</v>
-      </c>
       <c r="AP24">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ24">
-        <v>4.7</v>
+        <v>25</v>
       </c>
       <c r="AR24">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="AS24">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AT24">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AU24">
         <v>10.5</v>
       </c>
       <c r="AV24">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW24">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AX24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ24">
         <v>18.5</v>
       </c>
       <c r="BA24">
-        <v>5.1</v>
+        <v>44</v>
       </c>
       <c r="BB24">
+        <v>11.5</v>
+      </c>
+      <c r="BC24">
+        <v>12</v>
+      </c>
+      <c r="BD24">
+        <v>22</v>
+      </c>
+      <c r="BE24">
         <v>9.6</v>
       </c>
-      <c r="BC24">
-        <v>12.5</v>
-      </c>
-      <c r="BD24">
-        <v>24</v>
-      </c>
-      <c r="BE24">
-        <v>5.1</v>
-      </c>
       <c r="BF24">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BG24">
-        <v>5.1</v>
+        <v>50</v>
       </c>
       <c r="BH24">
         <v>4.7</v>
@@ -6564,7 +6564,7 @@
         <v>4.4</v>
       </c>
       <c r="BO24">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP24">
         <v>8.800000000000001</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="142">
   <si>
     <t>League</t>
   </si>
@@ -295,6 +295,9 @@
     <t>19:15:00</t>
   </si>
   <si>
+    <t>19:45:00</t>
+  </si>
+  <si>
     <t>20:00:00</t>
   </si>
   <si>
@@ -337,21 +340,21 @@
     <t>KV Vesturbaejar</t>
   </si>
   <si>
+    <t>Vikingur Olafsvik</t>
+  </si>
+  <si>
     <t>Throttur Vogar</t>
   </si>
   <si>
-    <t>Vikingur Olafsvik</t>
-  </si>
-  <si>
     <t>Grindavik</t>
   </si>
   <si>
+    <t>Kari</t>
+  </si>
+  <si>
     <t>Throttur</t>
   </si>
   <si>
-    <t>Kari</t>
-  </si>
-  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
@@ -397,21 +400,21 @@
     <t>Reynir Sandgeroi</t>
   </si>
   <si>
+    <t>Fjolnir</t>
+  </si>
+  <si>
     <t>Hviti Riddarinn</t>
   </si>
   <si>
-    <t>Fjolnir</t>
-  </si>
-  <si>
     <t>Leiknir R</t>
   </si>
   <si>
+    <t>Kormakur/Hvot</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>Kormakur/Hvot</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -436,7 +439,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 11:49:36</t>
+    <t>2026-07-29 13:57:47</t>
   </si>
 </sst>
 </file>
@@ -1024,31 +1027,31 @@
         <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F2">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G2">
         <v>2.5</v>
       </c>
       <c r="H2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I2">
         <v>4.1</v>
       </c>
       <c r="J2">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="K2">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="L2">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="M2">
         <v>1.2</v>
@@ -1057,19 +1060,19 @@
         <v>2.16</v>
       </c>
       <c r="O2">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="P2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q2">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R2">
         <v>1.11</v>
       </c>
       <c r="S2">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T2">
         <v>2.68</v>
@@ -1090,43 +1093,43 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AB2">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AC2">
         <v>7.2</v>
       </c>
       <c r="AD2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE2">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AF2">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG2">
         <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI2">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AJ2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AK2">
         <v>48</v>
       </c>
       <c r="AL2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AM2">
         <v>500</v>
@@ -1135,10 +1138,10 @@
         <v>65</v>
       </c>
       <c r="AO2">
-        <v>490</v>
+        <v>190</v>
       </c>
       <c r="AP2">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2">
         <v>8</v>
@@ -1150,7 +1153,7 @@
         <v>90</v>
       </c>
       <c r="AT2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU2">
         <v>6.6</v>
@@ -1189,19 +1192,19 @@
         <v>50</v>
       </c>
       <c r="BG2">
-        <v>42</v>
+        <v>80</v>
       </c>
       <c r="BH2">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="BI2">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="BJ2">
         <v>14</v>
       </c>
       <c r="BK2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BL2">
         <v>1000</v>
@@ -1213,46 +1216,46 @@
         <v>5</v>
       </c>
       <c r="BO2">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BR2">
         <v>65</v>
       </c>
       <c r="BS2">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="BT2">
         <v>7</v>
       </c>
       <c r="BU2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BV2">
         <v>50</v>
       </c>
       <c r="BW2">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="BZ2">
         <v>85</v>
       </c>
       <c r="CA2">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="CB2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1266,19 +1269,19 @@
         <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F3">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="H3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="I3">
         <v>12.5</v>
@@ -1287,7 +1290,7 @@
         <v>7.2</v>
       </c>
       <c r="K3">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>1.17</v>
@@ -1296,70 +1299,70 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="O3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="Q3">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="R3">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="S3">
         <v>1.68</v>
       </c>
       <c r="T3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="U3">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="V3">
         <v>1.08</v>
       </c>
       <c r="W3">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X3">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="Y3">
         <v>130</v>
       </c>
       <c r="Z3">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AA3">
         <v>370</v>
       </c>
       <c r="AB3">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AC3">
         <v>22</v>
       </c>
       <c r="AD3">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="AE3">
         <v>260</v>
       </c>
       <c r="AF3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH3">
         <v>24</v>
       </c>
       <c r="AI3">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="AJ3">
         <v>14.5</v>
@@ -1368,22 +1371,22 @@
         <v>13.5</v>
       </c>
       <c r="AL3">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AM3">
         <v>320</v>
       </c>
       <c r="AN3">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="AO3">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AP3">
         <v>42</v>
       </c>
       <c r="AQ3">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AR3">
         <v>11.5</v>
@@ -1392,10 +1395,10 @@
         <v>12</v>
       </c>
       <c r="AT3">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU3">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AV3">
         <v>36</v>
@@ -1404,16 +1407,16 @@
         <v>11.5</v>
       </c>
       <c r="AX3">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY3">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA3">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BB3">
         <v>12</v>
@@ -1428,7 +1431,7 @@
         <v>28</v>
       </c>
       <c r="BF3">
-        <v>2.42</v>
+        <v>2.66</v>
       </c>
       <c r="BG3">
         <v>11</v>
@@ -1437,7 +1440,7 @@
         <v>6.8</v>
       </c>
       <c r="BI3">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
@@ -1494,7 +1497,7 @@
         <v>5.5</v>
       </c>
       <c r="CB3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1508,58 +1511,58 @@
         <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F4">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="G4">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H4">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I4">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J4">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L4">
         <v>1.21</v>
       </c>
       <c r="M4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="O4">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P4">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="Q4">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="R4">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="S4">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="T4">
         <v>1.47</v>
       </c>
       <c r="U4">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1568,13 +1571,13 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Y4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="Z4">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AA4">
         <v>160</v>
@@ -1583,7 +1586,7 @@
         <v>21</v>
       </c>
       <c r="AC4">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AD4">
         <v>20</v>
@@ -1604,94 +1607,94 @@
         <v>36</v>
       </c>
       <c r="AJ4">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK4">
         <v>16.5</v>
       </c>
       <c r="AL4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM4">
         <v>46</v>
       </c>
       <c r="AN4">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AO4">
         <v>22</v>
       </c>
       <c r="AP4">
-        <v>22</v>
+        <v>8.4</v>
       </c>
       <c r="AQ4">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR4">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="AS4">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AT4">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AU4">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AV4">
         <v>16.5</v>
       </c>
       <c r="AW4">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="AX4">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY4">
         <v>9</v>
       </c>
       <c r="AZ4">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BA4">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BB4">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BC4">
         <v>13.5</v>
       </c>
       <c r="BD4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BE4">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="BF4">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="BG4">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BH4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BI4">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BJ4">
         <v>8.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BN4">
         <v>5.6</v>
@@ -1703,16 +1706,16 @@
         <v>11.5</v>
       </c>
       <c r="BQ4">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BR4">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BS4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BT4">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU4">
         <v>4.7</v>
@@ -1721,22 +1724,22 @@
         <v>28</v>
       </c>
       <c r="BW4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BX4">
         <v>28</v>
       </c>
       <c r="BY4">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ4">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA4">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="CB4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1750,25 +1753,25 @@
         <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F5">
         <v>3.1</v>
       </c>
       <c r="G5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H5">
         <v>2.04</v>
       </c>
       <c r="I5">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="J5">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K5">
         <v>5.2</v>
@@ -1786,28 +1789,28 @@
         <v>1.07</v>
       </c>
       <c r="P5">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Q5">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="R5">
         <v>2.46</v>
       </c>
       <c r="S5">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="T5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="U5">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="V5">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="W5">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="X5">
         <v>500</v>
@@ -1816,7 +1819,7 @@
         <v>65</v>
       </c>
       <c r="Z5">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AA5">
         <v>70</v>
@@ -1849,31 +1852,31 @@
         <v>220</v>
       </c>
       <c r="AK5">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AL5">
         <v>26</v>
       </c>
       <c r="AM5">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="AN5">
         <v>11</v>
       </c>
       <c r="AO5">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AP5">
-        <v>8.6</v>
+        <v>17.5</v>
       </c>
       <c r="AQ5">
-        <v>13.5</v>
+        <v>24</v>
       </c>
       <c r="AR5">
         <v>12.5</v>
       </c>
       <c r="AS5">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT5">
         <v>14</v>
@@ -1903,16 +1906,16 @@
         <v>8.6</v>
       </c>
       <c r="BC5">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BD5">
-        <v>12</v>
+        <v>17.5</v>
       </c>
       <c r="BE5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG5">
         <v>4.7</v>
@@ -1927,19 +1930,19 @@
         <v>8.6</v>
       </c>
       <c r="BK5">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN5">
         <v>8.4</v>
       </c>
       <c r="BO5">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BP5">
         <v>21</v>
@@ -1951,7 +1954,7 @@
         <v>20</v>
       </c>
       <c r="BS5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BT5">
         <v>6.8</v>
@@ -1963,22 +1966,22 @@
         <v>13</v>
       </c>
       <c r="BW5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BX5">
         <v>16</v>
       </c>
       <c r="BY5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BZ5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="CA5">
         <v>6</v>
       </c>
       <c r="CB5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1992,19 +1995,19 @@
         <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F6">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G6">
         <v>1.48</v>
       </c>
       <c r="H6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="I6">
         <v>8</v>
@@ -2016,19 +2019,19 @@
         <v>6</v>
       </c>
       <c r="L6">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="O6">
         <v>1.15</v>
       </c>
       <c r="P6">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Q6">
         <v>1.47</v>
@@ -2037,13 +2040,13 @@
         <v>1.78</v>
       </c>
       <c r="S6">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T6">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U6">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>1.14</v>
@@ -2052,13 +2055,13 @@
         <v>3</v>
       </c>
       <c r="X6">
-        <v>38</v>
+        <v>950</v>
       </c>
       <c r="Y6">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="Z6">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AA6">
         <v>700</v>
@@ -2082,7 +2085,7 @@
         <v>11.5</v>
       </c>
       <c r="AH6">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI6">
         <v>700</v>
@@ -2100,7 +2103,7 @@
         <v>580</v>
       </c>
       <c r="AN6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AO6">
         <v>70</v>
@@ -2109,13 +2112,13 @@
         <v>12.5</v>
       </c>
       <c r="AQ6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR6">
         <v>8.6</v>
       </c>
       <c r="AS6">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT6">
         <v>11.5</v>
@@ -2124,10 +2127,10 @@
         <v>11</v>
       </c>
       <c r="AV6">
-        <v>21</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2136,10 +2139,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ6">
-        <v>16.5</v>
+        <v>7.6</v>
       </c>
       <c r="BA6">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB6">
         <v>12</v>
@@ -2151,10 +2154,10 @@
         <v>21</v>
       </c>
       <c r="BE6">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
         <v>10.5</v>
@@ -2169,13 +2172,13 @@
         <v>11</v>
       </c>
       <c r="BK6">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN6">
         <v>4.4</v>
@@ -2187,40 +2190,40 @@
         <v>8.4</v>
       </c>
       <c r="BQ6">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BR6">
         <v>18</v>
       </c>
       <c r="BS6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT6">
         <v>12</v>
       </c>
       <c r="BU6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ6">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="CA6">
         <v>5.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2234,25 +2237,25 @@
         <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F7">
         <v>3.25</v>
       </c>
       <c r="G7">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H7">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I7">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J7">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K7">
         <v>3.25</v>
@@ -2273,25 +2276,25 @@
         <v>1.75</v>
       </c>
       <c r="Q7">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R7">
         <v>1.27</v>
       </c>
       <c r="S7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T7">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U7">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="W7">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X7">
         <v>11.5</v>
@@ -2318,10 +2321,10 @@
         <v>34</v>
       </c>
       <c r="AF7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG7">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH7">
         <v>18</v>
@@ -2384,7 +2387,7 @@
         <v>38</v>
       </c>
       <c r="BB7">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC7">
         <v>34</v>
@@ -2393,25 +2396,25 @@
         <v>27</v>
       </c>
       <c r="BE7">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BH7">
         <v>3.1</v>
       </c>
       <c r="BI7">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ7">
         <v>10.5</v>
       </c>
       <c r="BK7">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
@@ -2462,7 +2465,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2476,13 +2479,13 @@
         <v>92</v>
       </c>
       <c r="D8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F8">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -2491,112 +2494,112 @@
         <v>2.1</v>
       </c>
       <c r="I8">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="J8">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K8">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="L8">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="M8">
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="O8">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="P8">
-        <v>5.4</v>
+        <v>6.4</v>
       </c>
       <c r="Q8">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="R8">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="S8">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="T8">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="U8">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="V8">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="W8">
         <v>1.5</v>
       </c>
       <c r="X8">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="Y8">
+        <v>55</v>
+      </c>
+      <c r="Z8">
+        <v>42</v>
+      </c>
+      <c r="AA8">
         <v>44</v>
       </c>
-      <c r="Z8">
-        <v>36</v>
-      </c>
-      <c r="AA8">
-        <v>42</v>
-      </c>
       <c r="AB8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AC8">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AD8">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="AE8">
         <v>22</v>
       </c>
       <c r="AF8">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AG8">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI8">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AJ8">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AK8">
         <v>29</v>
       </c>
       <c r="AL8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM8">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="AN8">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AO8">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="AP8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ8">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AR8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
         <v>14.5</v>
@@ -2605,10 +2608,10 @@
         <v>17.5</v>
       </c>
       <c r="AU8">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AV8">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW8">
         <v>17.5</v>
@@ -2617,16 +2620,16 @@
         <v>17.5</v>
       </c>
       <c r="AY8">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AZ8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA8">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BB8">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BC8">
         <v>12.5</v>
@@ -2635,76 +2638,76 @@
         <v>18.5</v>
       </c>
       <c r="BE8">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BF8">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BG8">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BH8">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BI8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BJ8">
         <v>8.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BL8">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BM8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BN8">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BO8">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BP8">
         <v>19</v>
       </c>
       <c r="BQ8">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR8">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BS8">
         <v>6.4</v>
       </c>
       <c r="BT8">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU8">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BV8">
         <v>14</v>
       </c>
       <c r="BW8">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BX8">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BY8">
         <v>6</v>
       </c>
       <c r="BZ8">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="CA8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="CB8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2718,235 +2721,235 @@
         <v>92</v>
       </c>
       <c r="D9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F9">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="G9">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="H9">
-        <v>3.35</v>
+        <v>2.14</v>
       </c>
       <c r="I9">
-        <v>3.55</v>
+        <v>2.24</v>
       </c>
       <c r="J9">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
       <c r="L9">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="M9">
         <v>1.02</v>
       </c>
       <c r="N9">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="O9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P9">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="Q9">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="R9">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="T9">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="U9">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="V9">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="W9">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
       <c r="X9">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="Y9">
+        <v>26</v>
+      </c>
+      <c r="Z9">
+        <v>25</v>
+      </c>
+      <c r="AA9">
+        <v>34</v>
+      </c>
+      <c r="AB9">
+        <v>30</v>
+      </c>
+      <c r="AC9">
+        <v>14</v>
+      </c>
+      <c r="AD9">
+        <v>14</v>
+      </c>
+      <c r="AE9">
+        <v>21</v>
+      </c>
+      <c r="AF9">
+        <v>34</v>
+      </c>
+      <c r="AG9">
+        <v>16.5</v>
+      </c>
+      <c r="AH9">
+        <v>14.5</v>
+      </c>
+      <c r="AI9">
+        <v>23</v>
+      </c>
+      <c r="AJ9">
+        <v>55</v>
+      </c>
+      <c r="AK9">
+        <v>27</v>
+      </c>
+      <c r="AL9">
+        <v>26</v>
+      </c>
+      <c r="AM9">
+        <v>38</v>
+      </c>
+      <c r="AN9">
+        <v>11.5</v>
+      </c>
+      <c r="AO9">
+        <v>7.4</v>
+      </c>
+      <c r="AP9">
         <v>29</v>
       </c>
-      <c r="Z9">
+      <c r="AQ9">
+        <v>21</v>
+      </c>
+      <c r="AR9">
+        <v>20</v>
+      </c>
+      <c r="AS9">
+        <v>25</v>
+      </c>
+      <c r="AT9">
+        <v>23</v>
+      </c>
+      <c r="AU9">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV9">
+        <v>10</v>
+      </c>
+      <c r="AW9">
+        <v>17</v>
+      </c>
+      <c r="AX9">
+        <v>27</v>
+      </c>
+      <c r="AY9">
+        <v>13</v>
+      </c>
+      <c r="AZ9">
+        <v>11.5</v>
+      </c>
+      <c r="BA9">
+        <v>18.5</v>
+      </c>
+      <c r="BB9">
         <v>34</v>
       </c>
-      <c r="AA9">
-        <v>60</v>
-      </c>
-      <c r="AB9">
-        <v>22</v>
-      </c>
-      <c r="AC9">
-        <v>13</v>
-      </c>
-      <c r="AD9">
-        <v>17</v>
-      </c>
-      <c r="AE9">
-        <v>32</v>
-      </c>
-      <c r="AF9">
-        <v>22</v>
-      </c>
-      <c r="AG9">
-        <v>13.5</v>
-      </c>
-      <c r="AH9">
-        <v>15</v>
-      </c>
-      <c r="AI9">
-        <v>30</v>
-      </c>
-      <c r="AJ9">
-        <v>29</v>
-      </c>
-      <c r="AK9">
+      <c r="BC9">
         <v>19.5</v>
-      </c>
-      <c r="AL9">
-        <v>23</v>
-      </c>
-      <c r="AM9">
-        <v>42</v>
-      </c>
-      <c r="AN9">
-        <v>7.4</v>
-      </c>
-      <c r="AO9">
-        <v>15</v>
-      </c>
-      <c r="AP9">
-        <v>19</v>
-      </c>
-      <c r="AQ9">
-        <v>16</v>
-      </c>
-      <c r="AR9">
-        <v>15.5</v>
-      </c>
-      <c r="AS9">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT9">
-        <v>17.5</v>
-      </c>
-      <c r="AU9">
-        <v>10.5</v>
-      </c>
-      <c r="AV9">
-        <v>14</v>
-      </c>
-      <c r="AW9">
-        <v>14</v>
-      </c>
-      <c r="AX9">
-        <v>17.5</v>
-      </c>
-      <c r="AY9">
-        <v>10.5</v>
-      </c>
-      <c r="AZ9">
-        <v>12</v>
-      </c>
-      <c r="BA9">
-        <v>13</v>
-      </c>
-      <c r="BB9">
-        <v>15</v>
-      </c>
-      <c r="BC9">
-        <v>16</v>
       </c>
       <c r="BD9">
         <v>19</v>
       </c>
       <c r="BE9">
-        <v>17.5</v>
+        <v>29</v>
       </c>
       <c r="BF9">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="BG9">
-        <v>12</v>
+        <v>6.4</v>
       </c>
       <c r="BH9">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BI9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BJ9">
         <v>8.4</v>
       </c>
       <c r="BK9">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BL9">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BM9">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BN9">
+        <v>7.8</v>
+      </c>
+      <c r="BO9">
+        <v>5.6</v>
+      </c>
+      <c r="BP9">
+        <v>19.5</v>
+      </c>
+      <c r="BQ9">
+        <v>6.4</v>
+      </c>
+      <c r="BR9">
+        <v>22</v>
+      </c>
+      <c r="BS9">
+        <v>6.6</v>
+      </c>
+      <c r="BT9">
+        <v>6.6</v>
+      </c>
+      <c r="BU9">
+        <v>4.8</v>
+      </c>
+      <c r="BV9">
+        <v>14.5</v>
+      </c>
+      <c r="BW9">
+        <v>5.7</v>
+      </c>
+      <c r="BX9">
+        <v>18.5</v>
+      </c>
+      <c r="BY9">
         <v>6.2</v>
       </c>
-      <c r="BO9">
-        <v>3.8</v>
-      </c>
-      <c r="BP9">
-        <v>13.5</v>
-      </c>
-      <c r="BQ9">
-        <v>5.7</v>
-      </c>
-      <c r="BR9">
-        <v>18.5</v>
-      </c>
-      <c r="BS9">
-        <v>6.4</v>
-      </c>
-      <c r="BT9">
-        <v>8</v>
-      </c>
-      <c r="BU9">
-        <v>4.4</v>
-      </c>
-      <c r="BV9">
-        <v>22</v>
-      </c>
-      <c r="BW9">
-        <v>6.8</v>
-      </c>
-      <c r="BX9">
-        <v>24</v>
-      </c>
-      <c r="BY9">
-        <v>7</v>
-      </c>
       <c r="BZ9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="CA9">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="CB9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2960,178 +2963,178 @@
         <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="G10">
-        <v>3.1</v>
+        <v>2.04</v>
       </c>
       <c r="H10">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="I10">
-        <v>2.24</v>
+        <v>3.6</v>
       </c>
       <c r="J10">
         <v>4.5</v>
       </c>
       <c r="K10">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M10">
         <v>1.02</v>
       </c>
       <c r="N10">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="O10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P10">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="Q10">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R10">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="S10">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="T10">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="V10">
-        <v>1.8</v>
+        <v>1.38</v>
       </c>
       <c r="W10">
-        <v>1.47</v>
+        <v>1.96</v>
       </c>
       <c r="X10">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Y10">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Z10">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AA10">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AB10">
+        <v>22</v>
+      </c>
+      <c r="AC10">
+        <v>13</v>
+      </c>
+      <c r="AD10">
+        <v>17.5</v>
+      </c>
+      <c r="AE10">
+        <v>32</v>
+      </c>
+      <c r="AF10">
+        <v>22</v>
+      </c>
+      <c r="AG10">
+        <v>13.5</v>
+      </c>
+      <c r="AH10">
+        <v>15</v>
+      </c>
+      <c r="AI10">
         <v>30</v>
       </c>
-      <c r="AC10">
+      <c r="AJ10">
+        <v>29</v>
+      </c>
+      <c r="AK10">
+        <v>19.5</v>
+      </c>
+      <c r="AL10">
+        <v>23</v>
+      </c>
+      <c r="AM10">
+        <v>42</v>
+      </c>
+      <c r="AN10">
+        <v>7.2</v>
+      </c>
+      <c r="AO10">
+        <v>15</v>
+      </c>
+      <c r="AP10">
+        <v>18.5</v>
+      </c>
+      <c r="AQ10">
+        <v>16.5</v>
+      </c>
+      <c r="AR10">
+        <v>15.5</v>
+      </c>
+      <c r="AS10">
+        <v>8.4</v>
+      </c>
+      <c r="AT10">
+        <v>17.5</v>
+      </c>
+      <c r="AU10">
+        <v>10.5</v>
+      </c>
+      <c r="AV10">
         <v>14</v>
       </c>
-      <c r="AD10">
+      <c r="AW10">
         <v>14</v>
       </c>
-      <c r="AE10">
-        <v>21</v>
-      </c>
-      <c r="AF10">
-        <v>34</v>
-      </c>
-      <c r="AG10">
-        <v>16.5</v>
-      </c>
-      <c r="AH10">
-        <v>14.5</v>
-      </c>
-      <c r="AI10">
+      <c r="AX10">
+        <v>17.5</v>
+      </c>
+      <c r="AY10">
+        <v>10.5</v>
+      </c>
+      <c r="AZ10">
+        <v>12</v>
+      </c>
+      <c r="BA10">
+        <v>13</v>
+      </c>
+      <c r="BB10">
         <v>23</v>
       </c>
-      <c r="AJ10">
-        <v>60</v>
-      </c>
-      <c r="AK10">
-        <v>27</v>
-      </c>
-      <c r="AL10">
-        <v>26</v>
-      </c>
-      <c r="AM10">
-        <v>38</v>
-      </c>
-      <c r="AN10">
-        <v>11.5</v>
-      </c>
-      <c r="AO10">
-        <v>7.4</v>
-      </c>
-      <c r="AP10">
-        <v>29</v>
-      </c>
-      <c r="AQ10">
-        <v>21</v>
-      </c>
-      <c r="AR10">
-        <v>20</v>
-      </c>
-      <c r="AS10">
-        <v>23</v>
-      </c>
-      <c r="AT10">
-        <v>23</v>
-      </c>
-      <c r="AU10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV10">
-        <v>10</v>
-      </c>
-      <c r="AW10">
+      <c r="BC10">
+        <v>15.5</v>
+      </c>
+      <c r="BD10">
+        <v>18.5</v>
+      </c>
+      <c r="BE10">
         <v>17.5</v>
       </c>
-      <c r="AX10">
-        <v>27</v>
-      </c>
-      <c r="AY10">
-        <v>13</v>
-      </c>
-      <c r="AZ10">
-        <v>11.5</v>
-      </c>
-      <c r="BA10">
-        <v>18.5</v>
-      </c>
-      <c r="BB10">
-        <v>36</v>
-      </c>
-      <c r="BC10">
-        <v>19</v>
-      </c>
-      <c r="BD10">
-        <v>19</v>
-      </c>
-      <c r="BE10">
-        <v>29</v>
-      </c>
       <c r="BF10">
-        <v>9.6</v>
+        <v>6</v>
       </c>
       <c r="BG10">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BH10">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BI10">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BJ10">
         <v>8.4</v>
@@ -3140,55 +3143,55 @@
         <v>4.5</v>
       </c>
       <c r="BL10">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BM10">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BN10">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BO10">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BP10">
-        <v>19</v>
+        <v>13.5</v>
       </c>
       <c r="BQ10">
+        <v>5.7</v>
+      </c>
+      <c r="BR10">
+        <v>18.5</v>
+      </c>
+      <c r="BS10">
         <v>6.4</v>
       </c>
-      <c r="BR10">
-        <v>21</v>
-      </c>
-      <c r="BS10">
-        <v>6.6</v>
-      </c>
       <c r="BT10">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BU10">
-        <v>3.95</v>
+        <v>6</v>
       </c>
       <c r="BV10">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="BW10">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BX10">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BY10">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BZ10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CA10">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="CB10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3202,16 +3205,16 @@
         <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F11">
         <v>2.44</v>
       </c>
       <c r="G11">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H11">
         <v>2.9</v>
@@ -3220,7 +3223,7 @@
         <v>3.05</v>
       </c>
       <c r="J11">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K11">
         <v>3.95</v>
@@ -3232,28 +3235,28 @@
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O11">
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R11">
         <v>1.55</v>
       </c>
       <c r="S11">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T11">
         <v>1.58</v>
       </c>
       <c r="U11">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="V11">
         <v>1.48</v>
@@ -3268,7 +3271,7 @@
         <v>17.5</v>
       </c>
       <c r="Z11">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AA11">
         <v>60</v>
@@ -3283,7 +3286,7 @@
         <v>13.5</v>
       </c>
       <c r="AE11">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="AF11">
         <v>22</v>
@@ -3298,10 +3301,10 @@
         <v>48</v>
       </c>
       <c r="AJ11">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK11">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL11">
         <v>46</v>
@@ -3310,13 +3313,13 @@
         <v>80</v>
       </c>
       <c r="AN11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO11">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP11">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AQ11">
         <v>14.5</v>
@@ -3325,7 +3328,7 @@
         <v>18</v>
       </c>
       <c r="AS11">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AT11">
         <v>12.5</v>
@@ -3364,10 +3367,10 @@
         <v>46</v>
       </c>
       <c r="BF11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BH11">
         <v>4.2</v>
@@ -3379,13 +3382,13 @@
         <v>8.6</v>
       </c>
       <c r="BK11">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN11">
         <v>5.7</v>
@@ -3397,16 +3400,16 @@
         <v>16.5</v>
       </c>
       <c r="BQ11">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR11">
         <v>25</v>
       </c>
       <c r="BS11">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BT11">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU11">
         <v>5.7</v>
@@ -3415,27 +3418,27 @@
         <v>1000</v>
       </c>
       <c r="BW11">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX11">
         <v>1000</v>
       </c>
       <c r="BY11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BZ11">
         <v>17.5</v>
       </c>
       <c r="CA11">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>88</v>
@@ -3444,477 +3447,477 @@
         <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F12">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="G12">
-        <v>2.46</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="I12">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="K12">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="L12">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="M12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N12">
-        <v>6.4</v>
+        <v>9.6</v>
       </c>
       <c r="O12">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="P12">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="R12">
+        <v>2.22</v>
+      </c>
+      <c r="S12">
         <v>1.75</v>
       </c>
-      <c r="S12">
-        <v>2.24</v>
-      </c>
       <c r="T12">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="U12">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="V12">
-        <v>1.52</v>
+        <v>1.01</v>
       </c>
       <c r="W12">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>30</v>
+        <v>150</v>
       </c>
       <c r="Y12">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="Z12">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AA12">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AB12">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AC12">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AD12">
+        <v>17</v>
+      </c>
+      <c r="AE12">
+        <v>36</v>
+      </c>
+      <c r="AF12">
+        <v>34</v>
+      </c>
+      <c r="AG12">
         <v>14.5</v>
-      </c>
-      <c r="AE12">
-        <v>27</v>
-      </c>
-      <c r="AF12">
-        <v>22</v>
-      </c>
-      <c r="AG12">
-        <v>12.5</v>
       </c>
       <c r="AH12">
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AJ12">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK12">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL12">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AM12">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AN12">
+        <v>6.8</v>
+      </c>
+      <c r="AO12">
+        <v>10.5</v>
+      </c>
+      <c r="AP12">
+        <v>22</v>
+      </c>
+      <c r="AQ12">
+        <v>25</v>
+      </c>
+      <c r="AR12">
+        <v>27</v>
+      </c>
+      <c r="AS12">
+        <v>38</v>
+      </c>
+      <c r="AT12">
+        <v>21</v>
+      </c>
+      <c r="AU12">
         <v>11.5</v>
       </c>
-      <c r="AO12">
-        <v>15</v>
-      </c>
-      <c r="AP12">
-        <v>20</v>
-      </c>
-      <c r="AQ12">
-        <v>17.5</v>
-      </c>
-      <c r="AR12">
-        <v>21</v>
-      </c>
-      <c r="AS12">
-        <v>30</v>
-      </c>
-      <c r="AT12">
-        <v>15.5</v>
-      </c>
-      <c r="AU12">
-        <v>9</v>
-      </c>
       <c r="AV12">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW12">
         <v>21</v>
       </c>
       <c r="AX12">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AY12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ12">
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="BB12">
+        <v>24</v>
+      </c>
+      <c r="BC12">
+        <v>17</v>
+      </c>
+      <c r="BD12">
+        <v>17.5</v>
+      </c>
+      <c r="BE12">
         <v>29</v>
       </c>
-      <c r="BC12">
-        <v>19</v>
-      </c>
-      <c r="BD12">
-        <v>20</v>
-      </c>
-      <c r="BE12">
-        <v>38</v>
-      </c>
       <c r="BF12">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="BG12">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BH12">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BI12">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BJ12">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BK12">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BL12">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN12">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BP12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BQ12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR12">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BS12">
+        <v>7.6</v>
+      </c>
+      <c r="BT12">
         <v>7.8</v>
       </c>
-      <c r="BT12">
-        <v>6.8</v>
-      </c>
       <c r="BU12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BV12">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BX12">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
         <v>8</v>
       </c>
       <c r="BZ12">
-        <v>14</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CA12">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="CB12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" t="s">
         <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F13">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="G13">
-        <v>2.26</v>
+        <v>2.46</v>
       </c>
       <c r="H13">
-        <v>2.92</v>
+        <v>2.78</v>
       </c>
       <c r="I13">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="J13">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="M13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N13">
-        <v>9.4</v>
+        <v>6.6</v>
       </c>
       <c r="O13">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>3.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q13">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="R13">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="S13">
-        <v>1.75</v>
+        <v>2.22</v>
       </c>
       <c r="T13">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="U13">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="V13">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="W13">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="X13">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="Y13">
-        <v>60</v>
+        <v>21</v>
       </c>
       <c r="Z13">
+        <v>27</v>
+      </c>
+      <c r="AA13">
         <v>55</v>
       </c>
-      <c r="AA13">
-        <v>210</v>
-      </c>
       <c r="AB13">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AC13">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AD13">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE13">
-        <v>210</v>
+        <v>27</v>
       </c>
       <c r="AF13">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AG13">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13">
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>500</v>
+        <v>30</v>
       </c>
       <c r="AJ13">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="AK13">
-        <v>160</v>
+        <v>23</v>
       </c>
       <c r="AL13">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AM13">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="AN13">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AO13">
+        <v>14.5</v>
+      </c>
+      <c r="AP13">
+        <v>20</v>
+      </c>
+      <c r="AQ13">
+        <v>17.5</v>
+      </c>
+      <c r="AR13">
+        <v>21</v>
+      </c>
+      <c r="AS13">
+        <v>30</v>
+      </c>
+      <c r="AT13">
+        <v>15.5</v>
+      </c>
+      <c r="AU13">
+        <v>9</v>
+      </c>
+      <c r="AV13">
+        <v>11.5</v>
+      </c>
+      <c r="AW13">
+        <v>21</v>
+      </c>
+      <c r="AX13">
+        <v>17.5</v>
+      </c>
+      <c r="AY13">
         <v>10.5</v>
-      </c>
-      <c r="AP13">
-        <v>10.5</v>
-      </c>
-      <c r="AQ13">
-        <v>14</v>
-      </c>
-      <c r="AR13">
-        <v>27</v>
-      </c>
-      <c r="AS13">
-        <v>18</v>
-      </c>
-      <c r="AT13">
-        <v>21</v>
-      </c>
-      <c r="AU13">
-        <v>11.5</v>
-      </c>
-      <c r="AV13">
-        <v>13.5</v>
-      </c>
-      <c r="AW13">
-        <v>18.5</v>
-      </c>
-      <c r="AX13">
-        <v>20</v>
-      </c>
-      <c r="AY13">
-        <v>11.5</v>
       </c>
       <c r="AZ13">
         <v>12</v>
       </c>
       <c r="BA13">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="BB13">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="BC13">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BD13">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BE13">
-        <v>9.800000000000001</v>
+        <v>38</v>
       </c>
       <c r="BF13">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="BG13">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BH13">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BI13">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="BJ13">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BK13">
         <v>4.9</v>
       </c>
       <c r="BL13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BM13">
         <v>10</v>
       </c>
       <c r="BN13">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BO13">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BP13">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BQ13">
         <v>6.8</v>
       </c>
       <c r="BR13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BS13">
+        <v>7.8</v>
+      </c>
+      <c r="BT13">
+        <v>6.8</v>
+      </c>
+      <c r="BU13">
+        <v>5.8</v>
+      </c>
+      <c r="BV13">
+        <v>19.5</v>
+      </c>
+      <c r="BW13">
         <v>7.4</v>
       </c>
-      <c r="BT13">
-        <v>7.8</v>
-      </c>
-      <c r="BU13">
-        <v>6</v>
-      </c>
-      <c r="BV13">
-        <v>18.5</v>
-      </c>
-      <c r="BW13">
-        <v>7.6</v>
-      </c>
       <c r="BX13">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ13">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="CA13">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="CB13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3925,73 +3928,73 @@
         <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F14">
         <v>2.46</v>
       </c>
       <c r="G14">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I14">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="J14">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="K14">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="L14">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="M14">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="N14">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="O14">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="P14">
         <v>1.43</v>
       </c>
       <c r="Q14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R14">
         <v>1.14</v>
       </c>
       <c r="S14">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T14">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="U14">
+        <v>1.66</v>
+      </c>
+      <c r="V14">
+        <v>1.33</v>
+      </c>
+      <c r="W14">
         <v>1.65</v>
-      </c>
-      <c r="V14">
-        <v>1.34</v>
-      </c>
-      <c r="W14">
-        <v>1.66</v>
       </c>
       <c r="X14">
         <v>6.8</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z14">
         <v>25</v>
@@ -4009,13 +4012,13 @@
         <v>18.5</v>
       </c>
       <c r="AE14">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF14">
         <v>13</v>
       </c>
       <c r="AG14">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH14">
         <v>30</v>
@@ -4036,10 +4039,10 @@
         <v>500</v>
       </c>
       <c r="AN14">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP14">
         <v>6.4</v>
@@ -4054,10 +4057,10 @@
         <v>60</v>
       </c>
       <c r="AT14">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AU14">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV14">
         <v>16.5</v>
@@ -4075,7 +4078,7 @@
         <v>27</v>
       </c>
       <c r="BA14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BB14">
         <v>34</v>
@@ -4093,25 +4096,25 @@
         <v>40</v>
       </c>
       <c r="BG14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BH14">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="BI14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="BJ14">
         <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BN14">
         <v>5</v>
@@ -4120,16 +4123,16 @@
         <v>4.5</v>
       </c>
       <c r="BP14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BQ14">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BR14">
         <v>55</v>
       </c>
       <c r="BS14">
-        <v>14.5</v>
+        <v>2.1</v>
       </c>
       <c r="BT14">
         <v>6.8</v>
@@ -4138,25 +4141,25 @@
         <v>6</v>
       </c>
       <c r="BV14">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW14">
-        <v>13.5</v>
+        <v>2.06</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BY14">
-        <v>2.12</v>
+        <v>18</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="CA14">
-        <v>2.12</v>
+        <v>17.5</v>
       </c>
       <c r="CB14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4167,28 +4170,28 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D15" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F15">
         <v>1.75</v>
       </c>
       <c r="G15">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="H15">
         <v>5.6</v>
       </c>
       <c r="I15">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="J15">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K15">
         <v>3.85</v>
@@ -4200,22 +4203,22 @@
         <v>1.09</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O15">
         <v>1.41</v>
       </c>
       <c r="P15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="Q15">
         <v>2.26</v>
       </c>
       <c r="R15">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S15">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T15">
         <v>2.08</v>
@@ -4227,16 +4230,16 @@
         <v>1.18</v>
       </c>
       <c r="W15">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="X15">
         <v>11.5</v>
       </c>
       <c r="Y15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Z15">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AA15">
         <v>900</v>
@@ -4248,13 +4251,13 @@
         <v>8.6</v>
       </c>
       <c r="AD15">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="AE15">
         <v>700</v>
       </c>
       <c r="AF15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG15">
         <v>11.5</v>
@@ -4266,7 +4269,7 @@
         <v>700</v>
       </c>
       <c r="AJ15">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK15">
         <v>24</v>
@@ -4293,7 +4296,7 @@
         <v>24</v>
       </c>
       <c r="AS15">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT15">
         <v>5.9</v>
@@ -4305,7 +4308,7 @@
         <v>20</v>
       </c>
       <c r="AW15">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX15">
         <v>8</v>
@@ -4317,10 +4320,10 @@
         <v>20</v>
       </c>
       <c r="BA15">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BC15">
         <v>18.5</v>
@@ -4329,7 +4332,7 @@
         <v>22</v>
       </c>
       <c r="BE15">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
@@ -4341,19 +4344,19 @@
         <v>3.15</v>
       </c>
       <c r="BI15">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ15">
         <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
@@ -4362,7 +4365,7 @@
         <v>3.3</v>
       </c>
       <c r="BP15">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BQ15">
         <v>9.4</v>
@@ -4371,7 +4374,7 @@
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15">
         <v>10</v>
@@ -4383,22 +4386,22 @@
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
         <v>7.8</v>
       </c>
       <c r="CB15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4409,28 +4412,28 @@
         <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F16">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G16">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="H16">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I16">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J16">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K16">
         <v>3.2</v>
@@ -4442,7 +4445,7 @@
         <v>1.1</v>
       </c>
       <c r="N16">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O16">
         <v>1.38</v>
@@ -4466,7 +4469,7 @@
         <v>2.08</v>
       </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W16">
         <v>1.38</v>
@@ -4523,7 +4526,7 @@
         <v>55</v>
       </c>
       <c r="AO16">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP16">
         <v>9.4</v>
@@ -4640,7 +4643,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="CB16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4651,25 +4654,25 @@
         <v>88</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F17">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G17">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="H17">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="I17">
-        <v>2.08</v>
+        <v>1.99</v>
       </c>
       <c r="J17">
         <v>3.25</v>
@@ -4678,55 +4681,55 @@
         <v>3.35</v>
       </c>
       <c r="L17">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="M17">
         <v>1.13</v>
       </c>
       <c r="N17">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O17">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P17">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q17">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="R17">
         <v>1.19</v>
       </c>
       <c r="S17">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="T17">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="V17">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="W17">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="X17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Y17">
         <v>6.6</v>
       </c>
       <c r="Z17">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AA17">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC17">
         <v>7.6</v>
@@ -4735,37 +4738,37 @@
         <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AF17">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AG17">
         <v>21</v>
       </c>
       <c r="AH17">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI17">
         <v>65</v>
       </c>
       <c r="AJ17">
+        <v>140</v>
+      </c>
+      <c r="AK17">
+        <v>95</v>
+      </c>
+      <c r="AL17">
         <v>130</v>
       </c>
-      <c r="AK17">
-        <v>90</v>
-      </c>
-      <c r="AL17">
-        <v>120</v>
-      </c>
       <c r="AM17">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="AN17">
-        <v>150</v>
+        <v>190</v>
       </c>
       <c r="AO17">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AP17">
         <v>7.8</v>
@@ -4774,16 +4777,16 @@
         <v>6</v>
       </c>
       <c r="AR17">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS17">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT17">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU17">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV17">
         <v>10.5</v>
@@ -4792,13 +4795,13 @@
         <v>25</v>
       </c>
       <c r="AX17">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AY17">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AZ17">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA17">
         <v>55</v>
@@ -4807,19 +4810,19 @@
         <v>28</v>
       </c>
       <c r="BC17">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BD17">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="BE17">
         <v>36</v>
       </c>
       <c r="BF17">
-        <v>16</v>
+        <v>110</v>
       </c>
       <c r="BG17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BH17">
         <v>2.7</v>
@@ -4828,7 +4831,7 @@
         <v>2.34</v>
       </c>
       <c r="BJ17">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BK17">
         <v>7.2</v>
@@ -4837,37 +4840,37 @@
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BN17">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BO17">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BP17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BQ17">
         <v>13.5</v>
       </c>
       <c r="BR17">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS17">
         <v>14.5</v>
       </c>
       <c r="BT17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU17">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="BV17">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BW17">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX17">
         <v>42</v>
@@ -4876,13 +4879,13 @@
         <v>12.5</v>
       </c>
       <c r="BZ17">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="CA17">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="CB17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -4893,148 +4896,148 @@
         <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D18" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G18">
         <v>1.76</v>
       </c>
       <c r="H18">
+        <v>5.5</v>
+      </c>
+      <c r="I18">
         <v>5.7</v>
       </c>
-      <c r="I18">
-        <v>5.8</v>
-      </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
         <v>4</v>
       </c>
       <c r="L18">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N18">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O18">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="P18">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="Q18">
+        <v>1.99</v>
+      </c>
+      <c r="R18">
+        <v>1.38</v>
+      </c>
+      <c r="S18">
+        <v>3.55</v>
+      </c>
+      <c r="T18">
+        <v>1.92</v>
+      </c>
+      <c r="U18">
         <v>2.04</v>
       </c>
-      <c r="R18">
-        <v>1.34</v>
-      </c>
-      <c r="S18">
-        <v>3.75</v>
-      </c>
-      <c r="T18">
-        <v>2</v>
-      </c>
-      <c r="U18">
-        <v>1.96</v>
-      </c>
       <c r="V18">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W18">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X18">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z18">
         <v>44</v>
       </c>
       <c r="AA18">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB18">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC18">
         <v>8.800000000000001</v>
       </c>
       <c r="AD18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE18">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF18">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG18">
         <v>9.4</v>
       </c>
       <c r="AH18">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI18">
+        <v>80</v>
+      </c>
+      <c r="AJ18">
+        <v>17.5</v>
+      </c>
+      <c r="AK18">
+        <v>18.5</v>
+      </c>
+      <c r="AL18">
+        <v>38</v>
+      </c>
+      <c r="AM18">
+        <v>120</v>
+      </c>
+      <c r="AN18">
+        <v>11</v>
+      </c>
+      <c r="AO18">
         <v>90</v>
       </c>
-      <c r="AJ18">
+      <c r="AP18">
+        <v>13</v>
+      </c>
+      <c r="AQ18">
         <v>17</v>
-      </c>
-      <c r="AK18">
-        <v>19</v>
-      </c>
-      <c r="AL18">
-        <v>40</v>
-      </c>
-      <c r="AM18">
-        <v>130</v>
-      </c>
-      <c r="AN18">
-        <v>12</v>
-      </c>
-      <c r="AO18">
-        <v>100</v>
-      </c>
-      <c r="AP18">
-        <v>12.5</v>
-      </c>
-      <c r="AQ18">
-        <v>16.5</v>
       </c>
       <c r="AR18">
         <v>38</v>
       </c>
       <c r="AS18">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AT18">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AU18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV18">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW18">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AX18">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY18">
         <v>9</v>
@@ -5043,88 +5046,88 @@
         <v>19.5</v>
       </c>
       <c r="BA18">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BB18">
         <v>16</v>
       </c>
       <c r="BC18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD18">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE18">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF18">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BG18">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BH18">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="BI18">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BL18">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="BM18">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BN18">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BO18">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BP18">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BQ18">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BR18">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS18">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="BT18">
         <v>8.800000000000001</v>
       </c>
       <c r="BU18">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV18">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BW18">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="BX18">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BY18">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BZ18">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="CA18">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="CB18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5135,31 +5138,31 @@
         <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F19">
+        <v>3.9</v>
+      </c>
+      <c r="G19">
         <v>3.95</v>
       </c>
-      <c r="G19">
-        <v>4</v>
-      </c>
       <c r="H19">
+        <v>2.1</v>
+      </c>
+      <c r="I19">
         <v>2.12</v>
       </c>
-      <c r="I19">
-        <v>2.14</v>
-      </c>
       <c r="J19">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L19">
         <v>1.44</v>
@@ -5168,22 +5171,22 @@
         <v>1.08</v>
       </c>
       <c r="N19">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O19">
         <v>1.35</v>
       </c>
       <c r="P19">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q19">
         <v>2.06</v>
       </c>
       <c r="R19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S19">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T19">
         <v>1.86</v>
@@ -5192,13 +5195,13 @@
         <v>2.1</v>
       </c>
       <c r="V19">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="W19">
         <v>1.33</v>
       </c>
       <c r="X19">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y19">
         <v>9</v>
@@ -5213,7 +5216,7 @@
         <v>14</v>
       </c>
       <c r="AC19">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD19">
         <v>9.800000000000001</v>
@@ -5237,7 +5240,7 @@
         <v>80</v>
       </c>
       <c r="AK19">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AL19">
         <v>60</v>
@@ -5249,10 +5252,10 @@
         <v>55</v>
       </c>
       <c r="AO19">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AP19">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
         <v>8.6</v>
@@ -5279,7 +5282,7 @@
         <v>26</v>
       </c>
       <c r="AY19">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ19">
         <v>17</v>
@@ -5300,19 +5303,19 @@
         <v>80</v>
       </c>
       <c r="BF19">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG19">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BH19">
         <v>3.3</v>
       </c>
       <c r="BI19">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ19">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK19">
         <v>7.4</v>
@@ -5321,52 +5324,52 @@
         <v>130</v>
       </c>
       <c r="BM19">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN19">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BO19">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BP19">
         <v>34</v>
       </c>
       <c r="BQ19">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR19">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BS19">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BT19">
         <v>4.7</v>
       </c>
       <c r="BU19">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BV19">
         <v>15</v>
       </c>
       <c r="BW19">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BX19">
         <v>30</v>
       </c>
       <c r="BY19">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BZ19">
         <v>27</v>
       </c>
       <c r="CA19">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="CB19" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5377,139 +5380,139 @@
         <v>88</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F20">
-        <v>1.99</v>
+        <v>1.92</v>
       </c>
       <c r="G20">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="H20">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="I20">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J20">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K20">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L20">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M20">
         <v>1.1</v>
       </c>
       <c r="N20">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="O20">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P20">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q20">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="R20">
         <v>1.24</v>
       </c>
       <c r="S20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T20">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U20">
         <v>1.84</v>
       </c>
       <c r="V20">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="W20">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="X20">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y20">
         <v>15</v>
       </c>
       <c r="Z20">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA20">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AB20">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AC20">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE20">
         <v>85</v>
       </c>
       <c r="AF20">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AG20">
         <v>12.5</v>
       </c>
       <c r="AH20">
+        <v>26</v>
+      </c>
+      <c r="AI20">
+        <v>100</v>
+      </c>
+      <c r="AJ20">
         <v>24</v>
       </c>
-      <c r="AI20">
-        <v>110</v>
-      </c>
-      <c r="AJ20">
+      <c r="AK20">
         <v>26</v>
       </c>
-      <c r="AK20">
-        <v>28</v>
-      </c>
       <c r="AL20">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM20">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN20">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AO20">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AP20">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ20">
         <v>12</v>
       </c>
       <c r="AR20">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AS20">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AT20">
         <v>6.6</v>
       </c>
       <c r="AU20">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV20">
         <v>17</v>
@@ -5533,82 +5536,82 @@
         <v>20</v>
       </c>
       <c r="BC20">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD20">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE20">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF20">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BG20">
         <v>75</v>
       </c>
       <c r="BH20">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BI20">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="BJ20">
         <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="BN20">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BO20">
         <v>3.45</v>
       </c>
       <c r="BP20">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BQ20">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT20">
         <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BV20">
         <v>55</v>
       </c>
       <c r="BW20">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5619,46 +5622,46 @@
         <v>88</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E21" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F21">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="G21">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="H21">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I21">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J21">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K21">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L21">
         <v>1.28</v>
       </c>
       <c r="M21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N21">
         <v>5.7</v>
       </c>
       <c r="O21">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q21">
         <v>1.57</v>
@@ -5667,28 +5670,28 @@
         <v>1.65</v>
       </c>
       <c r="S21">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T21">
         <v>1.77</v>
       </c>
       <c r="U21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V21">
         <v>1.13</v>
       </c>
       <c r="W21">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="X21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Y21">
         <v>34</v>
       </c>
       <c r="Z21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AA21">
         <v>260</v>
@@ -5703,7 +5706,7 @@
         <v>30</v>
       </c>
       <c r="AE21">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="AF21">
         <v>10.5</v>
@@ -5721,22 +5724,22 @@
         <v>14</v>
       </c>
       <c r="AK21">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM21">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AN21">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AO21">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="AP21">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="AQ21">
         <v>27</v>
@@ -5745,19 +5748,19 @@
         <v>55</v>
       </c>
       <c r="AS21">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT21">
         <v>9.800000000000001</v>
       </c>
       <c r="AU21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV21">
         <v>24</v>
       </c>
       <c r="AW21">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AX21">
         <v>9.199999999999999</v>
@@ -5769,10 +5772,10 @@
         <v>18.5</v>
       </c>
       <c r="BA21">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB21">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC21">
         <v>12</v>
@@ -5781,13 +5784,13 @@
         <v>22</v>
       </c>
       <c r="BE21">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BF21">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BG21">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="BH21">
         <v>4.8</v>
@@ -5850,7 +5853,7 @@
         <v>5.4</v>
       </c>
       <c r="CB21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-07-29.xlsx
@@ -439,7 +439,7 @@
     <t>Birmingham Legion FC</t>
   </si>
   <si>
-    <t>2026-07-29 13:57:47</t>
+    <t>2026-07-29 16:07:01</t>
   </si>
 </sst>
 </file>
@@ -1033,226 +1033,226 @@
         <v>121</v>
       </c>
       <c r="F2">
-        <v>2.48</v>
+        <v>1.26</v>
       </c>
       <c r="G2">
-        <v>2.5</v>
+        <v>1.28</v>
       </c>
       <c r="H2">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="I2">
-        <v>4.1</v>
+        <v>42</v>
       </c>
       <c r="J2">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="K2">
-        <v>2.88</v>
+        <v>5.4</v>
       </c>
       <c r="L2">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="O2">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="P2">
-        <v>1.35</v>
+        <v>1.12</v>
       </c>
       <c r="Q2">
-        <v>3.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="R2">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="S2">
-        <v>9.199999999999999</v>
+        <v>65</v>
       </c>
       <c r="T2">
-        <v>2.68</v>
+        <v>3.5</v>
       </c>
       <c r="U2">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.02</v>
       </c>
       <c r="W2">
-        <v>1.67</v>
+        <v>4.7</v>
       </c>
       <c r="X2">
-        <v>6</v>
+        <v>1000</v>
       </c>
       <c r="Y2">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA2">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AB2">
-        <v>6</v>
+        <v>1.87</v>
       </c>
       <c r="AC2">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="AD2">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AE2">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF2">
-        <v>13</v>
+        <v>6.4</v>
       </c>
       <c r="AG2">
-        <v>14.5</v>
+        <v>22</v>
       </c>
       <c r="AH2">
-        <v>36</v>
+        <v>990</v>
       </c>
       <c r="AI2">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AK2">
+        <v>1000</v>
+      </c>
+      <c r="AL2">
+        <v>1000</v>
+      </c>
+      <c r="AM2">
+        <v>1000</v>
+      </c>
+      <c r="AN2">
+        <v>1000</v>
+      </c>
+      <c r="AO2">
+        <v>1000</v>
+      </c>
+      <c r="AP2">
+        <v>10.5</v>
+      </c>
+      <c r="AQ2">
+        <v>10</v>
+      </c>
+      <c r="AR2">
+        <v>10</v>
+      </c>
+      <c r="AS2">
+        <v>10.5</v>
+      </c>
+      <c r="AT2">
+        <v>1.82</v>
+      </c>
+      <c r="AU2">
+        <v>5.4</v>
+      </c>
+      <c r="AV2">
+        <v>29</v>
+      </c>
+      <c r="AW2">
+        <v>170</v>
+      </c>
+      <c r="AX2">
+        <v>5.9</v>
+      </c>
+      <c r="AY2">
+        <v>17</v>
+      </c>
+      <c r="AZ2">
+        <v>60</v>
+      </c>
+      <c r="BA2">
+        <v>10.5</v>
+      </c>
+      <c r="BB2">
+        <v>11</v>
+      </c>
+      <c r="BC2">
+        <v>38</v>
+      </c>
+      <c r="BD2">
+        <v>10</v>
+      </c>
+      <c r="BE2">
         <v>48</v>
       </c>
-      <c r="AL2">
-        <v>120</v>
-      </c>
-      <c r="AM2">
-        <v>500</v>
-      </c>
-      <c r="AN2">
-        <v>65</v>
-      </c>
-      <c r="AO2">
-        <v>190</v>
-      </c>
-      <c r="AP2">
-        <v>5.7</v>
-      </c>
-      <c r="AQ2">
-        <v>8</v>
-      </c>
-      <c r="AR2">
-        <v>23</v>
-      </c>
-      <c r="AS2">
-        <v>90</v>
-      </c>
-      <c r="AT2">
-        <v>5.8</v>
-      </c>
-      <c r="AU2">
-        <v>6.6</v>
-      </c>
-      <c r="AV2">
-        <v>18.5</v>
-      </c>
-      <c r="AW2">
-        <v>75</v>
-      </c>
-      <c r="AX2">
-        <v>12</v>
-      </c>
-      <c r="AY2">
-        <v>13</v>
-      </c>
-      <c r="AZ2">
-        <v>30</v>
-      </c>
-      <c r="BA2">
-        <v>60</v>
-      </c>
-      <c r="BB2">
-        <v>36</v>
-      </c>
-      <c r="BC2">
-        <v>40</v>
-      </c>
-      <c r="BD2">
-        <v>70</v>
-      </c>
-      <c r="BE2">
-        <v>230</v>
-      </c>
       <c r="BF2">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="BG2">
         <v>80</v>
       </c>
       <c r="BH2">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="BI2">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="BJ2">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BK2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="BN2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO2">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BP2">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BQ2">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BR2">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BS2">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BT2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BU2">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BV2">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BW2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BX2">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="BY2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BZ2">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="CA2">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="s">
         <v>141</v>
@@ -1275,226 +1275,226 @@
         <v>122</v>
       </c>
       <c r="F3">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="G3">
-        <v>1.28</v>
+        <v>3.35</v>
       </c>
       <c r="H3">
-        <v>11</v>
+        <v>2.28</v>
       </c>
       <c r="I3">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>7.2</v>
+        <v>2.6</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="L3">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="M3">
         <v>1.01</v>
       </c>
       <c r="N3">
+        <v>2.5</v>
+      </c>
+      <c r="O3">
+        <v>1.63</v>
+      </c>
+      <c r="P3">
+        <v>1.48</v>
+      </c>
+      <c r="Q3">
+        <v>2.94</v>
+      </c>
+      <c r="R3">
+        <v>1.18</v>
+      </c>
+      <c r="S3">
+        <v>6.4</v>
+      </c>
+      <c r="T3">
+        <v>1.11</v>
+      </c>
+      <c r="U3">
+        <v>1.02</v>
+      </c>
+      <c r="V3">
+        <v>1.12</v>
+      </c>
+      <c r="W3">
+        <v>1.5</v>
+      </c>
+      <c r="X3">
+        <v>1000</v>
+      </c>
+      <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>1000</v>
+      </c>
+      <c r="AA3">
+        <v>1000</v>
+      </c>
+      <c r="AB3">
+        <v>1000</v>
+      </c>
+      <c r="AC3">
+        <v>6.4</v>
+      </c>
+      <c r="AD3">
+        <v>990</v>
+      </c>
+      <c r="AE3">
+        <v>1000</v>
+      </c>
+      <c r="AF3">
+        <v>1000</v>
+      </c>
+      <c r="AG3">
+        <v>990</v>
+      </c>
+      <c r="AH3">
+        <v>26</v>
+      </c>
+      <c r="AI3">
+        <v>1000</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>28</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>300</v>
+      </c>
+      <c r="AO3">
+        <v>1000</v>
+      </c>
+      <c r="AP3">
+        <v>2.7</v>
+      </c>
+      <c r="AQ3">
+        <v>6.6</v>
+      </c>
+      <c r="AR3">
         <v>11</v>
       </c>
-      <c r="O3">
-        <v>1.09</v>
-      </c>
-      <c r="P3">
-        <v>4.1</v>
-      </c>
-      <c r="Q3">
-        <v>1.28</v>
-      </c>
-      <c r="R3">
-        <v>2.38</v>
-      </c>
-      <c r="S3">
-        <v>1.68</v>
-      </c>
-      <c r="T3">
-        <v>1.61</v>
-      </c>
-      <c r="U3">
-        <v>2.42</v>
-      </c>
-      <c r="V3">
-        <v>1.08</v>
-      </c>
-      <c r="W3">
-        <v>4.5</v>
-      </c>
-      <c r="X3">
-        <v>60</v>
-      </c>
-      <c r="Y3">
-        <v>130</v>
-      </c>
-      <c r="Z3">
-        <v>140</v>
-      </c>
-      <c r="AA3">
-        <v>370</v>
-      </c>
-      <c r="AB3">
-        <v>19.5</v>
-      </c>
-      <c r="AC3">
-        <v>22</v>
-      </c>
-      <c r="AD3">
-        <v>100</v>
-      </c>
-      <c r="AE3">
-        <v>260</v>
-      </c>
-      <c r="AF3">
-        <v>14</v>
-      </c>
-      <c r="AG3">
-        <v>13.5</v>
-      </c>
-      <c r="AH3">
-        <v>24</v>
-      </c>
-      <c r="AI3">
-        <v>230</v>
-      </c>
-      <c r="AJ3">
-        <v>14.5</v>
-      </c>
-      <c r="AK3">
-        <v>13.5</v>
-      </c>
-      <c r="AL3">
-        <v>26</v>
-      </c>
-      <c r="AM3">
-        <v>320</v>
-      </c>
-      <c r="AN3">
+      <c r="AS3">
+        <v>2.28</v>
+      </c>
+      <c r="AT3">
+        <v>2.46</v>
+      </c>
+      <c r="AU3">
+        <v>4.2</v>
+      </c>
+      <c r="AV3">
+        <v>7.6</v>
+      </c>
+      <c r="AW3">
+        <v>2.28</v>
+      </c>
+      <c r="AX3">
+        <v>1.92</v>
+      </c>
+      <c r="AY3">
+        <v>5.2</v>
+      </c>
+      <c r="AZ3">
+        <v>2.68</v>
+      </c>
+      <c r="BA3">
         <v>2.9</v>
       </c>
-      <c r="AO3">
-        <v>110</v>
-      </c>
-      <c r="AP3">
-        <v>42</v>
-      </c>
-      <c r="AQ3">
-        <v>46</v>
-      </c>
-      <c r="AR3">
-        <v>11.5</v>
-      </c>
-      <c r="AS3">
-        <v>12</v>
-      </c>
-      <c r="AT3">
-        <v>16.5</v>
-      </c>
-      <c r="AU3">
-        <v>16.5</v>
-      </c>
-      <c r="AV3">
-        <v>36</v>
-      </c>
-      <c r="AW3">
-        <v>11.5</v>
-      </c>
-      <c r="AX3">
-        <v>11.5</v>
-      </c>
-      <c r="AY3">
-        <v>10.5</v>
-      </c>
-      <c r="AZ3">
-        <v>20</v>
-      </c>
-      <c r="BA3">
-        <v>34</v>
-      </c>
       <c r="BB3">
-        <v>12</v>
+        <v>1.92</v>
       </c>
       <c r="BC3">
-        <v>11</v>
+        <v>2.46</v>
       </c>
       <c r="BD3">
-        <v>20</v>
+        <v>2.9</v>
       </c>
       <c r="BE3">
-        <v>28</v>
+        <v>2.68</v>
       </c>
       <c r="BF3">
-        <v>2.66</v>
+        <v>1.84</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>2.6</v>
       </c>
       <c r="BH3">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BI3">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BJ3">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL3">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BM3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BN3">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO3">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BP3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BQ3">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BR3">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BS3">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BT3">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BU3">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BV3">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BX3">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BZ3">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="CA3">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="s">
         <v>141</v>
@@ -1517,52 +1517,52 @@
         <v>123</v>
       </c>
       <c r="F4">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="G4">
-        <v>1.79</v>
+        <v>1.29</v>
       </c>
       <c r="H4">
-        <v>4.2</v>
+        <v>14.5</v>
       </c>
       <c r="I4">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="J4">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="K4">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="L4">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N4">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="S4">
         <v>1.11</v>
       </c>
-      <c r="P4">
-        <v>3.6</v>
-      </c>
-      <c r="Q4">
-        <v>1.34</v>
-      </c>
-      <c r="R4">
-        <v>2.04</v>
-      </c>
-      <c r="S4">
-        <v>1.87</v>
-      </c>
       <c r="T4">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V4">
         <v>1.01</v>
@@ -1571,172 +1571,172 @@
         <v>1.01</v>
       </c>
       <c r="X4">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH4">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AI4">
-        <v>36</v>
+        <v>930</v>
       </c>
       <c r="AJ4">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>16.5</v>
+        <v>8</v>
       </c>
       <c r="AL4">
+        <v>8.6</v>
+      </c>
+      <c r="AM4">
         <v>22</v>
       </c>
-      <c r="AM4">
+      <c r="AN4">
+        <v>2.7</v>
+      </c>
+      <c r="AO4">
         <v>46</v>
       </c>
-      <c r="AN4">
-        <v>5.5</v>
-      </c>
-      <c r="AO4">
-        <v>22</v>
-      </c>
       <c r="AP4">
-        <v>8.4</v>
+        <v>7</v>
       </c>
       <c r="AQ4">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="AR4">
-        <v>16</v>
+        <v>6.8</v>
       </c>
       <c r="AS4">
-        <v>23</v>
+        <v>6.8</v>
       </c>
       <c r="AT4">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="AU4">
-        <v>11.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="AW4">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="AX4">
-        <v>16</v>
+        <v>6.6</v>
       </c>
       <c r="AY4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AZ4">
-        <v>13</v>
+        <v>4.8</v>
       </c>
       <c r="BA4">
-        <v>7.8</v>
+        <v>25</v>
       </c>
       <c r="BB4">
-        <v>19</v>
+        <v>6.6</v>
       </c>
       <c r="BC4">
-        <v>13.5</v>
+        <v>6</v>
       </c>
       <c r="BD4">
+        <v>7</v>
+      </c>
+      <c r="BE4">
         <v>18</v>
       </c>
-      <c r="BE4">
-        <v>20</v>
-      </c>
       <c r="BF4">
-        <v>4.6</v>
+        <v>2.32</v>
       </c>
       <c r="BG4">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="BH4">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BI4">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BJ4">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BK4">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BL4">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BN4">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BO4">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BP4">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BQ4">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BR4">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BS4">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BT4">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BW4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BY4">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BZ4">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="CA4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="s">
         <v>141</v>
@@ -1759,226 +1759,226 @@
         <v>124</v>
       </c>
       <c r="F5">
-        <v>3.1</v>
+        <v>1.24</v>
       </c>
       <c r="G5">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="H5">
-        <v>2.04</v>
+        <v>13</v>
       </c>
       <c r="I5">
-        <v>2.14</v>
+        <v>15.5</v>
       </c>
       <c r="J5">
+        <v>7</v>
+      </c>
+      <c r="K5">
+        <v>7.8</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>7.2</v>
+      </c>
+      <c r="Q5">
+        <v>1.08</v>
+      </c>
+      <c r="R5">
+        <v>2.72</v>
+      </c>
+      <c r="S5">
+        <v>1.53</v>
+      </c>
+      <c r="T5">
+        <v>1.38</v>
+      </c>
+      <c r="U5">
+        <v>3.3</v>
+      </c>
+      <c r="V5">
+        <v>1.07</v>
+      </c>
+      <c r="W5">
         <v>4.5</v>
       </c>
-      <c r="K5">
-        <v>5.2</v>
-      </c>
-      <c r="L5">
-        <v>1.17</v>
-      </c>
-      <c r="M5">
-        <v>1.01</v>
-      </c>
-      <c r="N5">
-        <v>11</v>
-      </c>
-      <c r="O5">
-        <v>1.07</v>
-      </c>
-      <c r="P5">
-        <v>4.5</v>
-      </c>
-      <c r="Q5">
-        <v>1.25</v>
-      </c>
-      <c r="R5">
-        <v>2.46</v>
-      </c>
-      <c r="S5">
-        <v>1.62</v>
-      </c>
-      <c r="T5">
-        <v>1.3</v>
-      </c>
-      <c r="U5">
-        <v>3.8</v>
-      </c>
-      <c r="V5">
-        <v>1.87</v>
-      </c>
-      <c r="W5">
-        <v>1.41</v>
-      </c>
       <c r="X5">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>12</v>
+      </c>
+      <c r="AG5">
+        <v>9</v>
+      </c>
+      <c r="AH5">
+        <v>12</v>
+      </c>
+      <c r="AI5">
+        <v>32</v>
+      </c>
+      <c r="AJ5">
+        <v>10.5</v>
+      </c>
+      <c r="AK5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AL5">
+        <v>14</v>
+      </c>
+      <c r="AM5">
+        <v>32</v>
+      </c>
+      <c r="AN5">
+        <v>4</v>
+      </c>
+      <c r="AO5">
         <v>36</v>
       </c>
-      <c r="AA5">
-        <v>70</v>
-      </c>
-      <c r="AB5">
-        <v>85</v>
-      </c>
-      <c r="AC5">
-        <v>17</v>
-      </c>
-      <c r="AD5">
-        <v>15.5</v>
-      </c>
-      <c r="AE5">
-        <v>22</v>
-      </c>
-      <c r="AF5">
-        <v>100</v>
-      </c>
-      <c r="AG5">
-        <v>20</v>
-      </c>
-      <c r="AH5">
-        <v>14.5</v>
-      </c>
-      <c r="AI5">
-        <v>30</v>
-      </c>
-      <c r="AJ5">
-        <v>220</v>
-      </c>
-      <c r="AK5">
-        <v>220</v>
-      </c>
-      <c r="AL5">
-        <v>26</v>
-      </c>
-      <c r="AM5">
-        <v>38</v>
-      </c>
-      <c r="AN5">
-        <v>11</v>
-      </c>
-      <c r="AO5">
-        <v>5.5</v>
-      </c>
       <c r="AP5">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="AQ5">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="AR5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AS5">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AT5">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AU5">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AW5">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="AX5">
-        <v>15.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY5">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="AZ5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BA5">
+        <v>8.4</v>
+      </c>
+      <c r="BB5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC5">
+        <v>6.6</v>
+      </c>
+      <c r="BD5">
         <v>11.5</v>
       </c>
-      <c r="BA5">
-        <v>16</v>
-      </c>
-      <c r="BB5">
-        <v>8.6</v>
-      </c>
-      <c r="BC5">
-        <v>21</v>
-      </c>
-      <c r="BD5">
-        <v>17.5</v>
-      </c>
       <c r="BE5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BF5">
-        <v>9</v>
+        <v>3.6</v>
       </c>
       <c r="BG5">
-        <v>4.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH5">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BI5">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BJ5">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BK5">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BN5">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BO5">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BP5">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BQ5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BS5">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BU5">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BV5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BW5">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BX5">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BY5">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BZ5">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="CA5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="s">
         <v>141</v>
@@ -2001,226 +2001,226 @@
         <v>125</v>
       </c>
       <c r="F6">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
       <c r="G6">
-        <v>1.48</v>
+        <v>1.32</v>
       </c>
       <c r="H6">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="I6">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="J6">
-        <v>5.2</v>
+        <v>1.02</v>
       </c>
       <c r="K6">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
         <v>1.02</v>
       </c>
       <c r="N6">
-        <v>6.6</v>
+        <v>1.1</v>
       </c>
       <c r="O6">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="P6">
-        <v>2.88</v>
+        <v>1.25</v>
       </c>
       <c r="Q6">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="R6">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="S6">
-        <v>2.14</v>
+        <v>1.02</v>
       </c>
       <c r="T6">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="V6">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="W6">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="X6">
         <v>950</v>
       </c>
       <c r="Y6">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>970</v>
+      </c>
+      <c r="AC6">
+        <v>990</v>
+      </c>
+      <c r="AD6">
+        <v>950</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>970</v>
+      </c>
+      <c r="AG6">
+        <v>970</v>
+      </c>
+      <c r="AH6">
+        <v>970</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>970</v>
+      </c>
+      <c r="AK6">
+        <v>970</v>
+      </c>
+      <c r="AL6">
+        <v>46</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>970</v>
+      </c>
+      <c r="AO6">
         <v>110</v>
       </c>
-      <c r="AA6">
-        <v>700</v>
-      </c>
-      <c r="AB6">
-        <v>14</v>
-      </c>
-      <c r="AC6">
-        <v>14</v>
-      </c>
-      <c r="AD6">
-        <v>500</v>
-      </c>
-      <c r="AE6">
-        <v>700</v>
-      </c>
-      <c r="AF6">
-        <v>12.5</v>
-      </c>
-      <c r="AG6">
-        <v>11.5</v>
-      </c>
-      <c r="AH6">
-        <v>22</v>
-      </c>
-      <c r="AI6">
-        <v>700</v>
-      </c>
-      <c r="AJ6">
-        <v>14.5</v>
-      </c>
-      <c r="AK6">
-        <v>15</v>
-      </c>
-      <c r="AL6">
-        <v>160</v>
-      </c>
-      <c r="AM6">
-        <v>580</v>
-      </c>
-      <c r="AN6">
-        <v>4.8</v>
-      </c>
-      <c r="AO6">
-        <v>70</v>
-      </c>
       <c r="AP6">
-        <v>12.5</v>
+        <v>1.74</v>
       </c>
       <c r="AQ6">
-        <v>13</v>
+        <v>1.81</v>
       </c>
       <c r="AR6">
-        <v>8.6</v>
+        <v>1.81</v>
       </c>
       <c r="AS6">
-        <v>9.4</v>
+        <v>1.81</v>
       </c>
       <c r="AT6">
-        <v>11.5</v>
+        <v>1.64</v>
       </c>
       <c r="AU6">
-        <v>11</v>
+        <v>1.81</v>
       </c>
       <c r="AV6">
-        <v>9.199999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="AW6">
-        <v>8.800000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>1.58</v>
       </c>
       <c r="AY6">
-        <v>9.199999999999999</v>
+        <v>1.59</v>
       </c>
       <c r="AZ6">
-        <v>7.6</v>
+        <v>1.71</v>
       </c>
       <c r="BA6">
-        <v>8.6</v>
+        <v>1.81</v>
       </c>
       <c r="BB6">
-        <v>12</v>
+        <v>2.96</v>
       </c>
       <c r="BC6">
-        <v>12</v>
+        <v>1.68</v>
       </c>
       <c r="BD6">
-        <v>21</v>
+        <v>1.74</v>
       </c>
       <c r="BE6">
-        <v>8.800000000000001</v>
+        <v>1.81</v>
       </c>
       <c r="BF6">
-        <v>4.1</v>
+        <v>1.81</v>
       </c>
       <c r="BG6">
-        <v>10.5</v>
+        <v>1.78</v>
       </c>
       <c r="BH6">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BI6">
-        <v>4.2</v>
+        <v>1.04</v>
       </c>
       <c r="BJ6">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>5.4</v>
+        <v>1.19</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>9.6</v>
+        <v>1.19</v>
       </c>
       <c r="BN6">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>3.65</v>
+        <v>1.19</v>
       </c>
       <c r="BP6">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>4.7</v>
+        <v>1.19</v>
       </c>
       <c r="BR6">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>6.6</v>
+        <v>1.19</v>
       </c>
       <c r="BT6">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>5.6</v>
+        <v>1.19</v>
       </c>
       <c r="BV6">
         <v>1000</v>
       </c>
       <c r="BW6">
-        <v>9</v>
+        <v>1.19</v>
       </c>
       <c r="BX6">
         <v>1000</v>
       </c>
       <c r="BY6">
-        <v>8.800000000000001</v>
+        <v>1.19</v>
       </c>
       <c r="BZ6">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>5.1</v>
+        <v>1.19</v>
       </c>
       <c r="CB6" t="s">
         <v>141</v>
@@ -2243,220 +2243,220 @@
         <v>126</v>
       </c>
       <c r="F7">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="G7">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="H7">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="I7">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="J7">
+        <v>3.1</v>
+      </c>
+      <c r="K7">
+        <v>3.3</v>
+      </c>
+      <c r="L7">
+        <v>1.55</v>
+      </c>
+      <c r="M7">
+        <v>1.11</v>
+      </c>
+      <c r="N7">
         <v>3.05</v>
       </c>
-      <c r="K7">
-        <v>3.25</v>
-      </c>
-      <c r="L7">
-        <v>1.49</v>
-      </c>
-      <c r="M7">
-        <v>1.1</v>
-      </c>
-      <c r="N7">
-        <v>3.25</v>
-      </c>
       <c r="O7">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="P7">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="Q7">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S7">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="T7">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="U7">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V7">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="W7">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="X7">
+        <v>10.5</v>
+      </c>
+      <c r="Y7">
+        <v>8.6</v>
+      </c>
+      <c r="Z7">
+        <v>14</v>
+      </c>
+      <c r="AA7">
+        <v>34</v>
+      </c>
+      <c r="AB7">
+        <v>13.5</v>
+      </c>
+      <c r="AC7">
+        <v>7</v>
+      </c>
+      <c r="AD7">
         <v>11.5</v>
       </c>
-      <c r="Y7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z7">
-        <v>17</v>
-      </c>
-      <c r="AA7">
-        <v>65</v>
-      </c>
-      <c r="AB7">
-        <v>12</v>
-      </c>
-      <c r="AC7">
-        <v>7.4</v>
-      </c>
-      <c r="AD7">
-        <v>12.5</v>
-      </c>
       <c r="AE7">
+        <v>30</v>
+      </c>
+      <c r="AF7">
         <v>34</v>
       </c>
-      <c r="AF7">
-        <v>23</v>
-      </c>
       <c r="AG7">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH7">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI7">
         <v>50</v>
       </c>
       <c r="AJ7">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AK7">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="AL7">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="AM7">
-        <v>580</v>
+        <v>150</v>
       </c>
       <c r="AN7">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="AO7">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AP7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ7">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS7">
-        <v>17.5</v>
+        <v>26</v>
       </c>
       <c r="AT7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV7">
         <v>10</v>
       </c>
       <c r="AW7">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="AX7">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY7">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AZ7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA7">
+        <v>44</v>
+      </c>
+      <c r="BB7">
+        <v>65</v>
+      </c>
+      <c r="BC7">
+        <v>44</v>
+      </c>
+      <c r="BD7">
+        <v>60</v>
+      </c>
+      <c r="BE7">
+        <v>100</v>
+      </c>
+      <c r="BF7">
+        <v>50</v>
+      </c>
+      <c r="BG7">
+        <v>20</v>
+      </c>
+      <c r="BH7">
+        <v>2.82</v>
+      </c>
+      <c r="BI7">
+        <v>2.62</v>
+      </c>
+      <c r="BJ7">
+        <v>11</v>
+      </c>
+      <c r="BK7">
+        <v>9.6</v>
+      </c>
+      <c r="BL7">
+        <v>190</v>
+      </c>
+      <c r="BM7">
+        <v>110</v>
+      </c>
+      <c r="BN7">
+        <v>6.6</v>
+      </c>
+      <c r="BO7">
+        <v>5.8</v>
+      </c>
+      <c r="BP7">
         <v>38</v>
       </c>
-      <c r="BB7">
-        <v>9</v>
-      </c>
-      <c r="BC7">
+      <c r="BQ7">
+        <v>26</v>
+      </c>
+      <c r="BR7">
+        <v>60</v>
+      </c>
+      <c r="BS7">
+        <v>44</v>
+      </c>
+      <c r="BT7">
+        <v>5</v>
+      </c>
+      <c r="BU7">
+        <v>4.4</v>
+      </c>
+      <c r="BV7">
+        <v>19.5</v>
+      </c>
+      <c r="BW7">
+        <v>16</v>
+      </c>
+      <c r="BX7">
+        <v>44</v>
+      </c>
+      <c r="BY7">
         <v>34</v>
-      </c>
-      <c r="BD7">
-        <v>27</v>
-      </c>
-      <c r="BE7">
-        <v>9.4</v>
-      </c>
-      <c r="BF7">
-        <v>8.4</v>
-      </c>
-      <c r="BG7">
-        <v>7.6</v>
-      </c>
-      <c r="BH7">
-        <v>3.1</v>
-      </c>
-      <c r="BI7">
-        <v>2.76</v>
-      </c>
-      <c r="BJ7">
-        <v>10.5</v>
-      </c>
-      <c r="BK7">
-        <v>6</v>
-      </c>
-      <c r="BL7">
-        <v>1000</v>
-      </c>
-      <c r="BM7">
-        <v>11.5</v>
-      </c>
-      <c r="BN7">
-        <v>6.4</v>
-      </c>
-      <c r="BO7">
-        <v>5.5</v>
-      </c>
-      <c r="BP7">
-        <v>28</v>
-      </c>
-      <c r="BQ7">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BR7">
-        <v>44</v>
-      </c>
-      <c r="BS7">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BT7">
-        <v>5.4</v>
-      </c>
-      <c r="BU7">
-        <v>4.7</v>
-      </c>
-      <c r="BV7">
-        <v>22</v>
-      </c>
-      <c r="BW7">
-        <v>8</v>
-      </c>
-      <c r="BX7">
-        <v>38</v>
-      </c>
-      <c r="BY7">
-        <v>9.6</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2485,22 +2485,22 @@
         <v>127</v>
       </c>
       <c r="F8">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H8">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I8">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J8">
         <v>5</v>
       </c>
       <c r="K8">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L8">
         <v>1.12</v>
@@ -2509,49 +2509,49 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="O8">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P8">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="Q8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="R8">
         <v>3.2</v>
       </c>
       <c r="S8">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T8">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="U8">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="V8">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="W8">
         <v>1.5</v>
       </c>
       <c r="X8">
-        <v>950</v>
+        <v>110</v>
       </c>
       <c r="Y8">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Z8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA8">
         <v>44</v>
       </c>
       <c r="AB8">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="AC8">
         <v>23</v>
@@ -2563,7 +2563,7 @@
         <v>22</v>
       </c>
       <c r="AF8">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AG8">
         <v>22</v>
@@ -2587,13 +2587,13 @@
         <v>25</v>
       </c>
       <c r="AN8">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AO8">
         <v>4.6</v>
       </c>
       <c r="AP8">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ8">
         <v>15</v>
@@ -2602,10 +2602,10 @@
         <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="AT8">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AU8">
         <v>19</v>
@@ -2629,10 +2629,10 @@
         <v>16</v>
       </c>
       <c r="BB8">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BC8">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="BD8">
         <v>18.5</v>
@@ -2641,16 +2641,16 @@
         <v>20</v>
       </c>
       <c r="BF8">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BG8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH8">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BI8">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ8">
         <v>8.199999999999999</v>
@@ -2671,10 +2671,10 @@
         <v>4.9</v>
       </c>
       <c r="BP8">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BQ8">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR8">
         <v>17</v>
@@ -2683,10 +2683,10 @@
         <v>6.4</v>
       </c>
       <c r="BT8">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU8">
-        <v>5.8</v>
+        <v>4.5</v>
       </c>
       <c r="BV8">
         <v>14</v>
@@ -2704,7 +2704,7 @@
         <v>6.2</v>
       </c>
       <c r="CA8">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="CB8" t="s">
         <v>141</v>
@@ -2739,10 +2739,10 @@
         <v>2.24</v>
       </c>
       <c r="J9">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L9">
         <v>1.19</v>
@@ -2754,25 +2754,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="O9">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P9">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="Q9">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="R9">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="S9">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="T9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="U9">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="V9">
         <v>1.8</v>
@@ -2781,7 +2781,7 @@
         <v>1.47</v>
       </c>
       <c r="X9">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="Y9">
         <v>26</v>
@@ -2808,7 +2808,7 @@
         <v>34</v>
       </c>
       <c r="AG9">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH9">
         <v>14.5</v>
@@ -2844,22 +2844,22 @@
         <v>20</v>
       </c>
       <c r="AS9">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AT9">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW9">
         <v>17</v>
       </c>
       <c r="AX9">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY9">
         <v>13</v>
@@ -2874,79 +2874,79 @@
         <v>34</v>
       </c>
       <c r="BC9">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BD9">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BE9">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BF9">
         <v>9.6</v>
       </c>
       <c r="BG9">
+        <v>6.2</v>
+      </c>
+      <c r="BH9">
+        <v>6.2</v>
+      </c>
+      <c r="BI9">
+        <v>5.2</v>
+      </c>
+      <c r="BJ9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BK9">
         <v>6.4</v>
-      </c>
-      <c r="BH9">
-        <v>6.4</v>
-      </c>
-      <c r="BI9">
-        <v>4.6</v>
-      </c>
-      <c r="BJ9">
-        <v>8.4</v>
-      </c>
-      <c r="BK9">
-        <v>6</v>
       </c>
       <c r="BL9">
         <v>48</v>
       </c>
       <c r="BM9">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN9">
         <v>7.8</v>
       </c>
       <c r="BO9">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BP9">
         <v>19.5</v>
       </c>
       <c r="BQ9">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BR9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS9">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BT9">
         <v>6.6</v>
       </c>
       <c r="BU9">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV9">
         <v>14.5</v>
       </c>
       <c r="BW9">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BX9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BY9">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BZ9">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CA9">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="CB9" t="s">
         <v>141</v>
@@ -2969,7 +2969,7 @@
         <v>129</v>
       </c>
       <c r="F10">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G10">
         <v>2.04</v>
@@ -2978,13 +2978,13 @@
         <v>3.4</v>
       </c>
       <c r="I10">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J10">
         <v>4.5</v>
       </c>
       <c r="K10">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10">
         <v>1.2</v>
@@ -2999,25 +2999,25 @@
         <v>1.11</v>
       </c>
       <c r="P10">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="R10">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="S10">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="T10">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="U10">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="V10">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W10">
         <v>1.96</v>
@@ -3029,7 +3029,7 @@
         <v>29</v>
       </c>
       <c r="Z10">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA10">
         <v>60</v>
@@ -3041,7 +3041,7 @@
         <v>13</v>
       </c>
       <c r="AD10">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE10">
         <v>32</v>
@@ -3062,34 +3062,34 @@
         <v>29</v>
       </c>
       <c r="AK10">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL10">
         <v>23</v>
       </c>
       <c r="AM10">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AN10">
         <v>7.2</v>
       </c>
       <c r="AO10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP10">
-        <v>18.5</v>
+        <v>29</v>
       </c>
       <c r="AQ10">
-        <v>16.5</v>
+        <v>25</v>
       </c>
       <c r="AR10">
-        <v>15.5</v>
+        <v>30</v>
       </c>
       <c r="AS10">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AT10">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU10">
         <v>10.5</v>
@@ -3098,7 +3098,7 @@
         <v>14</v>
       </c>
       <c r="AW10">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AX10">
         <v>17.5</v>
@@ -3110,7 +3110,7 @@
         <v>12</v>
       </c>
       <c r="BA10">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="BB10">
         <v>23</v>
@@ -3122,10 +3122,10 @@
         <v>18.5</v>
       </c>
       <c r="BE10">
-        <v>17.5</v>
+        <v>32</v>
       </c>
       <c r="BF10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BG10">
         <v>12</v>
@@ -3134,58 +3134,58 @@
         <v>5.9</v>
       </c>
       <c r="BI10">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="BJ10">
         <v>8.4</v>
       </c>
       <c r="BK10">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="BL10">
         <v>55</v>
       </c>
       <c r="BM10">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN10">
         <v>6.2</v>
       </c>
       <c r="BO10">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BP10">
         <v>13.5</v>
       </c>
       <c r="BQ10">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BR10">
         <v>18.5</v>
       </c>
       <c r="BS10">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BT10">
         <v>8</v>
       </c>
       <c r="BU10">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BV10">
         <v>22</v>
       </c>
       <c r="BW10">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX10">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BY10">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BZ10">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CA10">
         <v>5.2</v>
@@ -3211,172 +3211,172 @@
         <v>130</v>
       </c>
       <c r="F11">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="G11">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="H11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I11">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="J11">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K11">
         <v>3.95</v>
       </c>
       <c r="L11">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="M11">
         <v>1.05</v>
       </c>
       <c r="N11">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O11">
         <v>1.22</v>
       </c>
       <c r="P11">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q11">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S11">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T11">
         <v>1.58</v>
       </c>
       <c r="U11">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="V11">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W11">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y11">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z11">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AA11">
         <v>60</v>
       </c>
       <c r="AB11">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC11">
         <v>8.800000000000001</v>
       </c>
       <c r="AD11">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE11">
         <v>40</v>
       </c>
       <c r="AF11">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH11">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AI11">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AK11">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AL11">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM11">
         <v>80</v>
       </c>
       <c r="AN11">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AO11">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AP11">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AQ11">
         <v>14.5</v>
       </c>
       <c r="AR11">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AS11">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AT11">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AU11">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV11">
         <v>11.5</v>
       </c>
       <c r="AW11">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AX11">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AY11">
         <v>10.5</v>
       </c>
       <c r="AZ11">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BB11">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC11">
         <v>20</v>
       </c>
       <c r="BD11">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BE11">
         <v>46</v>
       </c>
       <c r="BF11">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BG11">
-        <v>14</v>
+        <v>19.5</v>
       </c>
       <c r="BH11">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BI11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
         <v>8.6</v>
@@ -3391,13 +3391,13 @@
         <v>13.5</v>
       </c>
       <c r="BN11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO11">
         <v>5</v>
       </c>
       <c r="BP11">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BQ11">
         <v>8.199999999999999</v>
@@ -3406,31 +3406,31 @@
         <v>25</v>
       </c>
       <c r="BS11">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BT11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU11">
         <v>5.7</v>
       </c>
       <c r="BV11">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY11">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ11">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="CA11">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="CB11" t="s">
         <v>141</v>
@@ -3453,19 +3453,19 @@
         <v>131</v>
       </c>
       <c r="F12">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="H12">
+        <v>2.8</v>
+      </c>
+      <c r="I12">
         <v>2.96</v>
       </c>
-      <c r="I12">
-        <v>3.15</v>
-      </c>
       <c r="J12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K12">
         <v>5</v>
@@ -3477,25 +3477,25 @@
         <v>1.02</v>
       </c>
       <c r="N12">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="O12">
         <v>1.09</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
         <v>1.3</v>
       </c>
       <c r="R12">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S12">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="T12">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="U12">
         <v>3.4</v>
@@ -3507,28 +3507,28 @@
         <v>1.01</v>
       </c>
       <c r="X12">
-        <v>150</v>
+        <v>55</v>
       </c>
       <c r="Y12">
+        <v>42</v>
+      </c>
+      <c r="Z12">
         <v>44</v>
-      </c>
-      <c r="Z12">
-        <v>48</v>
       </c>
       <c r="AA12">
         <v>60</v>
       </c>
       <c r="AB12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AC12">
         <v>14</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>34</v>
@@ -3540,25 +3540,25 @@
         <v>14.5</v>
       </c>
       <c r="AI12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AJ12">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AK12">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL12">
         <v>22</v>
       </c>
       <c r="AM12">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AN12">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AP12">
         <v>22</v>
@@ -3570,22 +3570,22 @@
         <v>27</v>
       </c>
       <c r="AS12">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT12">
         <v>21</v>
       </c>
       <c r="AU12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV12">
         <v>13.5</v>
       </c>
       <c r="AW12">
+        <v>22</v>
+      </c>
+      <c r="AX12">
         <v>21</v>
-      </c>
-      <c r="AX12">
-        <v>20</v>
       </c>
       <c r="AY12">
         <v>11.5</v>
@@ -3594,37 +3594,37 @@
         <v>12</v>
       </c>
       <c r="BA12">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD12">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE12">
         <v>29</v>
       </c>
       <c r="BF12">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG12">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH12">
         <v>6.6</v>
       </c>
       <c r="BI12">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BJ12">
         <v>8</v>
       </c>
       <c r="BK12">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
         <v>6.6</v>
       </c>
       <c r="BO12">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BP12">
         <v>14</v>
@@ -3651,28 +3651,28 @@
         <v>7.6</v>
       </c>
       <c r="BT12">
+        <v>7.6</v>
+      </c>
+      <c r="BU12">
+        <v>6.2</v>
+      </c>
+      <c r="BV12">
+        <v>1000</v>
+      </c>
+      <c r="BW12">
         <v>7.8</v>
       </c>
-      <c r="BU12">
-        <v>6</v>
-      </c>
-      <c r="BV12">
-        <v>1000</v>
-      </c>
-      <c r="BW12">
-        <v>8</v>
-      </c>
       <c r="BX12">
         <v>1000</v>
       </c>
       <c r="BY12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ12">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="CA12">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="CB12" t="s">
         <v>141</v>
@@ -3695,16 +3695,16 @@
         <v>132</v>
       </c>
       <c r="F13">
-        <v>2.36</v>
+        <v>2.54</v>
       </c>
       <c r="G13">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="H13">
-        <v>2.78</v>
+        <v>2.58</v>
       </c>
       <c r="I13">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="J13">
         <v>4.1</v>
@@ -3719,94 +3719,94 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="Q13">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="R13">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="S13">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="U13">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V13">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="X13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="Y13">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z13">
         <v>27</v>
       </c>
       <c r="AA13">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AB13">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AC13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD13">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE13">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG13">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH13">
         <v>14.5</v>
       </c>
       <c r="AI13">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AJ13">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AK13">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL13">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AN13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO13">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP13">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AQ13">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AR13">
         <v>21</v>
@@ -3815,58 +3815,58 @@
         <v>30</v>
       </c>
       <c r="AT13">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AU13">
         <v>9</v>
       </c>
       <c r="AV13">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW13">
         <v>21</v>
       </c>
       <c r="AX13">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY13">
         <v>10.5</v>
       </c>
       <c r="AZ13">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BA13">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB13">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC13">
         <v>19</v>
       </c>
       <c r="BD13">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE13">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BF13">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG13">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH13">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BI13">
         <v>4.2</v>
       </c>
       <c r="BJ13">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BK13">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="BL13">
         <v>65</v>
@@ -3875,37 +3875,37 @@
         <v>10</v>
       </c>
       <c r="BN13">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BO13">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BP13">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BQ13">
-        <v>6.8</v>
+        <v>13</v>
       </c>
       <c r="BR13">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BS13">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT13">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BU13">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="BV13">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BW13">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="BX13">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BY13">
         <v>8</v>
@@ -3937,16 +3937,16 @@
         <v>133</v>
       </c>
       <c r="F14">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G14">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H14">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J14">
         <v>2.9</v>
@@ -3955,55 +3955,55 @@
         <v>2.92</v>
       </c>
       <c r="L14">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="M14">
         <v>1.18</v>
       </c>
       <c r="N14">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O14">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="P14">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Q14">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R14">
         <v>1.14</v>
       </c>
       <c r="S14">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="T14">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V14">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W14">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X14">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Y14">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z14">
         <v>25</v>
       </c>
       <c r="AA14">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC14">
         <v>7</v>
@@ -4018,40 +4018,40 @@
         <v>13</v>
       </c>
       <c r="AG14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI14">
-        <v>190</v>
+        <v>260</v>
       </c>
       <c r="AJ14">
         <v>40</v>
       </c>
       <c r="AK14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL14">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AM14">
         <v>500</v>
       </c>
       <c r="AN14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AO14">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="AP14">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AQ14">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS14">
         <v>60</v>
@@ -4060,25 +4060,25 @@
         <v>6</v>
       </c>
       <c r="AU14">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV14">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW14">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AX14">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BB14">
         <v>34</v>
@@ -4087,52 +4087,52 @@
         <v>36</v>
       </c>
       <c r="BD14">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="BE14">
         <v>110</v>
       </c>
       <c r="BF14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="BG14">
-        <v>90</v>
+        <v>44</v>
       </c>
       <c r="BH14">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BI14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="BJ14">
         <v>12.5</v>
       </c>
       <c r="BK14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>22</v>
+        <v>2.14</v>
       </c>
       <c r="BN14">
         <v>5</v>
       </c>
       <c r="BO14">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP14">
         <v>24</v>
       </c>
       <c r="BQ14">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BR14">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS14">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="BT14">
         <v>6.8</v>
@@ -4141,22 +4141,22 @@
         <v>6</v>
       </c>
       <c r="BV14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BW14">
-        <v>2.06</v>
+        <v>16.5</v>
       </c>
       <c r="BX14">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="BY14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BZ14">
         <v>70</v>
       </c>
       <c r="CA14">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="CB14" t="s">
         <v>141</v>
@@ -4179,34 +4179,34 @@
         <v>134</v>
       </c>
       <c r="F15">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="G15">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I15">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>3.45</v>
       </c>
       <c r="K15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L15">
         <v>1.48</v>
       </c>
       <c r="M15">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N15">
         <v>3.05</v>
       </c>
       <c r="O15">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P15">
         <v>1.7</v>
@@ -4221,13 +4221,13 @@
         <v>4.3</v>
       </c>
       <c r="T15">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="U15">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="V15">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
         <v>2.2</v>
@@ -4236,10 +4236,10 @@
         <v>11.5</v>
       </c>
       <c r="Y15">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z15">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AA15">
         <v>900</v>
@@ -4251,7 +4251,7 @@
         <v>8.6</v>
       </c>
       <c r="AD15">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AE15">
         <v>700</v>
@@ -4260,10 +4260,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH15">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AI15">
         <v>700</v>
@@ -4272,55 +4272,55 @@
         <v>19</v>
       </c>
       <c r="AK15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL15">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AM15">
         <v>580</v>
       </c>
       <c r="AN15">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO15">
         <v>210</v>
       </c>
       <c r="AP15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AQ15">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR15">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AS15">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AT15">
         <v>5.9</v>
       </c>
       <c r="AU15">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV15">
         <v>20</v>
       </c>
       <c r="AW15">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX15">
         <v>8</v>
       </c>
       <c r="AY15">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA15">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15">
         <v>15</v>
@@ -4329,46 +4329,46 @@
         <v>18.5</v>
       </c>
       <c r="BD15">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BE15">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF15">
         <v>12.5</v>
       </c>
       <c r="BG15">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BH15">
         <v>3.15</v>
       </c>
       <c r="BI15">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15">
         <v>12.5</v>
       </c>
       <c r="BK15">
-        <v>5.7</v>
+        <v>9.6</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN15">
         <v>4.2</v>
       </c>
       <c r="BO15">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="BP15">
         <v>12.5</v>
       </c>
       <c r="BQ15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BR15">
         <v>1000</v>
@@ -4380,25 +4380,25 @@
         <v>10</v>
       </c>
       <c r="BU15">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BV15">
         <v>1000</v>
       </c>
       <c r="BW15">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX15">
         <v>1000</v>
       </c>
       <c r="BY15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ15">
         <v>1000</v>
       </c>
       <c r="CA15">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB15" t="s">
         <v>141</v>
@@ -4421,28 +4421,28 @@
         <v>135</v>
       </c>
       <c r="F16">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="G16">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="H16">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="I16">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="J16">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="L16">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N16">
         <v>3.35</v>
@@ -4451,52 +4451,52 @@
         <v>1.38</v>
       </c>
       <c r="P16">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S16">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T16">
         <v>1.83</v>
       </c>
       <c r="U16">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V16">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="W16">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="X16">
+        <v>12</v>
+      </c>
+      <c r="Y16">
+        <v>8.6</v>
+      </c>
+      <c r="Z16">
+        <v>14</v>
+      </c>
+      <c r="AA16">
+        <v>34</v>
+      </c>
+      <c r="AB16">
+        <v>14</v>
+      </c>
+      <c r="AC16">
+        <v>7.6</v>
+      </c>
+      <c r="AD16">
         <v>11</v>
       </c>
-      <c r="Y16">
-        <v>9.6</v>
-      </c>
-      <c r="Z16">
-        <v>16</v>
-      </c>
-      <c r="AA16">
-        <v>38</v>
-      </c>
-      <c r="AB16">
-        <v>13.5</v>
-      </c>
-      <c r="AC16">
-        <v>7</v>
-      </c>
-      <c r="AD16">
-        <v>12</v>
-      </c>
       <c r="AE16">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AF16">
         <v>26</v>
@@ -4505,142 +4505,142 @@
         <v>16.5</v>
       </c>
       <c r="AH16">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI16">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AJ16">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AK16">
+        <v>55</v>
+      </c>
+      <c r="AL16">
         <v>65</v>
       </c>
-      <c r="AL16">
-        <v>90</v>
-      </c>
       <c r="AM16">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AN16">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO16">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AP16">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AR16">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AS16">
-        <v>17.5</v>
+        <v>27</v>
       </c>
       <c r="AT16">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV16">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW16">
         <v>22</v>
       </c>
       <c r="AX16">
+        <v>22</v>
+      </c>
+      <c r="AY16">
+        <v>14.5</v>
+      </c>
+      <c r="AZ16">
+        <v>17</v>
+      </c>
+      <c r="BA16">
+        <v>36</v>
+      </c>
+      <c r="BB16">
+        <v>30</v>
+      </c>
+      <c r="BC16">
+        <v>42</v>
+      </c>
+      <c r="BD16">
+        <v>32</v>
+      </c>
+      <c r="BE16">
+        <v>28</v>
+      </c>
+      <c r="BF16">
+        <v>12.5</v>
+      </c>
+      <c r="BG16">
         <v>20</v>
       </c>
-      <c r="AY16">
-        <v>13</v>
-      </c>
-      <c r="AZ16">
-        <v>14.5</v>
-      </c>
-      <c r="BA16">
-        <v>25</v>
-      </c>
-      <c r="BB16">
-        <v>20</v>
-      </c>
-      <c r="BC16">
-        <v>32</v>
-      </c>
-      <c r="BD16">
+      <c r="BH16">
+        <v>3.2</v>
+      </c>
+      <c r="BI16">
+        <v>2.86</v>
+      </c>
+      <c r="BJ16">
+        <v>10</v>
+      </c>
+      <c r="BK16">
+        <v>6</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>12.5</v>
+      </c>
+      <c r="BN16">
+        <v>6.6</v>
+      </c>
+      <c r="BO16">
+        <v>5.7</v>
+      </c>
+      <c r="BP16">
+        <v>30</v>
+      </c>
+      <c r="BQ16">
         <v>9.4</v>
-      </c>
-      <c r="BE16">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF16">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG16">
-        <v>7.8</v>
-      </c>
-      <c r="BH16">
-        <v>3.15</v>
-      </c>
-      <c r="BI16">
-        <v>2.8</v>
-      </c>
-      <c r="BJ16">
-        <v>10.5</v>
-      </c>
-      <c r="BK16">
-        <v>8.6</v>
-      </c>
-      <c r="BL16">
-        <v>1000</v>
-      </c>
-      <c r="BM16">
-        <v>11.5</v>
-      </c>
-      <c r="BN16">
-        <v>6.4</v>
-      </c>
-      <c r="BO16">
-        <v>5.5</v>
-      </c>
-      <c r="BP16">
-        <v>28</v>
-      </c>
-      <c r="BQ16">
-        <v>8.6</v>
       </c>
       <c r="BR16">
         <v>44</v>
       </c>
       <c r="BS16">
+        <v>10.5</v>
+      </c>
+      <c r="BT16">
+        <v>5.2</v>
+      </c>
+      <c r="BU16">
+        <v>4.5</v>
+      </c>
+      <c r="BV16">
+        <v>19</v>
+      </c>
+      <c r="BW16">
+        <v>8</v>
+      </c>
+      <c r="BX16">
+        <v>36</v>
+      </c>
+      <c r="BY16">
+        <v>10</v>
+      </c>
+      <c r="BZ16">
+        <v>34</v>
+      </c>
+      <c r="CA16">
         <v>9.800000000000001</v>
-      </c>
-      <c r="BT16">
-        <v>5.4</v>
-      </c>
-      <c r="BU16">
-        <v>4.7</v>
-      </c>
-      <c r="BV16">
-        <v>21</v>
-      </c>
-      <c r="BW16">
-        <v>7.8</v>
-      </c>
-      <c r="BX16">
-        <v>38</v>
-      </c>
-      <c r="BY16">
-        <v>9.4</v>
-      </c>
-      <c r="BZ16">
-        <v>36</v>
-      </c>
-      <c r="CA16">
-        <v>9.199999999999999</v>
       </c>
       <c r="CB16" t="s">
         <v>141</v>
@@ -4663,22 +4663,22 @@
         <v>136</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G17">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="H17">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="I17">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="J17">
+        <v>3.2</v>
+      </c>
+      <c r="K17">
         <v>3.25</v>
-      </c>
-      <c r="K17">
-        <v>3.35</v>
       </c>
       <c r="L17">
         <v>1.61</v>
@@ -4696,7 +4696,7 @@
         <v>1.56</v>
       </c>
       <c r="Q17">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="R17">
         <v>1.19</v>
@@ -4705,115 +4705,115 @@
         <v>5.8</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U17">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="W17">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="X17">
         <v>8.4</v>
       </c>
       <c r="Y17">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="Z17">
         <v>10.5</v>
       </c>
       <c r="AA17">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AB17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC17">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD17">
         <v>11.5</v>
       </c>
       <c r="AE17">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AF17">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AG17">
         <v>21</v>
       </c>
       <c r="AH17">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI17">
         <v>65</v>
       </c>
       <c r="AJ17">
+        <v>120</v>
+      </c>
+      <c r="AK17">
+        <v>85</v>
+      </c>
+      <c r="AL17">
+        <v>110</v>
+      </c>
+      <c r="AM17">
+        <v>220</v>
+      </c>
+      <c r="AN17">
         <v>140</v>
       </c>
-      <c r="AK17">
-        <v>95</v>
-      </c>
-      <c r="AL17">
-        <v>130</v>
-      </c>
-      <c r="AM17">
-        <v>500</v>
-      </c>
-      <c r="AN17">
-        <v>190</v>
-      </c>
       <c r="AO17">
+        <v>28</v>
+      </c>
+      <c r="AP17">
+        <v>8</v>
+      </c>
+      <c r="AQ17">
+        <v>6.2</v>
+      </c>
+      <c r="AR17">
+        <v>10</v>
+      </c>
+      <c r="AS17">
         <v>24</v>
       </c>
-      <c r="AP17">
-        <v>7.8</v>
-      </c>
-      <c r="AQ17">
-        <v>6</v>
-      </c>
-      <c r="AR17">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS17">
-        <v>21</v>
-      </c>
       <c r="AT17">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV17">
         <v>10.5</v>
       </c>
       <c r="AW17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX17">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AY17">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AZ17">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA17">
         <v>55</v>
       </c>
       <c r="BB17">
-        <v>28</v>
+        <v>95</v>
       </c>
       <c r="BC17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BD17">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="BE17">
         <v>36</v>
@@ -4822,67 +4822,67 @@
         <v>110</v>
       </c>
       <c r="BG17">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BH17">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="BI17">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="BJ17">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK17">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BL17">
         <v>1000</v>
       </c>
       <c r="BM17">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="BN17">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BO17">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BP17">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="BQ17">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BR17">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BS17">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="BT17">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BU17">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BV17">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BW17">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BX17">
         <v>42</v>
       </c>
       <c r="BY17">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BZ17">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="CA17">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="CB17" t="s">
         <v>141</v>
@@ -4905,22 +4905,22 @@
         <v>137</v>
       </c>
       <c r="F18">
+        <v>1.74</v>
+      </c>
+      <c r="G18">
         <v>1.75</v>
       </c>
-      <c r="G18">
-        <v>1.76</v>
-      </c>
       <c r="H18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I18">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J18">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K18">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>1.42</v>
@@ -4932,31 +4932,31 @@
         <v>3.9</v>
       </c>
       <c r="O18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P18">
         <v>2</v>
       </c>
       <c r="Q18">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S18">
         <v>3.55</v>
       </c>
       <c r="T18">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U18">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
         <v>1.21</v>
       </c>
       <c r="W18">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X18">
         <v>14.5</v>
@@ -4965,13 +4965,13 @@
         <v>18.5</v>
       </c>
       <c r="Z18">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA18">
         <v>140</v>
       </c>
       <c r="AB18">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC18">
         <v>8.800000000000001</v>
@@ -4995,7 +4995,7 @@
         <v>80</v>
       </c>
       <c r="AJ18">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK18">
         <v>18.5</v>
@@ -5010,7 +5010,7 @@
         <v>11</v>
       </c>
       <c r="AO18">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP18">
         <v>13</v>
@@ -5025,10 +5025,10 @@
         <v>120</v>
       </c>
       <c r="AT18">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU18">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV18">
         <v>19.5</v>
@@ -5040,7 +5040,7 @@
         <v>9.6</v>
       </c>
       <c r="AY18">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ18">
         <v>19.5</v>
@@ -5058,7 +5058,7 @@
         <v>34</v>
       </c>
       <c r="BE18">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="BF18">
         <v>10</v>
@@ -5067,22 +5067,22 @@
         <v>75</v>
       </c>
       <c r="BH18">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI18">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BJ18">
         <v>10.5</v>
       </c>
       <c r="BK18">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BL18">
         <v>130</v>
       </c>
       <c r="BM18">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BN18">
         <v>4.2</v>
@@ -5094,13 +5094,13 @@
         <v>11.5</v>
       </c>
       <c r="BQ18">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BR18">
         <v>27</v>
       </c>
       <c r="BS18">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BT18">
         <v>8.800000000000001</v>
@@ -5112,19 +5112,19 @@
         <v>48</v>
       </c>
       <c r="BW18">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BX18">
         <v>55</v>
       </c>
       <c r="BY18">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="BZ18">
         <v>21</v>
       </c>
       <c r="CA18">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="CB18" t="s">
         <v>141</v>
@@ -5147,22 +5147,22 @@
         <v>138</v>
       </c>
       <c r="F19">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G19">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H19">
+        <v>2.08</v>
+      </c>
+      <c r="I19">
         <v>2.1</v>
       </c>
-      <c r="I19">
-        <v>2.12</v>
-      </c>
       <c r="J19">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K19">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L19">
         <v>1.44</v>
@@ -5177,28 +5177,28 @@
         <v>1.35</v>
       </c>
       <c r="P19">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q19">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R19">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S19">
         <v>3.75</v>
       </c>
       <c r="T19">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V19">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W19">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X19">
         <v>13</v>
@@ -5210,13 +5210,13 @@
         <v>13</v>
       </c>
       <c r="AA19">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB19">
         <v>14</v>
       </c>
       <c r="AC19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19">
         <v>9.800000000000001</v>
@@ -5237,10 +5237,10 @@
         <v>40</v>
       </c>
       <c r="AJ19">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK19">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AL19">
         <v>60</v>
@@ -5252,7 +5252,7 @@
         <v>55</v>
       </c>
       <c r="AO19">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP19">
         <v>12</v>
@@ -5264,13 +5264,13 @@
         <v>12</v>
       </c>
       <c r="AS19">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT19">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU19">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV19">
         <v>9.6</v>
@@ -5279,7 +5279,7 @@
         <v>21</v>
       </c>
       <c r="AX19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY19">
         <v>15</v>
@@ -5291,16 +5291,16 @@
         <v>36</v>
       </c>
       <c r="BB19">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BC19">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD19">
         <v>50</v>
       </c>
       <c r="BE19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="BF19">
         <v>50</v>
@@ -5324,10 +5324,10 @@
         <v>130</v>
       </c>
       <c r="BM19">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="BN19">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BO19">
         <v>6.4</v>
@@ -5336,13 +5336,13 @@
         <v>34</v>
       </c>
       <c r="BQ19">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BR19">
         <v>44</v>
       </c>
       <c r="BS19">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="BT19">
         <v>4.7</v>
@@ -5354,19 +5354,19 @@
         <v>15</v>
       </c>
       <c r="BW19">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BX19">
         <v>30</v>
       </c>
       <c r="BY19">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BZ19">
         <v>27</v>
       </c>
       <c r="CA19">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="CB19" t="s">
         <v>141</v>
@@ -5389,22 +5389,22 @@
         <v>139</v>
       </c>
       <c r="F20">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G20">
         <v>1.95</v>
       </c>
       <c r="H20">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I20">
         <v>5.1</v>
       </c>
       <c r="J20">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K20">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L20">
         <v>1.53</v>
@@ -5416,16 +5416,16 @@
         <v>3.05</v>
       </c>
       <c r="O20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P20">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q20">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="R20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
         <v>4.7</v>
@@ -5443,7 +5443,7 @@
         <v>2.04</v>
       </c>
       <c r="X20">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y20">
         <v>15</v>
@@ -5461,10 +5461,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE20">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF20">
         <v>10.5</v>
@@ -5476,25 +5476,25 @@
         <v>26</v>
       </c>
       <c r="AI20">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AJ20">
         <v>24</v>
       </c>
       <c r="AK20">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL20">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM20">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN20">
         <v>21</v>
       </c>
       <c r="AO20">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP20">
         <v>10</v>
@@ -5506,7 +5506,7 @@
         <v>30</v>
       </c>
       <c r="AS20">
-        <v>90</v>
+        <v>12.5</v>
       </c>
       <c r="AT20">
         <v>6.6</v>
@@ -5518,7 +5518,7 @@
         <v>17</v>
       </c>
       <c r="AW20">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AX20">
         <v>9.6</v>
@@ -5542,19 +5542,19 @@
         <v>42</v>
       </c>
       <c r="BE20">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BF20">
         <v>17.5</v>
       </c>
       <c r="BG20">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BH20">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="BI20">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="BJ20">
         <v>11.5</v>
@@ -5566,49 +5566,49 @@
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>2.46</v>
+        <v>17.5</v>
       </c>
       <c r="BN20">
         <v>4.3</v>
       </c>
       <c r="BO20">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="BP20">
         <v>15</v>
       </c>
       <c r="BQ20">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BR20">
         <v>38</v>
       </c>
       <c r="BS20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT20">
         <v>8.199999999999999</v>
       </c>
       <c r="BU20">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV20">
         <v>55</v>
       </c>
       <c r="BW20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BX20">
         <v>1000</v>
       </c>
       <c r="BY20">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BZ20">
         <v>1000</v>
       </c>
       <c r="CA20">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CB20" t="s">
         <v>141</v>
@@ -5631,7 +5631,7 @@
         <v>140</v>
       </c>
       <c r="F21">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G21">
         <v>1.46</v>
@@ -5640,13 +5640,13 @@
         <v>7.8</v>
       </c>
       <c r="I21">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J21">
         <v>5.3</v>
       </c>
       <c r="K21">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -5655,28 +5655,28 @@
         <v>1.03</v>
       </c>
       <c r="N21">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="O21">
         <v>1.18</v>
       </c>
       <c r="P21">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q21">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S21">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T21">
         <v>1.77</v>
       </c>
       <c r="U21">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V21">
         <v>1.13</v>
@@ -5718,7 +5718,7 @@
         <v>23</v>
       </c>
       <c r="AI21">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AJ21">
         <v>14</v>
@@ -5781,7 +5781,7 @@
         <v>12</v>
       </c>
       <c r="BD21">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BE21">
         <v>11</v>
